--- a/CLB07N.xlsx
+++ b/CLB07N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2124" uniqueCount="766">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2118" uniqueCount="765">
   <si>
     <t/>
   </si>
@@ -967,12 +967,6 @@
     <t>FRESTEA TEH APEL 500</t>
   </si>
   <si>
-    <t>20072802</t>
-  </si>
-  <si>
-    <t>FRSTEA TEH MRKSA 350</t>
-  </si>
-  <si>
     <t>20138841</t>
   </si>
   <si>
@@ -2296,13 +2290,16 @@
     <t>IDM AIR MN 8+ BTL500</t>
   </si>
   <si>
+    <t>RT,(E-15H)</t>
+  </si>
+  <si>
+    <t>20052629</t>
+  </si>
+  <si>
+    <t>IDM AIR DGN OKSGN600</t>
+  </si>
+  <si>
     <t>PT,(E-15H)</t>
-  </si>
-  <si>
-    <t>20052629</t>
-  </si>
-  <si>
-    <t>IDM AIR DGN OKSGN600</t>
   </si>
   <si>
     <t>20005529</t>
@@ -2701,7 +2698,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F354"/>
+  <dimension ref="A1:F353"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -5625,10 +5622,10 @@
         <v>307</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
@@ -5642,10 +5639,10 @@
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>307</v>
+        <v>322</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>23</v>
@@ -5653,19 +5650,19 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D148" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="B148" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="C148" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D148" s="1" t="s">
-        <v>324</v>
-      </c>
       <c r="E148" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>23</v>
@@ -5682,10 +5679,10 @@
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>23</v>
@@ -5702,10 +5699,10 @@
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>23</v>
@@ -5722,10 +5719,10 @@
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>23</v>
@@ -5742,13 +5739,13 @@
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
@@ -5762,13 +5759,13 @@
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
@@ -5782,13 +5779,13 @@
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
@@ -5802,10 +5799,10 @@
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>40</v>
+        <v>126</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>28</v>
@@ -5822,30 +5819,30 @@
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>324</v>
+        <v>341</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>126</v>
+        <v>4</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="B157" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="C157" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D157" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="B157" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="C157" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D157" s="1" t="s">
-        <v>343</v>
-      </c>
       <c r="E157" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>23</v>
@@ -5862,13 +5859,13 @@
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
@@ -5882,13 +5879,13 @@
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
@@ -5902,10 +5899,10 @@
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>23</v>
@@ -5922,10 +5919,10 @@
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>23</v>
@@ -5942,10 +5939,10 @@
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>23</v>
@@ -5962,10 +5959,10 @@
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F163" s="1" t="s">
         <v>23</v>
@@ -5982,10 +5979,10 @@
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>343</v>
+        <v>358</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>23</v>
@@ -5993,19 +5990,19 @@
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="B165" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D165" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="B165" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="C165" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D165" s="1" t="s">
-        <v>360</v>
-      </c>
       <c r="E165" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>23</v>
@@ -6022,10 +6019,10 @@
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>23</v>
@@ -6042,10 +6039,10 @@
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>23</v>
@@ -6062,10 +6059,10 @@
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>23</v>
@@ -6082,10 +6079,10 @@
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>23</v>
@@ -6102,10 +6099,10 @@
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="F170" s="1" t="s">
         <v>23</v>
@@ -6122,13 +6119,13 @@
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
@@ -6142,10 +6139,10 @@
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>40</v>
+        <v>126</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>5</v>
@@ -6162,33 +6159,33 @@
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>360</v>
+        <v>377</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>126</v>
+        <v>4</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>5</v>
+        <v>70</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="B174" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="C174" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D174" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="B174" s="1" t="s">
-        <v>378</v>
-      </c>
-      <c r="C174" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D174" s="1" t="s">
-        <v>379</v>
-      </c>
       <c r="E174" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>70</v>
+        <v>23</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
@@ -6202,10 +6199,10 @@
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>23</v>
@@ -6222,13 +6219,13 @@
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>23</v>
+        <v>67</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
@@ -6242,10 +6239,10 @@
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F177" s="1" t="s">
         <v>67</v>
@@ -6262,13 +6259,13 @@
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>67</v>
+        <v>23</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
@@ -6282,13 +6279,13 @@
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>23</v>
+        <v>70</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
@@ -6302,10 +6299,10 @@
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>70</v>
@@ -6322,13 +6319,13 @@
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>40</v>
+        <v>126</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>70</v>
+        <v>23</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
@@ -6342,10 +6339,10 @@
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>23</v>
@@ -6362,10 +6359,10 @@
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>379</v>
+        <v>398</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>145</v>
+        <v>4</v>
       </c>
       <c r="F183" s="1" t="s">
         <v>23</v>
@@ -6373,22 +6370,22 @@
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="B184" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="C184" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D184" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="B184" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="C184" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D184" s="1" t="s">
-        <v>400</v>
-      </c>
       <c r="E184" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
@@ -6402,13 +6399,13 @@
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>28</v>
+        <v>70</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
@@ -6422,13 +6419,13 @@
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
@@ -6442,13 +6439,13 @@
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>81</v>
+        <v>23</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
@@ -6462,13 +6459,13 @@
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
@@ -6482,10 +6479,10 @@
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="F189" s="1" t="s">
         <v>28</v>
@@ -6502,13 +6499,13 @@
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
@@ -6522,10 +6519,10 @@
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>40</v>
+        <v>126</v>
       </c>
       <c r="F191" s="1" t="s">
         <v>23</v>
@@ -6542,10 +6539,10 @@
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>400</v>
+        <v>417</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>126</v>
+        <v>4</v>
       </c>
       <c r="F192" s="1" t="s">
         <v>23</v>
@@ -6553,19 +6550,19 @@
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="B193" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="C193" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D193" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="B193" s="1" t="s">
-        <v>418</v>
-      </c>
-      <c r="C193" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D193" s="1" t="s">
-        <v>419</v>
-      </c>
       <c r="E193" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F193" s="1" t="s">
         <v>23</v>
@@ -6582,10 +6579,10 @@
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F194" s="1" t="s">
         <v>23</v>
@@ -6602,10 +6599,10 @@
         <v>3</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>23</v>
@@ -6622,10 +6619,10 @@
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F196" s="1" t="s">
         <v>23</v>
@@ -6642,13 +6639,13 @@
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>23</v>
+        <v>163</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
@@ -6662,10 +6659,10 @@
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="F198" s="1" t="s">
         <v>163</v>
@@ -6682,13 +6679,13 @@
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F199" s="1" t="s">
-        <v>163</v>
+        <v>23</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
@@ -6702,10 +6699,10 @@
         <v>3</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>40</v>
+        <v>126</v>
       </c>
       <c r="F200" s="1" t="s">
         <v>23</v>
@@ -6722,10 +6719,10 @@
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="F201" s="1" t="s">
         <v>23</v>
@@ -6742,30 +6739,30 @@
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>419</v>
+        <v>438</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>145</v>
+        <v>4</v>
       </c>
       <c r="F202" s="1" t="s">
-        <v>23</v>
+        <v>70</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="B203" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="C203" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D203" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="B203" s="1" t="s">
-        <v>439</v>
-      </c>
-      <c r="C203" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D203" s="1" t="s">
-        <v>440</v>
-      </c>
       <c r="E203" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F203" s="1" t="s">
         <v>70</v>
@@ -6782,10 +6779,10 @@
         <v>3</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F204" s="1" t="s">
         <v>70</v>
@@ -6802,10 +6799,10 @@
         <v>3</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F205" s="1" t="s">
         <v>70</v>
@@ -6822,10 +6819,10 @@
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F206" s="1" t="s">
         <v>70</v>
@@ -6842,10 +6839,10 @@
         <v>3</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F207" s="1" t="s">
         <v>70</v>
@@ -6862,13 +6859,13 @@
         <v>3</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="F208" s="1" t="s">
-        <v>70</v>
+        <v>23</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
@@ -6882,10 +6879,10 @@
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F209" s="1" t="s">
         <v>23</v>
@@ -6902,10 +6899,10 @@
         <v>3</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>40</v>
+        <v>126</v>
       </c>
       <c r="F210" s="1" t="s">
         <v>23</v>
@@ -6922,33 +6919,33 @@
         <v>3</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>440</v>
+        <v>457</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>126</v>
+        <v>4</v>
       </c>
       <c r="F211" s="1" t="s">
-        <v>23</v>
+        <v>70</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="B212" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="C212" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D212" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="B212" s="1" t="s">
-        <v>458</v>
-      </c>
-      <c r="C212" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D212" s="1" t="s">
-        <v>459</v>
-      </c>
       <c r="E212" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F212" s="1" t="s">
-        <v>70</v>
+        <v>23</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
@@ -6962,13 +6959,13 @@
         <v>3</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
@@ -6982,10 +6979,10 @@
         <v>3</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F214" s="1" t="s">
         <v>5</v>
@@ -7002,13 +6999,13 @@
         <v>3</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F215" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
@@ -7022,10 +7019,10 @@
         <v>3</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F216" s="1" t="s">
         <v>23</v>
@@ -7042,10 +7039,10 @@
         <v>3</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="F217" s="1" t="s">
         <v>23</v>
@@ -7062,10 +7059,10 @@
         <v>3</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F218" s="1" t="s">
         <v>23</v>
@@ -7082,13 +7079,13 @@
         <v>3</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>40</v>
+        <v>126</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>23</v>
+        <v>70</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
@@ -7102,13 +7099,13 @@
         <v>3</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>70</v>
+        <v>23</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
@@ -7122,10 +7119,10 @@
         <v>3</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>459</v>
+        <v>478</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>145</v>
+        <v>4</v>
       </c>
       <c r="F221" s="1" t="s">
         <v>23</v>
@@ -7133,19 +7130,19 @@
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="B222" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="C222" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D222" s="1" t="s">
         <v>478</v>
       </c>
-      <c r="B222" s="1" t="s">
-        <v>479</v>
-      </c>
-      <c r="C222" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D222" s="1" t="s">
-        <v>480</v>
-      </c>
       <c r="E222" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F222" s="1" t="s">
         <v>23</v>
@@ -7162,10 +7159,10 @@
         <v>3</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F223" s="1" t="s">
         <v>23</v>
@@ -7182,10 +7179,10 @@
         <v>3</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F224" s="1" t="s">
         <v>23</v>
@@ -7202,10 +7199,10 @@
         <v>3</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F225" s="1" t="s">
         <v>23</v>
@@ -7222,10 +7219,10 @@
         <v>3</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F226" s="1" t="s">
         <v>23</v>
@@ -7242,13 +7239,13 @@
         <v>3</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
@@ -7262,10 +7259,10 @@
         <v>3</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F228" s="1" t="s">
         <v>28</v>
@@ -7282,10 +7279,10 @@
         <v>3</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>480</v>
+        <v>495</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="F229" s="1" t="s">
         <v>28</v>
@@ -7293,19 +7290,19 @@
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="B230" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="C230" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D230" s="1" t="s">
         <v>495</v>
       </c>
-      <c r="B230" s="1" t="s">
-        <v>496</v>
-      </c>
-      <c r="C230" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D230" s="1" t="s">
-        <v>497</v>
-      </c>
       <c r="E230" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F230" s="1" t="s">
         <v>28</v>
@@ -7322,10 +7319,10 @@
         <v>3</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F231" s="1" t="s">
         <v>28</v>
@@ -7342,13 +7339,13 @@
         <v>3</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F232" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
@@ -7362,10 +7359,10 @@
         <v>3</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F233" s="1" t="s">
         <v>23</v>
@@ -7382,13 +7379,13 @@
         <v>3</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F234" s="1" t="s">
-        <v>23</v>
+        <v>163</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
@@ -7402,10 +7399,10 @@
         <v>3</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="F235" s="1" t="s">
         <v>163</v>
@@ -7422,30 +7419,30 @@
         <v>3</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>497</v>
+        <v>510</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="F236" s="1" t="s">
-        <v>163</v>
+        <v>28</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="B237" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="C237" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D237" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="B237" s="1" t="s">
-        <v>511</v>
-      </c>
-      <c r="C237" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D237" s="1" t="s">
-        <v>512</v>
-      </c>
       <c r="E237" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F237" s="1" t="s">
         <v>28</v>
@@ -7462,10 +7459,10 @@
         <v>3</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="E238" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F238" s="1" t="s">
         <v>28</v>
@@ -7482,10 +7479,10 @@
         <v>3</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="E239" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F239" s="1" t="s">
         <v>28</v>
@@ -7502,10 +7499,10 @@
         <v>3</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="E240" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F240" s="1" t="s">
         <v>28</v>
@@ -7522,13 +7519,13 @@
         <v>3</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="E241" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F241" s="1" t="s">
-        <v>28</v>
+        <v>163</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
@@ -7542,10 +7539,10 @@
         <v>3</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="E242" s="1" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="F242" s="1" t="s">
         <v>163</v>
@@ -7562,33 +7559,33 @@
         <v>3</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="E243" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F243" s="1" t="s">
-        <v>163</v>
+        <v>525</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C244" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="E244" s="1" t="s">
-        <v>40</v>
+        <v>126</v>
       </c>
       <c r="F244" s="1" t="s">
-        <v>527</v>
+        <v>70</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
@@ -7602,30 +7599,30 @@
         <v>3</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>512</v>
+        <v>530</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>126</v>
+        <v>4</v>
       </c>
       <c r="F245" s="1" t="s">
-        <v>70</v>
+        <v>23</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="B246" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="C246" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D246" s="1" t="s">
         <v>530</v>
       </c>
-      <c r="B246" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="C246" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D246" s="1" t="s">
-        <v>532</v>
-      </c>
       <c r="E246" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F246" s="1" t="s">
         <v>23</v>
@@ -7642,10 +7639,10 @@
         <v>3</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F247" s="1" t="s">
         <v>23</v>
@@ -7662,10 +7659,10 @@
         <v>3</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F248" s="1" t="s">
         <v>23</v>
@@ -7682,13 +7679,13 @@
         <v>3</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F249" s="1" t="s">
-        <v>23</v>
+        <v>70</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
@@ -7702,13 +7699,13 @@
         <v>3</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="E250" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F250" s="1" t="s">
-        <v>70</v>
+        <v>28</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
@@ -7722,10 +7719,10 @@
         <v>3</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="F251" s="1" t="s">
         <v>28</v>
@@ -7742,10 +7739,10 @@
         <v>3</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="E252" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F252" s="1" t="s">
         <v>28</v>
@@ -7762,30 +7759,30 @@
         <v>3</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>532</v>
+        <v>547</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="F253" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="B254" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="C254" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D254" s="1" t="s">
         <v>547</v>
       </c>
-      <c r="B254" s="1" t="s">
-        <v>548</v>
-      </c>
-      <c r="C254" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D254" s="1" t="s">
-        <v>549</v>
-      </c>
       <c r="E254" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F254" s="1" t="s">
         <v>23</v>
@@ -7802,10 +7799,10 @@
         <v>3</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F255" s="1" t="s">
         <v>23</v>
@@ -7822,10 +7819,10 @@
         <v>3</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="E256" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F256" s="1" t="s">
         <v>23</v>
@@ -7842,13 +7839,13 @@
         <v>3</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="E257" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F257" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
@@ -7862,13 +7859,13 @@
         <v>3</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F258" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
@@ -7882,10 +7879,10 @@
         <v>3</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="F259" s="1" t="s">
         <v>23</v>
@@ -7902,10 +7899,10 @@
         <v>3</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F260" s="1" t="s">
         <v>23</v>
@@ -7922,30 +7919,30 @@
         <v>3</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>549</v>
+        <v>564</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="F261" s="1" t="s">
-        <v>23</v>
+        <v>70</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="B262" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="C262" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D262" s="1" t="s">
         <v>564</v>
       </c>
-      <c r="B262" s="1" t="s">
-        <v>565</v>
-      </c>
-      <c r="C262" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D262" s="1" t="s">
-        <v>566</v>
-      </c>
       <c r="E262" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F262" s="1" t="s">
         <v>70</v>
@@ -7953,22 +7950,22 @@
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="B263" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="B263" s="1" t="s">
-        <v>565</v>
-      </c>
       <c r="C263" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="E263" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F263" s="1" t="s">
-        <v>70</v>
+        <v>23</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
@@ -7982,10 +7979,10 @@
         <v>3</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="E264" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F264" s="1" t="s">
         <v>23</v>
@@ -8002,10 +7999,10 @@
         <v>3</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="E265" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F265" s="1" t="s">
         <v>23</v>
@@ -8022,10 +8019,10 @@
         <v>3</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F266" s="1" t="s">
         <v>23</v>
@@ -8042,10 +8039,10 @@
         <v>3</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="E267" s="1" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="F267" s="1" t="s">
         <v>23</v>
@@ -8062,10 +8059,10 @@
         <v>3</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F268" s="1" t="s">
         <v>23</v>
@@ -8082,10 +8079,10 @@
         <v>3</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>40</v>
+        <v>126</v>
       </c>
       <c r="F269" s="1" t="s">
         <v>23</v>
@@ -8102,10 +8099,10 @@
         <v>3</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>566</v>
+        <v>582</v>
       </c>
       <c r="E270" s="1" t="s">
-        <v>126</v>
+        <v>4</v>
       </c>
       <c r="F270" s="1" t="s">
         <v>23</v>
@@ -8113,19 +8110,19 @@
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="B271" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="C271" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D271" s="1" t="s">
         <v>582</v>
       </c>
-      <c r="B271" s="1" t="s">
-        <v>583</v>
-      </c>
-      <c r="C271" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D271" s="1" t="s">
-        <v>584</v>
-      </c>
       <c r="E271" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F271" s="1" t="s">
         <v>23</v>
@@ -8142,10 +8139,10 @@
         <v>3</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="E272" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F272" s="1" t="s">
         <v>23</v>
@@ -8162,10 +8159,10 @@
         <v>3</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F273" s="1" t="s">
         <v>23</v>
@@ -8182,10 +8179,10 @@
         <v>3</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F274" s="1" t="s">
         <v>23</v>
@@ -8202,10 +8199,10 @@
         <v>3</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="E275" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F275" s="1" t="s">
         <v>23</v>
@@ -8222,10 +8219,10 @@
         <v>3</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="E276" s="1" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="F276" s="1" t="s">
         <v>23</v>
@@ -8242,10 +8239,10 @@
         <v>3</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="E277" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F277" s="1" t="s">
         <v>23</v>
@@ -8262,10 +8259,10 @@
         <v>3</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>40</v>
+        <v>126</v>
       </c>
       <c r="F278" s="1" t="s">
         <v>23</v>
@@ -8282,10 +8279,10 @@
         <v>3</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="E279" s="1" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="F279" s="1" t="s">
         <v>23</v>
@@ -8302,10 +8299,10 @@
         <v>3</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="E280" s="1" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="F280" s="1" t="s">
         <v>23</v>
@@ -8322,10 +8319,10 @@
         <v>3</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>584</v>
+        <v>605</v>
       </c>
       <c r="E281" s="1" t="s">
-        <v>162</v>
+        <v>4</v>
       </c>
       <c r="F281" s="1" t="s">
         <v>23</v>
@@ -8333,19 +8330,19 @@
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="B282" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="C282" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D282" s="1" t="s">
         <v>605</v>
       </c>
-      <c r="B282" s="1" t="s">
-        <v>606</v>
-      </c>
-      <c r="C282" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D282" s="1" t="s">
-        <v>607</v>
-      </c>
       <c r="E282" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F282" s="1" t="s">
         <v>23</v>
@@ -8362,10 +8359,10 @@
         <v>3</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E283" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F283" s="1" t="s">
         <v>23</v>
@@ -8382,10 +8379,10 @@
         <v>3</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F284" s="1" t="s">
         <v>23</v>
@@ -8402,10 +8399,10 @@
         <v>3</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E285" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F285" s="1" t="s">
         <v>23</v>
@@ -8422,10 +8419,10 @@
         <v>3</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F286" s="1" t="s">
         <v>23</v>
@@ -8442,33 +8439,33 @@
         <v>3</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="F287" s="1" t="s">
-        <v>23</v>
+        <v>618</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288" s="1" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C288" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F288" s="1" t="s">
-        <v>620</v>
+        <v>23</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
@@ -8482,10 +8479,10 @@
         <v>3</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E289" s="1" t="s">
-        <v>40</v>
+        <v>126</v>
       </c>
       <c r="F289" s="1" t="s">
         <v>23</v>
@@ -8502,10 +8499,10 @@
         <v>3</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E290" s="1" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="F290" s="1" t="s">
         <v>23</v>
@@ -8522,33 +8519,33 @@
         <v>3</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>607</v>
+        <v>627</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>145</v>
+        <v>4</v>
       </c>
       <c r="F291" s="1" t="s">
-        <v>23</v>
+        <v>618</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A292" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="B292" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="C292" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D292" s="1" t="s">
         <v>627</v>
       </c>
-      <c r="B292" s="1" t="s">
-        <v>628</v>
-      </c>
-      <c r="C292" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D292" s="1" t="s">
-        <v>629</v>
-      </c>
       <c r="E292" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F292" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
@@ -8562,13 +8559,13 @@
         <v>3</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="E293" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F293" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
@@ -8582,13 +8579,13 @@
         <v>3</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="E294" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F294" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
@@ -8602,13 +8599,13 @@
         <v>3</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="E295" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F295" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
@@ -8622,13 +8619,13 @@
         <v>3</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="E296" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F296" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
@@ -8642,13 +8639,13 @@
         <v>3</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="F297" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
@@ -8662,13 +8659,13 @@
         <v>3</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F298" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
@@ -8682,13 +8679,13 @@
         <v>3</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>40</v>
+        <v>126</v>
       </c>
       <c r="F299" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
@@ -8702,30 +8699,30 @@
         <v>3</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>629</v>
+        <v>646</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>126</v>
+        <v>4</v>
       </c>
       <c r="F300" s="1" t="s">
-        <v>620</v>
+        <v>23</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A301" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="B301" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="C301" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D301" s="1" t="s">
         <v>646</v>
       </c>
-      <c r="B301" s="1" t="s">
-        <v>647</v>
-      </c>
-      <c r="C301" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D301" s="1" t="s">
-        <v>648</v>
-      </c>
       <c r="E301" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F301" s="1" t="s">
         <v>23</v>
@@ -8742,10 +8739,10 @@
         <v>3</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="E302" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F302" s="1" t="s">
         <v>23</v>
@@ -8762,10 +8759,10 @@
         <v>3</v>
       </c>
       <c r="D303" s="1" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="E303" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F303" s="1" t="s">
         <v>23</v>
@@ -8782,10 +8779,10 @@
         <v>3</v>
       </c>
       <c r="D304" s="1" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="E304" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F304" s="1" t="s">
         <v>23</v>
@@ -8802,10 +8799,10 @@
         <v>3</v>
       </c>
       <c r="D305" s="1" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="E305" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F305" s="1" t="s">
         <v>23</v>
@@ -8822,10 +8819,10 @@
         <v>3</v>
       </c>
       <c r="D306" s="1" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="E306" s="1" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="F306" s="1" t="s">
         <v>23</v>
@@ -8842,10 +8839,10 @@
         <v>3</v>
       </c>
       <c r="D307" s="1" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="E307" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F307" s="1" t="s">
         <v>23</v>
@@ -8862,10 +8859,10 @@
         <v>3</v>
       </c>
       <c r="D308" s="1" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="E308" s="1" t="s">
-        <v>40</v>
+        <v>126</v>
       </c>
       <c r="F308" s="1" t="s">
         <v>23</v>
@@ -8882,10 +8879,10 @@
         <v>3</v>
       </c>
       <c r="D309" s="1" t="s">
-        <v>648</v>
+        <v>665</v>
       </c>
       <c r="E309" s="1" t="s">
-        <v>126</v>
+        <v>4</v>
       </c>
       <c r="F309" s="1" t="s">
         <v>23</v>
@@ -8893,19 +8890,19 @@
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A310" s="1" t="s">
+        <v>666</v>
+      </c>
+      <c r="B310" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="C310" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D310" s="1" t="s">
         <v>665</v>
       </c>
-      <c r="B310" s="1" t="s">
-        <v>666</v>
-      </c>
-      <c r="C310" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D310" s="1" t="s">
-        <v>667</v>
-      </c>
       <c r="E310" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F310" s="1" t="s">
         <v>23</v>
@@ -8922,10 +8919,10 @@
         <v>3</v>
       </c>
       <c r="D311" s="1" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="E311" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F311" s="1" t="s">
         <v>23</v>
@@ -8942,10 +8939,10 @@
         <v>3</v>
       </c>
       <c r="D312" s="1" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="E312" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F312" s="1" t="s">
         <v>23</v>
@@ -8962,10 +8959,10 @@
         <v>3</v>
       </c>
       <c r="D313" s="1" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="E313" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F313" s="1" t="s">
         <v>23</v>
@@ -8982,10 +8979,10 @@
         <v>3</v>
       </c>
       <c r="D314" s="1" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="E314" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F314" s="1" t="s">
         <v>23</v>
@@ -9002,10 +8999,10 @@
         <v>3</v>
       </c>
       <c r="D315" s="1" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="E315" s="1" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="F315" s="1" t="s">
         <v>23</v>
@@ -9022,10 +9019,10 @@
         <v>3</v>
       </c>
       <c r="D316" s="1" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="E316" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F316" s="1" t="s">
         <v>23</v>
@@ -9042,10 +9039,10 @@
         <v>3</v>
       </c>
       <c r="D317" s="1" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="E317" s="1" t="s">
-        <v>40</v>
+        <v>126</v>
       </c>
       <c r="F317" s="1" t="s">
         <v>23</v>
@@ -9062,10 +9059,10 @@
         <v>3</v>
       </c>
       <c r="D318" s="1" t="s">
-        <v>667</v>
+        <v>684</v>
       </c>
       <c r="E318" s="1" t="s">
-        <v>126</v>
+        <v>4</v>
       </c>
       <c r="F318" s="1" t="s">
         <v>23</v>
@@ -9073,19 +9070,19 @@
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A319" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="B319" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="C319" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D319" s="1" t="s">
         <v>684</v>
       </c>
-      <c r="B319" s="1" t="s">
-        <v>685</v>
-      </c>
-      <c r="C319" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D319" s="1" t="s">
-        <v>686</v>
-      </c>
       <c r="E319" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F319" s="1" t="s">
         <v>23</v>
@@ -9102,10 +9099,10 @@
         <v>3</v>
       </c>
       <c r="D320" s="1" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="E320" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F320" s="1" t="s">
         <v>23</v>
@@ -9122,10 +9119,10 @@
         <v>3</v>
       </c>
       <c r="D321" s="1" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="E321" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F321" s="1" t="s">
         <v>23</v>
@@ -9142,10 +9139,10 @@
         <v>3</v>
       </c>
       <c r="D322" s="1" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="E322" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F322" s="1" t="s">
         <v>23</v>
@@ -9162,10 +9159,10 @@
         <v>3</v>
       </c>
       <c r="D323" s="1" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="E323" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F323" s="1" t="s">
         <v>23</v>
@@ -9182,10 +9179,10 @@
         <v>3</v>
       </c>
       <c r="D324" s="1" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="E324" s="1" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="F324" s="1" t="s">
         <v>23</v>
@@ -9202,10 +9199,10 @@
         <v>3</v>
       </c>
       <c r="D325" s="1" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="E325" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F325" s="1" t="s">
         <v>23</v>
@@ -9222,10 +9219,10 @@
         <v>3</v>
       </c>
       <c r="D326" s="1" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="E326" s="1" t="s">
-        <v>40</v>
+        <v>126</v>
       </c>
       <c r="F326" s="1" t="s">
         <v>23</v>
@@ -9242,10 +9239,10 @@
         <v>3</v>
       </c>
       <c r="D327" s="1" t="s">
-        <v>686</v>
+        <v>703</v>
       </c>
       <c r="E327" s="1" t="s">
-        <v>126</v>
+        <v>4</v>
       </c>
       <c r="F327" s="1" t="s">
         <v>23</v>
@@ -9253,19 +9250,19 @@
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A328" s="1" t="s">
+        <v>704</v>
+      </c>
+      <c r="B328" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="C328" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D328" s="1" t="s">
         <v>703</v>
       </c>
-      <c r="B328" s="1" t="s">
-        <v>704</v>
-      </c>
-      <c r="C328" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D328" s="1" t="s">
-        <v>705</v>
-      </c>
       <c r="E328" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F328" s="1" t="s">
         <v>23</v>
@@ -9282,13 +9279,13 @@
         <v>3</v>
       </c>
       <c r="D329" s="1" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="E329" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F329" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.25">
@@ -9302,10 +9299,10 @@
         <v>3</v>
       </c>
       <c r="D330" s="1" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="E330" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F330" s="1" t="s">
         <v>28</v>
@@ -9322,13 +9319,13 @@
         <v>3</v>
       </c>
       <c r="D331" s="1" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="E331" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F331" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.25">
@@ -9342,10 +9339,10 @@
         <v>3</v>
       </c>
       <c r="D332" s="1" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="E332" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F332" s="1" t="s">
         <v>23</v>
@@ -9362,10 +9359,10 @@
         <v>3</v>
       </c>
       <c r="D333" s="1" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="E333" s="1" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="F333" s="1" t="s">
         <v>23</v>
@@ -9382,10 +9379,10 @@
         <v>3</v>
       </c>
       <c r="D334" s="1" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="E334" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F334" s="1" t="s">
         <v>23</v>
@@ -9402,10 +9399,10 @@
         <v>3</v>
       </c>
       <c r="D335" s="1" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="E335" s="1" t="s">
-        <v>40</v>
+        <v>126</v>
       </c>
       <c r="F335" s="1" t="s">
         <v>23</v>
@@ -9422,10 +9419,10 @@
         <v>3</v>
       </c>
       <c r="D336" s="1" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="E336" s="1" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="F336" s="1" t="s">
         <v>23</v>
@@ -9442,33 +9439,33 @@
         <v>3</v>
       </c>
       <c r="D337" s="1" t="s">
-        <v>705</v>
+        <v>724</v>
       </c>
       <c r="E337" s="1" t="s">
-        <v>145</v>
+        <v>4</v>
       </c>
       <c r="F337" s="1" t="s">
-        <v>23</v>
+        <v>70</v>
       </c>
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A338" s="1" t="s">
+        <v>725</v>
+      </c>
+      <c r="B338" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="C338" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D338" s="1" t="s">
         <v>724</v>
       </c>
-      <c r="B338" s="1" t="s">
-        <v>725</v>
-      </c>
-      <c r="C338" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D338" s="1" t="s">
-        <v>726</v>
-      </c>
       <c r="E338" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F338" s="1" t="s">
-        <v>70</v>
+        <v>28</v>
       </c>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.25">
@@ -9482,13 +9479,13 @@
         <v>3</v>
       </c>
       <c r="D339" s="1" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="E339" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F339" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.25">
@@ -9502,13 +9499,13 @@
         <v>3</v>
       </c>
       <c r="D340" s="1" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="E340" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F340" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.25">
@@ -9522,13 +9519,13 @@
         <v>3</v>
       </c>
       <c r="D341" s="1" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="E341" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F341" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.25">
@@ -9542,10 +9539,10 @@
         <v>3</v>
       </c>
       <c r="D342" s="1" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="E342" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F342" s="1" t="s">
         <v>23</v>
@@ -9562,13 +9559,13 @@
         <v>3</v>
       </c>
       <c r="D343" s="1" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="E343" s="1" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="F343" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.25">
@@ -9582,33 +9579,33 @@
         <v>3</v>
       </c>
       <c r="D344" s="1" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="E344" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F344" s="1" t="s">
-        <v>28</v>
+        <v>739</v>
       </c>
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A345" s="1" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="B345" s="1" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C345" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D345" s="1" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="E345" s="1" t="s">
-        <v>40</v>
+        <v>126</v>
       </c>
       <c r="F345" s="1" t="s">
-        <v>741</v>
+        <v>70</v>
       </c>
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.25">
@@ -9622,30 +9619,30 @@
         <v>3</v>
       </c>
       <c r="D346" s="1" t="s">
-        <v>726</v>
+        <v>744</v>
       </c>
       <c r="E346" s="1" t="s">
-        <v>126</v>
+        <v>4</v>
       </c>
       <c r="F346" s="1" t="s">
-        <v>70</v>
+        <v>23</v>
       </c>
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A347" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="B347" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="C347" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D347" s="1" t="s">
         <v>744</v>
       </c>
-      <c r="B347" s="1" t="s">
-        <v>745</v>
-      </c>
-      <c r="C347" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D347" s="1" t="s">
-        <v>746</v>
-      </c>
       <c r="E347" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F347" s="1" t="s">
         <v>23</v>
@@ -9662,10 +9659,10 @@
         <v>3</v>
       </c>
       <c r="D348" s="1" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="E348" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F348" s="1" t="s">
         <v>23</v>
@@ -9673,121 +9670,101 @@
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A349" s="1" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B349" s="1" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="C349" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D349" s="1" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="E349" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F349" s="1" t="s">
-        <v>23</v>
+        <v>70</v>
       </c>
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A350" s="1" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="B350" s="1" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="C350" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D350" s="1" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="E350" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F350" s="1" t="s">
-        <v>70</v>
+        <v>756</v>
       </c>
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A351" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="B351" s="1" t="s">
+        <v>758</v>
+      </c>
+      <c r="C351" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D351" s="1" t="s">
         <v>755</v>
       </c>
-      <c r="B351" s="1" t="s">
-        <v>756</v>
-      </c>
-      <c r="C351" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D351" s="1" t="s">
-        <v>757</v>
-      </c>
       <c r="E351" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F351" s="1" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A352" s="1" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="B352" s="1" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="C352" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D352" s="1" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="E352" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F352" s="1" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
     </row>
     <row r="353" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A353" s="1" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="B353" s="1" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="C353" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D353" s="1" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="E353" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F353" s="1" t="s">
-        <v>761</v>
-      </c>
-    </row>
-    <row r="354" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A354" s="1" t="s">
-        <v>764</v>
-      </c>
-      <c r="B354" s="1" t="s">
-        <v>765</v>
-      </c>
-      <c r="C354" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D354" s="1" t="s">
-        <v>757</v>
-      </c>
-      <c r="E354" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F354" s="1" t="s">
         <v>23</v>
       </c>
     </row>

--- a/CLB07N.xlsx
+++ b/CLB07N.xlsx
@@ -91,6 +91,15 @@
     <t>AJE BIG NPS MADU 350</t>
   </si>
   <si>
+    <t>20127835</t>
+  </si>
+  <si>
+    <t>ALANG SARI JN 300ML</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
     <t>20124899</t>
   </si>
   <si>
@@ -106,867 +115,858 @@
     <t>CHI/FRST WHT/PCH 480</t>
   </si>
   <si>
+    <t>20135619</t>
+  </si>
+  <si>
+    <t>TEBS ZERO LYCHEE 300</t>
+  </si>
+  <si>
+    <t>20138893</t>
+  </si>
+  <si>
+    <t>AMO DRMY STRAW 180ML</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>20138894</t>
+  </si>
+  <si>
+    <t>AMO FIZZY EASY 180ML</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>20065778</t>
+  </si>
+  <si>
+    <t>COCA COLA PET 390 ML</t>
+  </si>
+  <si>
+    <t>20128821</t>
+  </si>
+  <si>
+    <t>COCA COLA ZERO 390ML</t>
+  </si>
+  <si>
+    <t>20140260</t>
+  </si>
+  <si>
+    <t>CC.COLA ZERO VAN 390</t>
+  </si>
+  <si>
+    <t>20065779</t>
+  </si>
+  <si>
+    <t>SPRITE PET 390 ML</t>
+  </si>
+  <si>
+    <t>20130667</t>
+  </si>
+  <si>
+    <t>SPRITE ZERO LIME 390</t>
+  </si>
+  <si>
+    <t>20065780</t>
+  </si>
+  <si>
+    <t>FANTA STRW PET 390ML</t>
+  </si>
+  <si>
+    <t>20137093</t>
+  </si>
+  <si>
+    <t>FANTA ZERO STRAWB390</t>
+  </si>
+  <si>
+    <t>20093993</t>
+  </si>
+  <si>
+    <t>FANTA GRAPE 390ML</t>
+  </si>
+  <si>
+    <t>20123500</t>
+  </si>
+  <si>
+    <t>A&amp;W DRINK SARSA 250</t>
+  </si>
+  <si>
+    <t>20068089</t>
+  </si>
+  <si>
+    <t>GR.SANDS LMN&amp;GRP 250</t>
+  </si>
+  <si>
+    <t>10000107</t>
+  </si>
+  <si>
+    <t>GREEN SAND ORGNL 330</t>
+  </si>
+  <si>
+    <t>10033567</t>
+  </si>
+  <si>
+    <t>BINTANG ZERO KLG 330</t>
+  </si>
+  <si>
+    <t>20135345</t>
+  </si>
+  <si>
+    <t>GROOVY ROOT BREW 330</t>
+  </si>
+  <si>
+    <t>RT,(E-2.5B)</t>
+  </si>
+  <si>
+    <t>20133709</t>
+  </si>
+  <si>
+    <t>POLARIS SARSAPRLA330</t>
+  </si>
+  <si>
+    <t>10037437</t>
+  </si>
+  <si>
+    <t>C/B PENY.STRAW 320</t>
+  </si>
+  <si>
+    <t>10003627</t>
+  </si>
+  <si>
+    <t>C/B PENY.ORANGE320</t>
+  </si>
+  <si>
+    <t>10004237</t>
+  </si>
+  <si>
+    <t>C/B PENY.LECI 320ML</t>
+  </si>
+  <si>
+    <t>10003842</t>
+  </si>
+  <si>
+    <t>C/B PENY.JAMBU 320</t>
+  </si>
+  <si>
+    <t>20037144</t>
+  </si>
+  <si>
+    <t>KAKI3 PENY.LECI 320</t>
+  </si>
+  <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20037150</t>
+  </si>
+  <si>
+    <t>KAKI3 PENY.JAMBU 320</t>
+  </si>
+  <si>
+    <t>20037147</t>
+  </si>
+  <si>
+    <t>KAKI TIGA STRO 320ML</t>
+  </si>
+  <si>
+    <t>20045995</t>
+  </si>
+  <si>
+    <t>KAKI3 ANAK STRO 238</t>
+  </si>
+  <si>
+    <t>20053540</t>
+  </si>
+  <si>
+    <t>ADEM SARI CK BTL 350</t>
+  </si>
+  <si>
+    <t>20122090</t>
+  </si>
+  <si>
+    <t>ADEM/S MD LMN TEA350</t>
+  </si>
+  <si>
+    <t>20083775</t>
+  </si>
+  <si>
+    <t>ADEMSARI CK HR.T 320</t>
+  </si>
+  <si>
+    <t>20040276</t>
+  </si>
+  <si>
+    <t>ADEM SARI CK KLG 320</t>
+  </si>
+  <si>
+    <t>20071642</t>
+  </si>
+  <si>
+    <t>ADEMSARI CK SPRK 320</t>
+  </si>
+  <si>
+    <t>20069199</t>
+  </si>
+  <si>
+    <t>KAKI3 LMN.LM KLG 320</t>
+  </si>
+  <si>
+    <t>20142024</t>
+  </si>
+  <si>
+    <t>COOLTOPIA MELON ORG</t>
+  </si>
+  <si>
+    <t>20045996</t>
+  </si>
+  <si>
+    <t>KAKI3 ANAK LECI 238</t>
+  </si>
+  <si>
+    <t>20102789</t>
+  </si>
+  <si>
+    <t>ABC CHOCMLT COFF 200</t>
+  </si>
+  <si>
+    <t>20102790</t>
+  </si>
+  <si>
+    <t>ABC MILK COFFEE 200</t>
+  </si>
+  <si>
+    <t>20120499</t>
+  </si>
+  <si>
+    <t>K/A SIGNT STRONG 200</t>
+  </si>
+  <si>
+    <t>20089792</t>
+  </si>
+  <si>
+    <t>K/A DRNK BLK COFF200</t>
+  </si>
+  <si>
+    <t>20124713</t>
+  </si>
+  <si>
+    <t>LUWAK KOPI+GULA 220</t>
+  </si>
+  <si>
+    <t>20123322</t>
+  </si>
+  <si>
+    <t>GOLDA CAPPUCCINO 200</t>
+  </si>
+  <si>
+    <t>20087542</t>
+  </si>
+  <si>
+    <t>GOLDA COFF.DOLCE 200</t>
+  </si>
+  <si>
+    <t>20109969</t>
+  </si>
+  <si>
+    <t>KOPIKO LUCKY DAY 180</t>
+  </si>
+  <si>
+    <t>20045415</t>
+  </si>
+  <si>
+    <t>KOPIKO 78C 240ML</t>
+  </si>
+  <si>
+    <t>20078206</t>
+  </si>
+  <si>
+    <t>LUWAK WHT ORGL 220ML</t>
+  </si>
+  <si>
+    <t>20093586</t>
+  </si>
+  <si>
+    <t>ICHTN THAI M.COFF300</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>20138025</t>
+  </si>
+  <si>
+    <t>HY BTS COFF TRMS 250</t>
+  </si>
+  <si>
+    <t>20138049</t>
+  </si>
+  <si>
+    <t>HY BTS COFF CPNO 250</t>
+  </si>
+  <si>
+    <t>20120904</t>
+  </si>
+  <si>
+    <t>KK BLACK AREN 220ML</t>
+  </si>
+  <si>
+    <t>20120906</t>
+  </si>
+  <si>
+    <t>KK MANTANCINO 220ML</t>
+  </si>
+  <si>
+    <t>20133409</t>
+  </si>
+  <si>
+    <t>KK CAFFE LATTE 200ML</t>
+  </si>
+  <si>
+    <t>20138168</t>
+  </si>
+  <si>
+    <t>KK CHEESE LATTEE 200</t>
+  </si>
+  <si>
+    <t>20138167</t>
+  </si>
+  <si>
+    <t>KK JPNS MATCHA 200</t>
+  </si>
+  <si>
+    <t>20027768</t>
+  </si>
+  <si>
+    <t>NESCAFE COFF CRM 180</t>
+  </si>
+  <si>
+    <t>20076770</t>
+  </si>
+  <si>
+    <t>G/DAY CAPPUCCINO 250</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>20045674</t>
+  </si>
+  <si>
+    <t>G/DAY F.MOCACINO 250</t>
+  </si>
+  <si>
+    <t>20045673</t>
+  </si>
+  <si>
+    <t>G/DAY TIRAMISU/B 250</t>
+  </si>
+  <si>
+    <t>20056193</t>
+  </si>
+  <si>
+    <t>GOOD DAY AVCDO/D 250</t>
+  </si>
+  <si>
+    <t>20132329</t>
+  </si>
+  <si>
+    <t>GOOD DAY GRVY CKS250</t>
+  </si>
+  <si>
+    <t>20132760</t>
+  </si>
+  <si>
+    <t>CAFINO RTD ESPRSO200</t>
+  </si>
+  <si>
+    <t>20132761</t>
+  </si>
+  <si>
+    <t>CAFINO RTD CPCINO200</t>
+  </si>
+  <si>
+    <t>20138035</t>
+  </si>
+  <si>
+    <t>CAFFINO OATMARIE 200</t>
+  </si>
+  <si>
+    <t>20139577</t>
+  </si>
+  <si>
+    <t>PC AREN LATTE 210ML</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20139578</t>
+  </si>
+  <si>
+    <t>PC GOLDN CARAMEL 210</t>
+  </si>
+  <si>
+    <t>20139576</t>
+  </si>
+  <si>
+    <t>PC CRMY CPUCCINO 210</t>
+  </si>
+  <si>
+    <t>20140431</t>
+  </si>
+  <si>
+    <t>NSCAFE KITKAT LAT220</t>
+  </si>
+  <si>
+    <t>20133058</t>
+  </si>
+  <si>
+    <t>NSCAFE OAT LATTE 220</t>
+  </si>
+  <si>
+    <t>20134557</t>
+  </si>
+  <si>
+    <t>OATSIDE CRML MCHT200</t>
+  </si>
+  <si>
+    <t>20129108</t>
+  </si>
+  <si>
+    <t>OATSDE COFFEE 200ML</t>
+  </si>
+  <si>
+    <t>20114494</t>
+  </si>
+  <si>
+    <t>NSCAFE CRML MCTO 220</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>20114495</t>
+  </si>
+  <si>
+    <t>NESCAFE CPUCCINO 220</t>
+  </si>
+  <si>
+    <t>20114493</t>
+  </si>
+  <si>
+    <t>NESCAFE LATTE 220ML</t>
+  </si>
+  <si>
+    <t>20138057</t>
+  </si>
+  <si>
+    <t>NSCAFE GULA AREN 220</t>
+  </si>
+  <si>
+    <t>20121456</t>
+  </si>
+  <si>
+    <t>NSCAFE ICE BLACK 220</t>
+  </si>
+  <si>
+    <t>20000787</t>
+  </si>
+  <si>
+    <t>NESCAFE ICE.CF OR220</t>
+  </si>
+  <si>
+    <t>20014954</t>
+  </si>
+  <si>
+    <t>NESCAFE ICE.CF MC220</t>
+  </si>
+  <si>
+    <t>20000786</t>
+  </si>
+  <si>
+    <t>NESCAFE ICE.CF LT220</t>
+  </si>
+  <si>
+    <t>20125115</t>
+  </si>
+  <si>
+    <t>STARBUCKS LATTE 220</t>
+  </si>
+  <si>
+    <t>20125126</t>
+  </si>
+  <si>
+    <t>STARBUCKS CARAMEL220</t>
+  </si>
+  <si>
+    <t>20014608</t>
+  </si>
+  <si>
+    <t>HRMVTON PSK BUMI 150</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>10006263</t>
+  </si>
+  <si>
+    <t>HEMAVITON ENERGY 150</t>
+  </si>
+  <si>
+    <t>10002602</t>
+  </si>
+  <si>
+    <t>M-150 HEALT DRINK150</t>
+  </si>
+  <si>
+    <t>10002595</t>
+  </si>
+  <si>
+    <t>KRATINGDAENG 150 ML</t>
+  </si>
+  <si>
+    <t>10003427</t>
+  </si>
+  <si>
+    <t>KRATINGDAENG SPR.150</t>
+  </si>
+  <si>
+    <t>20022431</t>
+  </si>
+  <si>
+    <t>RED BULL E/DRNK 250</t>
+  </si>
+  <si>
+    <t>20056989</t>
+  </si>
+  <si>
+    <t>RED BULL GOLD 250ML</t>
+  </si>
+  <si>
+    <t>20138252</t>
+  </si>
+  <si>
+    <t>EXTRA JOSS ULTIMT250</t>
+  </si>
+  <si>
+    <t>20080088</t>
+  </si>
+  <si>
+    <t>POKKA GREEN TEA 450</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>20037565</t>
+  </si>
+  <si>
+    <t>PUCUK/H TEH MLATI500</t>
+  </si>
+  <si>
+    <t>20048348</t>
+  </si>
+  <si>
+    <t>PUCUK/H TEH L/SGR500</t>
+  </si>
+  <si>
+    <t>20036157</t>
+  </si>
+  <si>
+    <t>SOSRO TEH BOTOL 450</t>
+  </si>
+  <si>
+    <t>20002203</t>
+  </si>
+  <si>
+    <t>SOSRO F.TEA APEL 500</t>
+  </si>
+  <si>
+    <t>20003698</t>
+  </si>
+  <si>
+    <t>SOSRO FR.TEA XTRM500</t>
+  </si>
+  <si>
+    <t>20002205</t>
+  </si>
+  <si>
+    <t>SOSRO F.TEA BLKCR500</t>
+  </si>
+  <si>
+    <t>20134046</t>
+  </si>
+  <si>
+    <t>FRUIT TEA FREEZE 500</t>
+  </si>
+  <si>
+    <t>20060210</t>
+  </si>
+  <si>
+    <t>IDM TEH HJAU MLT 330</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>20077509</t>
+  </si>
+  <si>
+    <t>IDM LEMON TEA 330ML</t>
+  </si>
+  <si>
+    <t>20126464</t>
+  </si>
+  <si>
+    <t>IDM TEH APL&amp;LYCHE350</t>
+  </si>
+  <si>
+    <t>20101897</t>
+  </si>
+  <si>
+    <t>IDM TEH APEL 350ML</t>
+  </si>
+  <si>
+    <t>20132840</t>
+  </si>
+  <si>
+    <t>IDM TEH BLCKCRRNT350</t>
+  </si>
+  <si>
+    <t>20066454</t>
+  </si>
+  <si>
+    <t>FRUIT TEA BLCKCR 350</t>
+  </si>
+  <si>
+    <t>20073495</t>
+  </si>
+  <si>
+    <t>FRUIT TEA FREEZE 350</t>
+  </si>
+  <si>
+    <t>20066455</t>
+  </si>
+  <si>
+    <t>FRUIT TEA APPLE 350</t>
+  </si>
+  <si>
+    <t>20079972</t>
+  </si>
+  <si>
+    <t>FRUIT TEA MRKISA 350</t>
+  </si>
+  <si>
+    <t>20060207</t>
+  </si>
+  <si>
+    <t>I/OCHA TEH MLATI 350</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>20048934</t>
+  </si>
+  <si>
+    <t>I/OCHA GRN TEA 350ML</t>
+  </si>
+  <si>
+    <t>20018904</t>
+  </si>
+  <si>
+    <t>NU GREEN TEA HNY 330</t>
+  </si>
+  <si>
+    <t>20053867</t>
+  </si>
+  <si>
+    <t>TEH GELAS BTL 350ML</t>
+  </si>
+  <si>
+    <t>20073396</t>
+  </si>
+  <si>
+    <t>S-TEE BTL 390ML</t>
+  </si>
+  <si>
+    <t>20072249</t>
+  </si>
+  <si>
+    <t>SOSRO TEH BOTOL 350</t>
+  </si>
+  <si>
+    <t>20122278</t>
+  </si>
+  <si>
+    <t>TEH BOTOL LS.SGR 350</t>
+  </si>
+  <si>
+    <t>20082395</t>
+  </si>
+  <si>
+    <t>TEH BOTOL TAWAR 350</t>
+  </si>
+  <si>
+    <t>RT,(E-3.5B)</t>
+  </si>
+  <si>
+    <t>20035484</t>
+  </si>
+  <si>
+    <t>PUCUK/H TEH MLATI350</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>20048155</t>
+  </si>
+  <si>
+    <t>PUCUK/H TEH L/SGR350</t>
+  </si>
+  <si>
+    <t>20026226</t>
+  </si>
+  <si>
+    <t>ULTRA TEH KOTAK 500</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>10036640</t>
+  </si>
+  <si>
+    <t>TEH KOTAK JASMINE300</t>
+  </si>
+  <si>
+    <t>20044334</t>
+  </si>
+  <si>
+    <t>SOSRO TEH BTL TPK300</t>
+  </si>
+  <si>
+    <t>10005128</t>
+  </si>
+  <si>
+    <t>SOSRO TEH KOTAK B250</t>
+  </si>
+  <si>
+    <t>20024315</t>
+  </si>
+  <si>
+    <t>TEH BOTOL LS.SGR 250</t>
+  </si>
+  <si>
+    <t>20002209</t>
+  </si>
+  <si>
+    <t>TEBS SPRK MIX FRT330</t>
+  </si>
+  <si>
+    <t>20048435</t>
+  </si>
+  <si>
+    <t>TEH KOTAK LESS/S 300</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>20100142</t>
+  </si>
+  <si>
+    <t>TEH KOTAK BLCKCR 300</t>
+  </si>
+  <si>
+    <t>20100143</t>
+  </si>
+  <si>
+    <t>TEH KOTAK APPLE 300</t>
+  </si>
+  <si>
+    <t>20137159</t>
+  </si>
+  <si>
+    <t>TEH KOTAK MANGGA 300</t>
+  </si>
+  <si>
+    <t>20087016</t>
+  </si>
+  <si>
+    <t>TEH KOTAK LEMON 300</t>
+  </si>
+  <si>
+    <t>20135647</t>
+  </si>
+  <si>
+    <t>TEH KOTAK LYCHEE 300</t>
+  </si>
+  <si>
+    <t>20117682</t>
+  </si>
+  <si>
+    <t>DLMNT BOBA RD.VEL240</t>
+  </si>
+  <si>
+    <t>20117687</t>
+  </si>
+  <si>
+    <t>DLMNT BOBA MTCHA 240</t>
+  </si>
+  <si>
+    <t>20003786</t>
+  </si>
+  <si>
+    <t>NU GREEN TEA HNY 450</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>20113059</t>
+  </si>
+  <si>
+    <t>NU YOGURT TEA 450ML</t>
+  </si>
+  <si>
+    <t>20139732</t>
+  </si>
+  <si>
+    <t>NU YOGRT TEA BRY 450</t>
+  </si>
+  <si>
+    <t>20012573</t>
+  </si>
+  <si>
+    <t>FRESTEA TEH MLATI500</t>
+  </si>
+  <si>
+    <t>20036765</t>
+  </si>
+  <si>
+    <t>FRESTEA GRN MADU 500</t>
+  </si>
+  <si>
+    <t>20012574</t>
+  </si>
+  <si>
+    <t>FRESTEA TEH APEL 500</t>
+  </si>
+  <si>
     <t>20035829</t>
   </si>
   <si>
     <t>TEBS TEA WT/SODA 500</t>
   </si>
   <si>
-    <t>20135619</t>
-  </si>
-  <si>
-    <t>TEBS ZERO LYCHEE 300</t>
-  </si>
-  <si>
-    <t>20138893</t>
-  </si>
-  <si>
-    <t>AMO DRMY STRAW 180ML</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>20138894</t>
-  </si>
-  <si>
-    <t>AMO FIZZY EASY 180ML</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>20065778</t>
-  </si>
-  <si>
-    <t>COCA COLA PET 390 ML</t>
-  </si>
-  <si>
-    <t>20128821</t>
-  </si>
-  <si>
-    <t>COCA COLA ZERO 390ML</t>
-  </si>
-  <si>
-    <t>20140260</t>
-  </si>
-  <si>
-    <t>CC.COLA ZERO VAN 390</t>
-  </si>
-  <si>
-    <t>20065779</t>
-  </si>
-  <si>
-    <t>SPRITE PET 390 ML</t>
-  </si>
-  <si>
-    <t>20130667</t>
-  </si>
-  <si>
-    <t>SPRITE ZERO LIME 390</t>
-  </si>
-  <si>
-    <t>20065780</t>
-  </si>
-  <si>
-    <t>FANTA STRW PET 390ML</t>
-  </si>
-  <si>
-    <t>20137093</t>
-  </si>
-  <si>
-    <t>FANTA ZERO STRAWB390</t>
-  </si>
-  <si>
-    <t>20093993</t>
-  </si>
-  <si>
-    <t>FANTA GRAPE 390ML</t>
-  </si>
-  <si>
-    <t>20123500</t>
-  </si>
-  <si>
-    <t>A&amp;W DRINK SARSA 250</t>
-  </si>
-  <si>
-    <t>20068089</t>
-  </si>
-  <si>
-    <t>GR.SANDS LMN&amp;GRP 250</t>
-  </si>
-  <si>
-    <t>10000107</t>
-  </si>
-  <si>
-    <t>GREEN SAND ORGNL 330</t>
-  </si>
-  <si>
-    <t>10033567</t>
-  </si>
-  <si>
-    <t>BINTANG ZERO KLG 330</t>
-  </si>
-  <si>
-    <t>20135345</t>
-  </si>
-  <si>
-    <t>GROOVY ROOT BREW 330</t>
-  </si>
-  <si>
-    <t>RT,(E-2.5B)</t>
-  </si>
-  <si>
-    <t>20133709</t>
-  </si>
-  <si>
-    <t>POLARIS SARSAPRLA330</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>10037437</t>
-  </si>
-  <si>
-    <t>C/B PENY.STRAW 320</t>
-  </si>
-  <si>
-    <t>10003627</t>
-  </si>
-  <si>
-    <t>C/B PENY.ORANGE320</t>
-  </si>
-  <si>
-    <t>10004237</t>
-  </si>
-  <si>
-    <t>C/B PENY.LECI 320ML</t>
-  </si>
-  <si>
-    <t>10003842</t>
-  </si>
-  <si>
-    <t>C/B PENY.JAMBU 320</t>
-  </si>
-  <si>
-    <t>20037144</t>
-  </si>
-  <si>
-    <t>KAKI3 PENY.LECI 320</t>
-  </si>
-  <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20037150</t>
-  </si>
-  <si>
-    <t>KAKI3 PENY.JAMBU 320</t>
-  </si>
-  <si>
-    <t>20037147</t>
-  </si>
-  <si>
-    <t>KAKI TIGA STRO 320ML</t>
-  </si>
-  <si>
-    <t>20045995</t>
-  </si>
-  <si>
-    <t>KAKI3 ANAK STRO 238</t>
-  </si>
-  <si>
-    <t>20127835</t>
-  </si>
-  <si>
-    <t>ALANG SARI JN 300ML</t>
-  </si>
-  <si>
-    <t>20053540</t>
-  </si>
-  <si>
-    <t>ADEM SARI CK BTL 350</t>
-  </si>
-  <si>
-    <t>20122090</t>
-  </si>
-  <si>
-    <t>ADEM/S MD LMN TEA350</t>
-  </si>
-  <si>
-    <t>20083775</t>
-  </si>
-  <si>
-    <t>ADEMSARI CK HR.T 320</t>
-  </si>
-  <si>
-    <t>20040276</t>
-  </si>
-  <si>
-    <t>ADEM SARI CK KLG 320</t>
-  </si>
-  <si>
-    <t>20071642</t>
-  </si>
-  <si>
-    <t>ADEMSARI CK SPRK 320</t>
-  </si>
-  <si>
-    <t>20069199</t>
-  </si>
-  <si>
-    <t>KAKI3 LMN.LM KLG 320</t>
-  </si>
-  <si>
-    <t>20045996</t>
-  </si>
-  <si>
-    <t>KAKI3 ANAK LECI 238</t>
-  </si>
-  <si>
-    <t>20102789</t>
-  </si>
-  <si>
-    <t>ABC CHOCMLT COFF 200</t>
-  </si>
-  <si>
-    <t>20102790</t>
-  </si>
-  <si>
-    <t>ABC MILK COFFEE 200</t>
-  </si>
-  <si>
-    <t>20120499</t>
-  </si>
-  <si>
-    <t>K/A SIGNT STRONG 200</t>
-  </si>
-  <si>
-    <t>20089792</t>
-  </si>
-  <si>
-    <t>K/A DRNK BLK COFF200</t>
-  </si>
-  <si>
-    <t>20124713</t>
-  </si>
-  <si>
-    <t>LUWAK KOPI+GULA 220</t>
-  </si>
-  <si>
-    <t>20123322</t>
-  </si>
-  <si>
-    <t>GOLDA CAPPUCCINO 200</t>
-  </si>
-  <si>
-    <t>20087542</t>
-  </si>
-  <si>
-    <t>GOLDA COFF.DOLCE 200</t>
-  </si>
-  <si>
-    <t>20109969</t>
-  </si>
-  <si>
-    <t>KOPIKO LUCKY DAY 180</t>
-  </si>
-  <si>
-    <t>20045415</t>
-  </si>
-  <si>
-    <t>KOPIKO 78C 240ML</t>
-  </si>
-  <si>
-    <t>20078206</t>
-  </si>
-  <si>
-    <t>LUWAK WHT ORGL 220ML</t>
-  </si>
-  <si>
-    <t>20093586</t>
-  </si>
-  <si>
-    <t>ICHTN THAI M.COFF300</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>20138025</t>
-  </si>
-  <si>
-    <t>HY BTS COFF TRMS 250</t>
-  </si>
-  <si>
-    <t>20138049</t>
-  </si>
-  <si>
-    <t>HY BTS COFF CPNO 250</t>
-  </si>
-  <si>
-    <t>20120904</t>
-  </si>
-  <si>
-    <t>KK BLACK AREN 220ML</t>
-  </si>
-  <si>
-    <t>20120906</t>
-  </si>
-  <si>
-    <t>KK MANTANCINO 220ML</t>
-  </si>
-  <si>
-    <t>20133409</t>
-  </si>
-  <si>
-    <t>KK CAFFE LATTE 200ML</t>
-  </si>
-  <si>
-    <t>20138168</t>
-  </si>
-  <si>
-    <t>KK CHEESE LATTEE 200</t>
-  </si>
-  <si>
-    <t>20138167</t>
-  </si>
-  <si>
-    <t>KK JPNS MATCHA 200</t>
-  </si>
-  <si>
-    <t>20027768</t>
-  </si>
-  <si>
-    <t>NESCAFE COFF CRM 180</t>
-  </si>
-  <si>
-    <t>20076770</t>
-  </si>
-  <si>
-    <t>G/DAY CAPPUCCINO 250</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>20045674</t>
-  </si>
-  <si>
-    <t>G/DAY F.MOCACINO 250</t>
-  </si>
-  <si>
-    <t>20045673</t>
-  </si>
-  <si>
-    <t>G/DAY TIRAMISU/B 250</t>
-  </si>
-  <si>
-    <t>20056193</t>
-  </si>
-  <si>
-    <t>GOOD DAY AVCDO/D 250</t>
-  </si>
-  <si>
-    <t>20132329</t>
-  </si>
-  <si>
-    <t>GOOD DAY GRVY CKS250</t>
-  </si>
-  <si>
-    <t>20132760</t>
-  </si>
-  <si>
-    <t>CAFINO RTD ESPRSO200</t>
-  </si>
-  <si>
-    <t>20132761</t>
-  </si>
-  <si>
-    <t>CAFINO RTD CPCINO200</t>
-  </si>
-  <si>
-    <t>20138035</t>
-  </si>
-  <si>
-    <t>CAFFINO OATMARIE 200</t>
-  </si>
-  <si>
-    <t>20139577</t>
-  </si>
-  <si>
-    <t>PC AREN LATTE 210ML</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20139578</t>
-  </si>
-  <si>
-    <t>PC GOLDN CARAMEL 210</t>
-  </si>
-  <si>
-    <t>20139576</t>
-  </si>
-  <si>
-    <t>PC CRMY CPUCCINO 210</t>
-  </si>
-  <si>
-    <t>20140431</t>
-  </si>
-  <si>
-    <t>NSCAFE KITKAT LAT220</t>
-  </si>
-  <si>
-    <t>20133058</t>
-  </si>
-  <si>
-    <t>NSCAFE OAT LATTE 220</t>
-  </si>
-  <si>
-    <t>20134557</t>
-  </si>
-  <si>
-    <t>OATSIDE CRML MCHT240</t>
-  </si>
-  <si>
-    <t>20129108</t>
-  </si>
-  <si>
-    <t>OATSDE COFFEE 240ML</t>
-  </si>
-  <si>
-    <t>20114494</t>
-  </si>
-  <si>
-    <t>NSCAFE CRML MCTO 220</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>20114495</t>
-  </si>
-  <si>
-    <t>NESCAFE CPUCCINO 220</t>
-  </si>
-  <si>
-    <t>20114493</t>
-  </si>
-  <si>
-    <t>NESCAFE LATTE 220ML</t>
-  </si>
-  <si>
-    <t>20138057</t>
-  </si>
-  <si>
-    <t>NSCAFE GULA AREN 220</t>
-  </si>
-  <si>
-    <t>20121456</t>
-  </si>
-  <si>
-    <t>NSCAFE ICE BLACK 220</t>
-  </si>
-  <si>
-    <t>20000787</t>
-  </si>
-  <si>
-    <t>NESCAFE ICE.CF OR220</t>
-  </si>
-  <si>
-    <t>20014954</t>
-  </si>
-  <si>
-    <t>NESCAFE ICE.CF MC220</t>
-  </si>
-  <si>
-    <t>20000786</t>
-  </si>
-  <si>
-    <t>NESCAFE ICE.CF LT220</t>
-  </si>
-  <si>
-    <t>20125115</t>
-  </si>
-  <si>
-    <t>STARBUCKS LATTE 220</t>
-  </si>
-  <si>
-    <t>20125126</t>
-  </si>
-  <si>
-    <t>STARBUCKS CARAMEL220</t>
-  </si>
-  <si>
-    <t>20014608</t>
-  </si>
-  <si>
-    <t>HRMVTON PSK BUMI 150</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>10006263</t>
-  </si>
-  <si>
-    <t>HEMAVITON ENERGY 150</t>
-  </si>
-  <si>
-    <t>10002602</t>
-  </si>
-  <si>
-    <t>M-150 HEALT DRINK150</t>
-  </si>
-  <si>
-    <t>10002595</t>
-  </si>
-  <si>
-    <t>KRATINGDAENG 150 ML</t>
-  </si>
-  <si>
-    <t>10003427</t>
-  </si>
-  <si>
-    <t>KRATINGDAENG SPR.150</t>
-  </si>
-  <si>
-    <t>20022431</t>
-  </si>
-  <si>
-    <t>RED BULL E/DRNK 250</t>
-  </si>
-  <si>
-    <t>20056989</t>
-  </si>
-  <si>
-    <t>RED BULL GOLD 250ML</t>
-  </si>
-  <si>
-    <t>20138252</t>
-  </si>
-  <si>
-    <t>EXTRA JOSS ULTIMT250</t>
-  </si>
-  <si>
-    <t>20072287</t>
-  </si>
-  <si>
-    <t>M150 MNN ENRG CN 250</t>
-  </si>
-  <si>
-    <t>20080088</t>
-  </si>
-  <si>
-    <t>POKKA GREEN TEA 450</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>20037565</t>
-  </si>
-  <si>
-    <t>PUCUK/H TEH MLATI500</t>
-  </si>
-  <si>
-    <t>20048348</t>
-  </si>
-  <si>
-    <t>PUCUK/H TEH L/SGR500</t>
-  </si>
-  <si>
-    <t>20036157</t>
-  </si>
-  <si>
-    <t>SOSRO TEH BOTOL 450</t>
-  </si>
-  <si>
-    <t>20002203</t>
-  </si>
-  <si>
-    <t>SOSRO F.TEA APEL 500</t>
-  </si>
-  <si>
-    <t>20003698</t>
-  </si>
-  <si>
-    <t>SOSRO FR.TEA XTRM500</t>
-  </si>
-  <si>
-    <t>20002205</t>
-  </si>
-  <si>
-    <t>SOSRO F.TEA BLKCR500</t>
-  </si>
-  <si>
-    <t>20134046</t>
-  </si>
-  <si>
-    <t>FRUIT TEA FREEZE 500</t>
-  </si>
-  <si>
-    <t>20060210</t>
-  </si>
-  <si>
-    <t>IDM TEH HJAU MLT 330</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>20077509</t>
-  </si>
-  <si>
-    <t>IDM LEMON TEA 330ML</t>
-  </si>
-  <si>
-    <t>20126464</t>
-  </si>
-  <si>
-    <t>IDM TEH APL&amp;LYCHE350</t>
-  </si>
-  <si>
-    <t>20101897</t>
-  </si>
-  <si>
-    <t>IDM TEH APEL 350ML</t>
-  </si>
-  <si>
-    <t>20132840</t>
-  </si>
-  <si>
-    <t>IDM TEH BLCKCRRNT350</t>
-  </si>
-  <si>
-    <t>20066454</t>
-  </si>
-  <si>
-    <t>FRUIT TEA BLCKCR 350</t>
-  </si>
-  <si>
-    <t>20073495</t>
-  </si>
-  <si>
-    <t>FRUIT TEA FREEZE 350</t>
-  </si>
-  <si>
-    <t>20066455</t>
-  </si>
-  <si>
-    <t>FRUIT TEA APPLE 350</t>
-  </si>
-  <si>
-    <t>20079972</t>
-  </si>
-  <si>
-    <t>FRUIT TEA MRKISA 350</t>
-  </si>
-  <si>
-    <t>20060207</t>
-  </si>
-  <si>
-    <t>I/OCHA TEH MLATI 350</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>20048934</t>
-  </si>
-  <si>
-    <t>I/OCHA GRN TEA 350ML</t>
-  </si>
-  <si>
-    <t>20018904</t>
-  </si>
-  <si>
-    <t>NU GREEN TEA HNY 330</t>
-  </si>
-  <si>
-    <t>20053867</t>
-  </si>
-  <si>
-    <t>TEH GELAS BTL 350ML</t>
-  </si>
-  <si>
-    <t>20073396</t>
-  </si>
-  <si>
-    <t>S-TEE BTL 390ML</t>
-  </si>
-  <si>
-    <t>20072249</t>
-  </si>
-  <si>
-    <t>SOSRO TEH BOTOL 350</t>
-  </si>
-  <si>
-    <t>20122278</t>
-  </si>
-  <si>
-    <t>TEH BOTOL LS.SGR 350</t>
-  </si>
-  <si>
-    <t>20082395</t>
-  </si>
-  <si>
-    <t>TEH BOTOL TAWAR 350</t>
-  </si>
-  <si>
-    <t>RT,(E-3.5B)</t>
-  </si>
-  <si>
-    <t>20035484</t>
-  </si>
-  <si>
-    <t>PUCUK/H TEH MLATI350</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>20048155</t>
-  </si>
-  <si>
-    <t>PUCUK/H TEH L/SGR350</t>
-  </si>
-  <si>
-    <t>20026226</t>
-  </si>
-  <si>
-    <t>ULTRA TEH KOTAK 500</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>10036640</t>
-  </si>
-  <si>
-    <t>TEH KOTAK JASMINE300</t>
-  </si>
-  <si>
-    <t>20044334</t>
-  </si>
-  <si>
-    <t>SOSRO TEH BTL TPK300</t>
-  </si>
-  <si>
-    <t>10005128</t>
-  </si>
-  <si>
-    <t>SOSRO TEH KOTAK B250</t>
-  </si>
-  <si>
-    <t>20024315</t>
-  </si>
-  <si>
-    <t>TEH BOTOL LS.SGR 250</t>
-  </si>
-  <si>
-    <t>20002209</t>
-  </si>
-  <si>
-    <t>TEBS SPRK MIX FRT330</t>
-  </si>
-  <si>
-    <t>20048435</t>
-  </si>
-  <si>
-    <t>TEH KOTAK LESS/S 300</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>20100142</t>
-  </si>
-  <si>
-    <t>TEH KOTAK BLCKCR 300</t>
-  </si>
-  <si>
-    <t>20100143</t>
-  </si>
-  <si>
-    <t>TEH KOTAK APPLE 300</t>
-  </si>
-  <si>
-    <t>20137159</t>
-  </si>
-  <si>
-    <t>TEH KOTAK MANGGA 300</t>
-  </si>
-  <si>
-    <t>20087016</t>
-  </si>
-  <si>
-    <t>TEH KOTAK LEMON 300</t>
-  </si>
-  <si>
-    <t>20135647</t>
-  </si>
-  <si>
-    <t>TEH KOTAK LYCHEE 300</t>
-  </si>
-  <si>
-    <t>20117682</t>
-  </si>
-  <si>
-    <t>DLMNT BOBA RD.VEL240</t>
-  </si>
-  <si>
-    <t>20117687</t>
-  </si>
-  <si>
-    <t>DLMNT BOBA MTCHA 240</t>
-  </si>
-  <si>
-    <t>20003786</t>
-  </si>
-  <si>
-    <t>NU GREEN TEA HNY 450</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>20113059</t>
-  </si>
-  <si>
-    <t>NU YOGURT TEA 450ML</t>
-  </si>
-  <si>
-    <t>20139732</t>
-  </si>
-  <si>
-    <t>NU YOGRT TEA BRY 450</t>
-  </si>
-  <si>
-    <t>20012573</t>
-  </si>
-  <si>
-    <t>FRESTEA TEH MLATI500</t>
-  </si>
-  <si>
-    <t>20036765</t>
-  </si>
-  <si>
-    <t>FRESTEA GRN MADU 500</t>
-  </si>
-  <si>
-    <t>20012574</t>
-  </si>
-  <si>
-    <t>FRESTEA TEH APEL 500</t>
-  </si>
-  <si>
     <t>20138841</t>
   </si>
   <si>
@@ -1051,12 +1051,6 @@
     <t>MINUTE MAID ORG 300</t>
   </si>
   <si>
-    <t>20137939</t>
-  </si>
-  <si>
-    <t>FRUITMN FITT JLW 350</t>
-  </si>
-  <si>
     <t>20062818</t>
   </si>
   <si>
@@ -1081,6 +1075,18 @@
     <t>COCO BIT HOK.MLN 350</t>
   </si>
   <si>
+    <t>20141981</t>
+  </si>
+  <si>
+    <t>DUM2 CHO MILK TEA330</t>
+  </si>
+  <si>
+    <t>20141980</t>
+  </si>
+  <si>
+    <t>DUM2 RYL MILK TEA330</t>
+  </si>
+  <si>
     <t>20042848</t>
   </si>
   <si>
@@ -1309,12 +1315,6 @@
     <t>ULTRA SR ASAM SLM250</t>
   </si>
   <si>
-    <t>20136647</t>
-  </si>
-  <si>
-    <t>DIAMOND JC GUAVA 200</t>
-  </si>
-  <si>
     <t>20136649</t>
   </si>
   <si>
@@ -1405,715 +1405,715 @@
     <t>MINUTE M. NB ORG 300</t>
   </si>
   <si>
+    <t>20129123</t>
+  </si>
+  <si>
+    <t>OATSDE CHOCO 200</t>
+  </si>
+  <si>
+    <t>20129102</t>
+  </si>
+  <si>
+    <t>OATSDE BR.BLEND 200</t>
+  </si>
+  <si>
+    <t>20139295</t>
+  </si>
+  <si>
+    <t>BROOKFARM ORI 200ML</t>
+  </si>
+  <si>
+    <t>20139300</t>
+  </si>
+  <si>
+    <t>BROOKFARM MATCHA 200</t>
+  </si>
+  <si>
+    <t>20108987</t>
+  </si>
+  <si>
+    <t>V-SOY MULTI-GRAIN200</t>
+  </si>
+  <si>
+    <t>20123171</t>
+  </si>
+  <si>
+    <t>LACTASOY MILK CLG250</t>
+  </si>
+  <si>
+    <t>20135311</t>
+  </si>
+  <si>
+    <t>HYDROPL ISTNC JRK350</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>20069773</t>
+  </si>
+  <si>
+    <t>ISOPLUS BTL 350ML</t>
+  </si>
+  <si>
+    <t>20128918</t>
+  </si>
+  <si>
+    <t>ISOPLUS COCO 350ML</t>
+  </si>
+  <si>
+    <t>20138959</t>
+  </si>
+  <si>
+    <t>IF COCONUT WTR 350ML</t>
+  </si>
+  <si>
+    <t>20135600</t>
+  </si>
+  <si>
+    <t>ICHTAN THAI COCO 300</t>
+  </si>
+  <si>
+    <t>20138837</t>
+  </si>
+  <si>
+    <t>MZONE COCO BOOST 500</t>
+  </si>
+  <si>
+    <t>20094167</t>
+  </si>
+  <si>
+    <t>MIZONE MOOD UP 500</t>
+  </si>
+  <si>
+    <t>20094164</t>
+  </si>
+  <si>
+    <t>MIZONE ACTIVE 500ML</t>
+  </si>
+  <si>
+    <t>20038777</t>
+  </si>
+  <si>
+    <t>POCARI SWEAT 900ML</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>20009722</t>
+  </si>
+  <si>
+    <t>POCARI SWEAT 500ML</t>
+  </si>
+  <si>
+    <t>20118832</t>
+  </si>
+  <si>
+    <t>ION WATER BTL 500ML</t>
+  </si>
+  <si>
+    <t>20019674</t>
+  </si>
+  <si>
+    <t>YOU C1000 ORG WTR500</t>
+  </si>
+  <si>
+    <t>20019673</t>
+  </si>
+  <si>
+    <t>YOU C1000 LMN WTR500</t>
+  </si>
+  <si>
+    <t>20141600</t>
+  </si>
+  <si>
+    <t>IDM ISOTONC FRUIT350</t>
+  </si>
+  <si>
+    <t>20141601</t>
+  </si>
+  <si>
+    <t>IDM ISOTONC LYCHE350</t>
+  </si>
+  <si>
+    <t>20015838</t>
+  </si>
+  <si>
+    <t>POCARI SWEAT 350ML</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>20065248</t>
+  </si>
+  <si>
+    <t>ION WATER BTL 350ML</t>
+  </si>
+  <si>
+    <t>20057867</t>
+  </si>
+  <si>
+    <t>HYDRO COCO 500ML</t>
+  </si>
+  <si>
+    <t>20119876</t>
+  </si>
+  <si>
+    <t>HYDR.COCO VITA-D 330</t>
+  </si>
+  <si>
+    <t>20018435</t>
+  </si>
+  <si>
+    <t>HYDRO COCO 250ML</t>
+  </si>
+  <si>
+    <t>20115548</t>
+  </si>
+  <si>
+    <t>IDM COCONUT WTR 250</t>
+  </si>
+  <si>
+    <t>20128561</t>
+  </si>
+  <si>
+    <t>IDM CCNT WTR ORGE250</t>
+  </si>
+  <si>
+    <t>20089821</t>
+  </si>
+  <si>
+    <t>ORONAMIN C DRINK 120</t>
+  </si>
+  <si>
+    <t>RT,(E-1.5B)</t>
+  </si>
+  <si>
+    <t>20115549</t>
+  </si>
+  <si>
+    <t>FIBE MINI 100ML</t>
+  </si>
+  <si>
+    <t>20009737</t>
+  </si>
+  <si>
+    <t>YOU C1000 DRK ORG140</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>10039897</t>
+  </si>
+  <si>
+    <t>YOU C1000 DRK LMN140</t>
+  </si>
+  <si>
+    <t>20032519</t>
+  </si>
+  <si>
+    <t>YOU C1000 DRK APL140</t>
+  </si>
+  <si>
+    <t>20115636</t>
+  </si>
+  <si>
+    <t>YOU C1000 DRK MGO140</t>
+  </si>
+  <si>
+    <t>20113135</t>
+  </si>
+  <si>
+    <t>AMUNIZER BTL 140ML</t>
+  </si>
+  <si>
+    <t>20048546</t>
+  </si>
+  <si>
+    <t>HEMAVITON C1000 330</t>
+  </si>
+  <si>
+    <t>20103178</t>
+  </si>
+  <si>
+    <t>HMVTON C1000 LSO 330</t>
+  </si>
+  <si>
+    <t>20103368</t>
+  </si>
+  <si>
+    <t>HMVTON C1000 LMN 330</t>
+  </si>
+  <si>
+    <t>20128794</t>
+  </si>
+  <si>
+    <t>NS/GOODNES KURMA 189</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>20103718</t>
+  </si>
+  <si>
+    <t>TJH KURMA SUSU KR189</t>
+  </si>
+  <si>
+    <t>20124409</t>
+  </si>
+  <si>
+    <t>INDOMLK STRL HNY 189</t>
+  </si>
+  <si>
+    <t>20136193</t>
+  </si>
+  <si>
+    <t>SO GOOD SUSU STRL189</t>
+  </si>
+  <si>
+    <t>20133805</t>
+  </si>
+  <si>
+    <t>ENTRASOL STERIL 180</t>
+  </si>
+  <si>
+    <t>20134968</t>
+  </si>
+  <si>
+    <t>COLLAGENA STERIL189</t>
+  </si>
+  <si>
+    <t>20140174</t>
+  </si>
+  <si>
+    <t>BEAR BRAND CLGEN 189</t>
+  </si>
+  <si>
+    <t>10004906</t>
+  </si>
+  <si>
+    <t>BEAR BRAND STERIL189</t>
+  </si>
+  <si>
+    <t>20136952</t>
+  </si>
+  <si>
+    <t>V-SOY SOYA BEAN 300</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>20048096</t>
+  </si>
+  <si>
+    <t>20038726</t>
+  </si>
+  <si>
+    <t>NARAYA KDLAI BTL320</t>
+  </si>
+  <si>
+    <t>20107748</t>
+  </si>
+  <si>
+    <t>MILKU SUSU CKLT 200</t>
+  </si>
+  <si>
+    <t>20107749</t>
+  </si>
+  <si>
+    <t>MILKU SUSU STRO 200</t>
+  </si>
+  <si>
+    <t>20141102</t>
+  </si>
+  <si>
+    <t>MILKU UHT MARIE 200</t>
+  </si>
+  <si>
+    <t>20134047</t>
+  </si>
+  <si>
+    <t>MILKU SUSU ORGNAL200</t>
+  </si>
+  <si>
+    <t>10003373</t>
+  </si>
+  <si>
+    <t>INDOMILK CAIR CHO190</t>
+  </si>
+  <si>
+    <t>10003426</t>
+  </si>
+  <si>
+    <t>INDOMILK CAIR STW190</t>
+  </si>
+  <si>
+    <t>10004443</t>
+  </si>
+  <si>
+    <t>INDOMILK UHT CKL 180</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>10004442</t>
+  </si>
+  <si>
+    <t>INDOMLK UHT STRW 180</t>
+  </si>
+  <si>
+    <t>20070569</t>
+  </si>
+  <si>
+    <t>INDOMLK BANANA 180</t>
+  </si>
+  <si>
+    <t>20134956</t>
+  </si>
+  <si>
+    <t>INDOMILK GOGUMA 180</t>
+  </si>
+  <si>
+    <t>20127735</t>
+  </si>
+  <si>
+    <t>INDMLK DLGNA COFF180</t>
+  </si>
+  <si>
+    <t>20126193</t>
+  </si>
+  <si>
+    <t>INDOMLK COFFE/LTE180</t>
+  </si>
+  <si>
+    <t>20125062</t>
+  </si>
+  <si>
+    <t>INDOMLK KR.BNANA 180</t>
+  </si>
+  <si>
+    <t>20132659</t>
+  </si>
+  <si>
+    <t>INDOMLK HK LYCHEE180</t>
+  </si>
+  <si>
+    <t>20091807</t>
+  </si>
+  <si>
+    <t>DIAMOND UHT CKLT 200</t>
+  </si>
+  <si>
+    <t>20136644</t>
+  </si>
+  <si>
+    <t>DIAMOND UHT MARSM200</t>
+  </si>
+  <si>
+    <t>20137977</t>
+  </si>
+  <si>
+    <t>DIAMOND UHT BBLGM200</t>
+  </si>
+  <si>
+    <t>20032643</t>
+  </si>
+  <si>
+    <t>ULTRA LOW FAT COK250</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>20032644</t>
+  </si>
+  <si>
+    <t>ULTRA LOW FAT PLN250</t>
+  </si>
+  <si>
+    <t>20130186</t>
+  </si>
+  <si>
+    <t>GRNFLD UHT CHOCO 250</t>
+  </si>
+  <si>
+    <t>20118209</t>
+  </si>
+  <si>
+    <t>GRNFLD UHT STRAW 250</t>
+  </si>
+  <si>
+    <t>20087413</t>
+  </si>
+  <si>
+    <t>GRNFLD UHT F.CRM 250</t>
+  </si>
+  <si>
+    <t>20138916</t>
+  </si>
+  <si>
+    <t>CIMORY THAI TEA 250</t>
+  </si>
+  <si>
+    <t>20136951</t>
+  </si>
+  <si>
+    <t>CMORY UHT MATCHA 250</t>
+  </si>
+  <si>
+    <t>RT,(E-0.5B)</t>
+  </si>
+  <si>
+    <t>20140795</t>
+  </si>
+  <si>
+    <t>CIMORY UHT CHOCO 225</t>
+  </si>
+  <si>
+    <t>20140794</t>
+  </si>
+  <si>
+    <t>CIMORY UHT MARIE 225</t>
+  </si>
+  <si>
+    <t>20140793</t>
+  </si>
+  <si>
+    <t>CIMORY UHT MTCHA 225</t>
+  </si>
+  <si>
+    <t>20122822</t>
+  </si>
+  <si>
+    <t>CMORY UHT MARIE 250</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>20115187</t>
+  </si>
+  <si>
+    <t>CMORY UHT HZLNUT 250</t>
+  </si>
+  <si>
+    <t>20115188</t>
+  </si>
+  <si>
+    <t>CMORY UHT ALMND 250</t>
+  </si>
+  <si>
+    <t>20104637</t>
+  </si>
+  <si>
+    <t>CIMORY UHT CSHEW 250</t>
+  </si>
+  <si>
+    <t>20099571</t>
+  </si>
+  <si>
+    <t>CIMORY UHT CHOCO 250</t>
+  </si>
+  <si>
+    <t>20104636</t>
+  </si>
+  <si>
+    <t>CIMORY UHT CHOML 250</t>
+  </si>
+  <si>
+    <t>20129109</t>
+  </si>
+  <si>
+    <t>CIMORY CHO.TRMSU 250</t>
+  </si>
+  <si>
+    <t>20099572</t>
+  </si>
+  <si>
+    <t>CIMORY UHT STRAW 250</t>
+  </si>
+  <si>
+    <t>20134390</t>
+  </si>
+  <si>
+    <t>CIMORY BBS LKTSA 250</t>
+  </si>
+  <si>
+    <t>20025753</t>
+  </si>
+  <si>
+    <t>F/F L/FAT COK TPK225</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>20088875</t>
+  </si>
+  <si>
+    <t>FF SWT.DLGHT TPK 225</t>
+  </si>
+  <si>
+    <t>20070253</t>
+  </si>
+  <si>
+    <t>FF COCONUT TPK 225ML</t>
+  </si>
+  <si>
+    <t>20034079</t>
+  </si>
+  <si>
+    <t>F/FLAG COKLT TPK 225</t>
+  </si>
+  <si>
+    <t>20034078</t>
+  </si>
+  <si>
+    <t>F/FLAG STRWB TPK 225</t>
+  </si>
+  <si>
+    <t>20034077</t>
+  </si>
+  <si>
+    <t>F/F FULL CRM TPK 225</t>
+  </si>
+  <si>
+    <t>20128754</t>
+  </si>
+  <si>
+    <t>FF SS.SEREAL CKL 225</t>
+  </si>
+  <si>
+    <t>20136769</t>
+  </si>
+  <si>
+    <t>F.FLAG UHT BERIS 225</t>
+  </si>
+  <si>
+    <t>20136768</t>
+  </si>
+  <si>
+    <t>F.FLAG UHT MATCH 225</t>
+  </si>
+  <si>
+    <t>10004669</t>
+  </si>
+  <si>
+    <t>ULTRA UHT CHOCO 250M</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>10004668</t>
+  </si>
+  <si>
+    <t>ULTRA UHT STRAW 250M</t>
+  </si>
+  <si>
+    <t>10004676</t>
+  </si>
+  <si>
+    <t>ULTRA PLAIN SLIM250M</t>
+  </si>
+  <si>
+    <t>10007380</t>
+  </si>
+  <si>
+    <t>ULTRA SLIM COKLAT200</t>
+  </si>
+  <si>
+    <t>10008095</t>
+  </si>
+  <si>
+    <t>ULTRA SLIM STRAW 200</t>
+  </si>
+  <si>
+    <t>10007379</t>
+  </si>
+  <si>
+    <t>ULTRA SLIM PLAIN 200</t>
+  </si>
+  <si>
+    <t>20090189</t>
+  </si>
+  <si>
+    <t>ULTRA SUSU KRML 200</t>
+  </si>
+  <si>
+    <t>20088964</t>
+  </si>
+  <si>
+    <t>ULTRA SUSU TARO 200</t>
+  </si>
+  <si>
+    <t>20138895</t>
+  </si>
+  <si>
+    <t>ULTRA UHT BLUBRY 200</t>
+  </si>
+  <si>
+    <t>20110968</t>
+  </si>
+  <si>
+    <t>MUJIGAE BNNA MLK 250</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>20110967</t>
+  </si>
+  <si>
+    <t>MUJIGAE CHOC BAN 250</t>
+  </si>
+  <si>
+    <t>20126897</t>
+  </si>
+  <si>
+    <t>MUJIGAE STRW BAN 250</t>
+  </si>
+  <si>
+    <t>20138050</t>
+  </si>
+  <si>
+    <t>MUJIGAE WTRMLN 250</t>
+  </si>
+  <si>
+    <t>20130518</t>
+  </si>
+  <si>
+    <t>TS ALMND.CHOCO 190ML</t>
+  </si>
+  <si>
+    <t>20118377</t>
+  </si>
+  <si>
+    <t>TS OAT VANILLA 190ML</t>
+  </si>
+  <si>
+    <t>20135795</t>
+  </si>
+  <si>
+    <t>TS COLLGN PEACH190ML</t>
+  </si>
+  <si>
+    <t>20135463</t>
+  </si>
+  <si>
+    <t>DNCW MLKY CHO.HZL180</t>
+  </si>
+  <si>
     <t>20135462</t>
   </si>
   <si>
     <t>DNCW MLKY CKS&amp;CRM180</t>
-  </si>
-  <si>
-    <t>20135463</t>
-  </si>
-  <si>
-    <t>DNCW MLKY CHO.HZL180</t>
-  </si>
-  <si>
-    <t>20139295</t>
-  </si>
-  <si>
-    <t>BROOKFARM ORI 200ML</t>
-  </si>
-  <si>
-    <t>20139300</t>
-  </si>
-  <si>
-    <t>BROOKFARM MATCHA 200</t>
-  </si>
-  <si>
-    <t>20108987</t>
-  </si>
-  <si>
-    <t>V-SOY MULTI-GRAIN200</t>
-  </si>
-  <si>
-    <t>20123171</t>
-  </si>
-  <si>
-    <t>LACTASOY MILK CLG250</t>
-  </si>
-  <si>
-    <t>20135311</t>
-  </si>
-  <si>
-    <t>HYDROPL ISTNC JRK350</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>20069773</t>
-  </si>
-  <si>
-    <t>ISOPLUS BTL 350ML</t>
-  </si>
-  <si>
-    <t>20128918</t>
-  </si>
-  <si>
-    <t>ISOPLUS COCO 350ML</t>
-  </si>
-  <si>
-    <t>20138959</t>
-  </si>
-  <si>
-    <t>IF COCONUT WTR 350ML</t>
-  </si>
-  <si>
-    <t>20135600</t>
-  </si>
-  <si>
-    <t>ICHTAN THAI COCO 300</t>
-  </si>
-  <si>
-    <t>20138837</t>
-  </si>
-  <si>
-    <t>MZONE COCO BOOST 500</t>
-  </si>
-  <si>
-    <t>20094167</t>
-  </si>
-  <si>
-    <t>MIZONE MOOD UP 500</t>
-  </si>
-  <si>
-    <t>20094164</t>
-  </si>
-  <si>
-    <t>MIZONE ACTIVE 500ML</t>
-  </si>
-  <si>
-    <t>20038777</t>
-  </si>
-  <si>
-    <t>POCARI SWEAT 900ML</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>20009722</t>
-  </si>
-  <si>
-    <t>POCARI SWEAT 500ML</t>
-  </si>
-  <si>
-    <t>20118832</t>
-  </si>
-  <si>
-    <t>ION WATER BTL 500ML</t>
-  </si>
-  <si>
-    <t>20019674</t>
-  </si>
-  <si>
-    <t>YOU C1000 ORG WTR500</t>
-  </si>
-  <si>
-    <t>20019673</t>
-  </si>
-  <si>
-    <t>YOU C1000 LMN WTR500</t>
-  </si>
-  <si>
-    <t>20141600</t>
-  </si>
-  <si>
-    <t>IDM ISOTONC FRUIT350</t>
-  </si>
-  <si>
-    <t>20141601</t>
-  </si>
-  <si>
-    <t>IDM ISOTONC LYCHE350</t>
-  </si>
-  <si>
-    <t>20015838</t>
-  </si>
-  <si>
-    <t>POCARI SWEAT 350ML</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>20065248</t>
-  </si>
-  <si>
-    <t>ION WATER BTL 350ML</t>
-  </si>
-  <si>
-    <t>20057867</t>
-  </si>
-  <si>
-    <t>HYDRO COCO 500ML</t>
-  </si>
-  <si>
-    <t>20119876</t>
-  </si>
-  <si>
-    <t>HYDR.COCO VITA-D 330</t>
-  </si>
-  <si>
-    <t>20018435</t>
-  </si>
-  <si>
-    <t>HYDRO COCO 250ML</t>
-  </si>
-  <si>
-    <t>20115548</t>
-  </si>
-  <si>
-    <t>IDM COCONUT WTR 250</t>
-  </si>
-  <si>
-    <t>20128561</t>
-  </si>
-  <si>
-    <t>IDM CCNT WTR ORGE250</t>
-  </si>
-  <si>
-    <t>20089821</t>
-  </si>
-  <si>
-    <t>ORONAMIN C DRINK 120</t>
-  </si>
-  <si>
-    <t>RT,(E-1.5B)</t>
-  </si>
-  <si>
-    <t>20115549</t>
-  </si>
-  <si>
-    <t>FIBE MINI 100ML</t>
-  </si>
-  <si>
-    <t>20009737</t>
-  </si>
-  <si>
-    <t>YOU C1000 DRK ORG140</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>10039897</t>
-  </si>
-  <si>
-    <t>YOU C1000 DRK LMN140</t>
-  </si>
-  <si>
-    <t>20032519</t>
-  </si>
-  <si>
-    <t>YOU C1000 DRK APL140</t>
-  </si>
-  <si>
-    <t>20115636</t>
-  </si>
-  <si>
-    <t>YOU C1000 DRK MGO140</t>
-  </si>
-  <si>
-    <t>20113135</t>
-  </si>
-  <si>
-    <t>AMUNIZER BTL 140ML</t>
-  </si>
-  <si>
-    <t>20048546</t>
-  </si>
-  <si>
-    <t>HEMAVITON C1000 330</t>
-  </si>
-  <si>
-    <t>20103178</t>
-  </si>
-  <si>
-    <t>HMVTON C1000 LSO 330</t>
-  </si>
-  <si>
-    <t>20103368</t>
-  </si>
-  <si>
-    <t>HMVTON C1000 LMN 330</t>
-  </si>
-  <si>
-    <t>20128794</t>
-  </si>
-  <si>
-    <t>NS/GOODNES KURMA 189</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>20103718</t>
-  </si>
-  <si>
-    <t>TJH KURMA SUSU KR189</t>
-  </si>
-  <si>
-    <t>20124409</t>
-  </si>
-  <si>
-    <t>INDOMLK STRL HNY 189</t>
-  </si>
-  <si>
-    <t>20136193</t>
-  </si>
-  <si>
-    <t>SO GOOD SUSU STRL189</t>
-  </si>
-  <si>
-    <t>20133805</t>
-  </si>
-  <si>
-    <t>ENTRASOL STERIL 180</t>
-  </si>
-  <si>
-    <t>20134968</t>
-  </si>
-  <si>
-    <t>COLLAGENA STERIL189</t>
-  </si>
-  <si>
-    <t>20140174</t>
-  </si>
-  <si>
-    <t>BEAR BRAND CLGEN 189</t>
-  </si>
-  <si>
-    <t>10004906</t>
-  </si>
-  <si>
-    <t>BEAR BRAND STERIL189</t>
-  </si>
-  <si>
-    <t>20136952</t>
-  </si>
-  <si>
-    <t>V-SOY SOYA BEAN 300</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>20048096</t>
-  </si>
-  <si>
-    <t>20038726</t>
-  </si>
-  <si>
-    <t>NARAYA KDLAI BTL320</t>
-  </si>
-  <si>
-    <t>20107748</t>
-  </si>
-  <si>
-    <t>MILKU SUSU CKLT 200</t>
-  </si>
-  <si>
-    <t>20107749</t>
-  </si>
-  <si>
-    <t>MILKU SUSU STRO 200</t>
-  </si>
-  <si>
-    <t>20141102</t>
-  </si>
-  <si>
-    <t>MILKU UHT MARIE 200</t>
-  </si>
-  <si>
-    <t>20134047</t>
-  </si>
-  <si>
-    <t>MILKU SUSU ORGNAL200</t>
-  </si>
-  <si>
-    <t>10003373</t>
-  </si>
-  <si>
-    <t>INDOMILK CAIR CHO190</t>
-  </si>
-  <si>
-    <t>10003426</t>
-  </si>
-  <si>
-    <t>INDOMILK CAIR STW190</t>
-  </si>
-  <si>
-    <t>10004443</t>
-  </si>
-  <si>
-    <t>INDOMILK UHT CKL 180</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>10004442</t>
-  </si>
-  <si>
-    <t>INDOMLK UHT STRW 180</t>
-  </si>
-  <si>
-    <t>20070569</t>
-  </si>
-  <si>
-    <t>INDOMLK BANANA 180</t>
-  </si>
-  <si>
-    <t>20134956</t>
-  </si>
-  <si>
-    <t>INDOMILK GOGUMA 180</t>
-  </si>
-  <si>
-    <t>20127735</t>
-  </si>
-  <si>
-    <t>INDMLK DLGNA COFF180</t>
-  </si>
-  <si>
-    <t>20126193</t>
-  </si>
-  <si>
-    <t>INDOMLK COFFE/LTE180</t>
-  </si>
-  <si>
-    <t>20125062</t>
-  </si>
-  <si>
-    <t>INDOMLK KR.BNANA 180</t>
-  </si>
-  <si>
-    <t>20132659</t>
-  </si>
-  <si>
-    <t>INDOMLK HK LYCHEE180</t>
-  </si>
-  <si>
-    <t>20091807</t>
-  </si>
-  <si>
-    <t>DIAMOND UHT CKLT 200</t>
-  </si>
-  <si>
-    <t>20136644</t>
-  </si>
-  <si>
-    <t>DIAMOND UHT MARSM200</t>
-  </si>
-  <si>
-    <t>20137977</t>
-  </si>
-  <si>
-    <t>DIAMOND UHT BBLGM200</t>
-  </si>
-  <si>
-    <t>20032643</t>
-  </si>
-  <si>
-    <t>ULTRA LOW FAT COK250</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>20032644</t>
-  </si>
-  <si>
-    <t>ULTRA LOW FAT PLN250</t>
-  </si>
-  <si>
-    <t>20130186</t>
-  </si>
-  <si>
-    <t>GRNFLD UHT CHOCO 250</t>
-  </si>
-  <si>
-    <t>20118209</t>
-  </si>
-  <si>
-    <t>GRNFLD UHT STRAW 250</t>
-  </si>
-  <si>
-    <t>20087413</t>
-  </si>
-  <si>
-    <t>GRNFLD UHT F.CRM 250</t>
-  </si>
-  <si>
-    <t>20138916</t>
-  </si>
-  <si>
-    <t>CIMORY THAI TEA 250</t>
-  </si>
-  <si>
-    <t>20136951</t>
-  </si>
-  <si>
-    <t>CMORY UHT MATCHA 250</t>
-  </si>
-  <si>
-    <t>RT,(E-0.5B)</t>
-  </si>
-  <si>
-    <t>20140795</t>
-  </si>
-  <si>
-    <t>CIMORY UHT CHOCO 225</t>
-  </si>
-  <si>
-    <t>20140794</t>
-  </si>
-  <si>
-    <t>CIMORY UHT MARIE 225</t>
-  </si>
-  <si>
-    <t>20140793</t>
-  </si>
-  <si>
-    <t>CIMORY UHT MTCHA 225</t>
-  </si>
-  <si>
-    <t>20122822</t>
-  </si>
-  <si>
-    <t>CMORY UHT MARIE 250</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>20115187</t>
-  </si>
-  <si>
-    <t>CMORY UHT HZLNUT 250</t>
-  </si>
-  <si>
-    <t>20115188</t>
-  </si>
-  <si>
-    <t>CMORY UHT ALMND 250</t>
-  </si>
-  <si>
-    <t>20104637</t>
-  </si>
-  <si>
-    <t>CIMORY UHT CSHEW 250</t>
-  </si>
-  <si>
-    <t>20099571</t>
-  </si>
-  <si>
-    <t>CIMORY UHT CHOCO 250</t>
-  </si>
-  <si>
-    <t>20104636</t>
-  </si>
-  <si>
-    <t>CIMORY UHT CHOML 250</t>
-  </si>
-  <si>
-    <t>20129109</t>
-  </si>
-  <si>
-    <t>CIMORY CHO.TRMSU 250</t>
-  </si>
-  <si>
-    <t>20099572</t>
-  </si>
-  <si>
-    <t>CIMORY UHT STRAW 250</t>
-  </si>
-  <si>
-    <t>20134390</t>
-  </si>
-  <si>
-    <t>CIMORY BBS LKTSA 250</t>
-  </si>
-  <si>
-    <t>20025753</t>
-  </si>
-  <si>
-    <t>F/F L/FAT COK TPK225</t>
-  </si>
-  <si>
-    <t>38</t>
-  </si>
-  <si>
-    <t>20088875</t>
-  </si>
-  <si>
-    <t>FF SWT.DLGHT TPK 225</t>
-  </si>
-  <si>
-    <t>20070253</t>
-  </si>
-  <si>
-    <t>FF COCONUT TPK 225ML</t>
-  </si>
-  <si>
-    <t>20034079</t>
-  </si>
-  <si>
-    <t>F/FLAG COKLT TPK 225</t>
-  </si>
-  <si>
-    <t>20034078</t>
-  </si>
-  <si>
-    <t>F/FLAG STRWB TPK 225</t>
-  </si>
-  <si>
-    <t>20034077</t>
-  </si>
-  <si>
-    <t>F/F FULL CRM TPK 225</t>
-  </si>
-  <si>
-    <t>20128754</t>
-  </si>
-  <si>
-    <t>FF SS.SEREAL CKL 225</t>
-  </si>
-  <si>
-    <t>20136769</t>
-  </si>
-  <si>
-    <t>F.FLAG UHT BERIS 225</t>
-  </si>
-  <si>
-    <t>20136768</t>
-  </si>
-  <si>
-    <t>F.FLAG UHT MATCH 225</t>
-  </si>
-  <si>
-    <t>10004669</t>
-  </si>
-  <si>
-    <t>ULTRA UHT CHOCO 250M</t>
-  </si>
-  <si>
-    <t>39</t>
-  </si>
-  <si>
-    <t>10004668</t>
-  </si>
-  <si>
-    <t>ULTRA UHT STRAW 250M</t>
-  </si>
-  <si>
-    <t>10004676</t>
-  </si>
-  <si>
-    <t>ULTRA PLAIN SLIM250M</t>
-  </si>
-  <si>
-    <t>10007380</t>
-  </si>
-  <si>
-    <t>ULTRA SLIM COKLAT200</t>
-  </si>
-  <si>
-    <t>10008095</t>
-  </si>
-  <si>
-    <t>ULTRA SLIM STRAW 200</t>
-  </si>
-  <si>
-    <t>10007379</t>
-  </si>
-  <si>
-    <t>ULTRA SLIM PLAIN 200</t>
-  </si>
-  <si>
-    <t>20090189</t>
-  </si>
-  <si>
-    <t>ULTRA SUSU KRML 200</t>
-  </si>
-  <si>
-    <t>20088964</t>
-  </si>
-  <si>
-    <t>ULTRA SUSU TARO 200</t>
-  </si>
-  <si>
-    <t>20138895</t>
-  </si>
-  <si>
-    <t>ULTRA UHT BLUBRY 200</t>
-  </si>
-  <si>
-    <t>20110968</t>
-  </si>
-  <si>
-    <t>MUJIGAE BNNA MLK 250</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>20110967</t>
-  </si>
-  <si>
-    <t>MUJIGAE CHOC BAN 250</t>
-  </si>
-  <si>
-    <t>20126897</t>
-  </si>
-  <si>
-    <t>MUJIGAE STRW BAN 250</t>
-  </si>
-  <si>
-    <t>20138050</t>
-  </si>
-  <si>
-    <t>MUJIGAE WTRMLN 250</t>
-  </si>
-  <si>
-    <t>20130518</t>
-  </si>
-  <si>
-    <t>TS ALMND.CHOCO 190ML</t>
-  </si>
-  <si>
-    <t>20118377</t>
-  </si>
-  <si>
-    <t>TS OAT VANILLA 190ML</t>
-  </si>
-  <si>
-    <t>20135795</t>
-  </si>
-  <si>
-    <t>TS COLLGN PEACH190ML</t>
-  </si>
-  <si>
-    <t>20129102</t>
-  </si>
-  <si>
-    <t>OATSDE BR.BLEND 200</t>
-  </si>
-  <si>
-    <t>20129123</t>
-  </si>
-  <si>
-    <t>OATSDE CHOCO 200</t>
   </si>
   <si>
     <t>20037974</t>
@@ -2925,15 +2925,15 @@
         <v>14</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
@@ -2945,15 +2945,15 @@
         <v>17</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
@@ -2970,10 +2970,10 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
@@ -2982,7 +2982,7 @@
         <v>8</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>23</v>
@@ -2990,10 +2990,10 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
@@ -3002,7 +3002,7 @@
         <v>8</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>23</v>
@@ -3010,10 +3010,10 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
@@ -3030,10 +3030,10 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
@@ -3050,10 +3050,10 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
@@ -3070,10 +3070,10 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
@@ -3090,10 +3090,10 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
@@ -3110,10 +3110,10 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
@@ -3130,10 +3130,10 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
@@ -3142,7 +3142,7 @@
         <v>11</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>5</v>
@@ -3150,10 +3150,10 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
@@ -3162,7 +3162,7 @@
         <v>11</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>5</v>
@@ -3170,10 +3170,10 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
@@ -3190,10 +3190,10 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
@@ -3210,10 +3210,10 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
@@ -3230,10 +3230,10 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
@@ -3250,10 +3250,10 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
@@ -3262,18 +3262,18 @@
         <v>14</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
@@ -3282,10 +3282,10 @@
         <v>14</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>70</v>
+        <v>28</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -3305,7 +3305,7 @@
         <v>4</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>70</v>
+        <v>28</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -3325,7 +3325,7 @@
         <v>8</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>70</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -3345,7 +3345,7 @@
         <v>11</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>70</v>
+        <v>28</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -3365,7 +3365,7 @@
         <v>14</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>70</v>
+        <v>28</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -3422,7 +3422,7 @@
         <v>17</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>81</v>
@@ -3442,7 +3442,7 @@
         <v>17</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>81</v>
@@ -3465,7 +3465,7 @@
         <v>4</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>70</v>
+        <v>23</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -3485,7 +3485,7 @@
         <v>8</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -3505,7 +3505,7 @@
         <v>11</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>70</v>
+        <v>23</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -3565,7 +3565,7 @@
         <v>20</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>23</v>
+        <v>81</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -3582,7 +3582,7 @@
         <v>20</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>81</v>
@@ -3602,7 +3602,7 @@
         <v>20</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>81</v>
@@ -3619,7 +3619,7 @@
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>4</v>
@@ -3639,7 +3639,7 @@
         <v>3</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>8</v>
@@ -3659,13 +3659,13 @@
         <v>3</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -3679,13 +3679,13 @@
         <v>3</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -3699,13 +3699,13 @@
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>17</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>70</v>
+        <v>28</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -3719,7 +3719,7 @@
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>4</v>
@@ -3739,7 +3739,7 @@
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>8</v>
@@ -3759,7 +3759,7 @@
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>11</v>
@@ -3779,7 +3779,7 @@
         <v>3</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>14</v>
@@ -3799,13 +3799,13 @@
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>17</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -3825,7 +3825,7 @@
         <v>4</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -3942,7 +3942,7 @@
         <v>126</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>23</v>
@@ -3962,7 +3962,7 @@
         <v>126</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>23</v>
@@ -4005,7 +4005,7 @@
         <v>4</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -4025,7 +4025,7 @@
         <v>8</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -4045,7 +4045,7 @@
         <v>11</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -4065,7 +4065,7 @@
         <v>14</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -4085,7 +4085,7 @@
         <v>17</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -4122,7 +4122,7 @@
         <v>145</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>23</v>
@@ -4142,7 +4142,7 @@
         <v>145</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>23</v>
@@ -4245,7 +4245,7 @@
         <v>17</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -4282,7 +4282,7 @@
         <v>162</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>23</v>
@@ -4305,7 +4305,7 @@
         <v>4</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -4325,7 +4325,7 @@
         <v>8</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -4345,7 +4345,7 @@
         <v>11</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -4385,7 +4385,7 @@
         <v>17</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -4405,7 +4405,7 @@
         <v>20</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -4422,10 +4422,10 @@
         <v>178</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
@@ -4442,10 +4442,10 @@
         <v>178</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -4505,7 +4505,7 @@
         <v>4</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>70</v>
+        <v>28</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -4525,7 +4525,7 @@
         <v>8</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>70</v>
+        <v>28</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -4605,7 +4605,7 @@
         <v>20</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>70</v>
+        <v>28</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -4622,7 +4622,7 @@
         <v>199</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>23</v>
@@ -4642,7 +4642,7 @@
         <v>199</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>23</v>
@@ -4659,33 +4659,33 @@
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>126</v>
+        <v>4</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>81</v>
+        <v>31</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D99" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="B99" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="C99" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>218</v>
-      </c>
       <c r="E99" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -4699,10 +4699,10 @@
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>23</v>
@@ -4719,10 +4719,10 @@
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>23</v>
@@ -4739,10 +4739,10 @@
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>23</v>
@@ -4759,10 +4759,10 @@
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>23</v>
@@ -4779,10 +4779,10 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>23</v>
@@ -4799,10 +4799,10 @@
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>23</v>
@@ -4819,30 +4819,30 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>218</v>
+        <v>233</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>23</v>
+        <v>163</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D107" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="B107" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="C107" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D107" s="1" t="s">
-        <v>235</v>
-      </c>
       <c r="E107" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>163</v>
@@ -4859,10 +4859,10 @@
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>163</v>
@@ -4879,10 +4879,10 @@
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>163</v>
@@ -4899,10 +4899,10 @@
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>163</v>
@@ -4919,13 +4919,13 @@
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>163</v>
+        <v>23</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -4939,10 +4939,10 @@
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>23</v>
@@ -4959,10 +4959,10 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>23</v>
@@ -4979,10 +4979,10 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>40</v>
+        <v>126</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>23</v>
@@ -4999,10 +4999,10 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>235</v>
+        <v>252</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>126</v>
+        <v>4</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>23</v>
@@ -5010,19 +5010,19 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D116" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="B116" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="C116" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D116" s="1" t="s">
-        <v>254</v>
-      </c>
       <c r="E116" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>23</v>
@@ -5039,10 +5039,10 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>23</v>
@@ -5059,10 +5059,10 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>23</v>
@@ -5079,10 +5079,10 @@
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>23</v>
@@ -5099,10 +5099,10 @@
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>23</v>
@@ -5119,10 +5119,10 @@
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>23</v>
@@ -5139,50 +5139,50 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>23</v>
+        <v>267</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>254</v>
+        <v>270</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>269</v>
+        <v>23</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D124" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="B124" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="C124" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D124" s="1" t="s">
-        <v>272</v>
-      </c>
       <c r="E124" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>23</v>
@@ -5199,10 +5199,10 @@
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>23</v>
@@ -5210,19 +5210,19 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D126" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="B126" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="C126" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D126" s="1" t="s">
-        <v>277</v>
-      </c>
       <c r="E126" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>23</v>
@@ -5239,10 +5239,10 @@
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>23</v>
@@ -5259,10 +5259,10 @@
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>23</v>
@@ -5279,10 +5279,10 @@
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>23</v>
@@ -5299,10 +5299,10 @@
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>23</v>
@@ -5319,10 +5319,10 @@
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>277</v>
+        <v>288</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>23</v>
@@ -5330,19 +5330,19 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D132" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="B132" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="C132" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D132" s="1" t="s">
-        <v>290</v>
-      </c>
       <c r="E132" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>23</v>
@@ -5359,10 +5359,10 @@
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>23</v>
@@ -5379,10 +5379,10 @@
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>23</v>
@@ -5399,10 +5399,10 @@
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>23</v>
@@ -5419,10 +5419,10 @@
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>23</v>
@@ -5439,13 +5439,13 @@
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
@@ -5459,13 +5459,13 @@
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>70</v>
+        <v>28</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
@@ -5479,30 +5479,30 @@
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>70</v>
+        <v>23</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D140" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="B140" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="C140" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D140" s="1" t="s">
-        <v>307</v>
-      </c>
       <c r="E140" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>23</v>
@@ -5519,10 +5519,10 @@
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>23</v>
@@ -5539,13 +5539,13 @@
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
@@ -5559,10 +5559,10 @@
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>5</v>
@@ -5579,10 +5579,10 @@
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>5</v>
@@ -5599,13 +5599,13 @@
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
@@ -5619,10 +5619,10 @@
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>23</v>
@@ -5745,7 +5745,7 @@
         <v>20</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
@@ -5762,7 +5762,7 @@
         <v>322</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>23</v>
@@ -5782,10 +5782,10 @@
         <v>322</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
@@ -5805,7 +5805,7 @@
         <v>126</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
@@ -5882,7 +5882,7 @@
         <v>341</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>23</v>
@@ -5902,7 +5902,7 @@
         <v>341</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>23</v>
@@ -5922,7 +5922,7 @@
         <v>341</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>23</v>
@@ -5942,7 +5942,7 @@
         <v>341</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>23</v>
@@ -5962,7 +5962,7 @@
         <v>341</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>40</v>
+        <v>126</v>
       </c>
       <c r="F163" s="1" t="s">
         <v>23</v>
@@ -5979,10 +5979,10 @@
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>358</v>
+        <v>341</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>4</v>
+        <v>145</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>23</v>
@@ -5990,19 +5990,19 @@
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="B165" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="B165" s="1" t="s">
+      <c r="C165" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D165" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="C165" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D165" s="1" t="s">
-        <v>358</v>
-      </c>
       <c r="E165" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>23</v>
@@ -6019,10 +6019,10 @@
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>23</v>
@@ -6039,10 +6039,10 @@
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>23</v>
@@ -6059,10 +6059,10 @@
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>23</v>
@@ -6079,10 +6079,10 @@
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>23</v>
@@ -6099,10 +6099,10 @@
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="F170" s="1" t="s">
         <v>23</v>
@@ -6119,13 +6119,13 @@
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
@@ -6139,10 +6139,10 @@
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>126</v>
+        <v>41</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>5</v>
@@ -6159,33 +6159,33 @@
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>377</v>
+        <v>360</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>4</v>
+        <v>126</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>70</v>
+        <v>5</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="B174" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="B174" s="1" t="s">
+      <c r="C174" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D174" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="C174" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D174" s="1" t="s">
-        <v>377</v>
-      </c>
       <c r="E174" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
@@ -6199,10 +6199,10 @@
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>23</v>
@@ -6219,13 +6219,13 @@
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>67</v>
+        <v>23</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
@@ -6239,13 +6239,13 @@
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
@@ -6259,13 +6259,13 @@
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
@@ -6279,13 +6279,13 @@
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>70</v>
+        <v>23</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
@@ -6299,13 +6299,13 @@
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>70</v>
+        <v>28</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
@@ -6319,13 +6319,13 @@
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>126</v>
+        <v>41</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
@@ -6339,10 +6339,10 @@
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>145</v>
+        <v>126</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>23</v>
@@ -6359,10 +6359,10 @@
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>398</v>
+        <v>379</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>4</v>
+        <v>145</v>
       </c>
       <c r="F183" s="1" t="s">
         <v>23</v>
@@ -6370,22 +6370,22 @@
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="B184" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="B184" s="1" t="s">
+      <c r="C184" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D184" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="C184" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D184" s="1" t="s">
-        <v>398</v>
-      </c>
       <c r="E184" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
@@ -6399,13 +6399,13 @@
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>70</v>
+        <v>31</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
@@ -6419,13 +6419,13 @@
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>81</v>
+        <v>28</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
@@ -6439,13 +6439,13 @@
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>23</v>
+        <v>81</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
@@ -6459,13 +6459,13 @@
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
@@ -6479,13 +6479,13 @@
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
@@ -6499,13 +6499,13 @@
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
@@ -6519,10 +6519,10 @@
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>126</v>
+        <v>41</v>
       </c>
       <c r="F191" s="1" t="s">
         <v>23</v>
@@ -6539,10 +6539,10 @@
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>417</v>
+        <v>400</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>4</v>
+        <v>126</v>
       </c>
       <c r="F192" s="1" t="s">
         <v>23</v>
@@ -6550,19 +6550,19 @@
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="B193" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="B193" s="1" t="s">
+      <c r="C193" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D193" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="C193" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D193" s="1" t="s">
-        <v>417</v>
-      </c>
       <c r="E193" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F193" s="1" t="s">
         <v>23</v>
@@ -6579,10 +6579,10 @@
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F194" s="1" t="s">
         <v>23</v>
@@ -6599,10 +6599,10 @@
         <v>3</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>23</v>
@@ -6619,10 +6619,10 @@
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F196" s="1" t="s">
         <v>23</v>
@@ -6639,13 +6639,13 @@
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>163</v>
+        <v>23</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
@@ -6659,10 +6659,10 @@
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="F198" s="1" t="s">
         <v>163</v>
@@ -6679,13 +6679,13 @@
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F199" s="1" t="s">
-        <v>23</v>
+        <v>163</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
@@ -6699,10 +6699,10 @@
         <v>3</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>126</v>
+        <v>41</v>
       </c>
       <c r="F200" s="1" t="s">
         <v>23</v>
@@ -6719,7 +6719,7 @@
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E201" s="1" t="s">
         <v>145</v>
@@ -6745,7 +6745,7 @@
         <v>4</v>
       </c>
       <c r="F202" s="1" t="s">
-        <v>70</v>
+        <v>28</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
@@ -6765,7 +6765,7 @@
         <v>8</v>
       </c>
       <c r="F203" s="1" t="s">
-        <v>70</v>
+        <v>28</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
@@ -6785,7 +6785,7 @@
         <v>11</v>
       </c>
       <c r="F204" s="1" t="s">
-        <v>70</v>
+        <v>28</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
@@ -6805,7 +6805,7 @@
         <v>14</v>
       </c>
       <c r="F205" s="1" t="s">
-        <v>70</v>
+        <v>28</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
@@ -6825,7 +6825,7 @@
         <v>17</v>
       </c>
       <c r="F206" s="1" t="s">
-        <v>70</v>
+        <v>28</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
@@ -6845,7 +6845,7 @@
         <v>20</v>
       </c>
       <c r="F207" s="1" t="s">
-        <v>70</v>
+        <v>28</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
@@ -6862,7 +6862,7 @@
         <v>438</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F208" s="1" t="s">
         <v>23</v>
@@ -6882,7 +6882,7 @@
         <v>438</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F209" s="1" t="s">
         <v>23</v>
@@ -6925,7 +6925,7 @@
         <v>4</v>
       </c>
       <c r="F211" s="1" t="s">
-        <v>70</v>
+        <v>28</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
@@ -7042,7 +7042,7 @@
         <v>457</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F217" s="1" t="s">
         <v>23</v>
@@ -7062,7 +7062,7 @@
         <v>457</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F218" s="1" t="s">
         <v>23</v>
@@ -7085,7 +7085,7 @@
         <v>126</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>70</v>
+        <v>28</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
@@ -7242,10 +7242,10 @@
         <v>478</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
@@ -7262,10 +7262,10 @@
         <v>478</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F228" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
@@ -7285,7 +7285,7 @@
         <v>4</v>
       </c>
       <c r="F229" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
@@ -7305,7 +7305,7 @@
         <v>8</v>
       </c>
       <c r="F230" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
@@ -7325,7 +7325,7 @@
         <v>11</v>
       </c>
       <c r="F231" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
@@ -7402,7 +7402,7 @@
         <v>495</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F235" s="1" t="s">
         <v>163</v>
@@ -7425,7 +7425,7 @@
         <v>4</v>
       </c>
       <c r="F236" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
@@ -7445,7 +7445,7 @@
         <v>8</v>
       </c>
       <c r="F237" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
@@ -7465,7 +7465,7 @@
         <v>11</v>
       </c>
       <c r="F238" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
@@ -7485,7 +7485,7 @@
         <v>14</v>
       </c>
       <c r="F239" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
@@ -7505,7 +7505,7 @@
         <v>17</v>
       </c>
       <c r="F240" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
@@ -7542,7 +7542,7 @@
         <v>510</v>
       </c>
       <c r="E242" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F242" s="1" t="s">
         <v>163</v>
@@ -7562,7 +7562,7 @@
         <v>510</v>
       </c>
       <c r="E243" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F243" s="1" t="s">
         <v>525</v>
@@ -7585,7 +7585,7 @@
         <v>126</v>
       </c>
       <c r="F244" s="1" t="s">
-        <v>70</v>
+        <v>28</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
@@ -7685,7 +7685,7 @@
         <v>17</v>
       </c>
       <c r="F249" s="1" t="s">
-        <v>70</v>
+        <v>28</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
@@ -7705,7 +7705,7 @@
         <v>20</v>
       </c>
       <c r="F250" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
@@ -7722,10 +7722,10 @@
         <v>530</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F251" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
@@ -7742,10 +7742,10 @@
         <v>530</v>
       </c>
       <c r="E252" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F252" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
@@ -7845,7 +7845,7 @@
         <v>17</v>
       </c>
       <c r="F257" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
@@ -7882,7 +7882,7 @@
         <v>547</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F259" s="1" t="s">
         <v>23</v>
@@ -7902,7 +7902,7 @@
         <v>547</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F260" s="1" t="s">
         <v>23</v>
@@ -7925,7 +7925,7 @@
         <v>4</v>
       </c>
       <c r="F261" s="1" t="s">
-        <v>70</v>
+        <v>28</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
@@ -7945,7 +7945,7 @@
         <v>8</v>
       </c>
       <c r="F262" s="1" t="s">
-        <v>70</v>
+        <v>28</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
@@ -8042,7 +8042,7 @@
         <v>564</v>
       </c>
       <c r="E267" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F267" s="1" t="s">
         <v>23</v>
@@ -8062,7 +8062,7 @@
         <v>564</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F268" s="1" t="s">
         <v>23</v>
@@ -8222,7 +8222,7 @@
         <v>582</v>
       </c>
       <c r="E276" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F276" s="1" t="s">
         <v>23</v>
@@ -8242,7 +8242,7 @@
         <v>582</v>
       </c>
       <c r="E277" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F277" s="1" t="s">
         <v>23</v>
@@ -8442,7 +8442,7 @@
         <v>605</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F287" s="1" t="s">
         <v>618</v>
@@ -8462,7 +8462,7 @@
         <v>605</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F288" s="1" t="s">
         <v>23</v>
@@ -8642,7 +8642,7 @@
         <v>627</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F297" s="1" t="s">
         <v>618</v>
@@ -8662,7 +8662,7 @@
         <v>627</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F298" s="1" t="s">
         <v>618</v>
@@ -8822,7 +8822,7 @@
         <v>646</v>
       </c>
       <c r="E306" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F306" s="1" t="s">
         <v>23</v>
@@ -8842,7 +8842,7 @@
         <v>646</v>
       </c>
       <c r="E307" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F307" s="1" t="s">
         <v>23</v>
@@ -9002,7 +9002,7 @@
         <v>665</v>
       </c>
       <c r="E315" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F315" s="1" t="s">
         <v>23</v>
@@ -9022,7 +9022,7 @@
         <v>665</v>
       </c>
       <c r="E316" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F316" s="1" t="s">
         <v>23</v>
@@ -9182,7 +9182,7 @@
         <v>684</v>
       </c>
       <c r="E324" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F324" s="1" t="s">
         <v>23</v>
@@ -9202,7 +9202,7 @@
         <v>684</v>
       </c>
       <c r="E325" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F325" s="1" t="s">
         <v>23</v>
@@ -9285,7 +9285,7 @@
         <v>11</v>
       </c>
       <c r="F329" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.25">
@@ -9305,7 +9305,7 @@
         <v>14</v>
       </c>
       <c r="F330" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.25">
@@ -9362,7 +9362,7 @@
         <v>703</v>
       </c>
       <c r="E333" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F333" s="1" t="s">
         <v>23</v>
@@ -9382,7 +9382,7 @@
         <v>703</v>
       </c>
       <c r="E334" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F334" s="1" t="s">
         <v>23</v>
@@ -9445,7 +9445,7 @@
         <v>4</v>
       </c>
       <c r="F337" s="1" t="s">
-        <v>70</v>
+        <v>28</v>
       </c>
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.25">
@@ -9465,7 +9465,7 @@
         <v>8</v>
       </c>
       <c r="F338" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.25">
@@ -9505,7 +9505,7 @@
         <v>14</v>
       </c>
       <c r="F340" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.25">
@@ -9562,10 +9562,10 @@
         <v>724</v>
       </c>
       <c r="E343" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F343" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.25">
@@ -9582,7 +9582,7 @@
         <v>724</v>
       </c>
       <c r="E344" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F344" s="1" t="s">
         <v>739</v>
@@ -9605,7 +9605,7 @@
         <v>126</v>
       </c>
       <c r="F345" s="1" t="s">
-        <v>70</v>
+        <v>28</v>
       </c>
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.25">
@@ -9685,7 +9685,7 @@
         <v>4</v>
       </c>
       <c r="F349" s="1" t="s">
-        <v>70</v>
+        <v>28</v>
       </c>
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.25">

--- a/CLB07N.xlsx
+++ b/CLB07N.xlsx
@@ -2197,7 +2197,7 @@
     <t>20090527</t>
   </si>
   <si>
-    <t>CRYSTALIN BTL 600ML</t>
+    <t>CRYSTALIN BTL 600mL</t>
   </si>
   <si>
     <t>20077499</t>

--- a/CLB07N.xlsx
+++ b/CLB07N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2118" uniqueCount="765">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2130" uniqueCount="769">
   <si>
     <t/>
   </si>
@@ -394,6 +394,12 @@
     <t>9</t>
   </si>
   <si>
+    <t>20136363</t>
+  </si>
+  <si>
+    <t>ICHTN DARK CHOCO 300</t>
+  </si>
+  <si>
     <t>20138025</t>
   </si>
   <si>
@@ -442,15 +448,15 @@
     <t>NESCAFE COFF CRM 180</t>
   </si>
   <si>
+    <t>10</t>
+  </si>
+  <si>
     <t>20076770</t>
   </si>
   <si>
     <t>G/DAY CAPPUCCINO 250</t>
   </si>
   <si>
-    <t>10</t>
-  </si>
-  <si>
     <t>20045674</t>
   </si>
   <si>
@@ -1000,12 +1006,6 @@
     <t>NU MATCHA LATTEA 330</t>
   </si>
   <si>
-    <t>20136363</t>
-  </si>
-  <si>
-    <t>ICHTN DARK CHOCO 300</t>
-  </si>
-  <si>
     <t>20113450</t>
   </si>
   <si>
@@ -1018,6 +1018,12 @@
     <t>ICHTAN KRN BANANA300</t>
   </si>
   <si>
+    <t>20142025</t>
+  </si>
+  <si>
+    <t>ICHITAN MLN MILK 300</t>
+  </si>
+  <si>
     <t>20085054</t>
   </si>
   <si>
@@ -2000,6 +2006,12 @@
   </si>
   <si>
     <t>F.FLAG UHT MATCH 225</t>
+  </si>
+  <si>
+    <t>20142233</t>
+  </si>
+  <si>
+    <t>INDOMILK JAPANE M180</t>
   </si>
   <si>
     <t>10004669</t>
@@ -2698,7 +2710,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F353"/>
+  <dimension ref="A1:F355"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -3999,13 +4011,13 @@
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E65" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="E65" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F65" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -4022,7 +4034,7 @@
         <v>145</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>31</v>
@@ -4042,7 +4054,7 @@
         <v>145</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>31</v>
@@ -4062,7 +4074,7 @@
         <v>145</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>31</v>
@@ -4082,7 +4094,7 @@
         <v>145</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>31</v>
@@ -4102,10 +4114,10 @@
         <v>145</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -4122,7 +4134,7 @@
         <v>145</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>23</v>
@@ -4142,7 +4154,7 @@
         <v>145</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>23</v>
@@ -4159,33 +4171,33 @@
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>163</v>
+        <v>23</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D74" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="B74" s="1" t="s">
+      <c r="E74" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F74" s="1" t="s">
         <v>165</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="E74" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F74" s="1" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -4199,13 +4211,13 @@
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -4219,13 +4231,13 @@
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>23</v>
+        <v>165</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -4239,13 +4251,13 @@
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -4259,13 +4271,13 @@
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -4279,10 +4291,10 @@
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>23</v>
@@ -4299,30 +4311,30 @@
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B81" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="B81" s="1" t="s">
+      <c r="C81" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D81" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="C81" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D81" s="1" t="s">
-        <v>178</v>
-      </c>
       <c r="E81" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>31</v>
@@ -4339,10 +4351,10 @@
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>31</v>
@@ -4359,13 +4371,13 @@
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -4379,13 +4391,13 @@
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -4399,10 +4411,10 @@
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>31</v>
@@ -4419,10 +4431,10 @@
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>31</v>
@@ -4439,10 +4451,10 @@
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>31</v>
@@ -4459,13 +4471,13 @@
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>126</v>
+        <v>41</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -4479,10 +4491,10 @@
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>145</v>
+        <v>126</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>23</v>
@@ -4499,30 +4511,30 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>199</v>
+        <v>180</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>4</v>
+        <v>145</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="B91" s="1" t="s">
+      <c r="C91" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D91" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="C91" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D91" s="1" t="s">
-        <v>199</v>
-      </c>
       <c r="E91" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>28</v>
@@ -4539,13 +4551,13 @@
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>81</v>
+        <v>28</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -4559,13 +4571,13 @@
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>23</v>
+        <v>81</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
@@ -4579,10 +4591,10 @@
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>23</v>
@@ -4599,13 +4611,13 @@
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -4619,13 +4631,13 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -4639,10 +4651,10 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>23</v>
@@ -4659,33 +4671,33 @@
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B99" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="B99" s="1" t="s">
+      <c r="C99" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D99" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="C99" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>216</v>
-      </c>
       <c r="E99" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -4699,10 +4711,10 @@
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>23</v>
@@ -4719,10 +4731,10 @@
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>23</v>
@@ -4739,10 +4751,10 @@
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>23</v>
@@ -4759,10 +4771,10 @@
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>23</v>
@@ -4779,10 +4791,10 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>23</v>
@@ -4799,10 +4811,10 @@
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>23</v>
@@ -4819,33 +4831,33 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>233</v>
+        <v>218</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>163</v>
+        <v>23</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B107" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="B107" s="1" t="s">
+      <c r="C107" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D107" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="C107" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D107" s="1" t="s">
-        <v>233</v>
-      </c>
       <c r="E107" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -4859,13 +4871,13 @@
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -4879,13 +4891,13 @@
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -4899,13 +4911,13 @@
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -4919,13 +4931,13 @@
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>23</v>
+        <v>165</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -4939,10 +4951,10 @@
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>23</v>
@@ -4959,10 +4971,10 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>23</v>
@@ -4979,10 +4991,10 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>126</v>
+        <v>41</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>23</v>
@@ -4999,10 +5011,10 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>252</v>
+        <v>235</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>4</v>
+        <v>126</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>23</v>
@@ -5010,19 +5022,19 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B116" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="B116" s="1" t="s">
+      <c r="C116" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D116" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="C116" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D116" s="1" t="s">
-        <v>252</v>
-      </c>
       <c r="E116" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>23</v>
@@ -5039,10 +5051,10 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>23</v>
@@ -5059,10 +5071,10 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>23</v>
@@ -5079,10 +5091,10 @@
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>23</v>
@@ -5099,10 +5111,10 @@
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>23</v>
@@ -5119,10 +5131,10 @@
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>23</v>
@@ -5139,50 +5151,50 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>267</v>
+        <v>23</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="B123" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="B123" s="1" t="s">
+      <c r="C123" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="E123" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F123" s="1" t="s">
         <v>269</v>
-      </c>
-      <c r="C123" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D123" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="E123" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F123" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="B124" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="B124" s="1" t="s">
+      <c r="C124" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D124" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="C124" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D124" s="1" t="s">
-        <v>270</v>
-      </c>
       <c r="E124" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>23</v>
@@ -5199,10 +5211,10 @@
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>23</v>
@@ -5210,19 +5222,19 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="B126" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="B126" s="1" t="s">
+      <c r="C126" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D126" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="C126" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D126" s="1" t="s">
-        <v>275</v>
-      </c>
       <c r="E126" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>23</v>
@@ -5239,10 +5251,10 @@
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>23</v>
@@ -5259,10 +5271,10 @@
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>23</v>
@@ -5279,10 +5291,10 @@
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>23</v>
@@ -5299,10 +5311,10 @@
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>23</v>
@@ -5319,10 +5331,10 @@
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>288</v>
+        <v>277</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>23</v>
@@ -5330,19 +5342,19 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B132" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="B132" s="1" t="s">
+      <c r="C132" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D132" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="C132" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D132" s="1" t="s">
-        <v>288</v>
-      </c>
       <c r="E132" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>23</v>
@@ -5359,10 +5371,10 @@
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>23</v>
@@ -5379,10 +5391,10 @@
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>23</v>
@@ -5399,10 +5411,10 @@
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>23</v>
@@ -5419,10 +5431,10 @@
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>23</v>
@@ -5439,13 +5451,13 @@
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
@@ -5459,10 +5471,10 @@
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>28</v>
@@ -5479,30 +5491,30 @@
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B140" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="B140" s="1" t="s">
+      <c r="C140" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D140" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="C140" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D140" s="1" t="s">
-        <v>305</v>
-      </c>
       <c r="E140" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>23</v>
@@ -5519,10 +5531,10 @@
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>23</v>
@@ -5539,13 +5551,13 @@
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
@@ -5559,10 +5571,10 @@
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>5</v>
@@ -5579,10 +5591,10 @@
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>5</v>
@@ -5599,13 +5611,13 @@
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
@@ -5619,10 +5631,10 @@
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>23</v>
@@ -5639,10 +5651,10 @@
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>322</v>
+        <v>307</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>23</v>
@@ -5650,19 +5662,19 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="B148" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="B148" s="1" t="s">
+      <c r="C148" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D148" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="C148" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D148" s="1" t="s">
-        <v>322</v>
-      </c>
       <c r="E148" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>23</v>
@@ -5679,10 +5691,10 @@
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>23</v>
@@ -5699,10 +5711,10 @@
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>23</v>
@@ -5719,10 +5731,10 @@
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>23</v>
@@ -5739,10 +5751,10 @@
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>31</v>
@@ -5759,10 +5771,10 @@
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>23</v>
@@ -5779,13 +5791,13 @@
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
@@ -5799,10 +5811,10 @@
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>126</v>
+        <v>41</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>31</v>
@@ -5819,30 +5831,30 @@
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>341</v>
+        <v>324</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>4</v>
+        <v>126</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="B157" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="B157" s="1" t="s">
+      <c r="C157" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D157" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="C157" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D157" s="1" t="s">
-        <v>341</v>
-      </c>
       <c r="E157" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>23</v>
@@ -5859,13 +5871,13 @@
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
@@ -5879,13 +5891,13 @@
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
@@ -5899,10 +5911,10 @@
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>23</v>
@@ -5919,10 +5931,10 @@
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>23</v>
@@ -5939,10 +5951,10 @@
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>23</v>
@@ -5959,10 +5971,10 @@
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>126</v>
+        <v>38</v>
       </c>
       <c r="F163" s="1" t="s">
         <v>23</v>
@@ -5979,10 +5991,10 @@
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>145</v>
+        <v>41</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>23</v>
@@ -5999,10 +6011,10 @@
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>360</v>
+        <v>343</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>4</v>
+        <v>126</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>23</v>
@@ -6010,19 +6022,19 @@
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="B166" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="B166" s="1" t="s">
+      <c r="C166" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D166" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="C166" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D166" s="1" t="s">
-        <v>360</v>
-      </c>
       <c r="E166" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>23</v>
@@ -6039,10 +6051,10 @@
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>23</v>
@@ -6059,10 +6071,10 @@
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>23</v>
@@ -6079,10 +6091,10 @@
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>23</v>
@@ -6099,10 +6111,10 @@
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F170" s="1" t="s">
         <v>23</v>
@@ -6119,10 +6131,10 @@
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>23</v>
@@ -6139,13 +6151,13 @@
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
@@ -6159,10 +6171,10 @@
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>126</v>
+        <v>41</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>5</v>
@@ -6179,33 +6191,33 @@
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>379</v>
+        <v>362</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>4</v>
+        <v>126</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="B175" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="B175" s="1" t="s">
+      <c r="C175" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D175" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="C175" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D175" s="1" t="s">
-        <v>379</v>
-      </c>
       <c r="E175" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
@@ -6219,10 +6231,10 @@
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>23</v>
@@ -6239,13 +6251,13 @@
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>68</v>
+        <v>23</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
@@ -6259,10 +6271,10 @@
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>68</v>
@@ -6279,13 +6291,13 @@
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
@@ -6299,13 +6311,13 @@
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
@@ -6319,10 +6331,10 @@
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>28</v>
@@ -6339,13 +6351,13 @@
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>126</v>
+        <v>41</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
@@ -6359,10 +6371,10 @@
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>145</v>
+        <v>126</v>
       </c>
       <c r="F183" s="1" t="s">
         <v>23</v>
@@ -6379,10 +6391,10 @@
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>400</v>
+        <v>381</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>4</v>
+        <v>145</v>
       </c>
       <c r="F184" s="1" t="s">
         <v>23</v>
@@ -6390,22 +6402,22 @@
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B185" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="B185" s="1" t="s">
+      <c r="C185" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D185" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="C185" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D185" s="1" t="s">
-        <v>400</v>
-      </c>
       <c r="E185" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
@@ -6419,13 +6431,13 @@
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
@@ -6439,13 +6451,13 @@
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>81</v>
+        <v>28</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
@@ -6459,13 +6471,13 @@
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>23</v>
+        <v>81</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
@@ -6479,13 +6491,13 @@
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
@@ -6499,10 +6511,10 @@
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F190" s="1" t="s">
         <v>31</v>
@@ -6519,13 +6531,13 @@
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
@@ -6539,10 +6551,10 @@
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>126</v>
+        <v>41</v>
       </c>
       <c r="F192" s="1" t="s">
         <v>23</v>
@@ -6559,10 +6571,10 @@
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>419</v>
+        <v>402</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>4</v>
+        <v>126</v>
       </c>
       <c r="F193" s="1" t="s">
         <v>23</v>
@@ -6570,19 +6582,19 @@
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="B194" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="B194" s="1" t="s">
+      <c r="C194" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D194" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="C194" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D194" s="1" t="s">
-        <v>419</v>
-      </c>
       <c r="E194" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F194" s="1" t="s">
         <v>23</v>
@@ -6599,10 +6611,10 @@
         <v>3</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>23</v>
@@ -6619,10 +6631,10 @@
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F196" s="1" t="s">
         <v>23</v>
@@ -6639,10 +6651,10 @@
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F197" s="1" t="s">
         <v>23</v>
@@ -6659,13 +6671,13 @@
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F198" s="1" t="s">
-        <v>163</v>
+        <v>23</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
@@ -6679,13 +6691,13 @@
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F199" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
@@ -6699,13 +6711,13 @@
         <v>3</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>23</v>
+        <v>165</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
@@ -6719,10 +6731,10 @@
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>145</v>
+        <v>41</v>
       </c>
       <c r="F201" s="1" t="s">
         <v>23</v>
@@ -6739,30 +6751,30 @@
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>438</v>
+        <v>421</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>4</v>
+        <v>145</v>
       </c>
       <c r="F202" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="B203" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="B203" s="1" t="s">
+      <c r="C203" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D203" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="C203" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D203" s="1" t="s">
-        <v>438</v>
-      </c>
       <c r="E203" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F203" s="1" t="s">
         <v>28</v>
@@ -6779,10 +6791,10 @@
         <v>3</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F204" s="1" t="s">
         <v>28</v>
@@ -6799,10 +6811,10 @@
         <v>3</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F205" s="1" t="s">
         <v>28</v>
@@ -6819,10 +6831,10 @@
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F206" s="1" t="s">
         <v>28</v>
@@ -6839,10 +6851,10 @@
         <v>3</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F207" s="1" t="s">
         <v>28</v>
@@ -6859,13 +6871,13 @@
         <v>3</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F208" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
@@ -6879,10 +6891,10 @@
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F209" s="1" t="s">
         <v>23</v>
@@ -6899,10 +6911,10 @@
         <v>3</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>126</v>
+        <v>41</v>
       </c>
       <c r="F210" s="1" t="s">
         <v>23</v>
@@ -6919,33 +6931,33 @@
         <v>3</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>457</v>
+        <v>440</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>4</v>
+        <v>126</v>
       </c>
       <c r="F211" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="B212" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="B212" s="1" t="s">
+      <c r="C212" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D212" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="C212" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D212" s="1" t="s">
-        <v>457</v>
-      </c>
       <c r="E212" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F212" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
@@ -6959,13 +6971,13 @@
         <v>3</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
@@ -6979,10 +6991,10 @@
         <v>3</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F214" s="1" t="s">
         <v>5</v>
@@ -6999,13 +7011,13 @@
         <v>3</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F215" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
@@ -7019,10 +7031,10 @@
         <v>3</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F216" s="1" t="s">
         <v>23</v>
@@ -7039,10 +7051,10 @@
         <v>3</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F217" s="1" t="s">
         <v>23</v>
@@ -7059,10 +7071,10 @@
         <v>3</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F218" s="1" t="s">
         <v>23</v>
@@ -7079,13 +7091,13 @@
         <v>3</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>126</v>
+        <v>41</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
@@ -7099,13 +7111,13 @@
         <v>3</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>145</v>
+        <v>126</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
@@ -7119,10 +7131,10 @@
         <v>3</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>478</v>
+        <v>459</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>4</v>
+        <v>145</v>
       </c>
       <c r="F221" s="1" t="s">
         <v>23</v>
@@ -7130,19 +7142,19 @@
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="B222" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="B222" s="1" t="s">
+      <c r="C222" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D222" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="C222" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D222" s="1" t="s">
-        <v>478</v>
-      </c>
       <c r="E222" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F222" s="1" t="s">
         <v>23</v>
@@ -7159,10 +7171,10 @@
         <v>3</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F223" s="1" t="s">
         <v>23</v>
@@ -7179,10 +7191,10 @@
         <v>3</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F224" s="1" t="s">
         <v>23</v>
@@ -7199,10 +7211,10 @@
         <v>3</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F225" s="1" t="s">
         <v>23</v>
@@ -7219,10 +7231,10 @@
         <v>3</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F226" s="1" t="s">
         <v>23</v>
@@ -7239,13 +7251,13 @@
         <v>3</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
@@ -7259,10 +7271,10 @@
         <v>3</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F228" s="1" t="s">
         <v>31</v>
@@ -7279,10 +7291,10 @@
         <v>3</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>495</v>
+        <v>480</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="F229" s="1" t="s">
         <v>31</v>
@@ -7290,19 +7302,19 @@
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="B230" s="1" t="s">
         <v>496</v>
       </c>
-      <c r="B230" s="1" t="s">
+      <c r="C230" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D230" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="C230" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D230" s="1" t="s">
-        <v>495</v>
-      </c>
       <c r="E230" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F230" s="1" t="s">
         <v>31</v>
@@ -7319,10 +7331,10 @@
         <v>3</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F231" s="1" t="s">
         <v>31</v>
@@ -7339,13 +7351,13 @@
         <v>3</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F232" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
@@ -7359,10 +7371,10 @@
         <v>3</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F233" s="1" t="s">
         <v>23</v>
@@ -7379,13 +7391,13 @@
         <v>3</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F234" s="1" t="s">
-        <v>163</v>
+        <v>23</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
@@ -7399,13 +7411,13 @@
         <v>3</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F235" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
@@ -7419,30 +7431,30 @@
         <v>3</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>510</v>
+        <v>497</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F236" s="1" t="s">
-        <v>31</v>
+        <v>165</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="B237" s="1" t="s">
         <v>511</v>
       </c>
-      <c r="B237" s="1" t="s">
+      <c r="C237" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D237" s="1" t="s">
         <v>512</v>
       </c>
-      <c r="C237" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D237" s="1" t="s">
-        <v>510</v>
-      </c>
       <c r="E237" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F237" s="1" t="s">
         <v>31</v>
@@ -7459,10 +7471,10 @@
         <v>3</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="E238" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F238" s="1" t="s">
         <v>31</v>
@@ -7479,10 +7491,10 @@
         <v>3</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="E239" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F239" s="1" t="s">
         <v>31</v>
@@ -7499,10 +7511,10 @@
         <v>3</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="E240" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F240" s="1" t="s">
         <v>31</v>
@@ -7519,13 +7531,13 @@
         <v>3</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="E241" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F241" s="1" t="s">
-        <v>163</v>
+        <v>31</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
@@ -7539,13 +7551,13 @@
         <v>3</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="E242" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F242" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
@@ -7559,33 +7571,33 @@
         <v>3</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="E243" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F243" s="1" t="s">
-        <v>525</v>
+        <v>165</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="B244" s="1" t="s">
         <v>526</v>
       </c>
-      <c r="B244" s="1" t="s">
+      <c r="C244" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D244" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="E244" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F244" s="1" t="s">
         <v>527</v>
-      </c>
-      <c r="C244" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D244" s="1" t="s">
-        <v>510</v>
-      </c>
-      <c r="E244" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="F244" s="1" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
@@ -7599,30 +7611,30 @@
         <v>3</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>530</v>
+        <v>512</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>4</v>
+        <v>126</v>
       </c>
       <c r="F245" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="B246" s="1" t="s">
         <v>531</v>
       </c>
-      <c r="B246" s="1" t="s">
+      <c r="C246" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D246" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="C246" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D246" s="1" t="s">
-        <v>530</v>
-      </c>
       <c r="E246" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F246" s="1" t="s">
         <v>23</v>
@@ -7639,10 +7651,10 @@
         <v>3</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F247" s="1" t="s">
         <v>23</v>
@@ -7659,10 +7671,10 @@
         <v>3</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F248" s="1" t="s">
         <v>23</v>
@@ -7679,13 +7691,13 @@
         <v>3</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F249" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
@@ -7699,13 +7711,13 @@
         <v>3</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="E250" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F250" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
@@ -7719,10 +7731,10 @@
         <v>3</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F251" s="1" t="s">
         <v>31</v>
@@ -7739,10 +7751,10 @@
         <v>3</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="E252" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F252" s="1" t="s">
         <v>31</v>
@@ -7759,30 +7771,30 @@
         <v>3</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>547</v>
+        <v>532</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="F253" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="B254" s="1" t="s">
         <v>548</v>
       </c>
-      <c r="B254" s="1" t="s">
+      <c r="C254" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D254" s="1" t="s">
         <v>549</v>
       </c>
-      <c r="C254" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D254" s="1" t="s">
-        <v>547</v>
-      </c>
       <c r="E254" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F254" s="1" t="s">
         <v>23</v>
@@ -7799,10 +7811,10 @@
         <v>3</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F255" s="1" t="s">
         <v>23</v>
@@ -7819,10 +7831,10 @@
         <v>3</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="E256" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F256" s="1" t="s">
         <v>23</v>
@@ -7839,13 +7851,13 @@
         <v>3</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="E257" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F257" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
@@ -7859,13 +7871,13 @@
         <v>3</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F258" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
@@ -7879,10 +7891,10 @@
         <v>3</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F259" s="1" t="s">
         <v>23</v>
@@ -7899,10 +7911,10 @@
         <v>3</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F260" s="1" t="s">
         <v>23</v>
@@ -7919,30 +7931,30 @@
         <v>3</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>564</v>
+        <v>549</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="F261" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="B262" s="1" t="s">
         <v>565</v>
       </c>
-      <c r="B262" s="1" t="s">
-        <v>563</v>
-      </c>
       <c r="C262" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F262" s="1" t="s">
         <v>28</v>
@@ -7950,22 +7962,22 @@
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="B263" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="C263" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D263" s="1" t="s">
         <v>566</v>
       </c>
-      <c r="B263" s="1" t="s">
-        <v>567</v>
-      </c>
-      <c r="C263" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D263" s="1" t="s">
-        <v>564</v>
-      </c>
       <c r="E263" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F263" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
@@ -7979,10 +7991,10 @@
         <v>3</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="E264" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F264" s="1" t="s">
         <v>23</v>
@@ -7999,10 +8011,10 @@
         <v>3</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="E265" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F265" s="1" t="s">
         <v>23</v>
@@ -8019,10 +8031,10 @@
         <v>3</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F266" s="1" t="s">
         <v>23</v>
@@ -8039,10 +8051,10 @@
         <v>3</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="E267" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F267" s="1" t="s">
         <v>23</v>
@@ -8059,10 +8071,10 @@
         <v>3</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F268" s="1" t="s">
         <v>23</v>
@@ -8079,10 +8091,10 @@
         <v>3</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>126</v>
+        <v>41</v>
       </c>
       <c r="F269" s="1" t="s">
         <v>23</v>
@@ -8099,10 +8111,10 @@
         <v>3</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>582</v>
+        <v>566</v>
       </c>
       <c r="E270" s="1" t="s">
-        <v>4</v>
+        <v>126</v>
       </c>
       <c r="F270" s="1" t="s">
         <v>23</v>
@@ -8110,19 +8122,19 @@
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="B271" s="1" t="s">
         <v>583</v>
       </c>
-      <c r="B271" s="1" t="s">
+      <c r="C271" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D271" s="1" t="s">
         <v>584</v>
       </c>
-      <c r="C271" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D271" s="1" t="s">
-        <v>582</v>
-      </c>
       <c r="E271" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F271" s="1" t="s">
         <v>23</v>
@@ -8139,10 +8151,10 @@
         <v>3</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="E272" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F272" s="1" t="s">
         <v>23</v>
@@ -8159,10 +8171,10 @@
         <v>3</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F273" s="1" t="s">
         <v>23</v>
@@ -8179,10 +8191,10 @@
         <v>3</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F274" s="1" t="s">
         <v>23</v>
@@ -8199,10 +8211,10 @@
         <v>3</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="E275" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F275" s="1" t="s">
         <v>23</v>
@@ -8219,10 +8231,10 @@
         <v>3</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="E276" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F276" s="1" t="s">
         <v>23</v>
@@ -8239,10 +8251,10 @@
         <v>3</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="E277" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F277" s="1" t="s">
         <v>23</v>
@@ -8259,10 +8271,10 @@
         <v>3</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>126</v>
+        <v>41</v>
       </c>
       <c r="F278" s="1" t="s">
         <v>23</v>
@@ -8279,10 +8291,10 @@
         <v>3</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="E279" s="1" t="s">
-        <v>145</v>
+        <v>126</v>
       </c>
       <c r="F279" s="1" t="s">
         <v>23</v>
@@ -8299,10 +8311,10 @@
         <v>3</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="E280" s="1" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="F280" s="1" t="s">
         <v>23</v>
@@ -8319,10 +8331,10 @@
         <v>3</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>605</v>
+        <v>584</v>
       </c>
       <c r="E281" s="1" t="s">
-        <v>4</v>
+        <v>164</v>
       </c>
       <c r="F281" s="1" t="s">
         <v>23</v>
@@ -8330,19 +8342,19 @@
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="B282" s="1" t="s">
         <v>606</v>
       </c>
-      <c r="B282" s="1" t="s">
+      <c r="C282" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D282" s="1" t="s">
         <v>607</v>
       </c>
-      <c r="C282" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D282" s="1" t="s">
-        <v>605</v>
-      </c>
       <c r="E282" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F282" s="1" t="s">
         <v>23</v>
@@ -8359,10 +8371,10 @@
         <v>3</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="E283" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F283" s="1" t="s">
         <v>23</v>
@@ -8379,10 +8391,10 @@
         <v>3</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F284" s="1" t="s">
         <v>23</v>
@@ -8399,10 +8411,10 @@
         <v>3</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="E285" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F285" s="1" t="s">
         <v>23</v>
@@ -8419,10 +8431,10 @@
         <v>3</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F286" s="1" t="s">
         <v>23</v>
@@ -8439,33 +8451,33 @@
         <v>3</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F287" s="1" t="s">
-        <v>618</v>
+        <v>23</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="B288" s="1" t="s">
         <v>619</v>
       </c>
-      <c r="B288" s="1" t="s">
+      <c r="C288" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D288" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="E288" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F288" s="1" t="s">
         <v>620</v>
-      </c>
-      <c r="C288" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D288" s="1" t="s">
-        <v>605</v>
-      </c>
-      <c r="E288" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F288" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
@@ -8479,10 +8491,10 @@
         <v>3</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="E289" s="1" t="s">
-        <v>126</v>
+        <v>41</v>
       </c>
       <c r="F289" s="1" t="s">
         <v>23</v>
@@ -8499,10 +8511,10 @@
         <v>3</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="E290" s="1" t="s">
-        <v>145</v>
+        <v>126</v>
       </c>
       <c r="F290" s="1" t="s">
         <v>23</v>
@@ -8519,33 +8531,33 @@
         <v>3</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>627</v>
+        <v>607</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>4</v>
+        <v>145</v>
       </c>
       <c r="F291" s="1" t="s">
-        <v>618</v>
+        <v>23</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A292" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="B292" s="1" t="s">
         <v>628</v>
       </c>
-      <c r="B292" s="1" t="s">
+      <c r="C292" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D292" s="1" t="s">
         <v>629</v>
       </c>
-      <c r="C292" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D292" s="1" t="s">
-        <v>627</v>
-      </c>
       <c r="E292" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F292" s="1" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
@@ -8559,13 +8571,13 @@
         <v>3</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="E293" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F293" s="1" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
@@ -8579,13 +8591,13 @@
         <v>3</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="E294" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F294" s="1" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
@@ -8599,13 +8611,13 @@
         <v>3</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="E295" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F295" s="1" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
@@ -8619,13 +8631,13 @@
         <v>3</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="E296" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F296" s="1" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
@@ -8639,13 +8651,13 @@
         <v>3</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F297" s="1" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
@@ -8659,13 +8671,13 @@
         <v>3</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F298" s="1" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
@@ -8679,13 +8691,13 @@
         <v>3</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>126</v>
+        <v>41</v>
       </c>
       <c r="F299" s="1" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
@@ -8699,30 +8711,30 @@
         <v>3</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>646</v>
+        <v>629</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>4</v>
+        <v>126</v>
       </c>
       <c r="F300" s="1" t="s">
-        <v>23</v>
+        <v>620</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A301" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="B301" s="1" t="s">
         <v>647</v>
       </c>
-      <c r="B301" s="1" t="s">
+      <c r="C301" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D301" s="1" t="s">
         <v>648</v>
       </c>
-      <c r="C301" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D301" s="1" t="s">
-        <v>646</v>
-      </c>
       <c r="E301" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F301" s="1" t="s">
         <v>23</v>
@@ -8739,10 +8751,10 @@
         <v>3</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="E302" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F302" s="1" t="s">
         <v>23</v>
@@ -8759,10 +8771,10 @@
         <v>3</v>
       </c>
       <c r="D303" s="1" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="E303" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F303" s="1" t="s">
         <v>23</v>
@@ -8779,10 +8791,10 @@
         <v>3</v>
       </c>
       <c r="D304" s="1" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="E304" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F304" s="1" t="s">
         <v>23</v>
@@ -8799,10 +8811,10 @@
         <v>3</v>
       </c>
       <c r="D305" s="1" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="E305" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F305" s="1" t="s">
         <v>23</v>
@@ -8819,10 +8831,10 @@
         <v>3</v>
       </c>
       <c r="D306" s="1" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="E306" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F306" s="1" t="s">
         <v>23</v>
@@ -8839,10 +8851,10 @@
         <v>3</v>
       </c>
       <c r="D307" s="1" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="E307" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F307" s="1" t="s">
         <v>23</v>
@@ -8859,10 +8871,10 @@
         <v>3</v>
       </c>
       <c r="D308" s="1" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="E308" s="1" t="s">
-        <v>126</v>
+        <v>41</v>
       </c>
       <c r="F308" s="1" t="s">
         <v>23</v>
@@ -8879,10 +8891,10 @@
         <v>3</v>
       </c>
       <c r="D309" s="1" t="s">
-        <v>665</v>
+        <v>648</v>
       </c>
       <c r="E309" s="1" t="s">
-        <v>4</v>
+        <v>126</v>
       </c>
       <c r="F309" s="1" t="s">
         <v>23</v>
@@ -8890,19 +8902,19 @@
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A310" s="1" t="s">
+        <v>665</v>
+      </c>
+      <c r="B310" s="1" t="s">
         <v>666</v>
       </c>
-      <c r="B310" s="1" t="s">
-        <v>667</v>
-      </c>
       <c r="C310" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D310" s="1" t="s">
-        <v>665</v>
+        <v>648</v>
       </c>
       <c r="E310" s="1" t="s">
-        <v>8</v>
+        <v>145</v>
       </c>
       <c r="F310" s="1" t="s">
         <v>23</v>
@@ -8910,19 +8922,19 @@
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A311" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="B311" s="1" t="s">
         <v>668</v>
       </c>
-      <c r="B311" s="1" t="s">
+      <c r="C311" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D311" s="1" t="s">
         <v>669</v>
       </c>
-      <c r="C311" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D311" s="1" t="s">
-        <v>665</v>
-      </c>
       <c r="E311" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F311" s="1" t="s">
         <v>23</v>
@@ -8939,10 +8951,10 @@
         <v>3</v>
       </c>
       <c r="D312" s="1" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="E312" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F312" s="1" t="s">
         <v>23</v>
@@ -8959,10 +8971,10 @@
         <v>3</v>
       </c>
       <c r="D313" s="1" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="E313" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F313" s="1" t="s">
         <v>23</v>
@@ -8979,10 +8991,10 @@
         <v>3</v>
       </c>
       <c r="D314" s="1" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="E314" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F314" s="1" t="s">
         <v>23</v>
@@ -8999,10 +9011,10 @@
         <v>3</v>
       </c>
       <c r="D315" s="1" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="E315" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F315" s="1" t="s">
         <v>23</v>
@@ -9019,10 +9031,10 @@
         <v>3</v>
       </c>
       <c r="D316" s="1" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="E316" s="1" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="F316" s="1" t="s">
         <v>23</v>
@@ -9039,10 +9051,10 @@
         <v>3</v>
       </c>
       <c r="D317" s="1" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="E317" s="1" t="s">
-        <v>126</v>
+        <v>38</v>
       </c>
       <c r="F317" s="1" t="s">
         <v>23</v>
@@ -9059,10 +9071,10 @@
         <v>3</v>
       </c>
       <c r="D318" s="1" t="s">
-        <v>684</v>
+        <v>669</v>
       </c>
       <c r="E318" s="1" t="s">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="F318" s="1" t="s">
         <v>23</v>
@@ -9070,19 +9082,19 @@
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A319" s="1" t="s">
+        <v>684</v>
+      </c>
+      <c r="B319" s="1" t="s">
         <v>685</v>
       </c>
-      <c r="B319" s="1" t="s">
-        <v>686</v>
-      </c>
       <c r="C319" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D319" s="1" t="s">
-        <v>684</v>
+        <v>669</v>
       </c>
       <c r="E319" s="1" t="s">
-        <v>8</v>
+        <v>126</v>
       </c>
       <c r="F319" s="1" t="s">
         <v>23</v>
@@ -9090,19 +9102,19 @@
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A320" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="B320" s="1" t="s">
         <v>687</v>
       </c>
-      <c r="B320" s="1" t="s">
+      <c r="C320" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D320" s="1" t="s">
         <v>688</v>
       </c>
-      <c r="C320" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D320" s="1" t="s">
-        <v>684</v>
-      </c>
       <c r="E320" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F320" s="1" t="s">
         <v>23</v>
@@ -9119,10 +9131,10 @@
         <v>3</v>
       </c>
       <c r="D321" s="1" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="E321" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F321" s="1" t="s">
         <v>23</v>
@@ -9139,10 +9151,10 @@
         <v>3</v>
       </c>
       <c r="D322" s="1" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="E322" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F322" s="1" t="s">
         <v>23</v>
@@ -9159,10 +9171,10 @@
         <v>3</v>
       </c>
       <c r="D323" s="1" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="E323" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F323" s="1" t="s">
         <v>23</v>
@@ -9179,10 +9191,10 @@
         <v>3</v>
       </c>
       <c r="D324" s="1" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="E324" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F324" s="1" t="s">
         <v>23</v>
@@ -9199,10 +9211,10 @@
         <v>3</v>
       </c>
       <c r="D325" s="1" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="E325" s="1" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="F325" s="1" t="s">
         <v>23</v>
@@ -9219,10 +9231,10 @@
         <v>3</v>
       </c>
       <c r="D326" s="1" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="E326" s="1" t="s">
-        <v>126</v>
+        <v>38</v>
       </c>
       <c r="F326" s="1" t="s">
         <v>23</v>
@@ -9239,10 +9251,10 @@
         <v>3</v>
       </c>
       <c r="D327" s="1" t="s">
-        <v>703</v>
+        <v>688</v>
       </c>
       <c r="E327" s="1" t="s">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="F327" s="1" t="s">
         <v>23</v>
@@ -9250,19 +9262,19 @@
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A328" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="B328" s="1" t="s">
         <v>704</v>
       </c>
-      <c r="B328" s="1" t="s">
-        <v>705</v>
-      </c>
       <c r="C328" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D328" s="1" t="s">
-        <v>703</v>
+        <v>688</v>
       </c>
       <c r="E328" s="1" t="s">
-        <v>8</v>
+        <v>126</v>
       </c>
       <c r="F328" s="1" t="s">
         <v>23</v>
@@ -9270,22 +9282,22 @@
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A329" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="B329" s="1" t="s">
         <v>706</v>
       </c>
-      <c r="B329" s="1" t="s">
+      <c r="C329" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D329" s="1" t="s">
         <v>707</v>
       </c>
-      <c r="C329" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D329" s="1" t="s">
-        <v>703</v>
-      </c>
       <c r="E329" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F329" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.25">
@@ -9299,13 +9311,13 @@
         <v>3</v>
       </c>
       <c r="D330" s="1" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="E330" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F330" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.25">
@@ -9319,13 +9331,13 @@
         <v>3</v>
       </c>
       <c r="D331" s="1" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="E331" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F331" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.25">
@@ -9339,13 +9351,13 @@
         <v>3</v>
       </c>
       <c r="D332" s="1" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="E332" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F332" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.25">
@@ -9359,10 +9371,10 @@
         <v>3</v>
       </c>
       <c r="D333" s="1" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="E333" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F333" s="1" t="s">
         <v>23</v>
@@ -9379,10 +9391,10 @@
         <v>3</v>
       </c>
       <c r="D334" s="1" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="E334" s="1" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="F334" s="1" t="s">
         <v>23</v>
@@ -9399,10 +9411,10 @@
         <v>3</v>
       </c>
       <c r="D335" s="1" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="E335" s="1" t="s">
-        <v>126</v>
+        <v>38</v>
       </c>
       <c r="F335" s="1" t="s">
         <v>23</v>
@@ -9419,10 +9431,10 @@
         <v>3</v>
       </c>
       <c r="D336" s="1" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="E336" s="1" t="s">
-        <v>145</v>
+        <v>41</v>
       </c>
       <c r="F336" s="1" t="s">
         <v>23</v>
@@ -9439,53 +9451,53 @@
         <v>3</v>
       </c>
       <c r="D337" s="1" t="s">
-        <v>724</v>
+        <v>707</v>
       </c>
       <c r="E337" s="1" t="s">
-        <v>4</v>
+        <v>126</v>
       </c>
       <c r="F337" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A338" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="B338" s="1" t="s">
         <v>725</v>
       </c>
-      <c r="B338" s="1" t="s">
-        <v>726</v>
-      </c>
       <c r="C338" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D338" s="1" t="s">
-        <v>724</v>
+        <v>707</v>
       </c>
       <c r="E338" s="1" t="s">
-        <v>8</v>
+        <v>145</v>
       </c>
       <c r="F338" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A339" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="B339" s="1" t="s">
         <v>727</v>
       </c>
-      <c r="B339" s="1" t="s">
+      <c r="C339" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D339" s="1" t="s">
         <v>728</v>
       </c>
-      <c r="C339" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D339" s="1" t="s">
-        <v>724</v>
-      </c>
       <c r="E339" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F339" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.25">
@@ -9499,10 +9511,10 @@
         <v>3</v>
       </c>
       <c r="D340" s="1" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="E340" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F340" s="1" t="s">
         <v>31</v>
@@ -9519,10 +9531,10 @@
         <v>3</v>
       </c>
       <c r="D341" s="1" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="E341" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F341" s="1" t="s">
         <v>23</v>
@@ -9539,13 +9551,13 @@
         <v>3</v>
       </c>
       <c r="D342" s="1" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="E342" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F342" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="343" spans="1:6" x14ac:dyDescent="0.25">
@@ -9559,13 +9571,13 @@
         <v>3</v>
       </c>
       <c r="D343" s="1" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="E343" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F343" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.25">
@@ -9579,87 +9591,87 @@
         <v>3</v>
       </c>
       <c r="D344" s="1" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="E344" s="1" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="F344" s="1" t="s">
-        <v>739</v>
+        <v>23</v>
       </c>
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A345" s="1" t="s">
+        <v>739</v>
+      </c>
+      <c r="B345" s="1" t="s">
         <v>740</v>
       </c>
-      <c r="B345" s="1" t="s">
-        <v>741</v>
-      </c>
       <c r="C345" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D345" s="1" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="E345" s="1" t="s">
-        <v>126</v>
+        <v>38</v>
       </c>
       <c r="F345" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A346" s="1" t="s">
+        <v>741</v>
+      </c>
+      <c r="B346" s="1" t="s">
         <v>742</v>
       </c>
-      <c r="B346" s="1" t="s">
+      <c r="C346" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D346" s="1" t="s">
+        <v>728</v>
+      </c>
+      <c r="E346" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F346" s="1" t="s">
         <v>743</v>
-      </c>
-      <c r="C346" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D346" s="1" t="s">
-        <v>744</v>
-      </c>
-      <c r="E346" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F346" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A347" s="1" t="s">
+        <v>744</v>
+      </c>
+      <c r="B347" s="1" t="s">
         <v>745</v>
       </c>
-      <c r="B347" s="1" t="s">
-        <v>746</v>
-      </c>
       <c r="C347" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D347" s="1" t="s">
-        <v>744</v>
+        <v>728</v>
       </c>
       <c r="E347" s="1" t="s">
-        <v>8</v>
+        <v>126</v>
       </c>
       <c r="F347" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A348" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="B348" s="1" t="s">
         <v>747</v>
       </c>
-      <c r="B348" s="1" t="s">
+      <c r="C348" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D348" s="1" t="s">
         <v>748</v>
-      </c>
-      <c r="C348" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D348" s="1" t="s">
-        <v>749</v>
       </c>
       <c r="E348" s="1" t="s">
         <v>4</v>
@@ -9670,101 +9682,141 @@
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A349" s="1" t="s">
+        <v>749</v>
+      </c>
+      <c r="B349" s="1" t="s">
         <v>750</v>
       </c>
-      <c r="B349" s="1" t="s">
-        <v>751</v>
-      </c>
       <c r="C349" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D349" s="1" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="E349" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F349" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A350" s="1" t="s">
+        <v>751</v>
+      </c>
+      <c r="B350" s="1" t="s">
+        <v>752</v>
+      </c>
+      <c r="C350" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D350" s="1" t="s">
         <v>753</v>
-      </c>
-      <c r="B350" s="1" t="s">
-        <v>754</v>
-      </c>
-      <c r="C350" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D350" s="1" t="s">
-        <v>755</v>
       </c>
       <c r="E350" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F350" s="1" t="s">
-        <v>756</v>
+        <v>23</v>
       </c>
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A351" s="1" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="B351" s="1" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="C351" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D351" s="1" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="E351" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F351" s="1" t="s">
-        <v>759</v>
+        <v>28</v>
       </c>
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A352" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="B352" s="1" t="s">
+        <v>758</v>
+      </c>
+      <c r="C352" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D352" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="E352" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F352" s="1" t="s">
         <v>760</v>
-      </c>
-      <c r="B352" s="1" t="s">
-        <v>761</v>
-      </c>
-      <c r="C352" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D352" s="1" t="s">
-        <v>755</v>
-      </c>
-      <c r="E352" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F352" s="1" t="s">
-        <v>762</v>
       </c>
     </row>
     <row r="353" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A353" s="1" t="s">
+        <v>761</v>
+      </c>
+      <c r="B353" s="1" t="s">
+        <v>762</v>
+      </c>
+      <c r="C353" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D353" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="E353" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F353" s="1" t="s">
         <v>763</v>
       </c>
-      <c r="B353" s="1" t="s">
+    </row>
+    <row r="354" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A354" s="1" t="s">
         <v>764</v>
       </c>
-      <c r="C353" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D353" s="1" t="s">
-        <v>755</v>
-      </c>
-      <c r="E353" s="1" t="s">
+      <c r="B354" s="1" t="s">
+        <v>765</v>
+      </c>
+      <c r="C354" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D354" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="E354" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F354" s="1" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="355" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A355" s="1" t="s">
+        <v>767</v>
+      </c>
+      <c r="B355" s="1" t="s">
+        <v>768</v>
+      </c>
+      <c r="C355" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D355" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="E355" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F353" s="1" t="s">
+      <c r="F355" s="1" t="s">
         <v>23</v>
       </c>
     </row>

--- a/CLB07N.xlsx
+++ b/CLB07N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2130" uniqueCount="769">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2124" uniqueCount="767">
   <si>
     <t/>
   </si>
@@ -124,7 +124,7 @@
     <t>20138893</t>
   </si>
   <si>
-    <t>AMO DRMY STRAW 180ML</t>
+    <t>AMO DRMY STRAW 200ML</t>
   </si>
   <si>
     <t>7</t>
@@ -133,7 +133,7 @@
     <t>20138894</t>
   </si>
   <si>
-    <t>AMO FIZZY EASY 180ML</t>
+    <t>AMO FIZZY EASY 200ML</t>
   </si>
   <si>
     <t>8</t>
@@ -211,6 +211,111 @@
     <t>BINTANG ZERO KLG 330</t>
   </si>
   <si>
+    <t>10037437</t>
+  </si>
+  <si>
+    <t>C/B PENY.STRAW 320</t>
+  </si>
+  <si>
+    <t>10003627</t>
+  </si>
+  <si>
+    <t>C/B PENY.ORANGE320</t>
+  </si>
+  <si>
+    <t>10004237</t>
+  </si>
+  <si>
+    <t>C/B PENY.LECI 320ML</t>
+  </si>
+  <si>
+    <t>10003842</t>
+  </si>
+  <si>
+    <t>C/B PENY.JAMBU 320</t>
+  </si>
+  <si>
+    <t>20037144</t>
+  </si>
+  <si>
+    <t>KAKI3 PENY.LECI 320</t>
+  </si>
+  <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20037150</t>
+  </si>
+  <si>
+    <t>KAKI3 PENY.JAMBU 320</t>
+  </si>
+  <si>
+    <t>20037147</t>
+  </si>
+  <si>
+    <t>KAKI TIGA STRO 320ML</t>
+  </si>
+  <si>
+    <t>20045995</t>
+  </si>
+  <si>
+    <t>KAKI3 ANAK STRO 238</t>
+  </si>
+  <si>
+    <t>20053540</t>
+  </si>
+  <si>
+    <t>ADEM SARI CK BTL 350</t>
+  </si>
+  <si>
+    <t>20122090</t>
+  </si>
+  <si>
+    <t>ADEM/S MD LMN TEA350</t>
+  </si>
+  <si>
+    <t>20083775</t>
+  </si>
+  <si>
+    <t>ADEMSARI CK HR.T 320</t>
+  </si>
+  <si>
+    <t>20040276</t>
+  </si>
+  <si>
+    <t>ADEM SARI CK KLG 320</t>
+  </si>
+  <si>
+    <t>20071642</t>
+  </si>
+  <si>
+    <t>ADEMSARI CK SPRK 320</t>
+  </si>
+  <si>
+    <t>20069199</t>
+  </si>
+  <si>
+    <t>KAKI3 LMN.LM KLG 320</t>
+  </si>
+  <si>
+    <t>20142024</t>
+  </si>
+  <si>
+    <t>COOLTOPIA MELON ORG</t>
+  </si>
+  <si>
+    <t>20045996</t>
+  </si>
+  <si>
+    <t>KAKI3 ANAK LECI 238</t>
+  </si>
+  <si>
+    <t>20133709</t>
+  </si>
+  <si>
+    <t>POLARIS SARSAPRLA330</t>
+  </si>
+  <si>
     <t>20135345</t>
   </si>
   <si>
@@ -220,111 +325,6 @@
     <t>RT,(E-2.5B)</t>
   </si>
   <si>
-    <t>20133709</t>
-  </si>
-  <si>
-    <t>POLARIS SARSAPRLA330</t>
-  </si>
-  <si>
-    <t>10037437</t>
-  </si>
-  <si>
-    <t>C/B PENY.STRAW 320</t>
-  </si>
-  <si>
-    <t>10003627</t>
-  </si>
-  <si>
-    <t>C/B PENY.ORANGE320</t>
-  </si>
-  <si>
-    <t>10004237</t>
-  </si>
-  <si>
-    <t>C/B PENY.LECI 320ML</t>
-  </si>
-  <si>
-    <t>10003842</t>
-  </si>
-  <si>
-    <t>C/B PENY.JAMBU 320</t>
-  </si>
-  <si>
-    <t>20037144</t>
-  </si>
-  <si>
-    <t>KAKI3 PENY.LECI 320</t>
-  </si>
-  <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20037150</t>
-  </si>
-  <si>
-    <t>KAKI3 PENY.JAMBU 320</t>
-  </si>
-  <si>
-    <t>20037147</t>
-  </si>
-  <si>
-    <t>KAKI TIGA STRO 320ML</t>
-  </si>
-  <si>
-    <t>20045995</t>
-  </si>
-  <si>
-    <t>KAKI3 ANAK STRO 238</t>
-  </si>
-  <si>
-    <t>20053540</t>
-  </si>
-  <si>
-    <t>ADEM SARI CK BTL 350</t>
-  </si>
-  <si>
-    <t>20122090</t>
-  </si>
-  <si>
-    <t>ADEM/S MD LMN TEA350</t>
-  </si>
-  <si>
-    <t>20083775</t>
-  </si>
-  <si>
-    <t>ADEMSARI CK HR.T 320</t>
-  </si>
-  <si>
-    <t>20040276</t>
-  </si>
-  <si>
-    <t>ADEM SARI CK KLG 320</t>
-  </si>
-  <si>
-    <t>20071642</t>
-  </si>
-  <si>
-    <t>ADEMSARI CK SPRK 320</t>
-  </si>
-  <si>
-    <t>20069199</t>
-  </si>
-  <si>
-    <t>KAKI3 LMN.LM KLG 320</t>
-  </si>
-  <si>
-    <t>20142024</t>
-  </si>
-  <si>
-    <t>COOLTOPIA MELON ORG</t>
-  </si>
-  <si>
-    <t>20045996</t>
-  </si>
-  <si>
-    <t>KAKI3 ANAK LECI 238</t>
-  </si>
-  <si>
     <t>20102789</t>
   </si>
   <si>
@@ -1472,12 +1472,6 @@
   </si>
   <si>
     <t>IF COCONUT WTR 350ML</t>
-  </si>
-  <si>
-    <t>20135600</t>
-  </si>
-  <si>
-    <t>ICHTAN THAI COCO 300</t>
   </si>
   <si>
     <t>20138837</t>
@@ -2710,7 +2704,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F355"/>
+  <dimension ref="A1:F354"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -3194,7 +3188,7 @@
         <v>14</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>5</v>
@@ -3214,7 +3208,7 @@
         <v>14</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>23</v>
@@ -3234,7 +3228,7 @@
         <v>14</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>23</v>
@@ -3254,7 +3248,7 @@
         <v>14</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>23</v>
@@ -3271,30 +3265,30 @@
         <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>68</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B29" s="1" t="s">
-        <v>70</v>
-      </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>28</v>
@@ -3302,10 +3296,10 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>72</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
@@ -3314,7 +3308,7 @@
         <v>17</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>28</v>
@@ -3322,10 +3316,10 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B31" s="1" t="s">
         <v>73</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>74</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
@@ -3334,7 +3328,7 @@
         <v>17</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>28</v>
@@ -3342,10 +3336,10 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>75</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>76</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
@@ -3354,10 +3348,10 @@
         <v>17</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>28</v>
+        <v>76</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -3374,10 +3368,10 @@
         <v>17</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>28</v>
+        <v>76</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -3394,18 +3388,18 @@
         <v>17</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>83</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>3</v>
@@ -3414,58 +3408,58 @@
         <v>17</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B36" s="1" t="s">
-        <v>85</v>
-      </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>81</v>
+        <v>23</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="B37" s="1" t="s">
-        <v>87</v>
-      </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>81</v>
+        <v>28</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B38" s="1" t="s">
         <v>88</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>89</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
@@ -3474,7 +3468,7 @@
         <v>20</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>23</v>
@@ -3482,10 +3476,10 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>91</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>3</v>
@@ -3494,18 +3488,18 @@
         <v>20</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>92</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>93</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
@@ -3514,7 +3508,7 @@
         <v>20</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>23</v>
@@ -3522,10 +3516,10 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>94</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>95</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
@@ -3534,18 +3528,18 @@
         <v>20</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>23</v>
+        <v>76</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>96</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>97</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
@@ -3554,18 +3548,18 @@
         <v>20</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>23</v>
+        <v>76</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B43" s="1" t="s">
         <v>98</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>99</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
@@ -3574,50 +3568,50 @@
         <v>20</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B44" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B44" s="1" t="s">
-        <v>101</v>
-      </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>81</v>
+        <v>28</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="C45" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" s="1" t="s">
         <v>103</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F45" s="1" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -3634,10 +3628,10 @@
         <v>38</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -3654,10 +3648,10 @@
         <v>38</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -3674,7 +3668,7 @@
         <v>38</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>31</v>
@@ -3694,7 +3688,7 @@
         <v>38</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>31</v>
@@ -3714,7 +3708,7 @@
         <v>38</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>28</v>
@@ -4577,7 +4571,7 @@
         <v>11</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
@@ -6277,7 +6271,7 @@
         <v>14</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>68</v>
+        <v>103</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
@@ -6297,7 +6291,7 @@
         <v>17</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>68</v>
+        <v>103</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
@@ -6477,7 +6471,7 @@
         <v>14</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
@@ -7234,7 +7228,7 @@
         <v>480</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F226" s="1" t="s">
         <v>23</v>
@@ -7254,10 +7248,10 @@
         <v>480</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
@@ -7274,7 +7268,7 @@
         <v>480</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F228" s="1" t="s">
         <v>31</v>
@@ -7291,10 +7285,10 @@
         <v>3</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>480</v>
+        <v>495</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="F229" s="1" t="s">
         <v>31</v>
@@ -7302,19 +7296,19 @@
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="B230" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="C230" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D230" s="1" t="s">
         <v>495</v>
       </c>
-      <c r="B230" s="1" t="s">
-        <v>496</v>
-      </c>
-      <c r="C230" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D230" s="1" t="s">
-        <v>497</v>
-      </c>
       <c r="E230" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F230" s="1" t="s">
         <v>31</v>
@@ -7331,10 +7325,10 @@
         <v>3</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F231" s="1" t="s">
         <v>31</v>
@@ -7351,13 +7345,13 @@
         <v>3</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F232" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
@@ -7371,10 +7365,10 @@
         <v>3</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F233" s="1" t="s">
         <v>23</v>
@@ -7391,13 +7385,13 @@
         <v>3</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F234" s="1" t="s">
-        <v>23</v>
+        <v>165</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
@@ -7411,10 +7405,10 @@
         <v>3</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="F235" s="1" t="s">
         <v>165</v>
@@ -7431,30 +7425,30 @@
         <v>3</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>497</v>
+        <v>510</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="F236" s="1" t="s">
-        <v>165</v>
+        <v>31</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="B237" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="C237" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D237" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="B237" s="1" t="s">
-        <v>511</v>
-      </c>
-      <c r="C237" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D237" s="1" t="s">
-        <v>512</v>
-      </c>
       <c r="E237" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F237" s="1" t="s">
         <v>31</v>
@@ -7471,10 +7465,10 @@
         <v>3</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="E238" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F238" s="1" t="s">
         <v>31</v>
@@ -7491,10 +7485,10 @@
         <v>3</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="E239" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F239" s="1" t="s">
         <v>31</v>
@@ -7511,10 +7505,10 @@
         <v>3</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="E240" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F240" s="1" t="s">
         <v>31</v>
@@ -7531,13 +7525,13 @@
         <v>3</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="E241" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F241" s="1" t="s">
-        <v>31</v>
+        <v>165</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
@@ -7551,10 +7545,10 @@
         <v>3</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="E242" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="F242" s="1" t="s">
         <v>165</v>
@@ -7571,33 +7565,33 @@
         <v>3</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="E243" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F243" s="1" t="s">
-        <v>165</v>
+        <v>525</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C244" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="E244" s="1" t="s">
-        <v>41</v>
+        <v>126</v>
       </c>
       <c r="F244" s="1" t="s">
-        <v>527</v>
+        <v>28</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
@@ -7611,30 +7605,30 @@
         <v>3</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>512</v>
+        <v>530</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>126</v>
+        <v>4</v>
       </c>
       <c r="F245" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="B246" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="C246" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D246" s="1" t="s">
         <v>530</v>
       </c>
-      <c r="B246" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="C246" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D246" s="1" t="s">
-        <v>532</v>
-      </c>
       <c r="E246" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F246" s="1" t="s">
         <v>23</v>
@@ -7651,10 +7645,10 @@
         <v>3</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F247" s="1" t="s">
         <v>23</v>
@@ -7671,10 +7665,10 @@
         <v>3</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F248" s="1" t="s">
         <v>23</v>
@@ -7691,13 +7685,13 @@
         <v>3</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F249" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
@@ -7711,13 +7705,13 @@
         <v>3</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="E250" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F250" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
@@ -7731,10 +7725,10 @@
         <v>3</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="F251" s="1" t="s">
         <v>31</v>
@@ -7751,10 +7745,10 @@
         <v>3</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="E252" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F252" s="1" t="s">
         <v>31</v>
@@ -7771,30 +7765,30 @@
         <v>3</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>532</v>
+        <v>547</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="F253" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="B254" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="C254" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D254" s="1" t="s">
         <v>547</v>
       </c>
-      <c r="B254" s="1" t="s">
-        <v>548</v>
-      </c>
-      <c r="C254" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D254" s="1" t="s">
-        <v>549</v>
-      </c>
       <c r="E254" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F254" s="1" t="s">
         <v>23</v>
@@ -7811,10 +7805,10 @@
         <v>3</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F255" s="1" t="s">
         <v>23</v>
@@ -7831,10 +7825,10 @@
         <v>3</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="E256" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F256" s="1" t="s">
         <v>23</v>
@@ -7851,13 +7845,13 @@
         <v>3</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="E257" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F257" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
@@ -7871,13 +7865,13 @@
         <v>3</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F258" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
@@ -7891,10 +7885,10 @@
         <v>3</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="F259" s="1" t="s">
         <v>23</v>
@@ -7911,10 +7905,10 @@
         <v>3</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F260" s="1" t="s">
         <v>23</v>
@@ -7931,30 +7925,30 @@
         <v>3</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>549</v>
+        <v>564</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="F261" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="B262" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="C262" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D262" s="1" t="s">
         <v>564</v>
       </c>
-      <c r="B262" s="1" t="s">
-        <v>565</v>
-      </c>
-      <c r="C262" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D262" s="1" t="s">
-        <v>566</v>
-      </c>
       <c r="E262" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F262" s="1" t="s">
         <v>28</v>
@@ -7962,22 +7956,22 @@
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="B263" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="B263" s="1" t="s">
-        <v>565</v>
-      </c>
       <c r="C263" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="E263" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F263" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
@@ -7991,10 +7985,10 @@
         <v>3</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="E264" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F264" s="1" t="s">
         <v>23</v>
@@ -8011,10 +8005,10 @@
         <v>3</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="E265" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F265" s="1" t="s">
         <v>23</v>
@@ -8031,10 +8025,10 @@
         <v>3</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F266" s="1" t="s">
         <v>23</v>
@@ -8051,10 +8045,10 @@
         <v>3</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="E267" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="F267" s="1" t="s">
         <v>23</v>
@@ -8071,10 +8065,10 @@
         <v>3</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F268" s="1" t="s">
         <v>23</v>
@@ -8091,10 +8085,10 @@
         <v>3</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>41</v>
+        <v>126</v>
       </c>
       <c r="F269" s="1" t="s">
         <v>23</v>
@@ -8111,10 +8105,10 @@
         <v>3</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>566</v>
+        <v>582</v>
       </c>
       <c r="E270" s="1" t="s">
-        <v>126</v>
+        <v>4</v>
       </c>
       <c r="F270" s="1" t="s">
         <v>23</v>
@@ -8122,19 +8116,19 @@
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="B271" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="C271" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D271" s="1" t="s">
         <v>582</v>
       </c>
-      <c r="B271" s="1" t="s">
-        <v>583</v>
-      </c>
-      <c r="C271" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D271" s="1" t="s">
-        <v>584</v>
-      </c>
       <c r="E271" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F271" s="1" t="s">
         <v>23</v>
@@ -8151,10 +8145,10 @@
         <v>3</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="E272" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F272" s="1" t="s">
         <v>23</v>
@@ -8171,10 +8165,10 @@
         <v>3</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F273" s="1" t="s">
         <v>23</v>
@@ -8191,10 +8185,10 @@
         <v>3</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F274" s="1" t="s">
         <v>23</v>
@@ -8211,10 +8205,10 @@
         <v>3</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="E275" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F275" s="1" t="s">
         <v>23</v>
@@ -8231,10 +8225,10 @@
         <v>3</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="E276" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="F276" s="1" t="s">
         <v>23</v>
@@ -8251,10 +8245,10 @@
         <v>3</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="E277" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F277" s="1" t="s">
         <v>23</v>
@@ -8271,10 +8265,10 @@
         <v>3</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>41</v>
+        <v>126</v>
       </c>
       <c r="F278" s="1" t="s">
         <v>23</v>
@@ -8291,10 +8285,10 @@
         <v>3</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="E279" s="1" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="F279" s="1" t="s">
         <v>23</v>
@@ -8311,10 +8305,10 @@
         <v>3</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="E280" s="1" t="s">
-        <v>145</v>
+        <v>164</v>
       </c>
       <c r="F280" s="1" t="s">
         <v>23</v>
@@ -8331,10 +8325,10 @@
         <v>3</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>584</v>
+        <v>605</v>
       </c>
       <c r="E281" s="1" t="s">
-        <v>164</v>
+        <v>4</v>
       </c>
       <c r="F281" s="1" t="s">
         <v>23</v>
@@ -8342,19 +8336,19 @@
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="B282" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="C282" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D282" s="1" t="s">
         <v>605</v>
       </c>
-      <c r="B282" s="1" t="s">
-        <v>606</v>
-      </c>
-      <c r="C282" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D282" s="1" t="s">
-        <v>607</v>
-      </c>
       <c r="E282" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F282" s="1" t="s">
         <v>23</v>
@@ -8371,10 +8365,10 @@
         <v>3</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E283" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F283" s="1" t="s">
         <v>23</v>
@@ -8391,10 +8385,10 @@
         <v>3</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F284" s="1" t="s">
         <v>23</v>
@@ -8411,10 +8405,10 @@
         <v>3</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E285" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F285" s="1" t="s">
         <v>23</v>
@@ -8431,10 +8425,10 @@
         <v>3</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F286" s="1" t="s">
         <v>23</v>
@@ -8451,33 +8445,33 @@
         <v>3</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="F287" s="1" t="s">
-        <v>23</v>
+        <v>618</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288" s="1" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C288" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F288" s="1" t="s">
-        <v>620</v>
+        <v>23</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
@@ -8491,10 +8485,10 @@
         <v>3</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E289" s="1" t="s">
-        <v>41</v>
+        <v>126</v>
       </c>
       <c r="F289" s="1" t="s">
         <v>23</v>
@@ -8511,10 +8505,10 @@
         <v>3</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E290" s="1" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="F290" s="1" t="s">
         <v>23</v>
@@ -8531,33 +8525,33 @@
         <v>3</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>607</v>
+        <v>627</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>145</v>
+        <v>4</v>
       </c>
       <c r="F291" s="1" t="s">
-        <v>23</v>
+        <v>618</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A292" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="B292" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="C292" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D292" s="1" t="s">
         <v>627</v>
       </c>
-      <c r="B292" s="1" t="s">
-        <v>628</v>
-      </c>
-      <c r="C292" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D292" s="1" t="s">
-        <v>629</v>
-      </c>
       <c r="E292" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F292" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
@@ -8571,13 +8565,13 @@
         <v>3</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="E293" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F293" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
@@ -8591,13 +8585,13 @@
         <v>3</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="E294" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F294" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
@@ -8611,13 +8605,13 @@
         <v>3</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="E295" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F295" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
@@ -8631,13 +8625,13 @@
         <v>3</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="E296" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F296" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
@@ -8651,13 +8645,13 @@
         <v>3</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="F297" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
@@ -8671,13 +8665,13 @@
         <v>3</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F298" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
@@ -8691,13 +8685,13 @@
         <v>3</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>41</v>
+        <v>126</v>
       </c>
       <c r="F299" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
@@ -8711,30 +8705,30 @@
         <v>3</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>629</v>
+        <v>646</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>126</v>
+        <v>4</v>
       </c>
       <c r="F300" s="1" t="s">
-        <v>620</v>
+        <v>23</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A301" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="B301" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="C301" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D301" s="1" t="s">
         <v>646</v>
       </c>
-      <c r="B301" s="1" t="s">
-        <v>647</v>
-      </c>
-      <c r="C301" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D301" s="1" t="s">
-        <v>648</v>
-      </c>
       <c r="E301" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F301" s="1" t="s">
         <v>23</v>
@@ -8751,10 +8745,10 @@
         <v>3</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="E302" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F302" s="1" t="s">
         <v>23</v>
@@ -8771,10 +8765,10 @@
         <v>3</v>
       </c>
       <c r="D303" s="1" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="E303" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F303" s="1" t="s">
         <v>23</v>
@@ -8791,10 +8785,10 @@
         <v>3</v>
       </c>
       <c r="D304" s="1" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="E304" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F304" s="1" t="s">
         <v>23</v>
@@ -8811,10 +8805,10 @@
         <v>3</v>
       </c>
       <c r="D305" s="1" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="E305" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F305" s="1" t="s">
         <v>23</v>
@@ -8831,10 +8825,10 @@
         <v>3</v>
       </c>
       <c r="D306" s="1" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="E306" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="F306" s="1" t="s">
         <v>23</v>
@@ -8851,10 +8845,10 @@
         <v>3</v>
       </c>
       <c r="D307" s="1" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="E307" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F307" s="1" t="s">
         <v>23</v>
@@ -8871,10 +8865,10 @@
         <v>3</v>
       </c>
       <c r="D308" s="1" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="E308" s="1" t="s">
-        <v>41</v>
+        <v>126</v>
       </c>
       <c r="F308" s="1" t="s">
         <v>23</v>
@@ -8891,10 +8885,10 @@
         <v>3</v>
       </c>
       <c r="D309" s="1" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="E309" s="1" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="F309" s="1" t="s">
         <v>23</v>
@@ -8911,10 +8905,10 @@
         <v>3</v>
       </c>
       <c r="D310" s="1" t="s">
-        <v>648</v>
+        <v>667</v>
       </c>
       <c r="E310" s="1" t="s">
-        <v>145</v>
+        <v>4</v>
       </c>
       <c r="F310" s="1" t="s">
         <v>23</v>
@@ -8922,19 +8916,19 @@
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A311" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="B311" s="1" t="s">
+        <v>669</v>
+      </c>
+      <c r="C311" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D311" s="1" t="s">
         <v>667</v>
       </c>
-      <c r="B311" s="1" t="s">
-        <v>668</v>
-      </c>
-      <c r="C311" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D311" s="1" t="s">
-        <v>669</v>
-      </c>
       <c r="E311" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F311" s="1" t="s">
         <v>23</v>
@@ -8951,10 +8945,10 @@
         <v>3</v>
       </c>
       <c r="D312" s="1" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="E312" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F312" s="1" t="s">
         <v>23</v>
@@ -8971,10 +8965,10 @@
         <v>3</v>
       </c>
       <c r="D313" s="1" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="E313" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F313" s="1" t="s">
         <v>23</v>
@@ -8991,10 +8985,10 @@
         <v>3</v>
       </c>
       <c r="D314" s="1" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="E314" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F314" s="1" t="s">
         <v>23</v>
@@ -9011,10 +9005,10 @@
         <v>3</v>
       </c>
       <c r="D315" s="1" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="E315" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F315" s="1" t="s">
         <v>23</v>
@@ -9031,10 +9025,10 @@
         <v>3</v>
       </c>
       <c r="D316" s="1" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="E316" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="F316" s="1" t="s">
         <v>23</v>
@@ -9051,10 +9045,10 @@
         <v>3</v>
       </c>
       <c r="D317" s="1" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="E317" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F317" s="1" t="s">
         <v>23</v>
@@ -9071,10 +9065,10 @@
         <v>3</v>
       </c>
       <c r="D318" s="1" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="E318" s="1" t="s">
-        <v>41</v>
+        <v>126</v>
       </c>
       <c r="F318" s="1" t="s">
         <v>23</v>
@@ -9091,10 +9085,10 @@
         <v>3</v>
       </c>
       <c r="D319" s="1" t="s">
-        <v>669</v>
+        <v>686</v>
       </c>
       <c r="E319" s="1" t="s">
-        <v>126</v>
+        <v>4</v>
       </c>
       <c r="F319" s="1" t="s">
         <v>23</v>
@@ -9102,19 +9096,19 @@
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A320" s="1" t="s">
+        <v>687</v>
+      </c>
+      <c r="B320" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="C320" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D320" s="1" t="s">
         <v>686</v>
       </c>
-      <c r="B320" s="1" t="s">
-        <v>687</v>
-      </c>
-      <c r="C320" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D320" s="1" t="s">
-        <v>688</v>
-      </c>
       <c r="E320" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F320" s="1" t="s">
         <v>23</v>
@@ -9131,10 +9125,10 @@
         <v>3</v>
       </c>
       <c r="D321" s="1" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="E321" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F321" s="1" t="s">
         <v>23</v>
@@ -9151,10 +9145,10 @@
         <v>3</v>
       </c>
       <c r="D322" s="1" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="E322" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F322" s="1" t="s">
         <v>23</v>
@@ -9171,10 +9165,10 @@
         <v>3</v>
       </c>
       <c r="D323" s="1" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="E323" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F323" s="1" t="s">
         <v>23</v>
@@ -9191,10 +9185,10 @@
         <v>3</v>
       </c>
       <c r="D324" s="1" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="E324" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F324" s="1" t="s">
         <v>23</v>
@@ -9211,10 +9205,10 @@
         <v>3</v>
       </c>
       <c r="D325" s="1" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="E325" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="F325" s="1" t="s">
         <v>23</v>
@@ -9231,10 +9225,10 @@
         <v>3</v>
       </c>
       <c r="D326" s="1" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="E326" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F326" s="1" t="s">
         <v>23</v>
@@ -9251,10 +9245,10 @@
         <v>3</v>
       </c>
       <c r="D327" s="1" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="E327" s="1" t="s">
-        <v>41</v>
+        <v>126</v>
       </c>
       <c r="F327" s="1" t="s">
         <v>23</v>
@@ -9271,10 +9265,10 @@
         <v>3</v>
       </c>
       <c r="D328" s="1" t="s">
-        <v>688</v>
+        <v>705</v>
       </c>
       <c r="E328" s="1" t="s">
-        <v>126</v>
+        <v>4</v>
       </c>
       <c r="F328" s="1" t="s">
         <v>23</v>
@@ -9282,19 +9276,19 @@
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A329" s="1" t="s">
+        <v>706</v>
+      </c>
+      <c r="B329" s="1" t="s">
+        <v>707</v>
+      </c>
+      <c r="C329" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D329" s="1" t="s">
         <v>705</v>
       </c>
-      <c r="B329" s="1" t="s">
-        <v>706</v>
-      </c>
-      <c r="C329" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D329" s="1" t="s">
-        <v>707</v>
-      </c>
       <c r="E329" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F329" s="1" t="s">
         <v>23</v>
@@ -9311,13 +9305,13 @@
         <v>3</v>
       </c>
       <c r="D330" s="1" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="E330" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F330" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.25">
@@ -9331,10 +9325,10 @@
         <v>3</v>
       </c>
       <c r="D331" s="1" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="E331" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F331" s="1" t="s">
         <v>31</v>
@@ -9351,13 +9345,13 @@
         <v>3</v>
       </c>
       <c r="D332" s="1" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="E332" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F332" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.25">
@@ -9371,10 +9365,10 @@
         <v>3</v>
       </c>
       <c r="D333" s="1" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="E333" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F333" s="1" t="s">
         <v>23</v>
@@ -9391,10 +9385,10 @@
         <v>3</v>
       </c>
       <c r="D334" s="1" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="E334" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="F334" s="1" t="s">
         <v>23</v>
@@ -9411,10 +9405,10 @@
         <v>3</v>
       </c>
       <c r="D335" s="1" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="E335" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F335" s="1" t="s">
         <v>23</v>
@@ -9431,10 +9425,10 @@
         <v>3</v>
       </c>
       <c r="D336" s="1" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="E336" s="1" t="s">
-        <v>41</v>
+        <v>126</v>
       </c>
       <c r="F336" s="1" t="s">
         <v>23</v>
@@ -9451,10 +9445,10 @@
         <v>3</v>
       </c>
       <c r="D337" s="1" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="E337" s="1" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="F337" s="1" t="s">
         <v>23</v>
@@ -9471,33 +9465,33 @@
         <v>3</v>
       </c>
       <c r="D338" s="1" t="s">
-        <v>707</v>
+        <v>726</v>
       </c>
       <c r="E338" s="1" t="s">
-        <v>145</v>
+        <v>4</v>
       </c>
       <c r="F338" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A339" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="B339" s="1" t="s">
+        <v>728</v>
+      </c>
+      <c r="C339" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D339" s="1" t="s">
         <v>726</v>
       </c>
-      <c r="B339" s="1" t="s">
-        <v>727</v>
-      </c>
-      <c r="C339" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D339" s="1" t="s">
-        <v>728</v>
-      </c>
       <c r="E339" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F339" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.25">
@@ -9511,13 +9505,13 @@
         <v>3</v>
       </c>
       <c r="D340" s="1" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="E340" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F340" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.25">
@@ -9531,13 +9525,13 @@
         <v>3</v>
       </c>
       <c r="D341" s="1" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="E341" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F341" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.25">
@@ -9551,13 +9545,13 @@
         <v>3</v>
       </c>
       <c r="D342" s="1" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="E342" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F342" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="343" spans="1:6" x14ac:dyDescent="0.25">
@@ -9571,10 +9565,10 @@
         <v>3</v>
       </c>
       <c r="D343" s="1" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="E343" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F343" s="1" t="s">
         <v>23</v>
@@ -9591,13 +9585,13 @@
         <v>3</v>
       </c>
       <c r="D344" s="1" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="E344" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="F344" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.25">
@@ -9611,33 +9605,33 @@
         <v>3</v>
       </c>
       <c r="D345" s="1" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="E345" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F345" s="1" t="s">
-        <v>31</v>
+        <v>741</v>
       </c>
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A346" s="1" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B346" s="1" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="C346" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D346" s="1" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="E346" s="1" t="s">
-        <v>41</v>
+        <v>126</v>
       </c>
       <c r="F346" s="1" t="s">
-        <v>743</v>
+        <v>28</v>
       </c>
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.25">
@@ -9651,30 +9645,30 @@
         <v>3</v>
       </c>
       <c r="D347" s="1" t="s">
-        <v>728</v>
+        <v>746</v>
       </c>
       <c r="E347" s="1" t="s">
-        <v>126</v>
+        <v>4</v>
       </c>
       <c r="F347" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A348" s="1" t="s">
+        <v>747</v>
+      </c>
+      <c r="B348" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="C348" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D348" s="1" t="s">
         <v>746</v>
       </c>
-      <c r="B348" s="1" t="s">
-        <v>747</v>
-      </c>
-      <c r="C348" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D348" s="1" t="s">
-        <v>748</v>
-      </c>
       <c r="E348" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F348" s="1" t="s">
         <v>23</v>
@@ -9691,10 +9685,10 @@
         <v>3</v>
       </c>
       <c r="D349" s="1" t="s">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="E349" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F349" s="1" t="s">
         <v>23</v>
@@ -9702,121 +9696,101 @@
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A350" s="1" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B350" s="1" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C350" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D350" s="1" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="E350" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F350" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A351" s="1" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B351" s="1" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="C351" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D351" s="1" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="E351" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F351" s="1" t="s">
-        <v>28</v>
+        <v>758</v>
       </c>
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A352" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="B352" s="1" t="s">
+        <v>760</v>
+      </c>
+      <c r="C352" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D352" s="1" t="s">
         <v>757</v>
       </c>
-      <c r="B352" s="1" t="s">
-        <v>758</v>
-      </c>
-      <c r="C352" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D352" s="1" t="s">
-        <v>759</v>
-      </c>
       <c r="E352" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F352" s="1" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
     </row>
     <row r="353" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A353" s="1" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="B353" s="1" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="C353" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D353" s="1" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="E353" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F353" s="1" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
     </row>
     <row r="354" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A354" s="1" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="B354" s="1" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="C354" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D354" s="1" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="E354" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F354" s="1" t="s">
-        <v>766</v>
-      </c>
-    </row>
-    <row r="355" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A355" s="1" t="s">
-        <v>767</v>
-      </c>
-      <c r="B355" s="1" t="s">
-        <v>768</v>
-      </c>
-      <c r="C355" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D355" s="1" t="s">
-        <v>759</v>
-      </c>
-      <c r="E355" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F355" s="1" t="s">
         <v>23</v>
       </c>
     </row>

--- a/CLB07N.xlsx
+++ b/CLB07N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2124" uniqueCount="767">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2118" uniqueCount="766">
   <si>
     <t/>
   </si>
@@ -661,300 +661,297 @@
     <t>EXTRA JOSS ULTIMT250</t>
   </si>
   <si>
+    <t>20003786</t>
+  </si>
+  <si>
+    <t>NU GREEN TEA HNY 450</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>20113059</t>
+  </si>
+  <si>
+    <t>NU YOGURT TEA 450ML</t>
+  </si>
+  <si>
+    <t>20139732</t>
+  </si>
+  <si>
+    <t>NU YOGRT TEA BRY 450</t>
+  </si>
+  <si>
+    <t>20002203</t>
+  </si>
+  <si>
+    <t>SOSRO F.TEA APEL 500</t>
+  </si>
+  <si>
+    <t>20003698</t>
+  </si>
+  <si>
+    <t>SOSRO FR.TEA XTRM500</t>
+  </si>
+  <si>
+    <t>20002205</t>
+  </si>
+  <si>
+    <t>SOSRO F.TEA BLKCR500</t>
+  </si>
+  <si>
+    <t>20134046</t>
+  </si>
+  <si>
+    <t>FRUIT TEA FREEZE 500</t>
+  </si>
+  <si>
+    <t>20035829</t>
+  </si>
+  <si>
+    <t>TEBS TEA WT/SODA 500</t>
+  </si>
+  <si>
+    <t>20126464</t>
+  </si>
+  <si>
+    <t>IDM TEH APL&amp;LYCHE350</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>20101897</t>
+  </si>
+  <si>
+    <t>IDM TEH APEL 350ML</t>
+  </si>
+  <si>
+    <t>20132840</t>
+  </si>
+  <si>
+    <t>IDM TEH BLCKCRRNT350</t>
+  </si>
+  <si>
+    <t>20066454</t>
+  </si>
+  <si>
+    <t>FRUIT TEA BLCKCR 350</t>
+  </si>
+  <si>
+    <t>20073495</t>
+  </si>
+  <si>
+    <t>FRUIT TEA FREEZE 350</t>
+  </si>
+  <si>
+    <t>20066455</t>
+  </si>
+  <si>
+    <t>FRUIT TEA APPLE 350</t>
+  </si>
+  <si>
+    <t>20079972</t>
+  </si>
+  <si>
+    <t>FRUIT TEA MRKISA 350</t>
+  </si>
+  <si>
+    <t>20060207</t>
+  </si>
+  <si>
+    <t>I/OCHA TEH MLATI 350</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>20048934</t>
+  </si>
+  <si>
+    <t>I/OCHA GRN TEA 350ML</t>
+  </si>
+  <si>
+    <t>20142077</t>
+  </si>
+  <si>
+    <t>TEH LEMON MADU 350ML</t>
+  </si>
+  <si>
+    <t>,(E-1B)</t>
+  </si>
+  <si>
+    <t>20018904</t>
+  </si>
+  <si>
+    <t>NU GREEN TEA HNY 330</t>
+  </si>
+  <si>
+    <t>20053867</t>
+  </si>
+  <si>
+    <t>TEH GELAS BTL 350ML</t>
+  </si>
+  <si>
+    <t>20073396</t>
+  </si>
+  <si>
+    <t>S-TEE BTL 390ML</t>
+  </si>
+  <si>
+    <t>20072249</t>
+  </si>
+  <si>
+    <t>SOSRO TEH BOTOL 350</t>
+  </si>
+  <si>
+    <t>20122278</t>
+  </si>
+  <si>
+    <t>TEH BOTOL LS.SGR 350</t>
+  </si>
+  <si>
+    <t>20082395</t>
+  </si>
+  <si>
+    <t>TEH BOTOL TAWAR 350</t>
+  </si>
+  <si>
+    <t>RT,(E-3.5B)</t>
+  </si>
+  <si>
+    <t>20035484</t>
+  </si>
+  <si>
+    <t>PUCUK/H TEH MLATI350</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>20048155</t>
+  </si>
+  <si>
+    <t>PUCUK/H TEH L/SGR350</t>
+  </si>
+  <si>
+    <t>20037565</t>
+  </si>
+  <si>
+    <t>PUCUK/H TEH MLATI500</t>
+  </si>
+  <si>
+    <t>20048348</t>
+  </si>
+  <si>
+    <t>PUCUK/H TEH L/SGR500</t>
+  </si>
+  <si>
+    <t>20036157</t>
+  </si>
+  <si>
+    <t>SOSRO TEH BOTOL 450</t>
+  </si>
+  <si>
+    <t>20026226</t>
+  </si>
+  <si>
+    <t>ULTRA TEH KOTAK 500</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>10036640</t>
+  </si>
+  <si>
+    <t>TEH KOTAK JASMINE300</t>
+  </si>
+  <si>
+    <t>20048435</t>
+  </si>
+  <si>
+    <t>TEH KOTAK LESS/S 300</t>
+  </si>
+  <si>
+    <t>20044334</t>
+  </si>
+  <si>
+    <t>SOSRO TEH BTL TPK300</t>
+  </si>
+  <si>
+    <t>10005128</t>
+  </si>
+  <si>
+    <t>SOSRO TEH KOTAK B250</t>
+  </si>
+  <si>
+    <t>20024315</t>
+  </si>
+  <si>
+    <t>TEH BOTOL LS.SGR 250</t>
+  </si>
+  <si>
+    <t>20002209</t>
+  </si>
+  <si>
+    <t>TEBS SPRK MIX FRT330</t>
+  </si>
+  <si>
+    <t>20100142</t>
+  </si>
+  <si>
+    <t>TEH KOTAK BLCKCR 300</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>20100143</t>
+  </si>
+  <si>
+    <t>TEH KOTAK APPLE 300</t>
+  </si>
+  <si>
+    <t>20137159</t>
+  </si>
+  <si>
+    <t>TEH KOTAK MANGGA 300</t>
+  </si>
+  <si>
+    <t>20087016</t>
+  </si>
+  <si>
+    <t>TEH KOTAK LEMON 300</t>
+  </si>
+  <si>
+    <t>20135647</t>
+  </si>
+  <si>
+    <t>TEH KOTAK LYCHEE 300</t>
+  </si>
+  <si>
+    <t>20117687</t>
+  </si>
+  <si>
+    <t>DLMNT BOBA MTCHA 240</t>
+  </si>
+  <si>
+    <t>20117682</t>
+  </si>
+  <si>
+    <t>DLMNT BOBA RD.VEL240</t>
+  </si>
+  <si>
     <t>20080088</t>
   </si>
   <si>
     <t>POKKA GREEN TEA 450</t>
   </si>
   <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>20037565</t>
-  </si>
-  <si>
-    <t>PUCUK/H TEH MLATI500</t>
-  </si>
-  <si>
-    <t>20048348</t>
-  </si>
-  <si>
-    <t>PUCUK/H TEH L/SGR500</t>
-  </si>
-  <si>
-    <t>20036157</t>
-  </si>
-  <si>
-    <t>SOSRO TEH BOTOL 450</t>
-  </si>
-  <si>
-    <t>20002203</t>
-  </si>
-  <si>
-    <t>SOSRO F.TEA APEL 500</t>
-  </si>
-  <si>
-    <t>20003698</t>
-  </si>
-  <si>
-    <t>SOSRO FR.TEA XTRM500</t>
-  </si>
-  <si>
-    <t>20002205</t>
-  </si>
-  <si>
-    <t>SOSRO F.TEA BLKCR500</t>
-  </si>
-  <si>
-    <t>20134046</t>
-  </si>
-  <si>
-    <t>FRUIT TEA FREEZE 500</t>
-  </si>
-  <si>
-    <t>20060210</t>
-  </si>
-  <si>
-    <t>IDM TEH HJAU MLT 330</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>20077509</t>
-  </si>
-  <si>
-    <t>IDM LEMON TEA 330ML</t>
-  </si>
-  <si>
-    <t>20126464</t>
-  </si>
-  <si>
-    <t>IDM TEH APL&amp;LYCHE350</t>
-  </si>
-  <si>
-    <t>20101897</t>
-  </si>
-  <si>
-    <t>IDM TEH APEL 350ML</t>
-  </si>
-  <si>
-    <t>20132840</t>
-  </si>
-  <si>
-    <t>IDM TEH BLCKCRRNT350</t>
-  </si>
-  <si>
-    <t>20066454</t>
-  </si>
-  <si>
-    <t>FRUIT TEA BLCKCR 350</t>
-  </si>
-  <si>
-    <t>20073495</t>
-  </si>
-  <si>
-    <t>FRUIT TEA FREEZE 350</t>
-  </si>
-  <si>
-    <t>20066455</t>
-  </si>
-  <si>
-    <t>FRUIT TEA APPLE 350</t>
-  </si>
-  <si>
-    <t>20079972</t>
-  </si>
-  <si>
-    <t>FRUIT TEA MRKISA 350</t>
-  </si>
-  <si>
-    <t>20060207</t>
-  </si>
-  <si>
-    <t>I/OCHA TEH MLATI 350</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>20048934</t>
-  </si>
-  <si>
-    <t>I/OCHA GRN TEA 350ML</t>
-  </si>
-  <si>
-    <t>20018904</t>
-  </si>
-  <si>
-    <t>NU GREEN TEA HNY 330</t>
-  </si>
-  <si>
-    <t>20053867</t>
-  </si>
-  <si>
-    <t>TEH GELAS BTL 350ML</t>
-  </si>
-  <si>
-    <t>20073396</t>
-  </si>
-  <si>
-    <t>S-TEE BTL 390ML</t>
-  </si>
-  <si>
-    <t>20072249</t>
-  </si>
-  <si>
-    <t>SOSRO TEH BOTOL 350</t>
-  </si>
-  <si>
-    <t>20122278</t>
-  </si>
-  <si>
-    <t>TEH BOTOL LS.SGR 350</t>
-  </si>
-  <si>
-    <t>20082395</t>
-  </si>
-  <si>
-    <t>TEH BOTOL TAWAR 350</t>
-  </si>
-  <si>
-    <t>RT,(E-3.5B)</t>
-  </si>
-  <si>
-    <t>20035484</t>
-  </si>
-  <si>
-    <t>PUCUK/H TEH MLATI350</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>20048155</t>
-  </si>
-  <si>
-    <t>PUCUK/H TEH L/SGR350</t>
-  </si>
-  <si>
-    <t>20026226</t>
-  </si>
-  <si>
-    <t>ULTRA TEH KOTAK 500</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>10036640</t>
-  </si>
-  <si>
-    <t>TEH KOTAK JASMINE300</t>
-  </si>
-  <si>
-    <t>20044334</t>
-  </si>
-  <si>
-    <t>SOSRO TEH BTL TPK300</t>
-  </si>
-  <si>
-    <t>10005128</t>
-  </si>
-  <si>
-    <t>SOSRO TEH KOTAK B250</t>
-  </si>
-  <si>
-    <t>20024315</t>
-  </si>
-  <si>
-    <t>TEH BOTOL LS.SGR 250</t>
-  </si>
-  <si>
-    <t>20002209</t>
-  </si>
-  <si>
-    <t>TEBS SPRK MIX FRT330</t>
-  </si>
-  <si>
-    <t>20048435</t>
-  </si>
-  <si>
-    <t>TEH KOTAK LESS/S 300</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>20100142</t>
-  </si>
-  <si>
-    <t>TEH KOTAK BLCKCR 300</t>
-  </si>
-  <si>
-    <t>20100143</t>
-  </si>
-  <si>
-    <t>TEH KOTAK APPLE 300</t>
-  </si>
-  <si>
-    <t>20137159</t>
-  </si>
-  <si>
-    <t>TEH KOTAK MANGGA 300</t>
-  </si>
-  <si>
-    <t>20087016</t>
-  </si>
-  <si>
-    <t>TEH KOTAK LEMON 300</t>
-  </si>
-  <si>
-    <t>20135647</t>
-  </si>
-  <si>
-    <t>TEH KOTAK LYCHEE 300</t>
-  </si>
-  <si>
-    <t>20117682</t>
-  </si>
-  <si>
-    <t>DLMNT BOBA RD.VEL240</t>
-  </si>
-  <si>
-    <t>20117687</t>
-  </si>
-  <si>
-    <t>DLMNT BOBA MTCHA 240</t>
-  </si>
-  <si>
-    <t>20003786</t>
-  </si>
-  <si>
-    <t>NU GREEN TEA HNY 450</t>
-  </si>
-  <si>
     <t>20</t>
   </si>
   <si>
-    <t>20113059</t>
-  </si>
-  <si>
-    <t>NU YOGURT TEA 450ML</t>
-  </si>
-  <si>
-    <t>20139732</t>
-  </si>
-  <si>
-    <t>NU YOGRT TEA BRY 450</t>
-  </si>
-  <si>
-    <t>20012573</t>
-  </si>
-  <si>
-    <t>FRESTEA TEH MLATI500</t>
-  </si>
-  <si>
     <t>20036765</t>
   </si>
   <si>
@@ -967,18 +964,24 @@
     <t>FRESTEA TEH APEL 500</t>
   </si>
   <si>
-    <t>20035829</t>
-  </si>
-  <si>
-    <t>TEBS TEA WT/SODA 500</t>
-  </si>
-  <si>
     <t>20138841</t>
   </si>
   <si>
     <t>POKKA NAT. H.ORG 350</t>
   </si>
   <si>
+    <t>20046315</t>
+  </si>
+  <si>
+    <t>MINUTE M. NB STRW300</t>
+  </si>
+  <si>
+    <t>20046314</t>
+  </si>
+  <si>
+    <t>MINUTE M. NB ORG 300</t>
+  </si>
+  <si>
     <t>20040383</t>
   </si>
   <si>
@@ -1360,12 +1363,6 @@
     <t>PORORO PEACH 235</t>
   </si>
   <si>
-    <t>20037138</t>
-  </si>
-  <si>
-    <t>PORORO APEL 235ML</t>
-  </si>
-  <si>
     <t>20141361</t>
   </si>
   <si>
@@ -1384,33 +1381,33 @@
     <t>B/BRAND GOLD MALT140</t>
   </si>
   <si>
+    <t>20069773</t>
+  </si>
+  <si>
+    <t>ISOPLUS BTL 350ML</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>20128918</t>
+  </si>
+  <si>
+    <t>ISOPLUS COCO 350ML</t>
+  </si>
+  <si>
     <t>20141124</t>
   </si>
   <si>
     <t>REGEN ORANGE 300ML</t>
   </si>
   <si>
-    <t>28</t>
-  </si>
-  <si>
     <t>20139550</t>
   </si>
   <si>
     <t>REGEN LMN LIME 300ML</t>
   </si>
   <si>
-    <t>20046315</t>
-  </si>
-  <si>
-    <t>MINUTE M. NB STRW300</t>
-  </si>
-  <si>
-    <t>20046314</t>
-  </si>
-  <si>
-    <t>MINUTE M. NB ORG 300</t>
-  </si>
-  <si>
     <t>20129123</t>
   </si>
   <si>
@@ -1456,22 +1453,22 @@
     <t>29</t>
   </si>
   <si>
-    <t>20069773</t>
-  </si>
-  <si>
-    <t>ISOPLUS BTL 350ML</t>
-  </si>
-  <si>
-    <t>20128918</t>
-  </si>
-  <si>
-    <t>ISOPLUS COCO 350ML</t>
-  </si>
-  <si>
     <t>20138959</t>
   </si>
   <si>
     <t>IF COCONUT WTR 350ML</t>
+  </si>
+  <si>
+    <t>20142358</t>
+  </si>
+  <si>
+    <t>POWRADE ACTIV WHT400</t>
+  </si>
+  <si>
+    <t>20142359</t>
+  </si>
+  <si>
+    <t>POWRADE ISOTN BLU400</t>
   </si>
   <si>
     <t>20138837</t>
@@ -2704,7 +2701,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F354"/>
+  <dimension ref="A1:F353"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -4691,7 +4688,7 @@
         <v>4</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -4848,7 +4845,7 @@
         <v>235</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>165</v>
@@ -4868,7 +4865,7 @@
         <v>235</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>165</v>
@@ -4888,7 +4885,7 @@
         <v>235</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>165</v>
@@ -4908,10 +4905,10 @@
         <v>235</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>165</v>
+        <v>23</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -4928,10 +4925,10 @@
         <v>235</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>165</v>
+        <v>23</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -4948,7 +4945,7 @@
         <v>235</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>23</v>
@@ -4968,7 +4965,7 @@
         <v>235</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>38</v>
+        <v>126</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>23</v>
@@ -4985,10 +4982,10 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>235</v>
+        <v>250</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>23</v>
@@ -4996,19 +4993,19 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D115" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="B115" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="C115" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D115" s="1" t="s">
-        <v>235</v>
-      </c>
       <c r="E115" s="1" t="s">
-        <v>126</v>
+        <v>8</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>23</v>
@@ -5016,39 +5013,39 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>23</v>
+        <v>255</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>23</v>
@@ -5056,19 +5053,19 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>23</v>
@@ -5076,19 +5073,19 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>23</v>
@@ -5096,19 +5093,19 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>23</v>
@@ -5116,19 +5113,19 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>23</v>
@@ -5136,59 +5133,59 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>38</v>
+        <v>126</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>23</v>
+        <v>268</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>254</v>
+        <v>271</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>269</v>
+        <v>23</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B124" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D124" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="C124" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D124" s="1" t="s">
-        <v>272</v>
-      </c>
       <c r="E124" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>23</v>
@@ -5196,19 +5193,19 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>23</v>
@@ -5216,19 +5213,19 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>23</v>
@@ -5245,10 +5242,10 @@
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>23</v>
@@ -5265,10 +5262,10 @@
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>23</v>
@@ -5276,19 +5273,19 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D129" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="B129" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="C129" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D129" s="1" t="s">
-        <v>277</v>
-      </c>
       <c r="E129" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>23</v>
@@ -5296,19 +5293,19 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>23</v>
@@ -5316,19 +5313,19 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>23</v>
@@ -5336,19 +5333,19 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>23</v>
@@ -5365,10 +5362,10 @@
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>23</v>
@@ -5385,10 +5382,10 @@
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>23</v>
@@ -5405,10 +5402,10 @@
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>23</v>
@@ -5416,19 +5413,19 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D136" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="B136" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="C136" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D136" s="1" t="s">
-        <v>290</v>
-      </c>
       <c r="E136" s="1" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>23</v>
@@ -5436,19 +5433,19 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>23</v>
@@ -5456,62 +5453,62 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
@@ -5525,13 +5522,13 @@
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
@@ -5545,30 +5542,30 @@
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D143" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="B143" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="C143" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D143" s="1" t="s">
-        <v>307</v>
-      </c>
       <c r="E143" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>5</v>
@@ -5576,19 +5573,19 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>5</v>
@@ -5596,76 +5593,76 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E148" s="1" t="s">
         <v>4</v>
@@ -5676,16 +5673,16 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D149" s="1" t="s">
         <v>325</v>
-      </c>
-      <c r="B149" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="C149" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D149" s="1" t="s">
-        <v>324</v>
       </c>
       <c r="E149" s="1" t="s">
         <v>8</v>
@@ -5696,16 +5693,16 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E150" s="1" t="s">
         <v>11</v>
@@ -5716,16 +5713,16 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E151" s="1" t="s">
         <v>14</v>
@@ -5736,16 +5733,16 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E152" s="1" t="s">
         <v>17</v>
@@ -5756,16 +5753,16 @@
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E153" s="1" t="s">
         <v>20</v>
@@ -5776,16 +5773,16 @@
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E154" s="1" t="s">
         <v>38</v>
@@ -5796,16 +5793,16 @@
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E155" s="1" t="s">
         <v>41</v>
@@ -5816,16 +5813,16 @@
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E156" s="1" t="s">
         <v>126</v>
@@ -5836,16 +5833,16 @@
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E157" s="1" t="s">
         <v>4</v>
@@ -5856,16 +5853,16 @@
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D158" s="1" t="s">
         <v>344</v>
-      </c>
-      <c r="B158" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="C158" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D158" s="1" t="s">
-        <v>343</v>
       </c>
       <c r="E158" s="1" t="s">
         <v>8</v>
@@ -5876,16 +5873,16 @@
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E159" s="1" t="s">
         <v>11</v>
@@ -5896,16 +5893,16 @@
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E160" s="1" t="s">
         <v>14</v>
@@ -5916,16 +5913,16 @@
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E161" s="1" t="s">
         <v>17</v>
@@ -5936,16 +5933,16 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E162" s="1" t="s">
         <v>20</v>
@@ -5956,16 +5953,16 @@
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E163" s="1" t="s">
         <v>38</v>
@@ -5976,16 +5973,16 @@
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E164" s="1" t="s">
         <v>41</v>
@@ -5996,16 +5993,16 @@
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E165" s="1" t="s">
         <v>126</v>
@@ -6016,16 +6013,16 @@
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E166" s="1" t="s">
         <v>4</v>
@@ -6036,16 +6033,16 @@
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="B167" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D167" s="1" t="s">
         <v>363</v>
-      </c>
-      <c r="B167" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="C167" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D167" s="1" t="s">
-        <v>362</v>
       </c>
       <c r="E167" s="1" t="s">
         <v>8</v>
@@ -6056,16 +6053,16 @@
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E168" s="1" t="s">
         <v>11</v>
@@ -6076,16 +6073,16 @@
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E169" s="1" t="s">
         <v>14</v>
@@ -6096,16 +6093,16 @@
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E170" s="1" t="s">
         <v>17</v>
@@ -6116,16 +6113,16 @@
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E171" s="1" t="s">
         <v>20</v>
@@ -6136,16 +6133,16 @@
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E172" s="1" t="s">
         <v>38</v>
@@ -6156,16 +6153,16 @@
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E173" s="1" t="s">
         <v>41</v>
@@ -6176,16 +6173,16 @@
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E174" s="1" t="s">
         <v>126</v>
@@ -6196,16 +6193,16 @@
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E175" s="1" t="s">
         <v>4</v>
@@ -6216,16 +6213,16 @@
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="B176" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="C176" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D176" s="1" t="s">
         <v>382</v>
-      </c>
-      <c r="B176" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="C176" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D176" s="1" t="s">
-        <v>381</v>
       </c>
       <c r="E176" s="1" t="s">
         <v>8</v>
@@ -6236,16 +6233,16 @@
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E177" s="1" t="s">
         <v>11</v>
@@ -6256,16 +6253,16 @@
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E178" s="1" t="s">
         <v>14</v>
@@ -6276,16 +6273,16 @@
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E179" s="1" t="s">
         <v>17</v>
@@ -6296,16 +6293,16 @@
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E180" s="1" t="s">
         <v>20</v>
@@ -6316,16 +6313,16 @@
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E181" s="1" t="s">
         <v>38</v>
@@ -6336,16 +6333,16 @@
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E182" s="1" t="s">
         <v>41</v>
@@ -6356,16 +6353,16 @@
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E183" s="1" t="s">
         <v>126</v>
@@ -6376,16 +6373,16 @@
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E184" s="1" t="s">
         <v>145</v>
@@ -6396,16 +6393,16 @@
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E185" s="1" t="s">
         <v>4</v>
@@ -6416,16 +6413,16 @@
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="B186" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="C186" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D186" s="1" t="s">
         <v>403</v>
-      </c>
-      <c r="B186" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="C186" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D186" s="1" t="s">
-        <v>402</v>
       </c>
       <c r="E186" s="1" t="s">
         <v>8</v>
@@ -6436,16 +6433,16 @@
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E187" s="1" t="s">
         <v>11</v>
@@ -6456,16 +6453,16 @@
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E188" s="1" t="s">
         <v>14</v>
@@ -6476,16 +6473,16 @@
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E189" s="1" t="s">
         <v>17</v>
@@ -6496,16 +6493,16 @@
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E190" s="1" t="s">
         <v>20</v>
@@ -6516,16 +6513,16 @@
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E191" s="1" t="s">
         <v>38</v>
@@ -6536,16 +6533,16 @@
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E192" s="1" t="s">
         <v>41</v>
@@ -6556,16 +6553,16 @@
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E193" s="1" t="s">
         <v>126</v>
@@ -6576,16 +6573,16 @@
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E194" s="1" t="s">
         <v>4</v>
@@ -6596,16 +6593,16 @@
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B195" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="C195" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D195" s="1" t="s">
         <v>422</v>
-      </c>
-      <c r="B195" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="C195" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D195" s="1" t="s">
-        <v>421</v>
       </c>
       <c r="E195" s="1" t="s">
         <v>8</v>
@@ -6616,16 +6613,16 @@
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E196" s="1" t="s">
         <v>11</v>
@@ -6636,16 +6633,16 @@
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E197" s="1" t="s">
         <v>14</v>
@@ -6656,16 +6653,16 @@
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E198" s="1" t="s">
         <v>17</v>
@@ -6676,16 +6673,16 @@
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E199" s="1" t="s">
         <v>20</v>
@@ -6696,16 +6693,16 @@
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E200" s="1" t="s">
         <v>38</v>
@@ -6716,16 +6713,16 @@
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E201" s="1" t="s">
         <v>41</v>
@@ -6736,16 +6733,16 @@
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E202" s="1" t="s">
         <v>145</v>
@@ -6756,16 +6753,16 @@
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E203" s="1" t="s">
         <v>4</v>
@@ -6776,16 +6773,16 @@
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="B204" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="C204" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D204" s="1" t="s">
         <v>441</v>
-      </c>
-      <c r="B204" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="C204" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D204" s="1" t="s">
-        <v>440</v>
       </c>
       <c r="E204" s="1" t="s">
         <v>8</v>
@@ -6796,16 +6793,16 @@
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E205" s="1" t="s">
         <v>11</v>
@@ -6816,16 +6813,16 @@
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E206" s="1" t="s">
         <v>14</v>
@@ -6836,16 +6833,16 @@
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C207" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E207" s="1" t="s">
         <v>17</v>
@@ -6856,39 +6853,39 @@
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="F208" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F209" s="1" t="s">
         <v>23</v>
@@ -6896,19 +6893,19 @@
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>41</v>
+        <v>126</v>
       </c>
       <c r="F210" s="1" t="s">
         <v>23</v>
@@ -6916,19 +6913,19 @@
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>440</v>
+        <v>458</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>126</v>
+        <v>4</v>
       </c>
       <c r="F211" s="1" t="s">
         <v>23</v>
@@ -6936,99 +6933,99 @@
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B212" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="C212" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D212" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="C212" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D212" s="1" t="s">
-        <v>459</v>
-      </c>
       <c r="E212" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F212" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F214" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F215" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F216" s="1" t="s">
         <v>23</v>
@@ -7036,19 +7033,19 @@
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C217" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="F217" s="1" t="s">
         <v>23</v>
@@ -7056,19 +7053,19 @@
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F218" s="1" t="s">
         <v>23</v>
@@ -7076,59 +7073,59 @@
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C219" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>41</v>
+        <v>126</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C220" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C221" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>459</v>
+        <v>479</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>145</v>
+        <v>4</v>
       </c>
       <c r="F221" s="1" t="s">
         <v>23</v>
@@ -7136,19 +7133,19 @@
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B222" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="C222" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D222" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="C222" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D222" s="1" t="s">
-        <v>480</v>
-      </c>
       <c r="E222" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F222" s="1" t="s">
         <v>23</v>
@@ -7156,19 +7153,19 @@
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C223" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F223" s="1" t="s">
         <v>23</v>
@@ -7176,19 +7173,19 @@
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C224" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F224" s="1" t="s">
         <v>23</v>
@@ -7196,19 +7193,19 @@
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C225" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F225" s="1" t="s">
         <v>23</v>
@@ -7216,39 +7213,39 @@
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C226" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C227" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F227" s="1" t="s">
         <v>31</v>
@@ -7256,19 +7253,19 @@
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C228" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>480</v>
+        <v>494</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="F228" s="1" t="s">
         <v>31</v>
@@ -7276,19 +7273,19 @@
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B229" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="C229" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D229" s="1" t="s">
         <v>494</v>
       </c>
-      <c r="C229" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D229" s="1" t="s">
-        <v>495</v>
-      </c>
       <c r="E229" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F229" s="1" t="s">
         <v>31</v>
@@ -7296,19 +7293,19 @@
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C230" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F230" s="1" t="s">
         <v>31</v>
@@ -7316,39 +7313,39 @@
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C231" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F231" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C232" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F232" s="1" t="s">
         <v>23</v>
@@ -7356,39 +7353,39 @@
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C233" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F233" s="1" t="s">
-        <v>23</v>
+        <v>165</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C234" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="F234" s="1" t="s">
         <v>165</v>
@@ -7396,39 +7393,39 @@
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C235" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>495</v>
+        <v>509</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="F235" s="1" t="s">
-        <v>165</v>
+        <v>31</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="B236" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="C236" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D236" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="C236" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D236" s="1" t="s">
-        <v>510</v>
-      </c>
       <c r="E236" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F236" s="1" t="s">
         <v>31</v>
@@ -7436,19 +7433,19 @@
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C237" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="E237" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F237" s="1" t="s">
         <v>31</v>
@@ -7456,19 +7453,19 @@
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C238" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="E238" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F238" s="1" t="s">
         <v>31</v>
@@ -7476,19 +7473,19 @@
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C239" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="E239" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F239" s="1" t="s">
         <v>31</v>
@@ -7496,39 +7493,39 @@
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C240" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="E240" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F240" s="1" t="s">
-        <v>31</v>
+        <v>165</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C241" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="E241" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="F241" s="1" t="s">
         <v>165</v>
@@ -7536,79 +7533,79 @@
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C242" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="E242" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F242" s="1" t="s">
-        <v>165</v>
+        <v>524</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C243" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="E243" s="1" t="s">
-        <v>41</v>
+        <v>126</v>
       </c>
       <c r="F243" s="1" t="s">
-        <v>525</v>
+        <v>28</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C244" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>510</v>
+        <v>529</v>
       </c>
       <c r="E244" s="1" t="s">
-        <v>126</v>
+        <v>4</v>
       </c>
       <c r="F244" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B245" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="C245" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D245" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="C245" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D245" s="1" t="s">
-        <v>530</v>
-      </c>
       <c r="E245" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F245" s="1" t="s">
         <v>23</v>
@@ -7616,19 +7613,19 @@
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C246" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F246" s="1" t="s">
         <v>23</v>
@@ -7636,19 +7633,19 @@
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C247" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F247" s="1" t="s">
         <v>23</v>
@@ -7656,59 +7653,59 @@
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C248" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F248" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C249" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F249" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C250" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="E250" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="F250" s="1" t="s">
         <v>31</v>
@@ -7716,19 +7713,19 @@
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C251" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F251" s="1" t="s">
         <v>31</v>
@@ -7736,39 +7733,39 @@
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C252" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>530</v>
+        <v>546</v>
       </c>
       <c r="E252" s="1" t="s">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="F252" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" s="1" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="B253" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="C253" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D253" s="1" t="s">
         <v>546</v>
       </c>
-      <c r="C253" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D253" s="1" t="s">
-        <v>547</v>
-      </c>
       <c r="E253" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F253" s="1" t="s">
         <v>23</v>
@@ -7776,19 +7773,19 @@
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" s="1" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C254" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F254" s="1" t="s">
         <v>23</v>
@@ -7796,19 +7793,19 @@
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C255" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F255" s="1" t="s">
         <v>23</v>
@@ -7816,59 +7813,59 @@
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256" s="1" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C256" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="E256" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F256" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C257" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="E257" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F257" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C258" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="F258" s="1" t="s">
         <v>23</v>
@@ -7876,19 +7873,19 @@
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C259" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F259" s="1" t="s">
         <v>23</v>
@@ -7896,39 +7893,39 @@
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C260" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>547</v>
+        <v>563</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="F260" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="B261" s="1" t="s">
         <v>562</v>
       </c>
-      <c r="B261" s="1" t="s">
+      <c r="C261" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D261" s="1" t="s">
         <v>563</v>
       </c>
-      <c r="C261" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D261" s="1" t="s">
-        <v>564</v>
-      </c>
       <c r="E261" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F261" s="1" t="s">
         <v>28</v>
@@ -7939,36 +7936,36 @@
         <v>565</v>
       </c>
       <c r="B262" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="C262" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D262" s="1" t="s">
         <v>563</v>
       </c>
-      <c r="C262" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D262" s="1" t="s">
-        <v>564</v>
-      </c>
       <c r="E262" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F262" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C263" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="E263" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F263" s="1" t="s">
         <v>23</v>
@@ -7976,19 +7973,19 @@
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C264" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="E264" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F264" s="1" t="s">
         <v>23</v>
@@ -7996,19 +7993,19 @@
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265" s="1" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B265" s="1" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C265" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="E265" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F265" s="1" t="s">
         <v>23</v>
@@ -8016,19 +8013,19 @@
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266" s="1" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C266" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="F266" s="1" t="s">
         <v>23</v>
@@ -8036,19 +8033,19 @@
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A267" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C267" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="E267" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F267" s="1" t="s">
         <v>23</v>
@@ -8056,19 +8053,19 @@
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C268" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>41</v>
+        <v>126</v>
       </c>
       <c r="F268" s="1" t="s">
         <v>23</v>
@@ -8076,19 +8073,19 @@
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" s="1" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C269" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>564</v>
+        <v>581</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>126</v>
+        <v>4</v>
       </c>
       <c r="F269" s="1" t="s">
         <v>23</v>
@@ -8096,19 +8093,19 @@
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270" s="1" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="B270" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="C270" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D270" s="1" t="s">
         <v>581</v>
       </c>
-      <c r="C270" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D270" s="1" t="s">
-        <v>582</v>
-      </c>
       <c r="E270" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F270" s="1" t="s">
         <v>23</v>
@@ -8116,19 +8113,19 @@
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C271" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E271" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F271" s="1" t="s">
         <v>23</v>
@@ -8136,19 +8133,19 @@
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C272" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E272" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F272" s="1" t="s">
         <v>23</v>
@@ -8156,19 +8153,19 @@
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B273" s="1" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C273" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F273" s="1" t="s">
         <v>23</v>
@@ -8176,19 +8173,19 @@
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C274" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F274" s="1" t="s">
         <v>23</v>
@@ -8196,19 +8193,19 @@
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" s="1" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C275" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E275" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="F275" s="1" t="s">
         <v>23</v>
@@ -8216,19 +8213,19 @@
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C276" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E276" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F276" s="1" t="s">
         <v>23</v>
@@ -8236,19 +8233,19 @@
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C277" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E277" s="1" t="s">
-        <v>41</v>
+        <v>126</v>
       </c>
       <c r="F277" s="1" t="s">
         <v>23</v>
@@ -8256,19 +8253,19 @@
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278" s="1" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C278" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="F278" s="1" t="s">
         <v>23</v>
@@ -8276,19 +8273,19 @@
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C279" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E279" s="1" t="s">
-        <v>145</v>
+        <v>164</v>
       </c>
       <c r="F279" s="1" t="s">
         <v>23</v>
@@ -8296,19 +8293,19 @@
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C280" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>582</v>
+        <v>604</v>
       </c>
       <c r="E280" s="1" t="s">
-        <v>164</v>
+        <v>4</v>
       </c>
       <c r="F280" s="1" t="s">
         <v>23</v>
@@ -8316,19 +8313,19 @@
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" s="1" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="B281" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="C281" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D281" s="1" t="s">
         <v>604</v>
       </c>
-      <c r="C281" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D281" s="1" t="s">
-        <v>605</v>
-      </c>
       <c r="E281" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F281" s="1" t="s">
         <v>23</v>
@@ -8336,19 +8333,19 @@
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C282" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="E282" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F282" s="1" t="s">
         <v>23</v>
@@ -8356,19 +8353,19 @@
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" s="1" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C283" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="E283" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F283" s="1" t="s">
         <v>23</v>
@@ -8376,19 +8373,19 @@
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284" s="1" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C284" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F284" s="1" t="s">
         <v>23</v>
@@ -8396,19 +8393,19 @@
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A285" s="1" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C285" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="E285" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F285" s="1" t="s">
         <v>23</v>
@@ -8416,59 +8413,59 @@
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A286" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C286" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="F286" s="1" t="s">
-        <v>23</v>
+        <v>617</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A287" s="1" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="C287" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F287" s="1" t="s">
-        <v>618</v>
+        <v>23</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288" s="1" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C288" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>41</v>
+        <v>126</v>
       </c>
       <c r="F288" s="1" t="s">
         <v>23</v>
@@ -8476,19 +8473,19 @@
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A289" s="1" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C289" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="E289" s="1" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="F289" s="1" t="s">
         <v>23</v>
@@ -8496,219 +8493,219 @@
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290" s="1" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C290" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>605</v>
+        <v>626</v>
       </c>
       <c r="E290" s="1" t="s">
-        <v>145</v>
+        <v>4</v>
       </c>
       <c r="F290" s="1" t="s">
-        <v>23</v>
+        <v>617</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A291" s="1" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="B291" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="C291" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D291" s="1" t="s">
         <v>626</v>
       </c>
-      <c r="C291" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D291" s="1" t="s">
-        <v>627</v>
-      </c>
       <c r="E291" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F291" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A292" s="1" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C292" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="E292" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F292" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A293" s="1" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B293" s="1" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C293" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="E293" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F293" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A294" s="1" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C294" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="E294" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F294" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A295" s="1" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B295" s="1" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C295" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="E295" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F295" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A296" s="1" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C296" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="E296" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="F296" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A297" s="1" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B297" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C297" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F297" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A298" s="1" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B298" s="1" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C298" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>41</v>
+        <v>126</v>
       </c>
       <c r="F298" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A299" s="1" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B299" s="1" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C299" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>627</v>
+        <v>645</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>126</v>
+        <v>4</v>
       </c>
       <c r="F299" s="1" t="s">
-        <v>618</v>
+        <v>23</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A300" s="1" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="B300" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="C300" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D300" s="1" t="s">
         <v>645</v>
       </c>
-      <c r="C300" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D300" s="1" t="s">
-        <v>646</v>
-      </c>
       <c r="E300" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F300" s="1" t="s">
         <v>23</v>
@@ -8716,19 +8713,19 @@
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A301" s="1" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B301" s="1" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C301" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="E301" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F301" s="1" t="s">
         <v>23</v>
@@ -8736,19 +8733,19 @@
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A302" s="1" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C302" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="E302" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F302" s="1" t="s">
         <v>23</v>
@@ -8756,19 +8753,19 @@
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A303" s="1" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B303" s="1" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C303" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D303" s="1" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="E303" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F303" s="1" t="s">
         <v>23</v>
@@ -8776,19 +8773,19 @@
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A304" s="1" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B304" s="1" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C304" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D304" s="1" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="E304" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F304" s="1" t="s">
         <v>23</v>
@@ -8796,19 +8793,19 @@
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A305" s="1" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B305" s="1" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C305" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D305" s="1" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="E305" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="F305" s="1" t="s">
         <v>23</v>
@@ -8816,19 +8813,19 @@
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A306" s="1" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B306" s="1" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C306" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D306" s="1" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="E306" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F306" s="1" t="s">
         <v>23</v>
@@ -8836,19 +8833,19 @@
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A307" s="1" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B307" s="1" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C307" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D307" s="1" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="E307" s="1" t="s">
-        <v>41</v>
+        <v>126</v>
       </c>
       <c r="F307" s="1" t="s">
         <v>23</v>
@@ -8856,19 +8853,19 @@
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A308" s="1" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B308" s="1" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C308" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D308" s="1" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="E308" s="1" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="F308" s="1" t="s">
         <v>23</v>
@@ -8876,19 +8873,19 @@
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A309" s="1" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B309" s="1" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C309" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D309" s="1" t="s">
-        <v>646</v>
+        <v>666</v>
       </c>
       <c r="E309" s="1" t="s">
-        <v>145</v>
+        <v>4</v>
       </c>
       <c r="F309" s="1" t="s">
         <v>23</v>
@@ -8896,19 +8893,19 @@
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A310" s="1" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="B310" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="C310" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D310" s="1" t="s">
         <v>666</v>
       </c>
-      <c r="C310" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D310" s="1" t="s">
-        <v>667</v>
-      </c>
       <c r="E310" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F310" s="1" t="s">
         <v>23</v>
@@ -8916,19 +8913,19 @@
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A311" s="1" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B311" s="1" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C311" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D311" s="1" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="E311" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F311" s="1" t="s">
         <v>23</v>
@@ -8936,19 +8933,19 @@
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A312" s="1" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B312" s="1" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C312" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D312" s="1" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="E312" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F312" s="1" t="s">
         <v>23</v>
@@ -8956,19 +8953,19 @@
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A313" s="1" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B313" s="1" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C313" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D313" s="1" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="E313" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F313" s="1" t="s">
         <v>23</v>
@@ -8976,19 +8973,19 @@
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A314" s="1" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B314" s="1" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C314" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D314" s="1" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="E314" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F314" s="1" t="s">
         <v>23</v>
@@ -8996,19 +8993,19 @@
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A315" s="1" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B315" s="1" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C315" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D315" s="1" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="E315" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="F315" s="1" t="s">
         <v>23</v>
@@ -9016,19 +9013,19 @@
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A316" s="1" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B316" s="1" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C316" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D316" s="1" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="E316" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F316" s="1" t="s">
         <v>23</v>
@@ -9036,19 +9033,19 @@
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A317" s="1" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B317" s="1" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C317" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D317" s="1" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="E317" s="1" t="s">
-        <v>41</v>
+        <v>126</v>
       </c>
       <c r="F317" s="1" t="s">
         <v>23</v>
@@ -9056,19 +9053,19 @@
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A318" s="1" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B318" s="1" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C318" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D318" s="1" t="s">
-        <v>667</v>
+        <v>685</v>
       </c>
       <c r="E318" s="1" t="s">
-        <v>126</v>
+        <v>4</v>
       </c>
       <c r="F318" s="1" t="s">
         <v>23</v>
@@ -9076,19 +9073,19 @@
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A319" s="1" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="B319" s="1" t="s">
+        <v>687</v>
+      </c>
+      <c r="C319" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D319" s="1" t="s">
         <v>685</v>
       </c>
-      <c r="C319" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D319" s="1" t="s">
-        <v>686</v>
-      </c>
       <c r="E319" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F319" s="1" t="s">
         <v>23</v>
@@ -9096,19 +9093,19 @@
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A320" s="1" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B320" s="1" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C320" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D320" s="1" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="E320" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F320" s="1" t="s">
         <v>23</v>
@@ -9116,19 +9113,19 @@
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A321" s="1" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B321" s="1" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C321" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D321" s="1" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="E321" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F321" s="1" t="s">
         <v>23</v>
@@ -9136,19 +9133,19 @@
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A322" s="1" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B322" s="1" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C322" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D322" s="1" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="E322" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F322" s="1" t="s">
         <v>23</v>
@@ -9156,19 +9153,19 @@
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A323" s="1" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B323" s="1" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C323" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D323" s="1" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="E323" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F323" s="1" t="s">
         <v>23</v>
@@ -9176,19 +9173,19 @@
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A324" s="1" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B324" s="1" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C324" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D324" s="1" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="E324" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="F324" s="1" t="s">
         <v>23</v>
@@ -9196,19 +9193,19 @@
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A325" s="1" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B325" s="1" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C325" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D325" s="1" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="E325" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F325" s="1" t="s">
         <v>23</v>
@@ -9216,19 +9213,19 @@
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A326" s="1" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B326" s="1" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C326" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D326" s="1" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="E326" s="1" t="s">
-        <v>41</v>
+        <v>126</v>
       </c>
       <c r="F326" s="1" t="s">
         <v>23</v>
@@ -9236,19 +9233,19 @@
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A327" s="1" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B327" s="1" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C327" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D327" s="1" t="s">
-        <v>686</v>
+        <v>704</v>
       </c>
       <c r="E327" s="1" t="s">
-        <v>126</v>
+        <v>4</v>
       </c>
       <c r="F327" s="1" t="s">
         <v>23</v>
@@ -9256,19 +9253,19 @@
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A328" s="1" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="B328" s="1" t="s">
+        <v>706</v>
+      </c>
+      <c r="C328" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D328" s="1" t="s">
         <v>704</v>
       </c>
-      <c r="C328" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D328" s="1" t="s">
-        <v>705</v>
-      </c>
       <c r="E328" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F328" s="1" t="s">
         <v>23</v>
@@ -9276,39 +9273,39 @@
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A329" s="1" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B329" s="1" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="C329" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D329" s="1" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="E329" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F329" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A330" s="1" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B330" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C330" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D330" s="1" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="E330" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F330" s="1" t="s">
         <v>31</v>
@@ -9316,39 +9313,39 @@
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A331" s="1" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B331" s="1" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C331" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D331" s="1" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="E331" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F331" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A332" s="1" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B332" s="1" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="C332" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D332" s="1" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="E332" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F332" s="1" t="s">
         <v>23</v>
@@ -9356,19 +9353,19 @@
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A333" s="1" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B333" s="1" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="C333" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D333" s="1" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="E333" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="F333" s="1" t="s">
         <v>23</v>
@@ -9376,19 +9373,19 @@
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A334" s="1" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="B334" s="1" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="C334" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D334" s="1" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="E334" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F334" s="1" t="s">
         <v>23</v>
@@ -9396,19 +9393,19 @@
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A335" s="1" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B335" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C335" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D335" s="1" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="E335" s="1" t="s">
-        <v>41</v>
+        <v>126</v>
       </c>
       <c r="F335" s="1" t="s">
         <v>23</v>
@@ -9416,19 +9413,19 @@
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A336" s="1" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B336" s="1" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C336" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D336" s="1" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="E336" s="1" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="F336" s="1" t="s">
         <v>23</v>
@@ -9436,119 +9433,119 @@
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A337" s="1" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B337" s="1" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C337" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D337" s="1" t="s">
-        <v>705</v>
+        <v>725</v>
       </c>
       <c r="E337" s="1" t="s">
-        <v>145</v>
+        <v>4</v>
       </c>
       <c r="F337" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A338" s="1" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="B338" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="C338" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D338" s="1" t="s">
         <v>725</v>
       </c>
-      <c r="C338" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D338" s="1" t="s">
-        <v>726</v>
-      </c>
       <c r="E338" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F338" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A339" s="1" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B339" s="1" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="C339" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D339" s="1" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E339" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F339" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A340" s="1" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="B340" s="1" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="C340" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D340" s="1" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E340" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F340" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A341" s="1" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="B341" s="1" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="C341" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D341" s="1" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E341" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F341" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A342" s="1" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="B342" s="1" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="C342" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D342" s="1" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E342" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F342" s="1" t="s">
         <v>23</v>
@@ -9556,99 +9553,99 @@
     </row>
     <row r="343" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A343" s="1" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B343" s="1" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="C343" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D343" s="1" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E343" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="F343" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A344" s="1" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="B344" s="1" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C344" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D344" s="1" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E344" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F344" s="1" t="s">
-        <v>31</v>
+        <v>740</v>
       </c>
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A345" s="1" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="B345" s="1" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="C345" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D345" s="1" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E345" s="1" t="s">
-        <v>41</v>
+        <v>126</v>
       </c>
       <c r="F345" s="1" t="s">
-        <v>741</v>
+        <v>28</v>
       </c>
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A346" s="1" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="B346" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C346" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D346" s="1" t="s">
-        <v>726</v>
+        <v>745</v>
       </c>
       <c r="E346" s="1" t="s">
-        <v>126</v>
+        <v>4</v>
       </c>
       <c r="F346" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A347" s="1" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="B347" s="1" t="s">
+        <v>747</v>
+      </c>
+      <c r="C347" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D347" s="1" t="s">
         <v>745</v>
       </c>
-      <c r="C347" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D347" s="1" t="s">
-        <v>746</v>
-      </c>
       <c r="E347" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F347" s="1" t="s">
         <v>23</v>
@@ -9656,19 +9653,19 @@
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A348" s="1" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B348" s="1" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="C348" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D348" s="1" t="s">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="E348" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F348" s="1" t="s">
         <v>23</v>
@@ -9676,121 +9673,101 @@
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A349" s="1" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="B349" s="1" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="C349" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D349" s="1" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="E349" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F349" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A350" s="1" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="B350" s="1" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="C350" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D350" s="1" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="E350" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F350" s="1" t="s">
-        <v>28</v>
+        <v>757</v>
       </c>
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A351" s="1" t="s">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="B351" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="C351" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D351" s="1" t="s">
         <v>756</v>
       </c>
-      <c r="C351" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D351" s="1" t="s">
-        <v>757</v>
-      </c>
       <c r="E351" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F351" s="1" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A352" s="1" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="B352" s="1" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="C352" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D352" s="1" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="E352" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F352" s="1" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
     </row>
     <row r="353" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A353" s="1" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="B353" s="1" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="C353" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D353" s="1" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="E353" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F353" s="1" t="s">
-        <v>764</v>
-      </c>
-    </row>
-    <row r="354" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A354" s="1" t="s">
-        <v>765</v>
-      </c>
-      <c r="B354" s="1" t="s">
-        <v>766</v>
-      </c>
-      <c r="C354" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D354" s="1" t="s">
-        <v>757</v>
-      </c>
-      <c r="E354" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F354" s="1" t="s">
         <v>23</v>
       </c>
     </row>

--- a/CLB07N.xlsx
+++ b/CLB07N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2118" uniqueCount="766">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2118" uniqueCount="765">
   <si>
     <t/>
   </si>
@@ -776,9 +776,6 @@
   </si>
   <si>
     <t>TEH LEMON MADU 350ML</t>
-  </si>
-  <si>
-    <t>,(E-1B)</t>
   </si>
   <si>
     <t>20018904</t>
@@ -5028,15 +5025,15 @@
         <v>11</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>255</v>
+        <v>23</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="B117" s="1" t="s">
         <v>256</v>
-      </c>
-      <c r="B117" s="1" t="s">
-        <v>257</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
@@ -5053,10 +5050,10 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B118" s="1" t="s">
         <v>258</v>
-      </c>
-      <c r="B118" s="1" t="s">
-        <v>259</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
@@ -5073,10 +5070,10 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B119" s="1" t="s">
         <v>260</v>
-      </c>
-      <c r="B119" s="1" t="s">
-        <v>261</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
@@ -5093,10 +5090,10 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B120" s="1" t="s">
         <v>262</v>
-      </c>
-      <c r="B120" s="1" t="s">
-        <v>263</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
@@ -5113,10 +5110,10 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="B121" s="1" t="s">
         <v>264</v>
-      </c>
-      <c r="B121" s="1" t="s">
-        <v>265</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>3</v>
@@ -5133,10 +5130,10 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B122" s="1" t="s">
         <v>266</v>
-      </c>
-      <c r="B122" s="1" t="s">
-        <v>267</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>3</v>
@@ -5148,21 +5145,21 @@
         <v>126</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="B123" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="B123" s="1" t="s">
+      <c r="C123" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D123" s="1" t="s">
         <v>270</v>
-      </c>
-      <c r="C123" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D123" s="1" t="s">
-        <v>271</v>
       </c>
       <c r="E123" s="1" t="s">
         <v>4</v>
@@ -5173,16 +5170,16 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="B124" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="B124" s="1" t="s">
-        <v>273</v>
-      </c>
       <c r="C124" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E124" s="1" t="s">
         <v>8</v>
@@ -5193,16 +5190,16 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="B125" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="B125" s="1" t="s">
-        <v>275</v>
-      </c>
       <c r="C125" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E125" s="1" t="s">
         <v>11</v>
@@ -5213,16 +5210,16 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="B126" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="B126" s="1" t="s">
-        <v>277</v>
-      </c>
       <c r="C126" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E126" s="1" t="s">
         <v>14</v>
@@ -5233,16 +5230,16 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="B127" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="B127" s="1" t="s">
-        <v>279</v>
-      </c>
       <c r="C127" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E127" s="1" t="s">
         <v>17</v>
@@ -5253,16 +5250,16 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B128" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="B128" s="1" t="s">
+      <c r="C128" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D128" s="1" t="s">
         <v>281</v>
-      </c>
-      <c r="C128" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D128" s="1" t="s">
-        <v>282</v>
       </c>
       <c r="E128" s="1" t="s">
         <v>4</v>
@@ -5273,16 +5270,16 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="B129" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="B129" s="1" t="s">
-        <v>284</v>
-      </c>
       <c r="C129" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E129" s="1" t="s">
         <v>8</v>
@@ -5293,16 +5290,16 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B130" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="B130" s="1" t="s">
-        <v>286</v>
-      </c>
       <c r="C130" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E130" s="1" t="s">
         <v>11</v>
@@ -5313,16 +5310,16 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B131" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="B131" s="1" t="s">
-        <v>288</v>
-      </c>
       <c r="C131" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E131" s="1" t="s">
         <v>14</v>
@@ -5333,16 +5330,16 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B132" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="B132" s="1" t="s">
-        <v>290</v>
-      </c>
       <c r="C132" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E132" s="1" t="s">
         <v>17</v>
@@ -5353,16 +5350,16 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="B133" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="B133" s="1" t="s">
-        <v>292</v>
-      </c>
       <c r="C133" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E133" s="1" t="s">
         <v>20</v>
@@ -5373,16 +5370,16 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B134" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="B134" s="1" t="s">
-        <v>294</v>
-      </c>
       <c r="C134" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E134" s="1" t="s">
         <v>38</v>
@@ -5393,16 +5390,16 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="B135" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="B135" s="1" t="s">
+      <c r="C135" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D135" s="1" t="s">
         <v>296</v>
-      </c>
-      <c r="C135" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D135" s="1" t="s">
-        <v>297</v>
       </c>
       <c r="E135" s="1" t="s">
         <v>4</v>
@@ -5413,16 +5410,16 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="B136" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="B136" s="1" t="s">
-        <v>299</v>
-      </c>
       <c r="C136" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E136" s="1" t="s">
         <v>8</v>
@@ -5433,16 +5430,16 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="B137" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="B137" s="1" t="s">
-        <v>301</v>
-      </c>
       <c r="C137" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E137" s="1" t="s">
         <v>11</v>
@@ -5453,16 +5450,16 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B138" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="B138" s="1" t="s">
-        <v>303</v>
-      </c>
       <c r="C138" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E138" s="1" t="s">
         <v>14</v>
@@ -5473,16 +5470,16 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B139" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="B139" s="1" t="s">
-        <v>305</v>
-      </c>
       <c r="C139" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E139" s="1" t="s">
         <v>17</v>
@@ -5493,16 +5490,16 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B140" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="B140" s="1" t="s">
-        <v>307</v>
-      </c>
       <c r="C140" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E140" s="1" t="s">
         <v>38</v>
@@ -5513,16 +5510,16 @@
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="B141" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="B141" s="1" t="s">
-        <v>309</v>
-      </c>
       <c r="C141" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E141" s="1" t="s">
         <v>41</v>
@@ -5533,16 +5530,16 @@
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="B142" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="B142" s="1" t="s">
+      <c r="C142" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D142" s="1" t="s">
         <v>311</v>
-      </c>
-      <c r="C142" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D142" s="1" t="s">
-        <v>312</v>
       </c>
       <c r="E142" s="1" t="s">
         <v>4</v>
@@ -5553,16 +5550,16 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="B143" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="B143" s="1" t="s">
-        <v>314</v>
-      </c>
       <c r="C143" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E143" s="1" t="s">
         <v>11</v>
@@ -5573,16 +5570,16 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="B144" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="B144" s="1" t="s">
-        <v>316</v>
-      </c>
       <c r="C144" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E144" s="1" t="s">
         <v>14</v>
@@ -5593,16 +5590,16 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="B145" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="B145" s="1" t="s">
-        <v>318</v>
-      </c>
       <c r="C145" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E145" s="1" t="s">
         <v>17</v>
@@ -5613,16 +5610,16 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="B146" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="B146" s="1" t="s">
-        <v>320</v>
-      </c>
       <c r="C146" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E146" s="1" t="s">
         <v>20</v>
@@ -5633,16 +5630,16 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B147" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="B147" s="1" t="s">
-        <v>322</v>
-      </c>
       <c r="C147" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E147" s="1" t="s">
         <v>38</v>
@@ -5653,16 +5650,16 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="B148" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="B148" s="1" t="s">
+      <c r="C148" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D148" s="1" t="s">
         <v>324</v>
-      </c>
-      <c r="C148" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D148" s="1" t="s">
-        <v>325</v>
       </c>
       <c r="E148" s="1" t="s">
         <v>4</v>
@@ -5673,16 +5670,16 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="B149" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="B149" s="1" t="s">
-        <v>327</v>
-      </c>
       <c r="C149" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E149" s="1" t="s">
         <v>8</v>
@@ -5693,16 +5690,16 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B150" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="B150" s="1" t="s">
-        <v>329</v>
-      </c>
       <c r="C150" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E150" s="1" t="s">
         <v>11</v>
@@ -5713,16 +5710,16 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="B151" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="B151" s="1" t="s">
-        <v>331</v>
-      </c>
       <c r="C151" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E151" s="1" t="s">
         <v>14</v>
@@ -5733,16 +5730,16 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="B152" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="B152" s="1" t="s">
-        <v>333</v>
-      </c>
       <c r="C152" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E152" s="1" t="s">
         <v>17</v>
@@ -5753,16 +5750,16 @@
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="B153" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="B153" s="1" t="s">
-        <v>335</v>
-      </c>
       <c r="C153" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E153" s="1" t="s">
         <v>20</v>
@@ -5773,16 +5770,16 @@
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="B154" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="B154" s="1" t="s">
-        <v>337</v>
-      </c>
       <c r="C154" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E154" s="1" t="s">
         <v>38</v>
@@ -5793,16 +5790,16 @@
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="B155" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="B155" s="1" t="s">
-        <v>339</v>
-      </c>
       <c r="C155" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E155" s="1" t="s">
         <v>41</v>
@@ -5813,16 +5810,16 @@
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="B156" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="B156" s="1" t="s">
-        <v>341</v>
-      </c>
       <c r="C156" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E156" s="1" t="s">
         <v>126</v>
@@ -5833,16 +5830,16 @@
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="B157" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="B157" s="1" t="s">
+      <c r="C157" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D157" s="1" t="s">
         <v>343</v>
-      </c>
-      <c r="C157" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D157" s="1" t="s">
-        <v>344</v>
       </c>
       <c r="E157" s="1" t="s">
         <v>4</v>
@@ -5853,16 +5850,16 @@
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="B158" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="B158" s="1" t="s">
-        <v>346</v>
-      </c>
       <c r="C158" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E158" s="1" t="s">
         <v>8</v>
@@ -5873,16 +5870,16 @@
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B159" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="B159" s="1" t="s">
-        <v>348</v>
-      </c>
       <c r="C159" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E159" s="1" t="s">
         <v>11</v>
@@ -5893,16 +5890,16 @@
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="B160" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="B160" s="1" t="s">
-        <v>350</v>
-      </c>
       <c r="C160" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E160" s="1" t="s">
         <v>14</v>
@@ -5913,16 +5910,16 @@
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="B161" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="B161" s="1" t="s">
-        <v>352</v>
-      </c>
       <c r="C161" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E161" s="1" t="s">
         <v>17</v>
@@ -5933,16 +5930,16 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="B162" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="B162" s="1" t="s">
-        <v>354</v>
-      </c>
       <c r="C162" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E162" s="1" t="s">
         <v>20</v>
@@ -5953,16 +5950,16 @@
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="B163" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="B163" s="1" t="s">
-        <v>356</v>
-      </c>
       <c r="C163" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E163" s="1" t="s">
         <v>38</v>
@@ -5973,16 +5970,16 @@
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="B164" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="B164" s="1" t="s">
-        <v>358</v>
-      </c>
       <c r="C164" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E164" s="1" t="s">
         <v>41</v>
@@ -5993,16 +5990,16 @@
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="B165" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="B165" s="1" t="s">
-        <v>360</v>
-      </c>
       <c r="C165" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E165" s="1" t="s">
         <v>126</v>
@@ -6013,16 +6010,16 @@
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="B166" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="B166" s="1" t="s">
+      <c r="C166" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D166" s="1" t="s">
         <v>362</v>
-      </c>
-      <c r="C166" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D166" s="1" t="s">
-        <v>363</v>
       </c>
       <c r="E166" s="1" t="s">
         <v>4</v>
@@ -6033,16 +6030,16 @@
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="B167" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="B167" s="1" t="s">
-        <v>365</v>
-      </c>
       <c r="C167" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E167" s="1" t="s">
         <v>8</v>
@@ -6053,16 +6050,16 @@
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="B168" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="B168" s="1" t="s">
-        <v>367</v>
-      </c>
       <c r="C168" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E168" s="1" t="s">
         <v>11</v>
@@ -6073,16 +6070,16 @@
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="B169" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="B169" s="1" t="s">
-        <v>369</v>
-      </c>
       <c r="C169" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E169" s="1" t="s">
         <v>14</v>
@@ -6093,16 +6090,16 @@
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="B170" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="B170" s="1" t="s">
-        <v>371</v>
-      </c>
       <c r="C170" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E170" s="1" t="s">
         <v>17</v>
@@ -6113,16 +6110,16 @@
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="B171" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="B171" s="1" t="s">
-        <v>373</v>
-      </c>
       <c r="C171" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E171" s="1" t="s">
         <v>20</v>
@@ -6133,16 +6130,16 @@
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="B172" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="B172" s="1" t="s">
-        <v>375</v>
-      </c>
       <c r="C172" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E172" s="1" t="s">
         <v>38</v>
@@ -6153,16 +6150,16 @@
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="B173" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="B173" s="1" t="s">
-        <v>377</v>
-      </c>
       <c r="C173" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E173" s="1" t="s">
         <v>41</v>
@@ -6173,16 +6170,16 @@
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="B174" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="B174" s="1" t="s">
-        <v>379</v>
-      </c>
       <c r="C174" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E174" s="1" t="s">
         <v>126</v>
@@ -6193,16 +6190,16 @@
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="B175" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="B175" s="1" t="s">
+      <c r="C175" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D175" s="1" t="s">
         <v>381</v>
-      </c>
-      <c r="C175" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D175" s="1" t="s">
-        <v>382</v>
       </c>
       <c r="E175" s="1" t="s">
         <v>4</v>
@@ -6213,16 +6210,16 @@
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="B176" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="B176" s="1" t="s">
-        <v>384</v>
-      </c>
       <c r="C176" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E176" s="1" t="s">
         <v>8</v>
@@ -6233,16 +6230,16 @@
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="B177" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="B177" s="1" t="s">
-        <v>386</v>
-      </c>
       <c r="C177" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E177" s="1" t="s">
         <v>11</v>
@@ -6253,16 +6250,16 @@
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="B178" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="B178" s="1" t="s">
-        <v>388</v>
-      </c>
       <c r="C178" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E178" s="1" t="s">
         <v>14</v>
@@ -6273,16 +6270,16 @@
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="B179" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="B179" s="1" t="s">
-        <v>390</v>
-      </c>
       <c r="C179" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E179" s="1" t="s">
         <v>17</v>
@@ -6293,16 +6290,16 @@
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="B180" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="B180" s="1" t="s">
-        <v>392</v>
-      </c>
       <c r="C180" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E180" s="1" t="s">
         <v>20</v>
@@ -6313,16 +6310,16 @@
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="B181" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="B181" s="1" t="s">
-        <v>394</v>
-      </c>
       <c r="C181" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E181" s="1" t="s">
         <v>38</v>
@@ -6333,16 +6330,16 @@
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="B182" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="B182" s="1" t="s">
-        <v>396</v>
-      </c>
       <c r="C182" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E182" s="1" t="s">
         <v>41</v>
@@ -6353,16 +6350,16 @@
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="B183" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="B183" s="1" t="s">
-        <v>398</v>
-      </c>
       <c r="C183" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E183" s="1" t="s">
         <v>126</v>
@@ -6373,16 +6370,16 @@
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="B184" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="B184" s="1" t="s">
-        <v>400</v>
-      </c>
       <c r="C184" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E184" s="1" t="s">
         <v>145</v>
@@ -6393,16 +6390,16 @@
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B185" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="B185" s="1" t="s">
+      <c r="C185" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D185" s="1" t="s">
         <v>402</v>
-      </c>
-      <c r="C185" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D185" s="1" t="s">
-        <v>403</v>
       </c>
       <c r="E185" s="1" t="s">
         <v>4</v>
@@ -6413,16 +6410,16 @@
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="B186" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="B186" s="1" t="s">
-        <v>405</v>
-      </c>
       <c r="C186" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E186" s="1" t="s">
         <v>8</v>
@@ -6433,16 +6430,16 @@
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="B187" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="B187" s="1" t="s">
-        <v>407</v>
-      </c>
       <c r="C187" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E187" s="1" t="s">
         <v>11</v>
@@ -6453,16 +6450,16 @@
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="B188" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="B188" s="1" t="s">
-        <v>409</v>
-      </c>
       <c r="C188" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E188" s="1" t="s">
         <v>14</v>
@@ -6473,16 +6470,16 @@
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="B189" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="B189" s="1" t="s">
-        <v>411</v>
-      </c>
       <c r="C189" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E189" s="1" t="s">
         <v>17</v>
@@ -6493,16 +6490,16 @@
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="B190" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="B190" s="1" t="s">
-        <v>413</v>
-      </c>
       <c r="C190" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E190" s="1" t="s">
         <v>20</v>
@@ -6513,16 +6510,16 @@
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="B191" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="B191" s="1" t="s">
-        <v>415</v>
-      </c>
       <c r="C191" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E191" s="1" t="s">
         <v>38</v>
@@ -6533,16 +6530,16 @@
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="B192" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="B192" s="1" t="s">
-        <v>417</v>
-      </c>
       <c r="C192" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E192" s="1" t="s">
         <v>41</v>
@@ -6553,16 +6550,16 @@
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="B193" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="B193" s="1" t="s">
-        <v>419</v>
-      </c>
       <c r="C193" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E193" s="1" t="s">
         <v>126</v>
@@ -6573,16 +6570,16 @@
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="B194" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="B194" s="1" t="s">
+      <c r="C194" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D194" s="1" t="s">
         <v>421</v>
-      </c>
-      <c r="C194" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D194" s="1" t="s">
-        <v>422</v>
       </c>
       <c r="E194" s="1" t="s">
         <v>4</v>
@@ -6593,16 +6590,16 @@
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="B195" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="B195" s="1" t="s">
-        <v>424</v>
-      </c>
       <c r="C195" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E195" s="1" t="s">
         <v>8</v>
@@ -6613,16 +6610,16 @@
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="B196" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="B196" s="1" t="s">
-        <v>426</v>
-      </c>
       <c r="C196" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E196" s="1" t="s">
         <v>11</v>
@@ -6633,16 +6630,16 @@
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="B197" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="B197" s="1" t="s">
-        <v>428</v>
-      </c>
       <c r="C197" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E197" s="1" t="s">
         <v>14</v>
@@ -6653,16 +6650,16 @@
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="B198" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="B198" s="1" t="s">
-        <v>430</v>
-      </c>
       <c r="C198" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E198" s="1" t="s">
         <v>17</v>
@@ -6673,16 +6670,16 @@
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="B199" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="B199" s="1" t="s">
-        <v>432</v>
-      </c>
       <c r="C199" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E199" s="1" t="s">
         <v>20</v>
@@ -6693,16 +6690,16 @@
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="B200" s="1" t="s">
         <v>433</v>
       </c>
-      <c r="B200" s="1" t="s">
-        <v>434</v>
-      </c>
       <c r="C200" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E200" s="1" t="s">
         <v>38</v>
@@ -6713,16 +6710,16 @@
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="B201" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="B201" s="1" t="s">
-        <v>436</v>
-      </c>
       <c r="C201" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E201" s="1" t="s">
         <v>41</v>
@@ -6733,16 +6730,16 @@
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="B202" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="B202" s="1" t="s">
-        <v>438</v>
-      </c>
       <c r="C202" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E202" s="1" t="s">
         <v>145</v>
@@ -6753,16 +6750,16 @@
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="B203" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="B203" s="1" t="s">
+      <c r="C203" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D203" s="1" t="s">
         <v>440</v>
-      </c>
-      <c r="C203" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D203" s="1" t="s">
-        <v>441</v>
       </c>
       <c r="E203" s="1" t="s">
         <v>4</v>
@@ -6773,16 +6770,16 @@
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="B204" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="B204" s="1" t="s">
-        <v>443</v>
-      </c>
       <c r="C204" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E204" s="1" t="s">
         <v>8</v>
@@ -6793,16 +6790,16 @@
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="B205" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="B205" s="1" t="s">
-        <v>445</v>
-      </c>
       <c r="C205" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E205" s="1" t="s">
         <v>11</v>
@@ -6813,16 +6810,16 @@
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="B206" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="B206" s="1" t="s">
-        <v>447</v>
-      </c>
       <c r="C206" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E206" s="1" t="s">
         <v>14</v>
@@ -6833,16 +6830,16 @@
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="B207" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="B207" s="1" t="s">
-        <v>449</v>
-      </c>
       <c r="C207" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E207" s="1" t="s">
         <v>17</v>
@@ -6853,16 +6850,16 @@
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="B208" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="B208" s="1" t="s">
-        <v>451</v>
-      </c>
       <c r="C208" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E208" s="1" t="s">
         <v>38</v>
@@ -6873,16 +6870,16 @@
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="B209" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="B209" s="1" t="s">
-        <v>453</v>
-      </c>
       <c r="C209" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E209" s="1" t="s">
         <v>41</v>
@@ -6893,16 +6890,16 @@
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="B210" s="1" t="s">
         <v>454</v>
       </c>
-      <c r="B210" s="1" t="s">
-        <v>455</v>
-      </c>
       <c r="C210" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E210" s="1" t="s">
         <v>126</v>
@@ -6913,16 +6910,16 @@
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="B211" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="B211" s="1" t="s">
+      <c r="C211" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D211" s="1" t="s">
         <v>457</v>
-      </c>
-      <c r="C211" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D211" s="1" t="s">
-        <v>458</v>
       </c>
       <c r="E211" s="1" t="s">
         <v>4</v>
@@ -6933,16 +6930,16 @@
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="B212" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="B212" s="1" t="s">
-        <v>460</v>
-      </c>
       <c r="C212" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="E212" s="1" t="s">
         <v>8</v>
@@ -6953,16 +6950,16 @@
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="B213" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="B213" s="1" t="s">
-        <v>462</v>
-      </c>
       <c r="C213" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="E213" s="1" t="s">
         <v>11</v>
@@ -6973,16 +6970,16 @@
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="B214" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="B214" s="1" t="s">
-        <v>464</v>
-      </c>
       <c r="C214" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="E214" s="1" t="s">
         <v>14</v>
@@ -6993,16 +6990,16 @@
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="B215" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="B215" s="1" t="s">
-        <v>466</v>
-      </c>
       <c r="C215" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="E215" s="1" t="s">
         <v>17</v>
@@ -7013,16 +7010,16 @@
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="B216" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="B216" s="1" t="s">
-        <v>468</v>
-      </c>
       <c r="C216" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="E216" s="1" t="s">
         <v>20</v>
@@ -7033,16 +7030,16 @@
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="B217" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="B217" s="1" t="s">
-        <v>470</v>
-      </c>
       <c r="C217" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="E217" s="1" t="s">
         <v>38</v>
@@ -7053,16 +7050,16 @@
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="B218" s="1" t="s">
         <v>471</v>
       </c>
-      <c r="B218" s="1" t="s">
-        <v>472</v>
-      </c>
       <c r="C218" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="E218" s="1" t="s">
         <v>41</v>
@@ -7073,16 +7070,16 @@
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="B219" s="1" t="s">
         <v>473</v>
       </c>
-      <c r="B219" s="1" t="s">
-        <v>474</v>
-      </c>
       <c r="C219" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="E219" s="1" t="s">
         <v>126</v>
@@ -7093,16 +7090,16 @@
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="B220" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="B220" s="1" t="s">
-        <v>476</v>
-      </c>
       <c r="C220" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="E220" s="1" t="s">
         <v>145</v>
@@ -7113,16 +7110,16 @@
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="B221" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="B221" s="1" t="s">
+      <c r="C221" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D221" s="1" t="s">
         <v>478</v>
-      </c>
-      <c r="C221" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D221" s="1" t="s">
-        <v>479</v>
       </c>
       <c r="E221" s="1" t="s">
         <v>4</v>
@@ -7133,16 +7130,16 @@
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="B222" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="B222" s="1" t="s">
-        <v>481</v>
-      </c>
       <c r="C222" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E222" s="1" t="s">
         <v>8</v>
@@ -7153,16 +7150,16 @@
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="B223" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="B223" s="1" t="s">
-        <v>483</v>
-      </c>
       <c r="C223" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E223" s="1" t="s">
         <v>14</v>
@@ -7173,16 +7170,16 @@
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="B224" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="B224" s="1" t="s">
-        <v>485</v>
-      </c>
       <c r="C224" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E224" s="1" t="s">
         <v>17</v>
@@ -7193,16 +7190,16 @@
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="B225" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="B225" s="1" t="s">
-        <v>487</v>
-      </c>
       <c r="C225" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E225" s="1" t="s">
         <v>20</v>
@@ -7213,16 +7210,16 @@
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="B226" s="1" t="s">
         <v>488</v>
       </c>
-      <c r="B226" s="1" t="s">
-        <v>489</v>
-      </c>
       <c r="C226" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E226" s="1" t="s">
         <v>38</v>
@@ -7233,16 +7230,16 @@
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="B227" s="1" t="s">
         <v>490</v>
       </c>
-      <c r="B227" s="1" t="s">
-        <v>491</v>
-      </c>
       <c r="C227" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E227" s="1" t="s">
         <v>41</v>
@@ -7253,16 +7250,16 @@
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="B228" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="B228" s="1" t="s">
+      <c r="C228" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D228" s="1" t="s">
         <v>493</v>
-      </c>
-      <c r="C228" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D228" s="1" t="s">
-        <v>494</v>
       </c>
       <c r="E228" s="1" t="s">
         <v>4</v>
@@ -7273,16 +7270,16 @@
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="B229" s="1" t="s">
         <v>495</v>
       </c>
-      <c r="B229" s="1" t="s">
-        <v>496</v>
-      </c>
       <c r="C229" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="E229" s="1" t="s">
         <v>8</v>
@@ -7293,16 +7290,16 @@
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="B230" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="B230" s="1" t="s">
-        <v>498</v>
-      </c>
       <c r="C230" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="E230" s="1" t="s">
         <v>11</v>
@@ -7313,16 +7310,16 @@
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="B231" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="B231" s="1" t="s">
-        <v>500</v>
-      </c>
       <c r="C231" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="E231" s="1" t="s">
         <v>14</v>
@@ -7333,16 +7330,16 @@
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="B232" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="B232" s="1" t="s">
-        <v>502</v>
-      </c>
       <c r="C232" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="E232" s="1" t="s">
         <v>17</v>
@@ -7353,16 +7350,16 @@
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="B233" s="1" t="s">
         <v>503</v>
       </c>
-      <c r="B233" s="1" t="s">
-        <v>504</v>
-      </c>
       <c r="C233" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="E233" s="1" t="s">
         <v>20</v>
@@ -7373,16 +7370,16 @@
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="B234" s="1" t="s">
         <v>505</v>
       </c>
-      <c r="B234" s="1" t="s">
-        <v>506</v>
-      </c>
       <c r="C234" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="E234" s="1" t="s">
         <v>38</v>
@@ -7393,16 +7390,16 @@
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="B235" s="1" t="s">
         <v>507</v>
       </c>
-      <c r="B235" s="1" t="s">
+      <c r="C235" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D235" s="1" t="s">
         <v>508</v>
-      </c>
-      <c r="C235" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D235" s="1" t="s">
-        <v>509</v>
       </c>
       <c r="E235" s="1" t="s">
         <v>4</v>
@@ -7413,16 +7410,16 @@
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="B236" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="B236" s="1" t="s">
-        <v>511</v>
-      </c>
       <c r="C236" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="E236" s="1" t="s">
         <v>8</v>
@@ -7433,16 +7430,16 @@
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="B237" s="1" t="s">
         <v>512</v>
       </c>
-      <c r="B237" s="1" t="s">
-        <v>513</v>
-      </c>
       <c r="C237" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="E237" s="1" t="s">
         <v>11</v>
@@ -7453,16 +7450,16 @@
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="B238" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="B238" s="1" t="s">
-        <v>515</v>
-      </c>
       <c r="C238" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="E238" s="1" t="s">
         <v>14</v>
@@ -7473,16 +7470,16 @@
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="B239" s="1" t="s">
         <v>516</v>
       </c>
-      <c r="B239" s="1" t="s">
-        <v>517</v>
-      </c>
       <c r="C239" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="E239" s="1" t="s">
         <v>17</v>
@@ -7493,16 +7490,16 @@
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="B240" s="1" t="s">
         <v>518</v>
       </c>
-      <c r="B240" s="1" t="s">
-        <v>519</v>
-      </c>
       <c r="C240" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="E240" s="1" t="s">
         <v>20</v>
@@ -7513,16 +7510,16 @@
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="B241" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="B241" s="1" t="s">
-        <v>521</v>
-      </c>
       <c r="C241" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="E241" s="1" t="s">
         <v>38</v>
@@ -7533,36 +7530,36 @@
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="B242" s="1" t="s">
         <v>522</v>
       </c>
-      <c r="B242" s="1" t="s">
-        <v>523</v>
-      </c>
       <c r="C242" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="E242" s="1" t="s">
         <v>41</v>
       </c>
       <c r="F242" s="1" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="B243" s="1" t="s">
         <v>525</v>
       </c>
-      <c r="B243" s="1" t="s">
-        <v>526</v>
-      </c>
       <c r="C243" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="E243" s="1" t="s">
         <v>126</v>
@@ -7573,16 +7570,16 @@
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="B244" s="1" t="s">
         <v>527</v>
       </c>
-      <c r="B244" s="1" t="s">
+      <c r="C244" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D244" s="1" t="s">
         <v>528</v>
-      </c>
-      <c r="C244" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D244" s="1" t="s">
-        <v>529</v>
       </c>
       <c r="E244" s="1" t="s">
         <v>4</v>
@@ -7593,16 +7590,16 @@
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="B245" s="1" t="s">
         <v>530</v>
       </c>
-      <c r="B245" s="1" t="s">
-        <v>531</v>
-      </c>
       <c r="C245" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="E245" s="1" t="s">
         <v>8</v>
@@ -7613,16 +7610,16 @@
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="B246" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="B246" s="1" t="s">
-        <v>533</v>
-      </c>
       <c r="C246" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="E246" s="1" t="s">
         <v>11</v>
@@ -7633,16 +7630,16 @@
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="B247" s="1" t="s">
         <v>534</v>
       </c>
-      <c r="B247" s="1" t="s">
-        <v>535</v>
-      </c>
       <c r="C247" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="E247" s="1" t="s">
         <v>14</v>
@@ -7653,16 +7650,16 @@
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="B248" s="1" t="s">
         <v>536</v>
       </c>
-      <c r="B248" s="1" t="s">
-        <v>537</v>
-      </c>
       <c r="C248" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="E248" s="1" t="s">
         <v>17</v>
@@ -7673,16 +7670,16 @@
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="B249" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="B249" s="1" t="s">
-        <v>539</v>
-      </c>
       <c r="C249" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="E249" s="1" t="s">
         <v>20</v>
@@ -7693,16 +7690,16 @@
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="B250" s="1" t="s">
         <v>540</v>
       </c>
-      <c r="B250" s="1" t="s">
-        <v>541</v>
-      </c>
       <c r="C250" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="E250" s="1" t="s">
         <v>38</v>
@@ -7713,16 +7710,16 @@
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="B251" s="1" t="s">
         <v>542</v>
       </c>
-      <c r="B251" s="1" t="s">
-        <v>543</v>
-      </c>
       <c r="C251" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="E251" s="1" t="s">
         <v>41</v>
@@ -7733,16 +7730,16 @@
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="B252" s="1" t="s">
         <v>544</v>
       </c>
-      <c r="B252" s="1" t="s">
+      <c r="C252" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D252" s="1" t="s">
         <v>545</v>
-      </c>
-      <c r="C252" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D252" s="1" t="s">
-        <v>546</v>
       </c>
       <c r="E252" s="1" t="s">
         <v>4</v>
@@ -7753,16 +7750,16 @@
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="B253" s="1" t="s">
         <v>547</v>
       </c>
-      <c r="B253" s="1" t="s">
-        <v>548</v>
-      </c>
       <c r="C253" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="E253" s="1" t="s">
         <v>8</v>
@@ -7773,16 +7770,16 @@
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="B254" s="1" t="s">
         <v>549</v>
       </c>
-      <c r="B254" s="1" t="s">
-        <v>550</v>
-      </c>
       <c r="C254" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="E254" s="1" t="s">
         <v>11</v>
@@ -7793,16 +7790,16 @@
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="B255" s="1" t="s">
         <v>551</v>
       </c>
-      <c r="B255" s="1" t="s">
-        <v>552</v>
-      </c>
       <c r="C255" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="E255" s="1" t="s">
         <v>14</v>
@@ -7813,16 +7810,16 @@
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="B256" s="1" t="s">
         <v>553</v>
       </c>
-      <c r="B256" s="1" t="s">
-        <v>554</v>
-      </c>
       <c r="C256" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="E256" s="1" t="s">
         <v>17</v>
@@ -7833,16 +7830,16 @@
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="B257" s="1" t="s">
         <v>555</v>
       </c>
-      <c r="B257" s="1" t="s">
-        <v>556</v>
-      </c>
       <c r="C257" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="E257" s="1" t="s">
         <v>20</v>
@@ -7853,16 +7850,16 @@
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="B258" s="1" t="s">
         <v>557</v>
       </c>
-      <c r="B258" s="1" t="s">
-        <v>558</v>
-      </c>
       <c r="C258" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="E258" s="1" t="s">
         <v>38</v>
@@ -7873,16 +7870,16 @@
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="B259" s="1" t="s">
         <v>559</v>
       </c>
-      <c r="B259" s="1" t="s">
-        <v>560</v>
-      </c>
       <c r="C259" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="E259" s="1" t="s">
         <v>41</v>
@@ -7893,16 +7890,16 @@
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="B260" s="1" t="s">
         <v>561</v>
       </c>
-      <c r="B260" s="1" t="s">
+      <c r="C260" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D260" s="1" t="s">
         <v>562</v>
-      </c>
-      <c r="C260" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D260" s="1" t="s">
-        <v>563</v>
       </c>
       <c r="E260" s="1" t="s">
         <v>4</v>
@@ -7913,16 +7910,16 @@
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B261" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="C261" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D261" s="1" t="s">
         <v>562</v>
-      </c>
-      <c r="C261" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D261" s="1" t="s">
-        <v>563</v>
       </c>
       <c r="E261" s="1" t="s">
         <v>8</v>
@@ -7933,16 +7930,16 @@
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="B262" s="1" t="s">
         <v>565</v>
       </c>
-      <c r="B262" s="1" t="s">
-        <v>566</v>
-      </c>
       <c r="C262" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E262" s="1" t="s">
         <v>11</v>
@@ -7953,16 +7950,16 @@
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="B263" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="B263" s="1" t="s">
-        <v>568</v>
-      </c>
       <c r="C263" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E263" s="1" t="s">
         <v>14</v>
@@ -7973,16 +7970,16 @@
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="B264" s="1" t="s">
         <v>569</v>
       </c>
-      <c r="B264" s="1" t="s">
-        <v>570</v>
-      </c>
       <c r="C264" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E264" s="1" t="s">
         <v>17</v>
@@ -7993,16 +7990,16 @@
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="B265" s="1" t="s">
         <v>571</v>
       </c>
-      <c r="B265" s="1" t="s">
-        <v>572</v>
-      </c>
       <c r="C265" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E265" s="1" t="s">
         <v>20</v>
@@ -8013,16 +8010,16 @@
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="B266" s="1" t="s">
         <v>573</v>
       </c>
-      <c r="B266" s="1" t="s">
-        <v>574</v>
-      </c>
       <c r="C266" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E266" s="1" t="s">
         <v>38</v>
@@ -8033,16 +8030,16 @@
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A267" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="B267" s="1" t="s">
         <v>575</v>
       </c>
-      <c r="B267" s="1" t="s">
-        <v>576</v>
-      </c>
       <c r="C267" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E267" s="1" t="s">
         <v>41</v>
@@ -8053,16 +8050,16 @@
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="B268" s="1" t="s">
         <v>577</v>
       </c>
-      <c r="B268" s="1" t="s">
-        <v>578</v>
-      </c>
       <c r="C268" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E268" s="1" t="s">
         <v>126</v>
@@ -8073,16 +8070,16 @@
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="B269" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="B269" s="1" t="s">
+      <c r="C269" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D269" s="1" t="s">
         <v>580</v>
-      </c>
-      <c r="C269" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D269" s="1" t="s">
-        <v>581</v>
       </c>
       <c r="E269" s="1" t="s">
         <v>4</v>
@@ -8093,16 +8090,16 @@
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="B270" s="1" t="s">
         <v>582</v>
       </c>
-      <c r="B270" s="1" t="s">
-        <v>583</v>
-      </c>
       <c r="C270" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="E270" s="1" t="s">
         <v>8</v>
@@ -8113,16 +8110,16 @@
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="B271" s="1" t="s">
         <v>584</v>
       </c>
-      <c r="B271" s="1" t="s">
-        <v>585</v>
-      </c>
       <c r="C271" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="E271" s="1" t="s">
         <v>11</v>
@@ -8133,16 +8130,16 @@
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="B272" s="1" t="s">
         <v>586</v>
       </c>
-      <c r="B272" s="1" t="s">
-        <v>587</v>
-      </c>
       <c r="C272" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="E272" s="1" t="s">
         <v>14</v>
@@ -8153,16 +8150,16 @@
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="B273" s="1" t="s">
         <v>588</v>
       </c>
-      <c r="B273" s="1" t="s">
-        <v>589</v>
-      </c>
       <c r="C273" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="E273" s="1" t="s">
         <v>17</v>
@@ -8173,16 +8170,16 @@
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="B274" s="1" t="s">
         <v>590</v>
       </c>
-      <c r="B274" s="1" t="s">
-        <v>591</v>
-      </c>
       <c r="C274" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="E274" s="1" t="s">
         <v>20</v>
@@ -8193,16 +8190,16 @@
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="B275" s="1" t="s">
         <v>592</v>
       </c>
-      <c r="B275" s="1" t="s">
-        <v>593</v>
-      </c>
       <c r="C275" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="E275" s="1" t="s">
         <v>38</v>
@@ -8213,16 +8210,16 @@
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="B276" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="B276" s="1" t="s">
-        <v>595</v>
-      </c>
       <c r="C276" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="E276" s="1" t="s">
         <v>41</v>
@@ -8233,16 +8230,16 @@
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="B277" s="1" t="s">
         <v>596</v>
       </c>
-      <c r="B277" s="1" t="s">
-        <v>597</v>
-      </c>
       <c r="C277" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="E277" s="1" t="s">
         <v>126</v>
@@ -8253,16 +8250,16 @@
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="B278" s="1" t="s">
         <v>598</v>
       </c>
-      <c r="B278" s="1" t="s">
-        <v>599</v>
-      </c>
       <c r="C278" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="E278" s="1" t="s">
         <v>145</v>
@@ -8273,16 +8270,16 @@
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="B279" s="1" t="s">
         <v>600</v>
       </c>
-      <c r="B279" s="1" t="s">
-        <v>601</v>
-      </c>
       <c r="C279" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="E279" s="1" t="s">
         <v>164</v>
@@ -8293,16 +8290,16 @@
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="B280" s="1" t="s">
         <v>602</v>
       </c>
-      <c r="B280" s="1" t="s">
+      <c r="C280" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D280" s="1" t="s">
         <v>603</v>
-      </c>
-      <c r="C280" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D280" s="1" t="s">
-        <v>604</v>
       </c>
       <c r="E280" s="1" t="s">
         <v>4</v>
@@ -8313,16 +8310,16 @@
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="B281" s="1" t="s">
         <v>605</v>
       </c>
-      <c r="B281" s="1" t="s">
-        <v>606</v>
-      </c>
       <c r="C281" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="E281" s="1" t="s">
         <v>8</v>
@@ -8333,16 +8330,16 @@
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="B282" s="1" t="s">
         <v>607</v>
       </c>
-      <c r="B282" s="1" t="s">
-        <v>608</v>
-      </c>
       <c r="C282" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="E282" s="1" t="s">
         <v>11</v>
@@ -8353,16 +8350,16 @@
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" s="1" t="s">
+        <v>608</v>
+      </c>
+      <c r="B283" s="1" t="s">
         <v>609</v>
       </c>
-      <c r="B283" s="1" t="s">
-        <v>610</v>
-      </c>
       <c r="C283" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="E283" s="1" t="s">
         <v>14</v>
@@ -8373,16 +8370,16 @@
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="B284" s="1" t="s">
         <v>611</v>
       </c>
-      <c r="B284" s="1" t="s">
-        <v>612</v>
-      </c>
       <c r="C284" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="E284" s="1" t="s">
         <v>17</v>
@@ -8393,16 +8390,16 @@
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A285" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="B285" s="1" t="s">
         <v>613</v>
       </c>
-      <c r="B285" s="1" t="s">
-        <v>614</v>
-      </c>
       <c r="C285" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="E285" s="1" t="s">
         <v>20</v>
@@ -8413,36 +8410,36 @@
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A286" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="B286" s="1" t="s">
         <v>615</v>
       </c>
-      <c r="B286" s="1" t="s">
-        <v>616</v>
-      </c>
       <c r="C286" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="E286" s="1" t="s">
         <v>38</v>
       </c>
       <c r="F286" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A287" s="1" t="s">
+        <v>617</v>
+      </c>
+      <c r="B287" s="1" t="s">
         <v>618</v>
       </c>
-      <c r="B287" s="1" t="s">
-        <v>619</v>
-      </c>
       <c r="C287" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="E287" s="1" t="s">
         <v>41</v>
@@ -8453,16 +8450,16 @@
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288" s="1" t="s">
+        <v>619</v>
+      </c>
+      <c r="B288" s="1" t="s">
         <v>620</v>
       </c>
-      <c r="B288" s="1" t="s">
-        <v>621</v>
-      </c>
       <c r="C288" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="E288" s="1" t="s">
         <v>126</v>
@@ -8473,16 +8470,16 @@
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A289" s="1" t="s">
+        <v>621</v>
+      </c>
+      <c r="B289" s="1" t="s">
         <v>622</v>
       </c>
-      <c r="B289" s="1" t="s">
-        <v>623</v>
-      </c>
       <c r="C289" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="E289" s="1" t="s">
         <v>145</v>
@@ -8493,196 +8490,196 @@
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290" s="1" t="s">
+        <v>623</v>
+      </c>
+      <c r="B290" s="1" t="s">
         <v>624</v>
       </c>
-      <c r="B290" s="1" t="s">
+      <c r="C290" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D290" s="1" t="s">
         <v>625</v>
-      </c>
-      <c r="C290" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D290" s="1" t="s">
-        <v>626</v>
       </c>
       <c r="E290" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F290" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A291" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="B291" s="1" t="s">
         <v>627</v>
       </c>
-      <c r="B291" s="1" t="s">
-        <v>628</v>
-      </c>
       <c r="C291" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="E291" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F291" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A292" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="B292" s="1" t="s">
         <v>629</v>
       </c>
-      <c r="B292" s="1" t="s">
-        <v>630</v>
-      </c>
       <c r="C292" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="E292" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F292" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A293" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="B293" s="1" t="s">
         <v>631</v>
       </c>
-      <c r="B293" s="1" t="s">
-        <v>632</v>
-      </c>
       <c r="C293" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="E293" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F293" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A294" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="B294" s="1" t="s">
         <v>633</v>
       </c>
-      <c r="B294" s="1" t="s">
-        <v>634</v>
-      </c>
       <c r="C294" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="E294" s="1" t="s">
         <v>17</v>
       </c>
       <c r="F294" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A295" s="1" t="s">
+        <v>634</v>
+      </c>
+      <c r="B295" s="1" t="s">
         <v>635</v>
       </c>
-      <c r="B295" s="1" t="s">
-        <v>636</v>
-      </c>
       <c r="C295" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="E295" s="1" t="s">
         <v>20</v>
       </c>
       <c r="F295" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A296" s="1" t="s">
+        <v>636</v>
+      </c>
+      <c r="B296" s="1" t="s">
         <v>637</v>
       </c>
-      <c r="B296" s="1" t="s">
-        <v>638</v>
-      </c>
       <c r="C296" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="E296" s="1" t="s">
         <v>38</v>
       </c>
       <c r="F296" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A297" s="1" t="s">
+        <v>638</v>
+      </c>
+      <c r="B297" s="1" t="s">
         <v>639</v>
       </c>
-      <c r="B297" s="1" t="s">
-        <v>640</v>
-      </c>
       <c r="C297" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="E297" s="1" t="s">
         <v>41</v>
       </c>
       <c r="F297" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A298" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="B298" s="1" t="s">
         <v>641</v>
       </c>
-      <c r="B298" s="1" t="s">
-        <v>642</v>
-      </c>
       <c r="C298" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="E298" s="1" t="s">
         <v>126</v>
       </c>
       <c r="F298" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A299" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="B299" s="1" t="s">
         <v>643</v>
       </c>
-      <c r="B299" s="1" t="s">
+      <c r="C299" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D299" s="1" t="s">
         <v>644</v>
-      </c>
-      <c r="C299" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D299" s="1" t="s">
-        <v>645</v>
       </c>
       <c r="E299" s="1" t="s">
         <v>4</v>
@@ -8693,16 +8690,16 @@
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A300" s="1" t="s">
+        <v>645</v>
+      </c>
+      <c r="B300" s="1" t="s">
         <v>646</v>
       </c>
-      <c r="B300" s="1" t="s">
-        <v>647</v>
-      </c>
       <c r="C300" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="E300" s="1" t="s">
         <v>8</v>
@@ -8713,16 +8710,16 @@
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A301" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="B301" s="1" t="s">
         <v>648</v>
       </c>
-      <c r="B301" s="1" t="s">
-        <v>649</v>
-      </c>
       <c r="C301" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="E301" s="1" t="s">
         <v>11</v>
@@ -8733,16 +8730,16 @@
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A302" s="1" t="s">
+        <v>649</v>
+      </c>
+      <c r="B302" s="1" t="s">
         <v>650</v>
       </c>
-      <c r="B302" s="1" t="s">
-        <v>651</v>
-      </c>
       <c r="C302" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="E302" s="1" t="s">
         <v>14</v>
@@ -8753,16 +8750,16 @@
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A303" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="B303" s="1" t="s">
         <v>652</v>
       </c>
-      <c r="B303" s="1" t="s">
-        <v>653</v>
-      </c>
       <c r="C303" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D303" s="1" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="E303" s="1" t="s">
         <v>17</v>
@@ -8773,16 +8770,16 @@
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A304" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="B304" s="1" t="s">
         <v>654</v>
       </c>
-      <c r="B304" s="1" t="s">
-        <v>655</v>
-      </c>
       <c r="C304" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D304" s="1" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="E304" s="1" t="s">
         <v>20</v>
@@ -8793,16 +8790,16 @@
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A305" s="1" t="s">
+        <v>655</v>
+      </c>
+      <c r="B305" s="1" t="s">
         <v>656</v>
       </c>
-      <c r="B305" s="1" t="s">
-        <v>657</v>
-      </c>
       <c r="C305" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D305" s="1" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="E305" s="1" t="s">
         <v>38</v>
@@ -8813,16 +8810,16 @@
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A306" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="B306" s="1" t="s">
         <v>658</v>
       </c>
-      <c r="B306" s="1" t="s">
-        <v>659</v>
-      </c>
       <c r="C306" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D306" s="1" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="E306" s="1" t="s">
         <v>41</v>
@@ -8833,16 +8830,16 @@
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A307" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="B307" s="1" t="s">
         <v>660</v>
       </c>
-      <c r="B307" s="1" t="s">
-        <v>661</v>
-      </c>
       <c r="C307" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D307" s="1" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="E307" s="1" t="s">
         <v>126</v>
@@ -8853,16 +8850,16 @@
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A308" s="1" t="s">
+        <v>661</v>
+      </c>
+      <c r="B308" s="1" t="s">
         <v>662</v>
       </c>
-      <c r="B308" s="1" t="s">
-        <v>663</v>
-      </c>
       <c r="C308" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D308" s="1" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="E308" s="1" t="s">
         <v>145</v>
@@ -8873,16 +8870,16 @@
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A309" s="1" t="s">
+        <v>663</v>
+      </c>
+      <c r="B309" s="1" t="s">
         <v>664</v>
       </c>
-      <c r="B309" s="1" t="s">
+      <c r="C309" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D309" s="1" t="s">
         <v>665</v>
-      </c>
-      <c r="C309" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D309" s="1" t="s">
-        <v>666</v>
       </c>
       <c r="E309" s="1" t="s">
         <v>4</v>
@@ -8893,16 +8890,16 @@
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A310" s="1" t="s">
+        <v>666</v>
+      </c>
+      <c r="B310" s="1" t="s">
         <v>667</v>
       </c>
-      <c r="B310" s="1" t="s">
-        <v>668</v>
-      </c>
       <c r="C310" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D310" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="E310" s="1" t="s">
         <v>8</v>
@@ -8913,16 +8910,16 @@
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A311" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="B311" s="1" t="s">
         <v>669</v>
       </c>
-      <c r="B311" s="1" t="s">
-        <v>670</v>
-      </c>
       <c r="C311" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D311" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="E311" s="1" t="s">
         <v>11</v>
@@ -8933,16 +8930,16 @@
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A312" s="1" t="s">
+        <v>670</v>
+      </c>
+      <c r="B312" s="1" t="s">
         <v>671</v>
       </c>
-      <c r="B312" s="1" t="s">
-        <v>672</v>
-      </c>
       <c r="C312" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D312" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="E312" s="1" t="s">
         <v>14</v>
@@ -8953,16 +8950,16 @@
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A313" s="1" t="s">
+        <v>672</v>
+      </c>
+      <c r="B313" s="1" t="s">
         <v>673</v>
       </c>
-      <c r="B313" s="1" t="s">
-        <v>674</v>
-      </c>
       <c r="C313" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D313" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="E313" s="1" t="s">
         <v>17</v>
@@ -8973,16 +8970,16 @@
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A314" s="1" t="s">
+        <v>674</v>
+      </c>
+      <c r="B314" s="1" t="s">
         <v>675</v>
       </c>
-      <c r="B314" s="1" t="s">
-        <v>676</v>
-      </c>
       <c r="C314" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D314" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="E314" s="1" t="s">
         <v>20</v>
@@ -8993,16 +8990,16 @@
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A315" s="1" t="s">
+        <v>676</v>
+      </c>
+      <c r="B315" s="1" t="s">
         <v>677</v>
       </c>
-      <c r="B315" s="1" t="s">
-        <v>678</v>
-      </c>
       <c r="C315" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D315" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="E315" s="1" t="s">
         <v>38</v>
@@ -9013,16 +9010,16 @@
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A316" s="1" t="s">
+        <v>678</v>
+      </c>
+      <c r="B316" s="1" t="s">
         <v>679</v>
       </c>
-      <c r="B316" s="1" t="s">
-        <v>680</v>
-      </c>
       <c r="C316" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D316" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="E316" s="1" t="s">
         <v>41</v>
@@ -9033,16 +9030,16 @@
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A317" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="B317" s="1" t="s">
         <v>681</v>
       </c>
-      <c r="B317" s="1" t="s">
-        <v>682</v>
-      </c>
       <c r="C317" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D317" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="E317" s="1" t="s">
         <v>126</v>
@@ -9053,16 +9050,16 @@
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A318" s="1" t="s">
+        <v>682</v>
+      </c>
+      <c r="B318" s="1" t="s">
         <v>683</v>
       </c>
-      <c r="B318" s="1" t="s">
+      <c r="C318" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D318" s="1" t="s">
         <v>684</v>
-      </c>
-      <c r="C318" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D318" s="1" t="s">
-        <v>685</v>
       </c>
       <c r="E318" s="1" t="s">
         <v>4</v>
@@ -9073,16 +9070,16 @@
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A319" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="B319" s="1" t="s">
         <v>686</v>
       </c>
-      <c r="B319" s="1" t="s">
-        <v>687</v>
-      </c>
       <c r="C319" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D319" s="1" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="E319" s="1" t="s">
         <v>8</v>
@@ -9093,16 +9090,16 @@
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A320" s="1" t="s">
+        <v>687</v>
+      </c>
+      <c r="B320" s="1" t="s">
         <v>688</v>
       </c>
-      <c r="B320" s="1" t="s">
-        <v>689</v>
-      </c>
       <c r="C320" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D320" s="1" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="E320" s="1" t="s">
         <v>11</v>
@@ -9113,16 +9110,16 @@
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A321" s="1" t="s">
+        <v>689</v>
+      </c>
+      <c r="B321" s="1" t="s">
         <v>690</v>
       </c>
-      <c r="B321" s="1" t="s">
-        <v>691</v>
-      </c>
       <c r="C321" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D321" s="1" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="E321" s="1" t="s">
         <v>14</v>
@@ -9133,16 +9130,16 @@
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A322" s="1" t="s">
+        <v>691</v>
+      </c>
+      <c r="B322" s="1" t="s">
         <v>692</v>
       </c>
-      <c r="B322" s="1" t="s">
-        <v>693</v>
-      </c>
       <c r="C322" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D322" s="1" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="E322" s="1" t="s">
         <v>17</v>
@@ -9153,16 +9150,16 @@
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A323" s="1" t="s">
+        <v>693</v>
+      </c>
+      <c r="B323" s="1" t="s">
         <v>694</v>
       </c>
-      <c r="B323" s="1" t="s">
-        <v>695</v>
-      </c>
       <c r="C323" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D323" s="1" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="E323" s="1" t="s">
         <v>20</v>
@@ -9173,16 +9170,16 @@
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A324" s="1" t="s">
+        <v>695</v>
+      </c>
+      <c r="B324" s="1" t="s">
         <v>696</v>
       </c>
-      <c r="B324" s="1" t="s">
-        <v>697</v>
-      </c>
       <c r="C324" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D324" s="1" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="E324" s="1" t="s">
         <v>38</v>
@@ -9193,16 +9190,16 @@
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A325" s="1" t="s">
+        <v>697</v>
+      </c>
+      <c r="B325" s="1" t="s">
         <v>698</v>
       </c>
-      <c r="B325" s="1" t="s">
-        <v>699</v>
-      </c>
       <c r="C325" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D325" s="1" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="E325" s="1" t="s">
         <v>41</v>
@@ -9213,16 +9210,16 @@
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A326" s="1" t="s">
+        <v>699</v>
+      </c>
+      <c r="B326" s="1" t="s">
         <v>700</v>
       </c>
-      <c r="B326" s="1" t="s">
-        <v>701</v>
-      </c>
       <c r="C326" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D326" s="1" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="E326" s="1" t="s">
         <v>126</v>
@@ -9233,16 +9230,16 @@
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A327" s="1" t="s">
+        <v>701</v>
+      </c>
+      <c r="B327" s="1" t="s">
         <v>702</v>
       </c>
-      <c r="B327" s="1" t="s">
+      <c r="C327" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D327" s="1" t="s">
         <v>703</v>
-      </c>
-      <c r="C327" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D327" s="1" t="s">
-        <v>704</v>
       </c>
       <c r="E327" s="1" t="s">
         <v>4</v>
@@ -9253,16 +9250,16 @@
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A328" s="1" t="s">
+        <v>704</v>
+      </c>
+      <c r="B328" s="1" t="s">
         <v>705</v>
       </c>
-      <c r="B328" s="1" t="s">
-        <v>706</v>
-      </c>
       <c r="C328" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D328" s="1" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="E328" s="1" t="s">
         <v>8</v>
@@ -9273,16 +9270,16 @@
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A329" s="1" t="s">
+        <v>706</v>
+      </c>
+      <c r="B329" s="1" t="s">
         <v>707</v>
       </c>
-      <c r="B329" s="1" t="s">
-        <v>708</v>
-      </c>
       <c r="C329" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D329" s="1" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="E329" s="1" t="s">
         <v>11</v>
@@ -9293,16 +9290,16 @@
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A330" s="1" t="s">
+        <v>708</v>
+      </c>
+      <c r="B330" s="1" t="s">
         <v>709</v>
       </c>
-      <c r="B330" s="1" t="s">
-        <v>710</v>
-      </c>
       <c r="C330" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D330" s="1" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="E330" s="1" t="s">
         <v>14</v>
@@ -9313,16 +9310,16 @@
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A331" s="1" t="s">
+        <v>710</v>
+      </c>
+      <c r="B331" s="1" t="s">
         <v>711</v>
       </c>
-      <c r="B331" s="1" t="s">
-        <v>712</v>
-      </c>
       <c r="C331" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D331" s="1" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="E331" s="1" t="s">
         <v>17</v>
@@ -9333,16 +9330,16 @@
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A332" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B332" s="1" t="s">
         <v>713</v>
       </c>
-      <c r="B332" s="1" t="s">
-        <v>714</v>
-      </c>
       <c r="C332" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D332" s="1" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="E332" s="1" t="s">
         <v>20</v>
@@ -9353,16 +9350,16 @@
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A333" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="B333" s="1" t="s">
         <v>715</v>
       </c>
-      <c r="B333" s="1" t="s">
-        <v>716</v>
-      </c>
       <c r="C333" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D333" s="1" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="E333" s="1" t="s">
         <v>38</v>
@@ -9373,16 +9370,16 @@
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A334" s="1" t="s">
+        <v>716</v>
+      </c>
+      <c r="B334" s="1" t="s">
         <v>717</v>
       </c>
-      <c r="B334" s="1" t="s">
-        <v>718</v>
-      </c>
       <c r="C334" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D334" s="1" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="E334" s="1" t="s">
         <v>41</v>
@@ -9393,16 +9390,16 @@
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A335" s="1" t="s">
+        <v>718</v>
+      </c>
+      <c r="B335" s="1" t="s">
         <v>719</v>
       </c>
-      <c r="B335" s="1" t="s">
-        <v>720</v>
-      </c>
       <c r="C335" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D335" s="1" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="E335" s="1" t="s">
         <v>126</v>
@@ -9413,16 +9410,16 @@
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A336" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="B336" s="1" t="s">
         <v>721</v>
       </c>
-      <c r="B336" s="1" t="s">
-        <v>722</v>
-      </c>
       <c r="C336" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D336" s="1" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="E336" s="1" t="s">
         <v>145</v>
@@ -9433,16 +9430,16 @@
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A337" s="1" t="s">
+        <v>722</v>
+      </c>
+      <c r="B337" s="1" t="s">
         <v>723</v>
       </c>
-      <c r="B337" s="1" t="s">
+      <c r="C337" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D337" s="1" t="s">
         <v>724</v>
-      </c>
-      <c r="C337" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D337" s="1" t="s">
-        <v>725</v>
       </c>
       <c r="E337" s="1" t="s">
         <v>4</v>
@@ -9453,16 +9450,16 @@
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A338" s="1" t="s">
+        <v>725</v>
+      </c>
+      <c r="B338" s="1" t="s">
         <v>726</v>
       </c>
-      <c r="B338" s="1" t="s">
-        <v>727</v>
-      </c>
       <c r="C338" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D338" s="1" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E338" s="1" t="s">
         <v>8</v>
@@ -9473,16 +9470,16 @@
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A339" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="B339" s="1" t="s">
         <v>728</v>
       </c>
-      <c r="B339" s="1" t="s">
-        <v>729</v>
-      </c>
       <c r="C339" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D339" s="1" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E339" s="1" t="s">
         <v>11</v>
@@ -9493,16 +9490,16 @@
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A340" s="1" t="s">
+        <v>729</v>
+      </c>
+      <c r="B340" s="1" t="s">
         <v>730</v>
       </c>
-      <c r="B340" s="1" t="s">
-        <v>731</v>
-      </c>
       <c r="C340" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D340" s="1" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E340" s="1" t="s">
         <v>14</v>
@@ -9513,16 +9510,16 @@
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A341" s="1" t="s">
+        <v>731</v>
+      </c>
+      <c r="B341" s="1" t="s">
         <v>732</v>
       </c>
-      <c r="B341" s="1" t="s">
-        <v>733</v>
-      </c>
       <c r="C341" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D341" s="1" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E341" s="1" t="s">
         <v>17</v>
@@ -9533,16 +9530,16 @@
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A342" s="1" t="s">
+        <v>733</v>
+      </c>
+      <c r="B342" s="1" t="s">
         <v>734</v>
       </c>
-      <c r="B342" s="1" t="s">
-        <v>735</v>
-      </c>
       <c r="C342" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D342" s="1" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E342" s="1" t="s">
         <v>20</v>
@@ -9553,16 +9550,16 @@
     </row>
     <row r="343" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A343" s="1" t="s">
+        <v>735</v>
+      </c>
+      <c r="B343" s="1" t="s">
         <v>736</v>
       </c>
-      <c r="B343" s="1" t="s">
-        <v>737</v>
-      </c>
       <c r="C343" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D343" s="1" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E343" s="1" t="s">
         <v>38</v>
@@ -9573,36 +9570,36 @@
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A344" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="B344" s="1" t="s">
         <v>738</v>
       </c>
-      <c r="B344" s="1" t="s">
-        <v>739</v>
-      </c>
       <c r="C344" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D344" s="1" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E344" s="1" t="s">
         <v>41</v>
       </c>
       <c r="F344" s="1" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A345" s="1" t="s">
+        <v>740</v>
+      </c>
+      <c r="B345" s="1" t="s">
         <v>741</v>
       </c>
-      <c r="B345" s="1" t="s">
-        <v>742</v>
-      </c>
       <c r="C345" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D345" s="1" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E345" s="1" t="s">
         <v>126</v>
@@ -9613,16 +9610,16 @@
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A346" s="1" t="s">
+        <v>742</v>
+      </c>
+      <c r="B346" s="1" t="s">
         <v>743</v>
       </c>
-      <c r="B346" s="1" t="s">
+      <c r="C346" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D346" s="1" t="s">
         <v>744</v>
-      </c>
-      <c r="C346" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D346" s="1" t="s">
-        <v>745</v>
       </c>
       <c r="E346" s="1" t="s">
         <v>4</v>
@@ -9633,16 +9630,16 @@
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A347" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="B347" s="1" t="s">
         <v>746</v>
       </c>
-      <c r="B347" s="1" t="s">
-        <v>747</v>
-      </c>
       <c r="C347" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D347" s="1" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="E347" s="1" t="s">
         <v>8</v>
@@ -9653,16 +9650,16 @@
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A348" s="1" t="s">
+        <v>747</v>
+      </c>
+      <c r="B348" s="1" t="s">
         <v>748</v>
       </c>
-      <c r="B348" s="1" t="s">
+      <c r="C348" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D348" s="1" t="s">
         <v>749</v>
-      </c>
-      <c r="C348" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D348" s="1" t="s">
-        <v>750</v>
       </c>
       <c r="E348" s="1" t="s">
         <v>4</v>
@@ -9673,16 +9670,16 @@
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A349" s="1" t="s">
+        <v>750</v>
+      </c>
+      <c r="B349" s="1" t="s">
         <v>751</v>
       </c>
-      <c r="B349" s="1" t="s">
+      <c r="C349" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D349" s="1" t="s">
         <v>752</v>
-      </c>
-      <c r="C349" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D349" s="1" t="s">
-        <v>753</v>
       </c>
       <c r="E349" s="1" t="s">
         <v>4</v>
@@ -9693,76 +9690,76 @@
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A350" s="1" t="s">
+        <v>753</v>
+      </c>
+      <c r="B350" s="1" t="s">
         <v>754</v>
       </c>
-      <c r="B350" s="1" t="s">
+      <c r="C350" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D350" s="1" t="s">
         <v>755</v>
-      </c>
-      <c r="C350" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D350" s="1" t="s">
-        <v>756</v>
       </c>
       <c r="E350" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F350" s="1" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A351" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="B351" s="1" t="s">
         <v>758</v>
       </c>
-      <c r="B351" s="1" t="s">
-        <v>759</v>
-      </c>
       <c r="C351" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D351" s="1" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="E351" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F351" s="1" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A352" s="1" t="s">
+        <v>760</v>
+      </c>
+      <c r="B352" s="1" t="s">
         <v>761</v>
       </c>
-      <c r="B352" s="1" t="s">
-        <v>762</v>
-      </c>
       <c r="C352" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D352" s="1" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="E352" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F352" s="1" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="353" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A353" s="1" t="s">
+        <v>763</v>
+      </c>
+      <c r="B353" s="1" t="s">
         <v>764</v>
       </c>
-      <c r="B353" s="1" t="s">
-        <v>765</v>
-      </c>
       <c r="C353" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D353" s="1" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="E353" s="1" t="s">
         <v>14</v>

--- a/CLB07N.xlsx
+++ b/CLB07N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2118" uniqueCount="765">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2130" uniqueCount="769">
   <si>
     <t/>
   </si>
@@ -355,6 +355,18 @@
     <t>LUWAK KOPI+GULA 220</t>
   </si>
   <si>
+    <t>20093586</t>
+  </si>
+  <si>
+    <t>ICHTN THAI M.COFF300</t>
+  </si>
+  <si>
+    <t>20136363</t>
+  </si>
+  <si>
+    <t>ICHTN DARK CHOCO 300</t>
+  </si>
+  <si>
     <t>20123322</t>
   </si>
   <si>
@@ -379,67 +391,160 @@
     <t>KOPIKO 78C 240ML</t>
   </si>
   <si>
+    <t>20138025</t>
+  </si>
+  <si>
+    <t>HY BTS COFF TRMS 250</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>20138049</t>
+  </si>
+  <si>
+    <t>HY BTS COFF CPNO 250</t>
+  </si>
+  <si>
+    <t>20120904</t>
+  </si>
+  <si>
+    <t>KK BLACK AREN 220ML</t>
+  </si>
+  <si>
+    <t>20120906</t>
+  </si>
+  <si>
+    <t>KK MANTANCINO 220ML</t>
+  </si>
+  <si>
+    <t>20133409</t>
+  </si>
+  <si>
+    <t>KK CAFFE LATTE 200ML</t>
+  </si>
+  <si>
+    <t>20138168</t>
+  </si>
+  <si>
+    <t>KK CHEESE LATTEE 200</t>
+  </si>
+  <si>
+    <t>20138167</t>
+  </si>
+  <si>
+    <t>KK JPNS MATCHA 200</t>
+  </si>
+  <si>
+    <t>20132760</t>
+  </si>
+  <si>
+    <t>CAFINO RTD ESPRSO200</t>
+  </si>
+  <si>
+    <t>20132761</t>
+  </si>
+  <si>
+    <t>CAFINO RTD CPCINO200</t>
+  </si>
+  <si>
+    <t>20138035</t>
+  </si>
+  <si>
+    <t>CAFFINO OATMARIE 200</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
     <t>20078206</t>
   </si>
   <si>
     <t>LUWAK WHT ORGL 220ML</t>
   </si>
   <si>
-    <t>20093586</t>
-  </si>
-  <si>
-    <t>ICHTN THAI M.COFF300</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>20136363</t>
-  </si>
-  <si>
-    <t>ICHTN DARK CHOCO 300</t>
-  </si>
-  <si>
-    <t>20138025</t>
-  </si>
-  <si>
-    <t>HY BTS COFF TRMS 250</t>
-  </si>
-  <si>
-    <t>20138049</t>
-  </si>
-  <si>
-    <t>HY BTS COFF CPNO 250</t>
-  </si>
-  <si>
-    <t>20120904</t>
-  </si>
-  <si>
-    <t>KK BLACK AREN 220ML</t>
-  </si>
-  <si>
-    <t>20120906</t>
-  </si>
-  <si>
-    <t>KK MANTANCINO 220ML</t>
-  </si>
-  <si>
-    <t>20133409</t>
-  </si>
-  <si>
-    <t>KK CAFFE LATTE 200ML</t>
-  </si>
-  <si>
-    <t>20138168</t>
-  </si>
-  <si>
-    <t>KK CHEESE LATTEE 200</t>
-  </si>
-  <si>
-    <t>20138167</t>
-  </si>
-  <si>
-    <t>KK JPNS MATCHA 200</t>
+    <t>20076770</t>
+  </si>
+  <si>
+    <t>G/DAY CAPPUCCINO 250</t>
+  </si>
+  <si>
+    <t>20045674</t>
+  </si>
+  <si>
+    <t>G/DAY F.MOCACINO 250</t>
+  </si>
+  <si>
+    <t>20045673</t>
+  </si>
+  <si>
+    <t>G/DAY TIRAMISU/B 250</t>
+  </si>
+  <si>
+    <t>20056193</t>
+  </si>
+  <si>
+    <t>GOOD DAY AVCDO/D 250</t>
+  </si>
+  <si>
+    <t>20132329</t>
+  </si>
+  <si>
+    <t>GOOD DAY GRVY CKS250</t>
+  </si>
+  <si>
+    <t>20134557</t>
+  </si>
+  <si>
+    <t>OATSIDE CRML MCHT200</t>
+  </si>
+  <si>
+    <t>20129108</t>
+  </si>
+  <si>
+    <t>OATSDE COFFEE 200ML</t>
+  </si>
+  <si>
+    <t>20142499</t>
+  </si>
+  <si>
+    <t>OATSDE ESPR RST 240</t>
+  </si>
+  <si>
+    <t>20139577</t>
+  </si>
+  <si>
+    <t>PC AREN LATTE 210ML</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20139578</t>
+  </si>
+  <si>
+    <t>PC GOLDN CARAMEL 210</t>
+  </si>
+  <si>
+    <t>20139576</t>
+  </si>
+  <si>
+    <t>PC CRMY CPUCCINO 210</t>
+  </si>
+  <si>
+    <t>20140431</t>
+  </si>
+  <si>
+    <t>NSCAFE KITKAT LAT220</t>
+  </si>
+  <si>
+    <t>20133058</t>
+  </si>
+  <si>
+    <t>NSCAFE OAT LATTE 220</t>
   </si>
   <si>
     <t>20027768</t>
@@ -448,105 +553,6 @@
     <t>NESCAFE COFF CRM 180</t>
   </si>
   <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>20076770</t>
-  </si>
-  <si>
-    <t>G/DAY CAPPUCCINO 250</t>
-  </si>
-  <si>
-    <t>20045674</t>
-  </si>
-  <si>
-    <t>G/DAY F.MOCACINO 250</t>
-  </si>
-  <si>
-    <t>20045673</t>
-  </si>
-  <si>
-    <t>G/DAY TIRAMISU/B 250</t>
-  </si>
-  <si>
-    <t>20056193</t>
-  </si>
-  <si>
-    <t>GOOD DAY AVCDO/D 250</t>
-  </si>
-  <si>
-    <t>20132329</t>
-  </si>
-  <si>
-    <t>GOOD DAY GRVY CKS250</t>
-  </si>
-  <si>
-    <t>20132760</t>
-  </si>
-  <si>
-    <t>CAFINO RTD ESPRSO200</t>
-  </si>
-  <si>
-    <t>20132761</t>
-  </si>
-  <si>
-    <t>CAFINO RTD CPCINO200</t>
-  </si>
-  <si>
-    <t>20138035</t>
-  </si>
-  <si>
-    <t>CAFFINO OATMARIE 200</t>
-  </si>
-  <si>
-    <t>20139577</t>
-  </si>
-  <si>
-    <t>PC AREN LATTE 210ML</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20139578</t>
-  </si>
-  <si>
-    <t>PC GOLDN CARAMEL 210</t>
-  </si>
-  <si>
-    <t>20139576</t>
-  </si>
-  <si>
-    <t>PC CRMY CPUCCINO 210</t>
-  </si>
-  <si>
-    <t>20140431</t>
-  </si>
-  <si>
-    <t>NSCAFE KITKAT LAT220</t>
-  </si>
-  <si>
-    <t>20133058</t>
-  </si>
-  <si>
-    <t>NSCAFE OAT LATTE 220</t>
-  </si>
-  <si>
-    <t>20134557</t>
-  </si>
-  <si>
-    <t>OATSIDE CRML MCHT200</t>
-  </si>
-  <si>
-    <t>20129108</t>
-  </si>
-  <si>
-    <t>OATSDE COFFEE 200ML</t>
-  </si>
-  <si>
     <t>20114494</t>
   </si>
   <si>
@@ -682,6 +688,12 @@
     <t>NU YOGRT TEA BRY 450</t>
   </si>
   <si>
+    <t>20036157</t>
+  </si>
+  <si>
+    <t>SOSRO TEH BOTOL 450</t>
+  </si>
+  <si>
     <t>20002203</t>
   </si>
   <si>
@@ -706,261 +718,255 @@
     <t>FRUIT TEA FREEZE 500</t>
   </si>
   <si>
+    <t>20126464</t>
+  </si>
+  <si>
+    <t>IDM TEH APL&amp;LYCHE350</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>20101897</t>
+  </si>
+  <si>
+    <t>IDM TEH APEL 350ML</t>
+  </si>
+  <si>
+    <t>20132840</t>
+  </si>
+  <si>
+    <t>IDM TEH BLCKCRRNT350</t>
+  </si>
+  <si>
+    <t>20066454</t>
+  </si>
+  <si>
+    <t>FRUIT TEA BLCKCR 350</t>
+  </si>
+  <si>
+    <t>20073495</t>
+  </si>
+  <si>
+    <t>FRUIT TEA FREEZE 350</t>
+  </si>
+  <si>
+    <t>20066455</t>
+  </si>
+  <si>
+    <t>FRUIT TEA APPLE 350</t>
+  </si>
+  <si>
+    <t>20079972</t>
+  </si>
+  <si>
+    <t>FRUIT TEA MRKISA 350</t>
+  </si>
+  <si>
+    <t>20060207</t>
+  </si>
+  <si>
+    <t>I/OCHA TEH MLATI 350</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>20048934</t>
+  </si>
+  <si>
+    <t>I/OCHA GRN TEA 350ML</t>
+  </si>
+  <si>
+    <t>20142077</t>
+  </si>
+  <si>
+    <t>TEH LEMON MADU 350ML</t>
+  </si>
+  <si>
+    <t>20018904</t>
+  </si>
+  <si>
+    <t>NU GREEN TEA HNY 330</t>
+  </si>
+  <si>
+    <t>20053867</t>
+  </si>
+  <si>
+    <t>TEH GELAS BTL 350ML</t>
+  </si>
+  <si>
+    <t>20073396</t>
+  </si>
+  <si>
+    <t>S-TEE BTL 390ML</t>
+  </si>
+  <si>
+    <t>20072249</t>
+  </si>
+  <si>
+    <t>SOSRO TEH BOTOL 350</t>
+  </si>
+  <si>
+    <t>20122278</t>
+  </si>
+  <si>
+    <t>TEH BOTOL LS.SGR 350</t>
+  </si>
+  <si>
+    <t>20082395</t>
+  </si>
+  <si>
+    <t>TEH BOTOL TAWAR 350</t>
+  </si>
+  <si>
+    <t>RT,(E-3.5B)</t>
+  </si>
+  <si>
+    <t>20035484</t>
+  </si>
+  <si>
+    <t>PUCUK/H TEH MLATI350</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>20048155</t>
+  </si>
+  <si>
+    <t>PUCUK/H TEH L/SGR350</t>
+  </si>
+  <si>
+    <t>20037565</t>
+  </si>
+  <si>
+    <t>PUCUK/H TEH MLATI500</t>
+  </si>
+  <si>
+    <t>20048348</t>
+  </si>
+  <si>
+    <t>PUCUK/H TEH L/SGR500</t>
+  </si>
+  <si>
+    <t>20026226</t>
+  </si>
+  <si>
+    <t>ULTRA TEH KOTAK 500</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>10036640</t>
+  </si>
+  <si>
+    <t>TEH KOTAK JASMINE300</t>
+  </si>
+  <si>
+    <t>20048435</t>
+  </si>
+  <si>
+    <t>TEH KOTAK LESS/S 300</t>
+  </si>
+  <si>
+    <t>20044334</t>
+  </si>
+  <si>
+    <t>SOSRO TEH BTL TPK300</t>
+  </si>
+  <si>
+    <t>10005128</t>
+  </si>
+  <si>
+    <t>SOSRO TEH KOTAK B250</t>
+  </si>
+  <si>
+    <t>20024315</t>
+  </si>
+  <si>
+    <t>TEH BOTOL LS.SGR 250</t>
+  </si>
+  <si>
+    <t>20002209</t>
+  </si>
+  <si>
+    <t>TEBS SPRK MIX FRT330</t>
+  </si>
+  <si>
+    <t>20100142</t>
+  </si>
+  <si>
+    <t>TEH KOTAK BLCKCR 300</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>20100143</t>
+  </si>
+  <si>
+    <t>TEH KOTAK APPLE 300</t>
+  </si>
+  <si>
+    <t>20137159</t>
+  </si>
+  <si>
+    <t>TEH KOTAK MANGGA 300</t>
+  </si>
+  <si>
+    <t>20087016</t>
+  </si>
+  <si>
+    <t>TEH KOTAK LEMON 300</t>
+  </si>
+  <si>
+    <t>20135647</t>
+  </si>
+  <si>
+    <t>TEH KOTAK LYCHEE 300</t>
+  </si>
+  <si>
+    <t>20117687</t>
+  </si>
+  <si>
+    <t>DLMNT BOBA MTCHA 240</t>
+  </si>
+  <si>
+    <t>20117682</t>
+  </si>
+  <si>
+    <t>DLMNT BOBA RD.VEL240</t>
+  </si>
+  <si>
+    <t>20080088</t>
+  </si>
+  <si>
+    <t>POKKA GREEN TEA 450</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>20036765</t>
+  </si>
+  <si>
+    <t>FRESTEA GRN MADU 500</t>
+  </si>
+  <si>
+    <t>20012574</t>
+  </si>
+  <si>
+    <t>FRESTEA TEH APEL 500</t>
+  </si>
+  <si>
     <t>20035829</t>
   </si>
   <si>
     <t>TEBS TEA WT/SODA 500</t>
   </si>
   <si>
-    <t>20126464</t>
-  </si>
-  <si>
-    <t>IDM TEH APL&amp;LYCHE350</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>20101897</t>
-  </si>
-  <si>
-    <t>IDM TEH APEL 350ML</t>
-  </si>
-  <si>
-    <t>20132840</t>
-  </si>
-  <si>
-    <t>IDM TEH BLCKCRRNT350</t>
-  </si>
-  <si>
-    <t>20066454</t>
-  </si>
-  <si>
-    <t>FRUIT TEA BLCKCR 350</t>
-  </si>
-  <si>
-    <t>20073495</t>
-  </si>
-  <si>
-    <t>FRUIT TEA FREEZE 350</t>
-  </si>
-  <si>
-    <t>20066455</t>
-  </si>
-  <si>
-    <t>FRUIT TEA APPLE 350</t>
-  </si>
-  <si>
-    <t>20079972</t>
-  </si>
-  <si>
-    <t>FRUIT TEA MRKISA 350</t>
-  </si>
-  <si>
-    <t>20060207</t>
-  </si>
-  <si>
-    <t>I/OCHA TEH MLATI 350</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>20048934</t>
-  </si>
-  <si>
-    <t>I/OCHA GRN TEA 350ML</t>
-  </si>
-  <si>
-    <t>20142077</t>
-  </si>
-  <si>
-    <t>TEH LEMON MADU 350ML</t>
-  </si>
-  <si>
-    <t>20018904</t>
-  </si>
-  <si>
-    <t>NU GREEN TEA HNY 330</t>
-  </si>
-  <si>
-    <t>20053867</t>
-  </si>
-  <si>
-    <t>TEH GELAS BTL 350ML</t>
-  </si>
-  <si>
-    <t>20073396</t>
-  </si>
-  <si>
-    <t>S-TEE BTL 390ML</t>
-  </si>
-  <si>
-    <t>20072249</t>
-  </si>
-  <si>
-    <t>SOSRO TEH BOTOL 350</t>
-  </si>
-  <si>
-    <t>20122278</t>
-  </si>
-  <si>
-    <t>TEH BOTOL LS.SGR 350</t>
-  </si>
-  <si>
-    <t>20082395</t>
-  </si>
-  <si>
-    <t>TEH BOTOL TAWAR 350</t>
-  </si>
-  <si>
-    <t>RT,(E-3.5B)</t>
-  </si>
-  <si>
-    <t>20035484</t>
-  </si>
-  <si>
-    <t>PUCUK/H TEH MLATI350</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>20048155</t>
-  </si>
-  <si>
-    <t>PUCUK/H TEH L/SGR350</t>
-  </si>
-  <si>
-    <t>20037565</t>
-  </si>
-  <si>
-    <t>PUCUK/H TEH MLATI500</t>
-  </si>
-  <si>
-    <t>20048348</t>
-  </si>
-  <si>
-    <t>PUCUK/H TEH L/SGR500</t>
-  </si>
-  <si>
-    <t>20036157</t>
-  </si>
-  <si>
-    <t>SOSRO TEH BOTOL 450</t>
-  </si>
-  <si>
-    <t>20026226</t>
-  </si>
-  <si>
-    <t>ULTRA TEH KOTAK 500</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>10036640</t>
-  </si>
-  <si>
-    <t>TEH KOTAK JASMINE300</t>
-  </si>
-  <si>
-    <t>20048435</t>
-  </si>
-  <si>
-    <t>TEH KOTAK LESS/S 300</t>
-  </si>
-  <si>
-    <t>20044334</t>
-  </si>
-  <si>
-    <t>SOSRO TEH BTL TPK300</t>
-  </si>
-  <si>
-    <t>10005128</t>
-  </si>
-  <si>
-    <t>SOSRO TEH KOTAK B250</t>
-  </si>
-  <si>
-    <t>20024315</t>
-  </si>
-  <si>
-    <t>TEH BOTOL LS.SGR 250</t>
-  </si>
-  <si>
-    <t>20002209</t>
-  </si>
-  <si>
-    <t>TEBS SPRK MIX FRT330</t>
-  </si>
-  <si>
-    <t>20100142</t>
-  </si>
-  <si>
-    <t>TEH KOTAK BLCKCR 300</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>20100143</t>
-  </si>
-  <si>
-    <t>TEH KOTAK APPLE 300</t>
-  </si>
-  <si>
-    <t>20137159</t>
-  </si>
-  <si>
-    <t>TEH KOTAK MANGGA 300</t>
-  </si>
-  <si>
-    <t>20087016</t>
-  </si>
-  <si>
-    <t>TEH KOTAK LEMON 300</t>
-  </si>
-  <si>
-    <t>20135647</t>
-  </si>
-  <si>
-    <t>TEH KOTAK LYCHEE 300</t>
-  </si>
-  <si>
-    <t>20117687</t>
-  </si>
-  <si>
-    <t>DLMNT BOBA MTCHA 240</t>
-  </si>
-  <si>
-    <t>20117682</t>
-  </si>
-  <si>
-    <t>DLMNT BOBA RD.VEL240</t>
-  </si>
-  <si>
-    <t>20080088</t>
-  </si>
-  <si>
-    <t>POKKA GREEN TEA 450</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>20036765</t>
-  </si>
-  <si>
-    <t>FRESTEA GRN MADU 500</t>
-  </si>
-  <si>
-    <t>20012574</t>
-  </si>
-  <si>
-    <t>FRESTEA TEH APEL 500</t>
-  </si>
-  <si>
     <t>20138841</t>
   </si>
   <si>
@@ -1450,102 +1456,102 @@
     <t>29</t>
   </si>
   <si>
+    <t>20141600</t>
+  </si>
+  <si>
+    <t>IDM ISOTONC FRUIT350</t>
+  </si>
+  <si>
+    <t>20141601</t>
+  </si>
+  <si>
+    <t>IDM ISOTONC LYCHE350</t>
+  </si>
+  <si>
+    <t>20142358</t>
+  </si>
+  <si>
+    <t>POWRADE ACTIV WHT400</t>
+  </si>
+  <si>
+    <t>20142359</t>
+  </si>
+  <si>
+    <t>POWRADE ISOTN BLU400</t>
+  </si>
+  <si>
+    <t>20138837</t>
+  </si>
+  <si>
+    <t>MZONE COCO BOOST 500</t>
+  </si>
+  <si>
+    <t>20094167</t>
+  </si>
+  <si>
+    <t>MIZONE MOOD UP 500</t>
+  </si>
+  <si>
+    <t>20094164</t>
+  </si>
+  <si>
+    <t>MIZONE ACTIVE 500ML</t>
+  </si>
+  <si>
+    <t>20065248</t>
+  </si>
+  <si>
+    <t>ION WATER BTL 350ML</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>20118832</t>
+  </si>
+  <si>
+    <t>ION WATER BTL 500ML</t>
+  </si>
+  <si>
+    <t>20015838</t>
+  </si>
+  <si>
+    <t>POCARI SWEAT 350ML</t>
+  </si>
+  <si>
+    <t>20038777</t>
+  </si>
+  <si>
+    <t>POCARI SWEAT 900ML</t>
+  </si>
+  <si>
+    <t>20009722</t>
+  </si>
+  <si>
+    <t>POCARI SWEAT 500ML</t>
+  </si>
+  <si>
+    <t>20019674</t>
+  </si>
+  <si>
+    <t>YOU C1000 ORG WTR500</t>
+  </si>
+  <si>
+    <t>20019673</t>
+  </si>
+  <si>
+    <t>YOU C1000 LMN WTR500</t>
+  </si>
+  <si>
     <t>20138959</t>
   </si>
   <si>
     <t>IF COCONUT WTR 350ML</t>
   </si>
   <si>
-    <t>20142358</t>
-  </si>
-  <si>
-    <t>POWRADE ACTIV WHT400</t>
-  </si>
-  <si>
-    <t>20142359</t>
-  </si>
-  <si>
-    <t>POWRADE ISOTN BLU400</t>
-  </si>
-  <si>
-    <t>20138837</t>
-  </si>
-  <si>
-    <t>MZONE COCO BOOST 500</t>
-  </si>
-  <si>
-    <t>20094167</t>
-  </si>
-  <si>
-    <t>MIZONE MOOD UP 500</t>
-  </si>
-  <si>
-    <t>20094164</t>
-  </si>
-  <si>
-    <t>MIZONE ACTIVE 500ML</t>
-  </si>
-  <si>
-    <t>20038777</t>
-  </si>
-  <si>
-    <t>POCARI SWEAT 900ML</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>20009722</t>
-  </si>
-  <si>
-    <t>POCARI SWEAT 500ML</t>
-  </si>
-  <si>
-    <t>20118832</t>
-  </si>
-  <si>
-    <t>ION WATER BTL 500ML</t>
-  </si>
-  <si>
-    <t>20019674</t>
-  </si>
-  <si>
-    <t>YOU C1000 ORG WTR500</t>
-  </si>
-  <si>
-    <t>20019673</t>
-  </si>
-  <si>
-    <t>YOU C1000 LMN WTR500</t>
-  </si>
-  <si>
-    <t>20141600</t>
-  </si>
-  <si>
-    <t>IDM ISOTONC FRUIT350</t>
-  </si>
-  <si>
-    <t>20141601</t>
-  </si>
-  <si>
-    <t>IDM ISOTONC LYCHE350</t>
-  </si>
-  <si>
-    <t>20015838</t>
-  </si>
-  <si>
-    <t>POCARI SWEAT 350ML</t>
-  </si>
-  <si>
     <t>31</t>
   </si>
   <si>
-    <t>20065248</t>
-  </si>
-  <si>
-    <t>ION WATER BTL 350ML</t>
-  </si>
-  <si>
     <t>20057867</t>
   </si>
   <si>
@@ -1589,6 +1595,12 @@
   </si>
   <si>
     <t>FIBE MINI 100ML</t>
+  </si>
+  <si>
+    <t>20142467</t>
+  </si>
+  <si>
+    <t>FIT ME UP RLX 160</t>
   </si>
   <si>
     <t>20009737</t>
@@ -2698,7 +2710,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F353"/>
+  <dimension ref="A1:F355"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -3725,7 +3737,7 @@
         <v>4</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -3805,7 +3817,7 @@
         <v>17</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -3819,30 +3831,30 @@
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>126</v>
+        <v>41</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B57" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B57" s="1" t="s">
+      <c r="C57" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D57" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="C57" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>126</v>
-      </c>
       <c r="E57" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>23</v>
@@ -3859,10 +3871,10 @@
         <v>3</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>23</v>
@@ -3879,10 +3891,10 @@
         <v>3</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>23</v>
@@ -3899,10 +3911,10 @@
         <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>23</v>
@@ -3919,10 +3931,10 @@
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>23</v>
@@ -3939,10 +3951,10 @@
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>23</v>
@@ -3959,10 +3971,10 @@
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>23</v>
@@ -3979,10 +3991,10 @@
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>126</v>
+        <v>41</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>23</v>
@@ -3999,10 +4011,10 @@
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>23</v>
@@ -4010,22 +4022,22 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B66" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="B66" s="1" t="s">
+      <c r="C66" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E66" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="C66" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="E66" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F66" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -4039,10 +4051,10 @@
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>31</v>
@@ -4059,10 +4071,10 @@
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>31</v>
@@ -4079,10 +4091,10 @@
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>31</v>
@@ -4099,10 +4111,10 @@
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>31</v>
@@ -4119,13 +4131,13 @@
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -4139,13 +4151,13 @@
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -4159,10 +4171,10 @@
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>23</v>
@@ -4179,53 +4191,53 @@
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>164</v>
+        <v>147</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>165</v>
+        <v>23</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>164</v>
+        <v>147</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>8</v>
+        <v>128</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>165</v>
+        <v>23</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D76" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="B76" s="1" t="s">
+      <c r="E76" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F76" s="1" t="s">
         <v>169</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="E76" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F76" s="1" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -4239,13 +4251,13 @@
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>23</v>
+        <v>169</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -4259,13 +4271,13 @@
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>31</v>
+        <v>169</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -4279,10 +4291,10 @@
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>23</v>
@@ -4299,13 +4311,13 @@
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -4319,30 +4331,30 @@
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B82" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="B82" s="1" t="s">
+      <c r="C82" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D82" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="C82" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>180</v>
-      </c>
       <c r="E82" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>31</v>
@@ -4359,10 +4371,10 @@
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>31</v>
@@ -4379,13 +4391,13 @@
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -4399,13 +4411,13 @@
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -4419,10 +4431,10 @@
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>31</v>
@@ -4439,10 +4451,10 @@
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>31</v>
@@ -4459,10 +4471,10 @@
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>31</v>
@@ -4479,13 +4491,13 @@
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>126</v>
+        <v>41</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -4499,10 +4511,10 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>23</v>
@@ -4519,30 +4531,30 @@
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>201</v>
+        <v>182</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>4</v>
+        <v>147</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B92" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="B92" s="1" t="s">
+      <c r="C92" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D92" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="C92" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>201</v>
-      </c>
       <c r="E92" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>28</v>
@@ -4559,13 +4571,13 @@
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>76</v>
+        <v>28</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
@@ -4579,13 +4591,13 @@
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>23</v>
+        <v>76</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -4599,10 +4611,10 @@
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>23</v>
@@ -4619,13 +4631,13 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -4639,13 +4651,13 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -4659,10 +4671,10 @@
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>23</v>
@@ -4679,10 +4691,10 @@
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>218</v>
+        <v>203</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>23</v>
@@ -4690,19 +4702,19 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B100" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="B100" s="1" t="s">
+      <c r="C100" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D100" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="C100" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>218</v>
-      </c>
       <c r="E100" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>23</v>
@@ -4719,10 +4731,10 @@
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>23</v>
@@ -4739,10 +4751,10 @@
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>23</v>
@@ -4759,10 +4771,10 @@
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>23</v>
@@ -4779,10 +4791,10 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>23</v>
@@ -4799,10 +4811,10 @@
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>23</v>
@@ -4819,10 +4831,10 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>23</v>
@@ -4839,33 +4851,33 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>235</v>
+        <v>220</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>165</v>
+        <v>23</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B108" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="B108" s="1" t="s">
+      <c r="C108" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D108" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="C108" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D108" s="1" t="s">
-        <v>235</v>
-      </c>
       <c r="E108" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -4879,13 +4891,13 @@
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -4899,13 +4911,13 @@
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>23</v>
+        <v>169</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -4919,10 +4931,10 @@
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>23</v>
@@ -4939,10 +4951,10 @@
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>23</v>
@@ -4959,10 +4971,10 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>126</v>
+        <v>41</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>23</v>
@@ -4979,10 +4991,10 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>250</v>
+        <v>237</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>4</v>
+        <v>128</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>23</v>
@@ -4990,19 +5002,19 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B115" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="B115" s="1" t="s">
+      <c r="C115" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D115" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="C115" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D115" s="1" t="s">
-        <v>250</v>
-      </c>
       <c r="E115" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>23</v>
@@ -5019,10 +5031,10 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>23</v>
@@ -5039,10 +5051,10 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>23</v>
@@ -5059,10 +5071,10 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>23</v>
@@ -5079,10 +5091,10 @@
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>23</v>
@@ -5099,10 +5111,10 @@
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>23</v>
@@ -5119,10 +5131,10 @@
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>23</v>
@@ -5139,50 +5151,50 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>126</v>
+        <v>41</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>267</v>
+        <v>23</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="B123" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="B123" s="1" t="s">
+      <c r="C123" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="E123" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F123" s="1" t="s">
         <v>269</v>
-      </c>
-      <c r="C123" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D123" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="E123" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F123" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="B124" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="B124" s="1" t="s">
+      <c r="C124" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D124" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="C124" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D124" s="1" t="s">
-        <v>270</v>
-      </c>
       <c r="E124" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>23</v>
@@ -5199,10 +5211,10 @@
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>23</v>
@@ -5219,10 +5231,10 @@
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>23</v>
@@ -5239,10 +5251,10 @@
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>23</v>
@@ -5562,7 +5574,7 @@
         <v>311</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>5</v>
@@ -5582,7 +5594,7 @@
         <v>311</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>5</v>
@@ -5602,7 +5614,7 @@
         <v>311</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>23</v>
@@ -5622,10 +5634,10 @@
         <v>311</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
@@ -5642,7 +5654,7 @@
         <v>311</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>5</v>
@@ -5659,30 +5671,30 @@
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>324</v>
+        <v>311</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="B149" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="B149" s="1" t="s">
+      <c r="C149" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D149" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="C149" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D149" s="1" t="s">
-        <v>324</v>
-      </c>
       <c r="E149" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>23</v>
@@ -5699,10 +5711,10 @@
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>23</v>
@@ -5719,10 +5731,10 @@
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>23</v>
@@ -5739,13 +5751,13 @@
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
@@ -5759,13 +5771,13 @@
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
@@ -5779,10 +5791,10 @@
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>23</v>
@@ -5799,13 +5811,13 @@
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
@@ -5819,10 +5831,10 @@
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>126</v>
+        <v>41</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>31</v>
@@ -5839,30 +5851,30 @@
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>343</v>
+        <v>326</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>4</v>
+        <v>128</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="B158" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="B158" s="1" t="s">
+      <c r="C158" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D158" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="C158" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D158" s="1" t="s">
-        <v>343</v>
-      </c>
       <c r="E158" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>23</v>
@@ -5879,13 +5891,13 @@
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
@@ -5899,13 +5911,13 @@
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
@@ -5919,10 +5931,10 @@
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>23</v>
@@ -5939,10 +5951,10 @@
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>23</v>
@@ -5959,10 +5971,10 @@
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F163" s="1" t="s">
         <v>23</v>
@@ -5979,10 +5991,10 @@
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>23</v>
@@ -5999,10 +6011,10 @@
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>126</v>
+        <v>41</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>23</v>
@@ -6019,10 +6031,10 @@
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>362</v>
+        <v>345</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>4</v>
+        <v>128</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>23</v>
@@ -6030,19 +6042,19 @@
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B167" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="B167" s="1" t="s">
+      <c r="C167" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D167" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="C167" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D167" s="1" t="s">
-        <v>362</v>
-      </c>
       <c r="E167" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>23</v>
@@ -6059,10 +6071,10 @@
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>23</v>
@@ -6079,10 +6091,10 @@
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>23</v>
@@ -6099,10 +6111,10 @@
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F170" s="1" t="s">
         <v>23</v>
@@ -6119,10 +6131,10 @@
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>23</v>
@@ -6139,10 +6151,10 @@
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>23</v>
@@ -6159,13 +6171,13 @@
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
@@ -6179,10 +6191,10 @@
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>126</v>
+        <v>41</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>5</v>
@@ -6199,33 +6211,33 @@
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>381</v>
+        <v>364</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>4</v>
+        <v>128</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="B176" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="B176" s="1" t="s">
+      <c r="C176" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D176" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="C176" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D176" s="1" t="s">
-        <v>381</v>
-      </c>
       <c r="E176" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
@@ -6239,10 +6251,10 @@
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F177" s="1" t="s">
         <v>23</v>
@@ -6259,13 +6271,13 @@
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>103</v>
+        <v>23</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
@@ -6279,10 +6291,10 @@
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>103</v>
@@ -6299,13 +6311,13 @@
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>23</v>
+        <v>103</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
@@ -6319,13 +6331,13 @@
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
@@ -6339,10 +6351,10 @@
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>28</v>
@@ -6359,13 +6371,13 @@
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>126</v>
+        <v>41</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
@@ -6379,10 +6391,10 @@
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="F184" s="1" t="s">
         <v>23</v>
@@ -6399,10 +6411,10 @@
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>402</v>
+        <v>383</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>4</v>
+        <v>147</v>
       </c>
       <c r="F185" s="1" t="s">
         <v>23</v>
@@ -6410,22 +6422,22 @@
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="B186" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="B186" s="1" t="s">
+      <c r="C186" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D186" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="C186" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D186" s="1" t="s">
-        <v>402</v>
-      </c>
       <c r="E186" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
@@ -6439,13 +6451,13 @@
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
@@ -6459,13 +6471,13 @@
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>76</v>
+        <v>28</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
@@ -6479,13 +6491,13 @@
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>23</v>
+        <v>76</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
@@ -6499,13 +6511,13 @@
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
@@ -6519,10 +6531,10 @@
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F191" s="1" t="s">
         <v>31</v>
@@ -6539,13 +6551,13 @@
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
@@ -6559,10 +6571,10 @@
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>126</v>
+        <v>41</v>
       </c>
       <c r="F193" s="1" t="s">
         <v>23</v>
@@ -6579,10 +6591,10 @@
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>421</v>
+        <v>404</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>4</v>
+        <v>128</v>
       </c>
       <c r="F194" s="1" t="s">
         <v>23</v>
@@ -6590,19 +6602,19 @@
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="B195" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="B195" s="1" t="s">
+      <c r="C195" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D195" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="C195" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D195" s="1" t="s">
-        <v>421</v>
-      </c>
       <c r="E195" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>23</v>
@@ -6619,10 +6631,10 @@
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F196" s="1" t="s">
         <v>23</v>
@@ -6639,10 +6651,10 @@
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F197" s="1" t="s">
         <v>23</v>
@@ -6659,10 +6671,10 @@
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F198" s="1" t="s">
         <v>23</v>
@@ -6679,13 +6691,13 @@
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F199" s="1" t="s">
-        <v>165</v>
+        <v>23</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
@@ -6699,13 +6711,13 @@
         <v>3</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
@@ -6719,13 +6731,13 @@
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>23</v>
+        <v>169</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
@@ -6739,10 +6751,10 @@
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>145</v>
+        <v>41</v>
       </c>
       <c r="F202" s="1" t="s">
         <v>23</v>
@@ -6759,33 +6771,33 @@
         <v>3</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>440</v>
+        <v>423</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>4</v>
+        <v>147</v>
       </c>
       <c r="F203" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="B204" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="B204" s="1" t="s">
+      <c r="C204" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D204" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="C204" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D204" s="1" t="s">
-        <v>440</v>
-      </c>
       <c r="E204" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F204" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
@@ -6799,13 +6811,13 @@
         <v>3</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F205" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
@@ -6819,13 +6831,13 @@
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F206" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
@@ -6839,13 +6851,13 @@
         <v>3</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F207" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
@@ -6859,10 +6871,10 @@
         <v>3</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F208" s="1" t="s">
         <v>23</v>
@@ -6879,10 +6891,10 @@
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F209" s="1" t="s">
         <v>23</v>
@@ -6899,10 +6911,10 @@
         <v>3</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>126</v>
+        <v>41</v>
       </c>
       <c r="F210" s="1" t="s">
         <v>23</v>
@@ -6919,10 +6931,10 @@
         <v>3</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>457</v>
+        <v>442</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>4</v>
+        <v>128</v>
       </c>
       <c r="F211" s="1" t="s">
         <v>23</v>
@@ -6930,19 +6942,19 @@
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="B212" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="B212" s="1" t="s">
+      <c r="C212" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D212" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="C212" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D212" s="1" t="s">
-        <v>457</v>
-      </c>
       <c r="E212" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F212" s="1" t="s">
         <v>23</v>
@@ -6959,13 +6971,13 @@
         <v>3</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
@@ -6979,13 +6991,13 @@
         <v>3</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F214" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
@@ -6999,10 +7011,10 @@
         <v>3</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F215" s="1" t="s">
         <v>23</v>
@@ -7019,10 +7031,10 @@
         <v>3</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F216" s="1" t="s">
         <v>23</v>
@@ -7039,10 +7051,10 @@
         <v>3</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F217" s="1" t="s">
         <v>23</v>
@@ -7059,10 +7071,10 @@
         <v>3</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F218" s="1" t="s">
         <v>23</v>
@@ -7079,13 +7091,13 @@
         <v>3</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>126</v>
+        <v>41</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
@@ -7099,13 +7111,13 @@
         <v>3</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
@@ -7119,10 +7131,10 @@
         <v>3</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>478</v>
+        <v>459</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>4</v>
+        <v>147</v>
       </c>
       <c r="F221" s="1" t="s">
         <v>23</v>
@@ -7130,19 +7142,19 @@
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="B222" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="B222" s="1" t="s">
+      <c r="C222" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D222" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="C222" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D222" s="1" t="s">
-        <v>478</v>
-      </c>
       <c r="E222" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F222" s="1" t="s">
         <v>23</v>
@@ -7159,13 +7171,13 @@
         <v>3</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F223" s="1" t="s">
-        <v>23</v>
+        <v>169</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
@@ -7179,13 +7191,13 @@
         <v>3</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>23</v>
+        <v>169</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
@@ -7199,10 +7211,10 @@
         <v>3</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F225" s="1" t="s">
         <v>23</v>
@@ -7219,13 +7231,13 @@
         <v>3</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
@@ -7239,13 +7251,13 @@
         <v>3</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
@@ -7259,10 +7271,10 @@
         <v>3</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>493</v>
+        <v>480</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F228" s="1" t="s">
         <v>31</v>
@@ -7270,19 +7282,19 @@
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="B229" s="1" t="s">
         <v>494</v>
       </c>
-      <c r="B229" s="1" t="s">
-        <v>495</v>
-      </c>
       <c r="C229" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>493</v>
+        <v>480</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="F229" s="1" t="s">
         <v>31</v>
@@ -7290,19 +7302,19 @@
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="B230" s="1" t="s">
         <v>496</v>
       </c>
-      <c r="B230" s="1" t="s">
+      <c r="C230" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D230" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="C230" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D230" s="1" t="s">
-        <v>493</v>
-      </c>
       <c r="E230" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F230" s="1" t="s">
         <v>31</v>
@@ -7319,13 +7331,13 @@
         <v>3</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F231" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
@@ -7339,13 +7351,13 @@
         <v>3</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F232" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
@@ -7359,13 +7371,13 @@
         <v>3</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F233" s="1" t="s">
-        <v>165</v>
+        <v>31</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
@@ -7379,13 +7391,13 @@
         <v>3</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F234" s="1" t="s">
-        <v>165</v>
+        <v>31</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
@@ -7399,53 +7411,53 @@
         <v>3</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>508</v>
+        <v>497</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F235" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="B236" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="B236" s="1" t="s">
-        <v>510</v>
-      </c>
       <c r="C236" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>508</v>
+        <v>497</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="F236" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="B237" s="1" t="s">
         <v>511</v>
       </c>
-      <c r="B237" s="1" t="s">
+      <c r="C237" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D237" s="1" t="s">
         <v>512</v>
       </c>
-      <c r="C237" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D237" s="1" t="s">
-        <v>508</v>
-      </c>
       <c r="E237" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F237" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
@@ -7459,10 +7471,10 @@
         <v>3</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="E238" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F238" s="1" t="s">
         <v>31</v>
@@ -7479,10 +7491,10 @@
         <v>3</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="E239" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F239" s="1" t="s">
         <v>31</v>
@@ -7499,13 +7511,13 @@
         <v>3</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="E240" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F240" s="1" t="s">
-        <v>165</v>
+        <v>31</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
@@ -7519,13 +7531,13 @@
         <v>3</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="E241" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F241" s="1" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
@@ -7539,33 +7551,33 @@
         <v>3</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="E242" s="1" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="F242" s="1" t="s">
-        <v>523</v>
+        <v>169</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="B243" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="B243" s="1" t="s">
+      <c r="C243" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D243" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="E243" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F243" s="1" t="s">
         <v>525</v>
-      </c>
-      <c r="C243" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D243" s="1" t="s">
-        <v>508</v>
-      </c>
-      <c r="E243" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="F243" s="1" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
@@ -7579,30 +7591,30 @@
         <v>3</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>528</v>
+        <v>512</v>
       </c>
       <c r="E244" s="1" t="s">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="F244" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="B245" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="B245" s="1" t="s">
-        <v>530</v>
-      </c>
       <c r="C245" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>528</v>
+        <v>512</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>8</v>
+        <v>128</v>
       </c>
       <c r="F245" s="1" t="s">
         <v>23</v>
@@ -7610,19 +7622,19 @@
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="B246" s="1" t="s">
         <v>531</v>
       </c>
-      <c r="B246" s="1" t="s">
+      <c r="C246" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D246" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="C246" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D246" s="1" t="s">
-        <v>528</v>
-      </c>
       <c r="E246" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F246" s="1" t="s">
         <v>23</v>
@@ -7639,10 +7651,10 @@
         <v>3</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F247" s="1" t="s">
         <v>23</v>
@@ -7659,13 +7671,13 @@
         <v>3</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F248" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
@@ -7679,13 +7691,13 @@
         <v>3</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F249" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
@@ -7699,13 +7711,13 @@
         <v>3</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="E250" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F250" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
@@ -7719,10 +7731,10 @@
         <v>3</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="F251" s="1" t="s">
         <v>31</v>
@@ -7739,50 +7751,50 @@
         <v>3</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>545</v>
+        <v>532</v>
       </c>
       <c r="E252" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F252" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="B253" s="1" t="s">
         <v>546</v>
       </c>
-      <c r="B253" s="1" t="s">
-        <v>547</v>
-      </c>
       <c r="C253" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>545</v>
+        <v>532</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="F253" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="B254" s="1" t="s">
         <v>548</v>
       </c>
-      <c r="B254" s="1" t="s">
+      <c r="C254" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D254" s="1" t="s">
         <v>549</v>
       </c>
-      <c r="C254" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D254" s="1" t="s">
-        <v>545</v>
-      </c>
       <c r="E254" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F254" s="1" t="s">
         <v>23</v>
@@ -7799,10 +7811,10 @@
         <v>3</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F255" s="1" t="s">
         <v>23</v>
@@ -7819,13 +7831,13 @@
         <v>3</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="E256" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F256" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
@@ -7839,10 +7851,10 @@
         <v>3</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="E257" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F257" s="1" t="s">
         <v>23</v>
@@ -7859,13 +7871,13 @@
         <v>3</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F258" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
@@ -7879,10 +7891,10 @@
         <v>3</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="F259" s="1" t="s">
         <v>23</v>
@@ -7899,33 +7911,33 @@
         <v>3</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>562</v>
+        <v>549</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F260" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="B261" s="1" t="s">
         <v>563</v>
       </c>
-      <c r="B261" s="1" t="s">
-        <v>561</v>
-      </c>
       <c r="C261" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>562</v>
+        <v>549</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="F261" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
@@ -7939,33 +7951,33 @@
         <v>3</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F262" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="B263" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="C263" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D263" s="1" t="s">
         <v>566</v>
       </c>
-      <c r="B263" s="1" t="s">
-        <v>567</v>
-      </c>
-      <c r="C263" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D263" s="1" t="s">
-        <v>562</v>
-      </c>
       <c r="E263" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F263" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
@@ -7979,10 +7991,10 @@
         <v>3</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="E264" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F264" s="1" t="s">
         <v>23</v>
@@ -7999,10 +8011,10 @@
         <v>3</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="E265" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F265" s="1" t="s">
         <v>23</v>
@@ -8019,10 +8031,10 @@
         <v>3</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F266" s="1" t="s">
         <v>23</v>
@@ -8039,10 +8051,10 @@
         <v>3</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="E267" s="1" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="F267" s="1" t="s">
         <v>23</v>
@@ -8059,10 +8071,10 @@
         <v>3</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>126</v>
+        <v>38</v>
       </c>
       <c r="F268" s="1" t="s">
         <v>23</v>
@@ -8079,10 +8091,10 @@
         <v>3</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>580</v>
+        <v>566</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="F269" s="1" t="s">
         <v>23</v>
@@ -8090,19 +8102,19 @@
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="B270" s="1" t="s">
         <v>581</v>
       </c>
-      <c r="B270" s="1" t="s">
-        <v>582</v>
-      </c>
       <c r="C270" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>580</v>
+        <v>566</v>
       </c>
       <c r="E270" s="1" t="s">
-        <v>8</v>
+        <v>128</v>
       </c>
       <c r="F270" s="1" t="s">
         <v>23</v>
@@ -8110,19 +8122,19 @@
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="B271" s="1" t="s">
         <v>583</v>
       </c>
-      <c r="B271" s="1" t="s">
+      <c r="C271" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D271" s="1" t="s">
         <v>584</v>
       </c>
-      <c r="C271" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D271" s="1" t="s">
-        <v>580</v>
-      </c>
       <c r="E271" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F271" s="1" t="s">
         <v>23</v>
@@ -8139,10 +8151,10 @@
         <v>3</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="E272" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F272" s="1" t="s">
         <v>23</v>
@@ -8159,10 +8171,10 @@
         <v>3</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F273" s="1" t="s">
         <v>23</v>
@@ -8179,10 +8191,10 @@
         <v>3</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F274" s="1" t="s">
         <v>23</v>
@@ -8199,10 +8211,10 @@
         <v>3</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="E275" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F275" s="1" t="s">
         <v>23</v>
@@ -8219,10 +8231,10 @@
         <v>3</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="E276" s="1" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="F276" s="1" t="s">
         <v>23</v>
@@ -8239,10 +8251,10 @@
         <v>3</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="E277" s="1" t="s">
-        <v>126</v>
+        <v>38</v>
       </c>
       <c r="F277" s="1" t="s">
         <v>23</v>
@@ -8259,10 +8271,10 @@
         <v>3</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>145</v>
+        <v>41</v>
       </c>
       <c r="F278" s="1" t="s">
         <v>23</v>
@@ -8279,10 +8291,10 @@
         <v>3</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="E279" s="1" t="s">
-        <v>164</v>
+        <v>128</v>
       </c>
       <c r="F279" s="1" t="s">
         <v>23</v>
@@ -8299,10 +8311,10 @@
         <v>3</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>603</v>
+        <v>584</v>
       </c>
       <c r="E280" s="1" t="s">
-        <v>4</v>
+        <v>147</v>
       </c>
       <c r="F280" s="1" t="s">
         <v>23</v>
@@ -8310,19 +8322,19 @@
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="B281" s="1" t="s">
         <v>604</v>
       </c>
-      <c r="B281" s="1" t="s">
-        <v>605</v>
-      </c>
       <c r="C281" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>603</v>
+        <v>584</v>
       </c>
       <c r="E281" s="1" t="s">
-        <v>8</v>
+        <v>168</v>
       </c>
       <c r="F281" s="1" t="s">
         <v>23</v>
@@ -8330,19 +8342,19 @@
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="B282" s="1" t="s">
         <v>606</v>
       </c>
-      <c r="B282" s="1" t="s">
+      <c r="C282" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D282" s="1" t="s">
         <v>607</v>
       </c>
-      <c r="C282" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D282" s="1" t="s">
-        <v>603</v>
-      </c>
       <c r="E282" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F282" s="1" t="s">
         <v>23</v>
@@ -8359,10 +8371,10 @@
         <v>3</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="E283" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F283" s="1" t="s">
         <v>23</v>
@@ -8379,10 +8391,10 @@
         <v>3</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F284" s="1" t="s">
         <v>23</v>
@@ -8399,10 +8411,10 @@
         <v>3</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="E285" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F285" s="1" t="s">
         <v>23</v>
@@ -8419,30 +8431,30 @@
         <v>3</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F286" s="1" t="s">
-        <v>616</v>
+        <v>23</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A287" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="B287" s="1" t="s">
         <v>617</v>
       </c>
-      <c r="B287" s="1" t="s">
-        <v>618</v>
-      </c>
       <c r="C287" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="F287" s="1" t="s">
         <v>23</v>
@@ -8450,22 +8462,22 @@
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="B288" s="1" t="s">
         <v>619</v>
       </c>
-      <c r="B288" s="1" t="s">
+      <c r="C288" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D288" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="E288" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F288" s="1" t="s">
         <v>620</v>
-      </c>
-      <c r="C288" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D288" s="1" t="s">
-        <v>603</v>
-      </c>
-      <c r="E288" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="F288" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
@@ -8479,10 +8491,10 @@
         <v>3</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="E289" s="1" t="s">
-        <v>145</v>
+        <v>41</v>
       </c>
       <c r="F289" s="1" t="s">
         <v>23</v>
@@ -8499,53 +8511,53 @@
         <v>3</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>625</v>
+        <v>607</v>
       </c>
       <c r="E290" s="1" t="s">
-        <v>4</v>
+        <v>128</v>
       </c>
       <c r="F290" s="1" t="s">
-        <v>616</v>
+        <v>23</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A291" s="1" t="s">
+        <v>625</v>
+      </c>
+      <c r="B291" s="1" t="s">
         <v>626</v>
       </c>
-      <c r="B291" s="1" t="s">
-        <v>627</v>
-      </c>
       <c r="C291" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>625</v>
+        <v>607</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>8</v>
+        <v>147</v>
       </c>
       <c r="F291" s="1" t="s">
-        <v>616</v>
+        <v>23</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A292" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="B292" s="1" t="s">
         <v>628</v>
       </c>
-      <c r="B292" s="1" t="s">
+      <c r="C292" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D292" s="1" t="s">
         <v>629</v>
       </c>
-      <c r="C292" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D292" s="1" t="s">
-        <v>625</v>
-      </c>
       <c r="E292" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F292" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
@@ -8559,13 +8571,13 @@
         <v>3</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="E293" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F293" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
@@ -8579,13 +8591,13 @@
         <v>3</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="E294" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F294" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
@@ -8599,13 +8611,13 @@
         <v>3</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="E295" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F295" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
@@ -8619,13 +8631,13 @@
         <v>3</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="E296" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F296" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
@@ -8639,13 +8651,13 @@
         <v>3</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="F297" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
@@ -8659,13 +8671,13 @@
         <v>3</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>126</v>
+        <v>38</v>
       </c>
       <c r="F298" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
@@ -8679,50 +8691,50 @@
         <v>3</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>644</v>
+        <v>629</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="F299" s="1" t="s">
-        <v>23</v>
+        <v>620</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A300" s="1" t="s">
+        <v>644</v>
+      </c>
+      <c r="B300" s="1" t="s">
         <v>645</v>
       </c>
-      <c r="B300" s="1" t="s">
-        <v>646</v>
-      </c>
       <c r="C300" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>644</v>
+        <v>629</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>8</v>
+        <v>128</v>
       </c>
       <c r="F300" s="1" t="s">
-        <v>23</v>
+        <v>620</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A301" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="B301" s="1" t="s">
         <v>647</v>
       </c>
-      <c r="B301" s="1" t="s">
+      <c r="C301" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D301" s="1" t="s">
         <v>648</v>
       </c>
-      <c r="C301" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D301" s="1" t="s">
-        <v>644</v>
-      </c>
       <c r="E301" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F301" s="1" t="s">
         <v>23</v>
@@ -8739,10 +8751,10 @@
         <v>3</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="E302" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F302" s="1" t="s">
         <v>23</v>
@@ -8759,10 +8771,10 @@
         <v>3</v>
       </c>
       <c r="D303" s="1" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="E303" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F303" s="1" t="s">
         <v>23</v>
@@ -8779,10 +8791,10 @@
         <v>3</v>
       </c>
       <c r="D304" s="1" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="E304" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F304" s="1" t="s">
         <v>23</v>
@@ -8799,10 +8811,10 @@
         <v>3</v>
       </c>
       <c r="D305" s="1" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="E305" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F305" s="1" t="s">
         <v>23</v>
@@ -8819,10 +8831,10 @@
         <v>3</v>
       </c>
       <c r="D306" s="1" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="E306" s="1" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="F306" s="1" t="s">
         <v>23</v>
@@ -8839,10 +8851,10 @@
         <v>3</v>
       </c>
       <c r="D307" s="1" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="E307" s="1" t="s">
-        <v>126</v>
+        <v>38</v>
       </c>
       <c r="F307" s="1" t="s">
         <v>23</v>
@@ -8859,10 +8871,10 @@
         <v>3</v>
       </c>
       <c r="D308" s="1" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="E308" s="1" t="s">
-        <v>145</v>
+        <v>41</v>
       </c>
       <c r="F308" s="1" t="s">
         <v>23</v>
@@ -8879,10 +8891,10 @@
         <v>3</v>
       </c>
       <c r="D309" s="1" t="s">
-        <v>665</v>
+        <v>648</v>
       </c>
       <c r="E309" s="1" t="s">
-        <v>4</v>
+        <v>128</v>
       </c>
       <c r="F309" s="1" t="s">
         <v>23</v>
@@ -8890,19 +8902,19 @@
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A310" s="1" t="s">
+        <v>665</v>
+      </c>
+      <c r="B310" s="1" t="s">
         <v>666</v>
       </c>
-      <c r="B310" s="1" t="s">
-        <v>667</v>
-      </c>
       <c r="C310" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D310" s="1" t="s">
-        <v>665</v>
+        <v>648</v>
       </c>
       <c r="E310" s="1" t="s">
-        <v>8</v>
+        <v>147</v>
       </c>
       <c r="F310" s="1" t="s">
         <v>23</v>
@@ -8910,19 +8922,19 @@
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A311" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="B311" s="1" t="s">
         <v>668</v>
       </c>
-      <c r="B311" s="1" t="s">
+      <c r="C311" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D311" s="1" t="s">
         <v>669</v>
       </c>
-      <c r="C311" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D311" s="1" t="s">
-        <v>665</v>
-      </c>
       <c r="E311" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F311" s="1" t="s">
         <v>23</v>
@@ -8939,10 +8951,10 @@
         <v>3</v>
       </c>
       <c r="D312" s="1" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="E312" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F312" s="1" t="s">
         <v>23</v>
@@ -8959,10 +8971,10 @@
         <v>3</v>
       </c>
       <c r="D313" s="1" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="E313" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F313" s="1" t="s">
         <v>23</v>
@@ -8979,10 +8991,10 @@
         <v>3</v>
       </c>
       <c r="D314" s="1" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="E314" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F314" s="1" t="s">
         <v>23</v>
@@ -8999,10 +9011,10 @@
         <v>3</v>
       </c>
       <c r="D315" s="1" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="E315" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F315" s="1" t="s">
         <v>23</v>
@@ -9019,10 +9031,10 @@
         <v>3</v>
       </c>
       <c r="D316" s="1" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="E316" s="1" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="F316" s="1" t="s">
         <v>23</v>
@@ -9039,10 +9051,10 @@
         <v>3</v>
       </c>
       <c r="D317" s="1" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="E317" s="1" t="s">
-        <v>126</v>
+        <v>38</v>
       </c>
       <c r="F317" s="1" t="s">
         <v>23</v>
@@ -9059,10 +9071,10 @@
         <v>3</v>
       </c>
       <c r="D318" s="1" t="s">
-        <v>684</v>
+        <v>669</v>
       </c>
       <c r="E318" s="1" t="s">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="F318" s="1" t="s">
         <v>23</v>
@@ -9070,19 +9082,19 @@
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A319" s="1" t="s">
+        <v>684</v>
+      </c>
+      <c r="B319" s="1" t="s">
         <v>685</v>
       </c>
-      <c r="B319" s="1" t="s">
-        <v>686</v>
-      </c>
       <c r="C319" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D319" s="1" t="s">
-        <v>684</v>
+        <v>669</v>
       </c>
       <c r="E319" s="1" t="s">
-        <v>8</v>
+        <v>128</v>
       </c>
       <c r="F319" s="1" t="s">
         <v>23</v>
@@ -9090,19 +9102,19 @@
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A320" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="B320" s="1" t="s">
         <v>687</v>
       </c>
-      <c r="B320" s="1" t="s">
+      <c r="C320" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D320" s="1" t="s">
         <v>688</v>
       </c>
-      <c r="C320" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D320" s="1" t="s">
-        <v>684</v>
-      </c>
       <c r="E320" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F320" s="1" t="s">
         <v>23</v>
@@ -9119,10 +9131,10 @@
         <v>3</v>
       </c>
       <c r="D321" s="1" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="E321" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F321" s="1" t="s">
         <v>23</v>
@@ -9139,10 +9151,10 @@
         <v>3</v>
       </c>
       <c r="D322" s="1" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="E322" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F322" s="1" t="s">
         <v>23</v>
@@ -9159,10 +9171,10 @@
         <v>3</v>
       </c>
       <c r="D323" s="1" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="E323" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F323" s="1" t="s">
         <v>23</v>
@@ -9179,10 +9191,10 @@
         <v>3</v>
       </c>
       <c r="D324" s="1" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="E324" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F324" s="1" t="s">
         <v>23</v>
@@ -9199,10 +9211,10 @@
         <v>3</v>
       </c>
       <c r="D325" s="1" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="E325" s="1" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="F325" s="1" t="s">
         <v>23</v>
@@ -9219,10 +9231,10 @@
         <v>3</v>
       </c>
       <c r="D326" s="1" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="E326" s="1" t="s">
-        <v>126</v>
+        <v>38</v>
       </c>
       <c r="F326" s="1" t="s">
         <v>23</v>
@@ -9239,10 +9251,10 @@
         <v>3</v>
       </c>
       <c r="D327" s="1" t="s">
-        <v>703</v>
+        <v>688</v>
       </c>
       <c r="E327" s="1" t="s">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="F327" s="1" t="s">
         <v>23</v>
@@ -9250,19 +9262,19 @@
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A328" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="B328" s="1" t="s">
         <v>704</v>
       </c>
-      <c r="B328" s="1" t="s">
-        <v>705</v>
-      </c>
       <c r="C328" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D328" s="1" t="s">
-        <v>703</v>
+        <v>688</v>
       </c>
       <c r="E328" s="1" t="s">
-        <v>8</v>
+        <v>128</v>
       </c>
       <c r="F328" s="1" t="s">
         <v>23</v>
@@ -9270,22 +9282,22 @@
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A329" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="B329" s="1" t="s">
         <v>706</v>
       </c>
-      <c r="B329" s="1" t="s">
+      <c r="C329" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D329" s="1" t="s">
         <v>707</v>
       </c>
-      <c r="C329" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D329" s="1" t="s">
-        <v>703</v>
-      </c>
       <c r="E329" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F329" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.25">
@@ -9299,13 +9311,13 @@
         <v>3</v>
       </c>
       <c r="D330" s="1" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="E330" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F330" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.25">
@@ -9319,13 +9331,13 @@
         <v>3</v>
       </c>
       <c r="D331" s="1" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="E331" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F331" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.25">
@@ -9339,13 +9351,13 @@
         <v>3</v>
       </c>
       <c r="D332" s="1" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="E332" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F332" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.25">
@@ -9359,10 +9371,10 @@
         <v>3</v>
       </c>
       <c r="D333" s="1" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="E333" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F333" s="1" t="s">
         <v>23</v>
@@ -9379,10 +9391,10 @@
         <v>3</v>
       </c>
       <c r="D334" s="1" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="E334" s="1" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="F334" s="1" t="s">
         <v>23</v>
@@ -9399,10 +9411,10 @@
         <v>3</v>
       </c>
       <c r="D335" s="1" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="E335" s="1" t="s">
-        <v>126</v>
+        <v>38</v>
       </c>
       <c r="F335" s="1" t="s">
         <v>23</v>
@@ -9419,10 +9431,10 @@
         <v>3</v>
       </c>
       <c r="D336" s="1" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="E336" s="1" t="s">
-        <v>145</v>
+        <v>41</v>
       </c>
       <c r="F336" s="1" t="s">
         <v>23</v>
@@ -9439,53 +9451,53 @@
         <v>3</v>
       </c>
       <c r="D337" s="1" t="s">
-        <v>724</v>
+        <v>707</v>
       </c>
       <c r="E337" s="1" t="s">
-        <v>4</v>
+        <v>128</v>
       </c>
       <c r="F337" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A338" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="B338" s="1" t="s">
         <v>725</v>
       </c>
-      <c r="B338" s="1" t="s">
-        <v>726</v>
-      </c>
       <c r="C338" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D338" s="1" t="s">
-        <v>724</v>
+        <v>707</v>
       </c>
       <c r="E338" s="1" t="s">
-        <v>8</v>
+        <v>147</v>
       </c>
       <c r="F338" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A339" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="B339" s="1" t="s">
         <v>727</v>
       </c>
-      <c r="B339" s="1" t="s">
+      <c r="C339" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D339" s="1" t="s">
         <v>728</v>
       </c>
-      <c r="C339" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D339" s="1" t="s">
-        <v>724</v>
-      </c>
       <c r="E339" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F339" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.25">
@@ -9499,10 +9511,10 @@
         <v>3</v>
       </c>
       <c r="D340" s="1" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="E340" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F340" s="1" t="s">
         <v>31</v>
@@ -9519,10 +9531,10 @@
         <v>3</v>
       </c>
       <c r="D341" s="1" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="E341" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F341" s="1" t="s">
         <v>23</v>
@@ -9539,13 +9551,13 @@
         <v>3</v>
       </c>
       <c r="D342" s="1" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="E342" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F342" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="343" spans="1:6" x14ac:dyDescent="0.25">
@@ -9559,13 +9571,13 @@
         <v>3</v>
       </c>
       <c r="D343" s="1" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="E343" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F343" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.25">
@@ -9579,87 +9591,87 @@
         <v>3</v>
       </c>
       <c r="D344" s="1" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="E344" s="1" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="F344" s="1" t="s">
-        <v>739</v>
+        <v>23</v>
       </c>
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A345" s="1" t="s">
+        <v>739</v>
+      </c>
+      <c r="B345" s="1" t="s">
         <v>740</v>
       </c>
-      <c r="B345" s="1" t="s">
-        <v>741</v>
-      </c>
       <c r="C345" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D345" s="1" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="E345" s="1" t="s">
-        <v>126</v>
+        <v>38</v>
       </c>
       <c r="F345" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A346" s="1" t="s">
+        <v>741</v>
+      </c>
+      <c r="B346" s="1" t="s">
         <v>742</v>
       </c>
-      <c r="B346" s="1" t="s">
+      <c r="C346" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D346" s="1" t="s">
+        <v>728</v>
+      </c>
+      <c r="E346" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F346" s="1" t="s">
         <v>743</v>
-      </c>
-      <c r="C346" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D346" s="1" t="s">
-        <v>744</v>
-      </c>
-      <c r="E346" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F346" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A347" s="1" t="s">
+        <v>744</v>
+      </c>
+      <c r="B347" s="1" t="s">
         <v>745</v>
       </c>
-      <c r="B347" s="1" t="s">
-        <v>746</v>
-      </c>
       <c r="C347" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D347" s="1" t="s">
-        <v>744</v>
+        <v>728</v>
       </c>
       <c r="E347" s="1" t="s">
-        <v>8</v>
+        <v>128</v>
       </c>
       <c r="F347" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A348" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="B348" s="1" t="s">
         <v>747</v>
       </c>
-      <c r="B348" s="1" t="s">
+      <c r="C348" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D348" s="1" t="s">
         <v>748</v>
-      </c>
-      <c r="C348" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D348" s="1" t="s">
-        <v>749</v>
       </c>
       <c r="E348" s="1" t="s">
         <v>4</v>
@@ -9670,101 +9682,141 @@
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A349" s="1" t="s">
+        <v>749</v>
+      </c>
+      <c r="B349" s="1" t="s">
         <v>750</v>
       </c>
-      <c r="B349" s="1" t="s">
-        <v>751</v>
-      </c>
       <c r="C349" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D349" s="1" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="E349" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F349" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A350" s="1" t="s">
+        <v>751</v>
+      </c>
+      <c r="B350" s="1" t="s">
+        <v>752</v>
+      </c>
+      <c r="C350" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D350" s="1" t="s">
         <v>753</v>
-      </c>
-      <c r="B350" s="1" t="s">
-        <v>754</v>
-      </c>
-      <c r="C350" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D350" s="1" t="s">
-        <v>755</v>
       </c>
       <c r="E350" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F350" s="1" t="s">
-        <v>756</v>
+        <v>23</v>
       </c>
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A351" s="1" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="B351" s="1" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="C351" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D351" s="1" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="E351" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F351" s="1" t="s">
-        <v>759</v>
+        <v>28</v>
       </c>
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A352" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="B352" s="1" t="s">
+        <v>758</v>
+      </c>
+      <c r="C352" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D352" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="E352" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F352" s="1" t="s">
         <v>760</v>
-      </c>
-      <c r="B352" s="1" t="s">
-        <v>761</v>
-      </c>
-      <c r="C352" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D352" s="1" t="s">
-        <v>755</v>
-      </c>
-      <c r="E352" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F352" s="1" t="s">
-        <v>762</v>
       </c>
     </row>
     <row r="353" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A353" s="1" t="s">
+        <v>761</v>
+      </c>
+      <c r="B353" s="1" t="s">
+        <v>762</v>
+      </c>
+      <c r="C353" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D353" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="E353" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F353" s="1" t="s">
         <v>763</v>
       </c>
-      <c r="B353" s="1" t="s">
+    </row>
+    <row r="354" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A354" s="1" t="s">
         <v>764</v>
       </c>
-      <c r="C353" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D353" s="1" t="s">
-        <v>755</v>
-      </c>
-      <c r="E353" s="1" t="s">
+      <c r="B354" s="1" t="s">
+        <v>765</v>
+      </c>
+      <c r="C354" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D354" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="E354" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F354" s="1" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="355" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A355" s="1" t="s">
+        <v>767</v>
+      </c>
+      <c r="B355" s="1" t="s">
+        <v>768</v>
+      </c>
+      <c r="C355" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D355" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="E355" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F353" s="1" t="s">
+      <c r="F355" s="1" t="s">
         <v>23</v>
       </c>
     </row>

--- a/CLB07N.xlsx
+++ b/CLB07N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2130" uniqueCount="769">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2124" uniqueCount="767">
   <si>
     <t/>
   </si>
@@ -2108,12 +2108,6 @@
   </si>
   <si>
     <t>TS OAT VANILLA 190ML</t>
-  </si>
-  <si>
-    <t>20135795</t>
-  </si>
-  <si>
-    <t>TS COLLGN PEACH190ML</t>
   </si>
   <si>
     <t>20135463</t>
@@ -2710,7 +2704,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F355"/>
+  <dimension ref="A1:F354"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -9271,10 +9265,10 @@
         <v>3</v>
       </c>
       <c r="D328" s="1" t="s">
-        <v>688</v>
+        <v>705</v>
       </c>
       <c r="E328" s="1" t="s">
-        <v>128</v>
+        <v>4</v>
       </c>
       <c r="F328" s="1" t="s">
         <v>23</v>
@@ -9282,19 +9276,19 @@
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A329" s="1" t="s">
+        <v>706</v>
+      </c>
+      <c r="B329" s="1" t="s">
+        <v>707</v>
+      </c>
+      <c r="C329" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D329" s="1" t="s">
         <v>705</v>
       </c>
-      <c r="B329" s="1" t="s">
-        <v>706</v>
-      </c>
-      <c r="C329" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D329" s="1" t="s">
-        <v>707</v>
-      </c>
       <c r="E329" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F329" s="1" t="s">
         <v>23</v>
@@ -9311,13 +9305,13 @@
         <v>3</v>
       </c>
       <c r="D330" s="1" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="E330" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F330" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.25">
@@ -9331,10 +9325,10 @@
         <v>3</v>
       </c>
       <c r="D331" s="1" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="E331" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F331" s="1" t="s">
         <v>31</v>
@@ -9351,13 +9345,13 @@
         <v>3</v>
       </c>
       <c r="D332" s="1" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="E332" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F332" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.25">
@@ -9371,10 +9365,10 @@
         <v>3</v>
       </c>
       <c r="D333" s="1" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="E333" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F333" s="1" t="s">
         <v>23</v>
@@ -9391,10 +9385,10 @@
         <v>3</v>
       </c>
       <c r="D334" s="1" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="E334" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="F334" s="1" t="s">
         <v>23</v>
@@ -9411,10 +9405,10 @@
         <v>3</v>
       </c>
       <c r="D335" s="1" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="E335" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F335" s="1" t="s">
         <v>23</v>
@@ -9431,10 +9425,10 @@
         <v>3</v>
       </c>
       <c r="D336" s="1" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="E336" s="1" t="s">
-        <v>41</v>
+        <v>128</v>
       </c>
       <c r="F336" s="1" t="s">
         <v>23</v>
@@ -9451,10 +9445,10 @@
         <v>3</v>
       </c>
       <c r="D337" s="1" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="E337" s="1" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="F337" s="1" t="s">
         <v>23</v>
@@ -9471,33 +9465,33 @@
         <v>3</v>
       </c>
       <c r="D338" s="1" t="s">
-        <v>707</v>
+        <v>726</v>
       </c>
       <c r="E338" s="1" t="s">
-        <v>147</v>
+        <v>4</v>
       </c>
       <c r="F338" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A339" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="B339" s="1" t="s">
+        <v>728</v>
+      </c>
+      <c r="C339" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D339" s="1" t="s">
         <v>726</v>
       </c>
-      <c r="B339" s="1" t="s">
-        <v>727</v>
-      </c>
-      <c r="C339" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D339" s="1" t="s">
-        <v>728</v>
-      </c>
       <c r="E339" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F339" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.25">
@@ -9511,13 +9505,13 @@
         <v>3</v>
       </c>
       <c r="D340" s="1" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="E340" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F340" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.25">
@@ -9531,13 +9525,13 @@
         <v>3</v>
       </c>
       <c r="D341" s="1" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="E341" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F341" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.25">
@@ -9551,13 +9545,13 @@
         <v>3</v>
       </c>
       <c r="D342" s="1" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="E342" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F342" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="343" spans="1:6" x14ac:dyDescent="0.25">
@@ -9571,10 +9565,10 @@
         <v>3</v>
       </c>
       <c r="D343" s="1" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="E343" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F343" s="1" t="s">
         <v>23</v>
@@ -9591,13 +9585,13 @@
         <v>3</v>
       </c>
       <c r="D344" s="1" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="E344" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="F344" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.25">
@@ -9611,33 +9605,33 @@
         <v>3</v>
       </c>
       <c r="D345" s="1" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="E345" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F345" s="1" t="s">
-        <v>31</v>
+        <v>741</v>
       </c>
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A346" s="1" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B346" s="1" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="C346" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D346" s="1" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="E346" s="1" t="s">
-        <v>41</v>
+        <v>128</v>
       </c>
       <c r="F346" s="1" t="s">
-        <v>743</v>
+        <v>28</v>
       </c>
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.25">
@@ -9651,30 +9645,30 @@
         <v>3</v>
       </c>
       <c r="D347" s="1" t="s">
-        <v>728</v>
+        <v>746</v>
       </c>
       <c r="E347" s="1" t="s">
-        <v>128</v>
+        <v>4</v>
       </c>
       <c r="F347" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A348" s="1" t="s">
+        <v>747</v>
+      </c>
+      <c r="B348" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="C348" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D348" s="1" t="s">
         <v>746</v>
       </c>
-      <c r="B348" s="1" t="s">
-        <v>747</v>
-      </c>
-      <c r="C348" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D348" s="1" t="s">
-        <v>748</v>
-      </c>
       <c r="E348" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F348" s="1" t="s">
         <v>23</v>
@@ -9691,10 +9685,10 @@
         <v>3</v>
       </c>
       <c r="D349" s="1" t="s">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="E349" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F349" s="1" t="s">
         <v>23</v>
@@ -9702,121 +9696,101 @@
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A350" s="1" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B350" s="1" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C350" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D350" s="1" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="E350" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F350" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A351" s="1" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B351" s="1" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="C351" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D351" s="1" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="E351" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F351" s="1" t="s">
-        <v>28</v>
+        <v>758</v>
       </c>
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A352" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="B352" s="1" t="s">
+        <v>760</v>
+      </c>
+      <c r="C352" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D352" s="1" t="s">
         <v>757</v>
       </c>
-      <c r="B352" s="1" t="s">
-        <v>758</v>
-      </c>
-      <c r="C352" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D352" s="1" t="s">
-        <v>759</v>
-      </c>
       <c r="E352" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F352" s="1" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
     </row>
     <row r="353" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A353" s="1" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="B353" s="1" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="C353" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D353" s="1" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="E353" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F353" s="1" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
     </row>
     <row r="354" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A354" s="1" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="B354" s="1" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="C354" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D354" s="1" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="E354" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F354" s="1" t="s">
-        <v>766</v>
-      </c>
-    </row>
-    <row r="355" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A355" s="1" t="s">
-        <v>767</v>
-      </c>
-      <c r="B355" s="1" t="s">
-        <v>768</v>
-      </c>
-      <c r="C355" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D355" s="1" t="s">
-        <v>759</v>
-      </c>
-      <c r="E355" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F355" s="1" t="s">
         <v>23</v>
       </c>
     </row>

--- a/CLB07N.xlsx
+++ b/CLB07N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2124" uniqueCount="767">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2136" uniqueCount="771">
   <si>
     <t/>
   </si>
@@ -175,6 +175,12 @@
     <t>FANTA STRW PET 390ML</t>
   </si>
   <si>
+    <t>20142491</t>
+  </si>
+  <si>
+    <t>SPRITE NIPIS MINT390</t>
+  </si>
+  <si>
     <t>20137093</t>
   </si>
   <si>
@@ -187,6 +193,9 @@
     <t>FANTA GRAPE 390ML</t>
   </si>
   <si>
+    <t>9</t>
+  </si>
+  <si>
     <t>20123500</t>
   </si>
   <si>
@@ -397,9 +406,6 @@
     <t>HY BTS COFF TRMS 250</t>
   </si>
   <si>
-    <t>9</t>
-  </si>
-  <si>
     <t>20138049</t>
   </si>
   <si>
@@ -533,6 +539,12 @@
   </si>
   <si>
     <t>PC CRMY CPUCCINO 210</t>
+  </si>
+  <si>
+    <t>20142601</t>
+  </si>
+  <si>
+    <t>NSCAFE MTCHA ESP 220</t>
   </si>
   <si>
     <t>20140431</t>
@@ -2704,7 +2716,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F354"/>
+  <dimension ref="A1:F356"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -3185,10 +3197,10 @@
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>5</v>
@@ -3196,10 +3208,10 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
@@ -3208,18 +3220,18 @@
         <v>14</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
@@ -3228,7 +3240,7 @@
         <v>14</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>23</v>
@@ -3236,10 +3248,10 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
@@ -3248,7 +3260,7 @@
         <v>14</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>23</v>
@@ -3256,30 +3268,30 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
@@ -3288,7 +3300,7 @@
         <v>17</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>28</v>
@@ -3296,10 +3308,10 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
@@ -3308,7 +3320,7 @@
         <v>17</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>28</v>
@@ -3316,10 +3328,10 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
@@ -3328,7 +3340,7 @@
         <v>17</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>28</v>
@@ -3336,10 +3348,10 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
@@ -3348,10 +3360,10 @@
         <v>17</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>76</v>
+        <v>28</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -3368,18 +3380,18 @@
         <v>17</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>3</v>
@@ -3388,18 +3400,18 @@
         <v>17</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>3</v>
@@ -3408,38 +3420,38 @@
         <v>17</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>23</v>
+        <v>79</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
@@ -3448,18 +3460,18 @@
         <v>20</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
@@ -3468,18 +3480,18 @@
         <v>20</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>3</v>
@@ -3488,7 +3500,7 @@
         <v>20</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>23</v>
@@ -3496,10 +3508,10 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
@@ -3508,7 +3520,7 @@
         <v>20</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>23</v>
@@ -3516,10 +3528,10 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
@@ -3528,18 +3540,18 @@
         <v>20</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>76</v>
+        <v>23</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
@@ -3548,18 +3560,18 @@
         <v>20</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
@@ -3568,38 +3580,38 @@
         <v>20</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>28</v>
+        <v>79</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
@@ -3608,10 +3620,10 @@
         <v>38</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>103</v>
+        <v>28</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -3628,18 +3640,18 @@
         <v>38</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>76</v>
+        <v>106</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
@@ -3648,18 +3660,18 @@
         <v>38</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
@@ -3668,18 +3680,18 @@
         <v>38</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>31</v>
+        <v>79</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
@@ -3688,7 +3700,7 @@
         <v>38</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>31</v>
@@ -3696,10 +3708,10 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
@@ -3708,38 +3720,38 @@
         <v>38</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>3</v>
@@ -3748,18 +3760,18 @@
         <v>41</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>3</v>
@@ -3768,7 +3780,7 @@
         <v>41</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>23</v>
@@ -3776,10 +3788,10 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>3</v>
@@ -3788,7 +3800,7 @@
         <v>41</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>23</v>
@@ -3796,10 +3808,10 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>3</v>
@@ -3808,7 +3820,7 @@
         <v>41</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>23</v>
@@ -3816,10 +3828,10 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>3</v>
@@ -3828,7 +3840,7 @@
         <v>41</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>23</v>
@@ -3836,19 +3848,19 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>128</v>
+        <v>41</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>23</v>
@@ -3865,10 +3877,10 @@
         <v>3</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>128</v>
+        <v>60</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>23</v>
@@ -3885,10 +3897,10 @@
         <v>3</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>128</v>
+        <v>60</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>23</v>
@@ -3905,10 +3917,10 @@
         <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>128</v>
+        <v>60</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>23</v>
@@ -3925,10 +3937,10 @@
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>128</v>
+        <v>60</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>23</v>
@@ -3945,10 +3957,10 @@
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>128</v>
+        <v>60</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>23</v>
@@ -3965,10 +3977,10 @@
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>128</v>
+        <v>60</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>23</v>
@@ -3985,10 +3997,10 @@
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>128</v>
+        <v>60</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>23</v>
@@ -4005,10 +4017,10 @@
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>128</v>
+        <v>60</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>128</v>
+        <v>41</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>23</v>
@@ -4025,10 +4037,10 @@
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>128</v>
+        <v>60</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>147</v>
+        <v>60</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>23</v>
@@ -4036,22 +4048,22 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B67" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="B67" s="1" t="s">
+      <c r="C67" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E67" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="C67" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="E67" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F67" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -4065,10 +4077,10 @@
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>31</v>
@@ -4085,10 +4097,10 @@
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>31</v>
@@ -4105,10 +4117,10 @@
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>31</v>
@@ -4125,10 +4137,10 @@
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>31</v>
@@ -4145,10 +4157,10 @@
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>31</v>
@@ -4165,13 +4177,13 @@
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -4185,10 +4197,10 @@
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>23</v>
@@ -4205,10 +4217,10 @@
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>128</v>
+        <v>41</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>23</v>
@@ -4225,33 +4237,33 @@
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>168</v>
+        <v>149</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>169</v>
+        <v>23</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D77" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="B77" s="1" t="s">
+      <c r="E77" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F77" s="1" t="s">
         <v>171</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="E77" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F77" s="1" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -4265,13 +4277,13 @@
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -4285,13 +4297,13 @@
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>23</v>
+        <v>171</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -4305,13 +4317,13 @@
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -4325,10 +4337,10 @@
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>23</v>
@@ -4345,10 +4357,10 @@
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>31</v>
@@ -4356,39 +4368,39 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B83" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="B83" s="1" t="s">
-        <v>184</v>
-      </c>
       <c r="C83" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B84" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="B84" s="1" t="s">
+      <c r="C84" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D84" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="C84" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>182</v>
-      </c>
       <c r="E84" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>31</v>
@@ -4405,13 +4417,13 @@
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -4425,10 +4437,10 @@
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>31</v>
@@ -4445,13 +4457,13 @@
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -4465,10 +4477,10 @@
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>31</v>
@@ -4485,10 +4497,10 @@
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>31</v>
@@ -4505,13 +4517,13 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>128</v>
+        <v>38</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -4525,13 +4537,13 @@
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>147</v>
+        <v>41</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -4545,53 +4557,53 @@
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>203</v>
+        <v>186</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B93" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="B93" s="1" t="s">
-        <v>205</v>
-      </c>
       <c r="C93" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>203</v>
+        <v>186</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>8</v>
+        <v>149</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B94" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="B94" s="1" t="s">
+      <c r="C94" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D94" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="C94" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>203</v>
-      </c>
       <c r="E94" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>76</v>
+        <v>28</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -4605,13 +4617,13 @@
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -4625,13 +4637,13 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>23</v>
+        <v>79</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -4645,13 +4657,13 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -4665,10 +4677,10 @@
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>23</v>
@@ -4685,13 +4697,13 @@
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -4705,10 +4717,10 @@
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>23</v>
@@ -4716,19 +4728,19 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B101" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="B101" s="1" t="s">
-        <v>222</v>
-      </c>
       <c r="C101" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>23</v>
@@ -4736,19 +4748,19 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B102" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B102" s="1" t="s">
+      <c r="C102" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D102" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="C102" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>220</v>
-      </c>
       <c r="E102" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>23</v>
@@ -4765,10 +4777,10 @@
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>23</v>
@@ -4785,10 +4797,10 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>23</v>
@@ -4805,10 +4817,10 @@
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>23</v>
@@ -4825,10 +4837,10 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>23</v>
@@ -4845,10 +4857,10 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>23</v>
@@ -4865,53 +4877,53 @@
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>237</v>
+        <v>224</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>169</v>
+        <v>23</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B109" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="B109" s="1" t="s">
-        <v>239</v>
-      </c>
       <c r="C109" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>237</v>
+        <v>224</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>169</v>
+        <v>23</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B110" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="B110" s="1" t="s">
+      <c r="C110" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D110" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="C110" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D110" s="1" t="s">
-        <v>237</v>
-      </c>
       <c r="E110" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -4925,13 +4937,13 @@
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>23</v>
+        <v>171</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -4945,13 +4957,13 @@
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>23</v>
+        <v>171</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
@@ -4965,10 +4977,10 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>23</v>
@@ -4985,10 +4997,10 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>128</v>
+        <v>38</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>23</v>
@@ -5005,10 +5017,10 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>23</v>
@@ -5016,19 +5028,19 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B116" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="B116" s="1" t="s">
-        <v>254</v>
-      </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>23</v>
@@ -5036,19 +5048,19 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B117" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="B117" s="1" t="s">
+      <c r="C117" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D117" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="C117" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D117" s="1" t="s">
-        <v>252</v>
-      </c>
       <c r="E117" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>23</v>
@@ -5065,10 +5077,10 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>23</v>
@@ -5085,10 +5097,10 @@
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>23</v>
@@ -5105,10 +5117,10 @@
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>23</v>
@@ -5125,10 +5137,10 @@
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>23</v>
@@ -5145,10 +5157,10 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>23</v>
@@ -5165,30 +5177,30 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>128</v>
+        <v>38</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>269</v>
+        <v>23</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B124" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="B124" s="1" t="s">
-        <v>271</v>
-      </c>
       <c r="C124" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>272</v>
+        <v>256</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>23</v>
@@ -5196,39 +5208,39 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="E125" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F125" s="1" t="s">
         <v>273</v>
-      </c>
-      <c r="B125" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="C125" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D125" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="E125" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F125" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="B126" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="B126" s="1" t="s">
+      <c r="C126" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D126" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="C126" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D126" s="1" t="s">
-        <v>272</v>
-      </c>
       <c r="E126" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>23</v>
@@ -5245,10 +5257,10 @@
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>23</v>
@@ -5265,10 +5277,10 @@
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>23</v>
@@ -5276,19 +5288,19 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="B129" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="B129" s="1" t="s">
-        <v>283</v>
-      </c>
       <c r="C129" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>23</v>
@@ -5296,19 +5308,19 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B130" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B130" s="1" t="s">
+      <c r="C130" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D130" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="C130" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D130" s="1" t="s">
-        <v>281</v>
-      </c>
       <c r="E130" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>23</v>
@@ -5325,10 +5337,10 @@
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>23</v>
@@ -5345,10 +5357,10 @@
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>23</v>
@@ -5365,10 +5377,10 @@
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>23</v>
@@ -5385,10 +5397,10 @@
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>23</v>
@@ -5405,10 +5417,10 @@
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>296</v>
+        <v>285</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>23</v>
@@ -5416,19 +5428,19 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="B136" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="B136" s="1" t="s">
-        <v>298</v>
-      </c>
       <c r="C136" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>296</v>
+        <v>285</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>23</v>
@@ -5436,19 +5448,19 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="B137" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="B137" s="1" t="s">
+      <c r="C137" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D137" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="C137" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D137" s="1" t="s">
-        <v>296</v>
-      </c>
       <c r="E137" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>23</v>
@@ -5465,10 +5477,10 @@
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>23</v>
@@ -5485,10 +5497,10 @@
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>23</v>
@@ -5505,13 +5517,13 @@
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
@@ -5525,13 +5537,13 @@
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
@@ -5545,53 +5557,53 @@
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>311</v>
+        <v>300</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="B143" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="B143" s="1" t="s">
-        <v>313</v>
-      </c>
       <c r="C143" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>311</v>
+        <v>300</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="B144" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="B144" s="1" t="s">
+      <c r="C144" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D144" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="C144" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D144" s="1" t="s">
-        <v>311</v>
-      </c>
       <c r="E144" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
@@ -5605,13 +5617,13 @@
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
@@ -5625,13 +5637,13 @@
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
@@ -5645,13 +5657,13 @@
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
@@ -5665,13 +5677,13 @@
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
@@ -5685,50 +5697,50 @@
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>326</v>
+        <v>315</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="B150" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="B150" s="1" t="s">
-        <v>328</v>
-      </c>
       <c r="C150" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>326</v>
+        <v>315</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="B151" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="B151" s="1" t="s">
+      <c r="C151" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D151" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="C151" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D151" s="1" t="s">
-        <v>326</v>
-      </c>
       <c r="E151" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>23</v>
@@ -5745,10 +5757,10 @@
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>23</v>
@@ -5765,13 +5777,13 @@
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
@@ -5785,10 +5797,10 @@
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>23</v>
@@ -5805,13 +5817,13 @@
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
@@ -5825,13 +5837,13 @@
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
@@ -5845,13 +5857,13 @@
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>128</v>
+        <v>38</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
@@ -5865,53 +5877,53 @@
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>345</v>
+        <v>330</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="B159" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="B159" s="1" t="s">
-        <v>347</v>
-      </c>
       <c r="C159" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>345</v>
+        <v>330</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="B160" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="B160" s="1" t="s">
+      <c r="C160" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D160" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="C160" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D160" s="1" t="s">
-        <v>345</v>
-      </c>
       <c r="E160" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
@@ -5925,10 +5937,10 @@
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>23</v>
@@ -5945,13 +5957,13 @@
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
@@ -5965,10 +5977,10 @@
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F163" s="1" t="s">
         <v>23</v>
@@ -5985,10 +5997,10 @@
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>23</v>
@@ -6005,10 +6017,10 @@
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>23</v>
@@ -6025,10 +6037,10 @@
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>128</v>
+        <v>38</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>23</v>
@@ -6045,10 +6057,10 @@
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>364</v>
+        <v>349</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>23</v>
@@ -6056,19 +6068,19 @@
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="B168" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="B168" s="1" t="s">
-        <v>366</v>
-      </c>
       <c r="C168" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>364</v>
+        <v>349</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>23</v>
@@ -6076,19 +6088,19 @@
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="B169" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="B169" s="1" t="s">
+      <c r="C169" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D169" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="C169" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D169" s="1" t="s">
-        <v>364</v>
-      </c>
       <c r="E169" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>23</v>
@@ -6105,10 +6117,10 @@
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F170" s="1" t="s">
         <v>23</v>
@@ -6125,10 +6137,10 @@
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>23</v>
@@ -6145,10 +6157,10 @@
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>23</v>
@@ -6165,10 +6177,10 @@
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>23</v>
@@ -6185,13 +6197,13 @@
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
@@ -6205,13 +6217,13 @@
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>128</v>
+        <v>38</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
@@ -6225,53 +6237,53 @@
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>383</v>
+        <v>368</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="B177" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="B177" s="1" t="s">
-        <v>385</v>
-      </c>
       <c r="C177" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>383</v>
+        <v>368</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="B178" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="B178" s="1" t="s">
+      <c r="C178" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D178" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="C178" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D178" s="1" t="s">
-        <v>383</v>
-      </c>
       <c r="E178" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
@@ -6285,13 +6297,13 @@
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>103</v>
+        <v>23</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
@@ -6305,13 +6317,13 @@
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>103</v>
+        <v>23</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
@@ -6325,13 +6337,13 @@
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>23</v>
+        <v>106</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
@@ -6345,13 +6357,13 @@
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>28</v>
+        <v>106</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
@@ -6365,13 +6377,13 @@
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
@@ -6385,13 +6397,13 @@
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>128</v>
+        <v>38</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
@@ -6405,13 +6417,13 @@
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>147</v>
+        <v>41</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
@@ -6425,10 +6437,10 @@
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>404</v>
+        <v>387</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="F186" s="1" t="s">
         <v>23</v>
@@ -6436,42 +6448,42 @@
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="B187" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="B187" s="1" t="s">
-        <v>406</v>
-      </c>
       <c r="C187" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>404</v>
+        <v>387</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>8</v>
+        <v>149</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="B188" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="B188" s="1" t="s">
+      <c r="C188" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D188" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="C188" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D188" s="1" t="s">
-        <v>404</v>
-      </c>
       <c r="E188" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
@@ -6485,13 +6497,13 @@
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>76</v>
+        <v>31</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
@@ -6505,13 +6517,13 @@
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
@@ -6525,13 +6537,13 @@
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>31</v>
+        <v>79</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
@@ -6545,13 +6557,13 @@
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
@@ -6565,13 +6577,13 @@
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
@@ -6585,13 +6597,13 @@
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>128</v>
+        <v>38</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
@@ -6605,10 +6617,10 @@
         <v>3</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>423</v>
+        <v>408</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>23</v>
@@ -6616,19 +6628,19 @@
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B196" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="B196" s="1" t="s">
-        <v>425</v>
-      </c>
       <c r="C196" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>423</v>
+        <v>408</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="F196" s="1" t="s">
         <v>23</v>
@@ -6636,19 +6648,19 @@
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B197" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="B197" s="1" t="s">
+      <c r="C197" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D197" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="C197" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D197" s="1" t="s">
-        <v>423</v>
-      </c>
       <c r="E197" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F197" s="1" t="s">
         <v>23</v>
@@ -6665,10 +6677,10 @@
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F198" s="1" t="s">
         <v>23</v>
@@ -6685,10 +6697,10 @@
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F199" s="1" t="s">
         <v>23</v>
@@ -6705,13 +6717,13 @@
         <v>3</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>169</v>
+        <v>23</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
@@ -6725,13 +6737,13 @@
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>169</v>
+        <v>23</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
@@ -6745,13 +6757,13 @@
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="F202" s="1" t="s">
-        <v>23</v>
+        <v>171</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
@@ -6765,13 +6777,13 @@
         <v>3</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>147</v>
+        <v>38</v>
       </c>
       <c r="F203" s="1" t="s">
-        <v>23</v>
+        <v>171</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
@@ -6785,10 +6797,10 @@
         <v>3</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>442</v>
+        <v>427</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="F204" s="1" t="s">
         <v>23</v>
@@ -6796,19 +6808,19 @@
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="B205" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="B205" s="1" t="s">
-        <v>444</v>
-      </c>
       <c r="C205" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>442</v>
+        <v>427</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>8</v>
+        <v>149</v>
       </c>
       <c r="F205" s="1" t="s">
         <v>23</v>
@@ -6816,19 +6828,19 @@
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="B206" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="B206" s="1" t="s">
+      <c r="C206" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D206" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="C206" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D206" s="1" t="s">
-        <v>442</v>
-      </c>
       <c r="E206" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F206" s="1" t="s">
         <v>23</v>
@@ -6845,10 +6857,10 @@
         <v>3</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F207" s="1" t="s">
         <v>23</v>
@@ -6865,10 +6877,10 @@
         <v>3</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F208" s="1" t="s">
         <v>23</v>
@@ -6885,10 +6897,10 @@
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="F209" s="1" t="s">
         <v>23</v>
@@ -6905,10 +6917,10 @@
         <v>3</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="F210" s="1" t="s">
         <v>23</v>
@@ -6925,10 +6937,10 @@
         <v>3</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>128</v>
+        <v>38</v>
       </c>
       <c r="F211" s="1" t="s">
         <v>23</v>
@@ -6945,10 +6957,10 @@
         <v>3</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>459</v>
+        <v>446</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="F212" s="1" t="s">
         <v>23</v>
@@ -6956,19 +6968,19 @@
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="B213" s="1" t="s">
         <v>460</v>
       </c>
-      <c r="B213" s="1" t="s">
-        <v>461</v>
-      </c>
       <c r="C213" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>459</v>
+        <v>446</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="F213" s="1" t="s">
         <v>23</v>
@@ -6976,22 +6988,22 @@
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="B214" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="B214" s="1" t="s">
+      <c r="C214" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D214" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="C214" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D214" s="1" t="s">
-        <v>459</v>
-      </c>
       <c r="E214" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F214" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
@@ -7005,10 +7017,10 @@
         <v>3</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F215" s="1" t="s">
         <v>23</v>
@@ -7025,13 +7037,13 @@
         <v>3</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
@@ -7045,10 +7057,10 @@
         <v>3</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F217" s="1" t="s">
         <v>23</v>
@@ -7065,10 +7077,10 @@
         <v>3</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F218" s="1" t="s">
         <v>23</v>
@@ -7085,10 +7097,10 @@
         <v>3</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="F219" s="1" t="s">
         <v>23</v>
@@ -7105,13 +7117,13 @@
         <v>3</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>128</v>
+        <v>38</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
@@ -7125,10 +7137,10 @@
         <v>3</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>147</v>
+        <v>41</v>
       </c>
       <c r="F221" s="1" t="s">
         <v>23</v>
@@ -7145,53 +7157,53 @@
         <v>3</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>480</v>
+        <v>463</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="F222" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="B223" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="B223" s="1" t="s">
-        <v>482</v>
-      </c>
       <c r="C223" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>480</v>
+        <v>463</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>8</v>
+        <v>149</v>
       </c>
       <c r="F223" s="1" t="s">
-        <v>169</v>
+        <v>23</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="B224" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="B224" s="1" t="s">
+      <c r="C224" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D224" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="C224" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D224" s="1" t="s">
-        <v>480</v>
-      </c>
       <c r="E224" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>169</v>
+        <v>23</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
@@ -7205,13 +7217,13 @@
         <v>3</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>23</v>
+        <v>171</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
@@ -7225,13 +7237,13 @@
         <v>3</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>23</v>
+        <v>171</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
@@ -7245,10 +7257,10 @@
         <v>3</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F227" s="1" t="s">
         <v>23</v>
@@ -7265,13 +7277,13 @@
         <v>3</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F228" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
@@ -7285,13 +7297,13 @@
         <v>3</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="F229" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
@@ -7305,10 +7317,10 @@
         <v>3</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>497</v>
+        <v>484</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F230" s="1" t="s">
         <v>31</v>
@@ -7316,19 +7328,19 @@
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="B231" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="B231" s="1" t="s">
-        <v>499</v>
-      </c>
       <c r="C231" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>497</v>
+        <v>484</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="F231" s="1" t="s">
         <v>31</v>
@@ -7336,19 +7348,19 @@
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="B232" s="1" t="s">
         <v>500</v>
       </c>
-      <c r="B232" s="1" t="s">
+      <c r="C232" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D232" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="C232" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D232" s="1" t="s">
-        <v>497</v>
-      </c>
       <c r="E232" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F232" s="1" t="s">
         <v>31</v>
@@ -7365,10 +7377,10 @@
         <v>3</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F233" s="1" t="s">
         <v>31</v>
@@ -7385,10 +7397,10 @@
         <v>3</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F234" s="1" t="s">
         <v>31</v>
@@ -7405,13 +7417,13 @@
         <v>3</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F235" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
@@ -7425,13 +7437,13 @@
         <v>3</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F236" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
@@ -7445,10 +7457,10 @@
         <v>3</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>512</v>
+        <v>501</v>
       </c>
       <c r="E237" s="1" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F237" s="1" t="s">
         <v>23</v>
@@ -7456,42 +7468,42 @@
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="B238" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="B238" s="1" t="s">
-        <v>514</v>
-      </c>
       <c r="C238" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>512</v>
+        <v>501</v>
       </c>
       <c r="E238" s="1" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="F238" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="B239" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="B239" s="1" t="s">
+      <c r="C239" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D239" s="1" t="s">
         <v>516</v>
       </c>
-      <c r="C239" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D239" s="1" t="s">
-        <v>512</v>
-      </c>
       <c r="E239" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F239" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
@@ -7505,10 +7517,10 @@
         <v>3</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="E240" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F240" s="1" t="s">
         <v>31</v>
@@ -7525,13 +7537,13 @@
         <v>3</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="E241" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F241" s="1" t="s">
-        <v>169</v>
+        <v>31</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
@@ -7545,13 +7557,13 @@
         <v>3</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="E242" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F242" s="1" t="s">
-        <v>169</v>
+        <v>31</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
@@ -7565,53 +7577,53 @@
         <v>3</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="E243" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F243" s="1" t="s">
-        <v>525</v>
+        <v>171</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="B244" s="1" t="s">
         <v>526</v>
       </c>
-      <c r="B244" s="1" t="s">
-        <v>527</v>
-      </c>
       <c r="C244" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="E244" s="1" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="F244" s="1" t="s">
-        <v>28</v>
+        <v>171</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="B245" s="1" t="s">
         <v>528</v>
       </c>
-      <c r="B245" s="1" t="s">
+      <c r="C245" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D245" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="E245" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F245" s="1" t="s">
         <v>529</v>
-      </c>
-      <c r="C245" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D245" s="1" t="s">
-        <v>512</v>
-      </c>
-      <c r="E245" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="F245" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
@@ -7625,30 +7637,30 @@
         <v>3</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>532</v>
+        <v>516</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="F246" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="B247" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="B247" s="1" t="s">
-        <v>534</v>
-      </c>
       <c r="C247" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>532</v>
+        <v>516</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="F247" s="1" t="s">
         <v>23</v>
@@ -7656,19 +7668,19 @@
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="B248" s="1" t="s">
         <v>535</v>
       </c>
-      <c r="B248" s="1" t="s">
+      <c r="C248" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D248" s="1" t="s">
         <v>536</v>
       </c>
-      <c r="C248" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D248" s="1" t="s">
-        <v>532</v>
-      </c>
       <c r="E248" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F248" s="1" t="s">
         <v>23</v>
@@ -7685,10 +7697,10 @@
         <v>3</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F249" s="1" t="s">
         <v>23</v>
@@ -7705,13 +7717,13 @@
         <v>3</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="E250" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F250" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
@@ -7725,13 +7737,13 @@
         <v>3</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F251" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
@@ -7745,13 +7757,13 @@
         <v>3</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="E252" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F252" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
@@ -7765,10 +7777,10 @@
         <v>3</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="F253" s="1" t="s">
         <v>31</v>
@@ -7785,50 +7797,50 @@
         <v>3</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>549</v>
+        <v>536</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F254" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="B255" s="1" t="s">
         <v>550</v>
       </c>
-      <c r="B255" s="1" t="s">
-        <v>551</v>
-      </c>
       <c r="C255" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>549</v>
+        <v>536</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="F255" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="B256" s="1" t="s">
         <v>552</v>
       </c>
-      <c r="B256" s="1" t="s">
+      <c r="C256" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D256" s="1" t="s">
         <v>553</v>
       </c>
-      <c r="C256" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D256" s="1" t="s">
-        <v>549</v>
-      </c>
       <c r="E256" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F256" s="1" t="s">
         <v>23</v>
@@ -7845,10 +7857,10 @@
         <v>3</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="E257" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F257" s="1" t="s">
         <v>23</v>
@@ -7865,13 +7877,13 @@
         <v>3</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F258" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
@@ -7885,10 +7897,10 @@
         <v>3</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F259" s="1" t="s">
         <v>23</v>
@@ -7905,13 +7917,13 @@
         <v>3</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F260" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
@@ -7925,10 +7937,10 @@
         <v>3</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="F261" s="1" t="s">
         <v>23</v>
@@ -7945,33 +7957,33 @@
         <v>3</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>566</v>
+        <v>553</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F262" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="B263" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="B263" s="1" t="s">
-        <v>565</v>
-      </c>
       <c r="C263" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>566</v>
+        <v>553</v>
       </c>
       <c r="E263" s="1" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="F263" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
@@ -7985,33 +7997,33 @@
         <v>3</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="E264" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F264" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="B265" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="C265" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D265" s="1" t="s">
         <v>570</v>
       </c>
-      <c r="B265" s="1" t="s">
-        <v>571</v>
-      </c>
-      <c r="C265" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D265" s="1" t="s">
-        <v>566</v>
-      </c>
       <c r="E265" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F265" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
@@ -8025,10 +8037,10 @@
         <v>3</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F266" s="1" t="s">
         <v>23</v>
@@ -8045,10 +8057,10 @@
         <v>3</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="E267" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F267" s="1" t="s">
         <v>23</v>
@@ -8065,10 +8077,10 @@
         <v>3</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F268" s="1" t="s">
         <v>23</v>
@@ -8085,10 +8097,10 @@
         <v>3</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="F269" s="1" t="s">
         <v>23</v>
@@ -8105,10 +8117,10 @@
         <v>3</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="E270" s="1" t="s">
-        <v>128</v>
+        <v>38</v>
       </c>
       <c r="F270" s="1" t="s">
         <v>23</v>
@@ -8125,10 +8137,10 @@
         <v>3</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>584</v>
+        <v>570</v>
       </c>
       <c r="E271" s="1" t="s">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="F271" s="1" t="s">
         <v>23</v>
@@ -8136,19 +8148,19 @@
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="B272" s="1" t="s">
         <v>585</v>
       </c>
-      <c r="B272" s="1" t="s">
-        <v>586</v>
-      </c>
       <c r="C272" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>584</v>
+        <v>570</v>
       </c>
       <c r="E272" s="1" t="s">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="F272" s="1" t="s">
         <v>23</v>
@@ -8156,19 +8168,19 @@
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="B273" s="1" t="s">
         <v>587</v>
       </c>
-      <c r="B273" s="1" t="s">
+      <c r="C273" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D273" s="1" t="s">
         <v>588</v>
       </c>
-      <c r="C273" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D273" s="1" t="s">
-        <v>584</v>
-      </c>
       <c r="E273" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F273" s="1" t="s">
         <v>23</v>
@@ -8185,10 +8197,10 @@
         <v>3</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F274" s="1" t="s">
         <v>23</v>
@@ -8205,10 +8217,10 @@
         <v>3</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="E275" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F275" s="1" t="s">
         <v>23</v>
@@ -8225,10 +8237,10 @@
         <v>3</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="E276" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F276" s="1" t="s">
         <v>23</v>
@@ -8245,10 +8257,10 @@
         <v>3</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="E277" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F277" s="1" t="s">
         <v>23</v>
@@ -8265,10 +8277,10 @@
         <v>3</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="F278" s="1" t="s">
         <v>23</v>
@@ -8285,10 +8297,10 @@
         <v>3</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="E279" s="1" t="s">
-        <v>128</v>
+        <v>38</v>
       </c>
       <c r="F279" s="1" t="s">
         <v>23</v>
@@ -8305,10 +8317,10 @@
         <v>3</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="E280" s="1" t="s">
-        <v>147</v>
+        <v>41</v>
       </c>
       <c r="F280" s="1" t="s">
         <v>23</v>
@@ -8325,10 +8337,10 @@
         <v>3</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="E281" s="1" t="s">
-        <v>168</v>
+        <v>60</v>
       </c>
       <c r="F281" s="1" t="s">
         <v>23</v>
@@ -8345,10 +8357,10 @@
         <v>3</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>607</v>
+        <v>588</v>
       </c>
       <c r="E282" s="1" t="s">
-        <v>4</v>
+        <v>149</v>
       </c>
       <c r="F282" s="1" t="s">
         <v>23</v>
@@ -8356,19 +8368,19 @@
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="B283" s="1" t="s">
         <v>608</v>
       </c>
-      <c r="B283" s="1" t="s">
-        <v>609</v>
-      </c>
       <c r="C283" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>607</v>
+        <v>588</v>
       </c>
       <c r="E283" s="1" t="s">
-        <v>8</v>
+        <v>170</v>
       </c>
       <c r="F283" s="1" t="s">
         <v>23</v>
@@ -8376,19 +8388,19 @@
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="B284" s="1" t="s">
         <v>610</v>
       </c>
-      <c r="B284" s="1" t="s">
+      <c r="C284" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D284" s="1" t="s">
         <v>611</v>
       </c>
-      <c r="C284" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D284" s="1" t="s">
-        <v>607</v>
-      </c>
       <c r="E284" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F284" s="1" t="s">
         <v>23</v>
@@ -8405,10 +8417,10 @@
         <v>3</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="E285" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F285" s="1" t="s">
         <v>23</v>
@@ -8425,10 +8437,10 @@
         <v>3</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F286" s="1" t="s">
         <v>23</v>
@@ -8445,10 +8457,10 @@
         <v>3</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F287" s="1" t="s">
         <v>23</v>
@@ -8465,30 +8477,30 @@
         <v>3</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F288" s="1" t="s">
-        <v>620</v>
+        <v>23</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A289" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="B289" s="1" t="s">
         <v>621</v>
       </c>
-      <c r="B289" s="1" t="s">
-        <v>622</v>
-      </c>
       <c r="C289" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="E289" s="1" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="F289" s="1" t="s">
         <v>23</v>
@@ -8496,22 +8508,22 @@
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="B290" s="1" t="s">
         <v>623</v>
       </c>
-      <c r="B290" s="1" t="s">
+      <c r="C290" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D290" s="1" t="s">
+        <v>611</v>
+      </c>
+      <c r="E290" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F290" s="1" t="s">
         <v>624</v>
-      </c>
-      <c r="C290" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D290" s="1" t="s">
-        <v>607</v>
-      </c>
-      <c r="E290" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="F290" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
@@ -8525,10 +8537,10 @@
         <v>3</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>147</v>
+        <v>41</v>
       </c>
       <c r="F291" s="1" t="s">
         <v>23</v>
@@ -8545,53 +8557,53 @@
         <v>3</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>629</v>
+        <v>611</v>
       </c>
       <c r="E292" s="1" t="s">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="F292" s="1" t="s">
-        <v>620</v>
+        <v>23</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A293" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="B293" s="1" t="s">
         <v>630</v>
       </c>
-      <c r="B293" s="1" t="s">
-        <v>631</v>
-      </c>
       <c r="C293" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>629</v>
+        <v>611</v>
       </c>
       <c r="E293" s="1" t="s">
-        <v>8</v>
+        <v>149</v>
       </c>
       <c r="F293" s="1" t="s">
-        <v>620</v>
+        <v>23</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A294" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="B294" s="1" t="s">
         <v>632</v>
       </c>
-      <c r="B294" s="1" t="s">
+      <c r="C294" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D294" s="1" t="s">
         <v>633</v>
       </c>
-      <c r="C294" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D294" s="1" t="s">
-        <v>629</v>
-      </c>
       <c r="E294" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F294" s="1" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
@@ -8605,13 +8617,13 @@
         <v>3</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="E295" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F295" s="1" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
@@ -8625,13 +8637,13 @@
         <v>3</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="E296" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F296" s="1" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
@@ -8645,13 +8657,13 @@
         <v>3</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F297" s="1" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
@@ -8665,13 +8677,13 @@
         <v>3</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F298" s="1" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
@@ -8685,13 +8697,13 @@
         <v>3</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="F299" s="1" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
@@ -8705,13 +8717,13 @@
         <v>3</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>128</v>
+        <v>38</v>
       </c>
       <c r="F300" s="1" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
@@ -8725,50 +8737,50 @@
         <v>3</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>648</v>
+        <v>633</v>
       </c>
       <c r="E301" s="1" t="s">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="F301" s="1" t="s">
-        <v>23</v>
+        <v>624</v>
       </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A302" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="B302" s="1" t="s">
         <v>649</v>
       </c>
-      <c r="B302" s="1" t="s">
-        <v>650</v>
-      </c>
       <c r="C302" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>648</v>
+        <v>633</v>
       </c>
       <c r="E302" s="1" t="s">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="F302" s="1" t="s">
-        <v>23</v>
+        <v>624</v>
       </c>
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A303" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="B303" s="1" t="s">
         <v>651</v>
       </c>
-      <c r="B303" s="1" t="s">
+      <c r="C303" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D303" s="1" t="s">
         <v>652</v>
       </c>
-      <c r="C303" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D303" s="1" t="s">
-        <v>648</v>
-      </c>
       <c r="E303" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F303" s="1" t="s">
         <v>23</v>
@@ -8785,10 +8797,10 @@
         <v>3</v>
       </c>
       <c r="D304" s="1" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="E304" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F304" s="1" t="s">
         <v>23</v>
@@ -8805,10 +8817,10 @@
         <v>3</v>
       </c>
       <c r="D305" s="1" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="E305" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F305" s="1" t="s">
         <v>23</v>
@@ -8825,10 +8837,10 @@
         <v>3</v>
       </c>
       <c r="D306" s="1" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="E306" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F306" s="1" t="s">
         <v>23</v>
@@ -8845,10 +8857,10 @@
         <v>3</v>
       </c>
       <c r="D307" s="1" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="E307" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F307" s="1" t="s">
         <v>23</v>
@@ -8865,10 +8877,10 @@
         <v>3</v>
       </c>
       <c r="D308" s="1" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="E308" s="1" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="F308" s="1" t="s">
         <v>23</v>
@@ -8885,10 +8897,10 @@
         <v>3</v>
       </c>
       <c r="D309" s="1" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="E309" s="1" t="s">
-        <v>128</v>
+        <v>38</v>
       </c>
       <c r="F309" s="1" t="s">
         <v>23</v>
@@ -8905,10 +8917,10 @@
         <v>3</v>
       </c>
       <c r="D310" s="1" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="E310" s="1" t="s">
-        <v>147</v>
+        <v>41</v>
       </c>
       <c r="F310" s="1" t="s">
         <v>23</v>
@@ -8925,10 +8937,10 @@
         <v>3</v>
       </c>
       <c r="D311" s="1" t="s">
-        <v>669</v>
+        <v>652</v>
       </c>
       <c r="E311" s="1" t="s">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="F311" s="1" t="s">
         <v>23</v>
@@ -8936,19 +8948,19 @@
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A312" s="1" t="s">
+        <v>669</v>
+      </c>
+      <c r="B312" s="1" t="s">
         <v>670</v>
       </c>
-      <c r="B312" s="1" t="s">
-        <v>671</v>
-      </c>
       <c r="C312" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D312" s="1" t="s">
-        <v>669</v>
+        <v>652</v>
       </c>
       <c r="E312" s="1" t="s">
-        <v>8</v>
+        <v>149</v>
       </c>
       <c r="F312" s="1" t="s">
         <v>23</v>
@@ -8956,19 +8968,19 @@
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A313" s="1" t="s">
+        <v>671</v>
+      </c>
+      <c r="B313" s="1" t="s">
         <v>672</v>
       </c>
-      <c r="B313" s="1" t="s">
+      <c r="C313" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D313" s="1" t="s">
         <v>673</v>
       </c>
-      <c r="C313" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D313" s="1" t="s">
-        <v>669</v>
-      </c>
       <c r="E313" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F313" s="1" t="s">
         <v>23</v>
@@ -8985,10 +8997,10 @@
         <v>3</v>
       </c>
       <c r="D314" s="1" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="E314" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F314" s="1" t="s">
         <v>23</v>
@@ -9005,10 +9017,10 @@
         <v>3</v>
       </c>
       <c r="D315" s="1" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="E315" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F315" s="1" t="s">
         <v>23</v>
@@ -9025,10 +9037,10 @@
         <v>3</v>
       </c>
       <c r="D316" s="1" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="E316" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F316" s="1" t="s">
         <v>23</v>
@@ -9045,10 +9057,10 @@
         <v>3</v>
       </c>
       <c r="D317" s="1" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="E317" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F317" s="1" t="s">
         <v>23</v>
@@ -9065,10 +9077,10 @@
         <v>3</v>
       </c>
       <c r="D318" s="1" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="E318" s="1" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="F318" s="1" t="s">
         <v>23</v>
@@ -9085,10 +9097,10 @@
         <v>3</v>
       </c>
       <c r="D319" s="1" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="E319" s="1" t="s">
-        <v>128</v>
+        <v>38</v>
       </c>
       <c r="F319" s="1" t="s">
         <v>23</v>
@@ -9105,10 +9117,10 @@
         <v>3</v>
       </c>
       <c r="D320" s="1" t="s">
-        <v>688</v>
+        <v>673</v>
       </c>
       <c r="E320" s="1" t="s">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="F320" s="1" t="s">
         <v>23</v>
@@ -9116,19 +9128,19 @@
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A321" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="B321" s="1" t="s">
         <v>689</v>
       </c>
-      <c r="B321" s="1" t="s">
-        <v>690</v>
-      </c>
       <c r="C321" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D321" s="1" t="s">
-        <v>688</v>
+        <v>673</v>
       </c>
       <c r="E321" s="1" t="s">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="F321" s="1" t="s">
         <v>23</v>
@@ -9136,19 +9148,19 @@
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A322" s="1" t="s">
+        <v>690</v>
+      </c>
+      <c r="B322" s="1" t="s">
         <v>691</v>
       </c>
-      <c r="B322" s="1" t="s">
+      <c r="C322" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D322" s="1" t="s">
         <v>692</v>
       </c>
-      <c r="C322" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D322" s="1" t="s">
-        <v>688</v>
-      </c>
       <c r="E322" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F322" s="1" t="s">
         <v>23</v>
@@ -9165,10 +9177,10 @@
         <v>3</v>
       </c>
       <c r="D323" s="1" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="E323" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F323" s="1" t="s">
         <v>23</v>
@@ -9185,10 +9197,10 @@
         <v>3</v>
       </c>
       <c r="D324" s="1" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="E324" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F324" s="1" t="s">
         <v>23</v>
@@ -9205,10 +9217,10 @@
         <v>3</v>
       </c>
       <c r="D325" s="1" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="E325" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F325" s="1" t="s">
         <v>23</v>
@@ -9225,10 +9237,10 @@
         <v>3</v>
       </c>
       <c r="D326" s="1" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="E326" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F326" s="1" t="s">
         <v>23</v>
@@ -9245,10 +9257,10 @@
         <v>3</v>
       </c>
       <c r="D327" s="1" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="E327" s="1" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="F327" s="1" t="s">
         <v>23</v>
@@ -9265,10 +9277,10 @@
         <v>3</v>
       </c>
       <c r="D328" s="1" t="s">
-        <v>705</v>
+        <v>692</v>
       </c>
       <c r="E328" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F328" s="1" t="s">
         <v>23</v>
@@ -9276,19 +9288,19 @@
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A329" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="B329" s="1" t="s">
         <v>706</v>
       </c>
-      <c r="B329" s="1" t="s">
-        <v>707</v>
-      </c>
       <c r="C329" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D329" s="1" t="s">
-        <v>705</v>
+        <v>692</v>
       </c>
       <c r="E329" s="1" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="F329" s="1" t="s">
         <v>23</v>
@@ -9296,22 +9308,22 @@
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A330" s="1" t="s">
+        <v>707</v>
+      </c>
+      <c r="B330" s="1" t="s">
         <v>708</v>
       </c>
-      <c r="B330" s="1" t="s">
+      <c r="C330" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D330" s="1" t="s">
         <v>709</v>
       </c>
-      <c r="C330" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D330" s="1" t="s">
-        <v>705</v>
-      </c>
       <c r="E330" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F330" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.25">
@@ -9325,13 +9337,13 @@
         <v>3</v>
       </c>
       <c r="D331" s="1" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="E331" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F331" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.25">
@@ -9345,13 +9357,13 @@
         <v>3</v>
       </c>
       <c r="D332" s="1" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="E332" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F332" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.25">
@@ -9365,13 +9377,13 @@
         <v>3</v>
       </c>
       <c r="D333" s="1" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="E333" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F333" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.25">
@@ -9385,10 +9397,10 @@
         <v>3</v>
       </c>
       <c r="D334" s="1" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="E334" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F334" s="1" t="s">
         <v>23</v>
@@ -9405,10 +9417,10 @@
         <v>3</v>
       </c>
       <c r="D335" s="1" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="E335" s="1" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="F335" s="1" t="s">
         <v>23</v>
@@ -9425,10 +9437,10 @@
         <v>3</v>
       </c>
       <c r="D336" s="1" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="E336" s="1" t="s">
-        <v>128</v>
+        <v>38</v>
       </c>
       <c r="F336" s="1" t="s">
         <v>23</v>
@@ -9445,10 +9457,10 @@
         <v>3</v>
       </c>
       <c r="D337" s="1" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="E337" s="1" t="s">
-        <v>147</v>
+        <v>41</v>
       </c>
       <c r="F337" s="1" t="s">
         <v>23</v>
@@ -9465,53 +9477,53 @@
         <v>3</v>
       </c>
       <c r="D338" s="1" t="s">
-        <v>726</v>
+        <v>709</v>
       </c>
       <c r="E338" s="1" t="s">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="F338" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A339" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="B339" s="1" t="s">
         <v>727</v>
       </c>
-      <c r="B339" s="1" t="s">
-        <v>728</v>
-      </c>
       <c r="C339" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D339" s="1" t="s">
-        <v>726</v>
+        <v>709</v>
       </c>
       <c r="E339" s="1" t="s">
-        <v>8</v>
+        <v>149</v>
       </c>
       <c r="F339" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A340" s="1" t="s">
+        <v>728</v>
+      </c>
+      <c r="B340" s="1" t="s">
         <v>729</v>
       </c>
-      <c r="B340" s="1" t="s">
+      <c r="C340" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D340" s="1" t="s">
         <v>730</v>
       </c>
-      <c r="C340" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D340" s="1" t="s">
-        <v>726</v>
-      </c>
       <c r="E340" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F340" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.25">
@@ -9525,10 +9537,10 @@
         <v>3</v>
       </c>
       <c r="D341" s="1" t="s">
-        <v>726</v>
+        <v>730</v>
       </c>
       <c r="E341" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F341" s="1" t="s">
         <v>31</v>
@@ -9545,10 +9557,10 @@
         <v>3</v>
       </c>
       <c r="D342" s="1" t="s">
-        <v>726</v>
+        <v>730</v>
       </c>
       <c r="E342" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F342" s="1" t="s">
         <v>23</v>
@@ -9565,13 +9577,13 @@
         <v>3</v>
       </c>
       <c r="D343" s="1" t="s">
-        <v>726</v>
+        <v>730</v>
       </c>
       <c r="E343" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F343" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.25">
@@ -9585,13 +9597,13 @@
         <v>3</v>
       </c>
       <c r="D344" s="1" t="s">
-        <v>726</v>
+        <v>730</v>
       </c>
       <c r="E344" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F344" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.25">
@@ -9605,87 +9617,87 @@
         <v>3</v>
       </c>
       <c r="D345" s="1" t="s">
-        <v>726</v>
+        <v>730</v>
       </c>
       <c r="E345" s="1" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="F345" s="1" t="s">
-        <v>741</v>
+        <v>23</v>
       </c>
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A346" s="1" t="s">
+        <v>741</v>
+      </c>
+      <c r="B346" s="1" t="s">
         <v>742</v>
       </c>
-      <c r="B346" s="1" t="s">
-        <v>743</v>
-      </c>
       <c r="C346" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D346" s="1" t="s">
-        <v>726</v>
+        <v>730</v>
       </c>
       <c r="E346" s="1" t="s">
-        <v>128</v>
+        <v>38</v>
       </c>
       <c r="F346" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A347" s="1" t="s">
+        <v>743</v>
+      </c>
+      <c r="B347" s="1" t="s">
         <v>744</v>
       </c>
-      <c r="B347" s="1" t="s">
+      <c r="C347" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D347" s="1" t="s">
+        <v>730</v>
+      </c>
+      <c r="E347" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F347" s="1" t="s">
         <v>745</v>
-      </c>
-      <c r="C347" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D347" s="1" t="s">
-        <v>746</v>
-      </c>
-      <c r="E347" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F347" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A348" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="B348" s="1" t="s">
         <v>747</v>
       </c>
-      <c r="B348" s="1" t="s">
-        <v>748</v>
-      </c>
       <c r="C348" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D348" s="1" t="s">
-        <v>746</v>
+        <v>730</v>
       </c>
       <c r="E348" s="1" t="s">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="F348" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A349" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="B349" s="1" t="s">
         <v>749</v>
       </c>
-      <c r="B349" s="1" t="s">
+      <c r="C349" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D349" s="1" t="s">
         <v>750</v>
-      </c>
-      <c r="C349" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D349" s="1" t="s">
-        <v>751</v>
       </c>
       <c r="E349" s="1" t="s">
         <v>4</v>
@@ -9696,101 +9708,141 @@
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A350" s="1" t="s">
+        <v>751</v>
+      </c>
+      <c r="B350" s="1" t="s">
         <v>752</v>
       </c>
-      <c r="B350" s="1" t="s">
-        <v>753</v>
-      </c>
       <c r="C350" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D350" s="1" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
       <c r="E350" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F350" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A351" s="1" t="s">
+        <v>753</v>
+      </c>
+      <c r="B351" s="1" t="s">
+        <v>754</v>
+      </c>
+      <c r="C351" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D351" s="1" t="s">
         <v>755</v>
-      </c>
-      <c r="B351" s="1" t="s">
-        <v>756</v>
-      </c>
-      <c r="C351" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D351" s="1" t="s">
-        <v>757</v>
       </c>
       <c r="E351" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F351" s="1" t="s">
-        <v>758</v>
+        <v>23</v>
       </c>
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A352" s="1" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="B352" s="1" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="C352" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D352" s="1" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="E352" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F352" s="1" t="s">
-        <v>761</v>
+        <v>28</v>
       </c>
     </row>
     <row r="353" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A353" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="B353" s="1" t="s">
+        <v>760</v>
+      </c>
+      <c r="C353" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D353" s="1" t="s">
+        <v>761</v>
+      </c>
+      <c r="E353" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F353" s="1" t="s">
         <v>762</v>
-      </c>
-      <c r="B353" s="1" t="s">
-        <v>763</v>
-      </c>
-      <c r="C353" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D353" s="1" t="s">
-        <v>757</v>
-      </c>
-      <c r="E353" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F353" s="1" t="s">
-        <v>764</v>
       </c>
     </row>
     <row r="354" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A354" s="1" t="s">
+        <v>763</v>
+      </c>
+      <c r="B354" s="1" t="s">
+        <v>764</v>
+      </c>
+      <c r="C354" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D354" s="1" t="s">
+        <v>761</v>
+      </c>
+      <c r="E354" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F354" s="1" t="s">
         <v>765</v>
       </c>
-      <c r="B354" s="1" t="s">
+    </row>
+    <row r="355" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A355" s="1" t="s">
         <v>766</v>
       </c>
-      <c r="C354" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D354" s="1" t="s">
-        <v>757</v>
-      </c>
-      <c r="E354" s="1" t="s">
+      <c r="B355" s="1" t="s">
+        <v>767</v>
+      </c>
+      <c r="C355" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D355" s="1" t="s">
+        <v>761</v>
+      </c>
+      <c r="E355" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F355" s="1" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="356" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A356" s="1" t="s">
+        <v>769</v>
+      </c>
+      <c r="B356" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="C356" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D356" s="1" t="s">
+        <v>761</v>
+      </c>
+      <c r="E356" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F354" s="1" t="s">
+      <c r="F356" s="1" t="s">
         <v>23</v>
       </c>
     </row>

--- a/CLB07N.xlsx
+++ b/CLB07N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2112" uniqueCount="764">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2124" uniqueCount="768">
   <si>
     <t/>
   </si>
@@ -328,13 +328,13 @@
     <t>20102789</t>
   </si>
   <si>
-    <t>ABC CHOCMLT COFF 200</t>
+    <t>ABC CHOCMLT COFF 180</t>
   </si>
   <si>
     <t>20102790</t>
   </si>
   <si>
-    <t>ABC MILK COFFEE 200</t>
+    <t>ABC MILK COFFEE 180</t>
   </si>
   <si>
     <t>20120499</t>
@@ -451,31 +451,31 @@
     <t>20076770</t>
   </si>
   <si>
-    <t>G/DAY CAPPUCCINO 250</t>
+    <t>G/DAY CAPPUCCINO 230</t>
   </si>
   <si>
     <t>20045674</t>
   </si>
   <si>
-    <t>G/DAY F.MOCACINO 250</t>
+    <t>G/DAY F.MOCACINO 230</t>
   </si>
   <si>
     <t>20045673</t>
   </si>
   <si>
-    <t>G/DAY TIRAMISU/B 250</t>
+    <t>G/DAY TIRAMISU/B 230</t>
   </si>
   <si>
     <t>20056193</t>
   </si>
   <si>
-    <t>GOOD DAY AVCDO/D 250</t>
+    <t>GOOD DAY AVCDO/D 230</t>
   </si>
   <si>
     <t>20132329</t>
   </si>
   <si>
-    <t>GOOD DAY GRVY CKS250</t>
+    <t>GOOD DAY GRVY CKS230</t>
   </si>
   <si>
     <t>20134557</t>
@@ -1403,6 +1403,18 @@
   </si>
   <si>
     <t>EWATER LEMON 555ML</t>
+  </si>
+  <si>
+    <t>20142862</t>
+  </si>
+  <si>
+    <t>EWATER GRPFRT 380</t>
+  </si>
+  <si>
+    <t>20142863</t>
+  </si>
+  <si>
+    <t>EWATER LEMON 380</t>
   </si>
   <si>
     <t>20108987</t>
@@ -2695,7 +2707,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F352"/>
+  <dimension ref="A1:F354"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -7000,10 +7012,10 @@
         <v>455</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="F215" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
@@ -7020,7 +7032,7 @@
         <v>455</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="F216" s="1" t="s">
         <v>23</v>
@@ -7037,30 +7049,30 @@
         <v>3</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>470</v>
+        <v>455</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="F217" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="B218" s="1" t="s">
         <v>471</v>
       </c>
-      <c r="B218" s="1" t="s">
-        <v>472</v>
-      </c>
       <c r="C218" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>470</v>
+        <v>455</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="F218" s="1" t="s">
         <v>23</v>
@@ -7068,19 +7080,19 @@
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="B219" s="1" t="s">
         <v>473</v>
       </c>
-      <c r="B219" s="1" t="s">
+      <c r="C219" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D219" s="1" t="s">
         <v>474</v>
       </c>
-      <c r="C219" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D219" s="1" t="s">
-        <v>470</v>
-      </c>
       <c r="E219" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F219" s="1" t="s">
         <v>23</v>
@@ -7097,10 +7109,10 @@
         <v>3</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F220" s="1" t="s">
         <v>23</v>
@@ -7117,13 +7129,13 @@
         <v>3</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F221" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
@@ -7137,13 +7149,13 @@
         <v>3</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F222" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
@@ -7157,13 +7169,13 @@
         <v>3</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F223" s="1" t="s">
-        <v>164</v>
+        <v>31</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
@@ -7177,13 +7189,13 @@
         <v>3</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>164</v>
+        <v>31</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
@@ -7197,50 +7209,50 @@
         <v>3</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>487</v>
+        <v>474</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>31</v>
+        <v>164</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="B226" s="1" t="s">
         <v>488</v>
       </c>
-      <c r="B226" s="1" t="s">
-        <v>489</v>
-      </c>
       <c r="C226" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>487</v>
+        <v>474</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>31</v>
+        <v>164</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="B227" s="1" t="s">
         <v>490</v>
       </c>
-      <c r="B227" s="1" t="s">
+      <c r="C227" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D227" s="1" t="s">
         <v>491</v>
       </c>
-      <c r="C227" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D227" s="1" t="s">
-        <v>487</v>
-      </c>
       <c r="E227" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F227" s="1" t="s">
         <v>31</v>
@@ -7257,10 +7269,10 @@
         <v>3</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F228" s="1" t="s">
         <v>31</v>
@@ -7277,10 +7289,10 @@
         <v>3</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F229" s="1" t="s">
         <v>31</v>
@@ -7297,13 +7309,13 @@
         <v>3</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F230" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
@@ -7317,13 +7329,13 @@
         <v>3</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F231" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
@@ -7337,50 +7349,50 @@
         <v>3</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>502</v>
+        <v>491</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F232" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="B233" s="1" t="s">
         <v>503</v>
       </c>
-      <c r="B233" s="1" t="s">
-        <v>504</v>
-      </c>
       <c r="C233" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>502</v>
+        <v>491</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="F233" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="B234" s="1" t="s">
         <v>505</v>
       </c>
-      <c r="B234" s="1" t="s">
+      <c r="C234" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D234" s="1" t="s">
         <v>506</v>
       </c>
-      <c r="C234" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D234" s="1" t="s">
-        <v>502</v>
-      </c>
       <c r="E234" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F234" s="1" t="s">
         <v>31</v>
@@ -7397,13 +7409,13 @@
         <v>3</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F235" s="1" t="s">
-        <v>164</v>
+        <v>31</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
@@ -7417,53 +7429,53 @@
         <v>3</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F236" s="1" t="s">
-        <v>511</v>
+        <v>31</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="B237" s="1" t="s">
         <v>512</v>
       </c>
-      <c r="B237" s="1" t="s">
-        <v>513</v>
-      </c>
       <c r="C237" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="E237" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F237" s="1" t="s">
-        <v>28</v>
+        <v>164</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="B238" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="B238" s="1" t="s">
+      <c r="C238" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D238" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="E238" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F238" s="1" t="s">
         <v>515</v>
-      </c>
-      <c r="C238" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D238" s="1" t="s">
-        <v>502</v>
-      </c>
-      <c r="E238" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F238" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
@@ -7477,10 +7489,10 @@
         <v>3</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="E239" s="1" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="F239" s="1" t="s">
         <v>28</v>
@@ -7497,10 +7509,10 @@
         <v>3</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="E240" s="1" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="F240" s="1" t="s">
         <v>23</v>
@@ -7517,30 +7529,30 @@
         <v>3</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>522</v>
+        <v>506</v>
       </c>
       <c r="E241" s="1" t="s">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="F241" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="B242" s="1" t="s">
         <v>523</v>
       </c>
-      <c r="B242" s="1" t="s">
-        <v>524</v>
-      </c>
       <c r="C242" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>522</v>
+        <v>506</v>
       </c>
       <c r="E242" s="1" t="s">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="F242" s="1" t="s">
         <v>23</v>
@@ -7548,19 +7560,19 @@
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="B243" s="1" t="s">
         <v>525</v>
       </c>
-      <c r="B243" s="1" t="s">
+      <c r="C243" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D243" s="1" t="s">
         <v>526</v>
       </c>
-      <c r="C243" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D243" s="1" t="s">
-        <v>522</v>
-      </c>
       <c r="E243" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F243" s="1" t="s">
         <v>23</v>
@@ -7577,10 +7589,10 @@
         <v>3</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="E244" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F244" s="1" t="s">
         <v>23</v>
@@ -7597,13 +7609,13 @@
         <v>3</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F245" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
@@ -7617,13 +7629,13 @@
         <v>3</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F246" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
@@ -7637,13 +7649,13 @@
         <v>3</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F247" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
@@ -7657,10 +7669,10 @@
         <v>3</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="F248" s="1" t="s">
         <v>31</v>
@@ -7677,50 +7689,50 @@
         <v>3</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>539</v>
+        <v>526</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F249" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="B250" s="1" t="s">
         <v>540</v>
       </c>
-      <c r="B250" s="1" t="s">
-        <v>541</v>
-      </c>
       <c r="C250" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>539</v>
+        <v>526</v>
       </c>
       <c r="E250" s="1" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="F250" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="B251" s="1" t="s">
         <v>542</v>
       </c>
-      <c r="B251" s="1" t="s">
+      <c r="C251" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D251" s="1" t="s">
         <v>543</v>
       </c>
-      <c r="C251" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D251" s="1" t="s">
-        <v>539</v>
-      </c>
       <c r="E251" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F251" s="1" t="s">
         <v>23</v>
@@ -7737,10 +7749,10 @@
         <v>3</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="E252" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F252" s="1" t="s">
         <v>23</v>
@@ -7757,13 +7769,13 @@
         <v>3</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F253" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
@@ -7777,10 +7789,10 @@
         <v>3</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F254" s="1" t="s">
         <v>23</v>
@@ -7797,13 +7809,13 @@
         <v>3</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F255" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
@@ -7817,10 +7829,10 @@
         <v>3</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="E256" s="1" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="F256" s="1" t="s">
         <v>23</v>
@@ -7837,33 +7849,33 @@
         <v>3</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>556</v>
+        <v>543</v>
       </c>
       <c r="E257" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F257" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="B258" s="1" t="s">
         <v>557</v>
       </c>
-      <c r="B258" s="1" t="s">
-        <v>555</v>
-      </c>
       <c r="C258" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>556</v>
+        <v>543</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="F258" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
@@ -7877,33 +7889,33 @@
         <v>3</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F259" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="B260" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="C260" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D260" s="1" t="s">
         <v>560</v>
       </c>
-      <c r="B260" s="1" t="s">
-        <v>561</v>
-      </c>
-      <c r="C260" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D260" s="1" t="s">
-        <v>556</v>
-      </c>
       <c r="E260" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F260" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
@@ -7917,10 +7929,10 @@
         <v>3</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F261" s="1" t="s">
         <v>23</v>
@@ -7937,10 +7949,10 @@
         <v>3</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F262" s="1" t="s">
         <v>23</v>
@@ -7957,10 +7969,10 @@
         <v>3</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="E263" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F263" s="1" t="s">
         <v>23</v>
@@ -7977,10 +7989,10 @@
         <v>3</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="E264" s="1" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="F264" s="1" t="s">
         <v>23</v>
@@ -7997,10 +8009,10 @@
         <v>3</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="E265" s="1" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="F265" s="1" t="s">
         <v>23</v>
@@ -8017,10 +8029,10 @@
         <v>3</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="F266" s="1" t="s">
         <v>23</v>
@@ -8028,19 +8040,19 @@
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A267" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="B267" s="1" t="s">
         <v>575</v>
       </c>
-      <c r="B267" s="1" t="s">
-        <v>576</v>
-      </c>
       <c r="C267" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="E267" s="1" t="s">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="F267" s="1" t="s">
         <v>23</v>
@@ -8048,19 +8060,19 @@
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="B268" s="1" t="s">
         <v>577</v>
       </c>
-      <c r="B268" s="1" t="s">
+      <c r="C268" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D268" s="1" t="s">
         <v>578</v>
       </c>
-      <c r="C268" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D268" s="1" t="s">
-        <v>574</v>
-      </c>
       <c r="E268" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F268" s="1" t="s">
         <v>23</v>
@@ -8077,10 +8089,10 @@
         <v>3</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F269" s="1" t="s">
         <v>23</v>
@@ -8097,10 +8109,10 @@
         <v>3</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="E270" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F270" s="1" t="s">
         <v>23</v>
@@ -8117,10 +8129,10 @@
         <v>3</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="E271" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F271" s="1" t="s">
         <v>23</v>
@@ -8137,10 +8149,10 @@
         <v>3</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="E272" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F272" s="1" t="s">
         <v>23</v>
@@ -8157,10 +8169,10 @@
         <v>3</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="F273" s="1" t="s">
         <v>23</v>
@@ -8177,10 +8189,10 @@
         <v>3</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="F274" s="1" t="s">
         <v>23</v>
@@ -8197,10 +8209,10 @@
         <v>3</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="E275" s="1" t="s">
-        <v>142</v>
+        <v>41</v>
       </c>
       <c r="F275" s="1" t="s">
         <v>23</v>
@@ -8217,10 +8229,10 @@
         <v>3</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="E276" s="1" t="s">
-        <v>163</v>
+        <v>60</v>
       </c>
       <c r="F276" s="1" t="s">
         <v>23</v>
@@ -8237,10 +8249,10 @@
         <v>3</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>597</v>
+        <v>578</v>
       </c>
       <c r="E277" s="1" t="s">
-        <v>4</v>
+        <v>142</v>
       </c>
       <c r="F277" s="1" t="s">
         <v>23</v>
@@ -8248,19 +8260,19 @@
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="B278" s="1" t="s">
         <v>598</v>
       </c>
-      <c r="B278" s="1" t="s">
-        <v>599</v>
-      </c>
       <c r="C278" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>597</v>
+        <v>578</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>8</v>
+        <v>163</v>
       </c>
       <c r="F278" s="1" t="s">
         <v>23</v>
@@ -8268,19 +8280,19 @@
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="B279" s="1" t="s">
         <v>600</v>
       </c>
-      <c r="B279" s="1" t="s">
+      <c r="C279" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D279" s="1" t="s">
         <v>601</v>
       </c>
-      <c r="C279" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D279" s="1" t="s">
-        <v>597</v>
-      </c>
       <c r="E279" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F279" s="1" t="s">
         <v>23</v>
@@ -8297,10 +8309,10 @@
         <v>3</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="E280" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F280" s="1" t="s">
         <v>23</v>
@@ -8317,10 +8329,10 @@
         <v>3</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="E281" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F281" s="1" t="s">
         <v>23</v>
@@ -8337,10 +8349,10 @@
         <v>3</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="E282" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F282" s="1" t="s">
         <v>23</v>
@@ -8357,30 +8369,30 @@
         <v>3</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="E283" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F283" s="1" t="s">
-        <v>610</v>
+        <v>23</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="B284" s="1" t="s">
         <v>611</v>
       </c>
-      <c r="B284" s="1" t="s">
-        <v>612</v>
-      </c>
       <c r="C284" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="F284" s="1" t="s">
         <v>23</v>
@@ -8388,22 +8400,22 @@
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A285" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="B285" s="1" t="s">
         <v>613</v>
       </c>
-      <c r="B285" s="1" t="s">
+      <c r="C285" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D285" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="E285" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F285" s="1" t="s">
         <v>614</v>
-      </c>
-      <c r="C285" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D285" s="1" t="s">
-        <v>597</v>
-      </c>
-      <c r="E285" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="F285" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
@@ -8417,10 +8429,10 @@
         <v>3</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>142</v>
+        <v>41</v>
       </c>
       <c r="F286" s="1" t="s">
         <v>23</v>
@@ -8437,53 +8449,53 @@
         <v>3</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>619</v>
+        <v>601</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="F287" s="1" t="s">
-        <v>610</v>
+        <v>23</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288" s="1" t="s">
+        <v>619</v>
+      </c>
+      <c r="B288" s="1" t="s">
         <v>620</v>
       </c>
-      <c r="B288" s="1" t="s">
-        <v>621</v>
-      </c>
       <c r="C288" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>619</v>
+        <v>601</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>8</v>
+        <v>142</v>
       </c>
       <c r="F288" s="1" t="s">
-        <v>610</v>
+        <v>23</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A289" s="1" t="s">
+        <v>621</v>
+      </c>
+      <c r="B289" s="1" t="s">
         <v>622</v>
       </c>
-      <c r="B289" s="1" t="s">
+      <c r="C289" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D289" s="1" t="s">
         <v>623</v>
       </c>
-      <c r="C289" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D289" s="1" t="s">
-        <v>619</v>
-      </c>
       <c r="E289" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F289" s="1" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
@@ -8497,13 +8509,13 @@
         <v>3</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="E290" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F290" s="1" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
@@ -8517,13 +8529,13 @@
         <v>3</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F291" s="1" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
@@ -8537,13 +8549,13 @@
         <v>3</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="E292" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F292" s="1" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
@@ -8557,13 +8569,13 @@
         <v>3</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="E293" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F293" s="1" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
@@ -8577,13 +8589,13 @@
         <v>3</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="E294" s="1" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="F294" s="1" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
@@ -8597,13 +8609,13 @@
         <v>3</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="E295" s="1" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="F295" s="1" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
@@ -8617,50 +8629,50 @@
         <v>3</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>638</v>
+        <v>623</v>
       </c>
       <c r="E296" s="1" t="s">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="F296" s="1" t="s">
-        <v>23</v>
+        <v>614</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A297" s="1" t="s">
+        <v>638</v>
+      </c>
+      <c r="B297" s="1" t="s">
         <v>639</v>
       </c>
-      <c r="B297" s="1" t="s">
-        <v>640</v>
-      </c>
       <c r="C297" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>638</v>
+        <v>623</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="F297" s="1" t="s">
-        <v>23</v>
+        <v>614</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A298" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="B298" s="1" t="s">
         <v>641</v>
       </c>
-      <c r="B298" s="1" t="s">
+      <c r="C298" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D298" s="1" t="s">
         <v>642</v>
       </c>
-      <c r="C298" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D298" s="1" t="s">
-        <v>638</v>
-      </c>
       <c r="E298" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F298" s="1" t="s">
         <v>23</v>
@@ -8677,10 +8689,10 @@
         <v>3</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F299" s="1" t="s">
         <v>23</v>
@@ -8697,10 +8709,10 @@
         <v>3</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F300" s="1" t="s">
         <v>23</v>
@@ -8717,10 +8729,10 @@
         <v>3</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="E301" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F301" s="1" t="s">
         <v>23</v>
@@ -8737,10 +8749,10 @@
         <v>3</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="E302" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F302" s="1" t="s">
         <v>23</v>
@@ -8757,10 +8769,10 @@
         <v>3</v>
       </c>
       <c r="D303" s="1" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="E303" s="1" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="F303" s="1" t="s">
         <v>23</v>
@@ -8777,10 +8789,10 @@
         <v>3</v>
       </c>
       <c r="D304" s="1" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="E304" s="1" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="F304" s="1" t="s">
         <v>23</v>
@@ -8797,10 +8809,10 @@
         <v>3</v>
       </c>
       <c r="D305" s="1" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="E305" s="1" t="s">
-        <v>142</v>
+        <v>41</v>
       </c>
       <c r="F305" s="1" t="s">
         <v>23</v>
@@ -8817,10 +8829,10 @@
         <v>3</v>
       </c>
       <c r="D306" s="1" t="s">
-        <v>659</v>
+        <v>642</v>
       </c>
       <c r="E306" s="1" t="s">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="F306" s="1" t="s">
         <v>23</v>
@@ -8828,19 +8840,19 @@
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A307" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="B307" s="1" t="s">
         <v>660</v>
       </c>
-      <c r="B307" s="1" t="s">
-        <v>661</v>
-      </c>
       <c r="C307" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D307" s="1" t="s">
-        <v>659</v>
+        <v>642</v>
       </c>
       <c r="E307" s="1" t="s">
-        <v>8</v>
+        <v>142</v>
       </c>
       <c r="F307" s="1" t="s">
         <v>23</v>
@@ -8848,19 +8860,19 @@
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A308" s="1" t="s">
+        <v>661</v>
+      </c>
+      <c r="B308" s="1" t="s">
         <v>662</v>
       </c>
-      <c r="B308" s="1" t="s">
+      <c r="C308" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D308" s="1" t="s">
         <v>663</v>
       </c>
-      <c r="C308" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D308" s="1" t="s">
-        <v>659</v>
-      </c>
       <c r="E308" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F308" s="1" t="s">
         <v>23</v>
@@ -8877,10 +8889,10 @@
         <v>3</v>
       </c>
       <c r="D309" s="1" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="E309" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F309" s="1" t="s">
         <v>23</v>
@@ -8897,10 +8909,10 @@
         <v>3</v>
       </c>
       <c r="D310" s="1" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="E310" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F310" s="1" t="s">
         <v>23</v>
@@ -8917,10 +8929,10 @@
         <v>3</v>
       </c>
       <c r="D311" s="1" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="E311" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F311" s="1" t="s">
         <v>23</v>
@@ -8937,10 +8949,10 @@
         <v>3</v>
       </c>
       <c r="D312" s="1" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="E312" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F312" s="1" t="s">
         <v>23</v>
@@ -8957,10 +8969,10 @@
         <v>3</v>
       </c>
       <c r="D313" s="1" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="E313" s="1" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="F313" s="1" t="s">
         <v>23</v>
@@ -8977,10 +8989,10 @@
         <v>3</v>
       </c>
       <c r="D314" s="1" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="E314" s="1" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="F314" s="1" t="s">
         <v>23</v>
@@ -8997,10 +9009,10 @@
         <v>3</v>
       </c>
       <c r="D315" s="1" t="s">
-        <v>678</v>
+        <v>663</v>
       </c>
       <c r="E315" s="1" t="s">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="F315" s="1" t="s">
         <v>23</v>
@@ -9008,19 +9020,19 @@
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A316" s="1" t="s">
+        <v>678</v>
+      </c>
+      <c r="B316" s="1" t="s">
         <v>679</v>
       </c>
-      <c r="B316" s="1" t="s">
-        <v>680</v>
-      </c>
       <c r="C316" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D316" s="1" t="s">
-        <v>678</v>
+        <v>663</v>
       </c>
       <c r="E316" s="1" t="s">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="F316" s="1" t="s">
         <v>23</v>
@@ -9028,19 +9040,19 @@
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A317" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="B317" s="1" t="s">
         <v>681</v>
       </c>
-      <c r="B317" s="1" t="s">
+      <c r="C317" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D317" s="1" t="s">
         <v>682</v>
       </c>
-      <c r="C317" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D317" s="1" t="s">
-        <v>678</v>
-      </c>
       <c r="E317" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F317" s="1" t="s">
         <v>23</v>
@@ -9057,10 +9069,10 @@
         <v>3</v>
       </c>
       <c r="D318" s="1" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="E318" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F318" s="1" t="s">
         <v>23</v>
@@ -9077,10 +9089,10 @@
         <v>3</v>
       </c>
       <c r="D319" s="1" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="E319" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F319" s="1" t="s">
         <v>23</v>
@@ -9097,10 +9109,10 @@
         <v>3</v>
       </c>
       <c r="D320" s="1" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="E320" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F320" s="1" t="s">
         <v>23</v>
@@ -9117,10 +9129,10 @@
         <v>3</v>
       </c>
       <c r="D321" s="1" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="E321" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F321" s="1" t="s">
         <v>23</v>
@@ -9137,10 +9149,10 @@
         <v>3</v>
       </c>
       <c r="D322" s="1" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="E322" s="1" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="F322" s="1" t="s">
         <v>23</v>
@@ -9157,10 +9169,10 @@
         <v>3</v>
       </c>
       <c r="D323" s="1" t="s">
-        <v>695</v>
+        <v>682</v>
       </c>
       <c r="E323" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F323" s="1" t="s">
         <v>23</v>
@@ -9168,19 +9180,19 @@
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A324" s="1" t="s">
+        <v>695</v>
+      </c>
+      <c r="B324" s="1" t="s">
         <v>696</v>
       </c>
-      <c r="B324" s="1" t="s">
-        <v>697</v>
-      </c>
       <c r="C324" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D324" s="1" t="s">
-        <v>695</v>
+        <v>682</v>
       </c>
       <c r="E324" s="1" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="F324" s="1" t="s">
         <v>23</v>
@@ -9188,22 +9200,22 @@
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A325" s="1" t="s">
+        <v>697</v>
+      </c>
+      <c r="B325" s="1" t="s">
         <v>698</v>
       </c>
-      <c r="B325" s="1" t="s">
+      <c r="C325" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D325" s="1" t="s">
         <v>699</v>
       </c>
-      <c r="C325" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D325" s="1" t="s">
-        <v>695</v>
-      </c>
       <c r="E325" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F325" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.25">
@@ -9217,13 +9229,13 @@
         <v>3</v>
       </c>
       <c r="D326" s="1" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="E326" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F326" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.25">
@@ -9237,13 +9249,13 @@
         <v>3</v>
       </c>
       <c r="D327" s="1" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="E327" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F327" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.25">
@@ -9257,13 +9269,13 @@
         <v>3</v>
       </c>
       <c r="D328" s="1" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="E328" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F328" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.25">
@@ -9277,10 +9289,10 @@
         <v>3</v>
       </c>
       <c r="D329" s="1" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="E329" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F329" s="1" t="s">
         <v>23</v>
@@ -9297,10 +9309,10 @@
         <v>3</v>
       </c>
       <c r="D330" s="1" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="E330" s="1" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="F330" s="1" t="s">
         <v>23</v>
@@ -9317,10 +9329,10 @@
         <v>3</v>
       </c>
       <c r="D331" s="1" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="E331" s="1" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="F331" s="1" t="s">
         <v>23</v>
@@ -9337,10 +9349,10 @@
         <v>3</v>
       </c>
       <c r="D332" s="1" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="E332" s="1" t="s">
-        <v>142</v>
+        <v>41</v>
       </c>
       <c r="F332" s="1" t="s">
         <v>23</v>
@@ -9357,53 +9369,53 @@
         <v>3</v>
       </c>
       <c r="D333" s="1" t="s">
-        <v>716</v>
+        <v>699</v>
       </c>
       <c r="E333" s="1" t="s">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="F333" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A334" s="1" t="s">
+        <v>716</v>
+      </c>
+      <c r="B334" s="1" t="s">
         <v>717</v>
       </c>
-      <c r="B334" s="1" t="s">
-        <v>718</v>
-      </c>
       <c r="C334" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D334" s="1" t="s">
-        <v>716</v>
+        <v>699</v>
       </c>
       <c r="E334" s="1" t="s">
-        <v>8</v>
+        <v>142</v>
       </c>
       <c r="F334" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A335" s="1" t="s">
+        <v>718</v>
+      </c>
+      <c r="B335" s="1" t="s">
         <v>719</v>
       </c>
-      <c r="B335" s="1" t="s">
+      <c r="C335" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D335" s="1" t="s">
         <v>720</v>
       </c>
-      <c r="C335" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D335" s="1" t="s">
-        <v>716</v>
-      </c>
       <c r="E335" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F335" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.25">
@@ -9417,10 +9429,10 @@
         <v>3</v>
       </c>
       <c r="D336" s="1" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="E336" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F336" s="1" t="s">
         <v>31</v>
@@ -9437,10 +9449,10 @@
         <v>3</v>
       </c>
       <c r="D337" s="1" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="E337" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F337" s="1" t="s">
         <v>23</v>
@@ -9457,13 +9469,13 @@
         <v>3</v>
       </c>
       <c r="D338" s="1" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="E338" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F338" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.25">
@@ -9477,13 +9489,13 @@
         <v>3</v>
       </c>
       <c r="D339" s="1" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="E339" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F339" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.25">
@@ -9497,93 +9509,93 @@
         <v>3</v>
       </c>
       <c r="D340" s="1" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="E340" s="1" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="F340" s="1" t="s">
-        <v>731</v>
+        <v>23</v>
       </c>
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A341" s="1" t="s">
+        <v>731</v>
+      </c>
+      <c r="B341" s="1" t="s">
         <v>732</v>
       </c>
-      <c r="B341" s="1" t="s">
-        <v>733</v>
-      </c>
       <c r="C341" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D341" s="1" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="E341" s="1" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="F341" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A342" s="1" t="s">
+        <v>733</v>
+      </c>
+      <c r="B342" s="1" t="s">
         <v>734</v>
       </c>
-      <c r="B342" s="1" t="s">
+      <c r="C342" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D342" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="E342" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F342" s="1" t="s">
         <v>735</v>
-      </c>
-      <c r="C342" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D342" s="1" t="s">
-        <v>736</v>
-      </c>
-      <c r="E342" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F342" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="343" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A343" s="1" t="s">
+        <v>736</v>
+      </c>
+      <c r="B343" s="1" t="s">
         <v>737</v>
       </c>
-      <c r="B343" s="1" t="s">
-        <v>738</v>
-      </c>
       <c r="C343" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D343" s="1" t="s">
-        <v>736</v>
+        <v>720</v>
       </c>
       <c r="E343" s="1" t="s">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="F343" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A344" s="1" t="s">
+        <v>738</v>
+      </c>
+      <c r="B344" s="1" t="s">
         <v>739</v>
       </c>
-      <c r="B344" s="1" t="s">
+      <c r="C344" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D344" s="1" t="s">
         <v>740</v>
       </c>
-      <c r="C344" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D344" s="1" t="s">
-        <v>736</v>
-      </c>
       <c r="E344" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F344" s="1" t="s">
-        <v>164</v>
+        <v>23</v>
       </c>
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.25">
@@ -9597,10 +9609,10 @@
         <v>3</v>
       </c>
       <c r="D345" s="1" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="E345" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F345" s="1" t="s">
         <v>23</v>
@@ -9608,141 +9620,181 @@
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A346" s="1" t="s">
+        <v>743</v>
+      </c>
+      <c r="B346" s="1" t="s">
         <v>744</v>
       </c>
-      <c r="B346" s="1" t="s">
-        <v>745</v>
-      </c>
       <c r="C346" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D346" s="1" t="s">
-        <v>746</v>
+        <v>740</v>
       </c>
       <c r="E346" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F346" s="1" t="s">
-        <v>28</v>
+        <v>164</v>
       </c>
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A347" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="B347" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="C347" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D347" s="1" t="s">
         <v>747</v>
-      </c>
-      <c r="B347" s="1" t="s">
-        <v>748</v>
-      </c>
-      <c r="C347" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D347" s="1" t="s">
-        <v>749</v>
       </c>
       <c r="E347" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F347" s="1" t="s">
-        <v>750</v>
+        <v>23</v>
       </c>
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A348" s="1" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="B348" s="1" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="C348" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D348" s="1" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="E348" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F348" s="1" t="s">
-        <v>753</v>
+        <v>28</v>
       </c>
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A349" s="1" t="s">
+        <v>751</v>
+      </c>
+      <c r="B349" s="1" t="s">
+        <v>752</v>
+      </c>
+      <c r="C349" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D349" s="1" t="s">
+        <v>753</v>
+      </c>
+      <c r="E349" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F349" s="1" t="s">
         <v>754</v>
-      </c>
-      <c r="B349" s="1" t="s">
-        <v>755</v>
-      </c>
-      <c r="C349" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D349" s="1" t="s">
-        <v>749</v>
-      </c>
-      <c r="E349" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F349" s="1" t="s">
-        <v>756</v>
       </c>
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A350" s="1" t="s">
+        <v>755</v>
+      </c>
+      <c r="B350" s="1" t="s">
+        <v>756</v>
+      </c>
+      <c r="C350" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D350" s="1" t="s">
+        <v>753</v>
+      </c>
+      <c r="E350" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F350" s="1" t="s">
         <v>757</v>
-      </c>
-      <c r="B350" s="1" t="s">
-        <v>758</v>
-      </c>
-      <c r="C350" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D350" s="1" t="s">
-        <v>749</v>
-      </c>
-      <c r="E350" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F350" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A351" s="1" t="s">
+        <v>758</v>
+      </c>
+      <c r="B351" s="1" t="s">
         <v>759</v>
       </c>
-      <c r="B351" s="1" t="s">
+      <c r="C351" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D351" s="1" t="s">
+        <v>753</v>
+      </c>
+      <c r="E351" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F351" s="1" t="s">
         <v>760</v>
-      </c>
-      <c r="C351" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D351" s="1" t="s">
-        <v>761</v>
-      </c>
-      <c r="E351" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F351" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A352" s="1" t="s">
+        <v>761</v>
+      </c>
+      <c r="B352" s="1" t="s">
         <v>762</v>
       </c>
-      <c r="B352" s="1" t="s">
+      <c r="C352" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D352" s="1" t="s">
+        <v>753</v>
+      </c>
+      <c r="E352" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F352" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="353" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A353" s="1" t="s">
         <v>763</v>
       </c>
-      <c r="C352" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D352" s="1" t="s">
-        <v>761</v>
-      </c>
-      <c r="E352" s="1" t="s">
+      <c r="B353" s="1" t="s">
+        <v>764</v>
+      </c>
+      <c r="C353" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D353" s="1" t="s">
+        <v>765</v>
+      </c>
+      <c r="E353" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F353" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="354" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A354" s="1" t="s">
+        <v>766</v>
+      </c>
+      <c r="B354" s="1" t="s">
+        <v>767</v>
+      </c>
+      <c r="C354" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D354" s="1" t="s">
+        <v>765</v>
+      </c>
+      <c r="E354" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F352" s="1" t="s">
+      <c r="F354" s="1" t="s">
         <v>23</v>
       </c>
     </row>

--- a/CLB07N.xlsx
+++ b/CLB07N.xlsx
@@ -247,7 +247,7 @@
     <t>20037144</t>
   </si>
   <si>
-    <t>KAKI3 PENY.LECI 320</t>
+    <t>KAKI3 LECI 320 ML</t>
   </si>
   <si>
     <t>RT,(E-4B)</t>
@@ -256,13 +256,13 @@
     <t>20037150</t>
   </si>
   <si>
-    <t>KAKI3 PENY.JAMBU 320</t>
+    <t>KAKI3 JAMBU 320 ML</t>
   </si>
   <si>
     <t>20037147</t>
   </si>
   <si>
-    <t>KAKI TIGA STRO 320ML</t>
+    <t>KAKI3 STRO 320 ML</t>
   </si>
   <si>
     <t>20045995</t>
@@ -304,13 +304,13 @@
     <t>20069199</t>
   </si>
   <si>
-    <t>KAKI3 LMN.LM KLG 320</t>
+    <t>KAKI3 LMN.LM 320 ML</t>
   </si>
   <si>
     <t>20142024</t>
   </si>
   <si>
-    <t>COOLTOPIA MELON ORG</t>
+    <t>KAKI3 CLT MLN 320 ML</t>
   </si>
   <si>
     <t>20045996</t>
@@ -547,7 +547,7 @@
     <t>20114494</t>
   </si>
   <si>
-    <t>NSCAFE CRML MCTO 220</t>
+    <t>NSCAFE C MCTO 220 ML</t>
   </si>
   <si>
     <t>12</t>
@@ -556,25 +556,25 @@
     <t>20114495</t>
   </si>
   <si>
-    <t>NESCAFE CPUCCINO 220</t>
+    <t>NSCAFE CPCCN 220 ML</t>
   </si>
   <si>
     <t>20114493</t>
   </si>
   <si>
-    <t>NESCAFE LATTE 220ML</t>
+    <t>NSCAFE LATTE 220 ML</t>
   </si>
   <si>
     <t>20138057</t>
   </si>
   <si>
-    <t>NSCAFE GULA AREN 220</t>
+    <t>NSCAFE G AREN 220 ML</t>
   </si>
   <si>
     <t>20121456</t>
   </si>
   <si>
-    <t>NSCAFE ICE BLACK 220</t>
+    <t>NSCAFE I BLCK 220 ML</t>
   </si>
   <si>
     <t>20000787</t>
@@ -1678,13 +1678,13 @@
     <t>20140174</t>
   </si>
   <si>
-    <t>BEAR BRAND CLGEN 189</t>
+    <t>BEAR BRAND CO 189 ML</t>
   </si>
   <si>
     <t>10004906</t>
   </si>
   <si>
-    <t>BEAR BRAND STERIL189</t>
+    <t>BEAR BRAND ST 189 ML</t>
   </si>
   <si>
     <t>20136952</t>
@@ -2251,7 +2251,7 @@
     <t>20069208</t>
   </si>
   <si>
-    <t>LE MINERALE 600ML</t>
+    <t>LE MINERALE 600 ML</t>
   </si>
   <si>
     <t>44</t>

--- a/CLB07N.xlsx
+++ b/CLB07N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2124" uniqueCount="768">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2130" uniqueCount="770">
   <si>
     <t/>
   </si>
@@ -115,244 +115,865 @@
     <t>CHI/FRST WHT/PCH 480</t>
   </si>
   <si>
+    <t>20138893</t>
+  </si>
+  <si>
+    <t>AMO DRMY STRAW 200ML</t>
+  </si>
+  <si>
+    <t>20138894</t>
+  </si>
+  <si>
+    <t>AMO FIZZY EASY 200ML</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>20065778</t>
+  </si>
+  <si>
+    <t>COCA COLA PET 390 ML</t>
+  </si>
+  <si>
+    <t>20128821</t>
+  </si>
+  <si>
+    <t>COCA COLA ZERO 390ML</t>
+  </si>
+  <si>
+    <t>20140260</t>
+  </si>
+  <si>
+    <t>CC.COLA ZERO VAN 390</t>
+  </si>
+  <si>
+    <t>20065779</t>
+  </si>
+  <si>
+    <t>SPRITE PET 390 ML</t>
+  </si>
+  <si>
+    <t>20130667</t>
+  </si>
+  <si>
+    <t>SPRITE ZERO LIME 390</t>
+  </si>
+  <si>
+    <t>20065780</t>
+  </si>
+  <si>
+    <t>FANTA STRW PET 390ML</t>
+  </si>
+  <si>
+    <t>20142491</t>
+  </si>
+  <si>
+    <t>SPRITE NIPIS MINT390</t>
+  </si>
+  <si>
+    <t>20137093</t>
+  </si>
+  <si>
+    <t>FANTA ZERO STRAWB390</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>20093993</t>
+  </si>
+  <si>
+    <t>FANTA GRAPE 390ML</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>20123500</t>
+  </si>
+  <si>
+    <t>A&amp;W DRINK SARSA 250</t>
+  </si>
+  <si>
+    <t>20068089</t>
+  </si>
+  <si>
+    <t>GR.SANDS LMN&amp;GRP 250</t>
+  </si>
+  <si>
+    <t>10000107</t>
+  </si>
+  <si>
+    <t>GREEN SAND ORGNL 330</t>
+  </si>
+  <si>
+    <t>10033567</t>
+  </si>
+  <si>
+    <t>BINTANG ZERO KLG 330</t>
+  </si>
+  <si>
+    <t>10037437</t>
+  </si>
+  <si>
+    <t>C/B PENY.STRAW 320</t>
+  </si>
+  <si>
+    <t>10003627</t>
+  </si>
+  <si>
+    <t>C/B PENY.ORANGE320</t>
+  </si>
+  <si>
+    <t>10004237</t>
+  </si>
+  <si>
+    <t>C/B PENY.LECI 320ML</t>
+  </si>
+  <si>
+    <t>10003842</t>
+  </si>
+  <si>
+    <t>C/B PENY.JAMBU 320</t>
+  </si>
+  <si>
+    <t>20037144</t>
+  </si>
+  <si>
+    <t>KAKI3 PENY.LECI 320</t>
+  </si>
+  <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20037150</t>
+  </si>
+  <si>
+    <t>KAKI3 PENY.JAMBU 320</t>
+  </si>
+  <si>
+    <t>20037147</t>
+  </si>
+  <si>
+    <t>KAKI TIGA STRO 320ML</t>
+  </si>
+  <si>
+    <t>20045995</t>
+  </si>
+  <si>
+    <t>KAKI3 ANAK STRO 238</t>
+  </si>
+  <si>
+    <t>20053540</t>
+  </si>
+  <si>
+    <t>ADEM SARI CK BTL 350</t>
+  </si>
+  <si>
+    <t>20122090</t>
+  </si>
+  <si>
+    <t>ADEM/S MD LMN TEA350</t>
+  </si>
+  <si>
+    <t>20083775</t>
+  </si>
+  <si>
+    <t>ADEMSARI CK HR.T 320</t>
+  </si>
+  <si>
+    <t>20040276</t>
+  </si>
+  <si>
+    <t>ADEM SARI CK KLG 320</t>
+  </si>
+  <si>
+    <t>20071642</t>
+  </si>
+  <si>
+    <t>ADEMSARI CK SPRK 320</t>
+  </si>
+  <si>
+    <t>20069199</t>
+  </si>
+  <si>
+    <t>KAKI3 LMN.LM KLG 320</t>
+  </si>
+  <si>
+    <t>20142024</t>
+  </si>
+  <si>
+    <t>COOLTOPIA MELON ORG</t>
+  </si>
+  <si>
+    <t>20045996</t>
+  </si>
+  <si>
+    <t>KAKI3 ANAK LECI 238</t>
+  </si>
+  <si>
+    <t>20046315</t>
+  </si>
+  <si>
+    <t>MINUTE M. NB STRW300</t>
+  </si>
+  <si>
+    <t>20046314</t>
+  </si>
+  <si>
+    <t>MINUTE M. NB ORG 300</t>
+  </si>
+  <si>
+    <t>20133709</t>
+  </si>
+  <si>
+    <t>POLARIS SARSAPRLA330</t>
+  </si>
+  <si>
+    <t>20002209</t>
+  </si>
+  <si>
+    <t>TEBS SPRK MIX FRT330</t>
+  </si>
+  <si>
+    <t>20124713</t>
+  </si>
+  <si>
+    <t>LUWAK KOPI+GULA 220</t>
+  </si>
+  <si>
+    <t>20120499</t>
+  </si>
+  <si>
+    <t>K/A SIGNT STRONG 200</t>
+  </si>
+  <si>
+    <t>20089792</t>
+  </si>
+  <si>
+    <t>K/A DRNK BLK COFF200</t>
+  </si>
+  <si>
+    <t>20123322</t>
+  </si>
+  <si>
+    <t>GOLDA CAPPUCCINO 200</t>
+  </si>
+  <si>
+    <t>20087542</t>
+  </si>
+  <si>
+    <t>GOLDA COFF.DOLCE 200</t>
+  </si>
+  <si>
+    <t>20102789</t>
+  </si>
+  <si>
+    <t>ABC CHOCMLT COFF 180</t>
+  </si>
+  <si>
+    <t>20102790</t>
+  </si>
+  <si>
+    <t>ABC MILK COFFEE 180</t>
+  </si>
+  <si>
+    <t>20045415</t>
+  </si>
+  <si>
+    <t>KOPIKO 78C 240ML</t>
+  </si>
+  <si>
+    <t>20109969</t>
+  </si>
+  <si>
+    <t>KOPIKO LUCKY DAY 180</t>
+  </si>
+  <si>
+    <t>20120904</t>
+  </si>
+  <si>
+    <t>KK BLACK AREN 220ML</t>
+  </si>
+  <si>
+    <t>20120906</t>
+  </si>
+  <si>
+    <t>KK MANTANCINO 220ML</t>
+  </si>
+  <si>
+    <t>20133409</t>
+  </si>
+  <si>
+    <t>KK CAFFE LATTE 200ML</t>
+  </si>
+  <si>
+    <t>20138168</t>
+  </si>
+  <si>
+    <t>KK CHEESE LATTEE 200</t>
+  </si>
+  <si>
+    <t>20138167</t>
+  </si>
+  <si>
+    <t>KK JPNS MATCHA 200</t>
+  </si>
+  <si>
+    <t>20132760</t>
+  </si>
+  <si>
+    <t>CAFINO RTD ESPRSO200</t>
+  </si>
+  <si>
+    <t>20132761</t>
+  </si>
+  <si>
+    <t>CAFINO RTD CPCINO200</t>
+  </si>
+  <si>
+    <t>20138035</t>
+  </si>
+  <si>
+    <t>CAFFINO OATMARIE 200</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>20078206</t>
+  </si>
+  <si>
+    <t>LUWAK WHT ORGL 220ML</t>
+  </si>
+  <si>
+    <t>20076770</t>
+  </si>
+  <si>
+    <t>G/DAY CAPPUCCINO 230</t>
+  </si>
+  <si>
+    <t>20045674</t>
+  </si>
+  <si>
+    <t>G/DAY F.MOCACINO 230</t>
+  </si>
+  <si>
+    <t>20045673</t>
+  </si>
+  <si>
+    <t>G/DAY TIRAMISU/B 230</t>
+  </si>
+  <si>
+    <t>20056193</t>
+  </si>
+  <si>
+    <t>GOOD DAY AVCDO/D 230</t>
+  </si>
+  <si>
+    <t>20132329</t>
+  </si>
+  <si>
+    <t>GOOD DAY GRVY CKS230</t>
+  </si>
+  <si>
+    <t>20134557</t>
+  </si>
+  <si>
+    <t>OATSIDE CRML MCHT200</t>
+  </si>
+  <si>
+    <t>20129108</t>
+  </si>
+  <si>
+    <t>OATSDE COFFEE 200ML</t>
+  </si>
+  <si>
+    <t>20142499</t>
+  </si>
+  <si>
+    <t>OATSDE ESPR RST 240</t>
+  </si>
+  <si>
+    <t>20139577</t>
+  </si>
+  <si>
+    <t>PC AREN LATTE 210ML</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20139578</t>
+  </si>
+  <si>
+    <t>PC GOLDN CARAMEL 210</t>
+  </si>
+  <si>
+    <t>20139576</t>
+  </si>
+  <si>
+    <t>PC CRMY CPUCCINO 210</t>
+  </si>
+  <si>
+    <t>20142601</t>
+  </si>
+  <si>
+    <t>NSCAFE MTCHA ESP 220</t>
+  </si>
+  <si>
+    <t>20140431</t>
+  </si>
+  <si>
+    <t>NSCAFE KITKAT LAT220</t>
+  </si>
+  <si>
+    <t>20133058</t>
+  </si>
+  <si>
+    <t>NSCAFE OAT LATTE 220</t>
+  </si>
+  <si>
+    <t>20027768</t>
+  </si>
+  <si>
+    <t>NESCAFE COFF CRM 180</t>
+  </si>
+  <si>
+    <t>20114494</t>
+  </si>
+  <si>
+    <t>NSCAFE CRML MCTO 220</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>20114495</t>
+  </si>
+  <si>
+    <t>NESCAFE CPUCCINO 220</t>
+  </si>
+  <si>
+    <t>20114493</t>
+  </si>
+  <si>
+    <t>NESCAFE LATTE 220ML</t>
+  </si>
+  <si>
+    <t>20138057</t>
+  </si>
+  <si>
+    <t>NSCAFE GULA AREN 220</t>
+  </si>
+  <si>
+    <t>20121456</t>
+  </si>
+  <si>
+    <t>NSCAFE ICE BLACK 220</t>
+  </si>
+  <si>
+    <t>20000787</t>
+  </si>
+  <si>
+    <t>NESCAFE ICE.CF OR220</t>
+  </si>
+  <si>
+    <t>20014954</t>
+  </si>
+  <si>
+    <t>NESCAFE ICE.CF MC220</t>
+  </si>
+  <si>
+    <t>20000786</t>
+  </si>
+  <si>
+    <t>NESCAFE ICE.CF LT220</t>
+  </si>
+  <si>
+    <t>20125115</t>
+  </si>
+  <si>
+    <t>STARBUCKS LATTE 220</t>
+  </si>
+  <si>
+    <t>20125126</t>
+  </si>
+  <si>
+    <t>STARBUCKS CARAMEL220</t>
+  </si>
+  <si>
+    <t>20014608</t>
+  </si>
+  <si>
+    <t>HRMVTON PSK BUMI 150</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>10006263</t>
+  </si>
+  <si>
+    <t>HEMAVITON ENERGY 150</t>
+  </si>
+  <si>
+    <t>10002602</t>
+  </si>
+  <si>
+    <t>M-150 HEALT DRINK150</t>
+  </si>
+  <si>
+    <t>10002595</t>
+  </si>
+  <si>
+    <t>KRATINGDAENG 150 ML</t>
+  </si>
+  <si>
+    <t>10003427</t>
+  </si>
+  <si>
+    <t>KRATINGDAENG SPR.150</t>
+  </si>
+  <si>
+    <t>20022431</t>
+  </si>
+  <si>
+    <t>RED BULL E/DRNK 250</t>
+  </si>
+  <si>
+    <t>20056989</t>
+  </si>
+  <si>
+    <t>RED BULL GOLD 250ML</t>
+  </si>
+  <si>
+    <t>20138252</t>
+  </si>
+  <si>
+    <t>EXTRA JOSS ULTIMT250</t>
+  </si>
+  <si>
+    <t>20038425</t>
+  </si>
+  <si>
+    <t>NTRIVE/B BLCKRNT 100</t>
+  </si>
+  <si>
+    <t>20071510</t>
+  </si>
+  <si>
+    <t>NTRVE BNCOL LYCH 100</t>
+  </si>
+  <si>
+    <t>20003786</t>
+  </si>
+  <si>
+    <t>NU GREEN TEA HNY 450</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>20113059</t>
+  </si>
+  <si>
+    <t>NU YOGURT TEA 450ML</t>
+  </si>
+  <si>
+    <t>20139732</t>
+  </si>
+  <si>
+    <t>NU YOGRT TEA BRY 450</t>
+  </si>
+  <si>
+    <t>20036157</t>
+  </si>
+  <si>
+    <t>SOSRO TEH BOTOL 450</t>
+  </si>
+  <si>
+    <t>20002203</t>
+  </si>
+  <si>
+    <t>SOSRO F.TEA APEL 500</t>
+  </si>
+  <si>
+    <t>20003698</t>
+  </si>
+  <si>
+    <t>SOSRO FR.TEA XTRM500</t>
+  </si>
+  <si>
+    <t>20002205</t>
+  </si>
+  <si>
+    <t>SOSRO F.TEA BLKCR500</t>
+  </si>
+  <si>
+    <t>20134046</t>
+  </si>
+  <si>
+    <t>FRUIT TEA FREEZE 500</t>
+  </si>
+  <si>
+    <t>20126464</t>
+  </si>
+  <si>
+    <t>IDM TEH APL&amp;LYCHE350</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>20101897</t>
+  </si>
+  <si>
+    <t>IDM TEH APEL 350ML</t>
+  </si>
+  <si>
+    <t>20132840</t>
+  </si>
+  <si>
+    <t>IDM TEH BLCKCRRNT350</t>
+  </si>
+  <si>
+    <t>20066454</t>
+  </si>
+  <si>
+    <t>FRUIT TEA BLCKCR 350</t>
+  </si>
+  <si>
+    <t>20073495</t>
+  </si>
+  <si>
+    <t>FRUIT TEA FREEZE 350</t>
+  </si>
+  <si>
+    <t>20066455</t>
+  </si>
+  <si>
+    <t>FRUIT TEA APPLE 350</t>
+  </si>
+  <si>
+    <t>20079972</t>
+  </si>
+  <si>
+    <t>FRUIT TEA MRKISA 350</t>
+  </si>
+  <si>
+    <t>20138841</t>
+  </si>
+  <si>
+    <t>POKKA NAT. H.ORG 350</t>
+  </si>
+  <si>
     <t>20135619</t>
   </si>
   <si>
     <t>TEBS ZERO LYCHEE 300</t>
   </si>
   <si>
-    <t>20138893</t>
-  </si>
-  <si>
-    <t>AMO DRMY STRAW 200ML</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>20138894</t>
-  </si>
-  <si>
-    <t>AMO FIZZY EASY 200ML</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>20065778</t>
-  </si>
-  <si>
-    <t>COCA COLA PET 390 ML</t>
-  </si>
-  <si>
-    <t>20128821</t>
-  </si>
-  <si>
-    <t>COCA COLA ZERO 390ML</t>
-  </si>
-  <si>
-    <t>20140260</t>
-  </si>
-  <si>
-    <t>CC.COLA ZERO VAN 390</t>
-  </si>
-  <si>
-    <t>20065779</t>
-  </si>
-  <si>
-    <t>SPRITE PET 390 ML</t>
-  </si>
-  <si>
-    <t>20130667</t>
-  </si>
-  <si>
-    <t>SPRITE ZERO LIME 390</t>
-  </si>
-  <si>
-    <t>20065780</t>
-  </si>
-  <si>
-    <t>FANTA STRW PET 390ML</t>
-  </si>
-  <si>
-    <t>20142491</t>
-  </si>
-  <si>
-    <t>SPRITE NIPIS MINT390</t>
-  </si>
-  <si>
-    <t>20137093</t>
-  </si>
-  <si>
-    <t>FANTA ZERO STRAWB390</t>
-  </si>
-  <si>
-    <t>20093993</t>
-  </si>
-  <si>
-    <t>FANTA GRAPE 390ML</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>20123500</t>
-  </si>
-  <si>
-    <t>A&amp;W DRINK SARSA 250</t>
-  </si>
-  <si>
-    <t>20068089</t>
-  </si>
-  <si>
-    <t>GR.SANDS LMN&amp;GRP 250</t>
-  </si>
-  <si>
-    <t>10000107</t>
-  </si>
-  <si>
-    <t>GREEN SAND ORGNL 330</t>
-  </si>
-  <si>
-    <t>10033567</t>
-  </si>
-  <si>
-    <t>BINTANG ZERO KLG 330</t>
-  </si>
-  <si>
-    <t>10037437</t>
-  </si>
-  <si>
-    <t>C/B PENY.STRAW 320</t>
-  </si>
-  <si>
-    <t>10003627</t>
-  </si>
-  <si>
-    <t>C/B PENY.ORANGE320</t>
-  </si>
-  <si>
-    <t>10004237</t>
-  </si>
-  <si>
-    <t>C/B PENY.LECI 320ML</t>
-  </si>
-  <si>
-    <t>10003842</t>
-  </si>
-  <si>
-    <t>C/B PENY.JAMBU 320</t>
-  </si>
-  <si>
-    <t>20037144</t>
-  </si>
-  <si>
-    <t>KAKI3 LECI 320 ML</t>
-  </si>
-  <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20037150</t>
-  </si>
-  <si>
-    <t>KAKI3 JAMBU 320 ML</t>
-  </si>
-  <si>
-    <t>20037147</t>
-  </si>
-  <si>
-    <t>KAKI3 STRO 320 ML</t>
-  </si>
-  <si>
-    <t>20045995</t>
-  </si>
-  <si>
-    <t>KAKI3 ANAK STRO 238</t>
-  </si>
-  <si>
-    <t>20053540</t>
-  </si>
-  <si>
-    <t>ADEM SARI CK BTL 350</t>
-  </si>
-  <si>
-    <t>20122090</t>
-  </si>
-  <si>
-    <t>ADEM/S MD LMN TEA350</t>
-  </si>
-  <si>
-    <t>20083775</t>
-  </si>
-  <si>
-    <t>ADEMSARI CK HR.T 320</t>
-  </si>
-  <si>
-    <t>20040276</t>
-  </si>
-  <si>
-    <t>ADEM SARI CK KLG 320</t>
-  </si>
-  <si>
-    <t>20071642</t>
-  </si>
-  <si>
-    <t>ADEMSARI CK SPRK 320</t>
-  </si>
-  <si>
-    <t>20069199</t>
-  </si>
-  <si>
-    <t>KAKI3 LMN.LM 320 ML</t>
-  </si>
-  <si>
-    <t>20142024</t>
-  </si>
-  <si>
-    <t>KAKI3 CLT MLN 320 ML</t>
-  </si>
-  <si>
-    <t>20045996</t>
-  </si>
-  <si>
-    <t>KAKI3 ANAK LECI 238</t>
-  </si>
-  <si>
-    <t>20133709</t>
-  </si>
-  <si>
-    <t>POLARIS SARSAPRLA330</t>
-  </si>
-  <si>
-    <t>20102789</t>
-  </si>
-  <si>
-    <t>ABC CHOCMLT COFF 180</t>
-  </si>
-  <si>
-    <t>20102790</t>
-  </si>
-  <si>
-    <t>ABC MILK COFFEE 180</t>
-  </si>
-  <si>
-    <t>20120499</t>
-  </si>
-  <si>
-    <t>K/A SIGNT STRONG 200</t>
-  </si>
-  <si>
-    <t>20089792</t>
-  </si>
-  <si>
-    <t>K/A DRNK BLK COFF200</t>
-  </si>
-  <si>
-    <t>20124713</t>
-  </si>
-  <si>
-    <t>LUWAK KOPI+GULA 220</t>
+    <t>20060207</t>
+  </si>
+  <si>
+    <t>I/OCHA TEH MLATI 350</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>20048934</t>
+  </si>
+  <si>
+    <t>I/OCHA GRN TEA 350ML</t>
+  </si>
+  <si>
+    <t>20142077</t>
+  </si>
+  <si>
+    <t>TEH LEMON MADU 350ML</t>
+  </si>
+  <si>
+    <t>20018904</t>
+  </si>
+  <si>
+    <t>NU GREEN TEA HNY 330</t>
+  </si>
+  <si>
+    <t>20053867</t>
+  </si>
+  <si>
+    <t>TEH GELAS BTL 350ML</t>
+  </si>
+  <si>
+    <t>20073396</t>
+  </si>
+  <si>
+    <t>S-TEE BTL 390ML</t>
+  </si>
+  <si>
+    <t>20072249</t>
+  </si>
+  <si>
+    <t>SOSRO TEH BOTOL 350</t>
+  </si>
+  <si>
+    <t>20122278</t>
+  </si>
+  <si>
+    <t>TEH BOTOL LS.SGR 350</t>
+  </si>
+  <si>
+    <t>20082395</t>
+  </si>
+  <si>
+    <t>TEH BOTOL TAWAR 350</t>
+  </si>
+  <si>
+    <t>RT,(E-3.5B)</t>
+  </si>
+  <si>
+    <t>20035484</t>
+  </si>
+  <si>
+    <t>PUCUK/H TEH MLATI350</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>20048155</t>
+  </si>
+  <si>
+    <t>PUCUK/H TEH L/SGR350</t>
+  </si>
+  <si>
+    <t>20037565</t>
+  </si>
+  <si>
+    <t>PUCUK/H TEH MLATI500</t>
+  </si>
+  <si>
+    <t>20048348</t>
+  </si>
+  <si>
+    <t>PUCUK/H TEH L/SGR500</t>
+  </si>
+  <si>
+    <t>20026226</t>
+  </si>
+  <si>
+    <t>ULTRA TEH KOTAK 500</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>10036640</t>
+  </si>
+  <si>
+    <t>TEH KOTAK JASMINE300</t>
+  </si>
+  <si>
+    <t>20048435</t>
+  </si>
+  <si>
+    <t>TEH KOTAK LESS/S 300</t>
+  </si>
+  <si>
+    <t>20044334</t>
+  </si>
+  <si>
+    <t>SOSRO TEH BTL TPK300</t>
+  </si>
+  <si>
+    <t>10005128</t>
+  </si>
+  <si>
+    <t>SOSRO TEH KOTAK B250</t>
+  </si>
+  <si>
+    <t>20024315</t>
+  </si>
+  <si>
+    <t>TEH BOTOL LS.SGR 250</t>
+  </si>
+  <si>
+    <t>20100142</t>
+  </si>
+  <si>
+    <t>TEH KOTAK BLCKCR 300</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>20100143</t>
+  </si>
+  <si>
+    <t>TEH KOTAK APPLE 300</t>
+  </si>
+  <si>
+    <t>20137159</t>
+  </si>
+  <si>
+    <t>TEH KOTAK MANGGA 300</t>
+  </si>
+  <si>
+    <t>20087016</t>
+  </si>
+  <si>
+    <t>TEH KOTAK LEMON 300</t>
+  </si>
+  <si>
+    <t>20135647</t>
+  </si>
+  <si>
+    <t>TEH KOTAK LYCHEE 300</t>
+  </si>
+  <si>
+    <t>20117687</t>
+  </si>
+  <si>
+    <t>DLMNT BOBA MTCHA 240</t>
+  </si>
+  <si>
+    <t>20117682</t>
+  </si>
+  <si>
+    <t>DLMNT BOBA RD.VEL240</t>
+  </si>
+  <si>
+    <t>20080088</t>
+  </si>
+  <si>
+    <t>POKKA GREEN TEA 450</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>20036765</t>
+  </si>
+  <si>
+    <t>FRESTEA GRN MADU 500</t>
+  </si>
+  <si>
+    <t>20012574</t>
+  </si>
+  <si>
+    <t>FRESTEA TEH APEL 500</t>
+  </si>
+  <si>
+    <t>20035829</t>
+  </si>
+  <si>
+    <t>TEBS TEA WT/SODA 500</t>
   </si>
   <si>
     <t>20093586</t>
@@ -367,625 +988,16 @@
     <t>ICHTN DARK CHOCO 300</t>
   </si>
   <si>
-    <t>20123322</t>
-  </si>
-  <si>
-    <t>GOLDA CAPPUCCINO 200</t>
-  </si>
-  <si>
-    <t>20087542</t>
-  </si>
-  <si>
-    <t>GOLDA COFF.DOLCE 200</t>
-  </si>
-  <si>
-    <t>20109969</t>
-  </si>
-  <si>
-    <t>KOPIKO LUCKY DAY 180</t>
-  </si>
-  <si>
-    <t>20045415</t>
-  </si>
-  <si>
-    <t>KOPIKO 78C 240ML</t>
-  </si>
-  <si>
-    <t>20120904</t>
-  </si>
-  <si>
-    <t>KK BLACK AREN 220ML</t>
-  </si>
-  <si>
-    <t>20120906</t>
-  </si>
-  <si>
-    <t>KK MANTANCINO 220ML</t>
-  </si>
-  <si>
-    <t>20133409</t>
-  </si>
-  <si>
-    <t>KK CAFFE LATTE 200ML</t>
-  </si>
-  <si>
-    <t>20138168</t>
-  </si>
-  <si>
-    <t>KK CHEESE LATTEE 200</t>
-  </si>
-  <si>
-    <t>20138167</t>
-  </si>
-  <si>
-    <t>KK JPNS MATCHA 200</t>
-  </si>
-  <si>
-    <t>20132760</t>
-  </si>
-  <si>
-    <t>CAFINO RTD ESPRSO200</t>
-  </si>
-  <si>
-    <t>20132761</t>
-  </si>
-  <si>
-    <t>CAFINO RTD CPCINO200</t>
-  </si>
-  <si>
-    <t>20138035</t>
-  </si>
-  <si>
-    <t>CAFFINO OATMARIE 200</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>20078206</t>
-  </si>
-  <si>
-    <t>LUWAK WHT ORGL 220ML</t>
-  </si>
-  <si>
-    <t>20076770</t>
-  </si>
-  <si>
-    <t>G/DAY CAPPUCCINO 230</t>
-  </si>
-  <si>
-    <t>20045674</t>
-  </si>
-  <si>
-    <t>G/DAY F.MOCACINO 230</t>
-  </si>
-  <si>
-    <t>20045673</t>
-  </si>
-  <si>
-    <t>G/DAY TIRAMISU/B 230</t>
-  </si>
-  <si>
-    <t>20056193</t>
-  </si>
-  <si>
-    <t>GOOD DAY AVCDO/D 230</t>
-  </si>
-  <si>
-    <t>20132329</t>
-  </si>
-  <si>
-    <t>GOOD DAY GRVY CKS230</t>
-  </si>
-  <si>
-    <t>20134557</t>
-  </si>
-  <si>
-    <t>OATSIDE CRML MCHT200</t>
-  </si>
-  <si>
-    <t>20129108</t>
-  </si>
-  <si>
-    <t>OATSDE COFFEE 200ML</t>
-  </si>
-  <si>
-    <t>20142499</t>
-  </si>
-  <si>
-    <t>OATSDE ESPR RST 240</t>
-  </si>
-  <si>
-    <t>20139577</t>
-  </si>
-  <si>
-    <t>PC AREN LATTE 210ML</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20139578</t>
-  </si>
-  <si>
-    <t>PC GOLDN CARAMEL 210</t>
-  </si>
-  <si>
-    <t>20139576</t>
-  </si>
-  <si>
-    <t>PC CRMY CPUCCINO 210</t>
-  </si>
-  <si>
-    <t>20142601</t>
-  </si>
-  <si>
-    <t>NSCAFE MTCHA ESP 220</t>
-  </si>
-  <si>
-    <t>20140431</t>
-  </si>
-  <si>
-    <t>NSCAFE KITKAT LAT220</t>
-  </si>
-  <si>
-    <t>20133058</t>
-  </si>
-  <si>
-    <t>NSCAFE OAT LATTE 220</t>
-  </si>
-  <si>
-    <t>20027768</t>
-  </si>
-  <si>
-    <t>NESCAFE COFF CRM 180</t>
-  </si>
-  <si>
-    <t>20114494</t>
-  </si>
-  <si>
-    <t>NSCAFE C MCTO 220 ML</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>20114495</t>
-  </si>
-  <si>
-    <t>NSCAFE CPCCN 220 ML</t>
-  </si>
-  <si>
-    <t>20114493</t>
-  </si>
-  <si>
-    <t>NSCAFE LATTE 220 ML</t>
-  </si>
-  <si>
-    <t>20138057</t>
-  </si>
-  <si>
-    <t>NSCAFE G AREN 220 ML</t>
-  </si>
-  <si>
-    <t>20121456</t>
-  </si>
-  <si>
-    <t>NSCAFE I BLCK 220 ML</t>
-  </si>
-  <si>
-    <t>20000787</t>
-  </si>
-  <si>
-    <t>NESCAFE ICE.CF OR220</t>
-  </si>
-  <si>
-    <t>20014954</t>
-  </si>
-  <si>
-    <t>NESCAFE ICE.CF MC220</t>
-  </si>
-  <si>
-    <t>20000786</t>
-  </si>
-  <si>
-    <t>NESCAFE ICE.CF LT220</t>
-  </si>
-  <si>
-    <t>20125115</t>
-  </si>
-  <si>
-    <t>STARBUCKS LATTE 220</t>
-  </si>
-  <si>
-    <t>20125126</t>
-  </si>
-  <si>
-    <t>STARBUCKS CARAMEL220</t>
-  </si>
-  <si>
-    <t>20014608</t>
-  </si>
-  <si>
-    <t>HRMVTON PSK BUMI 150</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>10006263</t>
-  </si>
-  <si>
-    <t>HEMAVITON ENERGY 150</t>
-  </si>
-  <si>
-    <t>10002602</t>
-  </si>
-  <si>
-    <t>M-150 HEALT DRINK150</t>
-  </si>
-  <si>
-    <t>10002595</t>
-  </si>
-  <si>
-    <t>KRATINGDAENG 150 ML</t>
-  </si>
-  <si>
-    <t>10003427</t>
-  </si>
-  <si>
-    <t>KRATINGDAENG SPR.150</t>
-  </si>
-  <si>
-    <t>20022431</t>
-  </si>
-  <si>
-    <t>RED BULL E/DRNK 250</t>
-  </si>
-  <si>
-    <t>20056989</t>
-  </si>
-  <si>
-    <t>RED BULL GOLD 250ML</t>
-  </si>
-  <si>
-    <t>20138252</t>
-  </si>
-  <si>
-    <t>EXTRA JOSS ULTIMT250</t>
-  </si>
-  <si>
-    <t>20038425</t>
-  </si>
-  <si>
-    <t>NTRIVE/B BLCKRNT 100</t>
-  </si>
-  <si>
-    <t>20071510</t>
-  </si>
-  <si>
-    <t>NTRVE BNCOL LYCH 100</t>
-  </si>
-  <si>
-    <t>20003786</t>
-  </si>
-  <si>
-    <t>NU GREEN TEA HNY 450</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>20113059</t>
-  </si>
-  <si>
-    <t>NU YOGURT TEA 450ML</t>
-  </si>
-  <si>
-    <t>20139732</t>
-  </si>
-  <si>
-    <t>NU YOGRT TEA BRY 450</t>
-  </si>
-  <si>
-    <t>20036157</t>
-  </si>
-  <si>
-    <t>SOSRO TEH BOTOL 450</t>
-  </si>
-  <si>
-    <t>20002203</t>
-  </si>
-  <si>
-    <t>SOSRO F.TEA APEL 500</t>
-  </si>
-  <si>
-    <t>20003698</t>
-  </si>
-  <si>
-    <t>SOSRO FR.TEA XTRM500</t>
-  </si>
-  <si>
-    <t>20002205</t>
-  </si>
-  <si>
-    <t>SOSRO F.TEA BLKCR500</t>
-  </si>
-  <si>
-    <t>20134046</t>
-  </si>
-  <si>
-    <t>FRUIT TEA FREEZE 500</t>
-  </si>
-  <si>
-    <t>20126464</t>
-  </si>
-  <si>
-    <t>IDM TEH APL&amp;LYCHE350</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>20101897</t>
-  </si>
-  <si>
-    <t>IDM TEH APEL 350ML</t>
-  </si>
-  <si>
-    <t>20132840</t>
-  </si>
-  <si>
-    <t>IDM TEH BLCKCRRNT350</t>
-  </si>
-  <si>
-    <t>20066454</t>
-  </si>
-  <si>
-    <t>FRUIT TEA BLCKCR 350</t>
-  </si>
-  <si>
-    <t>20073495</t>
-  </si>
-  <si>
-    <t>FRUIT TEA FREEZE 350</t>
-  </si>
-  <si>
-    <t>20066455</t>
-  </si>
-  <si>
-    <t>FRUIT TEA APPLE 350</t>
-  </si>
-  <si>
-    <t>20079972</t>
-  </si>
-  <si>
-    <t>FRUIT TEA MRKISA 350</t>
-  </si>
-  <si>
-    <t>20060207</t>
-  </si>
-  <si>
-    <t>I/OCHA TEH MLATI 350</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>20048934</t>
-  </si>
-  <si>
-    <t>I/OCHA GRN TEA 350ML</t>
-  </si>
-  <si>
-    <t>20142077</t>
-  </si>
-  <si>
-    <t>TEH LEMON MADU 350ML</t>
-  </si>
-  <si>
-    <t>20018904</t>
-  </si>
-  <si>
-    <t>NU GREEN TEA HNY 330</t>
-  </si>
-  <si>
-    <t>20053867</t>
-  </si>
-  <si>
-    <t>TEH GELAS BTL 350ML</t>
-  </si>
-  <si>
-    <t>20073396</t>
-  </si>
-  <si>
-    <t>S-TEE BTL 390ML</t>
-  </si>
-  <si>
-    <t>20072249</t>
-  </si>
-  <si>
-    <t>SOSRO TEH BOTOL 350</t>
-  </si>
-  <si>
-    <t>20122278</t>
-  </si>
-  <si>
-    <t>TEH BOTOL LS.SGR 350</t>
-  </si>
-  <si>
-    <t>20082395</t>
-  </si>
-  <si>
-    <t>TEH BOTOL TAWAR 350</t>
-  </si>
-  <si>
-    <t>RT,(E-3.5B)</t>
-  </si>
-  <si>
-    <t>20035484</t>
-  </si>
-  <si>
-    <t>PUCUK/H TEH MLATI350</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>20048155</t>
-  </si>
-  <si>
-    <t>PUCUK/H TEH L/SGR350</t>
-  </si>
-  <si>
-    <t>20037565</t>
-  </si>
-  <si>
-    <t>PUCUK/H TEH MLATI500</t>
-  </si>
-  <si>
-    <t>20048348</t>
-  </si>
-  <si>
-    <t>PUCUK/H TEH L/SGR500</t>
-  </si>
-  <si>
-    <t>20026226</t>
-  </si>
-  <si>
-    <t>ULTRA TEH KOTAK 500</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>10036640</t>
-  </si>
-  <si>
-    <t>TEH KOTAK JASMINE300</t>
-  </si>
-  <si>
-    <t>20048435</t>
-  </si>
-  <si>
-    <t>TEH KOTAK LESS/S 300</t>
-  </si>
-  <si>
-    <t>20044334</t>
-  </si>
-  <si>
-    <t>SOSRO TEH BTL TPK300</t>
-  </si>
-  <si>
-    <t>10005128</t>
-  </si>
-  <si>
-    <t>SOSRO TEH KOTAK B250</t>
-  </si>
-  <si>
-    <t>20024315</t>
-  </si>
-  <si>
-    <t>TEH BOTOL LS.SGR 250</t>
-  </si>
-  <si>
-    <t>20002209</t>
-  </si>
-  <si>
-    <t>TEBS SPRK MIX FRT330</t>
-  </si>
-  <si>
-    <t>20100142</t>
-  </si>
-  <si>
-    <t>TEH KOTAK BLCKCR 300</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>20100143</t>
-  </si>
-  <si>
-    <t>TEH KOTAK APPLE 300</t>
-  </si>
-  <si>
-    <t>20137159</t>
-  </si>
-  <si>
-    <t>TEH KOTAK MANGGA 300</t>
-  </si>
-  <si>
-    <t>20087016</t>
-  </si>
-  <si>
-    <t>TEH KOTAK LEMON 300</t>
-  </si>
-  <si>
-    <t>20135647</t>
-  </si>
-  <si>
-    <t>TEH KOTAK LYCHEE 300</t>
-  </si>
-  <si>
-    <t>20117687</t>
-  </si>
-  <si>
-    <t>DLMNT BOBA MTCHA 240</t>
-  </si>
-  <si>
-    <t>20117682</t>
-  </si>
-  <si>
-    <t>DLMNT BOBA RD.VEL240</t>
-  </si>
-  <si>
-    <t>20080088</t>
-  </si>
-  <si>
-    <t>POKKA GREEN TEA 450</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>20036765</t>
-  </si>
-  <si>
-    <t>FRESTEA GRN MADU 500</t>
-  </si>
-  <si>
-    <t>20012574</t>
-  </si>
-  <si>
-    <t>FRESTEA TEH APEL 500</t>
-  </si>
-  <si>
-    <t>20035829</t>
-  </si>
-  <si>
-    <t>TEBS TEA WT/SODA 500</t>
-  </si>
-  <si>
-    <t>20138841</t>
-  </si>
-  <si>
-    <t>POKKA NAT. H.ORG 350</t>
-  </si>
-  <si>
-    <t>20046315</t>
-  </si>
-  <si>
-    <t>MINUTE M. NB STRW300</t>
-  </si>
-  <si>
-    <t>20046314</t>
-  </si>
-  <si>
-    <t>MINUTE M. NB ORG 300</t>
+    <t>20135599</t>
+  </si>
+  <si>
+    <t>ICHTAN KRN BANANA300</t>
+  </si>
+  <si>
+    <t>20142025</t>
+  </si>
+  <si>
+    <t>ICHITAN MLN MILK 300</t>
   </si>
   <si>
     <t>20040383</t>
@@ -1015,36 +1027,36 @@
     <t>NU MATCHA LATTEA 330</t>
   </si>
   <si>
+    <t>20141981</t>
+  </si>
+  <si>
+    <t>DUM2 CHO MILK TEA330</t>
+  </si>
+  <si>
+    <t>20141980</t>
+  </si>
+  <si>
+    <t>DUM2 RYL MILK TEA330</t>
+  </si>
+  <si>
+    <t>20085054</t>
+  </si>
+  <si>
+    <t>ICHTN THAI M.TEA 300</t>
+  </si>
+  <si>
+    <t>20101102</t>
+  </si>
+  <si>
+    <t>ICHTN MLK GR.TEA 300</t>
+  </si>
+  <si>
     <t>20113450</t>
   </si>
   <si>
     <t>ICHITAN MLK BRWN 300</t>
   </si>
   <si>
-    <t>20135599</t>
-  </si>
-  <si>
-    <t>ICHTAN KRN BANANA300</t>
-  </si>
-  <si>
-    <t>20142025</t>
-  </si>
-  <si>
-    <t>ICHITAN MLN MILK 300</t>
-  </si>
-  <si>
-    <t>20085054</t>
-  </si>
-  <si>
-    <t>ICHTN THAI M.TEA 300</t>
-  </si>
-  <si>
-    <t>20101102</t>
-  </si>
-  <si>
-    <t>ICHTN MLK GR.TEA 300</t>
-  </si>
-  <si>
     <t>20113377</t>
   </si>
   <si>
@@ -1072,6 +1084,12 @@
     <t>FRUITAMIN LYCHE 350</t>
   </si>
   <si>
+    <t>20091654</t>
+  </si>
+  <si>
+    <t>COCO BIT SP.GUAV 350</t>
+  </si>
+  <si>
     <t>20140331</t>
   </si>
   <si>
@@ -1090,18 +1108,6 @@
     <t>COCO BIT HOK.MLN 350</t>
   </si>
   <si>
-    <t>20141981</t>
-  </si>
-  <si>
-    <t>DUM2 CHO MILK TEA330</t>
-  </si>
-  <si>
-    <t>20141980</t>
-  </si>
-  <si>
-    <t>DUM2 RYL MILK TEA330</t>
-  </si>
-  <si>
     <t>20042848</t>
   </si>
   <si>
@@ -1678,13 +1684,13 @@
     <t>20140174</t>
   </si>
   <si>
-    <t>BEAR BRAND CO 189 ML</t>
+    <t>BEAR BRAND CLGEN 189</t>
   </si>
   <si>
     <t>10004906</t>
   </si>
   <si>
-    <t>BEAR BRAND ST 189 ML</t>
+    <t>BEAR BRAND STERIL189</t>
   </si>
   <si>
     <t>20136952</t>
@@ -2251,7 +2257,7 @@
     <t>20069208</t>
   </si>
   <si>
-    <t>LE MINERALE 600 ML</t>
+    <t>LE MINERALE 600ML</t>
   </si>
   <si>
     <t>44</t>
@@ -2302,19 +2308,19 @@
     <t>NESTLE PURE LIFE 600</t>
   </si>
   <si>
+    <t>20135462</t>
+  </si>
+  <si>
+    <t>DNCW MLKY CKS&amp;CRM180</t>
+  </si>
+  <si>
+    <t>998</t>
+  </si>
+  <si>
     <t>20135463</t>
   </si>
   <si>
     <t>DNCW MLKY CHO.HZL180</t>
-  </si>
-  <si>
-    <t>998</t>
-  </si>
-  <si>
-    <t>20135462</t>
-  </si>
-  <si>
-    <t>DNCW MLKY CKS&amp;CRM180</t>
   </si>
 </sst>
 </file>
@@ -2707,7 +2713,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F354"/>
+  <dimension ref="A1:F355"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -3009,21 +3015,21 @@
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
@@ -3032,7 +3038,7 @@
         <v>11</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>5</v>
@@ -3040,10 +3046,10 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>44</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>45</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
@@ -3052,7 +3058,7 @@
         <v>11</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>5</v>
@@ -3060,10 +3066,10 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>46</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>47</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
@@ -3072,7 +3078,7 @@
         <v>11</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>5</v>
@@ -3080,10 +3086,10 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>48</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>49</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
@@ -3092,7 +3098,7 @@
         <v>11</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>5</v>
@@ -3100,10 +3106,10 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>50</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>51</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
@@ -3112,7 +3118,7 @@
         <v>11</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>5</v>
@@ -3120,10 +3126,10 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>53</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
@@ -3132,7 +3138,7 @@
         <v>11</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>5</v>
@@ -3140,10 +3146,10 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>54</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>55</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
@@ -3152,7 +3158,7 @@
         <v>11</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>5</v>
@@ -3172,7 +3178,7 @@
         <v>11</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>5</v>
@@ -3180,19 +3186,19 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>5</v>
@@ -3212,10 +3218,10 @@
         <v>14</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -3232,7 +3238,7 @@
         <v>14</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>23</v>
@@ -3252,7 +3258,7 @@
         <v>14</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>23</v>
@@ -3269,13 +3275,13 @@
         <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -3292,7 +3298,7 @@
         <v>17</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>28</v>
@@ -3312,7 +3318,7 @@
         <v>17</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>28</v>
@@ -3332,7 +3338,7 @@
         <v>17</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>28</v>
@@ -3352,18 +3358,18 @@
         <v>17</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>28</v>
+        <v>77</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
@@ -3372,10 +3378,10 @@
         <v>17</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -3392,10 +3398,10 @@
         <v>17</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -3412,10 +3418,10 @@
         <v>17</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -3429,13 +3435,13 @@
         <v>3</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>79</v>
+        <v>23</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -3452,10 +3458,10 @@
         <v>20</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -3472,10 +3478,10 @@
         <v>20</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -3492,7 +3498,7 @@
         <v>20</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>23</v>
@@ -3512,7 +3518,7 @@
         <v>20</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>23</v>
@@ -3532,10 +3538,10 @@
         <v>20</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>23</v>
+        <v>77</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -3552,10 +3558,10 @@
         <v>20</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -3572,10 +3578,10 @@
         <v>20</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -3589,13 +3595,13 @@
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>79</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -3612,10 +3618,10 @@
         <v>38</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -3635,7 +3641,7 @@
         <v>11</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -3655,7 +3661,7 @@
         <v>14</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>79</v>
+        <v>23</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -3675,7 +3681,7 @@
         <v>17</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -3715,7 +3721,7 @@
         <v>38</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -3729,13 +3735,13 @@
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -3749,7 +3755,7 @@
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>8</v>
@@ -3769,13 +3775,13 @@
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>23</v>
+        <v>77</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -3789,13 +3795,13 @@
         <v>3</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>23</v>
+        <v>77</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -3809,10 +3815,10 @@
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>23</v>
@@ -3829,10 +3835,10 @@
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>23</v>
@@ -3849,7 +3855,7 @@
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>11</v>
@@ -3869,7 +3875,7 @@
         <v>3</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>14</v>
@@ -3889,7 +3895,7 @@
         <v>3</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>17</v>
@@ -3909,7 +3915,7 @@
         <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>20</v>
@@ -3929,7 +3935,7 @@
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>38</v>
@@ -3949,10 +3955,10 @@
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>23</v>
@@ -3969,10 +3975,10 @@
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>23</v>
@@ -3989,7 +3995,7 @@
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>142</v>
@@ -4152,7 +4158,7 @@
         <v>142</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>23</v>
@@ -4172,7 +4178,7 @@
         <v>142</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>23</v>
@@ -4472,7 +4478,7 @@
         <v>179</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>31</v>
@@ -4492,7 +4498,7 @@
         <v>179</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>23</v>
@@ -4575,7 +4581,7 @@
         <v>11</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
@@ -4672,7 +4678,7 @@
         <v>200</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>23</v>
@@ -4692,7 +4698,7 @@
         <v>200</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>5</v>
@@ -4872,7 +4878,7 @@
         <v>221</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>23</v>
@@ -4892,7 +4898,7 @@
         <v>238</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>164</v>
@@ -4912,7 +4918,7 @@
         <v>238</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>164</v>
@@ -4932,7 +4938,7 @@
         <v>238</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>164</v>
@@ -4952,7 +4958,7 @@
         <v>238</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>23</v>
@@ -4972,7 +4978,7 @@
         <v>238</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>23</v>
@@ -4992,7 +4998,7 @@
         <v>238</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>23</v>
@@ -5012,7 +5018,7 @@
         <v>238</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>23</v>
@@ -5029,10 +5035,10 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>253</v>
+        <v>238</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>23</v>
@@ -5040,19 +5046,19 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B117" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="B117" s="1" t="s">
-        <v>255</v>
-      </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>253</v>
+        <v>238</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>23</v>
@@ -5060,19 +5066,19 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="B118" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="B118" s="1" t="s">
+      <c r="C118" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D118" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="C118" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D118" s="1" t="s">
-        <v>253</v>
-      </c>
       <c r="E118" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>23</v>
@@ -5089,10 +5095,10 @@
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>23</v>
@@ -5109,10 +5115,10 @@
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>23</v>
@@ -5129,10 +5135,10 @@
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>23</v>
@@ -5149,10 +5155,10 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>23</v>
@@ -5169,10 +5175,10 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>23</v>
@@ -5189,30 +5195,30 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>270</v>
+        <v>23</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="B125" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="B125" s="1" t="s">
-        <v>272</v>
-      </c>
       <c r="C125" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>273</v>
+        <v>257</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>23</v>
@@ -5220,39 +5226,39 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="E126" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F126" s="1" t="s">
         <v>274</v>
-      </c>
-      <c r="B126" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="C126" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D126" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="E126" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F126" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="B127" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="B127" s="1" t="s">
+      <c r="C127" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D127" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="C127" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D127" s="1" t="s">
-        <v>273</v>
-      </c>
       <c r="E127" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>23</v>
@@ -5269,10 +5275,10 @@
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>23</v>
@@ -5289,10 +5295,10 @@
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>23</v>
@@ -5300,19 +5306,19 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="B130" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="B130" s="1" t="s">
-        <v>284</v>
-      </c>
       <c r="C130" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>23</v>
@@ -5320,19 +5326,19 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B131" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="B131" s="1" t="s">
+      <c r="C131" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D131" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="C131" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D131" s="1" t="s">
-        <v>282</v>
-      </c>
       <c r="E131" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>23</v>
@@ -5349,10 +5355,10 @@
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>23</v>
@@ -5369,10 +5375,10 @@
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>23</v>
@@ -5389,10 +5395,10 @@
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>23</v>
@@ -5409,10 +5415,10 @@
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>23</v>
@@ -5429,10 +5435,10 @@
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>297</v>
+        <v>286</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>23</v>
@@ -5440,19 +5446,19 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="B137" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="B137" s="1" t="s">
+      <c r="C137" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D137" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="C137" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D137" s="1" t="s">
-        <v>297</v>
-      </c>
       <c r="E137" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>23</v>
@@ -5469,10 +5475,10 @@
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>23</v>
@@ -5489,10 +5495,10 @@
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>23</v>
@@ -5509,10 +5515,10 @@
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>23</v>
@@ -5529,13 +5535,13 @@
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
@@ -5549,10 +5555,10 @@
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>28</v>
@@ -5569,33 +5575,33 @@
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="B144" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="B144" s="1" t="s">
+      <c r="C144" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D144" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="C144" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D144" s="1" t="s">
-        <v>312</v>
-      </c>
       <c r="E144" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
@@ -5609,10 +5615,10 @@
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>5</v>
@@ -5629,13 +5635,13 @@
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
@@ -5649,10 +5655,10 @@
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>23</v>
@@ -5669,13 +5675,13 @@
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
@@ -5689,13 +5695,13 @@
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
@@ -5709,10 +5715,10 @@
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>327</v>
+        <v>314</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>23</v>
@@ -5720,19 +5726,19 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B151" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="B151" s="1" t="s">
-        <v>329</v>
-      </c>
       <c r="C151" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>327</v>
+        <v>314</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>23</v>
@@ -5740,19 +5746,19 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="B152" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="B152" s="1" t="s">
+      <c r="C152" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D152" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="C152" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D152" s="1" t="s">
-        <v>327</v>
-      </c>
       <c r="E152" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>23</v>
@@ -5769,10 +5775,10 @@
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>23</v>
@@ -5789,13 +5795,13 @@
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
@@ -5809,10 +5815,10 @@
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>23</v>
@@ -5829,10 +5835,10 @@
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>23</v>
@@ -5849,13 +5855,13 @@
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
@@ -5869,10 +5875,10 @@
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>31</v>
@@ -5889,53 +5895,53 @@
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>346</v>
+        <v>331</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B160" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="B160" s="1" t="s">
-        <v>348</v>
-      </c>
       <c r="C160" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>346</v>
+        <v>331</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="B161" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="B161" s="1" t="s">
+      <c r="C161" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D161" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="C161" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D161" s="1" t="s">
-        <v>346</v>
-      </c>
       <c r="E161" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
@@ -5949,10 +5955,10 @@
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>23</v>
@@ -5969,13 +5975,13 @@
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
@@ -5989,10 +5995,10 @@
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>23</v>
@@ -6009,10 +6015,10 @@
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>23</v>
@@ -6029,10 +6035,10 @@
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>23</v>
@@ -6049,10 +6055,10 @@
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>23</v>
@@ -6069,10 +6075,10 @@
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>365</v>
+        <v>350</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>23</v>
@@ -6080,19 +6086,19 @@
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="B169" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="B169" s="1" t="s">
+      <c r="C169" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D169" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="C169" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D169" s="1" t="s">
-        <v>365</v>
-      </c>
       <c r="E169" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>23</v>
@@ -6109,10 +6115,10 @@
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F170" s="1" t="s">
         <v>23</v>
@@ -6129,10 +6135,10 @@
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>23</v>
@@ -6149,10 +6155,10 @@
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>23</v>
@@ -6169,10 +6175,10 @@
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>23</v>
@@ -6189,10 +6195,10 @@
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>23</v>
@@ -6209,33 +6215,33 @@
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>380</v>
+        <v>367</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B176" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="B176" s="1" t="s">
+      <c r="C176" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D176" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="C176" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D176" s="1" t="s">
-        <v>380</v>
-      </c>
       <c r="E176" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
@@ -6249,10 +6255,10 @@
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F177" s="1" t="s">
         <v>23</v>
@@ -6269,33 +6275,33 @@
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>387</v>
+        <v>23</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="B179" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="B179" s="1" t="s">
+      <c r="C179" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D179" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="E179" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F179" s="1" t="s">
         <v>389</v>
-      </c>
-      <c r="C179" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D179" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="E179" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F179" s="1" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
@@ -6309,13 +6315,13 @@
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>23</v>
+        <v>389</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
@@ -6329,13 +6335,13 @@
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
@@ -6349,10 +6355,10 @@
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>28</v>
@@ -6369,33 +6375,33 @@
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>398</v>
+        <v>382</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="B184" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="B184" s="1" t="s">
+      <c r="C184" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D184" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="C184" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D184" s="1" t="s">
-        <v>398</v>
-      </c>
       <c r="E184" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
@@ -6409,13 +6415,13 @@
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
@@ -6429,13 +6435,13 @@
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
@@ -6449,13 +6455,13 @@
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>23</v>
+        <v>77</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
@@ -6469,13 +6475,13 @@
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
@@ -6489,10 +6495,10 @@
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F189" s="1" t="s">
         <v>31</v>
@@ -6509,13 +6515,13 @@
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
@@ -6529,10 +6535,10 @@
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F191" s="1" t="s">
         <v>23</v>
@@ -6549,10 +6555,10 @@
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>417</v>
+        <v>400</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="F192" s="1" t="s">
         <v>23</v>
@@ -6560,19 +6566,19 @@
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="B193" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="B193" s="1" t="s">
+      <c r="C193" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D193" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="C193" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D193" s="1" t="s">
-        <v>417</v>
-      </c>
       <c r="E193" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F193" s="1" t="s">
         <v>23</v>
@@ -6589,10 +6595,10 @@
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F194" s="1" t="s">
         <v>23</v>
@@ -6609,10 +6615,10 @@
         <v>3</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>23</v>
@@ -6629,10 +6635,10 @@
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F196" s="1" t="s">
         <v>23</v>
@@ -6649,13 +6655,13 @@
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>164</v>
+        <v>23</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
@@ -6669,10 +6675,10 @@
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F198" s="1" t="s">
         <v>164</v>
@@ -6689,13 +6695,13 @@
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F199" s="1" t="s">
-        <v>23</v>
+        <v>164</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
@@ -6709,10 +6715,10 @@
         <v>3</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>142</v>
+        <v>55</v>
       </c>
       <c r="F200" s="1" t="s">
         <v>23</v>
@@ -6729,10 +6735,10 @@
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>436</v>
+        <v>419</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="F201" s="1" t="s">
         <v>23</v>
@@ -6740,19 +6746,19 @@
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="B202" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="B202" s="1" t="s">
+      <c r="C202" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D202" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="C202" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D202" s="1" t="s">
-        <v>436</v>
-      </c>
       <c r="E202" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F202" s="1" t="s">
         <v>23</v>
@@ -6769,10 +6775,10 @@
         <v>3</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F203" s="1" t="s">
         <v>23</v>
@@ -6789,10 +6795,10 @@
         <v>3</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F204" s="1" t="s">
         <v>23</v>
@@ -6809,10 +6815,10 @@
         <v>3</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F205" s="1" t="s">
         <v>23</v>
@@ -6829,10 +6835,10 @@
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F206" s="1" t="s">
         <v>23</v>
@@ -6849,10 +6855,10 @@
         <v>3</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F207" s="1" t="s">
         <v>23</v>
@@ -6869,10 +6875,10 @@
         <v>3</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F208" s="1" t="s">
         <v>23</v>
@@ -6889,10 +6895,10 @@
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F209" s="1" t="s">
         <v>23</v>
@@ -6909,10 +6915,10 @@
         <v>3</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>455</v>
+        <v>438</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="F210" s="1" t="s">
         <v>23</v>
@@ -6920,19 +6926,19 @@
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="B211" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="B211" s="1" t="s">
+      <c r="C211" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D211" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="C211" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D211" s="1" t="s">
-        <v>455</v>
-      </c>
       <c r="E211" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F211" s="1" t="s">
         <v>23</v>
@@ -6949,10 +6955,10 @@
         <v>3</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F212" s="1" t="s">
         <v>23</v>
@@ -6969,10 +6975,10 @@
         <v>3</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F213" s="1" t="s">
         <v>23</v>
@@ -6989,10 +6995,10 @@
         <v>3</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F214" s="1" t="s">
         <v>23</v>
@@ -7009,10 +7015,10 @@
         <v>3</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F215" s="1" t="s">
         <v>23</v>
@@ -7029,10 +7035,10 @@
         <v>3</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F216" s="1" t="s">
         <v>23</v>
@@ -7049,13 +7055,13 @@
         <v>3</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F217" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
@@ -7069,13 +7075,13 @@
         <v>3</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F218" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
@@ -7089,10 +7095,10 @@
         <v>3</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>474</v>
+        <v>457</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="F219" s="1" t="s">
         <v>23</v>
@@ -7100,19 +7106,19 @@
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="B220" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="B220" s="1" t="s">
+      <c r="C220" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D220" s="1" t="s">
         <v>476</v>
       </c>
-      <c r="C220" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D220" s="1" t="s">
-        <v>474</v>
-      </c>
       <c r="E220" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F220" s="1" t="s">
         <v>23</v>
@@ -7129,10 +7135,10 @@
         <v>3</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F221" s="1" t="s">
         <v>23</v>
@@ -7149,10 +7155,10 @@
         <v>3</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F222" s="1" t="s">
         <v>23</v>
@@ -7169,13 +7175,13 @@
         <v>3</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F223" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
@@ -7189,10 +7195,10 @@
         <v>3</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F224" s="1" t="s">
         <v>31</v>
@@ -7209,13 +7215,13 @@
         <v>3</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>164</v>
+        <v>31</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
@@ -7229,10 +7235,10 @@
         <v>3</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F226" s="1" t="s">
         <v>164</v>
@@ -7249,30 +7255,30 @@
         <v>3</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>491</v>
+        <v>476</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>31</v>
+        <v>164</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="B228" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="B228" s="1" t="s">
+      <c r="C228" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D228" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="C228" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D228" s="1" t="s">
-        <v>491</v>
-      </c>
       <c r="E228" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F228" s="1" t="s">
         <v>31</v>
@@ -7289,10 +7295,10 @@
         <v>3</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F229" s="1" t="s">
         <v>31</v>
@@ -7309,10 +7315,10 @@
         <v>3</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F230" s="1" t="s">
         <v>31</v>
@@ -7329,10 +7335,10 @@
         <v>3</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F231" s="1" t="s">
         <v>31</v>
@@ -7349,13 +7355,13 @@
         <v>3</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F232" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
@@ -7369,10 +7375,10 @@
         <v>3</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F233" s="1" t="s">
         <v>23</v>
@@ -7389,30 +7395,30 @@
         <v>3</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>506</v>
+        <v>493</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F234" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="B235" s="1" t="s">
         <v>507</v>
       </c>
-      <c r="B235" s="1" t="s">
+      <c r="C235" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D235" s="1" t="s">
         <v>508</v>
       </c>
-      <c r="C235" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D235" s="1" t="s">
-        <v>506</v>
-      </c>
       <c r="E235" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F235" s="1" t="s">
         <v>31</v>
@@ -7429,10 +7435,10 @@
         <v>3</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F236" s="1" t="s">
         <v>31</v>
@@ -7449,13 +7455,13 @@
         <v>3</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="E237" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F237" s="1" t="s">
-        <v>164</v>
+        <v>31</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
@@ -7469,33 +7475,33 @@
         <v>3</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="E238" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F238" s="1" t="s">
-        <v>515</v>
+        <v>164</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="B239" s="1" t="s">
         <v>516</v>
       </c>
-      <c r="B239" s="1" t="s">
+      <c r="C239" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D239" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="E239" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F239" s="1" t="s">
         <v>517</v>
-      </c>
-      <c r="C239" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D239" s="1" t="s">
-        <v>506</v>
-      </c>
-      <c r="E239" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F239" s="1" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
@@ -7509,13 +7515,13 @@
         <v>3</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="E240" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F240" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
@@ -7529,13 +7535,13 @@
         <v>3</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="E241" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F241" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
@@ -7549,13 +7555,13 @@
         <v>3</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="E242" s="1" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F242" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
@@ -7569,10 +7575,10 @@
         <v>3</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>526</v>
+        <v>508</v>
       </c>
       <c r="E243" s="1" t="s">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="F243" s="1" t="s">
         <v>23</v>
@@ -7580,19 +7586,19 @@
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="B244" s="1" t="s">
         <v>527</v>
       </c>
-      <c r="B244" s="1" t="s">
+      <c r="C244" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D244" s="1" t="s">
         <v>528</v>
       </c>
-      <c r="C244" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D244" s="1" t="s">
-        <v>526</v>
-      </c>
       <c r="E244" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F244" s="1" t="s">
         <v>23</v>
@@ -7609,10 +7615,10 @@
         <v>3</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F245" s="1" t="s">
         <v>23</v>
@@ -7629,10 +7635,10 @@
         <v>3</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F246" s="1" t="s">
         <v>23</v>
@@ -7649,13 +7655,13 @@
         <v>3</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F247" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
@@ -7669,13 +7675,13 @@
         <v>3</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F248" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
@@ -7689,10 +7695,10 @@
         <v>3</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F249" s="1" t="s">
         <v>31</v>
@@ -7709,10 +7715,10 @@
         <v>3</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E250" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F250" s="1" t="s">
         <v>31</v>
@@ -7729,30 +7735,30 @@
         <v>3</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>543</v>
+        <v>528</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="F251" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="B252" s="1" t="s">
         <v>544</v>
       </c>
-      <c r="B252" s="1" t="s">
+      <c r="C252" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D252" s="1" t="s">
         <v>545</v>
       </c>
-      <c r="C252" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D252" s="1" t="s">
-        <v>543</v>
-      </c>
       <c r="E252" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F252" s="1" t="s">
         <v>23</v>
@@ -7769,10 +7775,10 @@
         <v>3</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F253" s="1" t="s">
         <v>23</v>
@@ -7789,10 +7795,10 @@
         <v>3</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F254" s="1" t="s">
         <v>23</v>
@@ -7809,13 +7815,13 @@
         <v>3</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F255" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
@@ -7829,13 +7835,13 @@
         <v>3</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="E256" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F256" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
@@ -7849,10 +7855,10 @@
         <v>3</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="E257" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F257" s="1" t="s">
         <v>23</v>
@@ -7869,10 +7875,10 @@
         <v>3</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F258" s="1" t="s">
         <v>23</v>
@@ -7889,30 +7895,30 @@
         <v>3</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>560</v>
+        <v>545</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="F259" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="B260" s="1" t="s">
         <v>561</v>
       </c>
-      <c r="B260" s="1" t="s">
-        <v>559</v>
-      </c>
       <c r="C260" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F260" s="1" t="s">
         <v>28</v>
@@ -7920,22 +7926,22 @@
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="B261" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="C261" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D261" s="1" t="s">
         <v>562</v>
       </c>
-      <c r="B261" s="1" t="s">
-        <v>563</v>
-      </c>
-      <c r="C261" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D261" s="1" t="s">
-        <v>560</v>
-      </c>
       <c r="E261" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F261" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
@@ -7949,10 +7955,10 @@
         <v>3</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F262" s="1" t="s">
         <v>23</v>
@@ -7969,10 +7975,10 @@
         <v>3</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="E263" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F263" s="1" t="s">
         <v>23</v>
@@ -7989,10 +7995,10 @@
         <v>3</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="E264" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F264" s="1" t="s">
         <v>23</v>
@@ -8009,10 +8015,10 @@
         <v>3</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="E265" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F265" s="1" t="s">
         <v>23</v>
@@ -8029,10 +8035,10 @@
         <v>3</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F266" s="1" t="s">
         <v>23</v>
@@ -8049,10 +8055,10 @@
         <v>3</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="E267" s="1" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F267" s="1" t="s">
         <v>23</v>
@@ -8069,10 +8075,10 @@
         <v>3</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>578</v>
+        <v>562</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="F268" s="1" t="s">
         <v>23</v>
@@ -8080,19 +8086,19 @@
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="B269" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="B269" s="1" t="s">
+      <c r="C269" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D269" s="1" t="s">
         <v>580</v>
       </c>
-      <c r="C269" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D269" s="1" t="s">
-        <v>578</v>
-      </c>
       <c r="E269" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F269" s="1" t="s">
         <v>23</v>
@@ -8109,10 +8115,10 @@
         <v>3</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="E270" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F270" s="1" t="s">
         <v>23</v>
@@ -8129,10 +8135,10 @@
         <v>3</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="E271" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F271" s="1" t="s">
         <v>23</v>
@@ -8149,10 +8155,10 @@
         <v>3</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="E272" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F272" s="1" t="s">
         <v>23</v>
@@ -8169,10 +8175,10 @@
         <v>3</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F273" s="1" t="s">
         <v>23</v>
@@ -8189,10 +8195,10 @@
         <v>3</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F274" s="1" t="s">
         <v>23</v>
@@ -8209,10 +8215,10 @@
         <v>3</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="E275" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F275" s="1" t="s">
         <v>23</v>
@@ -8229,10 +8235,10 @@
         <v>3</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="E276" s="1" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F276" s="1" t="s">
         <v>23</v>
@@ -8249,10 +8255,10 @@
         <v>3</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="E277" s="1" t="s">
-        <v>142</v>
+        <v>58</v>
       </c>
       <c r="F277" s="1" t="s">
         <v>23</v>
@@ -8269,10 +8275,10 @@
         <v>3</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>163</v>
+        <v>142</v>
       </c>
       <c r="F278" s="1" t="s">
         <v>23</v>
@@ -8289,10 +8295,10 @@
         <v>3</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>601</v>
+        <v>580</v>
       </c>
       <c r="E279" s="1" t="s">
-        <v>4</v>
+        <v>163</v>
       </c>
       <c r="F279" s="1" t="s">
         <v>23</v>
@@ -8300,19 +8306,19 @@
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="B280" s="1" t="s">
         <v>602</v>
       </c>
-      <c r="B280" s="1" t="s">
+      <c r="C280" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D280" s="1" t="s">
         <v>603</v>
       </c>
-      <c r="C280" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D280" s="1" t="s">
-        <v>601</v>
-      </c>
       <c r="E280" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F280" s="1" t="s">
         <v>23</v>
@@ -8329,10 +8335,10 @@
         <v>3</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="E281" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F281" s="1" t="s">
         <v>23</v>
@@ -8349,10 +8355,10 @@
         <v>3</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="E282" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F282" s="1" t="s">
         <v>23</v>
@@ -8369,10 +8375,10 @@
         <v>3</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="E283" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F283" s="1" t="s">
         <v>23</v>
@@ -8389,10 +8395,10 @@
         <v>3</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F284" s="1" t="s">
         <v>23</v>
@@ -8409,33 +8415,33 @@
         <v>3</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="E285" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F285" s="1" t="s">
-        <v>614</v>
+        <v>23</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A286" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="B286" s="1" t="s">
         <v>615</v>
       </c>
-      <c r="B286" s="1" t="s">
+      <c r="C286" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D286" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="E286" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F286" s="1" t="s">
         <v>616</v>
-      </c>
-      <c r="C286" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D286" s="1" t="s">
-        <v>601</v>
-      </c>
-      <c r="E286" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F286" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
@@ -8449,10 +8455,10 @@
         <v>3</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F287" s="1" t="s">
         <v>23</v>
@@ -8469,10 +8475,10 @@
         <v>3</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>142</v>
+        <v>58</v>
       </c>
       <c r="F288" s="1" t="s">
         <v>23</v>
@@ -8489,33 +8495,33 @@
         <v>3</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>623</v>
+        <v>603</v>
       </c>
       <c r="E289" s="1" t="s">
-        <v>4</v>
+        <v>142</v>
       </c>
       <c r="F289" s="1" t="s">
-        <v>614</v>
+        <v>23</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290" s="1" t="s">
+        <v>623</v>
+      </c>
+      <c r="B290" s="1" t="s">
         <v>624</v>
       </c>
-      <c r="B290" s="1" t="s">
+      <c r="C290" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D290" s="1" t="s">
         <v>625</v>
       </c>
-      <c r="C290" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D290" s="1" t="s">
-        <v>623</v>
-      </c>
       <c r="E290" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F290" s="1" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
@@ -8529,13 +8535,13 @@
         <v>3</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F291" s="1" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
@@ -8549,13 +8555,13 @@
         <v>3</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="E292" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F292" s="1" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
@@ -8569,13 +8575,13 @@
         <v>3</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="E293" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F293" s="1" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
@@ -8589,13 +8595,13 @@
         <v>3</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="E294" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F294" s="1" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
@@ -8609,13 +8615,13 @@
         <v>3</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="E295" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F295" s="1" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
@@ -8629,13 +8635,13 @@
         <v>3</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="E296" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F296" s="1" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
@@ -8649,13 +8655,13 @@
         <v>3</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F297" s="1" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
@@ -8669,30 +8675,30 @@
         <v>3</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>642</v>
+        <v>625</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="F298" s="1" t="s">
-        <v>23</v>
+        <v>616</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A299" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="B299" s="1" t="s">
         <v>643</v>
       </c>
-      <c r="B299" s="1" t="s">
+      <c r="C299" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D299" s="1" t="s">
         <v>644</v>
       </c>
-      <c r="C299" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D299" s="1" t="s">
-        <v>642</v>
-      </c>
       <c r="E299" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F299" s="1" t="s">
         <v>23</v>
@@ -8709,10 +8715,10 @@
         <v>3</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F300" s="1" t="s">
         <v>23</v>
@@ -8729,10 +8735,10 @@
         <v>3</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="E301" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F301" s="1" t="s">
         <v>23</v>
@@ -8749,10 +8755,10 @@
         <v>3</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="E302" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F302" s="1" t="s">
         <v>23</v>
@@ -8769,10 +8775,10 @@
         <v>3</v>
       </c>
       <c r="D303" s="1" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="E303" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F303" s="1" t="s">
         <v>23</v>
@@ -8789,10 +8795,10 @@
         <v>3</v>
       </c>
       <c r="D304" s="1" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="E304" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F304" s="1" t="s">
         <v>23</v>
@@ -8809,10 +8815,10 @@
         <v>3</v>
       </c>
       <c r="D305" s="1" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="E305" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F305" s="1" t="s">
         <v>23</v>
@@ -8829,10 +8835,10 @@
         <v>3</v>
       </c>
       <c r="D306" s="1" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="E306" s="1" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F306" s="1" t="s">
         <v>23</v>
@@ -8849,10 +8855,10 @@
         <v>3</v>
       </c>
       <c r="D307" s="1" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="E307" s="1" t="s">
-        <v>142</v>
+        <v>58</v>
       </c>
       <c r="F307" s="1" t="s">
         <v>23</v>
@@ -8869,10 +8875,10 @@
         <v>3</v>
       </c>
       <c r="D308" s="1" t="s">
-        <v>663</v>
+        <v>644</v>
       </c>
       <c r="E308" s="1" t="s">
-        <v>4</v>
+        <v>142</v>
       </c>
       <c r="F308" s="1" t="s">
         <v>23</v>
@@ -8880,19 +8886,19 @@
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A309" s="1" t="s">
+        <v>663</v>
+      </c>
+      <c r="B309" s="1" t="s">
         <v>664</v>
       </c>
-      <c r="B309" s="1" t="s">
+      <c r="C309" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D309" s="1" t="s">
         <v>665</v>
       </c>
-      <c r="C309" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D309" s="1" t="s">
-        <v>663</v>
-      </c>
       <c r="E309" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F309" s="1" t="s">
         <v>23</v>
@@ -8909,10 +8915,10 @@
         <v>3</v>
       </c>
       <c r="D310" s="1" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="E310" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F310" s="1" t="s">
         <v>23</v>
@@ -8929,10 +8935,10 @@
         <v>3</v>
       </c>
       <c r="D311" s="1" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="E311" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F311" s="1" t="s">
         <v>23</v>
@@ -8949,10 +8955,10 @@
         <v>3</v>
       </c>
       <c r="D312" s="1" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="E312" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F312" s="1" t="s">
         <v>23</v>
@@ -8969,10 +8975,10 @@
         <v>3</v>
       </c>
       <c r="D313" s="1" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="E313" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F313" s="1" t="s">
         <v>23</v>
@@ -8989,10 +8995,10 @@
         <v>3</v>
       </c>
       <c r="D314" s="1" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="E314" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F314" s="1" t="s">
         <v>23</v>
@@ -9009,10 +9015,10 @@
         <v>3</v>
       </c>
       <c r="D315" s="1" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="E315" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F315" s="1" t="s">
         <v>23</v>
@@ -9029,10 +9035,10 @@
         <v>3</v>
       </c>
       <c r="D316" s="1" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="E316" s="1" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F316" s="1" t="s">
         <v>23</v>
@@ -9049,10 +9055,10 @@
         <v>3</v>
       </c>
       <c r="D317" s="1" t="s">
-        <v>682</v>
+        <v>665</v>
       </c>
       <c r="E317" s="1" t="s">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="F317" s="1" t="s">
         <v>23</v>
@@ -9060,19 +9066,19 @@
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A318" s="1" t="s">
+        <v>682</v>
+      </c>
+      <c r="B318" s="1" t="s">
         <v>683</v>
       </c>
-      <c r="B318" s="1" t="s">
+      <c r="C318" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D318" s="1" t="s">
         <v>684</v>
       </c>
-      <c r="C318" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D318" s="1" t="s">
-        <v>682</v>
-      </c>
       <c r="E318" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F318" s="1" t="s">
         <v>23</v>
@@ -9089,10 +9095,10 @@
         <v>3</v>
       </c>
       <c r="D319" s="1" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="E319" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F319" s="1" t="s">
         <v>23</v>
@@ -9109,10 +9115,10 @@
         <v>3</v>
       </c>
       <c r="D320" s="1" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="E320" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F320" s="1" t="s">
         <v>23</v>
@@ -9129,10 +9135,10 @@
         <v>3</v>
       </c>
       <c r="D321" s="1" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="E321" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F321" s="1" t="s">
         <v>23</v>
@@ -9149,10 +9155,10 @@
         <v>3</v>
       </c>
       <c r="D322" s="1" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="E322" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F322" s="1" t="s">
         <v>23</v>
@@ -9169,10 +9175,10 @@
         <v>3</v>
       </c>
       <c r="D323" s="1" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="E323" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F323" s="1" t="s">
         <v>23</v>
@@ -9189,10 +9195,10 @@
         <v>3</v>
       </c>
       <c r="D324" s="1" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="E324" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F324" s="1" t="s">
         <v>23</v>
@@ -9209,10 +9215,10 @@
         <v>3</v>
       </c>
       <c r="D325" s="1" t="s">
-        <v>699</v>
+        <v>684</v>
       </c>
       <c r="E325" s="1" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="F325" s="1" t="s">
         <v>23</v>
@@ -9220,19 +9226,19 @@
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A326" s="1" t="s">
+        <v>699</v>
+      </c>
+      <c r="B326" s="1" t="s">
         <v>700</v>
       </c>
-      <c r="B326" s="1" t="s">
+      <c r="C326" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D326" s="1" t="s">
         <v>701</v>
       </c>
-      <c r="C326" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D326" s="1" t="s">
-        <v>699</v>
-      </c>
       <c r="E326" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F326" s="1" t="s">
         <v>23</v>
@@ -9249,13 +9255,13 @@
         <v>3</v>
       </c>
       <c r="D327" s="1" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="E327" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F327" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.25">
@@ -9269,10 +9275,10 @@
         <v>3</v>
       </c>
       <c r="D328" s="1" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="E328" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F328" s="1" t="s">
         <v>31</v>
@@ -9289,13 +9295,13 @@
         <v>3</v>
       </c>
       <c r="D329" s="1" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="E329" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F329" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.25">
@@ -9309,10 +9315,10 @@
         <v>3</v>
       </c>
       <c r="D330" s="1" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="E330" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F330" s="1" t="s">
         <v>23</v>
@@ -9329,10 +9335,10 @@
         <v>3</v>
       </c>
       <c r="D331" s="1" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="E331" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F331" s="1" t="s">
         <v>23</v>
@@ -9349,10 +9355,10 @@
         <v>3</v>
       </c>
       <c r="D332" s="1" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="E332" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F332" s="1" t="s">
         <v>23</v>
@@ -9369,10 +9375,10 @@
         <v>3</v>
       </c>
       <c r="D333" s="1" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="E333" s="1" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F333" s="1" t="s">
         <v>23</v>
@@ -9389,10 +9395,10 @@
         <v>3</v>
       </c>
       <c r="D334" s="1" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="E334" s="1" t="s">
-        <v>142</v>
+        <v>58</v>
       </c>
       <c r="F334" s="1" t="s">
         <v>23</v>
@@ -9409,33 +9415,33 @@
         <v>3</v>
       </c>
       <c r="D335" s="1" t="s">
-        <v>720</v>
+        <v>701</v>
       </c>
       <c r="E335" s="1" t="s">
-        <v>4</v>
+        <v>142</v>
       </c>
       <c r="F335" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A336" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="B336" s="1" t="s">
         <v>721</v>
       </c>
-      <c r="B336" s="1" t="s">
+      <c r="C336" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D336" s="1" t="s">
         <v>722</v>
       </c>
-      <c r="C336" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D336" s="1" t="s">
-        <v>720</v>
-      </c>
       <c r="E336" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F336" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.25">
@@ -9449,13 +9455,13 @@
         <v>3</v>
       </c>
       <c r="D337" s="1" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="E337" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F337" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.25">
@@ -9469,13 +9475,13 @@
         <v>3</v>
       </c>
       <c r="D338" s="1" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="E338" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F338" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.25">
@@ -9489,13 +9495,13 @@
         <v>3</v>
       </c>
       <c r="D339" s="1" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="E339" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F339" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.25">
@@ -9509,10 +9515,10 @@
         <v>3</v>
       </c>
       <c r="D340" s="1" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="E340" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F340" s="1" t="s">
         <v>23</v>
@@ -9529,13 +9535,13 @@
         <v>3</v>
       </c>
       <c r="D341" s="1" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="E341" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F341" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.25">
@@ -9549,33 +9555,33 @@
         <v>3</v>
       </c>
       <c r="D342" s="1" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="E342" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F342" s="1" t="s">
-        <v>735</v>
+        <v>31</v>
       </c>
     </row>
     <row r="343" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A343" s="1" t="s">
+        <v>735</v>
+      </c>
+      <c r="B343" s="1" t="s">
         <v>736</v>
       </c>
-      <c r="B343" s="1" t="s">
+      <c r="C343" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D343" s="1" t="s">
+        <v>722</v>
+      </c>
+      <c r="E343" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F343" s="1" t="s">
         <v>737</v>
-      </c>
-      <c r="C343" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D343" s="1" t="s">
-        <v>720</v>
-      </c>
-      <c r="E343" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="F343" s="1" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.25">
@@ -9589,30 +9595,30 @@
         <v>3</v>
       </c>
       <c r="D344" s="1" t="s">
-        <v>740</v>
+        <v>722</v>
       </c>
       <c r="E344" s="1" t="s">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="F344" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A345" s="1" t="s">
+        <v>740</v>
+      </c>
+      <c r="B345" s="1" t="s">
         <v>741</v>
       </c>
-      <c r="B345" s="1" t="s">
+      <c r="C345" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D345" s="1" t="s">
         <v>742</v>
       </c>
-      <c r="C345" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D345" s="1" t="s">
-        <v>740</v>
-      </c>
       <c r="E345" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F345" s="1" t="s">
         <v>23</v>
@@ -9629,13 +9635,13 @@
         <v>3</v>
       </c>
       <c r="D346" s="1" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="E346" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F346" s="1" t="s">
-        <v>164</v>
+        <v>23</v>
       </c>
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.25">
@@ -9649,113 +9655,113 @@
         <v>3</v>
       </c>
       <c r="D347" s="1" t="s">
-        <v>747</v>
+        <v>742</v>
       </c>
       <c r="E347" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F347" s="1" t="s">
-        <v>23</v>
+        <v>164</v>
       </c>
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A348" s="1" t="s">
+        <v>747</v>
+      </c>
+      <c r="B348" s="1" t="s">
         <v>748</v>
       </c>
-      <c r="B348" s="1" t="s">
+      <c r="C348" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D348" s="1" t="s">
         <v>749</v>
-      </c>
-      <c r="C348" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D348" s="1" t="s">
-        <v>750</v>
       </c>
       <c r="E348" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F348" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A349" s="1" t="s">
+        <v>750</v>
+      </c>
+      <c r="B349" s="1" t="s">
         <v>751</v>
       </c>
-      <c r="B349" s="1" t="s">
+      <c r="C349" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D349" s="1" t="s">
         <v>752</v>
-      </c>
-      <c r="C349" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D349" s="1" t="s">
-        <v>753</v>
       </c>
       <c r="E349" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F349" s="1" t="s">
-        <v>754</v>
+        <v>28</v>
       </c>
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A350" s="1" t="s">
+        <v>753</v>
+      </c>
+      <c r="B350" s="1" t="s">
+        <v>754</v>
+      </c>
+      <c r="C350" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D350" s="1" t="s">
         <v>755</v>
       </c>
-      <c r="B350" s="1" t="s">
+      <c r="E350" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F350" s="1" t="s">
         <v>756</v>
-      </c>
-      <c r="C350" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D350" s="1" t="s">
-        <v>753</v>
-      </c>
-      <c r="E350" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F350" s="1" t="s">
-        <v>757</v>
       </c>
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A351" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="B351" s="1" t="s">
         <v>758</v>
       </c>
-      <c r="B351" s="1" t="s">
+      <c r="C351" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D351" s="1" t="s">
+        <v>755</v>
+      </c>
+      <c r="E351" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F351" s="1" t="s">
         <v>759</v>
-      </c>
-      <c r="C351" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D351" s="1" t="s">
-        <v>753</v>
-      </c>
-      <c r="E351" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F351" s="1" t="s">
-        <v>760</v>
       </c>
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A352" s="1" t="s">
+        <v>760</v>
+      </c>
+      <c r="B352" s="1" t="s">
         <v>761</v>
       </c>
-      <c r="B352" s="1" t="s">
+      <c r="C352" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D352" s="1" t="s">
+        <v>755</v>
+      </c>
+      <c r="E352" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F352" s="1" t="s">
         <v>762</v>
-      </c>
-      <c r="C352" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D352" s="1" t="s">
-        <v>753</v>
-      </c>
-      <c r="E352" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F352" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="353" spans="1:6" x14ac:dyDescent="0.25">
@@ -9769,10 +9775,10 @@
         <v>3</v>
       </c>
       <c r="D353" s="1" t="s">
-        <v>765</v>
+        <v>755</v>
       </c>
       <c r="E353" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F353" s="1" t="s">
         <v>23</v>
@@ -9780,21 +9786,41 @@
     </row>
     <row r="354" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A354" s="1" t="s">
+        <v>765</v>
+      </c>
+      <c r="B354" s="1" t="s">
         <v>766</v>
       </c>
-      <c r="B354" s="1" t="s">
+      <c r="C354" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D354" s="1" t="s">
         <v>767</v>
       </c>
-      <c r="C354" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D354" s="1" t="s">
-        <v>765</v>
-      </c>
       <c r="E354" s="1" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F354" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="355" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A355" s="1" t="s">
+        <v>768</v>
+      </c>
+      <c r="B355" s="1" t="s">
+        <v>769</v>
+      </c>
+      <c r="C355" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D355" s="1" t="s">
+        <v>767</v>
+      </c>
+      <c r="E355" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F355" s="1" t="s">
         <v>23</v>
       </c>
     </row>

--- a/CLB07N.xlsx
+++ b/CLB07N.xlsx
@@ -1672,7 +1672,7 @@
     <t>20133805</t>
   </si>
   <si>
-    <t>ENTRASOL STERIL 180</t>
+    <t>ENTRSL OLIVE STRL180</t>
   </si>
   <si>
     <t>20134968</t>

--- a/CLB07N.xlsx
+++ b/CLB07N.xlsx
@@ -6681,7 +6681,7 @@
         <v>20</v>
       </c>
       <c r="F198" s="1" t="s">
-        <v>164</v>
+        <v>23</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
@@ -6701,7 +6701,7 @@
         <v>38</v>
       </c>
       <c r="F199" s="1" t="s">
-        <v>164</v>
+        <v>23</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">

--- a/CLB07N.xlsx
+++ b/CLB07N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2130" uniqueCount="770">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2130" uniqueCount="769">
   <si>
     <t/>
   </si>
@@ -865,43 +865,58 @@
     <t>PUCUK/H TEH L/SGR500</t>
   </si>
   <si>
+    <t>10036640</t>
+  </si>
+  <si>
+    <t>TEH KOTAK JASMINE300</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>20048435</t>
+  </si>
+  <si>
+    <t>TEH KOTAK LESS/S 300</t>
+  </si>
+  <si>
+    <t>20143447</t>
+  </si>
+  <si>
+    <t>PUCUK/H TEH ORI 300</t>
+  </si>
+  <si>
+    <t>20143446</t>
+  </si>
+  <si>
+    <t>PUCUK/H TEH L/SGR300</t>
+  </si>
+  <si>
+    <t>20044334</t>
+  </si>
+  <si>
+    <t>SOSRO TEH BTL TPK300</t>
+  </si>
+  <si>
+    <t>10005128</t>
+  </si>
+  <si>
+    <t>SOSRO TEH KOTAK B250</t>
+  </si>
+  <si>
+    <t>20024315</t>
+  </si>
+  <si>
+    <t>TEH BOTOL LS.SGR 250</t>
+  </si>
+  <si>
     <t>20026226</t>
   </si>
   <si>
     <t>ULTRA TEH KOTAK 500</t>
   </si>
   <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>10036640</t>
-  </si>
-  <si>
-    <t>TEH KOTAK JASMINE300</t>
-  </si>
-  <si>
-    <t>20048435</t>
-  </si>
-  <si>
-    <t>TEH KOTAK LESS/S 300</t>
-  </si>
-  <si>
-    <t>20044334</t>
-  </si>
-  <si>
-    <t>SOSRO TEH BTL TPK300</t>
-  </si>
-  <si>
-    <t>10005128</t>
-  </si>
-  <si>
-    <t>SOSRO TEH KOTAK B250</t>
-  </si>
-  <si>
-    <t>20024315</t>
-  </si>
-  <si>
-    <t>TEH BOTOL LS.SGR 250</t>
+    <t>19</t>
   </si>
   <si>
     <t>20100142</t>
@@ -910,9 +925,6 @@
     <t>TEH KOTAK BLCKCR 300</t>
   </si>
   <si>
-    <t>19</t>
-  </si>
-  <si>
     <t>20100143</t>
   </si>
   <si>
@@ -2306,21 +2318,6 @@
   </si>
   <si>
     <t>NESTLE PURE LIFE 600</t>
-  </si>
-  <si>
-    <t>20135462</t>
-  </si>
-  <si>
-    <t>DNCW MLKY CKS&amp;CRM180</t>
-  </si>
-  <si>
-    <t>998</t>
-  </si>
-  <si>
-    <t>20135463</t>
-  </si>
-  <si>
-    <t>DNCW MLKY CHO.HZL180</t>
   </si>
 </sst>
 </file>
@@ -2719,8 +2716,7 @@
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="5" customWidth="1"/>
-    <col min="5" max="5" width="4" customWidth="1"/>
+    <col min="4" max="5" width="4" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5455,10 +5451,10 @@
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>299</v>
+        <v>286</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>23</v>
@@ -5466,19 +5462,19 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="B138" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="B138" s="1" t="s">
+      <c r="C138" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D138" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="C138" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D138" s="1" t="s">
-        <v>299</v>
-      </c>
       <c r="E138" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>23</v>
@@ -5495,10 +5491,10 @@
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>23</v>
@@ -5515,10 +5511,10 @@
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>23</v>
@@ -5535,10 +5531,10 @@
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>23</v>
@@ -5555,13 +5551,13 @@
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
@@ -5575,13 +5571,13 @@
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
@@ -5595,53 +5591,53 @@
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>314</v>
+        <v>301</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="B145" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="B145" s="1" t="s">
-        <v>316</v>
-      </c>
       <c r="C145" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>314</v>
+        <v>301</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="B146" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="B146" s="1" t="s">
+      <c r="C146" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D146" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="C146" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D146" s="1" t="s">
-        <v>314</v>
-      </c>
       <c r="E146" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
@@ -5655,13 +5651,13 @@
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
@@ -5675,13 +5671,13 @@
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
@@ -5695,10 +5691,10 @@
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>23</v>
@@ -5715,13 +5711,13 @@
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
@@ -5735,10 +5731,10 @@
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>23</v>
@@ -5755,10 +5751,10 @@
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>331</v>
+        <v>318</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>23</v>
@@ -5766,19 +5762,19 @@
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="B153" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="B153" s="1" t="s">
-        <v>333</v>
-      </c>
       <c r="C153" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>331</v>
+        <v>318</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>23</v>
@@ -5786,19 +5782,19 @@
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="B154" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="B154" s="1" t="s">
+      <c r="C154" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D154" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="C154" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D154" s="1" t="s">
-        <v>331</v>
-      </c>
       <c r="E154" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>23</v>
@@ -5815,10 +5811,10 @@
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>23</v>
@@ -5835,10 +5831,10 @@
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>23</v>
@@ -5855,10 +5851,10 @@
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>23</v>
@@ -5875,13 +5871,13 @@
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
@@ -5895,13 +5891,13 @@
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
@@ -5915,10 +5911,10 @@
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>31</v>
@@ -5935,53 +5931,53 @@
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>350</v>
+        <v>335</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="B162" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="B162" s="1" t="s">
-        <v>352</v>
-      </c>
       <c r="C162" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>350</v>
+        <v>335</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="B163" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="B163" s="1" t="s">
+      <c r="C163" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D163" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="C163" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D163" s="1" t="s">
-        <v>350</v>
-      </c>
       <c r="E163" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
@@ -5995,10 +5991,10 @@
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>23</v>
@@ -6015,13 +6011,13 @@
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
@@ -6035,10 +6031,10 @@
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>23</v>
@@ -6055,10 +6051,10 @@
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>23</v>
@@ -6075,10 +6071,10 @@
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>23</v>
@@ -6095,10 +6091,10 @@
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>23</v>
@@ -6106,19 +6102,19 @@
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="B170" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="B170" s="1" t="s">
-        <v>369</v>
-      </c>
       <c r="C170" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="F170" s="1" t="s">
         <v>23</v>
@@ -6126,19 +6122,19 @@
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="B171" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="B171" s="1" t="s">
+      <c r="C171" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D171" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="C171" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D171" s="1" t="s">
-        <v>367</v>
-      </c>
       <c r="E171" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>23</v>
@@ -6155,10 +6151,10 @@
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>23</v>
@@ -6175,10 +6171,10 @@
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>23</v>
@@ -6195,10 +6191,10 @@
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>23</v>
@@ -6215,10 +6211,10 @@
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>23</v>
@@ -6235,30 +6231,30 @@
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>382</v>
+        <v>371</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="B177" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="B177" s="1" t="s">
-        <v>384</v>
-      </c>
       <c r="C177" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>382</v>
+        <v>371</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="F177" s="1" t="s">
         <v>23</v>
@@ -6266,22 +6262,22 @@
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="B178" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="B178" s="1" t="s">
+      <c r="C178" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D178" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="C178" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D178" s="1" t="s">
-        <v>382</v>
-      </c>
       <c r="E178" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
@@ -6295,53 +6291,53 @@
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>389</v>
+        <v>23</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="B180" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="B180" s="1" t="s">
-        <v>391</v>
-      </c>
       <c r="C180" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>389</v>
+        <v>23</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="B181" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="B181" s="1" t="s">
+      <c r="C181" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D181" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="E181" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F181" s="1" t="s">
         <v>393</v>
-      </c>
-      <c r="C181" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D181" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="E181" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F181" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
@@ -6355,13 +6351,13 @@
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>28</v>
+        <v>393</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
@@ -6375,13 +6371,13 @@
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
@@ -6395,53 +6391,53 @@
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>400</v>
+        <v>386</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B185" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="B185" s="1" t="s">
-        <v>402</v>
-      </c>
       <c r="C185" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>400</v>
+        <v>386</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="B186" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="B186" s="1" t="s">
+      <c r="C186" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D186" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="C186" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D186" s="1" t="s">
-        <v>400</v>
-      </c>
       <c r="E186" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
@@ -6455,13 +6451,13 @@
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>77</v>
+        <v>31</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
@@ -6475,13 +6471,13 @@
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
@@ -6495,13 +6491,13 @@
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>31</v>
+        <v>77</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
@@ -6515,13 +6511,13 @@
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
@@ -6535,13 +6531,13 @@
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
@@ -6555,13 +6551,13 @@
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
@@ -6575,10 +6571,10 @@
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>419</v>
+        <v>404</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="F193" s="1" t="s">
         <v>23</v>
@@ -6586,19 +6582,19 @@
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="B194" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="B194" s="1" t="s">
-        <v>421</v>
-      </c>
       <c r="C194" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>419</v>
+        <v>404</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="F194" s="1" t="s">
         <v>23</v>
@@ -6606,19 +6602,19 @@
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="B195" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="B195" s="1" t="s">
+      <c r="C195" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D195" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="C195" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D195" s="1" t="s">
-        <v>419</v>
-      </c>
       <c r="E195" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>23</v>
@@ -6635,10 +6631,10 @@
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F196" s="1" t="s">
         <v>23</v>
@@ -6655,10 +6651,10 @@
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F197" s="1" t="s">
         <v>23</v>
@@ -6675,10 +6671,10 @@
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F198" s="1" t="s">
         <v>23</v>
@@ -6695,10 +6691,10 @@
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F199" s="1" t="s">
         <v>23</v>
@@ -6715,10 +6711,10 @@
         <v>3</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="F200" s="1" t="s">
         <v>23</v>
@@ -6735,10 +6731,10 @@
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F201" s="1" t="s">
         <v>23</v>
@@ -6755,10 +6751,10 @@
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>438</v>
+        <v>423</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="F202" s="1" t="s">
         <v>23</v>
@@ -6766,19 +6762,19 @@
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="B203" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="B203" s="1" t="s">
-        <v>440</v>
-      </c>
       <c r="C203" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>438</v>
+        <v>423</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="F203" s="1" t="s">
         <v>23</v>
@@ -6786,19 +6782,19 @@
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="B204" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="B204" s="1" t="s">
+      <c r="C204" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D204" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="C204" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D204" s="1" t="s">
-        <v>438</v>
-      </c>
       <c r="E204" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F204" s="1" t="s">
         <v>23</v>
@@ -6815,10 +6811,10 @@
         <v>3</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F205" s="1" t="s">
         <v>23</v>
@@ -6835,10 +6831,10 @@
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F206" s="1" t="s">
         <v>23</v>
@@ -6855,10 +6851,10 @@
         <v>3</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F207" s="1" t="s">
         <v>23</v>
@@ -6875,10 +6871,10 @@
         <v>3</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F208" s="1" t="s">
         <v>23</v>
@@ -6895,10 +6891,10 @@
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="F209" s="1" t="s">
         <v>23</v>
@@ -6915,10 +6911,10 @@
         <v>3</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F210" s="1" t="s">
         <v>23</v>
@@ -6935,10 +6931,10 @@
         <v>3</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>457</v>
+        <v>442</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="F211" s="1" t="s">
         <v>23</v>
@@ -6946,19 +6942,19 @@
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="B212" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="B212" s="1" t="s">
-        <v>459</v>
-      </c>
       <c r="C212" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>457</v>
+        <v>442</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="F212" s="1" t="s">
         <v>23</v>
@@ -6966,19 +6962,19 @@
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="B213" s="1" t="s">
         <v>460</v>
       </c>
-      <c r="B213" s="1" t="s">
+      <c r="C213" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D213" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="C213" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D213" s="1" t="s">
-        <v>457</v>
-      </c>
       <c r="E213" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F213" s="1" t="s">
         <v>23</v>
@@ -6995,10 +6991,10 @@
         <v>3</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F214" s="1" t="s">
         <v>23</v>
@@ -7015,10 +7011,10 @@
         <v>3</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F215" s="1" t="s">
         <v>23</v>
@@ -7035,10 +7031,10 @@
         <v>3</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F216" s="1" t="s">
         <v>23</v>
@@ -7055,10 +7051,10 @@
         <v>3</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F217" s="1" t="s">
         <v>23</v>
@@ -7075,13 +7071,13 @@
         <v>3</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="F218" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
@@ -7095,10 +7091,10 @@
         <v>3</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F219" s="1" t="s">
         <v>23</v>
@@ -7115,30 +7111,30 @@
         <v>3</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>476</v>
+        <v>461</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="B221" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="B221" s="1" t="s">
-        <v>478</v>
-      </c>
       <c r="C221" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>476</v>
+        <v>461</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="F221" s="1" t="s">
         <v>23</v>
@@ -7146,19 +7142,19 @@
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="B222" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="B222" s="1" t="s">
+      <c r="C222" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D222" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="C222" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D222" s="1" t="s">
-        <v>476</v>
-      </c>
       <c r="E222" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F222" s="1" t="s">
         <v>23</v>
@@ -7175,10 +7171,10 @@
         <v>3</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F223" s="1" t="s">
         <v>23</v>
@@ -7195,13 +7191,13 @@
         <v>3</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
@@ -7215,13 +7211,13 @@
         <v>3</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
@@ -7235,13 +7231,13 @@
         <v>3</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>164</v>
+        <v>31</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
@@ -7255,13 +7251,13 @@
         <v>3</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>164</v>
+        <v>31</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
@@ -7275,50 +7271,50 @@
         <v>3</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>493</v>
+        <v>480</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F228" s="1" t="s">
-        <v>31</v>
+        <v>164</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="B229" s="1" t="s">
         <v>494</v>
       </c>
-      <c r="B229" s="1" t="s">
-        <v>495</v>
-      </c>
       <c r="C229" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>493</v>
+        <v>480</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="F229" s="1" t="s">
-        <v>31</v>
+        <v>164</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="B230" s="1" t="s">
         <v>496</v>
       </c>
-      <c r="B230" s="1" t="s">
+      <c r="C230" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D230" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="C230" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D230" s="1" t="s">
-        <v>493</v>
-      </c>
       <c r="E230" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F230" s="1" t="s">
         <v>31</v>
@@ -7335,10 +7331,10 @@
         <v>3</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F231" s="1" t="s">
         <v>31</v>
@@ -7355,10 +7351,10 @@
         <v>3</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F232" s="1" t="s">
         <v>31</v>
@@ -7375,13 +7371,13 @@
         <v>3</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F233" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
@@ -7395,13 +7391,13 @@
         <v>3</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F234" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
@@ -7415,50 +7411,50 @@
         <v>3</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>508</v>
+        <v>497</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F235" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="B236" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="B236" s="1" t="s">
-        <v>510</v>
-      </c>
       <c r="C236" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>508</v>
+        <v>497</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="F236" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="B237" s="1" t="s">
         <v>511</v>
       </c>
-      <c r="B237" s="1" t="s">
+      <c r="C237" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D237" s="1" t="s">
         <v>512</v>
       </c>
-      <c r="C237" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D237" s="1" t="s">
-        <v>508</v>
-      </c>
       <c r="E237" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F237" s="1" t="s">
         <v>31</v>
@@ -7475,13 +7471,13 @@
         <v>3</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="E238" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F238" s="1" t="s">
-        <v>164</v>
+        <v>31</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
@@ -7495,53 +7491,53 @@
         <v>3</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="E239" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F239" s="1" t="s">
-        <v>517</v>
+        <v>31</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="B240" s="1" t="s">
         <v>518</v>
       </c>
-      <c r="B240" s="1" t="s">
-        <v>519</v>
-      </c>
       <c r="C240" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="E240" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F240" s="1" t="s">
-        <v>28</v>
+        <v>164</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="B241" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="B241" s="1" t="s">
+      <c r="C241" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D241" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="E241" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F241" s="1" t="s">
         <v>521</v>
-      </c>
-      <c r="C241" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D241" s="1" t="s">
-        <v>508</v>
-      </c>
-      <c r="E241" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F241" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
@@ -7555,10 +7551,10 @@
         <v>3</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="E242" s="1" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="F242" s="1" t="s">
         <v>28</v>
@@ -7575,10 +7571,10 @@
         <v>3</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="E243" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F243" s="1" t="s">
         <v>23</v>
@@ -7595,30 +7591,30 @@
         <v>3</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>528</v>
+        <v>512</v>
       </c>
       <c r="E244" s="1" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="F244" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="B245" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="B245" s="1" t="s">
-        <v>530</v>
-      </c>
       <c r="C245" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>528</v>
+        <v>512</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="F245" s="1" t="s">
         <v>23</v>
@@ -7626,19 +7622,19 @@
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="B246" s="1" t="s">
         <v>531</v>
       </c>
-      <c r="B246" s="1" t="s">
+      <c r="C246" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D246" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="C246" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D246" s="1" t="s">
-        <v>528</v>
-      </c>
       <c r="E246" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F246" s="1" t="s">
         <v>23</v>
@@ -7655,10 +7651,10 @@
         <v>3</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F247" s="1" t="s">
         <v>23</v>
@@ -7675,13 +7671,13 @@
         <v>3</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F248" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
@@ -7695,13 +7691,13 @@
         <v>3</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F249" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
@@ -7715,13 +7711,13 @@
         <v>3</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="E250" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F250" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
@@ -7735,10 +7731,10 @@
         <v>3</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="F251" s="1" t="s">
         <v>31</v>
@@ -7755,50 +7751,50 @@
         <v>3</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>545</v>
+        <v>532</v>
       </c>
       <c r="E252" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F252" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="B253" s="1" t="s">
         <v>546</v>
       </c>
-      <c r="B253" s="1" t="s">
-        <v>547</v>
-      </c>
       <c r="C253" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>545</v>
+        <v>532</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="F253" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="B254" s="1" t="s">
         <v>548</v>
       </c>
-      <c r="B254" s="1" t="s">
+      <c r="C254" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D254" s="1" t="s">
         <v>549</v>
       </c>
-      <c r="C254" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D254" s="1" t="s">
-        <v>545</v>
-      </c>
       <c r="E254" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F254" s="1" t="s">
         <v>23</v>
@@ -7815,10 +7811,10 @@
         <v>3</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F255" s="1" t="s">
         <v>23</v>
@@ -7835,13 +7831,13 @@
         <v>3</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="E256" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F256" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
@@ -7855,10 +7851,10 @@
         <v>3</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="E257" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F257" s="1" t="s">
         <v>23</v>
@@ -7875,13 +7871,13 @@
         <v>3</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F258" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
@@ -7895,10 +7891,10 @@
         <v>3</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="F259" s="1" t="s">
         <v>23</v>
@@ -7915,33 +7911,33 @@
         <v>3</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>562</v>
+        <v>549</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F260" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="B261" s="1" t="s">
         <v>563</v>
       </c>
-      <c r="B261" s="1" t="s">
-        <v>561</v>
-      </c>
       <c r="C261" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>562</v>
+        <v>549</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="F261" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
@@ -7955,33 +7951,33 @@
         <v>3</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F262" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="B263" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="C263" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D263" s="1" t="s">
         <v>566</v>
       </c>
-      <c r="B263" s="1" t="s">
-        <v>567</v>
-      </c>
-      <c r="C263" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D263" s="1" t="s">
-        <v>562</v>
-      </c>
       <c r="E263" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F263" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
@@ -7995,10 +7991,10 @@
         <v>3</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="E264" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F264" s="1" t="s">
         <v>23</v>
@@ -8015,10 +8011,10 @@
         <v>3</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="E265" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F265" s="1" t="s">
         <v>23</v>
@@ -8035,10 +8031,10 @@
         <v>3</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F266" s="1" t="s">
         <v>23</v>
@@ -8055,10 +8051,10 @@
         <v>3</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="E267" s="1" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="F267" s="1" t="s">
         <v>23</v>
@@ -8075,10 +8071,10 @@
         <v>3</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F268" s="1" t="s">
         <v>23</v>
@@ -8095,10 +8091,10 @@
         <v>3</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>580</v>
+        <v>566</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="F269" s="1" t="s">
         <v>23</v>
@@ -8106,19 +8102,19 @@
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="B270" s="1" t="s">
         <v>581</v>
       </c>
-      <c r="B270" s="1" t="s">
-        <v>582</v>
-      </c>
       <c r="C270" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>580</v>
+        <v>566</v>
       </c>
       <c r="E270" s="1" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="F270" s="1" t="s">
         <v>23</v>
@@ -8126,19 +8122,19 @@
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="B271" s="1" t="s">
         <v>583</v>
       </c>
-      <c r="B271" s="1" t="s">
+      <c r="C271" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D271" s="1" t="s">
         <v>584</v>
       </c>
-      <c r="C271" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D271" s="1" t="s">
-        <v>580</v>
-      </c>
       <c r="E271" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F271" s="1" t="s">
         <v>23</v>
@@ -8155,10 +8151,10 @@
         <v>3</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="E272" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F272" s="1" t="s">
         <v>23</v>
@@ -8175,10 +8171,10 @@
         <v>3</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F273" s="1" t="s">
         <v>23</v>
@@ -8195,10 +8191,10 @@
         <v>3</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F274" s="1" t="s">
         <v>23</v>
@@ -8215,10 +8211,10 @@
         <v>3</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="E275" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F275" s="1" t="s">
         <v>23</v>
@@ -8235,10 +8231,10 @@
         <v>3</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="E276" s="1" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="F276" s="1" t="s">
         <v>23</v>
@@ -8255,10 +8251,10 @@
         <v>3</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="E277" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F277" s="1" t="s">
         <v>23</v>
@@ -8275,10 +8271,10 @@
         <v>3</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>142</v>
+        <v>55</v>
       </c>
       <c r="F278" s="1" t="s">
         <v>23</v>
@@ -8295,10 +8291,10 @@
         <v>3</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="E279" s="1" t="s">
-        <v>163</v>
+        <v>58</v>
       </c>
       <c r="F279" s="1" t="s">
         <v>23</v>
@@ -8315,10 +8311,10 @@
         <v>3</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>603</v>
+        <v>584</v>
       </c>
       <c r="E280" s="1" t="s">
-        <v>4</v>
+        <v>142</v>
       </c>
       <c r="F280" s="1" t="s">
         <v>23</v>
@@ -8326,19 +8322,19 @@
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="B281" s="1" t="s">
         <v>604</v>
       </c>
-      <c r="B281" s="1" t="s">
-        <v>605</v>
-      </c>
       <c r="C281" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>603</v>
+        <v>584</v>
       </c>
       <c r="E281" s="1" t="s">
-        <v>8</v>
+        <v>163</v>
       </c>
       <c r="F281" s="1" t="s">
         <v>23</v>
@@ -8346,19 +8342,19 @@
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="B282" s="1" t="s">
         <v>606</v>
       </c>
-      <c r="B282" s="1" t="s">
+      <c r="C282" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D282" s="1" t="s">
         <v>607</v>
       </c>
-      <c r="C282" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D282" s="1" t="s">
-        <v>603</v>
-      </c>
       <c r="E282" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F282" s="1" t="s">
         <v>23</v>
@@ -8375,10 +8371,10 @@
         <v>3</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="E283" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F283" s="1" t="s">
         <v>23</v>
@@ -8395,10 +8391,10 @@
         <v>3</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F284" s="1" t="s">
         <v>23</v>
@@ -8415,10 +8411,10 @@
         <v>3</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="E285" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F285" s="1" t="s">
         <v>23</v>
@@ -8435,30 +8431,30 @@
         <v>3</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F286" s="1" t="s">
-        <v>616</v>
+        <v>23</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A287" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="B287" s="1" t="s">
         <v>617</v>
       </c>
-      <c r="B287" s="1" t="s">
-        <v>618</v>
-      </c>
       <c r="C287" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="F287" s="1" t="s">
         <v>23</v>
@@ -8466,22 +8462,22 @@
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="B288" s="1" t="s">
         <v>619</v>
       </c>
-      <c r="B288" s="1" t="s">
+      <c r="C288" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D288" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="E288" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F288" s="1" t="s">
         <v>620</v>
-      </c>
-      <c r="C288" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D288" s="1" t="s">
-        <v>603</v>
-      </c>
-      <c r="E288" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F288" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
@@ -8495,10 +8491,10 @@
         <v>3</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="E289" s="1" t="s">
-        <v>142</v>
+        <v>55</v>
       </c>
       <c r="F289" s="1" t="s">
         <v>23</v>
@@ -8515,53 +8511,53 @@
         <v>3</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>625</v>
+        <v>607</v>
       </c>
       <c r="E290" s="1" t="s">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="F290" s="1" t="s">
-        <v>616</v>
+        <v>23</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A291" s="1" t="s">
+        <v>625</v>
+      </c>
+      <c r="B291" s="1" t="s">
         <v>626</v>
       </c>
-      <c r="B291" s="1" t="s">
-        <v>627</v>
-      </c>
       <c r="C291" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>625</v>
+        <v>607</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>8</v>
+        <v>142</v>
       </c>
       <c r="F291" s="1" t="s">
-        <v>616</v>
+        <v>23</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A292" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="B292" s="1" t="s">
         <v>628</v>
       </c>
-      <c r="B292" s="1" t="s">
+      <c r="C292" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D292" s="1" t="s">
         <v>629</v>
       </c>
-      <c r="C292" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D292" s="1" t="s">
-        <v>625</v>
-      </c>
       <c r="E292" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F292" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
@@ -8575,13 +8571,13 @@
         <v>3</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="E293" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F293" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
@@ -8595,13 +8591,13 @@
         <v>3</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="E294" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F294" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
@@ -8615,13 +8611,13 @@
         <v>3</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="E295" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F295" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
@@ -8635,13 +8631,13 @@
         <v>3</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="E296" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F296" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
@@ -8655,13 +8651,13 @@
         <v>3</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="F297" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
@@ -8675,13 +8671,13 @@
         <v>3</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F298" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
@@ -8695,50 +8691,50 @@
         <v>3</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>644</v>
+        <v>629</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="F299" s="1" t="s">
-        <v>23</v>
+        <v>620</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A300" s="1" t="s">
+        <v>644</v>
+      </c>
+      <c r="B300" s="1" t="s">
         <v>645</v>
       </c>
-      <c r="B300" s="1" t="s">
-        <v>646</v>
-      </c>
       <c r="C300" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>644</v>
+        <v>629</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="F300" s="1" t="s">
-        <v>23</v>
+        <v>620</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A301" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="B301" s="1" t="s">
         <v>647</v>
       </c>
-      <c r="B301" s="1" t="s">
+      <c r="C301" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D301" s="1" t="s">
         <v>648</v>
       </c>
-      <c r="C301" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D301" s="1" t="s">
-        <v>644</v>
-      </c>
       <c r="E301" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F301" s="1" t="s">
         <v>23</v>
@@ -8755,10 +8751,10 @@
         <v>3</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="E302" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F302" s="1" t="s">
         <v>23</v>
@@ -8775,10 +8771,10 @@
         <v>3</v>
       </c>
       <c r="D303" s="1" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="E303" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F303" s="1" t="s">
         <v>23</v>
@@ -8795,10 +8791,10 @@
         <v>3</v>
       </c>
       <c r="D304" s="1" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="E304" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F304" s="1" t="s">
         <v>23</v>
@@ -8815,10 +8811,10 @@
         <v>3</v>
       </c>
       <c r="D305" s="1" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="E305" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F305" s="1" t="s">
         <v>23</v>
@@ -8835,10 +8831,10 @@
         <v>3</v>
       </c>
       <c r="D306" s="1" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="E306" s="1" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="F306" s="1" t="s">
         <v>23</v>
@@ -8855,10 +8851,10 @@
         <v>3</v>
       </c>
       <c r="D307" s="1" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="E307" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F307" s="1" t="s">
         <v>23</v>
@@ -8875,10 +8871,10 @@
         <v>3</v>
       </c>
       <c r="D308" s="1" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="E308" s="1" t="s">
-        <v>142</v>
+        <v>55</v>
       </c>
       <c r="F308" s="1" t="s">
         <v>23</v>
@@ -8895,10 +8891,10 @@
         <v>3</v>
       </c>
       <c r="D309" s="1" t="s">
-        <v>665</v>
+        <v>648</v>
       </c>
       <c r="E309" s="1" t="s">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="F309" s="1" t="s">
         <v>23</v>
@@ -8906,19 +8902,19 @@
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A310" s="1" t="s">
+        <v>665</v>
+      </c>
+      <c r="B310" s="1" t="s">
         <v>666</v>
       </c>
-      <c r="B310" s="1" t="s">
-        <v>667</v>
-      </c>
       <c r="C310" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D310" s="1" t="s">
-        <v>665</v>
+        <v>648</v>
       </c>
       <c r="E310" s="1" t="s">
-        <v>8</v>
+        <v>142</v>
       </c>
       <c r="F310" s="1" t="s">
         <v>23</v>
@@ -8926,19 +8922,19 @@
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A311" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="B311" s="1" t="s">
         <v>668</v>
       </c>
-      <c r="B311" s="1" t="s">
+      <c r="C311" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D311" s="1" t="s">
         <v>669</v>
       </c>
-      <c r="C311" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D311" s="1" t="s">
-        <v>665</v>
-      </c>
       <c r="E311" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F311" s="1" t="s">
         <v>23</v>
@@ -8955,10 +8951,10 @@
         <v>3</v>
       </c>
       <c r="D312" s="1" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="E312" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F312" s="1" t="s">
         <v>23</v>
@@ -8975,10 +8971,10 @@
         <v>3</v>
       </c>
       <c r="D313" s="1" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="E313" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F313" s="1" t="s">
         <v>23</v>
@@ -8995,10 +8991,10 @@
         <v>3</v>
       </c>
       <c r="D314" s="1" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="E314" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F314" s="1" t="s">
         <v>23</v>
@@ -9015,10 +9011,10 @@
         <v>3</v>
       </c>
       <c r="D315" s="1" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="E315" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F315" s="1" t="s">
         <v>23</v>
@@ -9035,10 +9031,10 @@
         <v>3</v>
       </c>
       <c r="D316" s="1" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="E316" s="1" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="F316" s="1" t="s">
         <v>23</v>
@@ -9055,10 +9051,10 @@
         <v>3</v>
       </c>
       <c r="D317" s="1" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="E317" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F317" s="1" t="s">
         <v>23</v>
@@ -9075,10 +9071,10 @@
         <v>3</v>
       </c>
       <c r="D318" s="1" t="s">
-        <v>684</v>
+        <v>669</v>
       </c>
       <c r="E318" s="1" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="F318" s="1" t="s">
         <v>23</v>
@@ -9086,19 +9082,19 @@
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A319" s="1" t="s">
+        <v>684</v>
+      </c>
+      <c r="B319" s="1" t="s">
         <v>685</v>
       </c>
-      <c r="B319" s="1" t="s">
-        <v>686</v>
-      </c>
       <c r="C319" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D319" s="1" t="s">
-        <v>684</v>
+        <v>669</v>
       </c>
       <c r="E319" s="1" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="F319" s="1" t="s">
         <v>23</v>
@@ -9106,19 +9102,19 @@
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A320" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="B320" s="1" t="s">
         <v>687</v>
       </c>
-      <c r="B320" s="1" t="s">
+      <c r="C320" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D320" s="1" t="s">
         <v>688</v>
       </c>
-      <c r="C320" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D320" s="1" t="s">
-        <v>684</v>
-      </c>
       <c r="E320" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F320" s="1" t="s">
         <v>23</v>
@@ -9135,10 +9131,10 @@
         <v>3</v>
       </c>
       <c r="D321" s="1" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="E321" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F321" s="1" t="s">
         <v>23</v>
@@ -9155,10 +9151,10 @@
         <v>3</v>
       </c>
       <c r="D322" s="1" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="E322" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F322" s="1" t="s">
         <v>23</v>
@@ -9175,10 +9171,10 @@
         <v>3</v>
       </c>
       <c r="D323" s="1" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="E323" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F323" s="1" t="s">
         <v>23</v>
@@ -9195,10 +9191,10 @@
         <v>3</v>
       </c>
       <c r="D324" s="1" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="E324" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F324" s="1" t="s">
         <v>23</v>
@@ -9215,10 +9211,10 @@
         <v>3</v>
       </c>
       <c r="D325" s="1" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="E325" s="1" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="F325" s="1" t="s">
         <v>23</v>
@@ -9235,10 +9231,10 @@
         <v>3</v>
       </c>
       <c r="D326" s="1" t="s">
-        <v>701</v>
+        <v>688</v>
       </c>
       <c r="E326" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F326" s="1" t="s">
         <v>23</v>
@@ -9246,19 +9242,19 @@
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A327" s="1" t="s">
+        <v>701</v>
+      </c>
+      <c r="B327" s="1" t="s">
         <v>702</v>
       </c>
-      <c r="B327" s="1" t="s">
-        <v>703</v>
-      </c>
       <c r="C327" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D327" s="1" t="s">
-        <v>701</v>
+        <v>688</v>
       </c>
       <c r="E327" s="1" t="s">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="F327" s="1" t="s">
         <v>23</v>
@@ -9266,22 +9262,22 @@
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A328" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="B328" s="1" t="s">
         <v>704</v>
       </c>
-      <c r="B328" s="1" t="s">
+      <c r="C328" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D328" s="1" t="s">
         <v>705</v>
       </c>
-      <c r="C328" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D328" s="1" t="s">
-        <v>701</v>
-      </c>
       <c r="E328" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F328" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.25">
@@ -9295,13 +9291,13 @@
         <v>3</v>
       </c>
       <c r="D329" s="1" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="E329" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F329" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.25">
@@ -9315,13 +9311,13 @@
         <v>3</v>
       </c>
       <c r="D330" s="1" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="E330" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F330" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.25">
@@ -9335,13 +9331,13 @@
         <v>3</v>
       </c>
       <c r="D331" s="1" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="E331" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F331" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.25">
@@ -9355,10 +9351,10 @@
         <v>3</v>
       </c>
       <c r="D332" s="1" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="E332" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F332" s="1" t="s">
         <v>23</v>
@@ -9375,10 +9371,10 @@
         <v>3</v>
       </c>
       <c r="D333" s="1" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="E333" s="1" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="F333" s="1" t="s">
         <v>23</v>
@@ -9395,10 +9391,10 @@
         <v>3</v>
       </c>
       <c r="D334" s="1" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="E334" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F334" s="1" t="s">
         <v>23</v>
@@ -9415,10 +9411,10 @@
         <v>3</v>
       </c>
       <c r="D335" s="1" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="E335" s="1" t="s">
-        <v>142</v>
+        <v>55</v>
       </c>
       <c r="F335" s="1" t="s">
         <v>23</v>
@@ -9435,53 +9431,53 @@
         <v>3</v>
       </c>
       <c r="D336" s="1" t="s">
-        <v>722</v>
+        <v>705</v>
       </c>
       <c r="E336" s="1" t="s">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="F336" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A337" s="1" t="s">
+        <v>722</v>
+      </c>
+      <c r="B337" s="1" t="s">
         <v>723</v>
       </c>
-      <c r="B337" s="1" t="s">
-        <v>724</v>
-      </c>
       <c r="C337" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D337" s="1" t="s">
-        <v>722</v>
+        <v>705</v>
       </c>
       <c r="E337" s="1" t="s">
-        <v>8</v>
+        <v>142</v>
       </c>
       <c r="F337" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A338" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="B338" s="1" t="s">
         <v>725</v>
       </c>
-      <c r="B338" s="1" t="s">
+      <c r="C338" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D338" s="1" t="s">
         <v>726</v>
       </c>
-      <c r="C338" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D338" s="1" t="s">
-        <v>722</v>
-      </c>
       <c r="E338" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F338" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.25">
@@ -9495,10 +9491,10 @@
         <v>3</v>
       </c>
       <c r="D339" s="1" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="E339" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F339" s="1" t="s">
         <v>31</v>
@@ -9515,10 +9511,10 @@
         <v>3</v>
       </c>
       <c r="D340" s="1" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="E340" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F340" s="1" t="s">
         <v>23</v>
@@ -9535,13 +9531,13 @@
         <v>3</v>
       </c>
       <c r="D341" s="1" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="E341" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F341" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.25">
@@ -9555,13 +9551,13 @@
         <v>3</v>
       </c>
       <c r="D342" s="1" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="E342" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F342" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="343" spans="1:6" x14ac:dyDescent="0.25">
@@ -9575,93 +9571,93 @@
         <v>3</v>
       </c>
       <c r="D343" s="1" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="E343" s="1" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="F343" s="1" t="s">
-        <v>737</v>
+        <v>23</v>
       </c>
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A344" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="B344" s="1" t="s">
         <v>738</v>
       </c>
-      <c r="B344" s="1" t="s">
-        <v>739</v>
-      </c>
       <c r="C344" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D344" s="1" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="E344" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F344" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A345" s="1" t="s">
+        <v>739</v>
+      </c>
+      <c r="B345" s="1" t="s">
         <v>740</v>
       </c>
-      <c r="B345" s="1" t="s">
+      <c r="C345" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D345" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="E345" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F345" s="1" t="s">
         <v>741</v>
-      </c>
-      <c r="C345" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D345" s="1" t="s">
-        <v>742</v>
-      </c>
-      <c r="E345" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F345" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A346" s="1" t="s">
+        <v>742</v>
+      </c>
+      <c r="B346" s="1" t="s">
         <v>743</v>
       </c>
-      <c r="B346" s="1" t="s">
-        <v>744</v>
-      </c>
       <c r="C346" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D346" s="1" t="s">
-        <v>742</v>
+        <v>726</v>
       </c>
       <c r="E346" s="1" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="F346" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A347" s="1" t="s">
+        <v>744</v>
+      </c>
+      <c r="B347" s="1" t="s">
         <v>745</v>
       </c>
-      <c r="B347" s="1" t="s">
+      <c r="C347" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D347" s="1" t="s">
         <v>746</v>
       </c>
-      <c r="C347" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D347" s="1" t="s">
-        <v>742</v>
-      </c>
       <c r="E347" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F347" s="1" t="s">
-        <v>164</v>
+        <v>23</v>
       </c>
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.25">
@@ -9675,10 +9671,10 @@
         <v>3</v>
       </c>
       <c r="D348" s="1" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="E348" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F348" s="1" t="s">
         <v>23</v>
@@ -9686,139 +9682,139 @@
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A349" s="1" t="s">
+        <v>749</v>
+      </c>
+      <c r="B349" s="1" t="s">
         <v>750</v>
       </c>
-      <c r="B349" s="1" t="s">
-        <v>751</v>
-      </c>
       <c r="C349" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D349" s="1" t="s">
-        <v>752</v>
+        <v>746</v>
       </c>
       <c r="E349" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F349" s="1" t="s">
-        <v>28</v>
+        <v>164</v>
       </c>
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A350" s="1" t="s">
+        <v>751</v>
+      </c>
+      <c r="B350" s="1" t="s">
+        <v>752</v>
+      </c>
+      <c r="C350" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D350" s="1" t="s">
         <v>753</v>
-      </c>
-      <c r="B350" s="1" t="s">
-        <v>754</v>
-      </c>
-      <c r="C350" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D350" s="1" t="s">
-        <v>755</v>
       </c>
       <c r="E350" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F350" s="1" t="s">
-        <v>756</v>
+        <v>23</v>
       </c>
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A351" s="1" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="B351" s="1" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="C351" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D351" s="1" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="E351" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F351" s="1" t="s">
-        <v>759</v>
+        <v>28</v>
       </c>
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A352" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="B352" s="1" t="s">
+        <v>758</v>
+      </c>
+      <c r="C352" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D352" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="E352" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F352" s="1" t="s">
         <v>760</v>
-      </c>
-      <c r="B352" s="1" t="s">
-        <v>761</v>
-      </c>
-      <c r="C352" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D352" s="1" t="s">
-        <v>755</v>
-      </c>
-      <c r="E352" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F352" s="1" t="s">
-        <v>762</v>
       </c>
     </row>
     <row r="353" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A353" s="1" t="s">
+        <v>761</v>
+      </c>
+      <c r="B353" s="1" t="s">
+        <v>762</v>
+      </c>
+      <c r="C353" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D353" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="E353" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F353" s="1" t="s">
         <v>763</v>
-      </c>
-      <c r="B353" s="1" t="s">
-        <v>764</v>
-      </c>
-      <c r="C353" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D353" s="1" t="s">
-        <v>755</v>
-      </c>
-      <c r="E353" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F353" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="354" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A354" s="1" t="s">
+        <v>764</v>
+      </c>
+      <c r="B354" s="1" t="s">
         <v>765</v>
       </c>
-      <c r="B354" s="1" t="s">
+      <c r="C354" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D354" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="E354" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F354" s="1" t="s">
         <v>766</v>
-      </c>
-      <c r="C354" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D354" s="1" t="s">
-        <v>767</v>
-      </c>
-      <c r="E354" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F354" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="355" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A355" s="1" t="s">
+        <v>767</v>
+      </c>
+      <c r="B355" s="1" t="s">
         <v>768</v>
       </c>
-      <c r="B355" s="1" t="s">
-        <v>769</v>
-      </c>
       <c r="C355" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D355" s="1" t="s">
-        <v>767</v>
+        <v>759</v>
       </c>
       <c r="E355" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F355" s="1" t="s">
         <v>23</v>

--- a/CLB07N.xlsx
+++ b/CLB07N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2130" uniqueCount="769">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2136" uniqueCount="772">
   <si>
     <t/>
   </si>
@@ -379,6 +379,75 @@
     <t>ABC MILK COFFEE 180</t>
   </si>
   <si>
+    <t>20078206</t>
+  </si>
+  <si>
+    <t>LUWAK WHT ORGL 220ML</t>
+  </si>
+  <si>
+    <t>20120904</t>
+  </si>
+  <si>
+    <t>KK BLACK AREN 220ML</t>
+  </si>
+  <si>
+    <t>20120906</t>
+  </si>
+  <si>
+    <t>KK MANTANCINO 220ML</t>
+  </si>
+  <si>
+    <t>20133409</t>
+  </si>
+  <si>
+    <t>KK CAFFE LATTE 200ML</t>
+  </si>
+  <si>
+    <t>20138168</t>
+  </si>
+  <si>
+    <t>KK CHEESE LATTEE 200</t>
+  </si>
+  <si>
+    <t>20138167</t>
+  </si>
+  <si>
+    <t>KK JPNS MATCHA 200</t>
+  </si>
+  <si>
+    <t>20129108</t>
+  </si>
+  <si>
+    <t>OATSDE COFFEE 200ML</t>
+  </si>
+  <si>
+    <t>20142499</t>
+  </si>
+  <si>
+    <t>OATSDE ESPR RST 240</t>
+  </si>
+  <si>
+    <t>20134557</t>
+  </si>
+  <si>
+    <t>OATSIDE CRML MCHT200</t>
+  </si>
+  <si>
+    <t>20129123</t>
+  </si>
+  <si>
+    <t>OATSDE CHOCO 200</t>
+  </si>
+  <si>
+    <t>20129102</t>
+  </si>
+  <si>
+    <t>OATSDE BR.BLEND 200</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
     <t>20045415</t>
   </si>
   <si>
@@ -391,34 +460,34 @@
     <t>KOPIKO LUCKY DAY 180</t>
   </si>
   <si>
-    <t>20120904</t>
-  </si>
-  <si>
-    <t>KK BLACK AREN 220ML</t>
-  </si>
-  <si>
-    <t>20120906</t>
-  </si>
-  <si>
-    <t>KK MANTANCINO 220ML</t>
-  </si>
-  <si>
-    <t>20133409</t>
-  </si>
-  <si>
-    <t>KK CAFFE LATTE 200ML</t>
-  </si>
-  <si>
-    <t>20138168</t>
-  </si>
-  <si>
-    <t>KK CHEESE LATTEE 200</t>
-  </si>
-  <si>
-    <t>20138167</t>
-  </si>
-  <si>
-    <t>KK JPNS MATCHA 200</t>
+    <t>20076770</t>
+  </si>
+  <si>
+    <t>G/DAY CAPPUCCINO 230</t>
+  </si>
+  <si>
+    <t>20045674</t>
+  </si>
+  <si>
+    <t>G/DAY F.MOCACINO 230</t>
+  </si>
+  <si>
+    <t>20045673</t>
+  </si>
+  <si>
+    <t>G/DAY TIRAMISU/B 230</t>
+  </si>
+  <si>
+    <t>20056193</t>
+  </si>
+  <si>
+    <t>GOOD DAY AVCDO/D 230</t>
+  </si>
+  <si>
+    <t>20132329</t>
+  </si>
+  <si>
+    <t>GOOD DAY GRVY CKS230</t>
   </si>
   <si>
     <t>20132760</t>
@@ -433,1891 +502,1831 @@
     <t>CAFINO RTD CPCINO200</t>
   </si>
   <si>
+    <t>20139577</t>
+  </si>
+  <si>
+    <t>PC AREN LATTE 210ML</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20139578</t>
+  </si>
+  <si>
+    <t>PC GOLDN CARAMEL 210</t>
+  </si>
+  <si>
+    <t>20139576</t>
+  </si>
+  <si>
+    <t>PC CRMY CPUCCINO 210</t>
+  </si>
+  <si>
+    <t>20142601</t>
+  </si>
+  <si>
+    <t>NSCAFE MTCHA ESP 220</t>
+  </si>
+  <si>
+    <t>20140431</t>
+  </si>
+  <si>
+    <t>NSCAFE KITKAT LAT220</t>
+  </si>
+  <si>
+    <t>20133058</t>
+  </si>
+  <si>
+    <t>NSCAFE OAT LATTE 220</t>
+  </si>
+  <si>
+    <t>20027768</t>
+  </si>
+  <si>
+    <t>NESCAFE COFF CRM 180</t>
+  </si>
+  <si>
+    <t>20114494</t>
+  </si>
+  <si>
+    <t>NSCAFE CRML MCTO 220</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>20114495</t>
+  </si>
+  <si>
+    <t>NESCAFE CPUCCINO 220</t>
+  </si>
+  <si>
+    <t>20114493</t>
+  </si>
+  <si>
+    <t>NESCAFE LATTE 220ML</t>
+  </si>
+  <si>
+    <t>20138057</t>
+  </si>
+  <si>
+    <t>NSCAFE GULA AREN 220</t>
+  </si>
+  <si>
+    <t>20121456</t>
+  </si>
+  <si>
+    <t>NSCAFE ICE BLACK 220</t>
+  </si>
+  <si>
+    <t>20000787</t>
+  </si>
+  <si>
+    <t>NESCAFE ICE.CF OR220</t>
+  </si>
+  <si>
+    <t>20014954</t>
+  </si>
+  <si>
+    <t>NESCAFE ICE.CF MC220</t>
+  </si>
+  <si>
+    <t>20000786</t>
+  </si>
+  <si>
+    <t>NESCAFE ICE.CF LT220</t>
+  </si>
+  <si>
+    <t>20125115</t>
+  </si>
+  <si>
+    <t>STARBUCKS LATTE 220</t>
+  </si>
+  <si>
+    <t>20125126</t>
+  </si>
+  <si>
+    <t>STARBUCKS CARAMEL220</t>
+  </si>
+  <si>
+    <t>20014608</t>
+  </si>
+  <si>
+    <t>HRMVTON PSK BUMI 150</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>10006263</t>
+  </si>
+  <si>
+    <t>HEMAVITON ENERGY 150</t>
+  </si>
+  <si>
+    <t>10002602</t>
+  </si>
+  <si>
+    <t>M-150 HEALT DRINK150</t>
+  </si>
+  <si>
+    <t>10002595</t>
+  </si>
+  <si>
+    <t>KRATINGDAENG 150 ML</t>
+  </si>
+  <si>
+    <t>10003427</t>
+  </si>
+  <si>
+    <t>KRATINGDAENG SPR.150</t>
+  </si>
+  <si>
+    <t>20022431</t>
+  </si>
+  <si>
+    <t>RED BULL E/DRNK 250</t>
+  </si>
+  <si>
+    <t>20056989</t>
+  </si>
+  <si>
+    <t>RED BULL GOLD 250ML</t>
+  </si>
+  <si>
+    <t>20138252</t>
+  </si>
+  <si>
+    <t>EXTRA JOSS ULTIMT250</t>
+  </si>
+  <si>
+    <t>20038425</t>
+  </si>
+  <si>
+    <t>NTRIVE/B BLCKRNT 100</t>
+  </si>
+  <si>
+    <t>20071510</t>
+  </si>
+  <si>
+    <t>NTRVE BNCOL LYCH 100</t>
+  </si>
+  <si>
+    <t>20003786</t>
+  </si>
+  <si>
+    <t>NU GREEN TEA HNY 450</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>20113059</t>
+  </si>
+  <si>
+    <t>NU YOGURT TEA 450ML</t>
+  </si>
+  <si>
+    <t>20139732</t>
+  </si>
+  <si>
+    <t>NU YOGRT TEA BRY 450</t>
+  </si>
+  <si>
+    <t>20036157</t>
+  </si>
+  <si>
+    <t>SOSRO TEH BOTOL 450</t>
+  </si>
+  <si>
+    <t>20002203</t>
+  </si>
+  <si>
+    <t>SOSRO F.TEA APEL 500</t>
+  </si>
+  <si>
+    <t>20003698</t>
+  </si>
+  <si>
+    <t>SOSRO FR.TEA XTRM500</t>
+  </si>
+  <si>
+    <t>20002205</t>
+  </si>
+  <si>
+    <t>SOSRO F.TEA BLKCR500</t>
+  </si>
+  <si>
+    <t>20134046</t>
+  </si>
+  <si>
+    <t>FRUIT TEA FREEZE 500</t>
+  </si>
+  <si>
+    <t>20126464</t>
+  </si>
+  <si>
+    <t>IDM TEH APL&amp;LYCHE350</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>20101897</t>
+  </si>
+  <si>
+    <t>IDM TEH APEL 350ML</t>
+  </si>
+  <si>
+    <t>20132840</t>
+  </si>
+  <si>
+    <t>IDM TEH BLCKCRRNT350</t>
+  </si>
+  <si>
+    <t>20066454</t>
+  </si>
+  <si>
+    <t>FRUIT TEA BLCKCR 350</t>
+  </si>
+  <si>
+    <t>20073495</t>
+  </si>
+  <si>
+    <t>FRUIT TEA FREEZE 350</t>
+  </si>
+  <si>
+    <t>20066455</t>
+  </si>
+  <si>
+    <t>FRUIT TEA APPLE 350</t>
+  </si>
+  <si>
+    <t>20079972</t>
+  </si>
+  <si>
+    <t>FRUIT TEA MRKISA 350</t>
+  </si>
+  <si>
+    <t>20138841</t>
+  </si>
+  <si>
+    <t>POKKA NAT. H.ORG 350</t>
+  </si>
+  <si>
+    <t>20135619</t>
+  </si>
+  <si>
+    <t>TEBS ZERO LYCHEE 300</t>
+  </si>
+  <si>
+    <t>20060207</t>
+  </si>
+  <si>
+    <t>I/OCHA TEH MLATI 350</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>20048934</t>
+  </si>
+  <si>
+    <t>I/OCHA GRN TEA 350ML</t>
+  </si>
+  <si>
+    <t>20142077</t>
+  </si>
+  <si>
+    <t>TEH LEMON MADU 350ML</t>
+  </si>
+  <si>
+    <t>20018904</t>
+  </si>
+  <si>
+    <t>NU GREEN TEA HNY 330</t>
+  </si>
+  <si>
+    <t>20053867</t>
+  </si>
+  <si>
+    <t>TEH GELAS BTL 350ML</t>
+  </si>
+  <si>
+    <t>20073396</t>
+  </si>
+  <si>
+    <t>S-TEE BTL 390ML</t>
+  </si>
+  <si>
+    <t>20072249</t>
+  </si>
+  <si>
+    <t>SOSRO TEH BOTOL 350</t>
+  </si>
+  <si>
+    <t>20122278</t>
+  </si>
+  <si>
+    <t>TEH BOTOL LS.SGR 350</t>
+  </si>
+  <si>
+    <t>20082395</t>
+  </si>
+  <si>
+    <t>TEH BOTOL TAWAR 350</t>
+  </si>
+  <si>
+    <t>RT,(E-3.5B)</t>
+  </si>
+  <si>
+    <t>20035484</t>
+  </si>
+  <si>
+    <t>PUCUK/H TEH MLATI350</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>20048155</t>
+  </si>
+  <si>
+    <t>PUCUK/H TEH L/SGR350</t>
+  </si>
+  <si>
+    <t>20037565</t>
+  </si>
+  <si>
+    <t>PUCUK/H TEH MLATI500</t>
+  </si>
+  <si>
+    <t>20048348</t>
+  </si>
+  <si>
+    <t>PUCUK/H TEH L/SGR500</t>
+  </si>
+  <si>
+    <t>10036640</t>
+  </si>
+  <si>
+    <t>TEH KOTAK JASMINE300</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>20048435</t>
+  </si>
+  <si>
+    <t>TEH KOTAK LESS/S 300</t>
+  </si>
+  <si>
+    <t>20143447</t>
+  </si>
+  <si>
+    <t>PUCUK/H TEH ORI 300</t>
+  </si>
+  <si>
+    <t>20143446</t>
+  </si>
+  <si>
+    <t>PUCUK/H TEH L/SGR300</t>
+  </si>
+  <si>
+    <t>20044334</t>
+  </si>
+  <si>
+    <t>SOSRO TEH BTL TPK300</t>
+  </si>
+  <si>
+    <t>10005128</t>
+  </si>
+  <si>
+    <t>SOSRO TEH KOTAK B250</t>
+  </si>
+  <si>
+    <t>20024315</t>
+  </si>
+  <si>
+    <t>TEH BOTOL LS.SGR 250</t>
+  </si>
+  <si>
+    <t>20026226</t>
+  </si>
+  <si>
+    <t>ULTRA TEH KOTAK 500</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>20100142</t>
+  </si>
+  <si>
+    <t>TEH KOTAK BLCKCR 300</t>
+  </si>
+  <si>
+    <t>20100143</t>
+  </si>
+  <si>
+    <t>TEH KOTAK APPLE 300</t>
+  </si>
+  <si>
+    <t>20137159</t>
+  </si>
+  <si>
+    <t>TEH KOTAK MANGGA 300</t>
+  </si>
+  <si>
+    <t>20087016</t>
+  </si>
+  <si>
+    <t>TEH KOTAK LEMON 300</t>
+  </si>
+  <si>
+    <t>20135647</t>
+  </si>
+  <si>
+    <t>TEH KOTAK LYCHEE 300</t>
+  </si>
+  <si>
+    <t>20117687</t>
+  </si>
+  <si>
+    <t>DLMNT BOBA MTCHA 240</t>
+  </si>
+  <si>
+    <t>20117682</t>
+  </si>
+  <si>
+    <t>DLMNT BOBA RD.VEL240</t>
+  </si>
+  <si>
+    <t>20080088</t>
+  </si>
+  <si>
+    <t>POKKA GREEN TEA 450</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>20036765</t>
+  </si>
+  <si>
+    <t>FRESTEA GRN MADU 500</t>
+  </si>
+  <si>
+    <t>20012574</t>
+  </si>
+  <si>
+    <t>FRESTEA TEH APEL 500</t>
+  </si>
+  <si>
+    <t>20035829</t>
+  </si>
+  <si>
+    <t>TEBS TEA WT/SODA 500</t>
+  </si>
+  <si>
+    <t>20093586</t>
+  </si>
+  <si>
+    <t>ICHTN THAI M.COFF300</t>
+  </si>
+  <si>
+    <t>20136363</t>
+  </si>
+  <si>
+    <t>ICHTN DARK CHOCO 300</t>
+  </si>
+  <si>
+    <t>20135599</t>
+  </si>
+  <si>
+    <t>ICHTAN KRN BANANA300</t>
+  </si>
+  <si>
+    <t>20142025</t>
+  </si>
+  <si>
+    <t>ICHITAN MLN MILK 300</t>
+  </si>
+  <si>
+    <t>20040383</t>
+  </si>
+  <si>
+    <t>NU MILK TEA 330ML</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>20069527</t>
+  </si>
+  <si>
+    <t>NU TEH TARIK 330ML</t>
+  </si>
+  <si>
+    <t>20128233</t>
+  </si>
+  <si>
+    <t>NU CHO TEA HZLTEA330</t>
+  </si>
+  <si>
+    <t>20138202</t>
+  </si>
+  <si>
+    <t>NU MATCHA LATTEA 330</t>
+  </si>
+  <si>
+    <t>20141981</t>
+  </si>
+  <si>
+    <t>DUM2 CHO MILK TEA330</t>
+  </si>
+  <si>
+    <t>20141980</t>
+  </si>
+  <si>
+    <t>DUM2 RYL MILK TEA330</t>
+  </si>
+  <si>
+    <t>20085054</t>
+  </si>
+  <si>
+    <t>ICHTN THAI M.TEA 300</t>
+  </si>
+  <si>
+    <t>20101102</t>
+  </si>
+  <si>
+    <t>ICHTN MLK GR.TEA 300</t>
+  </si>
+  <si>
+    <t>20113450</t>
+  </si>
+  <si>
+    <t>ICHITAN MLK BRWN 300</t>
+  </si>
+  <si>
+    <t>20113377</t>
+  </si>
+  <si>
+    <t>FLRDINA COCO BIT 350</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>20043877</t>
+  </si>
+  <si>
+    <t>FLORIDINA ORANGE 350</t>
+  </si>
+  <si>
+    <t>20021178</t>
+  </si>
+  <si>
+    <t>MINUTE MAID ORG 300</t>
+  </si>
+  <si>
+    <t>20062818</t>
+  </si>
+  <si>
+    <t>FRUITAMIN LYCHE 350</t>
+  </si>
+  <si>
+    <t>20091654</t>
+  </si>
+  <si>
+    <t>COCO BIT SP.GUAV 350</t>
+  </si>
+  <si>
+    <t>20140331</t>
+  </si>
+  <si>
+    <t>COCO BIT STRAW.S 350</t>
+  </si>
+  <si>
+    <t>20140327</t>
+  </si>
+  <si>
+    <t>COCO BIT KY.GRP 350</t>
+  </si>
+  <si>
+    <t>20140332</t>
+  </si>
+  <si>
+    <t>COCO BIT HOK.MLN 350</t>
+  </si>
+  <si>
+    <t>20042848</t>
+  </si>
+  <si>
+    <t>MOGU MOGU LYCHHE 320</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>20047245</t>
+  </si>
+  <si>
+    <t>MOGU MOGU CCONUT 320</t>
+  </si>
+  <si>
+    <t>20076486</t>
+  </si>
+  <si>
+    <t>MOGU MOGU MELON 320</t>
+  </si>
+  <si>
+    <t>20042859</t>
+  </si>
+  <si>
+    <t>MOGU MOGU MANGGA 320</t>
+  </si>
+  <si>
+    <t>20042860</t>
+  </si>
+  <si>
+    <t>MOGU MOGU STRWBRY320</t>
+  </si>
+  <si>
+    <t>20047244</t>
+  </si>
+  <si>
+    <t>MOGU MOGU GRAPE 320</t>
+  </si>
+  <si>
+    <t>20137095</t>
+  </si>
+  <si>
+    <t>MOGU2 BUBBLE GUM 320</t>
+  </si>
+  <si>
+    <t>20136277</t>
+  </si>
+  <si>
+    <t>SNPRD FRT MG.PINE220</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>20134353</t>
+  </si>
+  <si>
+    <t>IDM S/B NNS&amp;MRKSA220</t>
+  </si>
+  <si>
+    <t>20134354</t>
+  </si>
+  <si>
+    <t>IDM SARI BH NANAS220</t>
+  </si>
+  <si>
+    <t>20089805</t>
+  </si>
+  <si>
+    <t>OLATTE PEACH KLG 240</t>
+  </si>
+  <si>
+    <t>RT,(E-2.5B)</t>
+  </si>
+  <si>
+    <t>20089806</t>
+  </si>
+  <si>
+    <t>OLATTE PEAR KLG 240</t>
+  </si>
+  <si>
+    <t>20135975</t>
+  </si>
+  <si>
+    <t>OLATTE STRWB KLG 240</t>
+  </si>
+  <si>
+    <t>20052734</t>
+  </si>
+  <si>
+    <t>LOTTE MILKIS MLN 250</t>
+  </si>
+  <si>
+    <t>10028190</t>
+  </si>
+  <si>
+    <t>LOTTE MILKIS KLG 250</t>
+  </si>
+  <si>
+    <t>10008887</t>
+  </si>
+  <si>
+    <t>ULTRA KCNG HIJAU 250</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>10000278</t>
+  </si>
+  <si>
+    <t>ABC KACANG HIJAU 250</t>
+  </si>
+  <si>
+    <t>20120929</t>
+  </si>
+  <si>
+    <t>PANDA GR.JLY+BSL 310</t>
+  </si>
+  <si>
+    <t>20046319</t>
+  </si>
+  <si>
+    <t>PANDA GRASS JELY310</t>
+  </si>
+  <si>
+    <t>20141495</t>
+  </si>
+  <si>
+    <t>PANDA GRN GRS JEL310</t>
+  </si>
+  <si>
+    <t>20112383</t>
+  </si>
+  <si>
+    <t>MR.NATA JELI LECI126</t>
+  </si>
+  <si>
+    <t>20112382</t>
+  </si>
+  <si>
+    <t>MR.NATA JEL BLU/B126</t>
+  </si>
+  <si>
+    <t>20136250</t>
+  </si>
+  <si>
+    <t>JELE JELLY LYCHEE150</t>
+  </si>
+  <si>
+    <t>20055762</t>
+  </si>
+  <si>
+    <t>JELE COLLAGEN 150G</t>
+  </si>
+  <si>
+    <t>10007970</t>
+  </si>
+  <si>
+    <t>BUAVITA JAMBU SL 245</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>10007974</t>
+  </si>
+  <si>
+    <t>BUAVITA LYCHEE SL245</t>
+  </si>
+  <si>
+    <t>10007971</t>
+  </si>
+  <si>
+    <t>BUAVITA ORANGE SL245</t>
+  </si>
+  <si>
+    <t>10007973</t>
+  </si>
+  <si>
+    <t>BUAVITA MANGGA 245ML</t>
+  </si>
+  <si>
+    <t>10007972</t>
+  </si>
+  <si>
+    <t>BUAVITA JC APPLE 245</t>
+  </si>
+  <si>
+    <t>20140324</t>
+  </si>
+  <si>
+    <t>BUAVITA K.STRAW 245</t>
+  </si>
+  <si>
+    <t>20140328</t>
+  </si>
+  <si>
+    <t>BUAVITA K MS.GRP 245</t>
+  </si>
+  <si>
+    <t>10007385</t>
+  </si>
+  <si>
+    <t>ULTRA SR ASAM SLM250</t>
+  </si>
+  <si>
+    <t>20136649</t>
+  </si>
+  <si>
+    <t>DIAMOND JC CRANBR200</t>
+  </si>
+  <si>
+    <t>20065041</t>
+  </si>
+  <si>
+    <t>PORORO BLUEBERY235ML</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>20037137</t>
+  </si>
+  <si>
+    <t>PORORO STROBRI 235ML</t>
+  </si>
+  <si>
+    <t>20037136</t>
+  </si>
+  <si>
+    <t>PORORO SUSU 235ML</t>
+  </si>
+  <si>
+    <t>20085010</t>
+  </si>
+  <si>
+    <t>PORORO MANGO 235</t>
+  </si>
+  <si>
+    <t>20137094</t>
+  </si>
+  <si>
+    <t>PORORO PEACH 235</t>
+  </si>
+  <si>
+    <t>20141361</t>
+  </si>
+  <si>
+    <t>PORORO ZERO STRW 235</t>
+  </si>
+  <si>
+    <t>20141360</t>
+  </si>
+  <si>
+    <t>PORORO ZERO MILK 235</t>
+  </si>
+  <si>
+    <t>20143468</t>
+  </si>
+  <si>
+    <t>PRRO ZROSGR BLBRY235</t>
+  </si>
+  <si>
+    <t>20069773</t>
+  </si>
+  <si>
+    <t>ISOPLUS BTL 350ML</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>20128918</t>
+  </si>
+  <si>
+    <t>ISOPLUS COCO 350ML</t>
+  </si>
+  <si>
+    <t>20138959</t>
+  </si>
+  <si>
+    <t>IF COCONUT WTR 350ML</t>
+  </si>
+  <si>
+    <t>20142818</t>
+  </si>
+  <si>
+    <t>EWATER GRAPEFRT 555</t>
+  </si>
+  <si>
+    <t>20142819</t>
+  </si>
+  <si>
+    <t>EWATER LEMON 555ML</t>
+  </si>
+  <si>
+    <t>20142862</t>
+  </si>
+  <si>
+    <t>EWATER GRPFRT 380</t>
+  </si>
+  <si>
+    <t>20142863</t>
+  </si>
+  <si>
+    <t>EWATER LEMON 380</t>
+  </si>
+  <si>
+    <t>20108987</t>
+  </si>
+  <si>
+    <t>V-SOY MULTI-GRAIN200</t>
+  </si>
+  <si>
+    <t>20123171</t>
+  </si>
+  <si>
+    <t>LACTASOY MILK CLG250</t>
+  </si>
+  <si>
+    <t>20135311</t>
+  </si>
+  <si>
+    <t>HYDROPL ISTNC JRK350</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>20142358</t>
+  </si>
+  <si>
+    <t>POWRADE ACTIV WHT400</t>
+  </si>
+  <si>
+    <t>20142359</t>
+  </si>
+  <si>
+    <t>POWRADE ISOTN BLU400</t>
+  </si>
+  <si>
+    <t>20138837</t>
+  </si>
+  <si>
+    <t>MZONE COCO BOOST 500</t>
+  </si>
+  <si>
+    <t>20094167</t>
+  </si>
+  <si>
+    <t>MIZONE MOOD UP 500</t>
+  </si>
+  <si>
+    <t>20094164</t>
+  </si>
+  <si>
+    <t>MIZONE ACTIVE 500ML</t>
+  </si>
+  <si>
+    <t>20141600</t>
+  </si>
+  <si>
+    <t>IDM ISOTONC FRUIT350</t>
+  </si>
+  <si>
+    <t>20141601</t>
+  </si>
+  <si>
+    <t>IDM ISOTONC LYCHE350</t>
+  </si>
+  <si>
+    <t>20065248</t>
+  </si>
+  <si>
+    <t>ION WATER BTL 350ML</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>20118832</t>
+  </si>
+  <si>
+    <t>ION WATER BTL 500ML</t>
+  </si>
+  <si>
+    <t>20015838</t>
+  </si>
+  <si>
+    <t>POCARI SWEAT 350ML</t>
+  </si>
+  <si>
+    <t>20009722</t>
+  </si>
+  <si>
+    <t>POCARI SWEAT 500ML</t>
+  </si>
+  <si>
+    <t>20038777</t>
+  </si>
+  <si>
+    <t>POCARI SWEAT 900ML</t>
+  </si>
+  <si>
+    <t>20019674</t>
+  </si>
+  <si>
+    <t>YOU C1000 ORG WTR500</t>
+  </si>
+  <si>
+    <t>20019673</t>
+  </si>
+  <si>
+    <t>YOU C1000 LMN WTR500</t>
+  </si>
+  <si>
+    <t>20057867</t>
+  </si>
+  <si>
+    <t>HYDRO COCO 500ML</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>20119876</t>
+  </si>
+  <si>
+    <t>HYDR.COCO VITA-D 330</t>
+  </si>
+  <si>
+    <t>20018435</t>
+  </si>
+  <si>
+    <t>HYDRO COCO 250ML</t>
+  </si>
+  <si>
+    <t>20115548</t>
+  </si>
+  <si>
+    <t>IDM COCONUT WTR 250</t>
+  </si>
+  <si>
+    <t>20089821</t>
+  </si>
+  <si>
+    <t>ORONAMIN C DRINK 120</t>
+  </si>
+  <si>
+    <t>RT,(E-1.5B)</t>
+  </si>
+  <si>
+    <t>20115549</t>
+  </si>
+  <si>
+    <t>FIBE MINI 100ML</t>
+  </si>
+  <si>
+    <t>20142467</t>
+  </si>
+  <si>
+    <t>FIT ME UP RLX 160</t>
+  </si>
+  <si>
+    <t>20141124</t>
+  </si>
+  <si>
+    <t>REGEN ORANGE 300ML</t>
+  </si>
+  <si>
+    <t>20139550</t>
+  </si>
+  <si>
+    <t>REGEN LMN LIME 300ML</t>
+  </si>
+  <si>
+    <t>20009737</t>
+  </si>
+  <si>
+    <t>YOU C1000 DRK ORG140</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>10039897</t>
+  </si>
+  <si>
+    <t>YOU C1000 DRK LMN140</t>
+  </si>
+  <si>
+    <t>20032519</t>
+  </si>
+  <si>
+    <t>YOU C1000 DRK APL140</t>
+  </si>
+  <si>
+    <t>20115636</t>
+  </si>
+  <si>
+    <t>YOU C1000 DRK MGO140</t>
+  </si>
+  <si>
+    <t>20113135</t>
+  </si>
+  <si>
+    <t>AMUNIZER BTL 140ML</t>
+  </si>
+  <si>
+    <t>20048546</t>
+  </si>
+  <si>
+    <t>HEMAVITON C1000 330</t>
+  </si>
+  <si>
+    <t>20103178</t>
+  </si>
+  <si>
+    <t>HMVTON C1000 LSO 330</t>
+  </si>
+  <si>
+    <t>20103368</t>
+  </si>
+  <si>
+    <t>HMVTON C1000 LMN 330</t>
+  </si>
+  <si>
+    <t>20128794</t>
+  </si>
+  <si>
+    <t>NS/GOODNES KURMA 189</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>20103718</t>
+  </si>
+  <si>
+    <t>TJH KURMA SUSU KR189</t>
+  </si>
+  <si>
+    <t>20124409</t>
+  </si>
+  <si>
+    <t>INDOMLK STRL HNY 189</t>
+  </si>
+  <si>
+    <t>20136193</t>
+  </si>
+  <si>
+    <t>SO GOOD SUSU STRL189</t>
+  </si>
+  <si>
+    <t>20133805</t>
+  </si>
+  <si>
+    <t>ENTRSL OLIVE STRL180</t>
+  </si>
+  <si>
+    <t>20134968</t>
+  </si>
+  <si>
+    <t>COLLAGENA STERIL189</t>
+  </si>
+  <si>
+    <t>20140174</t>
+  </si>
+  <si>
+    <t>BEAR BRAND CLGEN 189</t>
+  </si>
+  <si>
+    <t>10004906</t>
+  </si>
+  <si>
+    <t>BEAR BRAND STERIL189</t>
+  </si>
+  <si>
+    <t>20136952</t>
+  </si>
+  <si>
+    <t>V-SOY SOYA BEAN 300</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>20048096</t>
+  </si>
+  <si>
+    <t>20038726</t>
+  </si>
+  <si>
+    <t>NARAYA KDLAI BTL320</t>
+  </si>
+  <si>
+    <t>20107748</t>
+  </si>
+  <si>
+    <t>MILKU SUSU CKLT 200</t>
+  </si>
+  <si>
+    <t>20107749</t>
+  </si>
+  <si>
+    <t>MILKU SUSU STRO 200</t>
+  </si>
+  <si>
+    <t>20141102</t>
+  </si>
+  <si>
+    <t>MILKU UHT MARIE 200</t>
+  </si>
+  <si>
+    <t>20134047</t>
+  </si>
+  <si>
+    <t>MILKU SUSU ORGNAL200</t>
+  </si>
+  <si>
+    <t>10003373</t>
+  </si>
+  <si>
+    <t>INDOMILK CAIR CHO190</t>
+  </si>
+  <si>
+    <t>10003426</t>
+  </si>
+  <si>
+    <t>INDOMILK CAIR STW190</t>
+  </si>
+  <si>
+    <t>10004443</t>
+  </si>
+  <si>
+    <t>INDOMILK UHT CKL 180</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>10004442</t>
+  </si>
+  <si>
+    <t>INDOMLK UHT STRW 180</t>
+  </si>
+  <si>
+    <t>20070569</t>
+  </si>
+  <si>
+    <t>INDOMLK BANANA 180</t>
+  </si>
+  <si>
+    <t>20134956</t>
+  </si>
+  <si>
+    <t>INDOMILK GOGUMA 180</t>
+  </si>
+  <si>
+    <t>20127735</t>
+  </si>
+  <si>
+    <t>INDMLK DLGNA COFF180</t>
+  </si>
+  <si>
+    <t>20125062</t>
+  </si>
+  <si>
+    <t>INDOMLK KR.BNANA 180</t>
+  </si>
+  <si>
+    <t>20132659</t>
+  </si>
+  <si>
+    <t>INDOMLK HK LYCHEE180</t>
+  </si>
+  <si>
+    <t>20091807</t>
+  </si>
+  <si>
+    <t>DIAMOND UHT CKLT 200</t>
+  </si>
+  <si>
+    <t>20136644</t>
+  </si>
+  <si>
+    <t>DIAMOND UHT MARSM200</t>
+  </si>
+  <si>
+    <t>20137977</t>
+  </si>
+  <si>
+    <t>DIAMOND UHT BBLGM200</t>
+  </si>
+  <si>
+    <t>20019179</t>
+  </si>
+  <si>
+    <t>B/BRAND GOLD MALT140</t>
+  </si>
+  <si>
+    <t>20032643</t>
+  </si>
+  <si>
+    <t>ULTRA LOW FAT COK250</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>20032644</t>
+  </si>
+  <si>
+    <t>ULTRA LOW FAT PLN250</t>
+  </si>
+  <si>
+    <t>20130186</t>
+  </si>
+  <si>
+    <t>GRNFLD UHT CHOCO 250</t>
+  </si>
+  <si>
+    <t>20118209</t>
+  </si>
+  <si>
+    <t>GRNFLD UHT STRAW 250</t>
+  </si>
+  <si>
+    <t>20087413</t>
+  </si>
+  <si>
+    <t>GRNFLD UHT F.CRM 250</t>
+  </si>
+  <si>
+    <t>20138916</t>
+  </si>
+  <si>
+    <t>CIMORY THAI TEA 250</t>
+  </si>
+  <si>
+    <t>20136951</t>
+  </si>
+  <si>
+    <t>CMORY UHT MATCHA 250</t>
+  </si>
+  <si>
+    <t>RT,(E-0.5B)</t>
+  </si>
+  <si>
+    <t>20140795</t>
+  </si>
+  <si>
+    <t>CIMORY UHT CHOCO 225</t>
+  </si>
+  <si>
+    <t>20140794</t>
+  </si>
+  <si>
+    <t>CIMORY UHT MARIE 225</t>
+  </si>
+  <si>
+    <t>20140793</t>
+  </si>
+  <si>
+    <t>CIMORY UHT MTCHA 225</t>
+  </si>
+  <si>
+    <t>20122822</t>
+  </si>
+  <si>
+    <t>CMORY UHT MARIE 250</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>20115187</t>
+  </si>
+  <si>
+    <t>CMORY UHT HZLNUT 250</t>
+  </si>
+  <si>
+    <t>20115188</t>
+  </si>
+  <si>
+    <t>CMORY UHT ALMND 250</t>
+  </si>
+  <si>
+    <t>20104637</t>
+  </si>
+  <si>
+    <t>CIMORY UHT CSHEW 250</t>
+  </si>
+  <si>
+    <t>20099571</t>
+  </si>
+  <si>
+    <t>CIMORY UHT CHOCO 250</t>
+  </si>
+  <si>
+    <t>20104636</t>
+  </si>
+  <si>
+    <t>CIMORY UHT CHOML 250</t>
+  </si>
+  <si>
+    <t>20129109</t>
+  </si>
+  <si>
+    <t>CIMORY CHO.TRMSU 250</t>
+  </si>
+  <si>
+    <t>20099572</t>
+  </si>
+  <si>
+    <t>CIMORY UHT STRAW 250</t>
+  </si>
+  <si>
+    <t>20134390</t>
+  </si>
+  <si>
+    <t>CIMORY BBS LKTSA 250</t>
+  </si>
+  <si>
+    <t>20025753</t>
+  </si>
+  <si>
+    <t>F/F L/FAT COK TPK225</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>20088875</t>
+  </si>
+  <si>
+    <t>FF SWT.DLGHT TPK 225</t>
+  </si>
+  <si>
+    <t>20070253</t>
+  </si>
+  <si>
+    <t>FF COCONUT TPK 225ML</t>
+  </si>
+  <si>
+    <t>20034079</t>
+  </si>
+  <si>
+    <t>F/FLAG COKLT TPK 225</t>
+  </si>
+  <si>
+    <t>20034078</t>
+  </si>
+  <si>
+    <t>F/FLAG STRWB TPK 225</t>
+  </si>
+  <si>
+    <t>20034077</t>
+  </si>
+  <si>
+    <t>F/F FULL CRM TPK 225</t>
+  </si>
+  <si>
+    <t>20128754</t>
+  </si>
+  <si>
+    <t>FF SS.SEREAL CKL 225</t>
+  </si>
+  <si>
+    <t>20136769</t>
+  </si>
+  <si>
+    <t>F.FLAG UHT BERIS 225</t>
+  </si>
+  <si>
+    <t>20136768</t>
+  </si>
+  <si>
+    <t>F.FLAG UHT MATCH 225</t>
+  </si>
+  <si>
+    <t>20142233</t>
+  </si>
+  <si>
+    <t>INDOMILK JAPANE M180</t>
+  </si>
+  <si>
+    <t>10004669</t>
+  </si>
+  <si>
+    <t>ULTRA UHT CHOCO 250M</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>10004668</t>
+  </si>
+  <si>
+    <t>ULTRA UHT STRAW 250M</t>
+  </si>
+  <si>
+    <t>10004676</t>
+  </si>
+  <si>
+    <t>ULTRA PLAIN SLIM250M</t>
+  </si>
+  <si>
+    <t>10007380</t>
+  </si>
+  <si>
+    <t>ULTRA SLIM COKLAT200</t>
+  </si>
+  <si>
+    <t>10008095</t>
+  </si>
+  <si>
+    <t>ULTRA SLIM STRAW 200</t>
+  </si>
+  <si>
+    <t>10007379</t>
+  </si>
+  <si>
+    <t>ULTRA SLIM PLAIN 200</t>
+  </si>
+  <si>
+    <t>20090189</t>
+  </si>
+  <si>
+    <t>ULTRA SUSU KRML 200</t>
+  </si>
+  <si>
+    <t>20088964</t>
+  </si>
+  <si>
+    <t>ULTRA SUSU TARO 200</t>
+  </si>
+  <si>
+    <t>20138895</t>
+  </si>
+  <si>
+    <t>ULTRA UHT BLUBRY 200</t>
+  </si>
+  <si>
+    <t>20110968</t>
+  </si>
+  <si>
+    <t>MUJIGAE BNNA MLK 250</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>20110967</t>
+  </si>
+  <si>
+    <t>MUJIGAE CHOC BAN 250</t>
+  </si>
+  <si>
+    <t>20126897</t>
+  </si>
+  <si>
+    <t>MUJIGAE STRW BAN 250</t>
+  </si>
+  <si>
+    <t>20138050</t>
+  </si>
+  <si>
+    <t>MUJIGAE WTRMLN 250</t>
+  </si>
+  <si>
+    <t>20130518</t>
+  </si>
+  <si>
+    <t>TS ALMND.CHOCO 190ML</t>
+  </si>
+  <si>
+    <t>20118377</t>
+  </si>
+  <si>
+    <t>TS OAT VANILLA 190ML</t>
+  </si>
+  <si>
+    <t>20139295</t>
+  </si>
+  <si>
+    <t>BROOKFARM ORI 200ML</t>
+  </si>
+  <si>
+    <t>20139300</t>
+  </si>
+  <si>
+    <t>BROOKFARM MATCHA 200</t>
+  </si>
+  <si>
+    <t>20037974</t>
+  </si>
+  <si>
+    <t>ULTRA UHT MOKA 250</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>20139359</t>
+  </si>
+  <si>
+    <t>KIT KAT CHO KLG 220</t>
+  </si>
+  <si>
+    <t>10014404</t>
+  </si>
+  <si>
+    <t>MILO HEALTY DRINK220</t>
+  </si>
+  <si>
+    <t>20037607</t>
+  </si>
+  <si>
+    <t>MILO DRINK KLG 220ML</t>
+  </si>
+  <si>
+    <t>20135340</t>
+  </si>
+  <si>
+    <t>MILO DRNK EXT.CHO220</t>
+  </si>
+  <si>
+    <t>20136206</t>
+  </si>
+  <si>
+    <t>MILO DRNK COOL 220</t>
+  </si>
+  <si>
+    <t>20139358</t>
+  </si>
+  <si>
+    <t>MILO PRO UHT 225ML</t>
+  </si>
+  <si>
+    <t>20019597</t>
+  </si>
+  <si>
+    <t>MILO ACTIV-GO 180ML</t>
+  </si>
+  <si>
+    <t>20133873</t>
+  </si>
+  <si>
+    <t>MILO CHOCO BANANA180</t>
+  </si>
+  <si>
+    <t>20133871</t>
+  </si>
+  <si>
+    <t>MILO CHOCO CEREAL180</t>
+  </si>
+  <si>
+    <t>20047247</t>
+  </si>
+  <si>
+    <t>AQUA AIR MINERAL 750</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>20008767</t>
+  </si>
+  <si>
+    <t>CLUB AIR MNRAL 600ML</t>
+  </si>
+  <si>
+    <t>20090527</t>
+  </si>
+  <si>
+    <t>CRYSTALIN BTL 600mL</t>
+  </si>
+  <si>
+    <t>20077499</t>
+  </si>
+  <si>
+    <t>PRISTINE 8.6+ BTL600</t>
+  </si>
+  <si>
+    <t>20139699</t>
+  </si>
+  <si>
+    <t>OASIS  MNRL PH9 500</t>
+  </si>
+  <si>
+    <t>20061938</t>
+  </si>
+  <si>
+    <t>SUPER O2 SPRTVO 600</t>
+  </si>
+  <si>
+    <t>20056219</t>
+  </si>
+  <si>
+    <t>ETERNALPLUS BTL 500</t>
+  </si>
+  <si>
+    <t>20045052</t>
+  </si>
+  <si>
+    <t>INDOMARET AIR MIN330</t>
+  </si>
+  <si>
+    <t>PT,(E-0.5B)</t>
+  </si>
+  <si>
+    <t>10015532</t>
+  </si>
+  <si>
+    <t>AQUA AIR MINERAL 330</t>
+  </si>
+  <si>
+    <t>20137991</t>
+  </si>
+  <si>
+    <t>AQUVIVA BTL 700ML</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>20037131</t>
+  </si>
+  <si>
+    <t>PRIM-A AIR MNRAL 600</t>
+  </si>
+  <si>
+    <t>20142495</t>
+  </si>
+  <si>
+    <t>INDOMARET AIR MIN 1L</t>
+  </si>
+  <si>
+    <t>20069208</t>
+  </si>
+  <si>
+    <t>LE MINERALE 600ML</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>10003814</t>
+  </si>
+  <si>
+    <t>AQUA AIR MINERAL 600</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>10004336</t>
+  </si>
+  <si>
+    <t>INDOMARET AIR MIN600</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>PT,(E-1H)</t>
+  </si>
+  <si>
+    <t>20089542</t>
+  </si>
+  <si>
+    <t>IDM AIR MN 8+ BTL500</t>
+  </si>
+  <si>
+    <t>RT,(E-15H)</t>
+  </si>
+  <si>
+    <t>20052629</t>
+  </si>
+  <si>
+    <t>IDM AIR DGN OKSGN600</t>
+  </si>
+  <si>
+    <t>PT,(E-15H)</t>
+  </si>
+  <si>
+    <t>20005529</t>
+  </si>
+  <si>
+    <t>NESTLE PURE LIFE 600</t>
+  </si>
+  <si>
     <t>20138035</t>
   </si>
   <si>
     <t>CAFFINO OATMARIE 200</t>
   </si>
   <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>20078206</t>
-  </si>
-  <si>
-    <t>LUWAK WHT ORGL 220ML</t>
-  </si>
-  <si>
-    <t>20076770</t>
-  </si>
-  <si>
-    <t>G/DAY CAPPUCCINO 230</t>
-  </si>
-  <si>
-    <t>20045674</t>
-  </si>
-  <si>
-    <t>G/DAY F.MOCACINO 230</t>
-  </si>
-  <si>
-    <t>20045673</t>
-  </si>
-  <si>
-    <t>G/DAY TIRAMISU/B 230</t>
-  </si>
-  <si>
-    <t>20056193</t>
-  </si>
-  <si>
-    <t>GOOD DAY AVCDO/D 230</t>
-  </si>
-  <si>
-    <t>20132329</t>
-  </si>
-  <si>
-    <t>GOOD DAY GRVY CKS230</t>
-  </si>
-  <si>
-    <t>20134557</t>
-  </si>
-  <si>
-    <t>OATSIDE CRML MCHT200</t>
-  </si>
-  <si>
-    <t>20129108</t>
-  </si>
-  <si>
-    <t>OATSDE COFFEE 200ML</t>
-  </si>
-  <si>
-    <t>20142499</t>
-  </si>
-  <si>
-    <t>OATSDE ESPR RST 240</t>
-  </si>
-  <si>
-    <t>20139577</t>
-  </si>
-  <si>
-    <t>PC AREN LATTE 210ML</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20139578</t>
-  </si>
-  <si>
-    <t>PC GOLDN CARAMEL 210</t>
-  </si>
-  <si>
-    <t>20139576</t>
-  </si>
-  <si>
-    <t>PC CRMY CPUCCINO 210</t>
-  </si>
-  <si>
-    <t>20142601</t>
-  </si>
-  <si>
-    <t>NSCAFE MTCHA ESP 220</t>
-  </si>
-  <si>
-    <t>20140431</t>
-  </si>
-  <si>
-    <t>NSCAFE KITKAT LAT220</t>
-  </si>
-  <si>
-    <t>20133058</t>
-  </si>
-  <si>
-    <t>NSCAFE OAT LATTE 220</t>
-  </si>
-  <si>
-    <t>20027768</t>
-  </si>
-  <si>
-    <t>NESCAFE COFF CRM 180</t>
-  </si>
-  <si>
-    <t>20114494</t>
-  </si>
-  <si>
-    <t>NSCAFE CRML MCTO 220</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>20114495</t>
-  </si>
-  <si>
-    <t>NESCAFE CPUCCINO 220</t>
-  </si>
-  <si>
-    <t>20114493</t>
-  </si>
-  <si>
-    <t>NESCAFE LATTE 220ML</t>
-  </si>
-  <si>
-    <t>20138057</t>
-  </si>
-  <si>
-    <t>NSCAFE GULA AREN 220</t>
-  </si>
-  <si>
-    <t>20121456</t>
-  </si>
-  <si>
-    <t>NSCAFE ICE BLACK 220</t>
-  </si>
-  <si>
-    <t>20000787</t>
-  </si>
-  <si>
-    <t>NESCAFE ICE.CF OR220</t>
-  </si>
-  <si>
-    <t>20014954</t>
-  </si>
-  <si>
-    <t>NESCAFE ICE.CF MC220</t>
-  </si>
-  <si>
-    <t>20000786</t>
-  </si>
-  <si>
-    <t>NESCAFE ICE.CF LT220</t>
-  </si>
-  <si>
-    <t>20125115</t>
-  </si>
-  <si>
-    <t>STARBUCKS LATTE 220</t>
-  </si>
-  <si>
-    <t>20125126</t>
-  </si>
-  <si>
-    <t>STARBUCKS CARAMEL220</t>
-  </si>
-  <si>
-    <t>20014608</t>
-  </si>
-  <si>
-    <t>HRMVTON PSK BUMI 150</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>10006263</t>
-  </si>
-  <si>
-    <t>HEMAVITON ENERGY 150</t>
-  </si>
-  <si>
-    <t>10002602</t>
-  </si>
-  <si>
-    <t>M-150 HEALT DRINK150</t>
-  </si>
-  <si>
-    <t>10002595</t>
-  </si>
-  <si>
-    <t>KRATINGDAENG 150 ML</t>
-  </si>
-  <si>
-    <t>10003427</t>
-  </si>
-  <si>
-    <t>KRATINGDAENG SPR.150</t>
-  </si>
-  <si>
-    <t>20022431</t>
-  </si>
-  <si>
-    <t>RED BULL E/DRNK 250</t>
-  </si>
-  <si>
-    <t>20056989</t>
-  </si>
-  <si>
-    <t>RED BULL GOLD 250ML</t>
-  </si>
-  <si>
-    <t>20138252</t>
-  </si>
-  <si>
-    <t>EXTRA JOSS ULTIMT250</t>
-  </si>
-  <si>
-    <t>20038425</t>
-  </si>
-  <si>
-    <t>NTRIVE/B BLCKRNT 100</t>
-  </si>
-  <si>
-    <t>20071510</t>
-  </si>
-  <si>
-    <t>NTRVE BNCOL LYCH 100</t>
-  </si>
-  <si>
-    <t>20003786</t>
-  </si>
-  <si>
-    <t>NU GREEN TEA HNY 450</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>20113059</t>
-  </si>
-  <si>
-    <t>NU YOGURT TEA 450ML</t>
-  </si>
-  <si>
-    <t>20139732</t>
-  </si>
-  <si>
-    <t>NU YOGRT TEA BRY 450</t>
-  </si>
-  <si>
-    <t>20036157</t>
-  </si>
-  <si>
-    <t>SOSRO TEH BOTOL 450</t>
-  </si>
-  <si>
-    <t>20002203</t>
-  </si>
-  <si>
-    <t>SOSRO F.TEA APEL 500</t>
-  </si>
-  <si>
-    <t>20003698</t>
-  </si>
-  <si>
-    <t>SOSRO FR.TEA XTRM500</t>
-  </si>
-  <si>
-    <t>20002205</t>
-  </si>
-  <si>
-    <t>SOSRO F.TEA BLKCR500</t>
-  </si>
-  <si>
-    <t>20134046</t>
-  </si>
-  <si>
-    <t>FRUIT TEA FREEZE 500</t>
-  </si>
-  <si>
-    <t>20126464</t>
-  </si>
-  <si>
-    <t>IDM TEH APL&amp;LYCHE350</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>20101897</t>
-  </si>
-  <si>
-    <t>IDM TEH APEL 350ML</t>
-  </si>
-  <si>
-    <t>20132840</t>
-  </si>
-  <si>
-    <t>IDM TEH BLCKCRRNT350</t>
-  </si>
-  <si>
-    <t>20066454</t>
-  </si>
-  <si>
-    <t>FRUIT TEA BLCKCR 350</t>
-  </si>
-  <si>
-    <t>20073495</t>
-  </si>
-  <si>
-    <t>FRUIT TEA FREEZE 350</t>
-  </si>
-  <si>
-    <t>20066455</t>
-  </si>
-  <si>
-    <t>FRUIT TEA APPLE 350</t>
-  </si>
-  <si>
-    <t>20079972</t>
-  </si>
-  <si>
-    <t>FRUIT TEA MRKISA 350</t>
-  </si>
-  <si>
-    <t>20138841</t>
-  </si>
-  <si>
-    <t>POKKA NAT. H.ORG 350</t>
-  </si>
-  <si>
-    <t>20135619</t>
-  </si>
-  <si>
-    <t>TEBS ZERO LYCHEE 300</t>
-  </si>
-  <si>
-    <t>20060207</t>
-  </si>
-  <si>
-    <t>I/OCHA TEH MLATI 350</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>20048934</t>
-  </si>
-  <si>
-    <t>I/OCHA GRN TEA 350ML</t>
-  </si>
-  <si>
-    <t>20142077</t>
-  </si>
-  <si>
-    <t>TEH LEMON MADU 350ML</t>
-  </si>
-  <si>
-    <t>20018904</t>
-  </si>
-  <si>
-    <t>NU GREEN TEA HNY 330</t>
-  </si>
-  <si>
-    <t>20053867</t>
-  </si>
-  <si>
-    <t>TEH GELAS BTL 350ML</t>
-  </si>
-  <si>
-    <t>20073396</t>
-  </si>
-  <si>
-    <t>S-TEE BTL 390ML</t>
-  </si>
-  <si>
-    <t>20072249</t>
-  </si>
-  <si>
-    <t>SOSRO TEH BOTOL 350</t>
-  </si>
-  <si>
-    <t>20122278</t>
-  </si>
-  <si>
-    <t>TEH BOTOL LS.SGR 350</t>
-  </si>
-  <si>
-    <t>20082395</t>
-  </si>
-  <si>
-    <t>TEH BOTOL TAWAR 350</t>
-  </si>
-  <si>
-    <t>RT,(E-3.5B)</t>
-  </si>
-  <si>
-    <t>20035484</t>
-  </si>
-  <si>
-    <t>PUCUK/H TEH MLATI350</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>20048155</t>
-  </si>
-  <si>
-    <t>PUCUK/H TEH L/SGR350</t>
-  </si>
-  <si>
-    <t>20037565</t>
-  </si>
-  <si>
-    <t>PUCUK/H TEH MLATI500</t>
-  </si>
-  <si>
-    <t>20048348</t>
-  </si>
-  <si>
-    <t>PUCUK/H TEH L/SGR500</t>
-  </si>
-  <si>
-    <t>10036640</t>
-  </si>
-  <si>
-    <t>TEH KOTAK JASMINE300</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>20048435</t>
-  </si>
-  <si>
-    <t>TEH KOTAK LESS/S 300</t>
-  </si>
-  <si>
-    <t>20143447</t>
-  </si>
-  <si>
-    <t>PUCUK/H TEH ORI 300</t>
-  </si>
-  <si>
-    <t>20143446</t>
-  </si>
-  <si>
-    <t>PUCUK/H TEH L/SGR300</t>
-  </si>
-  <si>
-    <t>20044334</t>
-  </si>
-  <si>
-    <t>SOSRO TEH BTL TPK300</t>
-  </si>
-  <si>
-    <t>10005128</t>
-  </si>
-  <si>
-    <t>SOSRO TEH KOTAK B250</t>
-  </si>
-  <si>
-    <t>20024315</t>
-  </si>
-  <si>
-    <t>TEH BOTOL LS.SGR 250</t>
-  </si>
-  <si>
-    <t>20026226</t>
-  </si>
-  <si>
-    <t>ULTRA TEH KOTAK 500</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>20100142</t>
-  </si>
-  <si>
-    <t>TEH KOTAK BLCKCR 300</t>
-  </si>
-  <si>
-    <t>20100143</t>
-  </si>
-  <si>
-    <t>TEH KOTAK APPLE 300</t>
-  </si>
-  <si>
-    <t>20137159</t>
-  </si>
-  <si>
-    <t>TEH KOTAK MANGGA 300</t>
-  </si>
-  <si>
-    <t>20087016</t>
-  </si>
-  <si>
-    <t>TEH KOTAK LEMON 300</t>
-  </si>
-  <si>
-    <t>20135647</t>
-  </si>
-  <si>
-    <t>TEH KOTAK LYCHEE 300</t>
-  </si>
-  <si>
-    <t>20117687</t>
-  </si>
-  <si>
-    <t>DLMNT BOBA MTCHA 240</t>
-  </si>
-  <si>
-    <t>20117682</t>
-  </si>
-  <si>
-    <t>DLMNT BOBA RD.VEL240</t>
-  </si>
-  <si>
-    <t>20080088</t>
-  </si>
-  <si>
-    <t>POKKA GREEN TEA 450</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>20036765</t>
-  </si>
-  <si>
-    <t>FRESTEA GRN MADU 500</t>
-  </si>
-  <si>
-    <t>20012574</t>
-  </si>
-  <si>
-    <t>FRESTEA TEH APEL 500</t>
-  </si>
-  <si>
-    <t>20035829</t>
-  </si>
-  <si>
-    <t>TEBS TEA WT/SODA 500</t>
-  </si>
-  <si>
-    <t>20093586</t>
-  </si>
-  <si>
-    <t>ICHTN THAI M.COFF300</t>
-  </si>
-  <si>
-    <t>20136363</t>
-  </si>
-  <si>
-    <t>ICHTN DARK CHOCO 300</t>
-  </si>
-  <si>
-    <t>20135599</t>
-  </si>
-  <si>
-    <t>ICHTAN KRN BANANA300</t>
-  </si>
-  <si>
-    <t>20142025</t>
-  </si>
-  <si>
-    <t>ICHITAN MLN MILK 300</t>
-  </si>
-  <si>
-    <t>20040383</t>
-  </si>
-  <si>
-    <t>NU MILK TEA 330ML</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>20069527</t>
-  </si>
-  <si>
-    <t>NU TEH TARIK 330ML</t>
-  </si>
-  <si>
-    <t>20128233</t>
-  </si>
-  <si>
-    <t>NU CHO TEA HZLTEA330</t>
-  </si>
-  <si>
-    <t>20138202</t>
-  </si>
-  <si>
-    <t>NU MATCHA LATTEA 330</t>
-  </si>
-  <si>
-    <t>20141981</t>
-  </si>
-  <si>
-    <t>DUM2 CHO MILK TEA330</t>
-  </si>
-  <si>
-    <t>20141980</t>
-  </si>
-  <si>
-    <t>DUM2 RYL MILK TEA330</t>
-  </si>
-  <si>
-    <t>20085054</t>
-  </si>
-  <si>
-    <t>ICHTN THAI M.TEA 300</t>
-  </si>
-  <si>
-    <t>20101102</t>
-  </si>
-  <si>
-    <t>ICHTN MLK GR.TEA 300</t>
-  </si>
-  <si>
-    <t>20113450</t>
-  </si>
-  <si>
-    <t>ICHITAN MLK BRWN 300</t>
-  </si>
-  <si>
-    <t>20113377</t>
-  </si>
-  <si>
-    <t>FLRDINA COCO BIT 350</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>20043877</t>
-  </si>
-  <si>
-    <t>FLORIDINA ORANGE 350</t>
-  </si>
-  <si>
-    <t>20021178</t>
-  </si>
-  <si>
-    <t>MINUTE MAID ORG 300</t>
-  </si>
-  <si>
-    <t>20062818</t>
-  </si>
-  <si>
-    <t>FRUITAMIN LYCHE 350</t>
-  </si>
-  <si>
-    <t>20091654</t>
-  </si>
-  <si>
-    <t>COCO BIT SP.GUAV 350</t>
-  </si>
-  <si>
-    <t>20140331</t>
-  </si>
-  <si>
-    <t>COCO BIT STRAW.S 350</t>
-  </si>
-  <si>
-    <t>20140327</t>
-  </si>
-  <si>
-    <t>COCO BIT KY.GRP 350</t>
-  </si>
-  <si>
-    <t>20140332</t>
-  </si>
-  <si>
-    <t>COCO BIT HOK.MLN 350</t>
-  </si>
-  <si>
-    <t>20042848</t>
-  </si>
-  <si>
-    <t>MOGU MOGU LYCHHE 320</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>20047245</t>
-  </si>
-  <si>
-    <t>MOGU MOGU CCONUT 320</t>
-  </si>
-  <si>
-    <t>20076486</t>
-  </si>
-  <si>
-    <t>MOGU MOGU MELON 320</t>
-  </si>
-  <si>
-    <t>20042859</t>
-  </si>
-  <si>
-    <t>MOGU MOGU MANGGA 320</t>
-  </si>
-  <si>
-    <t>20042860</t>
-  </si>
-  <si>
-    <t>MOGU MOGU STRWBRY320</t>
-  </si>
-  <si>
-    <t>20047244</t>
-  </si>
-  <si>
-    <t>MOGU MOGU GRAPE 320</t>
-  </si>
-  <si>
-    <t>20137095</t>
-  </si>
-  <si>
-    <t>MOGU2 BUBBLE GUM 320</t>
-  </si>
-  <si>
-    <t>20136277</t>
-  </si>
-  <si>
-    <t>SNPRD FRT MG.PINE220</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>20134353</t>
-  </si>
-  <si>
-    <t>IDM S/B NNS&amp;MRKSA220</t>
-  </si>
-  <si>
-    <t>20134354</t>
-  </si>
-  <si>
-    <t>IDM SARI BH NANAS220</t>
-  </si>
-  <si>
-    <t>20089805</t>
-  </si>
-  <si>
-    <t>OLATTE PEACH KLG 240</t>
-  </si>
-  <si>
-    <t>RT,(E-2.5B)</t>
-  </si>
-  <si>
-    <t>20089806</t>
-  </si>
-  <si>
-    <t>OLATTE PEAR KLG 240</t>
-  </si>
-  <si>
-    <t>20135975</t>
-  </si>
-  <si>
-    <t>OLATTE STRWB KLG 240</t>
-  </si>
-  <si>
-    <t>20052734</t>
-  </si>
-  <si>
-    <t>LOTTE MILKIS MLN 250</t>
-  </si>
-  <si>
-    <t>10028190</t>
-  </si>
-  <si>
-    <t>LOTTE MILKIS KLG 250</t>
-  </si>
-  <si>
-    <t>10008887</t>
-  </si>
-  <si>
-    <t>ULTRA KCNG HIJAU 250</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>10000278</t>
-  </si>
-  <si>
-    <t>ABC KACANG HIJAU 250</t>
-  </si>
-  <si>
-    <t>20120929</t>
-  </si>
-  <si>
-    <t>PANDA GR.JLY+BSL 310</t>
-  </si>
-  <si>
-    <t>20046319</t>
-  </si>
-  <si>
-    <t>PANDA GRASS JELY310</t>
-  </si>
-  <si>
-    <t>20141495</t>
-  </si>
-  <si>
-    <t>PANDA GRN GRS JEL310</t>
-  </si>
-  <si>
-    <t>20112383</t>
-  </si>
-  <si>
-    <t>MR.NATA JELI LECI126</t>
-  </si>
-  <si>
-    <t>20112382</t>
-  </si>
-  <si>
-    <t>MR.NATA JEL BLU/B126</t>
-  </si>
-  <si>
-    <t>20136250</t>
-  </si>
-  <si>
-    <t>JELE JELLY LYCHEE150</t>
-  </si>
-  <si>
-    <t>20055762</t>
-  </si>
-  <si>
-    <t>JELE COLLAGEN 150G</t>
-  </si>
-  <si>
-    <t>10007970</t>
-  </si>
-  <si>
-    <t>BUAVITA JAMBU SL 245</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>10007974</t>
-  </si>
-  <si>
-    <t>BUAVITA LYCHEE SL245</t>
-  </si>
-  <si>
-    <t>10007971</t>
-  </si>
-  <si>
-    <t>BUAVITA ORANGE SL245</t>
-  </si>
-  <si>
-    <t>10007973</t>
-  </si>
-  <si>
-    <t>BUAVITA MANGGA 245ML</t>
-  </si>
-  <si>
-    <t>10007972</t>
-  </si>
-  <si>
-    <t>BUAVITA JC APPLE 245</t>
-  </si>
-  <si>
-    <t>20140324</t>
-  </si>
-  <si>
-    <t>BUAVITA K.STRAW 245</t>
-  </si>
-  <si>
-    <t>20140328</t>
-  </si>
-  <si>
-    <t>BUAVITA K MS.GRP 245</t>
-  </si>
-  <si>
-    <t>10007385</t>
-  </si>
-  <si>
-    <t>ULTRA SR ASAM SLM250</t>
-  </si>
-  <si>
-    <t>20136649</t>
-  </si>
-  <si>
-    <t>DIAMOND JC CRANBR200</t>
-  </si>
-  <si>
-    <t>20065041</t>
-  </si>
-  <si>
-    <t>PORORO BLUEBERY235ML</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>20037137</t>
-  </si>
-  <si>
-    <t>PORORO STROBRI 235ML</t>
-  </si>
-  <si>
-    <t>20037136</t>
-  </si>
-  <si>
-    <t>PORORO SUSU 235ML</t>
-  </si>
-  <si>
-    <t>20085010</t>
-  </si>
-  <si>
-    <t>PORORO MANGO 235</t>
-  </si>
-  <si>
-    <t>20137094</t>
-  </si>
-  <si>
-    <t>PORORO PEACH 235</t>
-  </si>
-  <si>
-    <t>20141361</t>
-  </si>
-  <si>
-    <t>PORORO ZERO STRW 235</t>
-  </si>
-  <si>
-    <t>20141360</t>
-  </si>
-  <si>
-    <t>PORORO ZERO MILK 235</t>
-  </si>
-  <si>
-    <t>20129123</t>
-  </si>
-  <si>
-    <t>OATSDE CHOCO 200</t>
-  </si>
-  <si>
-    <t>20129102</t>
-  </si>
-  <si>
-    <t>OATSDE BR.BLEND 200</t>
-  </si>
-  <si>
-    <t>20069773</t>
-  </si>
-  <si>
-    <t>ISOPLUS BTL 350ML</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>20128918</t>
-  </si>
-  <si>
-    <t>ISOPLUS COCO 350ML</t>
-  </si>
-  <si>
-    <t>20138959</t>
-  </si>
-  <si>
-    <t>IF COCONUT WTR 350ML</t>
-  </si>
-  <si>
-    <t>20142818</t>
-  </si>
-  <si>
-    <t>EWATER GRAPEFRT 555</t>
-  </si>
-  <si>
-    <t>20142819</t>
-  </si>
-  <si>
-    <t>EWATER LEMON 555ML</t>
-  </si>
-  <si>
-    <t>20142862</t>
-  </si>
-  <si>
-    <t>EWATER GRPFRT 380</t>
-  </si>
-  <si>
-    <t>20142863</t>
-  </si>
-  <si>
-    <t>EWATER LEMON 380</t>
-  </si>
-  <si>
-    <t>20108987</t>
-  </si>
-  <si>
-    <t>V-SOY MULTI-GRAIN200</t>
-  </si>
-  <si>
-    <t>20123171</t>
-  </si>
-  <si>
-    <t>LACTASOY MILK CLG250</t>
-  </si>
-  <si>
-    <t>20135311</t>
-  </si>
-  <si>
-    <t>HYDROPL ISTNC JRK350</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>20142358</t>
-  </si>
-  <si>
-    <t>POWRADE ACTIV WHT400</t>
-  </si>
-  <si>
-    <t>20142359</t>
-  </si>
-  <si>
-    <t>POWRADE ISOTN BLU400</t>
-  </si>
-  <si>
-    <t>20138837</t>
-  </si>
-  <si>
-    <t>MZONE COCO BOOST 500</t>
-  </si>
-  <si>
-    <t>20094167</t>
-  </si>
-  <si>
-    <t>MIZONE MOOD UP 500</t>
-  </si>
-  <si>
-    <t>20094164</t>
-  </si>
-  <si>
-    <t>MIZONE ACTIVE 500ML</t>
-  </si>
-  <si>
-    <t>20141600</t>
-  </si>
-  <si>
-    <t>IDM ISOTONC FRUIT350</t>
-  </si>
-  <si>
-    <t>20141601</t>
-  </si>
-  <si>
-    <t>IDM ISOTONC LYCHE350</t>
-  </si>
-  <si>
-    <t>20065248</t>
-  </si>
-  <si>
-    <t>ION WATER BTL 350ML</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>20118832</t>
-  </si>
-  <si>
-    <t>ION WATER BTL 500ML</t>
-  </si>
-  <si>
-    <t>20015838</t>
-  </si>
-  <si>
-    <t>POCARI SWEAT 350ML</t>
-  </si>
-  <si>
-    <t>20009722</t>
-  </si>
-  <si>
-    <t>POCARI SWEAT 500ML</t>
-  </si>
-  <si>
-    <t>20038777</t>
-  </si>
-  <si>
-    <t>POCARI SWEAT 900ML</t>
-  </si>
-  <si>
-    <t>20019674</t>
-  </si>
-  <si>
-    <t>YOU C1000 ORG WTR500</t>
-  </si>
-  <si>
-    <t>20019673</t>
-  </si>
-  <si>
-    <t>YOU C1000 LMN WTR500</t>
-  </si>
-  <si>
-    <t>20057867</t>
-  </si>
-  <si>
-    <t>HYDRO COCO 500ML</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>20119876</t>
-  </si>
-  <si>
-    <t>HYDR.COCO VITA-D 330</t>
-  </si>
-  <si>
-    <t>20018435</t>
-  </si>
-  <si>
-    <t>HYDRO COCO 250ML</t>
-  </si>
-  <si>
-    <t>20115548</t>
-  </si>
-  <si>
-    <t>IDM COCONUT WTR 250</t>
-  </si>
-  <si>
-    <t>20089821</t>
-  </si>
-  <si>
-    <t>ORONAMIN C DRINK 120</t>
-  </si>
-  <si>
-    <t>RT,(E-1.5B)</t>
-  </si>
-  <si>
-    <t>20115549</t>
-  </si>
-  <si>
-    <t>FIBE MINI 100ML</t>
-  </si>
-  <si>
-    <t>20142467</t>
-  </si>
-  <si>
-    <t>FIT ME UP RLX 160</t>
-  </si>
-  <si>
-    <t>20141124</t>
-  </si>
-  <si>
-    <t>REGEN ORANGE 300ML</t>
-  </si>
-  <si>
-    <t>20139550</t>
-  </si>
-  <si>
-    <t>REGEN LMN LIME 300ML</t>
-  </si>
-  <si>
-    <t>20009737</t>
-  </si>
-  <si>
-    <t>YOU C1000 DRK ORG140</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>10039897</t>
-  </si>
-  <si>
-    <t>YOU C1000 DRK LMN140</t>
-  </si>
-  <si>
-    <t>20032519</t>
-  </si>
-  <si>
-    <t>YOU C1000 DRK APL140</t>
-  </si>
-  <si>
-    <t>20115636</t>
-  </si>
-  <si>
-    <t>YOU C1000 DRK MGO140</t>
-  </si>
-  <si>
-    <t>20113135</t>
-  </si>
-  <si>
-    <t>AMUNIZER BTL 140ML</t>
-  </si>
-  <si>
-    <t>20048546</t>
-  </si>
-  <si>
-    <t>HEMAVITON C1000 330</t>
-  </si>
-  <si>
-    <t>20103178</t>
-  </si>
-  <si>
-    <t>HMVTON C1000 LSO 330</t>
-  </si>
-  <si>
-    <t>20103368</t>
-  </si>
-  <si>
-    <t>HMVTON C1000 LMN 330</t>
-  </si>
-  <si>
-    <t>20128794</t>
-  </si>
-  <si>
-    <t>NS/GOODNES KURMA 189</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>20103718</t>
-  </si>
-  <si>
-    <t>TJH KURMA SUSU KR189</t>
-  </si>
-  <si>
-    <t>20124409</t>
-  </si>
-  <si>
-    <t>INDOMLK STRL HNY 189</t>
-  </si>
-  <si>
-    <t>20136193</t>
-  </si>
-  <si>
-    <t>SO GOOD SUSU STRL189</t>
-  </si>
-  <si>
-    <t>20133805</t>
-  </si>
-  <si>
-    <t>ENTRSL OLIVE STRL180</t>
-  </si>
-  <si>
-    <t>20134968</t>
-  </si>
-  <si>
-    <t>COLLAGENA STERIL189</t>
-  </si>
-  <si>
-    <t>20140174</t>
-  </si>
-  <si>
-    <t>BEAR BRAND CLGEN 189</t>
-  </si>
-  <si>
-    <t>10004906</t>
-  </si>
-  <si>
-    <t>BEAR BRAND STERIL189</t>
-  </si>
-  <si>
-    <t>20136952</t>
-  </si>
-  <si>
-    <t>V-SOY SOYA BEAN 300</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>20048096</t>
-  </si>
-  <si>
-    <t>20038726</t>
-  </si>
-  <si>
-    <t>NARAYA KDLAI BTL320</t>
-  </si>
-  <si>
-    <t>20107748</t>
-  </si>
-  <si>
-    <t>MILKU SUSU CKLT 200</t>
-  </si>
-  <si>
-    <t>20107749</t>
-  </si>
-  <si>
-    <t>MILKU SUSU STRO 200</t>
-  </si>
-  <si>
-    <t>20141102</t>
-  </si>
-  <si>
-    <t>MILKU UHT MARIE 200</t>
-  </si>
-  <si>
-    <t>20134047</t>
-  </si>
-  <si>
-    <t>MILKU SUSU ORGNAL200</t>
-  </si>
-  <si>
-    <t>10003373</t>
-  </si>
-  <si>
-    <t>INDOMILK CAIR CHO190</t>
-  </si>
-  <si>
-    <t>10003426</t>
-  </si>
-  <si>
-    <t>INDOMILK CAIR STW190</t>
-  </si>
-  <si>
-    <t>10004443</t>
-  </si>
-  <si>
-    <t>INDOMILK UHT CKL 180</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>10004442</t>
-  </si>
-  <si>
-    <t>INDOMLK UHT STRW 180</t>
-  </si>
-  <si>
-    <t>20070569</t>
-  </si>
-  <si>
-    <t>INDOMLK BANANA 180</t>
-  </si>
-  <si>
-    <t>20134956</t>
-  </si>
-  <si>
-    <t>INDOMILK GOGUMA 180</t>
-  </si>
-  <si>
-    <t>20127735</t>
-  </si>
-  <si>
-    <t>INDMLK DLGNA COFF180</t>
-  </si>
-  <si>
-    <t>20125062</t>
-  </si>
-  <si>
-    <t>INDOMLK KR.BNANA 180</t>
-  </si>
-  <si>
-    <t>20132659</t>
-  </si>
-  <si>
-    <t>INDOMLK HK LYCHEE180</t>
-  </si>
-  <si>
-    <t>20091807</t>
-  </si>
-  <si>
-    <t>DIAMOND UHT CKLT 200</t>
-  </si>
-  <si>
-    <t>20136644</t>
-  </si>
-  <si>
-    <t>DIAMOND UHT MARSM200</t>
-  </si>
-  <si>
-    <t>20137977</t>
-  </si>
-  <si>
-    <t>DIAMOND UHT BBLGM200</t>
-  </si>
-  <si>
-    <t>20019179</t>
-  </si>
-  <si>
-    <t>B/BRAND GOLD MALT140</t>
-  </si>
-  <si>
-    <t>20032643</t>
-  </si>
-  <si>
-    <t>ULTRA LOW FAT COK250</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>20032644</t>
-  </si>
-  <si>
-    <t>ULTRA LOW FAT PLN250</t>
-  </si>
-  <si>
-    <t>20130186</t>
-  </si>
-  <si>
-    <t>GRNFLD UHT CHOCO 250</t>
-  </si>
-  <si>
-    <t>20118209</t>
-  </si>
-  <si>
-    <t>GRNFLD UHT STRAW 250</t>
-  </si>
-  <si>
-    <t>20087413</t>
-  </si>
-  <si>
-    <t>GRNFLD UHT F.CRM 250</t>
-  </si>
-  <si>
-    <t>20138916</t>
-  </si>
-  <si>
-    <t>CIMORY THAI TEA 250</t>
-  </si>
-  <si>
-    <t>20136951</t>
-  </si>
-  <si>
-    <t>CMORY UHT MATCHA 250</t>
-  </si>
-  <si>
-    <t>RT,(E-0.5B)</t>
-  </si>
-  <si>
-    <t>20140795</t>
-  </si>
-  <si>
-    <t>CIMORY UHT CHOCO 225</t>
-  </si>
-  <si>
-    <t>20140794</t>
-  </si>
-  <si>
-    <t>CIMORY UHT MARIE 225</t>
-  </si>
-  <si>
-    <t>20140793</t>
-  </si>
-  <si>
-    <t>CIMORY UHT MTCHA 225</t>
-  </si>
-  <si>
-    <t>20122822</t>
-  </si>
-  <si>
-    <t>CMORY UHT MARIE 250</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>20115187</t>
-  </si>
-  <si>
-    <t>CMORY UHT HZLNUT 250</t>
-  </si>
-  <si>
-    <t>20115188</t>
-  </si>
-  <si>
-    <t>CMORY UHT ALMND 250</t>
-  </si>
-  <si>
-    <t>20104637</t>
-  </si>
-  <si>
-    <t>CIMORY UHT CSHEW 250</t>
-  </si>
-  <si>
-    <t>20099571</t>
-  </si>
-  <si>
-    <t>CIMORY UHT CHOCO 250</t>
-  </si>
-  <si>
-    <t>20104636</t>
-  </si>
-  <si>
-    <t>CIMORY UHT CHOML 250</t>
-  </si>
-  <si>
-    <t>20129109</t>
-  </si>
-  <si>
-    <t>CIMORY CHO.TRMSU 250</t>
-  </si>
-  <si>
-    <t>20099572</t>
-  </si>
-  <si>
-    <t>CIMORY UHT STRAW 250</t>
-  </si>
-  <si>
-    <t>20134390</t>
-  </si>
-  <si>
-    <t>CIMORY BBS LKTSA 250</t>
-  </si>
-  <si>
-    <t>20025753</t>
-  </si>
-  <si>
-    <t>F/F L/FAT COK TPK225</t>
-  </si>
-  <si>
-    <t>38</t>
-  </si>
-  <si>
-    <t>20088875</t>
-  </si>
-  <si>
-    <t>FF SWT.DLGHT TPK 225</t>
-  </si>
-  <si>
-    <t>20070253</t>
-  </si>
-  <si>
-    <t>FF COCONUT TPK 225ML</t>
-  </si>
-  <si>
-    <t>20034079</t>
-  </si>
-  <si>
-    <t>F/FLAG COKLT TPK 225</t>
-  </si>
-  <si>
-    <t>20034078</t>
-  </si>
-  <si>
-    <t>F/FLAG STRWB TPK 225</t>
-  </si>
-  <si>
-    <t>20034077</t>
-  </si>
-  <si>
-    <t>F/F FULL CRM TPK 225</t>
-  </si>
-  <si>
-    <t>20128754</t>
-  </si>
-  <si>
-    <t>FF SS.SEREAL CKL 225</t>
-  </si>
-  <si>
-    <t>20136769</t>
-  </si>
-  <si>
-    <t>F.FLAG UHT BERIS 225</t>
-  </si>
-  <si>
-    <t>20136768</t>
-  </si>
-  <si>
-    <t>F.FLAG UHT MATCH 225</t>
-  </si>
-  <si>
-    <t>20142233</t>
-  </si>
-  <si>
-    <t>INDOMILK JAPANE M180</t>
-  </si>
-  <si>
-    <t>10004669</t>
-  </si>
-  <si>
-    <t>ULTRA UHT CHOCO 250M</t>
-  </si>
-  <si>
-    <t>39</t>
-  </si>
-  <si>
-    <t>10004668</t>
-  </si>
-  <si>
-    <t>ULTRA UHT STRAW 250M</t>
-  </si>
-  <si>
-    <t>10004676</t>
-  </si>
-  <si>
-    <t>ULTRA PLAIN SLIM250M</t>
-  </si>
-  <si>
-    <t>10007380</t>
-  </si>
-  <si>
-    <t>ULTRA SLIM COKLAT200</t>
-  </si>
-  <si>
-    <t>10008095</t>
-  </si>
-  <si>
-    <t>ULTRA SLIM STRAW 200</t>
-  </si>
-  <si>
-    <t>10007379</t>
-  </si>
-  <si>
-    <t>ULTRA SLIM PLAIN 200</t>
-  </si>
-  <si>
-    <t>20090189</t>
-  </si>
-  <si>
-    <t>ULTRA SUSU KRML 200</t>
-  </si>
-  <si>
-    <t>20088964</t>
-  </si>
-  <si>
-    <t>ULTRA SUSU TARO 200</t>
-  </si>
-  <si>
-    <t>20138895</t>
-  </si>
-  <si>
-    <t>ULTRA UHT BLUBRY 200</t>
-  </si>
-  <si>
-    <t>20110968</t>
-  </si>
-  <si>
-    <t>MUJIGAE BNNA MLK 250</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>20110967</t>
-  </si>
-  <si>
-    <t>MUJIGAE CHOC BAN 250</t>
-  </si>
-  <si>
-    <t>20126897</t>
-  </si>
-  <si>
-    <t>MUJIGAE STRW BAN 250</t>
-  </si>
-  <si>
-    <t>20138050</t>
-  </si>
-  <si>
-    <t>MUJIGAE WTRMLN 250</t>
-  </si>
-  <si>
-    <t>20130518</t>
-  </si>
-  <si>
-    <t>TS ALMND.CHOCO 190ML</t>
-  </si>
-  <si>
-    <t>20118377</t>
-  </si>
-  <si>
-    <t>TS OAT VANILLA 190ML</t>
-  </si>
-  <si>
-    <t>20139295</t>
-  </si>
-  <si>
-    <t>BROOKFARM ORI 200ML</t>
-  </si>
-  <si>
-    <t>20139300</t>
-  </si>
-  <si>
-    <t>BROOKFARM MATCHA 200</t>
-  </si>
-  <si>
-    <t>20037974</t>
-  </si>
-  <si>
-    <t>ULTRA UHT MOKA 250</t>
-  </si>
-  <si>
-    <t>41</t>
-  </si>
-  <si>
-    <t>20139359</t>
-  </si>
-  <si>
-    <t>KIT KAT CHO KLG 220</t>
-  </si>
-  <si>
-    <t>10014404</t>
-  </si>
-  <si>
-    <t>MILO HEALTY DRINK220</t>
-  </si>
-  <si>
-    <t>20037607</t>
-  </si>
-  <si>
-    <t>MILO DRINK KLG 220ML</t>
-  </si>
-  <si>
-    <t>20135340</t>
-  </si>
-  <si>
-    <t>MILO DRNK EXT.CHO220</t>
-  </si>
-  <si>
-    <t>20136206</t>
-  </si>
-  <si>
-    <t>MILO DRNK COOL 220</t>
-  </si>
-  <si>
-    <t>20139358</t>
-  </si>
-  <si>
-    <t>MILO PRO UHT 225ML</t>
-  </si>
-  <si>
-    <t>20019597</t>
-  </si>
-  <si>
-    <t>MILO ACTIV-GO 180ML</t>
-  </si>
-  <si>
-    <t>20133873</t>
-  </si>
-  <si>
-    <t>MILO CHOCO BANANA180</t>
-  </si>
-  <si>
-    <t>20133871</t>
-  </si>
-  <si>
-    <t>MILO CHOCO CEREAL180</t>
-  </si>
-  <si>
-    <t>20047247</t>
-  </si>
-  <si>
-    <t>AQUA AIR MINERAL 750</t>
-  </si>
-  <si>
-    <t>42</t>
-  </si>
-  <si>
-    <t>20008767</t>
-  </si>
-  <si>
-    <t>CLUB AIR MNRAL 600ML</t>
-  </si>
-  <si>
-    <t>20090527</t>
-  </si>
-  <si>
-    <t>CRYSTALIN BTL 600mL</t>
-  </si>
-  <si>
-    <t>20077499</t>
-  </si>
-  <si>
-    <t>PRISTINE 8.6+ BTL600</t>
-  </si>
-  <si>
-    <t>20139699</t>
-  </si>
-  <si>
-    <t>OASIS  MNRL PH9 500</t>
-  </si>
-  <si>
-    <t>20061938</t>
-  </si>
-  <si>
-    <t>SUPER O2 SPRTVO 600</t>
-  </si>
-  <si>
-    <t>20056219</t>
-  </si>
-  <si>
-    <t>ETERNALPLUS BTL 500</t>
-  </si>
-  <si>
-    <t>20045052</t>
-  </si>
-  <si>
-    <t>INDOMARET AIR MIN330</t>
-  </si>
-  <si>
-    <t>PT,(E-0.5B)</t>
-  </si>
-  <si>
-    <t>10015532</t>
-  </si>
-  <si>
-    <t>AQUA AIR MINERAL 330</t>
-  </si>
-  <si>
-    <t>20137991</t>
-  </si>
-  <si>
-    <t>AQUVIVA BTL 700ML</t>
-  </si>
-  <si>
-    <t>43</t>
-  </si>
-  <si>
-    <t>20037131</t>
-  </si>
-  <si>
-    <t>PRIM-A AIR MNRAL 600</t>
-  </si>
-  <si>
-    <t>20142495</t>
-  </si>
-  <si>
-    <t>INDOMARET AIR MIN 1L</t>
-  </si>
-  <si>
-    <t>20069208</t>
-  </si>
-  <si>
-    <t>LE MINERALE 600ML</t>
-  </si>
-  <si>
-    <t>44</t>
-  </si>
-  <si>
-    <t>10003814</t>
-  </si>
-  <si>
-    <t>AQUA AIR MINERAL 600</t>
-  </si>
-  <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>10004336</t>
-  </si>
-  <si>
-    <t>INDOMARET AIR MIN600</t>
-  </si>
-  <si>
-    <t>46</t>
-  </si>
-  <si>
-    <t>PT,(E-1H)</t>
-  </si>
-  <si>
-    <t>20089542</t>
-  </si>
-  <si>
-    <t>IDM AIR MN 8+ BTL500</t>
-  </si>
-  <si>
-    <t>RT,(E-15H)</t>
-  </si>
-  <si>
-    <t>20052629</t>
-  </si>
-  <si>
-    <t>IDM AIR DGN OKSGN600</t>
-  </si>
-  <si>
-    <t>PT,(E-15H)</t>
-  </si>
-  <si>
-    <t>20005529</t>
-  </si>
-  <si>
-    <t>NESTLE PURE LIFE 600</t>
+    <t>998</t>
   </si>
 </sst>
 </file>
@@ -2710,13 +2719,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F355"/>
+  <dimension ref="A1:F356"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="5" width="4" customWidth="1"/>
+    <col min="4" max="4" width="5" customWidth="1"/>
+    <col min="5" max="5" width="4" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3774,7 +3784,7 @@
         <v>55</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>77</v>
@@ -3794,7 +3804,7 @@
         <v>55</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>77</v>
@@ -3811,13 +3821,13 @@
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -3834,7 +3844,7 @@
         <v>58</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>23</v>
@@ -3854,7 +3864,7 @@
         <v>58</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>23</v>
@@ -3874,7 +3884,7 @@
         <v>58</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>23</v>
@@ -3894,7 +3904,7 @@
         <v>58</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>23</v>
@@ -3914,7 +3924,7 @@
         <v>58</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>23</v>
@@ -3934,7 +3944,7 @@
         <v>58</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>23</v>
@@ -3954,7 +3964,7 @@
         <v>58</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>23</v>
@@ -3974,7 +3984,7 @@
         <v>58</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>23</v>
@@ -3994,7 +4004,7 @@
         <v>58</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>142</v>
+        <v>58</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>23</v>
@@ -4002,22 +4012,22 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B65" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="B65" s="1" t="s">
+      <c r="C65" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E65" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C65" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="E65" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F65" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -4031,13 +4041,13 @@
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -4051,13 +4061,13 @@
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -4071,10 +4081,10 @@
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>31</v>
@@ -4091,10 +4101,10 @@
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>31</v>
@@ -4111,10 +4121,10 @@
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>31</v>
@@ -4131,13 +4141,13 @@
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -4151,13 +4161,13 @@
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -4171,10 +4181,10 @@
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>23</v>
@@ -4191,33 +4201,33 @@
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>163</v>
+        <v>144</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>164</v>
+        <v>23</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D75" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B75" s="1" t="s">
+      <c r="E75" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F75" s="1" t="s">
         <v>166</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D75" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="E75" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F75" s="1" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -4231,13 +4241,13 @@
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -4251,13 +4261,13 @@
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>23</v>
+        <v>166</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -4271,10 +4281,10 @@
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>23</v>
@@ -4291,13 +4301,13 @@
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -4311,13 +4321,13 @@
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -4331,30 +4341,30 @@
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>179</v>
+        <v>165</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B82" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="B82" s="1" t="s">
+      <c r="C82" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D82" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="C82" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>179</v>
-      </c>
       <c r="E82" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>31</v>
@@ -4371,10 +4381,10 @@
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>31</v>
@@ -4391,13 +4401,13 @@
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -4411,13 +4421,13 @@
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -4431,10 +4441,10 @@
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>31</v>
@@ -4451,10 +4461,10 @@
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>31</v>
@@ -4471,10 +4481,10 @@
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>31</v>
@@ -4491,13 +4501,13 @@
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -4511,10 +4521,10 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>142</v>
+        <v>58</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>23</v>
@@ -4531,30 +4541,30 @@
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>200</v>
+        <v>181</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>4</v>
+        <v>144</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B92" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="B92" s="1" t="s">
+      <c r="C92" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D92" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="C92" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>200</v>
-      </c>
       <c r="E92" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>28</v>
@@ -4571,13 +4581,13 @@
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>77</v>
+        <v>28</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
@@ -4591,13 +4601,13 @@
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>23</v>
+        <v>77</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -4611,10 +4621,10 @@
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>23</v>
@@ -4631,13 +4641,13 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -4651,13 +4661,13 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -4671,10 +4681,10 @@
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>23</v>
@@ -4691,13 +4701,13 @@
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -4711,10 +4721,10 @@
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>142</v>
+        <v>58</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>5</v>
@@ -4731,30 +4741,30 @@
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>221</v>
+        <v>202</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>4</v>
+        <v>144</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B102" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B102" s="1" t="s">
+      <c r="C102" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D102" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="C102" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>221</v>
-      </c>
       <c r="E102" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>23</v>
@@ -4771,10 +4781,10 @@
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>23</v>
@@ -4791,10 +4801,10 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>23</v>
@@ -4811,10 +4821,10 @@
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>23</v>
@@ -4831,10 +4841,10 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>23</v>
@@ -4851,10 +4861,10 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>23</v>
@@ -4871,10 +4881,10 @@
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>23</v>
@@ -4891,33 +4901,33 @@
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>238</v>
+        <v>223</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>164</v>
+        <v>23</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="B110" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="B110" s="1" t="s">
+      <c r="C110" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D110" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="C110" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D110" s="1" t="s">
-        <v>238</v>
-      </c>
       <c r="E110" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -4931,13 +4941,13 @@
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -4951,13 +4961,13 @@
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>23</v>
+        <v>166</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
@@ -4971,10 +4981,10 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>23</v>
@@ -4991,10 +5001,10 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>23</v>
@@ -5011,10 +5021,10 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>23</v>
@@ -5031,10 +5041,10 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>23</v>
@@ -5051,10 +5061,10 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>23</v>
@@ -5071,10 +5081,10 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>257</v>
+        <v>240</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>23</v>
@@ -5082,19 +5092,19 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B119" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="B119" s="1" t="s">
+      <c r="C119" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D119" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="C119" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D119" s="1" t="s">
-        <v>257</v>
-      </c>
       <c r="E119" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>23</v>
@@ -5111,10 +5121,10 @@
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>23</v>
@@ -5131,10 +5141,10 @@
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>23</v>
@@ -5151,10 +5161,10 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>23</v>
@@ -5171,10 +5181,10 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>23</v>
@@ -5191,10 +5201,10 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>23</v>
@@ -5211,10 +5221,10 @@
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>23</v>
@@ -5231,50 +5241,50 @@
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>274</v>
+        <v>23</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="B127" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="B127" s="1" t="s">
+      <c r="C127" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="E127" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F127" s="1" t="s">
         <v>276</v>
-      </c>
-      <c r="C127" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D127" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="E127" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F127" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="B128" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="B128" s="1" t="s">
+      <c r="C128" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D128" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="C128" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D128" s="1" t="s">
-        <v>277</v>
-      </c>
       <c r="E128" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>23</v>
@@ -5291,10 +5301,10 @@
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>23</v>
@@ -5311,10 +5321,10 @@
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>23</v>
@@ -5331,10 +5341,10 @@
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>23</v>
@@ -5342,19 +5352,19 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B132" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="B132" s="1" t="s">
+      <c r="C132" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D132" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="C132" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D132" s="1" t="s">
-        <v>286</v>
-      </c>
       <c r="E132" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>23</v>
@@ -5371,10 +5381,10 @@
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>23</v>
@@ -5391,10 +5401,10 @@
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>23</v>
@@ -5411,10 +5421,10 @@
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>23</v>
@@ -5431,10 +5441,10 @@
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>23</v>
@@ -5451,10 +5461,10 @@
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>23</v>
@@ -5471,10 +5481,10 @@
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>301</v>
+        <v>288</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>23</v>
@@ -5482,19 +5492,19 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B139" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="B139" s="1" t="s">
+      <c r="C139" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D139" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="C139" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D139" s="1" t="s">
-        <v>301</v>
-      </c>
       <c r="E139" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>23</v>
@@ -5511,10 +5521,10 @@
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>23</v>
@@ -5531,10 +5541,10 @@
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>23</v>
@@ -5551,10 +5561,10 @@
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>23</v>
@@ -5571,10 +5581,10 @@
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>23</v>
@@ -5591,13 +5601,13 @@
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
@@ -5611,10 +5621,10 @@
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>28</v>
@@ -5631,33 +5641,33 @@
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>318</v>
+        <v>303</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="B147" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="B147" s="1" t="s">
+      <c r="C147" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D147" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="C147" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D147" s="1" t="s">
-        <v>318</v>
-      </c>
       <c r="E147" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
@@ -5671,10 +5681,10 @@
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>5</v>
@@ -5691,13 +5701,13 @@
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
@@ -5711,13 +5721,13 @@
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
@@ -5731,13 +5741,13 @@
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
@@ -5751,10 +5761,10 @@
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>23</v>
@@ -5771,10 +5781,10 @@
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>23</v>
@@ -5791,10 +5801,10 @@
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>335</v>
+        <v>320</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>23</v>
@@ -5802,19 +5812,19 @@
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="B155" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="B155" s="1" t="s">
+      <c r="C155" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D155" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="C155" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D155" s="1" t="s">
-        <v>335</v>
-      </c>
       <c r="E155" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>23</v>
@@ -5831,10 +5841,10 @@
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>23</v>
@@ -5851,10 +5861,10 @@
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>23</v>
@@ -5871,10 +5881,10 @@
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>23</v>
@@ -5891,10 +5901,10 @@
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>23</v>
@@ -5911,13 +5921,13 @@
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
@@ -5931,10 +5941,10 @@
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>31</v>
@@ -5951,10 +5961,10 @@
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>31</v>
@@ -5971,30 +5981,30 @@
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>354</v>
+        <v>337</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="B164" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="B164" s="1" t="s">
+      <c r="C164" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D164" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="C164" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D164" s="1" t="s">
-        <v>354</v>
-      </c>
       <c r="E164" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>23</v>
@@ -6011,13 +6021,13 @@
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
@@ -6031,13 +6041,13 @@
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
@@ -6051,10 +6061,10 @@
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>23</v>
@@ -6071,10 +6081,10 @@
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>23</v>
@@ -6091,10 +6101,10 @@
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>23</v>
@@ -6111,10 +6121,10 @@
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F170" s="1" t="s">
         <v>23</v>
@@ -6131,10 +6141,10 @@
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>371</v>
+        <v>356</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>23</v>
@@ -6142,19 +6152,19 @@
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="B172" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="B172" s="1" t="s">
+      <c r="C172" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D172" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="C172" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D172" s="1" t="s">
-        <v>371</v>
-      </c>
       <c r="E172" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>23</v>
@@ -6171,10 +6181,10 @@
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>23</v>
@@ -6191,10 +6201,10 @@
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>23</v>
@@ -6211,10 +6221,10 @@
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>23</v>
@@ -6231,10 +6241,10 @@
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>23</v>
@@ -6251,10 +6261,10 @@
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F177" s="1" t="s">
         <v>23</v>
@@ -6271,33 +6281,33 @@
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>386</v>
+        <v>373</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="B179" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="B179" s="1" t="s">
+      <c r="C179" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D179" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="C179" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D179" s="1" t="s">
-        <v>386</v>
-      </c>
       <c r="E179" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
@@ -6311,10 +6321,10 @@
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>23</v>
@@ -6331,33 +6341,33 @@
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>393</v>
+        <v>23</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="B182" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="B182" s="1" t="s">
+      <c r="C182" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D182" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="E182" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F182" s="1" t="s">
         <v>395</v>
-      </c>
-      <c r="C182" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D182" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="E182" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F182" s="1" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
@@ -6371,13 +6381,13 @@
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>23</v>
+        <v>395</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
@@ -6391,13 +6401,13 @@
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
@@ -6411,10 +6421,10 @@
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F185" s="1" t="s">
         <v>28</v>
@@ -6431,33 +6441,33 @@
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>404</v>
+        <v>388</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="B187" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="B187" s="1" t="s">
+      <c r="C187" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D187" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="C187" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D187" s="1" t="s">
-        <v>404</v>
-      </c>
       <c r="E187" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
@@ -6471,13 +6481,13 @@
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
@@ -6491,13 +6501,13 @@
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>77</v>
+        <v>28</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
@@ -6511,13 +6521,13 @@
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>23</v>
+        <v>77</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
@@ -6531,13 +6541,13 @@
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
@@ -6551,10 +6561,10 @@
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F192" s="1" t="s">
         <v>31</v>
@@ -6571,13 +6581,13 @@
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
@@ -6591,10 +6601,10 @@
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F194" s="1" t="s">
         <v>23</v>
@@ -6611,10 +6621,10 @@
         <v>3</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>423</v>
+        <v>406</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>23</v>
@@ -6622,19 +6632,19 @@
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B196" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="B196" s="1" t="s">
+      <c r="C196" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D196" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="C196" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D196" s="1" t="s">
-        <v>423</v>
-      </c>
       <c r="E196" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F196" s="1" t="s">
         <v>23</v>
@@ -6651,10 +6661,10 @@
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F197" s="1" t="s">
         <v>23</v>
@@ -6671,10 +6681,10 @@
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F198" s="1" t="s">
         <v>23</v>
@@ -6691,10 +6701,10 @@
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F199" s="1" t="s">
         <v>23</v>
@@ -6711,10 +6721,10 @@
         <v>3</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F200" s="1" t="s">
         <v>23</v>
@@ -6731,10 +6741,10 @@
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F201" s="1" t="s">
         <v>23</v>
@@ -6751,10 +6761,10 @@
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F202" s="1" t="s">
         <v>23</v>
@@ -6771,10 +6781,10 @@
         <v>3</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F203" s="1" t="s">
         <v>23</v>
@@ -6791,10 +6801,10 @@
         <v>3</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>442</v>
+        <v>425</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="F204" s="1" t="s">
         <v>23</v>
@@ -6802,19 +6812,19 @@
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="B205" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="B205" s="1" t="s">
+      <c r="C205" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D205" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="C205" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D205" s="1" t="s">
-        <v>442</v>
-      </c>
       <c r="E205" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F205" s="1" t="s">
         <v>23</v>
@@ -6831,10 +6841,10 @@
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F206" s="1" t="s">
         <v>23</v>
@@ -6851,10 +6861,10 @@
         <v>3</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F207" s="1" t="s">
         <v>23</v>
@@ -6871,10 +6881,10 @@
         <v>3</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F208" s="1" t="s">
         <v>23</v>
@@ -6891,10 +6901,10 @@
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F209" s="1" t="s">
         <v>23</v>
@@ -6911,10 +6921,10 @@
         <v>3</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F210" s="1" t="s">
         <v>23</v>
@@ -6931,10 +6941,10 @@
         <v>3</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F211" s="1" t="s">
         <v>23</v>
@@ -6951,10 +6961,10 @@
         <v>3</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F212" s="1" t="s">
         <v>23</v>
@@ -7277,7 +7287,7 @@
         <v>38</v>
       </c>
       <c r="F228" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
@@ -7297,7 +7307,7 @@
         <v>55</v>
       </c>
       <c r="F229" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
@@ -7517,7 +7527,7 @@
         <v>14</v>
       </c>
       <c r="F240" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
@@ -8314,7 +8324,7 @@
         <v>584</v>
       </c>
       <c r="E280" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F280" s="1" t="s">
         <v>23</v>
@@ -8334,7 +8344,7 @@
         <v>584</v>
       </c>
       <c r="E281" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F281" s="1" t="s">
         <v>23</v>
@@ -8534,7 +8544,7 @@
         <v>607</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F291" s="1" t="s">
         <v>23</v>
@@ -8914,7 +8924,7 @@
         <v>648</v>
       </c>
       <c r="E310" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F310" s="1" t="s">
         <v>23</v>
@@ -9454,7 +9464,7 @@
         <v>705</v>
       </c>
       <c r="E337" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F337" s="1" t="s">
         <v>23</v>
@@ -9697,7 +9707,7 @@
         <v>11</v>
       </c>
       <c r="F349" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.25">
@@ -9817,6 +9827,26 @@
         <v>14</v>
       </c>
       <c r="F355" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="356" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A356" s="1" t="s">
+        <v>769</v>
+      </c>
+      <c r="B356" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="C356" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D356" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="E356" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F356" s="1" t="s">
         <v>23</v>
       </c>
     </row>

--- a/CLB07N.xlsx
+++ b/CLB07N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2136" uniqueCount="772">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2130" uniqueCount="770">
   <si>
     <t/>
   </si>
@@ -304,7 +304,7 @@
     <t>20142024</t>
   </si>
   <si>
-    <t>COOLTOPIA MELON ORG</t>
+    <t>KK3 CLTPIA ML/ORG320</t>
   </si>
   <si>
     <t>20045996</t>
@@ -1778,12 +1778,6 @@
   </si>
   <si>
     <t>INDOMLK BANANA 180</t>
-  </si>
-  <si>
-    <t>20134956</t>
-  </si>
-  <si>
-    <t>INDOMILK GOGUMA 180</t>
   </si>
   <si>
     <t>20127735</t>
@@ -2719,7 +2713,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F356"/>
+  <dimension ref="A1:F355"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -8204,7 +8198,7 @@
         <v>584</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F274" s="1" t="s">
         <v>23</v>
@@ -8224,7 +8218,7 @@
         <v>584</v>
       </c>
       <c r="E275" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F275" s="1" t="s">
         <v>23</v>
@@ -8244,7 +8238,7 @@
         <v>584</v>
       </c>
       <c r="E276" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="F276" s="1" t="s">
         <v>23</v>
@@ -8264,7 +8258,7 @@
         <v>584</v>
       </c>
       <c r="E277" s="1" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="F277" s="1" t="s">
         <v>23</v>
@@ -8284,7 +8278,7 @@
         <v>584</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F278" s="1" t="s">
         <v>23</v>
@@ -8304,7 +8298,7 @@
         <v>584</v>
       </c>
       <c r="E279" s="1" t="s">
-        <v>58</v>
+        <v>144</v>
       </c>
       <c r="F279" s="1" t="s">
         <v>23</v>
@@ -8324,7 +8318,7 @@
         <v>584</v>
       </c>
       <c r="E280" s="1" t="s">
-        <v>144</v>
+        <v>165</v>
       </c>
       <c r="F280" s="1" t="s">
         <v>23</v>
@@ -8341,10 +8335,10 @@
         <v>3</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>584</v>
+        <v>605</v>
       </c>
       <c r="E281" s="1" t="s">
-        <v>165</v>
+        <v>4</v>
       </c>
       <c r="F281" s="1" t="s">
         <v>23</v>
@@ -8352,19 +8346,19 @@
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="B282" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="C282" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D282" s="1" t="s">
         <v>605</v>
       </c>
-      <c r="B282" s="1" t="s">
-        <v>606</v>
-      </c>
-      <c r="C282" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D282" s="1" t="s">
-        <v>607</v>
-      </c>
       <c r="E282" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F282" s="1" t="s">
         <v>23</v>
@@ -8381,10 +8375,10 @@
         <v>3</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E283" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F283" s="1" t="s">
         <v>23</v>
@@ -8401,10 +8395,10 @@
         <v>3</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F284" s="1" t="s">
         <v>23</v>
@@ -8421,10 +8415,10 @@
         <v>3</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E285" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F285" s="1" t="s">
         <v>23</v>
@@ -8441,10 +8435,10 @@
         <v>3</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F286" s="1" t="s">
         <v>23</v>
@@ -8461,33 +8455,33 @@
         <v>3</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="F287" s="1" t="s">
-        <v>23</v>
+        <v>618</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288" s="1" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C288" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="F288" s="1" t="s">
-        <v>620</v>
+        <v>23</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
@@ -8501,10 +8495,10 @@
         <v>3</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E289" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F289" s="1" t="s">
         <v>23</v>
@@ -8521,10 +8515,10 @@
         <v>3</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E290" s="1" t="s">
-        <v>58</v>
+        <v>144</v>
       </c>
       <c r="F290" s="1" t="s">
         <v>23</v>
@@ -8541,33 +8535,33 @@
         <v>3</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>607</v>
+        <v>627</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>144</v>
+        <v>4</v>
       </c>
       <c r="F291" s="1" t="s">
-        <v>23</v>
+        <v>618</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A292" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="B292" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="C292" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D292" s="1" t="s">
         <v>627</v>
       </c>
-      <c r="B292" s="1" t="s">
-        <v>628</v>
-      </c>
-      <c r="C292" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D292" s="1" t="s">
-        <v>629</v>
-      </c>
       <c r="E292" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F292" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
@@ -8581,13 +8575,13 @@
         <v>3</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="E293" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F293" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
@@ -8601,13 +8595,13 @@
         <v>3</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="E294" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F294" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
@@ -8621,13 +8615,13 @@
         <v>3</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="E295" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F295" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
@@ -8641,13 +8635,13 @@
         <v>3</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="E296" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F296" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
@@ -8661,13 +8655,13 @@
         <v>3</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="F297" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
@@ -8681,13 +8675,13 @@
         <v>3</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="F298" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
@@ -8701,13 +8695,13 @@
         <v>3</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F299" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
@@ -8721,30 +8715,30 @@
         <v>3</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>629</v>
+        <v>646</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>58</v>
+        <v>4</v>
       </c>
       <c r="F300" s="1" t="s">
-        <v>620</v>
+        <v>23</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A301" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="B301" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="C301" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D301" s="1" t="s">
         <v>646</v>
       </c>
-      <c r="B301" s="1" t="s">
-        <v>647</v>
-      </c>
-      <c r="C301" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D301" s="1" t="s">
-        <v>648</v>
-      </c>
       <c r="E301" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F301" s="1" t="s">
         <v>23</v>
@@ -8761,10 +8755,10 @@
         <v>3</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="E302" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F302" s="1" t="s">
         <v>23</v>
@@ -8781,10 +8775,10 @@
         <v>3</v>
       </c>
       <c r="D303" s="1" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="E303" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F303" s="1" t="s">
         <v>23</v>
@@ -8801,10 +8795,10 @@
         <v>3</v>
       </c>
       <c r="D304" s="1" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="E304" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F304" s="1" t="s">
         <v>23</v>
@@ -8821,10 +8815,10 @@
         <v>3</v>
       </c>
       <c r="D305" s="1" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="E305" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F305" s="1" t="s">
         <v>23</v>
@@ -8841,10 +8835,10 @@
         <v>3</v>
       </c>
       <c r="D306" s="1" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="E306" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="F306" s="1" t="s">
         <v>23</v>
@@ -8861,10 +8855,10 @@
         <v>3</v>
       </c>
       <c r="D307" s="1" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="E307" s="1" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="F307" s="1" t="s">
         <v>23</v>
@@ -8881,10 +8875,10 @@
         <v>3</v>
       </c>
       <c r="D308" s="1" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="E308" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F308" s="1" t="s">
         <v>23</v>
@@ -8901,10 +8895,10 @@
         <v>3</v>
       </c>
       <c r="D309" s="1" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="E309" s="1" t="s">
-        <v>58</v>
+        <v>144</v>
       </c>
       <c r="F309" s="1" t="s">
         <v>23</v>
@@ -8921,10 +8915,10 @@
         <v>3</v>
       </c>
       <c r="D310" s="1" t="s">
-        <v>648</v>
+        <v>667</v>
       </c>
       <c r="E310" s="1" t="s">
-        <v>144</v>
+        <v>4</v>
       </c>
       <c r="F310" s="1" t="s">
         <v>23</v>
@@ -8932,19 +8926,19 @@
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A311" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="B311" s="1" t="s">
+        <v>669</v>
+      </c>
+      <c r="C311" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D311" s="1" t="s">
         <v>667</v>
       </c>
-      <c r="B311" s="1" t="s">
-        <v>668</v>
-      </c>
-      <c r="C311" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D311" s="1" t="s">
-        <v>669</v>
-      </c>
       <c r="E311" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F311" s="1" t="s">
         <v>23</v>
@@ -8961,10 +8955,10 @@
         <v>3</v>
       </c>
       <c r="D312" s="1" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="E312" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F312" s="1" t="s">
         <v>23</v>
@@ -8981,10 +8975,10 @@
         <v>3</v>
       </c>
       <c r="D313" s="1" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="E313" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F313" s="1" t="s">
         <v>23</v>
@@ -9001,10 +8995,10 @@
         <v>3</v>
       </c>
       <c r="D314" s="1" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="E314" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F314" s="1" t="s">
         <v>23</v>
@@ -9021,10 +9015,10 @@
         <v>3</v>
       </c>
       <c r="D315" s="1" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="E315" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F315" s="1" t="s">
         <v>23</v>
@@ -9041,10 +9035,10 @@
         <v>3</v>
       </c>
       <c r="D316" s="1" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="E316" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="F316" s="1" t="s">
         <v>23</v>
@@ -9061,10 +9055,10 @@
         <v>3</v>
       </c>
       <c r="D317" s="1" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="E317" s="1" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="F317" s="1" t="s">
         <v>23</v>
@@ -9081,10 +9075,10 @@
         <v>3</v>
       </c>
       <c r="D318" s="1" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="E318" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F318" s="1" t="s">
         <v>23</v>
@@ -9101,10 +9095,10 @@
         <v>3</v>
       </c>
       <c r="D319" s="1" t="s">
-        <v>669</v>
+        <v>686</v>
       </c>
       <c r="E319" s="1" t="s">
-        <v>58</v>
+        <v>4</v>
       </c>
       <c r="F319" s="1" t="s">
         <v>23</v>
@@ -9112,19 +9106,19 @@
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A320" s="1" t="s">
+        <v>687</v>
+      </c>
+      <c r="B320" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="C320" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D320" s="1" t="s">
         <v>686</v>
       </c>
-      <c r="B320" s="1" t="s">
-        <v>687</v>
-      </c>
-      <c r="C320" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D320" s="1" t="s">
-        <v>688</v>
-      </c>
       <c r="E320" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F320" s="1" t="s">
         <v>23</v>
@@ -9141,10 +9135,10 @@
         <v>3</v>
       </c>
       <c r="D321" s="1" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="E321" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F321" s="1" t="s">
         <v>23</v>
@@ -9161,10 +9155,10 @@
         <v>3</v>
       </c>
       <c r="D322" s="1" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="E322" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F322" s="1" t="s">
         <v>23</v>
@@ -9181,10 +9175,10 @@
         <v>3</v>
       </c>
       <c r="D323" s="1" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="E323" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F323" s="1" t="s">
         <v>23</v>
@@ -9201,10 +9195,10 @@
         <v>3</v>
       </c>
       <c r="D324" s="1" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="E324" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F324" s="1" t="s">
         <v>23</v>
@@ -9221,10 +9215,10 @@
         <v>3</v>
       </c>
       <c r="D325" s="1" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="E325" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="F325" s="1" t="s">
         <v>23</v>
@@ -9241,10 +9235,10 @@
         <v>3</v>
       </c>
       <c r="D326" s="1" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="E326" s="1" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="F326" s="1" t="s">
         <v>23</v>
@@ -9261,10 +9255,10 @@
         <v>3</v>
       </c>
       <c r="D327" s="1" t="s">
-        <v>688</v>
+        <v>703</v>
       </c>
       <c r="E327" s="1" t="s">
-        <v>55</v>
+        <v>4</v>
       </c>
       <c r="F327" s="1" t="s">
         <v>23</v>
@@ -9272,19 +9266,19 @@
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A328" s="1" t="s">
+        <v>704</v>
+      </c>
+      <c r="B328" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="C328" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D328" s="1" t="s">
         <v>703</v>
       </c>
-      <c r="B328" s="1" t="s">
-        <v>704</v>
-      </c>
-      <c r="C328" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D328" s="1" t="s">
-        <v>705</v>
-      </c>
       <c r="E328" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F328" s="1" t="s">
         <v>23</v>
@@ -9301,13 +9295,13 @@
         <v>3</v>
       </c>
       <c r="D329" s="1" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="E329" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F329" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.25">
@@ -9321,10 +9315,10 @@
         <v>3</v>
       </c>
       <c r="D330" s="1" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="E330" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F330" s="1" t="s">
         <v>31</v>
@@ -9341,13 +9335,13 @@
         <v>3</v>
       </c>
       <c r="D331" s="1" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="E331" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F331" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.25">
@@ -9361,10 +9355,10 @@
         <v>3</v>
       </c>
       <c r="D332" s="1" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="E332" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F332" s="1" t="s">
         <v>23</v>
@@ -9381,10 +9375,10 @@
         <v>3</v>
       </c>
       <c r="D333" s="1" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="E333" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="F333" s="1" t="s">
         <v>23</v>
@@ -9401,10 +9395,10 @@
         <v>3</v>
       </c>
       <c r="D334" s="1" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="E334" s="1" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="F334" s="1" t="s">
         <v>23</v>
@@ -9421,10 +9415,10 @@
         <v>3</v>
       </c>
       <c r="D335" s="1" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="E335" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F335" s="1" t="s">
         <v>23</v>
@@ -9441,10 +9435,10 @@
         <v>3</v>
       </c>
       <c r="D336" s="1" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="E336" s="1" t="s">
-        <v>58</v>
+        <v>144</v>
       </c>
       <c r="F336" s="1" t="s">
         <v>23</v>
@@ -9461,33 +9455,33 @@
         <v>3</v>
       </c>
       <c r="D337" s="1" t="s">
-        <v>705</v>
+        <v>724</v>
       </c>
       <c r="E337" s="1" t="s">
-        <v>144</v>
+        <v>4</v>
       </c>
       <c r="F337" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A338" s="1" t="s">
+        <v>725</v>
+      </c>
+      <c r="B338" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="C338" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D338" s="1" t="s">
         <v>724</v>
       </c>
-      <c r="B338" s="1" t="s">
-        <v>725</v>
-      </c>
-      <c r="C338" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D338" s="1" t="s">
-        <v>726</v>
-      </c>
       <c r="E338" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F338" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.25">
@@ -9501,13 +9495,13 @@
         <v>3</v>
       </c>
       <c r="D339" s="1" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="E339" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F339" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.25">
@@ -9521,13 +9515,13 @@
         <v>3</v>
       </c>
       <c r="D340" s="1" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="E340" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F340" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.25">
@@ -9541,13 +9535,13 @@
         <v>3</v>
       </c>
       <c r="D341" s="1" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="E341" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F341" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.25">
@@ -9561,10 +9555,10 @@
         <v>3</v>
       </c>
       <c r="D342" s="1" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="E342" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F342" s="1" t="s">
         <v>23</v>
@@ -9581,13 +9575,13 @@
         <v>3</v>
       </c>
       <c r="D343" s="1" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="E343" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="F343" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.25">
@@ -9601,33 +9595,33 @@
         <v>3</v>
       </c>
       <c r="D344" s="1" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="E344" s="1" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="F344" s="1" t="s">
-        <v>31</v>
+        <v>739</v>
       </c>
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A345" s="1" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="B345" s="1" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C345" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D345" s="1" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="E345" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F345" s="1" t="s">
-        <v>741</v>
+        <v>28</v>
       </c>
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.25">
@@ -9641,30 +9635,30 @@
         <v>3</v>
       </c>
       <c r="D346" s="1" t="s">
-        <v>726</v>
+        <v>744</v>
       </c>
       <c r="E346" s="1" t="s">
-        <v>58</v>
+        <v>4</v>
       </c>
       <c r="F346" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A347" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="B347" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="C347" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D347" s="1" t="s">
         <v>744</v>
       </c>
-      <c r="B347" s="1" t="s">
-        <v>745</v>
-      </c>
-      <c r="C347" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D347" s="1" t="s">
-        <v>746</v>
-      </c>
       <c r="E347" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F347" s="1" t="s">
         <v>23</v>
@@ -9681,13 +9675,13 @@
         <v>3</v>
       </c>
       <c r="D348" s="1" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="E348" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F348" s="1" t="s">
-        <v>23</v>
+        <v>166</v>
       </c>
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.25">
@@ -9701,113 +9695,113 @@
         <v>3</v>
       </c>
       <c r="D349" s="1" t="s">
-        <v>746</v>
+        <v>751</v>
       </c>
       <c r="E349" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F349" s="1" t="s">
-        <v>166</v>
+        <v>23</v>
       </c>
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A350" s="1" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B350" s="1" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C350" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D350" s="1" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="E350" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F350" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A351" s="1" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B351" s="1" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="C351" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D351" s="1" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="E351" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F351" s="1" t="s">
-        <v>28</v>
+        <v>758</v>
       </c>
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A352" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="B352" s="1" t="s">
+        <v>760</v>
+      </c>
+      <c r="C352" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D352" s="1" t="s">
         <v>757</v>
       </c>
-      <c r="B352" s="1" t="s">
-        <v>758</v>
-      </c>
-      <c r="C352" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D352" s="1" t="s">
-        <v>759</v>
-      </c>
       <c r="E352" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F352" s="1" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
     </row>
     <row r="353" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A353" s="1" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="B353" s="1" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="C353" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D353" s="1" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="E353" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F353" s="1" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
     </row>
     <row r="354" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A354" s="1" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="B354" s="1" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="C354" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D354" s="1" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="E354" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F354" s="1" t="s">
-        <v>766</v>
+        <v>23</v>
       </c>
     </row>
     <row r="355" spans="1:6" x14ac:dyDescent="0.25">
@@ -9821,32 +9815,12 @@
         <v>3</v>
       </c>
       <c r="D355" s="1" t="s">
-        <v>759</v>
+        <v>769</v>
       </c>
       <c r="E355" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F355" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="356" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A356" s="1" t="s">
-        <v>769</v>
-      </c>
-      <c r="B356" s="1" t="s">
-        <v>770</v>
-      </c>
-      <c r="C356" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D356" s="1" t="s">
-        <v>771</v>
-      </c>
-      <c r="E356" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F356" s="1" t="s">
         <v>23</v>
       </c>
     </row>

--- a/CLB07N.xlsx
+++ b/CLB07N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2130" uniqueCount="770">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2142" uniqueCount="774">
   <si>
     <t/>
   </si>
@@ -76,21 +76,36 @@
     <t>6</t>
   </si>
   <si>
+    <t>20124899</t>
+  </si>
+  <si>
+    <t>CHI/FRST LYC/FZY 480</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20124898</t>
+  </si>
+  <si>
+    <t>CHI/FRST WHT/PCH 480</t>
+  </si>
+  <si>
+    <t>20139698</t>
+  </si>
+  <si>
+    <t>AJE BIG NPS MADU 350</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
     <t>20129966</t>
   </si>
   <si>
     <t>N/P MINUMAN LIME 330</t>
   </si>
   <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20139698</t>
-  </si>
-  <si>
-    <t>AJE BIG NPS MADU 350</t>
-  </si>
-  <si>
     <t>20127835</t>
   </si>
   <si>
@@ -100,21 +115,6 @@
     <t>RT,(E-3B)</t>
   </si>
   <si>
-    <t>20124899</t>
-  </si>
-  <si>
-    <t>CHI/FRST LYC/FZY 480</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20124898</t>
-  </si>
-  <si>
-    <t>CHI/FRST WHT/PCH 480</t>
-  </si>
-  <si>
     <t>20138893</t>
   </si>
   <si>
@@ -337,22 +337,34 @@
     <t>TEBS SPRK MIX FRT330</t>
   </si>
   <si>
+    <t>20120499</t>
+  </si>
+  <si>
+    <t>K/A SIGNT STRONG 200</t>
+  </si>
+  <si>
+    <t>20089792</t>
+  </si>
+  <si>
+    <t>K/A DRNK BLK COFF200</t>
+  </si>
+  <si>
+    <t>20143469</t>
+  </si>
+  <si>
+    <t>GJAH K/TBRK GL BT200</t>
+  </si>
+  <si>
     <t>20124713</t>
   </si>
   <si>
     <t>LUWAK KOPI+GULA 220</t>
   </si>
   <si>
-    <t>20120499</t>
-  </si>
-  <si>
-    <t>K/A SIGNT STRONG 200</t>
-  </si>
-  <si>
-    <t>20089792</t>
-  </si>
-  <si>
-    <t>K/A DRNK BLK COFF200</t>
+    <t>20078206</t>
+  </si>
+  <si>
+    <t>LUWAK WHT ORGL 220ML</t>
   </si>
   <si>
     <t>20123322</t>
@@ -379,12 +391,6 @@
     <t>ABC MILK COFFEE 180</t>
   </si>
   <si>
-    <t>20078206</t>
-  </si>
-  <si>
-    <t>LUWAK WHT ORGL 220ML</t>
-  </si>
-  <si>
     <t>20120904</t>
   </si>
   <si>
@@ -994,16 +1000,73 @@
     <t>TEBS TEA WT/SODA 500</t>
   </si>
   <si>
+    <t>20141981</t>
+  </si>
+  <si>
+    <t>DUM2 CHO MILK TEA330</t>
+  </si>
+  <si>
+    <t>20141980</t>
+  </si>
+  <si>
+    <t>DUM2 RYL MILK TEA330</t>
+  </si>
+  <si>
+    <t>20136363</t>
+  </si>
+  <si>
+    <t>ICHTN DARK CHOCO 300</t>
+  </si>
+  <si>
     <t>20093586</t>
   </si>
   <si>
     <t>ICHTN THAI M.COFF300</t>
   </si>
   <si>
-    <t>20136363</t>
-  </si>
-  <si>
-    <t>ICHTN DARK CHOCO 300</t>
+    <t>20040383</t>
+  </si>
+  <si>
+    <t>NU MILK TEA 330ML</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>20069527</t>
+  </si>
+  <si>
+    <t>NU TEH TARIK 330ML</t>
+  </si>
+  <si>
+    <t>20128233</t>
+  </si>
+  <si>
+    <t>NU CHO TEA HZLTEA330</t>
+  </si>
+  <si>
+    <t>20138202</t>
+  </si>
+  <si>
+    <t>NU MATCHA LATTEA 330</t>
+  </si>
+  <si>
+    <t>20085054</t>
+  </si>
+  <si>
+    <t>ICHTN THAI M.TEA 300</t>
+  </si>
+  <si>
+    <t>20101102</t>
+  </si>
+  <si>
+    <t>ICHTN MLK GR.TEA 300</t>
+  </si>
+  <si>
+    <t>20113450</t>
+  </si>
+  <si>
+    <t>ICHITAN MLK BRWN 300</t>
   </si>
   <si>
     <t>20135599</t>
@@ -1018,63 +1081,6 @@
     <t>ICHITAN MLN MILK 300</t>
   </si>
   <si>
-    <t>20040383</t>
-  </si>
-  <si>
-    <t>NU MILK TEA 330ML</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>20069527</t>
-  </si>
-  <si>
-    <t>NU TEH TARIK 330ML</t>
-  </si>
-  <si>
-    <t>20128233</t>
-  </si>
-  <si>
-    <t>NU CHO TEA HZLTEA330</t>
-  </si>
-  <si>
-    <t>20138202</t>
-  </si>
-  <si>
-    <t>NU MATCHA LATTEA 330</t>
-  </si>
-  <si>
-    <t>20141981</t>
-  </si>
-  <si>
-    <t>DUM2 CHO MILK TEA330</t>
-  </si>
-  <si>
-    <t>20141980</t>
-  </si>
-  <si>
-    <t>DUM2 RYL MILK TEA330</t>
-  </si>
-  <si>
-    <t>20085054</t>
-  </si>
-  <si>
-    <t>ICHTN THAI M.TEA 300</t>
-  </si>
-  <si>
-    <t>20101102</t>
-  </si>
-  <si>
-    <t>ICHTN MLK GR.TEA 300</t>
-  </si>
-  <si>
-    <t>20113450</t>
-  </si>
-  <si>
-    <t>ICHITAN MLK BRWN 300</t>
-  </si>
-  <si>
     <t>20113377</t>
   </si>
   <si>
@@ -1390,6 +1396,12 @@
     <t>PRRO ZROSGR BLBRY235</t>
   </si>
   <si>
+    <t>20019179</t>
+  </si>
+  <si>
+    <t>B/BRAND GOLD MALT140</t>
+  </si>
+  <si>
     <t>20069773</t>
   </si>
   <si>
@@ -1816,10 +1828,10 @@
     <t>DIAMOND UHT BBLGM200</t>
   </si>
   <si>
-    <t>20019179</t>
-  </si>
-  <si>
-    <t>B/BRAND GOLD MALT140</t>
+    <t>20090314</t>
+  </si>
+  <si>
+    <t>DIAMOND UHT F/C200ML</t>
   </si>
   <si>
     <t>20032643</t>
@@ -2713,7 +2725,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F355"/>
+  <dimension ref="A1:F357"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2941,15 +2953,15 @@
         <v>14</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>33</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
@@ -2961,7 +2973,7 @@
         <v>17</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -2981,7 +2993,7 @@
         <v>20</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -3001,7 +3013,7 @@
         <v>38</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -3221,7 +3233,7 @@
         <v>20</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -3241,7 +3253,7 @@
         <v>38</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -3261,7 +3273,7 @@
         <v>55</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -3281,7 +3293,7 @@
         <v>4</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -3301,7 +3313,7 @@
         <v>8</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -3321,7 +3333,7 @@
         <v>11</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -3341,7 +3353,7 @@
         <v>14</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -3441,7 +3453,7 @@
         <v>4</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -3461,7 +3473,7 @@
         <v>8</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -3481,7 +3493,7 @@
         <v>11</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -3501,7 +3513,7 @@
         <v>14</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -3521,7 +3533,7 @@
         <v>17</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -3641,7 +3653,7 @@
         <v>11</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -3661,7 +3673,7 @@
         <v>14</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -3681,7 +3693,7 @@
         <v>17</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -3701,7 +3713,7 @@
         <v>20</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -3721,7 +3733,7 @@
         <v>38</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -3735,13 +3747,13 @@
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E51" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E51" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F51" s="1" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -3755,10 +3767,10 @@
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>23</v>
@@ -3778,10 +3790,10 @@
         <v>55</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>77</v>
+        <v>28</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -3798,10 +3810,10 @@
         <v>55</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>77</v>
+        <v>28</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -3818,10 +3830,10 @@
         <v>55</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>31</v>
+        <v>77</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -3835,13 +3847,13 @@
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>23</v>
+        <v>77</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -3858,10 +3870,10 @@
         <v>58</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -3878,10 +3890,10 @@
         <v>58</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -3898,10 +3910,10 @@
         <v>58</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -3918,10 +3930,10 @@
         <v>58</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -3938,10 +3950,10 @@
         <v>58</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -3958,10 +3970,10 @@
         <v>58</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -3978,10 +3990,10 @@
         <v>58</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -3998,10 +4010,10 @@
         <v>58</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -4018,30 +4030,30 @@
         <v>58</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>144</v>
+        <v>58</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B66" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="B66" s="1" t="s">
+      <c r="C66" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E66" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="C66" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="E66" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F66" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -4055,13 +4067,13 @@
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -4075,13 +4087,13 @@
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -4095,13 +4107,13 @@
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -4115,13 +4127,13 @@
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -4135,13 +4147,13 @@
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -4155,13 +4167,13 @@
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -4175,10 +4187,10 @@
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>23</v>
@@ -4195,13 +4207,13 @@
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -4215,33 +4227,33 @@
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>165</v>
+        <v>146</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>166</v>
+        <v>28</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D76" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="B76" s="1" t="s">
+      <c r="E76" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F76" s="1" t="s">
         <v>168</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="E76" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F76" s="1" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -4255,13 +4267,13 @@
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -4275,13 +4287,13 @@
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>23</v>
+        <v>168</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -4295,13 +4307,13 @@
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -4315,13 +4327,13 @@
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -4335,10 +4347,10 @@
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>23</v>
@@ -4355,33 +4367,33 @@
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B83" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="B83" s="1" t="s">
+      <c r="C83" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D83" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C83" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D83" s="1" t="s">
-        <v>181</v>
-      </c>
       <c r="E83" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -4395,13 +4407,13 @@
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -4415,10 +4427,10 @@
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>23</v>
@@ -4435,13 +4447,13 @@
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
@@ -4455,13 +4467,13 @@
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -4475,13 +4487,13 @@
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -4495,13 +4507,13 @@
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -4515,10 +4527,10 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>23</v>
@@ -4535,13 +4547,13 @@
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>144</v>
+        <v>58</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -4555,10 +4567,10 @@
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>202</v>
+        <v>183</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>4</v>
+        <v>146</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>28</v>
@@ -4566,22 +4578,22 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B93" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B93" s="1" t="s">
+      <c r="C93" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D93" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="C93" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>202</v>
-      </c>
       <c r="E93" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
@@ -4595,13 +4607,13 @@
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>77</v>
+        <v>33</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -4615,13 +4627,13 @@
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>23</v>
+        <v>77</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -4635,13 +4647,13 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -4655,10 +4667,10 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>28</v>
@@ -4675,13 +4687,13 @@
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -4695,13 +4707,13 @@
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -4715,13 +4727,13 @@
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -4735,10 +4747,10 @@
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>144</v>
+        <v>58</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>5</v>
@@ -4755,33 +4767,33 @@
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>223</v>
+        <v>204</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>4</v>
+        <v>146</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B103" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="B103" s="1" t="s">
+      <c r="C103" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D103" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="C103" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>223</v>
-      </c>
       <c r="E103" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
@@ -4795,13 +4807,13 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
@@ -4815,13 +4827,13 @@
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -4835,13 +4847,13 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -4855,13 +4867,13 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -4875,13 +4887,13 @@
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -4895,13 +4907,13 @@
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -4915,33 +4927,33 @@
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>166</v>
+        <v>28</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B111" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="B111" s="1" t="s">
+      <c r="C111" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D111" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="C111" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D111" s="1" t="s">
-        <v>240</v>
-      </c>
       <c r="E111" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -4955,13 +4967,13 @@
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
@@ -4975,13 +4987,13 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>23</v>
+        <v>168</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
@@ -4995,13 +5007,13 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
@@ -5015,13 +5027,13 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
@@ -5035,13 +5047,13 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
@@ -5055,13 +5067,13 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -5075,13 +5087,13 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -5095,33 +5107,33 @@
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>259</v>
+        <v>242</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B120" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="B120" s="1" t="s">
+      <c r="C120" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D120" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="C120" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D120" s="1" t="s">
-        <v>259</v>
-      </c>
       <c r="E120" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -5135,13 +5147,13 @@
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -5155,13 +5167,13 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -5175,13 +5187,13 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -5195,13 +5207,13 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -5215,13 +5227,13 @@
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -5235,13 +5247,13 @@
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -5255,53 +5267,53 @@
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>276</v>
+        <v>28</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="B128" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="B128" s="1" t="s">
+      <c r="C128" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="E128" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F128" s="1" t="s">
         <v>278</v>
-      </c>
-      <c r="C128" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D128" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="E128" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F128" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B129" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="B129" s="1" t="s">
+      <c r="C129" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D129" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="C129" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D129" s="1" t="s">
-        <v>279</v>
-      </c>
       <c r="E129" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -5315,13 +5327,13 @@
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -5335,13 +5347,13 @@
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
@@ -5355,33 +5367,33 @@
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B133" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="B133" s="1" t="s">
+      <c r="C133" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D133" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="C133" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D133" s="1" t="s">
-        <v>288</v>
-      </c>
       <c r="E133" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -5395,13 +5407,13 @@
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -5415,13 +5427,13 @@
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -5435,13 +5447,13 @@
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
@@ -5455,13 +5467,13 @@
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
@@ -5475,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
@@ -5495,33 +5507,33 @@
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>303</v>
+        <v>290</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B140" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="B140" s="1" t="s">
+      <c r="C140" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D140" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="C140" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D140" s="1" t="s">
-        <v>303</v>
-      </c>
       <c r="E140" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
@@ -5535,13 +5547,13 @@
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
@@ -5555,13 +5567,13 @@
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
@@ -5575,13 +5587,13 @@
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
@@ -5595,13 +5607,13 @@
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
@@ -5615,10 +5627,10 @@
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>28</v>
@@ -5635,13 +5647,13 @@
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
@@ -5655,33 +5667,33 @@
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>320</v>
+        <v>305</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B148" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="B148" s="1" t="s">
+      <c r="C148" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D148" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="C148" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D148" s="1" t="s">
-        <v>320</v>
-      </c>
       <c r="E148" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
@@ -5695,10 +5707,10 @@
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>5</v>
@@ -5715,13 +5727,13 @@
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
@@ -5735,13 +5747,13 @@
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
@@ -5755,13 +5767,13 @@
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
@@ -5775,13 +5787,13 @@
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
@@ -5795,13 +5807,13 @@
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
@@ -5815,10 +5827,10 @@
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>337</v>
+        <v>322</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>23</v>
@@ -5826,22 +5838,22 @@
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="B156" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="B156" s="1" t="s">
+      <c r="C156" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D156" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="C156" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D156" s="1" t="s">
-        <v>337</v>
-      </c>
       <c r="E156" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
@@ -5855,13 +5867,13 @@
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
@@ -5875,13 +5887,13 @@
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
@@ -5895,13 +5907,13 @@
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
@@ -5915,10 +5927,10 @@
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>23</v>
@@ -5935,13 +5947,13 @@
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
@@ -5955,13 +5967,13 @@
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
@@ -5975,13 +5987,13 @@
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
@@ -5995,33 +6007,33 @@
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>356</v>
+        <v>339</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="B165" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="B165" s="1" t="s">
+      <c r="C165" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D165" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="C165" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D165" s="1" t="s">
-        <v>356</v>
-      </c>
       <c r="E165" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
@@ -6035,13 +6047,13 @@
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
@@ -6055,13 +6067,13 @@
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
@@ -6075,13 +6087,13 @@
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
@@ -6095,13 +6107,13 @@
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
@@ -6115,13 +6127,13 @@
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
@@ -6135,13 +6147,13 @@
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
@@ -6155,33 +6167,33 @@
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>373</v>
+        <v>358</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="B173" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="B173" s="1" t="s">
+      <c r="C173" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D173" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="C173" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D173" s="1" t="s">
-        <v>373</v>
-      </c>
       <c r="E173" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
@@ -6195,13 +6207,13 @@
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
@@ -6215,13 +6227,13 @@
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
@@ -6235,13 +6247,13 @@
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
@@ -6255,13 +6267,13 @@
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
@@ -6275,13 +6287,13 @@
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
@@ -6295,10 +6307,10 @@
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>388</v>
+        <v>375</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>28</v>
@@ -6306,22 +6318,22 @@
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="B180" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="B180" s="1" t="s">
+      <c r="C180" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D180" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="C180" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D180" s="1" t="s">
-        <v>388</v>
-      </c>
       <c r="E180" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
@@ -6335,13 +6347,13 @@
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
@@ -6355,33 +6367,33 @@
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>395</v>
+        <v>28</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="B183" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="B183" s="1" t="s">
+      <c r="C183" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D183" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="E183" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F183" s="1" t="s">
         <v>397</v>
-      </c>
-      <c r="C183" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D183" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="E183" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F183" s="1" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
@@ -6395,13 +6407,13 @@
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>23</v>
+        <v>397</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
@@ -6415,10 +6427,10 @@
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F185" s="1" t="s">
         <v>28</v>
@@ -6435,13 +6447,13 @@
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
@@ -6455,33 +6467,33 @@
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>406</v>
+        <v>390</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="B188" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="B188" s="1" t="s">
+      <c r="C188" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D188" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="C188" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D188" s="1" t="s">
-        <v>406</v>
-      </c>
       <c r="E188" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
@@ -6495,13 +6507,13 @@
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
@@ -6515,13 +6527,13 @@
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>77</v>
+        <v>33</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
@@ -6535,13 +6547,13 @@
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>23</v>
+        <v>77</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
@@ -6555,13 +6567,13 @@
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
@@ -6575,13 +6587,13 @@
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
@@ -6595,10 +6607,10 @@
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F194" s="1" t="s">
         <v>23</v>
@@ -6615,13 +6627,13 @@
         <v>3</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F195" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
@@ -6635,33 +6647,33 @@
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>425</v>
+        <v>408</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="F196" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B197" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="B197" s="1" t="s">
+      <c r="C197" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D197" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="C197" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D197" s="1" t="s">
-        <v>425</v>
-      </c>
       <c r="E197" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
@@ -6675,13 +6687,13 @@
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F198" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
@@ -6695,13 +6707,13 @@
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F199" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
@@ -6715,13 +6727,13 @@
         <v>3</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
@@ -6735,13 +6747,13 @@
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
@@ -6755,13 +6767,13 @@
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F202" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
@@ -6775,13 +6787,13 @@
         <v>3</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F203" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
@@ -6795,13 +6807,13 @@
         <v>3</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F204" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
@@ -6815,33 +6827,33 @@
         <v>3</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>444</v>
+        <v>427</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="F205" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="B206" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="B206" s="1" t="s">
+      <c r="C206" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D206" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="C206" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D206" s="1" t="s">
-        <v>444</v>
-      </c>
       <c r="E206" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F206" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
@@ -6855,13 +6867,13 @@
         <v>3</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F207" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
@@ -6875,13 +6887,13 @@
         <v>3</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F208" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
@@ -6895,13 +6907,13 @@
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F209" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
@@ -6915,13 +6927,13 @@
         <v>3</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F210" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
@@ -6935,13 +6947,13 @@
         <v>3</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F211" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
@@ -6955,13 +6967,13 @@
         <v>3</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F212" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
@@ -6975,53 +6987,53 @@
         <v>3</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>461</v>
+        <v>446</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="B214" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="B214" s="1" t="s">
-        <v>463</v>
-      </c>
       <c r="C214" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>461</v>
+        <v>446</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="F214" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="B215" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="B215" s="1" t="s">
+      <c r="C215" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D215" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="C215" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D215" s="1" t="s">
-        <v>461</v>
-      </c>
       <c r="E215" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F215" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
@@ -7035,13 +7047,13 @@
         <v>3</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
@@ -7055,13 +7067,13 @@
         <v>3</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F217" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
@@ -7075,13 +7087,13 @@
         <v>3</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F218" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
@@ -7095,13 +7107,13 @@
         <v>3</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
@@ -7115,10 +7127,10 @@
         <v>3</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="F220" s="1" t="s">
         <v>28</v>
@@ -7135,13 +7147,13 @@
         <v>3</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F221" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
@@ -7155,53 +7167,53 @@
         <v>3</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>480</v>
+        <v>465</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="F222" s="1" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="B223" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="B223" s="1" t="s">
-        <v>482</v>
-      </c>
       <c r="C223" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>480</v>
+        <v>465</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="F223" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="B224" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="B224" s="1" t="s">
+      <c r="C224" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D224" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="C224" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D224" s="1" t="s">
-        <v>480</v>
-      </c>
       <c r="E224" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
@@ -7215,13 +7227,13 @@
         <v>3</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
@@ -7235,13 +7247,13 @@
         <v>3</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
@@ -7255,13 +7267,13 @@
         <v>3</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
@@ -7275,13 +7287,13 @@
         <v>3</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F228" s="1" t="s">
-        <v>166</v>
+        <v>23</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
@@ -7295,13 +7307,13 @@
         <v>3</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="F229" s="1" t="s">
-        <v>166</v>
+        <v>23</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
@@ -7315,53 +7327,53 @@
         <v>3</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>497</v>
+        <v>484</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F230" s="1" t="s">
-        <v>31</v>
+        <v>168</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="B231" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="B231" s="1" t="s">
-        <v>499</v>
-      </c>
       <c r="C231" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>497</v>
+        <v>484</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="F231" s="1" t="s">
-        <v>31</v>
+        <v>168</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="B232" s="1" t="s">
         <v>500</v>
       </c>
-      <c r="B232" s="1" t="s">
+      <c r="C232" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D232" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="C232" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D232" s="1" t="s">
-        <v>497</v>
-      </c>
       <c r="E232" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F232" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
@@ -7375,13 +7387,13 @@
         <v>3</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F233" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
@@ -7395,13 +7407,13 @@
         <v>3</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F234" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
@@ -7415,10 +7427,10 @@
         <v>3</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F235" s="1" t="s">
         <v>23</v>
@@ -7435,10 +7447,10 @@
         <v>3</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F236" s="1" t="s">
         <v>23</v>
@@ -7455,53 +7467,53 @@
         <v>3</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>512</v>
+        <v>501</v>
       </c>
       <c r="E237" s="1" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F237" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="B238" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="B238" s="1" t="s">
-        <v>514</v>
-      </c>
       <c r="C238" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>512</v>
+        <v>501</v>
       </c>
       <c r="E238" s="1" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="F238" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="B239" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="B239" s="1" t="s">
+      <c r="C239" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D239" s="1" t="s">
         <v>516</v>
       </c>
-      <c r="C239" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D239" s="1" t="s">
-        <v>512</v>
-      </c>
       <c r="E239" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F239" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
@@ -7515,13 +7527,13 @@
         <v>3</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="E240" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F240" s="1" t="s">
-        <v>166</v>
+        <v>23</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
@@ -7535,53 +7547,53 @@
         <v>3</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="E241" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F241" s="1" t="s">
-        <v>521</v>
+        <v>23</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="B242" s="1" t="s">
         <v>522</v>
       </c>
-      <c r="B242" s="1" t="s">
-        <v>523</v>
-      </c>
       <c r="C242" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="E242" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F242" s="1" t="s">
-        <v>28</v>
+        <v>168</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="B243" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="B243" s="1" t="s">
+      <c r="C243" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D243" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="E243" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F243" s="1" t="s">
         <v>525</v>
-      </c>
-      <c r="C243" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D243" s="1" t="s">
-        <v>512</v>
-      </c>
-      <c r="E243" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F243" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
@@ -7595,13 +7607,13 @@
         <v>3</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="E244" s="1" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="F244" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
@@ -7615,13 +7627,13 @@
         <v>3</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F245" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
@@ -7635,53 +7647,53 @@
         <v>3</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>532</v>
+        <v>516</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="F246" s="1" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="B247" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="B247" s="1" t="s">
-        <v>534</v>
-      </c>
       <c r="C247" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>532</v>
+        <v>516</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="F247" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="B248" s="1" t="s">
         <v>535</v>
       </c>
-      <c r="B248" s="1" t="s">
+      <c r="C248" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D248" s="1" t="s">
         <v>536</v>
       </c>
-      <c r="C248" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D248" s="1" t="s">
-        <v>532</v>
-      </c>
       <c r="E248" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F248" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
@@ -7695,13 +7707,13 @@
         <v>3</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F249" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
@@ -7715,10 +7727,10 @@
         <v>3</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="E250" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F250" s="1" t="s">
         <v>28</v>
@@ -7735,13 +7747,13 @@
         <v>3</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F251" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
@@ -7755,13 +7767,13 @@
         <v>3</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="E252" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F252" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
@@ -7775,13 +7787,13 @@
         <v>3</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="F253" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
@@ -7795,10 +7807,10 @@
         <v>3</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>549</v>
+        <v>536</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F254" s="1" t="s">
         <v>23</v>
@@ -7806,19 +7818,19 @@
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="B255" s="1" t="s">
         <v>550</v>
       </c>
-      <c r="B255" s="1" t="s">
-        <v>551</v>
-      </c>
       <c r="C255" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>549</v>
+        <v>536</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="F255" s="1" t="s">
         <v>23</v>
@@ -7826,22 +7838,22 @@
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="B256" s="1" t="s">
         <v>552</v>
       </c>
-      <c r="B256" s="1" t="s">
+      <c r="C256" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D256" s="1" t="s">
         <v>553</v>
       </c>
-      <c r="C256" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D256" s="1" t="s">
-        <v>549</v>
-      </c>
       <c r="E256" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F256" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
@@ -7855,13 +7867,13 @@
         <v>3</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="E257" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F257" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
@@ -7875,13 +7887,13 @@
         <v>3</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F258" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
@@ -7895,13 +7907,13 @@
         <v>3</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F259" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
@@ -7915,10 +7927,10 @@
         <v>3</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F260" s="1" t="s">
         <v>23</v>
@@ -7935,13 +7947,13 @@
         <v>3</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="F261" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
@@ -7955,10 +7967,10 @@
         <v>3</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>566</v>
+        <v>553</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F262" s="1" t="s">
         <v>28</v>
@@ -7966,19 +7978,19 @@
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="B263" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="B263" s="1" t="s">
-        <v>565</v>
-      </c>
       <c r="C263" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>566</v>
+        <v>553</v>
       </c>
       <c r="E263" s="1" t="s">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="F263" s="1" t="s">
         <v>28</v>
@@ -7995,33 +8007,33 @@
         <v>3</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="E264" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F264" s="1" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="B265" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="C265" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D265" s="1" t="s">
         <v>570</v>
       </c>
-      <c r="B265" s="1" t="s">
-        <v>571</v>
-      </c>
-      <c r="C265" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D265" s="1" t="s">
-        <v>566</v>
-      </c>
       <c r="E265" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F265" s="1" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
@@ -8035,13 +8047,13 @@
         <v>3</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F266" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
@@ -8055,13 +8067,13 @@
         <v>3</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="E267" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F267" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
@@ -8075,13 +8087,13 @@
         <v>3</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F268" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
@@ -8095,13 +8107,13 @@
         <v>3</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="F269" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
@@ -8115,13 +8127,13 @@
         <v>3</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="E270" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F270" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
@@ -8135,53 +8147,53 @@
         <v>3</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>584</v>
+        <v>570</v>
       </c>
       <c r="E271" s="1" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="F271" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="B272" s="1" t="s">
         <v>585</v>
       </c>
-      <c r="B272" s="1" t="s">
-        <v>586</v>
-      </c>
       <c r="C272" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>584</v>
+        <v>570</v>
       </c>
       <c r="E272" s="1" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="F272" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="B273" s="1" t="s">
         <v>587</v>
       </c>
-      <c r="B273" s="1" t="s">
+      <c r="C273" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D273" s="1" t="s">
         <v>588</v>
       </c>
-      <c r="C273" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D273" s="1" t="s">
-        <v>584</v>
-      </c>
       <c r="E273" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F273" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
@@ -8195,13 +8207,13 @@
         <v>3</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F274" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
@@ -8215,13 +8227,13 @@
         <v>3</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="E275" s="1" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F275" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
@@ -8235,13 +8247,13 @@
         <v>3</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="E276" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F276" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
@@ -8255,13 +8267,13 @@
         <v>3</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="E277" s="1" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="F277" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
@@ -8275,13 +8287,13 @@
         <v>3</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F278" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
@@ -8295,13 +8307,13 @@
         <v>3</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="E279" s="1" t="s">
-        <v>144</v>
+        <v>55</v>
       </c>
       <c r="F279" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
@@ -8315,13 +8327,13 @@
         <v>3</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="E280" s="1" t="s">
-        <v>165</v>
+        <v>58</v>
       </c>
       <c r="F280" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
@@ -8335,53 +8347,53 @@
         <v>3</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>605</v>
+        <v>588</v>
       </c>
       <c r="E281" s="1" t="s">
-        <v>4</v>
+        <v>146</v>
       </c>
       <c r="F281" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="B282" s="1" t="s">
         <v>606</v>
       </c>
-      <c r="B282" s="1" t="s">
-        <v>607</v>
-      </c>
       <c r="C282" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>605</v>
+        <v>588</v>
       </c>
       <c r="E282" s="1" t="s">
-        <v>8</v>
+        <v>167</v>
       </c>
       <c r="F282" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="B283" s="1" t="s">
         <v>608</v>
       </c>
-      <c r="B283" s="1" t="s">
+      <c r="C283" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D283" s="1" t="s">
         <v>609</v>
       </c>
-      <c r="C283" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D283" s="1" t="s">
-        <v>605</v>
-      </c>
       <c r="E283" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F283" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
@@ -8395,13 +8407,13 @@
         <v>3</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F284" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
@@ -8415,13 +8427,13 @@
         <v>3</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="E285" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F285" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
@@ -8435,13 +8447,13 @@
         <v>3</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F286" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
@@ -8455,53 +8467,53 @@
         <v>3</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F287" s="1" t="s">
-        <v>618</v>
+        <v>28</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="B288" s="1" t="s">
         <v>619</v>
       </c>
-      <c r="B288" s="1" t="s">
-        <v>620</v>
-      </c>
       <c r="C288" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="F288" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A289" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="B289" s="1" t="s">
         <v>621</v>
       </c>
-      <c r="B289" s="1" t="s">
+      <c r="C289" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D289" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="E289" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F289" s="1" t="s">
         <v>622</v>
-      </c>
-      <c r="C289" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D289" s="1" t="s">
-        <v>605</v>
-      </c>
-      <c r="E289" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F289" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
@@ -8515,13 +8527,13 @@
         <v>3</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="E290" s="1" t="s">
-        <v>144</v>
+        <v>55</v>
       </c>
       <c r="F290" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
@@ -8535,53 +8547,53 @@
         <v>3</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>627</v>
+        <v>609</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="F291" s="1" t="s">
-        <v>618</v>
+        <v>28</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A292" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="B292" s="1" t="s">
         <v>628</v>
       </c>
-      <c r="B292" s="1" t="s">
-        <v>629</v>
-      </c>
       <c r="C292" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>627</v>
+        <v>609</v>
       </c>
       <c r="E292" s="1" t="s">
-        <v>8</v>
+        <v>146</v>
       </c>
       <c r="F292" s="1" t="s">
-        <v>618</v>
+        <v>28</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A293" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="B293" s="1" t="s">
         <v>630</v>
       </c>
-      <c r="B293" s="1" t="s">
+      <c r="C293" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D293" s="1" t="s">
         <v>631</v>
       </c>
-      <c r="C293" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D293" s="1" t="s">
-        <v>627</v>
-      </c>
       <c r="E293" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F293" s="1" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
@@ -8595,13 +8607,13 @@
         <v>3</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="E294" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F294" s="1" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
@@ -8615,13 +8627,13 @@
         <v>3</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="E295" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F295" s="1" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
@@ -8635,13 +8647,13 @@
         <v>3</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="E296" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F296" s="1" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
@@ -8655,13 +8667,13 @@
         <v>3</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F297" s="1" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
@@ -8675,13 +8687,13 @@
         <v>3</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="F298" s="1" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
@@ -8695,13 +8707,13 @@
         <v>3</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F299" s="1" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
@@ -8715,53 +8727,53 @@
         <v>3</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>646</v>
+        <v>631</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="F300" s="1" t="s">
-        <v>23</v>
+        <v>622</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A301" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="B301" s="1" t="s">
         <v>647</v>
       </c>
-      <c r="B301" s="1" t="s">
-        <v>648</v>
-      </c>
       <c r="C301" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>646</v>
+        <v>631</v>
       </c>
       <c r="E301" s="1" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="F301" s="1" t="s">
-        <v>23</v>
+        <v>622</v>
       </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A302" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="B302" s="1" t="s">
         <v>649</v>
       </c>
-      <c r="B302" s="1" t="s">
+      <c r="C302" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D302" s="1" t="s">
         <v>650</v>
       </c>
-      <c r="C302" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D302" s="1" t="s">
-        <v>646</v>
-      </c>
       <c r="E302" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F302" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.25">
@@ -8775,13 +8787,13 @@
         <v>3</v>
       </c>
       <c r="D303" s="1" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="E303" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F303" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.25">
@@ -8795,13 +8807,13 @@
         <v>3</v>
       </c>
       <c r="D304" s="1" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="E304" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F304" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.25">
@@ -8815,13 +8827,13 @@
         <v>3</v>
       </c>
       <c r="D305" s="1" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="E305" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F305" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.25">
@@ -8835,13 +8847,13 @@
         <v>3</v>
       </c>
       <c r="D306" s="1" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="E306" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F306" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.25">
@@ -8855,13 +8867,13 @@
         <v>3</v>
       </c>
       <c r="D307" s="1" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="E307" s="1" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="F307" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.25">
@@ -8875,13 +8887,13 @@
         <v>3</v>
       </c>
       <c r="D308" s="1" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="E308" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F308" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.25">
@@ -8895,13 +8907,13 @@
         <v>3</v>
       </c>
       <c r="D309" s="1" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="E309" s="1" t="s">
-        <v>144</v>
+        <v>55</v>
       </c>
       <c r="F309" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.25">
@@ -8915,53 +8927,53 @@
         <v>3</v>
       </c>
       <c r="D310" s="1" t="s">
-        <v>667</v>
+        <v>650</v>
       </c>
       <c r="E310" s="1" t="s">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="F310" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A311" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="B311" s="1" t="s">
         <v>668</v>
       </c>
-      <c r="B311" s="1" t="s">
-        <v>669</v>
-      </c>
       <c r="C311" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D311" s="1" t="s">
-        <v>667</v>
+        <v>650</v>
       </c>
       <c r="E311" s="1" t="s">
-        <v>8</v>
+        <v>146</v>
       </c>
       <c r="F311" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A312" s="1" t="s">
+        <v>669</v>
+      </c>
+      <c r="B312" s="1" t="s">
         <v>670</v>
       </c>
-      <c r="B312" s="1" t="s">
+      <c r="C312" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D312" s="1" t="s">
         <v>671</v>
       </c>
-      <c r="C312" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D312" s="1" t="s">
-        <v>667</v>
-      </c>
       <c r="E312" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F312" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.25">
@@ -8975,13 +8987,13 @@
         <v>3</v>
       </c>
       <c r="D313" s="1" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="E313" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F313" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.25">
@@ -8995,13 +9007,13 @@
         <v>3</v>
       </c>
       <c r="D314" s="1" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="E314" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F314" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.25">
@@ -9015,13 +9027,13 @@
         <v>3</v>
       </c>
       <c r="D315" s="1" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="E315" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F315" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.25">
@@ -9035,13 +9047,13 @@
         <v>3</v>
       </c>
       <c r="D316" s="1" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="E316" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F316" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.25">
@@ -9055,13 +9067,13 @@
         <v>3</v>
       </c>
       <c r="D317" s="1" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="E317" s="1" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="F317" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.25">
@@ -9075,13 +9087,13 @@
         <v>3</v>
       </c>
       <c r="D318" s="1" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="E318" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F318" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.25">
@@ -9095,53 +9107,53 @@
         <v>3</v>
       </c>
       <c r="D319" s="1" t="s">
-        <v>686</v>
+        <v>671</v>
       </c>
       <c r="E319" s="1" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="F319" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A320" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="B320" s="1" t="s">
         <v>687</v>
       </c>
-      <c r="B320" s="1" t="s">
-        <v>688</v>
-      </c>
       <c r="C320" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D320" s="1" t="s">
-        <v>686</v>
+        <v>671</v>
       </c>
       <c r="E320" s="1" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="F320" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A321" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="B321" s="1" t="s">
         <v>689</v>
       </c>
-      <c r="B321" s="1" t="s">
+      <c r="C321" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D321" s="1" t="s">
         <v>690</v>
       </c>
-      <c r="C321" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D321" s="1" t="s">
-        <v>686</v>
-      </c>
       <c r="E321" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F321" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.25">
@@ -9155,13 +9167,13 @@
         <v>3</v>
       </c>
       <c r="D322" s="1" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="E322" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F322" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.25">
@@ -9175,13 +9187,13 @@
         <v>3</v>
       </c>
       <c r="D323" s="1" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="E323" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F323" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.25">
@@ -9195,13 +9207,13 @@
         <v>3</v>
       </c>
       <c r="D324" s="1" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="E324" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F324" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.25">
@@ -9215,13 +9227,13 @@
         <v>3</v>
       </c>
       <c r="D325" s="1" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="E325" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F325" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.25">
@@ -9235,13 +9247,13 @@
         <v>3</v>
       </c>
       <c r="D326" s="1" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="E326" s="1" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="F326" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.25">
@@ -9255,53 +9267,53 @@
         <v>3</v>
       </c>
       <c r="D327" s="1" t="s">
-        <v>703</v>
+        <v>690</v>
       </c>
       <c r="E327" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F327" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A328" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="B328" s="1" t="s">
         <v>704</v>
       </c>
-      <c r="B328" s="1" t="s">
-        <v>705</v>
-      </c>
       <c r="C328" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D328" s="1" t="s">
-        <v>703</v>
+        <v>690</v>
       </c>
       <c r="E328" s="1" t="s">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="F328" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A329" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="B329" s="1" t="s">
         <v>706</v>
       </c>
-      <c r="B329" s="1" t="s">
+      <c r="C329" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D329" s="1" t="s">
         <v>707</v>
       </c>
-      <c r="C329" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D329" s="1" t="s">
-        <v>703</v>
-      </c>
       <c r="E329" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F329" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.25">
@@ -9315,13 +9327,13 @@
         <v>3</v>
       </c>
       <c r="D330" s="1" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="E330" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F330" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.25">
@@ -9335,10 +9347,10 @@
         <v>3</v>
       </c>
       <c r="D331" s="1" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="E331" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F331" s="1" t="s">
         <v>23</v>
@@ -9355,10 +9367,10 @@
         <v>3</v>
       </c>
       <c r="D332" s="1" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="E332" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F332" s="1" t="s">
         <v>23</v>
@@ -9375,13 +9387,13 @@
         <v>3</v>
       </c>
       <c r="D333" s="1" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="E333" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F333" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.25">
@@ -9395,13 +9407,13 @@
         <v>3</v>
       </c>
       <c r="D334" s="1" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="E334" s="1" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="F334" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.25">
@@ -9415,13 +9427,13 @@
         <v>3</v>
       </c>
       <c r="D335" s="1" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="E335" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F335" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.25">
@@ -9435,13 +9447,13 @@
         <v>3</v>
       </c>
       <c r="D336" s="1" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="E336" s="1" t="s">
-        <v>144</v>
+        <v>55</v>
       </c>
       <c r="F336" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.25">
@@ -9455,10 +9467,10 @@
         <v>3</v>
       </c>
       <c r="D337" s="1" t="s">
-        <v>724</v>
+        <v>707</v>
       </c>
       <c r="E337" s="1" t="s">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="F337" s="1" t="s">
         <v>28</v>
@@ -9466,42 +9478,42 @@
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A338" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="B338" s="1" t="s">
         <v>725</v>
       </c>
-      <c r="B338" s="1" t="s">
-        <v>726</v>
-      </c>
       <c r="C338" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D338" s="1" t="s">
-        <v>724</v>
+        <v>707</v>
       </c>
       <c r="E338" s="1" t="s">
-        <v>8</v>
+        <v>146</v>
       </c>
       <c r="F338" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A339" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="B339" s="1" t="s">
         <v>727</v>
       </c>
-      <c r="B339" s="1" t="s">
+      <c r="C339" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D339" s="1" t="s">
         <v>728</v>
       </c>
-      <c r="C339" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D339" s="1" t="s">
-        <v>724</v>
-      </c>
       <c r="E339" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F339" s="1" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.25">
@@ -9515,13 +9527,13 @@
         <v>3</v>
       </c>
       <c r="D340" s="1" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="E340" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F340" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.25">
@@ -9535,13 +9547,13 @@
         <v>3</v>
       </c>
       <c r="D341" s="1" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="E341" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F341" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.25">
@@ -9555,10 +9567,10 @@
         <v>3</v>
       </c>
       <c r="D342" s="1" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="E342" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F342" s="1" t="s">
         <v>23</v>
@@ -9575,13 +9587,13 @@
         <v>3</v>
       </c>
       <c r="D343" s="1" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="E343" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F343" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.25">
@@ -9595,93 +9607,93 @@
         <v>3</v>
       </c>
       <c r="D344" s="1" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="E344" s="1" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="F344" s="1" t="s">
-        <v>739</v>
+        <v>28</v>
       </c>
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A345" s="1" t="s">
+        <v>739</v>
+      </c>
+      <c r="B345" s="1" t="s">
         <v>740</v>
       </c>
-      <c r="B345" s="1" t="s">
-        <v>741</v>
-      </c>
       <c r="C345" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D345" s="1" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="E345" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F345" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A346" s="1" t="s">
+        <v>741</v>
+      </c>
+      <c r="B346" s="1" t="s">
         <v>742</v>
       </c>
-      <c r="B346" s="1" t="s">
+      <c r="C346" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D346" s="1" t="s">
+        <v>728</v>
+      </c>
+      <c r="E346" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F346" s="1" t="s">
         <v>743</v>
-      </c>
-      <c r="C346" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D346" s="1" t="s">
-        <v>744</v>
-      </c>
-      <c r="E346" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F346" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A347" s="1" t="s">
+        <v>744</v>
+      </c>
+      <c r="B347" s="1" t="s">
         <v>745</v>
       </c>
-      <c r="B347" s="1" t="s">
-        <v>746</v>
-      </c>
       <c r="C347" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D347" s="1" t="s">
-        <v>744</v>
+        <v>728</v>
       </c>
       <c r="E347" s="1" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="F347" s="1" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A348" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="B348" s="1" t="s">
         <v>747</v>
       </c>
-      <c r="B348" s="1" t="s">
+      <c r="C348" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D348" s="1" t="s">
         <v>748</v>
       </c>
-      <c r="C348" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D348" s="1" t="s">
-        <v>744</v>
-      </c>
       <c r="E348" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F348" s="1" t="s">
-        <v>166</v>
+        <v>28</v>
       </c>
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.25">
@@ -9695,133 +9707,173 @@
         <v>3</v>
       </c>
       <c r="D349" s="1" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="E349" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F349" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A350" s="1" t="s">
+        <v>751</v>
+      </c>
+      <c r="B350" s="1" t="s">
         <v>752</v>
       </c>
-      <c r="B350" s="1" t="s">
-        <v>753</v>
-      </c>
       <c r="C350" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D350" s="1" t="s">
-        <v>754</v>
+        <v>748</v>
       </c>
       <c r="E350" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F350" s="1" t="s">
-        <v>28</v>
+        <v>168</v>
       </c>
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A351" s="1" t="s">
+        <v>753</v>
+      </c>
+      <c r="B351" s="1" t="s">
+        <v>754</v>
+      </c>
+      <c r="C351" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D351" s="1" t="s">
         <v>755</v>
-      </c>
-      <c r="B351" s="1" t="s">
-        <v>756</v>
-      </c>
-      <c r="C351" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D351" s="1" t="s">
-        <v>757</v>
       </c>
       <c r="E351" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F351" s="1" t="s">
-        <v>758</v>
+        <v>28</v>
       </c>
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A352" s="1" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="B352" s="1" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="C352" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D352" s="1" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="E352" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F352" s="1" t="s">
-        <v>761</v>
+        <v>33</v>
       </c>
     </row>
     <row r="353" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A353" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="B353" s="1" t="s">
+        <v>760</v>
+      </c>
+      <c r="C353" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D353" s="1" t="s">
+        <v>761</v>
+      </c>
+      <c r="E353" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F353" s="1" t="s">
         <v>762</v>
-      </c>
-      <c r="B353" s="1" t="s">
-        <v>763</v>
-      </c>
-      <c r="C353" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D353" s="1" t="s">
-        <v>757</v>
-      </c>
-      <c r="E353" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F353" s="1" t="s">
-        <v>764</v>
       </c>
     </row>
     <row r="354" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A354" s="1" t="s">
+        <v>763</v>
+      </c>
+      <c r="B354" s="1" t="s">
+        <v>764</v>
+      </c>
+      <c r="C354" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D354" s="1" t="s">
+        <v>761</v>
+      </c>
+      <c r="E354" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F354" s="1" t="s">
         <v>765</v>
-      </c>
-      <c r="B354" s="1" t="s">
-        <v>766</v>
-      </c>
-      <c r="C354" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D354" s="1" t="s">
-        <v>757</v>
-      </c>
-      <c r="E354" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F354" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="355" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A355" s="1" t="s">
+        <v>766</v>
+      </c>
+      <c r="B355" s="1" t="s">
         <v>767</v>
       </c>
-      <c r="B355" s="1" t="s">
+      <c r="C355" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D355" s="1" t="s">
+        <v>761</v>
+      </c>
+      <c r="E355" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F355" s="1" t="s">
         <v>768</v>
       </c>
-      <c r="C355" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D355" s="1" t="s">
+    </row>
+    <row r="356" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A356" s="1" t="s">
         <v>769</v>
       </c>
-      <c r="E355" s="1" t="s">
+      <c r="B356" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="C356" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D356" s="1" t="s">
+        <v>761</v>
+      </c>
+      <c r="E356" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F356" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="357" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A357" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="B357" s="1" t="s">
+        <v>772</v>
+      </c>
+      <c r="C357" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D357" s="1" t="s">
+        <v>773</v>
+      </c>
+      <c r="E357" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F355" s="1" t="s">
-        <v>23</v>
+      <c r="F357" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/CLB07N.xlsx
+++ b/CLB07N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2142" uniqueCount="774">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2148" uniqueCount="776">
   <si>
     <t/>
   </si>
@@ -214,6 +214,18 @@
     <t>BINTANG ZERO KLG 330</t>
   </si>
   <si>
+    <t>20133709</t>
+  </si>
+  <si>
+    <t>POLARIS SARSAPRLA330</t>
+  </si>
+  <si>
+    <t>20002209</t>
+  </si>
+  <si>
+    <t>TEBS SPRK MIX FRT330</t>
+  </si>
+  <si>
     <t>10037437</t>
   </si>
   <si>
@@ -325,18 +337,6 @@
     <t>MINUTE M. NB ORG 300</t>
   </si>
   <si>
-    <t>20133709</t>
-  </si>
-  <si>
-    <t>POLARIS SARSAPRLA330</t>
-  </si>
-  <si>
-    <t>20002209</t>
-  </si>
-  <si>
-    <t>TEBS SPRK MIX FRT330</t>
-  </si>
-  <si>
     <t>20120499</t>
   </si>
   <si>
@@ -907,7 +907,7 @@
     <t>20044334</t>
   </si>
   <si>
-    <t>SOSRO TEH BTL TPK300</t>
+    <t>SOSRO TEH KTK 300 ML</t>
   </si>
   <si>
     <t>10005128</t>
@@ -1345,6 +1345,12 @@
     <t>DIAMOND JC CRANBR200</t>
   </si>
   <si>
+    <t>20143652</t>
+  </si>
+  <si>
+    <t>DMND UNSWT BLBERY200</t>
+  </si>
+  <si>
     <t>20065041</t>
   </si>
   <si>
@@ -1540,7 +1546,7 @@
     <t>20038777</t>
   </si>
   <si>
-    <t>POCARI SWEAT 900ML</t>
+    <t>POCARI SWEAT 900 ML</t>
   </si>
   <si>
     <t>20019674</t>
@@ -1681,459 +1687,459 @@
     <t>TJH KURMA SUSU KR189</t>
   </si>
   <si>
+    <t>20136193</t>
+  </si>
+  <si>
+    <t>SO GOOD SUSU STRL189</t>
+  </si>
+  <si>
+    <t>20133805</t>
+  </si>
+  <si>
+    <t>ENTRSL OLIVE STRL180</t>
+  </si>
+  <si>
+    <t>20134968</t>
+  </si>
+  <si>
+    <t>COLLAGENA SRL 189 ML</t>
+  </si>
+  <si>
+    <t>20140174</t>
+  </si>
+  <si>
+    <t>BEAR BRAND CLGEN 189</t>
+  </si>
+  <si>
+    <t>10004906</t>
+  </si>
+  <si>
+    <t>BEAR BRAND STERIL189</t>
+  </si>
+  <si>
+    <t>20136952</t>
+  </si>
+  <si>
+    <t>V-SOY SOYA BEAN 300</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>20048096</t>
+  </si>
+  <si>
+    <t>20038726</t>
+  </si>
+  <si>
+    <t>NARAYA KDLAI BTL320</t>
+  </si>
+  <si>
+    <t>20107748</t>
+  </si>
+  <si>
+    <t>MILKU SUSU CKLT 200</t>
+  </si>
+  <si>
+    <t>20107749</t>
+  </si>
+  <si>
+    <t>MILKU SUSU STRO 200</t>
+  </si>
+  <si>
+    <t>20141102</t>
+  </si>
+  <si>
+    <t>MILKU UHT MARIE 200</t>
+  </si>
+  <si>
+    <t>20134047</t>
+  </si>
+  <si>
+    <t>MILKU SUSU ORGNAL200</t>
+  </si>
+  <si>
+    <t>10003373</t>
+  </si>
+  <si>
+    <t>INDOMILK CAIR CHO190</t>
+  </si>
+  <si>
+    <t>10003426</t>
+  </si>
+  <si>
+    <t>INDOMILK CAIR STW190</t>
+  </si>
+  <si>
+    <t>10004443</t>
+  </si>
+  <si>
+    <t>INDOMILK UHT CKL 180</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>10004442</t>
+  </si>
+  <si>
+    <t>INDOMLK UHT STRW 180</t>
+  </si>
+  <si>
+    <t>20070569</t>
+  </si>
+  <si>
+    <t>INDOMLK BANANA 180</t>
+  </si>
+  <si>
+    <t>20127735</t>
+  </si>
+  <si>
+    <t>INDMLK DLGNA COFF180</t>
+  </si>
+  <si>
+    <t>20125062</t>
+  </si>
+  <si>
+    <t>INDOMLK KR.BNANA 180</t>
+  </si>
+  <si>
+    <t>20132659</t>
+  </si>
+  <si>
+    <t>INDOMLK HK LYCHEE180</t>
+  </si>
+  <si>
+    <t>20091807</t>
+  </si>
+  <si>
+    <t>DIAMOND UHT CKLT 200</t>
+  </si>
+  <si>
+    <t>20136644</t>
+  </si>
+  <si>
+    <t>DIAMOND UHT MARSM200</t>
+  </si>
+  <si>
+    <t>20137977</t>
+  </si>
+  <si>
+    <t>DIAMOND UHT BBLGM200</t>
+  </si>
+  <si>
+    <t>20090314</t>
+  </si>
+  <si>
+    <t>DIAMOND UHT F/C200ML</t>
+  </si>
+  <si>
+    <t>20032643</t>
+  </si>
+  <si>
+    <t>ULTRA LOW FAT COK250</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>20032644</t>
+  </si>
+  <si>
+    <t>ULTRA LOW FAT PLN250</t>
+  </si>
+  <si>
+    <t>20130186</t>
+  </si>
+  <si>
+    <t>GRNFLD UHT CHOCO 250</t>
+  </si>
+  <si>
+    <t>20118209</t>
+  </si>
+  <si>
+    <t>GRNFLD UHT STRAW 250</t>
+  </si>
+  <si>
+    <t>20087413</t>
+  </si>
+  <si>
+    <t>GRNFLD UHT F.CRM 250</t>
+  </si>
+  <si>
+    <t>20138916</t>
+  </si>
+  <si>
+    <t>CIMORY THAI TEA 250</t>
+  </si>
+  <si>
+    <t>20136951</t>
+  </si>
+  <si>
+    <t>CMORY UHT MATCHA 250</t>
+  </si>
+  <si>
+    <t>RT,(E-0.5B)</t>
+  </si>
+  <si>
+    <t>20140795</t>
+  </si>
+  <si>
+    <t>CIMORY UHT CHOCO 225</t>
+  </si>
+  <si>
+    <t>20140794</t>
+  </si>
+  <si>
+    <t>CIMORY UHT MARIE 225</t>
+  </si>
+  <si>
+    <t>20140793</t>
+  </si>
+  <si>
+    <t>CIMORY UHT MTCHA 225</t>
+  </si>
+  <si>
+    <t>20122822</t>
+  </si>
+  <si>
+    <t>CMORY UHT MARIE 250</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>20115187</t>
+  </si>
+  <si>
+    <t>CMORY UHT HZLNUT 250</t>
+  </si>
+  <si>
+    <t>20115188</t>
+  </si>
+  <si>
+    <t>CMORY UHT ALMND 250</t>
+  </si>
+  <si>
+    <t>20104637</t>
+  </si>
+  <si>
+    <t>CIMORY UHT CSHEW 250</t>
+  </si>
+  <si>
+    <t>20099571</t>
+  </si>
+  <si>
+    <t>CIMORY UHT CHOCO 250</t>
+  </si>
+  <si>
+    <t>20104636</t>
+  </si>
+  <si>
+    <t>CIMORY UHT CHOML 250</t>
+  </si>
+  <si>
+    <t>20129109</t>
+  </si>
+  <si>
+    <t>CIMORY CHO.TRMSU 250</t>
+  </si>
+  <si>
+    <t>20099572</t>
+  </si>
+  <si>
+    <t>CIMORY UHT STRAW 250</t>
+  </si>
+  <si>
+    <t>20134390</t>
+  </si>
+  <si>
+    <t>CIMORY BBS LKTSA 250</t>
+  </si>
+  <si>
+    <t>20025753</t>
+  </si>
+  <si>
+    <t>F/F L/FAT COK TPK225</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>20088875</t>
+  </si>
+  <si>
+    <t>FF SWT.DLGHT TPK 225</t>
+  </si>
+  <si>
+    <t>20070253</t>
+  </si>
+  <si>
+    <t>FF COCONUT TPK 225ML</t>
+  </si>
+  <si>
+    <t>20034079</t>
+  </si>
+  <si>
+    <t>F/FLAG COKLT TPK 225</t>
+  </si>
+  <si>
+    <t>20034078</t>
+  </si>
+  <si>
+    <t>F/FLAG STRWB TPK 225</t>
+  </si>
+  <si>
+    <t>20034077</t>
+  </si>
+  <si>
+    <t>F/F FULL CRM TPK 225</t>
+  </si>
+  <si>
+    <t>20128754</t>
+  </si>
+  <si>
+    <t>FF SS.SEREAL CKL 225</t>
+  </si>
+  <si>
+    <t>20136769</t>
+  </si>
+  <si>
+    <t>F.FLAG UHT BERIS 225</t>
+  </si>
+  <si>
+    <t>20136768</t>
+  </si>
+  <si>
+    <t>F.FLAG UHT MATCH 225</t>
+  </si>
+  <si>
+    <t>20142233</t>
+  </si>
+  <si>
+    <t>INDOMILK JAPANE M180</t>
+  </si>
+  <si>
+    <t>20037974</t>
+  </si>
+  <si>
+    <t>ULTRA UHT MOKA 250</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>10004669</t>
+  </si>
+  <si>
+    <t>ULTRA UHT CHOCO 250M</t>
+  </si>
+  <si>
+    <t>10004668</t>
+  </si>
+  <si>
+    <t>ULTRA UHT STRAW 250M</t>
+  </si>
+  <si>
+    <t>10004676</t>
+  </si>
+  <si>
+    <t>ULTRA PLAIN SLIM250M</t>
+  </si>
+  <si>
+    <t>10007380</t>
+  </si>
+  <si>
+    <t>ULTRA SLIM COKLAT200</t>
+  </si>
+  <si>
+    <t>10008095</t>
+  </si>
+  <si>
+    <t>ULTRA SLIM STRAW 200</t>
+  </si>
+  <si>
+    <t>10007379</t>
+  </si>
+  <si>
+    <t>ULTRA SLIM PLAIN 200</t>
+  </si>
+  <si>
+    <t>20090189</t>
+  </si>
+  <si>
+    <t>ULTRA SUSU KRML 200</t>
+  </si>
+  <si>
+    <t>20088964</t>
+  </si>
+  <si>
+    <t>ULTRA SUSU TARO 200</t>
+  </si>
+  <si>
+    <t>20110968</t>
+  </si>
+  <si>
+    <t>MUJIGAE BNNA MLK 250</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>20110967</t>
+  </si>
+  <si>
+    <t>MUJIGAE CHOC BAN 250</t>
+  </si>
+  <si>
+    <t>20126897</t>
+  </si>
+  <si>
+    <t>MUJIGAE STRW BAN 250</t>
+  </si>
+  <si>
+    <t>20138050</t>
+  </si>
+  <si>
+    <t>MUJIGAE WTRMLN 250</t>
+  </si>
+  <si>
+    <t>20130518</t>
+  </si>
+  <si>
+    <t>TS ALMND.CHOCO 190ML</t>
+  </si>
+  <si>
+    <t>20118377</t>
+  </si>
+  <si>
+    <t>TS OAT VANILLA 190ML</t>
+  </si>
+  <si>
+    <t>20139295</t>
+  </si>
+  <si>
+    <t>BROOKFARM ORI 200ML</t>
+  </si>
+  <si>
+    <t>20139300</t>
+  </si>
+  <si>
+    <t>BROOKFARM MATCHA 200</t>
+  </si>
+  <si>
+    <t>20138895</t>
+  </si>
+  <si>
+    <t>ULTRA UHT BLUBRY 200</t>
+  </si>
+  <si>
     <t>20124409</t>
   </si>
   <si>
     <t>INDOMLK STRL HNY 189</t>
   </si>
   <si>
-    <t>20136193</t>
-  </si>
-  <si>
-    <t>SO GOOD SUSU STRL189</t>
-  </si>
-  <si>
-    <t>20133805</t>
-  </si>
-  <si>
-    <t>ENTRSL OLIVE STRL180</t>
-  </si>
-  <si>
-    <t>20134968</t>
-  </si>
-  <si>
-    <t>COLLAGENA STERIL189</t>
-  </si>
-  <si>
-    <t>20140174</t>
-  </si>
-  <si>
-    <t>BEAR BRAND CLGEN 189</t>
-  </si>
-  <si>
-    <t>10004906</t>
-  </si>
-  <si>
-    <t>BEAR BRAND STERIL189</t>
-  </si>
-  <si>
-    <t>20136952</t>
-  </si>
-  <si>
-    <t>V-SOY SOYA BEAN 300</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>20048096</t>
-  </si>
-  <si>
-    <t>20038726</t>
-  </si>
-  <si>
-    <t>NARAYA KDLAI BTL320</t>
-  </si>
-  <si>
-    <t>20107748</t>
-  </si>
-  <si>
-    <t>MILKU SUSU CKLT 200</t>
-  </si>
-  <si>
-    <t>20107749</t>
-  </si>
-  <si>
-    <t>MILKU SUSU STRO 200</t>
-  </si>
-  <si>
-    <t>20141102</t>
-  </si>
-  <si>
-    <t>MILKU UHT MARIE 200</t>
-  </si>
-  <si>
-    <t>20134047</t>
-  </si>
-  <si>
-    <t>MILKU SUSU ORGNAL200</t>
-  </si>
-  <si>
-    <t>10003373</t>
-  </si>
-  <si>
-    <t>INDOMILK CAIR CHO190</t>
-  </si>
-  <si>
-    <t>10003426</t>
-  </si>
-  <si>
-    <t>INDOMILK CAIR STW190</t>
-  </si>
-  <si>
-    <t>10004443</t>
-  </si>
-  <si>
-    <t>INDOMILK UHT CKL 180</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>10004442</t>
-  </si>
-  <si>
-    <t>INDOMLK UHT STRW 180</t>
-  </si>
-  <si>
-    <t>20070569</t>
-  </si>
-  <si>
-    <t>INDOMLK BANANA 180</t>
-  </si>
-  <si>
-    <t>20127735</t>
-  </si>
-  <si>
-    <t>INDMLK DLGNA COFF180</t>
-  </si>
-  <si>
-    <t>20125062</t>
-  </si>
-  <si>
-    <t>INDOMLK KR.BNANA 180</t>
-  </si>
-  <si>
-    <t>20132659</t>
-  </si>
-  <si>
-    <t>INDOMLK HK LYCHEE180</t>
-  </si>
-  <si>
-    <t>20091807</t>
-  </si>
-  <si>
-    <t>DIAMOND UHT CKLT 200</t>
-  </si>
-  <si>
-    <t>20136644</t>
-  </si>
-  <si>
-    <t>DIAMOND UHT MARSM200</t>
-  </si>
-  <si>
-    <t>20137977</t>
-  </si>
-  <si>
-    <t>DIAMOND UHT BBLGM200</t>
-  </si>
-  <si>
-    <t>20090314</t>
-  </si>
-  <si>
-    <t>DIAMOND UHT F/C200ML</t>
-  </si>
-  <si>
-    <t>20032643</t>
-  </si>
-  <si>
-    <t>ULTRA LOW FAT COK250</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>20032644</t>
-  </si>
-  <si>
-    <t>ULTRA LOW FAT PLN250</t>
-  </si>
-  <si>
-    <t>20130186</t>
-  </si>
-  <si>
-    <t>GRNFLD UHT CHOCO 250</t>
-  </si>
-  <si>
-    <t>20118209</t>
-  </si>
-  <si>
-    <t>GRNFLD UHT STRAW 250</t>
-  </si>
-  <si>
-    <t>20087413</t>
-  </si>
-  <si>
-    <t>GRNFLD UHT F.CRM 250</t>
-  </si>
-  <si>
-    <t>20138916</t>
-  </si>
-  <si>
-    <t>CIMORY THAI TEA 250</t>
-  </si>
-  <si>
-    <t>20136951</t>
-  </si>
-  <si>
-    <t>CMORY UHT MATCHA 250</t>
-  </si>
-  <si>
-    <t>RT,(E-0.5B)</t>
-  </si>
-  <si>
-    <t>20140795</t>
-  </si>
-  <si>
-    <t>CIMORY UHT CHOCO 225</t>
-  </si>
-  <si>
-    <t>20140794</t>
-  </si>
-  <si>
-    <t>CIMORY UHT MARIE 225</t>
-  </si>
-  <si>
-    <t>20140793</t>
-  </si>
-  <si>
-    <t>CIMORY UHT MTCHA 225</t>
-  </si>
-  <si>
-    <t>20122822</t>
-  </si>
-  <si>
-    <t>CMORY UHT MARIE 250</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>20115187</t>
-  </si>
-  <si>
-    <t>CMORY UHT HZLNUT 250</t>
-  </si>
-  <si>
-    <t>20115188</t>
-  </si>
-  <si>
-    <t>CMORY UHT ALMND 250</t>
-  </si>
-  <si>
-    <t>20104637</t>
-  </si>
-  <si>
-    <t>CIMORY UHT CSHEW 250</t>
-  </si>
-  <si>
-    <t>20099571</t>
-  </si>
-  <si>
-    <t>CIMORY UHT CHOCO 250</t>
-  </si>
-  <si>
-    <t>20104636</t>
-  </si>
-  <si>
-    <t>CIMORY UHT CHOML 250</t>
-  </si>
-  <si>
-    <t>20129109</t>
-  </si>
-  <si>
-    <t>CIMORY CHO.TRMSU 250</t>
-  </si>
-  <si>
-    <t>20099572</t>
-  </si>
-  <si>
-    <t>CIMORY UHT STRAW 250</t>
-  </si>
-  <si>
-    <t>20134390</t>
-  </si>
-  <si>
-    <t>CIMORY BBS LKTSA 250</t>
-  </si>
-  <si>
-    <t>20025753</t>
-  </si>
-  <si>
-    <t>F/F L/FAT COK TPK225</t>
-  </si>
-  <si>
-    <t>38</t>
-  </si>
-  <si>
-    <t>20088875</t>
-  </si>
-  <si>
-    <t>FF SWT.DLGHT TPK 225</t>
-  </si>
-  <si>
-    <t>20070253</t>
-  </si>
-  <si>
-    <t>FF COCONUT TPK 225ML</t>
-  </si>
-  <si>
-    <t>20034079</t>
-  </si>
-  <si>
-    <t>F/FLAG COKLT TPK 225</t>
-  </si>
-  <si>
-    <t>20034078</t>
-  </si>
-  <si>
-    <t>F/FLAG STRWB TPK 225</t>
-  </si>
-  <si>
-    <t>20034077</t>
-  </si>
-  <si>
-    <t>F/F FULL CRM TPK 225</t>
-  </si>
-  <si>
-    <t>20128754</t>
-  </si>
-  <si>
-    <t>FF SS.SEREAL CKL 225</t>
-  </si>
-  <si>
-    <t>20136769</t>
-  </si>
-  <si>
-    <t>F.FLAG UHT BERIS 225</t>
-  </si>
-  <si>
-    <t>20136768</t>
-  </si>
-  <si>
-    <t>F.FLAG UHT MATCH 225</t>
-  </si>
-  <si>
-    <t>20142233</t>
-  </si>
-  <si>
-    <t>INDOMILK JAPANE M180</t>
-  </si>
-  <si>
-    <t>10004669</t>
-  </si>
-  <si>
-    <t>ULTRA UHT CHOCO 250M</t>
-  </si>
-  <si>
-    <t>39</t>
-  </si>
-  <si>
-    <t>10004668</t>
-  </si>
-  <si>
-    <t>ULTRA UHT STRAW 250M</t>
-  </si>
-  <si>
-    <t>10004676</t>
-  </si>
-  <si>
-    <t>ULTRA PLAIN SLIM250M</t>
-  </si>
-  <si>
-    <t>10007380</t>
-  </si>
-  <si>
-    <t>ULTRA SLIM COKLAT200</t>
-  </si>
-  <si>
-    <t>10008095</t>
-  </si>
-  <si>
-    <t>ULTRA SLIM STRAW 200</t>
-  </si>
-  <si>
-    <t>10007379</t>
-  </si>
-  <si>
-    <t>ULTRA SLIM PLAIN 200</t>
-  </si>
-  <si>
-    <t>20090189</t>
-  </si>
-  <si>
-    <t>ULTRA SUSU KRML 200</t>
-  </si>
-  <si>
-    <t>20088964</t>
-  </si>
-  <si>
-    <t>ULTRA SUSU TARO 200</t>
-  </si>
-  <si>
-    <t>20138895</t>
-  </si>
-  <si>
-    <t>ULTRA UHT BLUBRY 200</t>
-  </si>
-  <si>
-    <t>20110968</t>
-  </si>
-  <si>
-    <t>MUJIGAE BNNA MLK 250</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>20110967</t>
-  </si>
-  <si>
-    <t>MUJIGAE CHOC BAN 250</t>
-  </si>
-  <si>
-    <t>20126897</t>
-  </si>
-  <si>
-    <t>MUJIGAE STRW BAN 250</t>
-  </si>
-  <si>
-    <t>20138050</t>
-  </si>
-  <si>
-    <t>MUJIGAE WTRMLN 250</t>
-  </si>
-  <si>
-    <t>20130518</t>
-  </si>
-  <si>
-    <t>TS ALMND.CHOCO 190ML</t>
-  </si>
-  <si>
-    <t>20118377</t>
-  </si>
-  <si>
-    <t>TS OAT VANILLA 190ML</t>
-  </si>
-  <si>
-    <t>20139295</t>
-  </si>
-  <si>
-    <t>BROOKFARM ORI 200ML</t>
-  </si>
-  <si>
-    <t>20139300</t>
-  </si>
-  <si>
-    <t>BROOKFARM MATCHA 200</t>
-  </si>
-  <si>
-    <t>20037974</t>
-  </si>
-  <si>
-    <t>ULTRA UHT MOKA 250</t>
-  </si>
-  <si>
     <t>41</t>
   </si>
   <si>
@@ -2275,7 +2281,7 @@
     <t>20069208</t>
   </si>
   <si>
-    <t>LE MINERALE 600ML</t>
+    <t>LE MINERALE 600 ML</t>
   </si>
   <si>
     <t>44</t>
@@ -2284,7 +2290,7 @@
     <t>10003814</t>
   </si>
   <si>
-    <t>AQUA AIR MINERAL 600</t>
+    <t>AQUA AIR MIN 600 ML</t>
   </si>
   <si>
     <t>45</t>
@@ -2332,7 +2338,7 @@
     <t>CAFFINO OATMARIE 200</t>
   </si>
   <si>
-    <t>998</t>
+    <t>999</t>
   </si>
 </sst>
 </file>
@@ -2725,7 +2731,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F357"/>
+  <dimension ref="A1:F358"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -3210,7 +3216,7 @@
         <v>14</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>5</v>
@@ -3230,7 +3236,7 @@
         <v>14</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>28</v>
@@ -3250,7 +3256,7 @@
         <v>14</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>28</v>
@@ -3270,7 +3276,7 @@
         <v>14</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>28</v>
@@ -3287,10 +3293,10 @@
         <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E28" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>33</v>
@@ -3307,13 +3313,13 @@
         <v>3</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -3330,7 +3336,7 @@
         <v>17</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>33</v>
@@ -3350,7 +3356,7 @@
         <v>17</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>33</v>
@@ -3370,18 +3376,18 @@
         <v>17</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>77</v>
+        <v>33</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>78</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>79</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
@@ -3390,18 +3396,18 @@
         <v>17</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>77</v>
+        <v>33</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>80</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>81</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>3</v>
@@ -3410,10 +3416,10 @@
         <v>17</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -3430,10 +3436,10 @@
         <v>17</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -3447,13 +3453,13 @@
         <v>3</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>28</v>
+        <v>81</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -3467,13 +3473,13 @@
         <v>3</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>33</v>
+        <v>81</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -3490,7 +3496,7 @@
         <v>20</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>28</v>
@@ -3510,10 +3516,10 @@
         <v>20</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -3530,7 +3536,7 @@
         <v>20</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>28</v>
@@ -3550,10 +3556,10 @@
         <v>20</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>77</v>
+        <v>28</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -3570,10 +3576,10 @@
         <v>20</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>77</v>
+        <v>28</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -3590,10 +3596,10 @@
         <v>20</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -3607,13 +3613,13 @@
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E44" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E44" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F44" s="1" t="s">
-        <v>5</v>
+        <v>81</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -3627,13 +3633,13 @@
         <v>3</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>5</v>
+        <v>81</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -3650,10 +3656,10 @@
         <v>38</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>33</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -3670,10 +3676,10 @@
         <v>38</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -3690,7 +3696,7 @@
         <v>38</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>23</v>
@@ -3710,7 +3716,7 @@
         <v>38</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>23</v>
@@ -3730,7 +3736,7 @@
         <v>38</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>28</v>
@@ -3750,7 +3756,7 @@
         <v>38</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>33</v>
@@ -3770,7 +3776,7 @@
         <v>38</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>23</v>
@@ -3833,7 +3839,7 @@
         <v>14</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -3853,7 +3859,7 @@
         <v>17</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -4633,7 +4639,7 @@
         <v>11</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -6553,7 +6559,7 @@
         <v>14</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
@@ -6847,10 +6853,10 @@
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>446</v>
+        <v>427</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>4</v>
+        <v>146</v>
       </c>
       <c r="F206" s="1" t="s">
         <v>28</v>
@@ -6858,19 +6864,19 @@
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="B207" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="B207" s="1" t="s">
+      <c r="C207" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D207" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="C207" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D207" s="1" t="s">
-        <v>446</v>
-      </c>
       <c r="E207" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F207" s="1" t="s">
         <v>28</v>
@@ -6887,10 +6893,10 @@
         <v>3</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F208" s="1" t="s">
         <v>28</v>
@@ -6907,10 +6913,10 @@
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F209" s="1" t="s">
         <v>28</v>
@@ -6927,10 +6933,10 @@
         <v>3</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F210" s="1" t="s">
         <v>28</v>
@@ -6947,10 +6953,10 @@
         <v>3</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F211" s="1" t="s">
         <v>28</v>
@@ -6967,10 +6973,10 @@
         <v>3</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F212" s="1" t="s">
         <v>28</v>
@@ -6987,10 +6993,10 @@
         <v>3</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F213" s="1" t="s">
         <v>28</v>
@@ -7007,10 +7013,10 @@
         <v>3</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F214" s="1" t="s">
         <v>28</v>
@@ -7027,10 +7033,10 @@
         <v>3</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>465</v>
+        <v>448</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="F215" s="1" t="s">
         <v>28</v>
@@ -7038,19 +7044,19 @@
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="B216" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="B216" s="1" t="s">
+      <c r="C216" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D216" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="C216" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D216" s="1" t="s">
-        <v>465</v>
-      </c>
       <c r="E216" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F216" s="1" t="s">
         <v>28</v>
@@ -7067,10 +7073,10 @@
         <v>3</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F217" s="1" t="s">
         <v>28</v>
@@ -7087,10 +7093,10 @@
         <v>3</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F218" s="1" t="s">
         <v>28</v>
@@ -7107,10 +7113,10 @@
         <v>3</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F219" s="1" t="s">
         <v>28</v>
@@ -7127,10 +7133,10 @@
         <v>3</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F220" s="1" t="s">
         <v>28</v>
@@ -7147,10 +7153,10 @@
         <v>3</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F221" s="1" t="s">
         <v>28</v>
@@ -7167,13 +7173,13 @@
         <v>3</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F222" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
@@ -7187,13 +7193,13 @@
         <v>3</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F223" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
@@ -7207,10 +7213,10 @@
         <v>3</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>484</v>
+        <v>467</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="F224" s="1" t="s">
         <v>28</v>
@@ -7218,19 +7224,19 @@
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="B225" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="B225" s="1" t="s">
+      <c r="C225" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D225" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="C225" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D225" s="1" t="s">
-        <v>484</v>
-      </c>
       <c r="E225" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F225" s="1" t="s">
         <v>28</v>
@@ -7247,10 +7253,10 @@
         <v>3</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F226" s="1" t="s">
         <v>28</v>
@@ -7267,10 +7273,10 @@
         <v>3</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F227" s="1" t="s">
         <v>28</v>
@@ -7287,13 +7293,13 @@
         <v>3</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F228" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
@@ -7307,10 +7313,10 @@
         <v>3</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F229" s="1" t="s">
         <v>23</v>
@@ -7327,13 +7333,13 @@
         <v>3</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F230" s="1" t="s">
-        <v>168</v>
+        <v>23</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
@@ -7347,10 +7353,10 @@
         <v>3</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F231" s="1" t="s">
         <v>168</v>
@@ -7367,30 +7373,30 @@
         <v>3</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>501</v>
+        <v>486</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="F232" s="1" t="s">
-        <v>23</v>
+        <v>168</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="B233" s="1" t="s">
         <v>502</v>
       </c>
-      <c r="B233" s="1" t="s">
+      <c r="C233" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D233" s="1" t="s">
         <v>503</v>
       </c>
-      <c r="C233" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D233" s="1" t="s">
-        <v>501</v>
-      </c>
       <c r="E233" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F233" s="1" t="s">
         <v>23</v>
@@ -7407,10 +7413,10 @@
         <v>3</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F234" s="1" t="s">
         <v>23</v>
@@ -7427,10 +7433,10 @@
         <v>3</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F235" s="1" t="s">
         <v>23</v>
@@ -7447,10 +7453,10 @@
         <v>3</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F236" s="1" t="s">
         <v>23</v>
@@ -7467,13 +7473,13 @@
         <v>3</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="E237" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F237" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
@@ -7487,10 +7493,10 @@
         <v>3</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="E238" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F238" s="1" t="s">
         <v>28</v>
@@ -7507,30 +7513,30 @@
         <v>3</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="E239" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F239" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="B240" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="B240" s="1" t="s">
+      <c r="C240" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D240" s="1" t="s">
         <v>518</v>
       </c>
-      <c r="C240" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D240" s="1" t="s">
-        <v>516</v>
-      </c>
       <c r="E240" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F240" s="1" t="s">
         <v>23</v>
@@ -7547,10 +7553,10 @@
         <v>3</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="E241" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F241" s="1" t="s">
         <v>23</v>
@@ -7567,13 +7573,13 @@
         <v>3</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="E242" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F242" s="1" t="s">
-        <v>168</v>
+        <v>23</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
@@ -7587,33 +7593,33 @@
         <v>3</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="E243" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F243" s="1" t="s">
-        <v>525</v>
+        <v>168</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="B244" s="1" t="s">
         <v>526</v>
       </c>
-      <c r="B244" s="1" t="s">
+      <c r="C244" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D244" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="E244" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F244" s="1" t="s">
         <v>527</v>
-      </c>
-      <c r="C244" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D244" s="1" t="s">
-        <v>516</v>
-      </c>
-      <c r="E244" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F244" s="1" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
@@ -7627,13 +7633,13 @@
         <v>3</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F245" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
@@ -7647,13 +7653,13 @@
         <v>3</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F246" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
@@ -7667,13 +7673,13 @@
         <v>3</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F247" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
@@ -7687,10 +7693,10 @@
         <v>3</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>536</v>
+        <v>518</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="F248" s="1" t="s">
         <v>28</v>
@@ -7698,19 +7704,19 @@
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="B249" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="B249" s="1" t="s">
+      <c r="C249" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D249" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="C249" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D249" s="1" t="s">
-        <v>536</v>
-      </c>
       <c r="E249" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F249" s="1" t="s">
         <v>28</v>
@@ -7727,10 +7733,10 @@
         <v>3</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="E250" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F250" s="1" t="s">
         <v>28</v>
@@ -7747,10 +7753,10 @@
         <v>3</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F251" s="1" t="s">
         <v>28</v>
@@ -7767,13 +7773,13 @@
         <v>3</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="E252" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F252" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
@@ -7787,13 +7793,13 @@
         <v>3</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F253" s="1" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
@@ -7807,10 +7813,10 @@
         <v>3</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F254" s="1" t="s">
         <v>23</v>
@@ -7827,10 +7833,10 @@
         <v>3</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F255" s="1" t="s">
         <v>23</v>
@@ -7847,30 +7853,30 @@
         <v>3</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>553</v>
+        <v>538</v>
       </c>
       <c r="E256" s="1" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="F256" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="B257" s="1" t="s">
         <v>554</v>
       </c>
-      <c r="B257" s="1" t="s">
+      <c r="C257" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D257" s="1" t="s">
         <v>555</v>
       </c>
-      <c r="C257" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D257" s="1" t="s">
-        <v>553</v>
-      </c>
       <c r="E257" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F257" s="1" t="s">
         <v>28</v>
@@ -7887,10 +7893,10 @@
         <v>3</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F258" s="1" t="s">
         <v>28</v>
@@ -7907,10 +7913,10 @@
         <v>3</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F259" s="1" t="s">
         <v>28</v>
@@ -7927,10 +7933,10 @@
         <v>3</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F260" s="1" t="s">
         <v>23</v>
@@ -7947,10 +7953,10 @@
         <v>3</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F261" s="1" t="s">
         <v>28</v>
@@ -7967,10 +7973,10 @@
         <v>3</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F262" s="1" t="s">
         <v>28</v>
@@ -7987,10 +7993,10 @@
         <v>3</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="E263" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F263" s="1" t="s">
         <v>28</v>
@@ -9307,10 +9313,10 @@
         <v>3</v>
       </c>
       <c r="D329" s="1" t="s">
-        <v>707</v>
+        <v>690</v>
       </c>
       <c r="E329" s="1" t="s">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="F329" s="1" t="s">
         <v>28</v>
@@ -9318,19 +9324,19 @@
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A330" s="1" t="s">
+        <v>707</v>
+      </c>
+      <c r="B330" s="1" t="s">
         <v>708</v>
       </c>
-      <c r="B330" s="1" t="s">
+      <c r="C330" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D330" s="1" t="s">
         <v>709</v>
       </c>
-      <c r="C330" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D330" s="1" t="s">
-        <v>707</v>
-      </c>
       <c r="E330" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F330" s="1" t="s">
         <v>28</v>
@@ -9347,13 +9353,13 @@
         <v>3</v>
       </c>
       <c r="D331" s="1" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="E331" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F331" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.25">
@@ -9367,10 +9373,10 @@
         <v>3</v>
       </c>
       <c r="D332" s="1" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="E332" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F332" s="1" t="s">
         <v>23</v>
@@ -9387,13 +9393,13 @@
         <v>3</v>
       </c>
       <c r="D333" s="1" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="E333" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F333" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.25">
@@ -9407,10 +9413,10 @@
         <v>3</v>
       </c>
       <c r="D334" s="1" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="E334" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F334" s="1" t="s">
         <v>28</v>
@@ -9427,10 +9433,10 @@
         <v>3</v>
       </c>
       <c r="D335" s="1" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="E335" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F335" s="1" t="s">
         <v>28</v>
@@ -9447,10 +9453,10 @@
         <v>3</v>
       </c>
       <c r="D336" s="1" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="E336" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F336" s="1" t="s">
         <v>28</v>
@@ -9467,10 +9473,10 @@
         <v>3</v>
       </c>
       <c r="D337" s="1" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="E337" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F337" s="1" t="s">
         <v>28</v>
@@ -9487,10 +9493,10 @@
         <v>3</v>
       </c>
       <c r="D338" s="1" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="E338" s="1" t="s">
-        <v>146</v>
+        <v>58</v>
       </c>
       <c r="F338" s="1" t="s">
         <v>28</v>
@@ -9507,33 +9513,33 @@
         <v>3</v>
       </c>
       <c r="D339" s="1" t="s">
-        <v>728</v>
+        <v>709</v>
       </c>
       <c r="E339" s="1" t="s">
-        <v>4</v>
+        <v>146</v>
       </c>
       <c r="F339" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A340" s="1" t="s">
+        <v>728</v>
+      </c>
+      <c r="B340" s="1" t="s">
         <v>729</v>
       </c>
-      <c r="B340" s="1" t="s">
+      <c r="C340" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D340" s="1" t="s">
         <v>730</v>
       </c>
-      <c r="C340" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D340" s="1" t="s">
-        <v>728</v>
-      </c>
       <c r="E340" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F340" s="1" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.25">
@@ -9547,13 +9553,13 @@
         <v>3</v>
       </c>
       <c r="D341" s="1" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="E341" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F341" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.25">
@@ -9567,13 +9573,13 @@
         <v>3</v>
       </c>
       <c r="D342" s="1" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="E342" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F342" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="343" spans="1:6" x14ac:dyDescent="0.25">
@@ -9587,13 +9593,13 @@
         <v>3</v>
       </c>
       <c r="D343" s="1" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="E343" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F343" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.25">
@@ -9607,10 +9613,10 @@
         <v>3</v>
       </c>
       <c r="D344" s="1" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="E344" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F344" s="1" t="s">
         <v>28</v>
@@ -9627,13 +9633,13 @@
         <v>3</v>
       </c>
       <c r="D345" s="1" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="E345" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F345" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.25">
@@ -9647,33 +9653,33 @@
         <v>3</v>
       </c>
       <c r="D346" s="1" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="E346" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F346" s="1" t="s">
-        <v>743</v>
+        <v>23</v>
       </c>
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A347" s="1" t="s">
+        <v>743</v>
+      </c>
+      <c r="B347" s="1" t="s">
         <v>744</v>
       </c>
-      <c r="B347" s="1" t="s">
+      <c r="C347" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D347" s="1" t="s">
+        <v>730</v>
+      </c>
+      <c r="E347" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F347" s="1" t="s">
         <v>745</v>
-      </c>
-      <c r="C347" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D347" s="1" t="s">
-        <v>728</v>
-      </c>
-      <c r="E347" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F347" s="1" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.25">
@@ -9687,30 +9693,30 @@
         <v>3</v>
       </c>
       <c r="D348" s="1" t="s">
-        <v>748</v>
+        <v>730</v>
       </c>
       <c r="E348" s="1" t="s">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="F348" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A349" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="B349" s="1" t="s">
         <v>749</v>
       </c>
-      <c r="B349" s="1" t="s">
+      <c r="C349" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D349" s="1" t="s">
         <v>750</v>
       </c>
-      <c r="C349" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D349" s="1" t="s">
-        <v>748</v>
-      </c>
       <c r="E349" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F349" s="1" t="s">
         <v>28</v>
@@ -9727,13 +9733,13 @@
         <v>3</v>
       </c>
       <c r="D350" s="1" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="E350" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F350" s="1" t="s">
-        <v>168</v>
+        <v>28</v>
       </c>
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.25">
@@ -9747,113 +9753,113 @@
         <v>3</v>
       </c>
       <c r="D351" s="1" t="s">
-        <v>755</v>
+        <v>750</v>
       </c>
       <c r="E351" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F351" s="1" t="s">
-        <v>28</v>
+        <v>168</v>
       </c>
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A352" s="1" t="s">
+        <v>755</v>
+      </c>
+      <c r="B352" s="1" t="s">
         <v>756</v>
       </c>
-      <c r="B352" s="1" t="s">
+      <c r="C352" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D352" s="1" t="s">
         <v>757</v>
-      </c>
-      <c r="C352" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D352" s="1" t="s">
-        <v>758</v>
       </c>
       <c r="E352" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F352" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="353" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A353" s="1" t="s">
+        <v>758</v>
+      </c>
+      <c r="B353" s="1" t="s">
         <v>759</v>
       </c>
-      <c r="B353" s="1" t="s">
+      <c r="C353" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D353" s="1" t="s">
         <v>760</v>
-      </c>
-      <c r="C353" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D353" s="1" t="s">
-        <v>761</v>
       </c>
       <c r="E353" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F353" s="1" t="s">
-        <v>762</v>
+        <v>33</v>
       </c>
     </row>
     <row r="354" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A354" s="1" t="s">
+        <v>761</v>
+      </c>
+      <c r="B354" s="1" t="s">
+        <v>762</v>
+      </c>
+      <c r="C354" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D354" s="1" t="s">
         <v>763</v>
       </c>
-      <c r="B354" s="1" t="s">
+      <c r="E354" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F354" s="1" t="s">
         <v>764</v>
-      </c>
-      <c r="C354" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D354" s="1" t="s">
-        <v>761</v>
-      </c>
-      <c r="E354" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F354" s="1" t="s">
-        <v>765</v>
       </c>
     </row>
     <row r="355" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A355" s="1" t="s">
+        <v>765</v>
+      </c>
+      <c r="B355" s="1" t="s">
         <v>766</v>
       </c>
-      <c r="B355" s="1" t="s">
+      <c r="C355" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D355" s="1" t="s">
+        <v>763</v>
+      </c>
+      <c r="E355" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F355" s="1" t="s">
         <v>767</v>
-      </c>
-      <c r="C355" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D355" s="1" t="s">
-        <v>761</v>
-      </c>
-      <c r="E355" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F355" s="1" t="s">
-        <v>768</v>
       </c>
     </row>
     <row r="356" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A356" s="1" t="s">
+        <v>768</v>
+      </c>
+      <c r="B356" s="1" t="s">
         <v>769</v>
       </c>
-      <c r="B356" s="1" t="s">
+      <c r="C356" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D356" s="1" t="s">
+        <v>763</v>
+      </c>
+      <c r="E356" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F356" s="1" t="s">
         <v>770</v>
-      </c>
-      <c r="C356" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D356" s="1" t="s">
-        <v>761</v>
-      </c>
-      <c r="E356" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F356" s="1" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="357" spans="1:6" x14ac:dyDescent="0.25">
@@ -9867,12 +9873,32 @@
         <v>3</v>
       </c>
       <c r="D357" s="1" t="s">
+        <v>763</v>
+      </c>
+      <c r="E357" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F357" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="358" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A358" s="1" t="s">
         <v>773</v>
       </c>
-      <c r="E357" s="1" t="s">
+      <c r="B358" s="1" t="s">
+        <v>774</v>
+      </c>
+      <c r="C358" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D358" s="1" t="s">
+        <v>775</v>
+      </c>
+      <c r="E358" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F357" s="1" t="s">
+      <c r="F358" s="1" t="s">
         <v>28</v>
       </c>
     </row>

--- a/CLB07N.xlsx
+++ b/CLB07N.xlsx
@@ -121,6 +121,9 @@
     <t>AMO DRMY STRAW 200ML</t>
   </si>
   <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
     <t>20138894</t>
   </si>
   <si>
@@ -517,9 +520,6 @@
     <t>11</t>
   </si>
   <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
     <t>20139578</t>
   </si>
   <si>
@@ -1180,7 +1180,7 @@
     <t>20136277</t>
   </si>
   <si>
-    <t>SNPRD FRT MG.PINE220</t>
+    <t>SNPRD FRT P/MANGO220</t>
   </si>
   <si>
     <t>24</t>
@@ -2999,15 +2999,15 @@
         <v>20</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
@@ -3016,18 +3016,18 @@
         <v>8</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
@@ -3044,10 +3044,10 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
@@ -3064,10 +3064,10 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
@@ -3084,10 +3084,10 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
@@ -3104,10 +3104,10 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
@@ -3124,10 +3124,10 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
@@ -3144,10 +3144,10 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
@@ -3156,7 +3156,7 @@
         <v>11</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>5</v>
@@ -3164,10 +3164,10 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
@@ -3176,7 +3176,7 @@
         <v>11</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>5</v>
@@ -3184,10 +3184,10 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
@@ -3196,7 +3196,7 @@
         <v>11</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>5</v>
@@ -3204,10 +3204,10 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
@@ -3224,10 +3224,10 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
@@ -3244,10 +3244,10 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
@@ -3264,10 +3264,10 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
@@ -3284,10 +3284,10 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
@@ -3304,10 +3304,10 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
@@ -3324,10 +3324,10 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
@@ -3344,10 +3344,10 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
@@ -3364,10 +3364,10 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
@@ -3384,10 +3384,10 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
@@ -3404,10 +3404,10 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>3</v>
@@ -3419,15 +3419,15 @@
         <v>17</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>3</v>
@@ -3439,15 +3439,15 @@
         <v>20</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
@@ -3456,18 +3456,18 @@
         <v>17</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
@@ -3476,18 +3476,18 @@
         <v>17</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
@@ -3504,10 +3504,10 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>3</v>
@@ -3524,10 +3524,10 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
@@ -3544,10 +3544,10 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
@@ -3564,10 +3564,10 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
@@ -3584,10 +3584,10 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
@@ -3599,15 +3599,15 @@
         <v>20</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
@@ -3616,18 +3616,18 @@
         <v>20</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
@@ -3636,24 +3636,24 @@
         <v>20</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>4</v>
@@ -3664,16 +3664,16 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>8</v>
@@ -3684,16 +3684,16 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>11</v>
@@ -3704,16 +3704,16 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>14</v>
@@ -3724,16 +3724,16 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>17</v>
@@ -3744,16 +3744,16 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>20</v>
@@ -3764,19 +3764,19 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>23</v>
@@ -3784,16 +3784,16 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>4</v>
@@ -3804,16 +3804,16 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>8</v>
@@ -3824,56 +3824,56 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>17</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>4</v>
@@ -3884,16 +3884,16 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>8</v>
@@ -3904,16 +3904,16 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>11</v>
@@ -3924,16 +3924,16 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>14</v>
@@ -3944,16 +3944,16 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>17</v>
@@ -3964,16 +3964,16 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>20</v>
@@ -3984,19 +3984,19 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>28</v>
@@ -4004,19 +4004,19 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>28</v>
@@ -4024,19 +4024,19 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>28</v>
@@ -4044,19 +4044,19 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>28</v>
@@ -4064,16 +4064,16 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D67" s="1" t="s">
         <v>147</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>146</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>4</v>
@@ -4084,16 +4084,16 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>8</v>
@@ -4104,16 +4104,16 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>11</v>
@@ -4124,16 +4124,16 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>14</v>
@@ -4144,16 +4144,16 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>17</v>
@@ -4164,16 +4164,16 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>20</v>
@@ -4184,19 +4184,19 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>23</v>
@@ -4204,19 +4204,19 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>28</v>
@@ -4224,19 +4224,19 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>28</v>
@@ -4244,22 +4244,22 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>168</v>
+        <v>36</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -4273,13 +4273,13 @@
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>168</v>
+        <v>36</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -4293,13 +4293,13 @@
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>168</v>
+        <v>36</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -4313,7 +4313,7 @@
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>14</v>
@@ -4333,7 +4333,7 @@
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>17</v>
@@ -4353,7 +4353,7 @@
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>20</v>
@@ -4373,10 +4373,10 @@
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>28</v>
@@ -4516,7 +4516,7 @@
         <v>183</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>23</v>
@@ -4536,7 +4536,7 @@
         <v>183</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>23</v>
@@ -4556,7 +4556,7 @@
         <v>183</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>28</v>
@@ -4576,7 +4576,7 @@
         <v>183</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>28</v>
@@ -4639,7 +4639,7 @@
         <v>11</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -4716,7 +4716,7 @@
         <v>204</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>28</v>
@@ -4736,7 +4736,7 @@
         <v>204</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>28</v>
@@ -4756,7 +4756,7 @@
         <v>204</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>5</v>
@@ -4776,7 +4776,7 @@
         <v>204</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>5</v>
@@ -4916,7 +4916,7 @@
         <v>225</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>28</v>
@@ -4936,7 +4936,7 @@
         <v>225</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>28</v>
@@ -4959,7 +4959,7 @@
         <v>4</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>168</v>
+        <v>36</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -4979,7 +4979,7 @@
         <v>8</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>168</v>
+        <v>36</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
@@ -4999,7 +4999,7 @@
         <v>11</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>168</v>
+        <v>36</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
@@ -5076,7 +5076,7 @@
         <v>242</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>28</v>
@@ -5096,7 +5096,7 @@
         <v>242</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>28</v>
@@ -5116,7 +5116,7 @@
         <v>242</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>28</v>
@@ -5256,7 +5256,7 @@
         <v>261</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>28</v>
@@ -5276,7 +5276,7 @@
         <v>261</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>28</v>
@@ -5296,7 +5296,7 @@
         <v>261</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>278</v>
@@ -5516,7 +5516,7 @@
         <v>290</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>28</v>
@@ -5656,7 +5656,7 @@
         <v>305</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>33</v>
@@ -5676,7 +5676,7 @@
         <v>305</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>33</v>
@@ -5816,7 +5816,7 @@
         <v>322</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>28</v>
@@ -5836,7 +5836,7 @@
         <v>322</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>23</v>
@@ -5976,7 +5976,7 @@
         <v>339</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>23</v>
@@ -5996,7 +5996,7 @@
         <v>339</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F163" s="1" t="s">
         <v>28</v>
@@ -6016,7 +6016,7 @@
         <v>339</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>28</v>
@@ -6156,7 +6156,7 @@
         <v>358</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>28</v>
@@ -6176,7 +6176,7 @@
         <v>358</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>28</v>
@@ -6316,7 +6316,7 @@
         <v>375</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>28</v>
@@ -6456,7 +6456,7 @@
         <v>390</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F186" s="1" t="s">
         <v>33</v>
@@ -6476,7 +6476,7 @@
         <v>390</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F187" s="1" t="s">
         <v>33</v>
@@ -6559,7 +6559,7 @@
         <v>14</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
@@ -6616,7 +6616,7 @@
         <v>408</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F194" s="1" t="s">
         <v>23</v>
@@ -6636,7 +6636,7 @@
         <v>408</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>28</v>
@@ -6656,7 +6656,7 @@
         <v>408</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F196" s="1" t="s">
         <v>28</v>
@@ -6796,7 +6796,7 @@
         <v>427</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F203" s="1" t="s">
         <v>28</v>
@@ -6816,7 +6816,7 @@
         <v>427</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F204" s="1" t="s">
         <v>28</v>
@@ -6836,7 +6836,7 @@
         <v>427</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F205" s="1" t="s">
         <v>28</v>
@@ -6856,7 +6856,7 @@
         <v>427</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F206" s="1" t="s">
         <v>28</v>
@@ -6996,7 +6996,7 @@
         <v>448</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F213" s="1" t="s">
         <v>28</v>
@@ -7016,7 +7016,7 @@
         <v>448</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F214" s="1" t="s">
         <v>28</v>
@@ -7036,10 +7036,10 @@
         <v>448</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F215" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
@@ -7176,7 +7176,7 @@
         <v>467</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F222" s="1" t="s">
         <v>28</v>
@@ -7196,7 +7196,7 @@
         <v>467</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F223" s="1" t="s">
         <v>33</v>
@@ -7216,7 +7216,7 @@
         <v>467</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F224" s="1" t="s">
         <v>28</v>
@@ -7356,10 +7356,10 @@
         <v>486</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F231" s="1" t="s">
-        <v>168</v>
+        <v>36</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
@@ -7376,10 +7376,10 @@
         <v>486</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F232" s="1" t="s">
-        <v>168</v>
+        <v>36</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
@@ -7516,7 +7516,7 @@
         <v>503</v>
       </c>
       <c r="E239" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F239" s="1" t="s">
         <v>28</v>
@@ -7599,7 +7599,7 @@
         <v>14</v>
       </c>
       <c r="F243" s="1" t="s">
-        <v>168</v>
+        <v>36</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
@@ -7656,7 +7656,7 @@
         <v>518</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F246" s="1" t="s">
         <v>28</v>
@@ -7676,7 +7676,7 @@
         <v>518</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F247" s="1" t="s">
         <v>33</v>
@@ -7696,7 +7696,7 @@
         <v>518</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F248" s="1" t="s">
         <v>28</v>
@@ -7836,7 +7836,7 @@
         <v>538</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F255" s="1" t="s">
         <v>23</v>
@@ -7856,7 +7856,7 @@
         <v>538</v>
       </c>
       <c r="E256" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F256" s="1" t="s">
         <v>23</v>
@@ -7996,7 +7996,7 @@
         <v>555</v>
       </c>
       <c r="E263" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F263" s="1" t="s">
         <v>28</v>
@@ -8136,7 +8136,7 @@
         <v>570</v>
       </c>
       <c r="E270" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F270" s="1" t="s">
         <v>28</v>
@@ -8156,7 +8156,7 @@
         <v>570</v>
       </c>
       <c r="E271" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F271" s="1" t="s">
         <v>28</v>
@@ -8176,7 +8176,7 @@
         <v>570</v>
       </c>
       <c r="E272" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F272" s="1" t="s">
         <v>28</v>
@@ -8296,7 +8296,7 @@
         <v>588</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F278" s="1" t="s">
         <v>28</v>
@@ -8316,7 +8316,7 @@
         <v>588</v>
       </c>
       <c r="E279" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F279" s="1" t="s">
         <v>28</v>
@@ -8336,7 +8336,7 @@
         <v>588</v>
       </c>
       <c r="E280" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F280" s="1" t="s">
         <v>28</v>
@@ -8356,7 +8356,7 @@
         <v>588</v>
       </c>
       <c r="E281" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F281" s="1" t="s">
         <v>28</v>
@@ -8376,7 +8376,7 @@
         <v>588</v>
       </c>
       <c r="E282" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F282" s="1" t="s">
         <v>28</v>
@@ -8516,7 +8516,7 @@
         <v>609</v>
       </c>
       <c r="E289" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F289" s="1" t="s">
         <v>622</v>
@@ -8536,7 +8536,7 @@
         <v>609</v>
       </c>
       <c r="E290" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F290" s="1" t="s">
         <v>28</v>
@@ -8556,7 +8556,7 @@
         <v>609</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F291" s="1" t="s">
         <v>28</v>
@@ -8576,7 +8576,7 @@
         <v>609</v>
       </c>
       <c r="E292" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F292" s="1" t="s">
         <v>28</v>
@@ -8716,7 +8716,7 @@
         <v>631</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F299" s="1" t="s">
         <v>622</v>
@@ -8736,7 +8736,7 @@
         <v>631</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F300" s="1" t="s">
         <v>622</v>
@@ -8756,7 +8756,7 @@
         <v>631</v>
       </c>
       <c r="E301" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F301" s="1" t="s">
         <v>622</v>
@@ -8896,7 +8896,7 @@
         <v>650</v>
       </c>
       <c r="E308" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F308" s="1" t="s">
         <v>28</v>
@@ -8916,7 +8916,7 @@
         <v>650</v>
       </c>
       <c r="E309" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F309" s="1" t="s">
         <v>28</v>
@@ -8936,7 +8936,7 @@
         <v>650</v>
       </c>
       <c r="E310" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F310" s="1" t="s">
         <v>28</v>
@@ -8956,7 +8956,7 @@
         <v>650</v>
       </c>
       <c r="E311" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F311" s="1" t="s">
         <v>28</v>
@@ -9096,7 +9096,7 @@
         <v>671</v>
       </c>
       <c r="E318" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F318" s="1" t="s">
         <v>28</v>
@@ -9116,7 +9116,7 @@
         <v>671</v>
       </c>
       <c r="E319" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F319" s="1" t="s">
         <v>28</v>
@@ -9136,7 +9136,7 @@
         <v>671</v>
       </c>
       <c r="E320" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F320" s="1" t="s">
         <v>28</v>
@@ -9276,7 +9276,7 @@
         <v>690</v>
       </c>
       <c r="E327" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F327" s="1" t="s">
         <v>28</v>
@@ -9296,7 +9296,7 @@
         <v>690</v>
       </c>
       <c r="E328" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F328" s="1" t="s">
         <v>28</v>
@@ -9316,7 +9316,7 @@
         <v>690</v>
       </c>
       <c r="E329" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F329" s="1" t="s">
         <v>28</v>
@@ -9456,7 +9456,7 @@
         <v>709</v>
       </c>
       <c r="E336" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F336" s="1" t="s">
         <v>28</v>
@@ -9476,7 +9476,7 @@
         <v>709</v>
       </c>
       <c r="E337" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F337" s="1" t="s">
         <v>28</v>
@@ -9496,7 +9496,7 @@
         <v>709</v>
       </c>
       <c r="E338" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F338" s="1" t="s">
         <v>28</v>
@@ -9516,7 +9516,7 @@
         <v>709</v>
       </c>
       <c r="E339" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F339" s="1" t="s">
         <v>28</v>
@@ -9656,7 +9656,7 @@
         <v>730</v>
       </c>
       <c r="E346" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F346" s="1" t="s">
         <v>23</v>
@@ -9676,7 +9676,7 @@
         <v>730</v>
       </c>
       <c r="E347" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F347" s="1" t="s">
         <v>745</v>
@@ -9696,7 +9696,7 @@
         <v>730</v>
       </c>
       <c r="E348" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F348" s="1" t="s">
         <v>33</v>
@@ -9759,7 +9759,7 @@
         <v>11</v>
       </c>
       <c r="F351" s="1" t="s">
-        <v>168</v>
+        <v>36</v>
       </c>
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.25">
